--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -229,18 +229,18 @@
     <author>STORM</author>
   </authors>
   <commentList>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>Retrieval 미사용과 target: 16 양쪽에 유효한 점수가 있는 공통 시드만 사용합니다. 각 시드에 여러 결과가 있으면 첫 번째 점수를 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: Retrieval 미사용의 공통 시드 평균 − STORM 논문 점수.
 target: 16 행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: (Retrieval 미사용 평균 − STORM 논문 점수) / (Human − Random).
 target: 16 행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
@@ -250,91 +250,105 @@
     <comment ref="Q19" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="Q20" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="E49" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="O52" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R52" authorId="0" shapeId="0">
+    <comment ref="T52" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="O53" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R53" authorId="0" shapeId="0">
+    <comment ref="T53" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I65" authorId="0" shapeId="0">
+    <comment ref="O54" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I66" authorId="0" shapeId="0">
+    <comment ref="T54" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="I67" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM-1/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I68" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I69" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
@@ -631,15 +645,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V95"/>
+  <dimension ref="A1:X97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
     <col width="41.1" customWidth="1" min="2" max="2"/>
-    <col width="3" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
-    <col width="46" customWidth="1" min="21" max="21"/>
-    <col width="32" customWidth="1" min="22" max="22"/>
+    <col width="3" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="46" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -703,24 +717,30 @@
         <v>6020</v>
       </c>
       <c r="R1" s="1" t="n">
+        <v>6030</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>9998</v>
+      </c>
+      <c r="T1" s="1" t="n">
         <v>9999</v>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>   </t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -756,11 +776,13 @@
       <c r="Q2" s="4" t="inlineStr"/>
       <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="6" t="n">
+      <c r="T2" s="4" t="inlineStr"/>
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr"/>
+      <c r="W2" s="6" t="n">
         <v>57.79999999999995</v>
       </c>
-      <c r="V2" s="7" t="n">
+      <c r="X2" s="7" t="n">
         <v>0.008376932999028966</v>
       </c>
     </row>
@@ -812,11 +834,13 @@
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
       <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="9" t="n">
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="8" t="inlineStr"/>
+      <c r="V3" s="9" t="n">
         <v>1041.8</v>
       </c>
-      <c r="U3" s="10" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr"/>
+      <c r="W3" s="10" t="inlineStr"/>
+      <c r="X3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -858,9 +882,11 @@
       <c r="Q4" s="8" t="inlineStr"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="9" t="inlineStr"/>
-      <c r="U4" s="10" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="8" t="inlineStr"/>
+      <c r="V4" s="9" t="inlineStr"/>
+      <c r="W4" s="10" t="inlineStr"/>
+      <c r="X4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -906,13 +932,15 @@
       <c r="Q5" s="8" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="8" t="inlineStr"/>
+      <c r="U5" s="8" t="inlineStr"/>
+      <c r="V5" s="9" t="n">
         <v>1091.1</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="W5" s="9" t="n">
         <v>49.29999999999995</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="X5" s="11" t="n">
         <v>0.007145031087407058</v>
       </c>
     </row>
@@ -946,11 +974,13 @@
       <c r="Q6" s="4" t="inlineStr"/>
       <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="6" t="n">
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="6" t="n">
         <v>2.849999999999994</v>
       </c>
-      <c r="V6" s="7" t="n">
+      <c r="X6" s="7" t="n">
         <v>0.001663068214973446</v>
       </c>
     </row>
@@ -1002,11 +1032,13 @@
       </c>
       <c r="R7" s="8" t="inlineStr"/>
       <c r="S7" s="8" t="inlineStr"/>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="8" t="inlineStr"/>
+      <c r="U7" s="8" t="inlineStr"/>
+      <c r="V7" s="9" t="n">
         <v>207.85</v>
       </c>
-      <c r="U7" s="10" t="inlineStr"/>
-      <c r="V7" s="11" t="inlineStr"/>
+      <c r="W7" s="10" t="inlineStr"/>
+      <c r="X7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="1" t="n"/>
@@ -1048,9 +1080,11 @@
       </c>
       <c r="R8" s="8" t="inlineStr"/>
       <c r="S8" s="8" t="inlineStr"/>
-      <c r="T8" s="9" t="inlineStr"/>
-      <c r="U8" s="10" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
+      <c r="T8" s="8" t="inlineStr"/>
+      <c r="U8" s="8" t="inlineStr"/>
+      <c r="V8" s="9" t="inlineStr"/>
+      <c r="W8" s="10" t="inlineStr"/>
+      <c r="X8" s="11" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="1" t="n"/>
@@ -1096,13 +1130,15 @@
       </c>
       <c r="R9" s="8" t="inlineStr"/>
       <c r="S9" s="8" t="inlineStr"/>
-      <c r="T9" s="9" t="n">
+      <c r="T9" s="8" t="inlineStr"/>
+      <c r="U9" s="8" t="inlineStr"/>
+      <c r="V9" s="9" t="n">
         <v>164.88</v>
       </c>
-      <c r="U9" s="9" t="n">
+      <c r="W9" s="9" t="n">
         <v>42.96999999999997</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="X9" s="11" t="n">
         <v>-0.02507440042014353</v>
       </c>
     </row>
@@ -1136,12 +1172,14 @@
       <c r="Q10" s="4" t="inlineStr"/>
       <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="6" t="n">
-        <v>-36.5625</v>
-      </c>
-      <c r="V10" s="7" t="n">
-        <v>-0.07036662817551963</v>
+      <c r="T10" s="4" t="inlineStr"/>
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr"/>
+      <c r="W10" s="6" t="n">
+        <v>-22.95000000000005</v>
+      </c>
+      <c r="X10" s="7" t="n">
+        <v>-0.04416859122401856</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
@@ -1192,11 +1230,13 @@
       <c r="Q11" s="8" t="inlineStr"/>
       <c r="R11" s="8" t="inlineStr"/>
       <c r="S11" s="8" t="inlineStr"/>
-      <c r="T11" s="9" t="n">
-        <v>764.4375</v>
-      </c>
-      <c r="U11" s="10" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
+      <c r="T11" s="8" t="inlineStr"/>
+      <c r="U11" s="8" t="inlineStr"/>
+      <c r="V11" s="9" t="n">
+        <v>778.05</v>
+      </c>
+      <c r="W11" s="10" t="inlineStr"/>
+      <c r="X11" s="11" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="1" t="n"/>
@@ -1238,9 +1278,11 @@
       <c r="Q12" s="8" t="inlineStr"/>
       <c r="R12" s="8" t="inlineStr"/>
       <c r="S12" s="8" t="inlineStr"/>
-      <c r="T12" s="9" t="inlineStr"/>
-      <c r="U12" s="10" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
+      <c r="T12" s="8" t="inlineStr"/>
+      <c r="U12" s="8" t="inlineStr"/>
+      <c r="V12" s="9" t="inlineStr"/>
+      <c r="W12" s="10" t="inlineStr"/>
+      <c r="X12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -1290,18 +1332,24 @@
           <t>724.80</t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr"/>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>723.85</t>
+        </is>
+      </c>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
       <c r="S13" s="8" t="inlineStr"/>
-      <c r="T13" s="9" t="n">
-        <v>700.9625000000001</v>
-      </c>
-      <c r="U13" s="9" t="n">
-        <v>63.47499999999991</v>
-      </c>
-      <c r="V13" s="11" t="n">
-        <v>-0.1221612779060814</v>
+      <c r="T13" s="8" t="inlineStr"/>
+      <c r="U13" s="8" t="inlineStr"/>
+      <c r="V13" s="9" t="n">
+        <v>705.5400000000001</v>
+      </c>
+      <c r="W13" s="9" t="n">
+        <v>72.50999999999988</v>
+      </c>
+      <c r="X13" s="11" t="n">
+        <v>-0.1395496535796764</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
@@ -1334,11 +1382,13 @@
       <c r="Q14" s="4" t="inlineStr"/>
       <c r="R14" s="4" t="inlineStr"/>
       <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="6" t="n">
+      <c r="T14" s="4" t="inlineStr"/>
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr"/>
+      <c r="W14" s="6" t="n">
         <v>-350.5</v>
       </c>
-      <c r="V14" s="7" t="n">
+      <c r="X14" s="7" t="n">
         <v>-0.04226303160382478</v>
       </c>
     </row>
@@ -1386,11 +1436,13 @@
       <c r="Q15" s="8" t="inlineStr"/>
       <c r="R15" s="8" t="inlineStr"/>
       <c r="S15" s="8" t="inlineStr"/>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="8" t="inlineStr"/>
+      <c r="U15" s="8" t="inlineStr"/>
+      <c r="V15" s="9" t="n">
         <v>677.5</v>
       </c>
-      <c r="U15" s="10" t="inlineStr"/>
-      <c r="V15" s="11" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr"/>
+      <c r="X15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -1428,9 +1480,11 @@
       <c r="Q16" s="8" t="inlineStr"/>
       <c r="R16" s="8" t="inlineStr"/>
       <c r="S16" s="8" t="inlineStr"/>
-      <c r="T16" s="9" t="inlineStr"/>
-      <c r="U16" s="10" t="inlineStr"/>
-      <c r="V16" s="11" t="inlineStr"/>
+      <c r="T16" s="8" t="inlineStr"/>
+      <c r="U16" s="8" t="inlineStr"/>
+      <c r="V16" s="9" t="inlineStr"/>
+      <c r="W16" s="10" t="inlineStr"/>
+      <c r="X16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -1472,13 +1526,15 @@
       <c r="Q17" s="8" t="inlineStr"/>
       <c r="R17" s="8" t="inlineStr"/>
       <c r="S17" s="8" t="inlineStr"/>
-      <c r="T17" s="9" t="n">
+      <c r="T17" s="8" t="inlineStr"/>
+      <c r="U17" s="8" t="inlineStr"/>
+      <c r="V17" s="9" t="n">
         <v>759.375</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="W17" s="9" t="n">
         <v>81.875</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="X17" s="11" t="n">
         <v>0.009872427139980468</v>
       </c>
     </row>
@@ -1512,11 +1568,13 @@
       <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="6" t="n">
+      <c r="T18" s="4" t="inlineStr"/>
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr"/>
+      <c r="W18" s="6" t="n">
         <v>-89.125</v>
       </c>
-      <c r="V18" s="7" t="n">
+      <c r="X18" s="7" t="n">
         <v>-0.120618486940046</v>
       </c>
     </row>
@@ -1566,17 +1624,19 @@
           <t>677.00</t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="R19" s="8" t="inlineStr"/>
+      <c r="S19" s="8" t="inlineStr"/>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>668.50</t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr"/>
-      <c r="T19" s="9" t="n">
+      <c r="U19" s="8" t="inlineStr"/>
+      <c r="V19" s="9" t="n">
         <v>551.875</v>
       </c>
-      <c r="U19" s="10" t="inlineStr"/>
-      <c r="V19" s="11" t="inlineStr"/>
+      <c r="W19" s="10" t="inlineStr"/>
+      <c r="X19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="1" t="n"/>
@@ -1600,15 +1660,17 @@
       <c r="O20" s="8" t="inlineStr"/>
       <c r="P20" s="8" t="inlineStr"/>
       <c r="Q20" s="12" t="inlineStr"/>
-      <c r="R20" s="8" t="inlineStr">
+      <c r="R20" s="8" t="inlineStr"/>
+      <c r="S20" s="8" t="inlineStr"/>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>507.50</t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr"/>
-      <c r="T20" s="9" t="inlineStr"/>
-      <c r="U20" s="10" t="inlineStr"/>
-      <c r="V20" s="11" t="inlineStr"/>
+      <c r="U20" s="8" t="inlineStr"/>
+      <c r="V20" s="9" t="inlineStr"/>
+      <c r="W20" s="10" t="inlineStr"/>
+      <c r="X20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="1" t="n"/>
@@ -1644,19 +1706,21 @@
           <t>114.00</t>
         </is>
       </c>
-      <c r="R21" s="8" t="inlineStr">
+      <c r="R21" s="8" t="inlineStr"/>
+      <c r="S21" s="8" t="inlineStr"/>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>565.00</t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr"/>
-      <c r="T21" s="9" t="n">
+      <c r="U21" s="8" t="inlineStr"/>
+      <c r="V21" s="9" t="n">
         <v>370.5</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="W21" s="9" t="n">
         <v>181.375</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="X21" s="11" t="n">
         <v>-0.2454662335904723</v>
       </c>
     </row>
@@ -1690,11 +1754,13 @@
       <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr"/>
       <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="6" t="n">
+      <c r="T22" s="4" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr"/>
+      <c r="W22" s="6" t="n">
         <v>-2965</v>
       </c>
-      <c r="V22" s="7" t="n">
+      <c r="X22" s="7" t="n">
         <v>-0.08513387409374776</v>
       </c>
     </row>
@@ -1746,11 +1812,13 @@
       </c>
       <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="8" t="inlineStr"/>
-      <c r="T23" s="9" t="n">
+      <c r="T23" s="8" t="inlineStr"/>
+      <c r="U23" s="8" t="inlineStr"/>
+      <c r="V23" s="9" t="n">
         <v>10575</v>
       </c>
-      <c r="U23" s="10" t="inlineStr"/>
-      <c r="V23" s="11" t="inlineStr"/>
+      <c r="W23" s="10" t="inlineStr"/>
+      <c r="X23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="1" t="n"/>
@@ -1796,9 +1864,11 @@
       </c>
       <c r="R24" s="8" t="inlineStr"/>
       <c r="S24" s="8" t="inlineStr"/>
-      <c r="T24" s="9" t="inlineStr"/>
-      <c r="U24" s="10" t="inlineStr"/>
-      <c r="V24" s="11" t="inlineStr"/>
+      <c r="T24" s="8" t="inlineStr"/>
+      <c r="U24" s="8" t="inlineStr"/>
+      <c r="V24" s="9" t="inlineStr"/>
+      <c r="W24" s="10" t="inlineStr"/>
+      <c r="X24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -1848,13 +1918,15 @@
       </c>
       <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="8" t="inlineStr"/>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="8" t="inlineStr"/>
+      <c r="U25" s="8" t="inlineStr"/>
+      <c r="V25" s="9" t="n">
         <v>10608.33333333333</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="W25" s="9" t="n">
         <v>33.33333333333394</v>
       </c>
-      <c r="V25" s="11" t="n">
+      <c r="X25" s="11" t="n">
         <v>0.0009570980786256245</v>
       </c>
     </row>
@@ -1888,11 +1960,13 @@
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="6" t="n">
+      <c r="T26" s="4" t="inlineStr"/>
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr"/>
+      <c r="W26" s="6" t="n">
         <v>-5.549999999999997</v>
       </c>
-      <c r="V26" s="7" t="n">
+      <c r="X26" s="7" t="n">
         <v>-0.4624999999999997</v>
       </c>
     </row>
@@ -1941,14 +2015,20 @@
           <t>77.80</t>
         </is>
       </c>
-      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="Q27" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="R27" s="8" t="inlineStr"/>
       <c r="S27" s="8" t="inlineStr"/>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="8" t="inlineStr"/>
+      <c r="U27" s="8" t="inlineStr"/>
+      <c r="V27" s="9" t="n">
         <v>74.45</v>
       </c>
-      <c r="U27" s="10" t="inlineStr"/>
-      <c r="V27" s="11" t="inlineStr"/>
+      <c r="W27" s="10" t="inlineStr"/>
+      <c r="X27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -1978,9 +2058,11 @@
       <c r="Q28" s="8" t="inlineStr"/>
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr"/>
-      <c r="T28" s="9" t="inlineStr"/>
-      <c r="U28" s="10" t="inlineStr"/>
-      <c r="V28" s="11" t="inlineStr"/>
+      <c r="T28" s="8" t="inlineStr"/>
+      <c r="U28" s="8" t="inlineStr"/>
+      <c r="V28" s="9" t="inlineStr"/>
+      <c r="W28" s="10" t="inlineStr"/>
+      <c r="X28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -2019,16 +2101,22 @@
           <t>85.05</t>
         </is>
       </c>
-      <c r="Q29" s="8" t="inlineStr"/>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>87.90</t>
+        </is>
+      </c>
       <c r="R29" s="8" t="inlineStr"/>
       <c r="S29" s="8" t="inlineStr"/>
-      <c r="T29" s="9" t="n">
+      <c r="T29" s="8" t="inlineStr"/>
+      <c r="U29" s="8" t="inlineStr"/>
+      <c r="V29" s="9" t="n">
         <v>72.71250000000001</v>
       </c>
-      <c r="U29" s="9" t="n">
+      <c r="W29" s="9" t="n">
         <v>1.737499999999997</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="X29" s="11" t="n">
         <v>-0.1447916666666664</v>
       </c>
     </row>
@@ -2062,11 +2150,13 @@
       <c r="Q30" s="4" t="inlineStr"/>
       <c r="R30" s="4" t="inlineStr"/>
       <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="6" t="n">
+      <c r="T30" s="4" t="inlineStr"/>
+      <c r="U30" s="4" t="inlineStr"/>
+      <c r="V30" s="5" t="inlineStr"/>
+      <c r="W30" s="6" t="n">
         <v>-4.266666666666666</v>
       </c>
-      <c r="V30" s="7" t="n">
+      <c r="X30" s="7" t="n">
         <v>-0.1481481481481481</v>
       </c>
     </row>
@@ -2114,11 +2204,13 @@
       <c r="Q31" s="8" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr"/>
       <c r="S31" s="8" t="inlineStr"/>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="8" t="inlineStr"/>
+      <c r="U31" s="8" t="inlineStr"/>
+      <c r="V31" s="9" t="n">
         <v>11.73333333333333</v>
       </c>
-      <c r="U31" s="10" t="inlineStr"/>
-      <c r="V31" s="11" t="inlineStr"/>
+      <c r="W31" s="10" t="inlineStr"/>
+      <c r="X31" s="11" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="1" t="n"/>
@@ -2141,7 +2233,11 @@
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="J32" s="8" t="inlineStr"/>
       <c r="K32" s="8" t="inlineStr"/>
       <c r="L32" s="8" t="inlineStr"/>
@@ -2152,9 +2248,11 @@
       <c r="Q32" s="8" t="inlineStr"/>
       <c r="R32" s="8" t="inlineStr"/>
       <c r="S32" s="8" t="inlineStr"/>
-      <c r="T32" s="9" t="inlineStr"/>
-      <c r="U32" s="10" t="inlineStr"/>
-      <c r="V32" s="11" t="inlineStr"/>
+      <c r="T32" s="8" t="inlineStr"/>
+      <c r="U32" s="8" t="inlineStr"/>
+      <c r="V32" s="9" t="inlineStr"/>
+      <c r="W32" s="10" t="inlineStr"/>
+      <c r="X32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="1" t="n"/>
@@ -2192,13 +2290,15 @@
       <c r="Q33" s="8" t="inlineStr"/>
       <c r="R33" s="8" t="inlineStr"/>
       <c r="S33" s="8" t="inlineStr"/>
-      <c r="T33" s="9" t="n">
+      <c r="T33" s="8" t="inlineStr"/>
+      <c r="U33" s="8" t="inlineStr"/>
+      <c r="V33" s="9" t="n">
         <v>12.36666666666667</v>
       </c>
-      <c r="U33" s="9" t="n">
+      <c r="W33" s="9" t="n">
         <v>0.6333333333333311</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="X33" s="11" t="n">
         <v>0.02199074074074066</v>
       </c>
     </row>
@@ -2232,11 +2332,13 @@
       <c r="Q34" s="4" t="inlineStr"/>
       <c r="R34" s="4" t="inlineStr"/>
       <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="6" t="n">
+      <c r="T34" s="4" t="inlineStr"/>
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr"/>
+      <c r="W34" s="6" t="n">
         <v>-289.6666666666667</v>
       </c>
-      <c r="V34" s="7" t="n">
+      <c r="X34" s="7" t="n">
         <v>-0.04404370920001623</v>
       </c>
     </row>
@@ -2284,11 +2386,13 @@
       <c r="Q35" s="8" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr"/>
-      <c r="T35" s="9" t="n">
+      <c r="T35" s="8" t="inlineStr"/>
+      <c r="U35" s="8" t="inlineStr"/>
+      <c r="V35" s="9" t="n">
         <v>1598.333333333333</v>
       </c>
-      <c r="U35" s="10" t="inlineStr"/>
-      <c r="V35" s="11" t="inlineStr"/>
+      <c r="W35" s="10" t="inlineStr"/>
+      <c r="X35" s="11" t="inlineStr"/>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="1" t="n"/>
@@ -2318,9 +2422,11 @@
       <c r="Q36" s="8" t="inlineStr"/>
       <c r="R36" s="8" t="inlineStr"/>
       <c r="S36" s="8" t="inlineStr"/>
-      <c r="T36" s="9" t="inlineStr"/>
-      <c r="U36" s="10" t="inlineStr"/>
-      <c r="V36" s="11" t="inlineStr"/>
+      <c r="T36" s="8" t="inlineStr"/>
+      <c r="U36" s="8" t="inlineStr"/>
+      <c r="V36" s="9" t="inlineStr"/>
+      <c r="W36" s="10" t="inlineStr"/>
+      <c r="X36" s="11" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="1" t="n"/>
@@ -2358,13 +2464,15 @@
       <c r="Q37" s="8" t="inlineStr"/>
       <c r="R37" s="8" t="inlineStr"/>
       <c r="S37" s="8" t="inlineStr"/>
-      <c r="T37" s="9" t="n">
+      <c r="T37" s="8" t="inlineStr"/>
+      <c r="U37" s="8" t="inlineStr"/>
+      <c r="V37" s="9" t="n">
         <v>1225</v>
       </c>
-      <c r="U37" s="9" t="n">
+      <c r="W37" s="9" t="n">
         <v>373.3333333333333</v>
       </c>
-      <c r="V37" s="11" t="n">
+      <c r="X37" s="11" t="n">
         <v>-0.05676519482625794</v>
       </c>
     </row>
@@ -2398,11 +2506,13 @@
       <c r="Q38" s="4" t="inlineStr"/>
       <c r="R38" s="4" t="inlineStr"/>
       <c r="S38" s="4" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="6" t="n">
+      <c r="T38" s="4" t="inlineStr"/>
+      <c r="U38" s="4" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr"/>
+      <c r="W38" s="6" t="n">
         <v>-9204.333333333336</v>
       </c>
-      <c r="V38" s="7" t="n">
+      <c r="X38" s="7" t="n">
         <v>-0.3674545921510859</v>
       </c>
     </row>
@@ -2450,11 +2560,13 @@
       <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
       <c r="S39" s="8" t="inlineStr"/>
-      <c r="T39" s="9" t="n">
+      <c r="T39" s="8" t="inlineStr"/>
+      <c r="U39" s="8" t="inlineStr"/>
+      <c r="V39" s="9" t="n">
         <v>57571.66666666666</v>
       </c>
-      <c r="U39" s="10" t="inlineStr"/>
-      <c r="V39" s="11" t="inlineStr"/>
+      <c r="W39" s="10" t="inlineStr"/>
+      <c r="X39" s="11" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="1" t="n"/>
@@ -2492,13 +2604,15 @@
       <c r="Q40" s="8" t="inlineStr"/>
       <c r="R40" s="8" t="inlineStr"/>
       <c r="S40" s="8" t="inlineStr"/>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="8" t="inlineStr"/>
+      <c r="U40" s="8" t="inlineStr"/>
+      <c r="V40" s="9" t="n">
         <v>57908.33333333334</v>
       </c>
-      <c r="U40" s="9" t="n">
+      <c r="W40" s="9" t="n">
         <v>336.6666666666715</v>
       </c>
-      <c r="V40" s="11" t="n">
+      <c r="X40" s="11" t="n">
         <v>0.01344037728869018</v>
       </c>
     </row>
@@ -2532,11 +2646,13 @@
       <c r="Q41" s="4" t="inlineStr"/>
       <c r="R41" s="4" t="inlineStr"/>
       <c r="S41" s="4" t="inlineStr"/>
-      <c r="T41" s="5" t="inlineStr"/>
-      <c r="U41" s="6" t="n">
+      <c r="T41" s="4" t="inlineStr"/>
+      <c r="U41" s="4" t="inlineStr"/>
+      <c r="V41" s="5" t="inlineStr"/>
+      <c r="W41" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="V41" s="7" t="n">
+      <c r="X41" s="7" t="n">
         <v>0.01539391940183627</v>
       </c>
     </row>
@@ -2584,11 +2700,13 @@
       <c r="Q42" s="8" t="inlineStr"/>
       <c r="R42" s="8" t="inlineStr"/>
       <c r="S42" s="8" t="inlineStr"/>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="8" t="inlineStr"/>
+      <c r="U42" s="8" t="inlineStr"/>
+      <c r="V42" s="9" t="n">
         <v>193</v>
       </c>
-      <c r="U42" s="10" t="inlineStr"/>
-      <c r="V42" s="11" t="inlineStr"/>
+      <c r="W42" s="10" t="inlineStr"/>
+      <c r="X42" s="11" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
@@ -2622,13 +2740,15 @@
       <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="8" t="inlineStr"/>
-      <c r="T43" s="9" t="n">
+      <c r="T43" s="8" t="inlineStr"/>
+      <c r="U43" s="8" t="inlineStr"/>
+      <c r="V43" s="9" t="n">
         <v>171.5</v>
       </c>
-      <c r="U43" s="9" t="n">
+      <c r="W43" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="V43" s="11" t="n">
+      <c r="X43" s="11" t="n">
         <v>-0.01182033096926714</v>
       </c>
     </row>
@@ -2662,11 +2782,13 @@
       <c r="Q44" s="4" t="inlineStr"/>
       <c r="R44" s="4" t="inlineStr"/>
       <c r="S44" s="4" t="inlineStr"/>
-      <c r="T44" s="5" t="inlineStr"/>
-      <c r="U44" s="6" t="n">
+      <c r="T44" s="4" t="inlineStr"/>
+      <c r="U44" s="4" t="inlineStr"/>
+      <c r="V44" s="5" t="inlineStr"/>
+      <c r="W44" s="6" t="n">
         <v>-0.7000000000000028</v>
       </c>
-      <c r="V44" s="7" t="n">
+      <c r="X44" s="7" t="n">
         <v>-0.02364864864864874</v>
       </c>
     </row>
@@ -2706,11 +2828,13 @@
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
       <c r="S45" s="8" t="inlineStr"/>
-      <c r="T45" s="9" t="n">
+      <c r="T45" s="8" t="inlineStr"/>
+      <c r="U45" s="8" t="inlineStr"/>
+      <c r="V45" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="U45" s="10" t="inlineStr"/>
-      <c r="V45" s="11" t="inlineStr"/>
+      <c r="W45" s="10" t="inlineStr"/>
+      <c r="X45" s="11" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="1" t="n"/>
@@ -2744,13 +2868,15 @@
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr"/>
-      <c r="T46" s="9" t="n">
+      <c r="T46" s="8" t="inlineStr"/>
+      <c r="U46" s="8" t="inlineStr"/>
+      <c r="V46" s="9" t="n">
         <v>33.15</v>
       </c>
-      <c r="U46" s="9" t="n">
+      <c r="W46" s="9" t="n">
         <v>0.1499999999999986</v>
       </c>
-      <c r="V46" s="11" t="n">
+      <c r="X46" s="11" t="n">
         <v>-0.005067567567567519</v>
       </c>
     </row>
@@ -2784,11 +2910,13 @@
       <c r="Q47" s="4" t="inlineStr"/>
       <c r="R47" s="4" t="inlineStr"/>
       <c r="S47" s="4" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="6" t="n">
+      <c r="T47" s="4" t="inlineStr"/>
+      <c r="U47" s="4" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr"/>
+      <c r="W47" s="6" t="n">
         <v>491.5</v>
       </c>
-      <c r="V47" s="7" t="n">
+      <c r="X47" s="7" t="n">
         <v>0.115118866377796</v>
       </c>
     </row>
@@ -2836,11 +2964,13 @@
       <c r="Q48" s="8" t="inlineStr"/>
       <c r="R48" s="8" t="inlineStr"/>
       <c r="S48" s="8" t="inlineStr"/>
-      <c r="T48" s="9" t="n">
+      <c r="T48" s="8" t="inlineStr"/>
+      <c r="U48" s="8" t="inlineStr"/>
+      <c r="V48" s="9" t="n">
         <v>1807.5</v>
       </c>
-      <c r="U48" s="10" t="inlineStr"/>
-      <c r="V48" s="11" t="inlineStr"/>
+      <c r="W48" s="10" t="inlineStr"/>
+      <c r="X48" s="11" t="inlineStr"/>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="1" t="n"/>
@@ -2886,9 +3016,11 @@
       <c r="Q49" s="8" t="inlineStr"/>
       <c r="R49" s="8" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr"/>
-      <c r="T49" s="9" t="inlineStr"/>
-      <c r="U49" s="10" t="inlineStr"/>
-      <c r="V49" s="11" t="inlineStr"/>
+      <c r="T49" s="8" t="inlineStr"/>
+      <c r="U49" s="8" t="inlineStr"/>
+      <c r="V49" s="9" t="inlineStr"/>
+      <c r="W49" s="10" t="inlineStr"/>
+      <c r="X49" s="11" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="1" t="n"/>
@@ -2942,13 +3074,15 @@
       <c r="Q50" s="8" t="inlineStr"/>
       <c r="R50" s="8" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr"/>
-      <c r="T50" s="9" t="n">
+      <c r="T50" s="8" t="inlineStr"/>
+      <c r="U50" s="8" t="inlineStr"/>
+      <c r="V50" s="9" t="n">
         <v>2012.1</v>
       </c>
-      <c r="U50" s="9" t="n">
+      <c r="W50" s="9" t="n">
         <v>204.5999999999999</v>
       </c>
-      <c r="V50" s="11" t="n">
+      <c r="X50" s="11" t="n">
         <v>0.0479213022602178</v>
       </c>
     </row>
@@ -2982,11 +3116,13 @@
       <c r="Q51" s="4" t="inlineStr"/>
       <c r="R51" s="4" t="inlineStr"/>
       <c r="S51" s="4" t="inlineStr"/>
-      <c r="T51" s="5" t="inlineStr"/>
-      <c r="U51" s="6" t="n">
+      <c r="T51" s="4" t="inlineStr"/>
+      <c r="U51" s="4" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr"/>
+      <c r="W51" s="6" t="n">
         <v>-5475.2</v>
       </c>
-      <c r="V51" s="7" t="n">
+      <c r="X51" s="7" t="n">
         <v>-2.540813958884403</v>
       </c>
     </row>
@@ -3040,38 +3176,36 @@
         </is>
       </c>
       <c r="Q52" s="8" t="inlineStr"/>
-      <c r="R52" s="12" t="inlineStr">
+      <c r="R52" s="8" t="inlineStr"/>
+      <c r="S52" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="T52" s="12" t="inlineStr">
         <is>
           <t>2594.00</t>
         </is>
       </c>
-      <c r="S52" s="8" t="inlineStr"/>
-      <c r="T52" s="9" t="n">
+      <c r="U52" s="8" t="inlineStr"/>
+      <c r="V52" s="9" t="n">
         <v>2764.8</v>
       </c>
-      <c r="U52" s="10" t="inlineStr"/>
-      <c r="V52" s="11" t="inlineStr"/>
+      <c r="W52" s="10" t="inlineStr"/>
+      <c r="X52" s="11" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr"/>
       <c r="D53" s="8" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>3327.00</t>
-        </is>
-      </c>
+      <c r="E53" s="8" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr"/>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>3829.00</t>
-        </is>
-      </c>
+      <c r="G53" s="8" t="inlineStr"/>
       <c r="H53" s="8" t="inlineStr"/>
       <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr"/>
@@ -3079,139 +3213,151 @@
       <c r="L53" s="8" t="inlineStr"/>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
-      <c r="O53" s="12" t="inlineStr">
+      <c r="O53" s="12" t="inlineStr"/>
+      <c r="P53" s="8" t="inlineStr"/>
+      <c r="Q53" s="8" t="inlineStr"/>
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="S53" s="8" t="inlineStr"/>
+      <c r="T53" s="12" t="inlineStr"/>
+      <c r="U53" s="8" t="inlineStr"/>
+      <c r="V53" s="9" t="inlineStr"/>
+      <c r="W53" s="10" t="inlineStr"/>
+      <c r="X53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr"/>
+      <c r="D54" s="8" t="inlineStr"/>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>3327.00</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>3829.00</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="inlineStr"/>
+      <c r="J54" s="8" t="inlineStr"/>
+      <c r="K54" s="8" t="inlineStr"/>
+      <c r="L54" s="8" t="inlineStr"/>
+      <c r="M54" s="8" t="inlineStr"/>
+      <c r="N54" s="8" t="inlineStr"/>
+      <c r="O54" s="12" t="inlineStr">
         <is>
           <t>1024.00</t>
         </is>
       </c>
-      <c r="P53" s="8" t="inlineStr">
+      <c r="P54" s="8" t="inlineStr">
         <is>
           <t>927.00</t>
         </is>
       </c>
-      <c r="Q53" s="8" t="inlineStr"/>
-      <c r="R53" s="12" t="inlineStr">
+      <c r="Q54" s="8" t="inlineStr">
+        <is>
+          <t>972.00</t>
+        </is>
+      </c>
+      <c r="R54" s="8" t="inlineStr"/>
+      <c r="S54" s="8" t="inlineStr">
+        <is>
+          <t>7531.00</t>
+        </is>
+      </c>
+      <c r="T54" s="12" t="inlineStr">
         <is>
           <t>1005.00</t>
         </is>
       </c>
-      <c r="S53" s="8" t="inlineStr"/>
-      <c r="T53" s="9" t="n">
+      <c r="U54" s="8" t="inlineStr"/>
+      <c r="V54" s="9" t="n">
         <v>2022.4</v>
       </c>
-      <c r="U53" s="9" t="n">
+      <c r="W54" s="9" t="n">
         <v>742.4000000000001</v>
       </c>
-      <c r="V53" s="11" t="n">
+      <c r="X54" s="11" t="n">
         <v>-0.3445171469673767</v>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Hero
 Random: 1027.0
 Human: 30826.4</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 11044</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr"/>
-      <c r="O54" s="4" t="inlineStr"/>
-      <c r="P54" s="4" t="inlineStr"/>
-      <c r="Q54" s="4" t="inlineStr"/>
-      <c r="R54" s="4" t="inlineStr"/>
-      <c r="S54" s="4" t="inlineStr"/>
-      <c r="T54" s="5" t="inlineStr"/>
-      <c r="U54" s="6" t="n">
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
+      <c r="P55" s="4" t="inlineStr"/>
+      <c r="Q55" s="4" t="inlineStr"/>
+      <c r="R55" s="4" t="inlineStr"/>
+      <c r="S55" s="4" t="inlineStr"/>
+      <c r="T55" s="4" t="inlineStr"/>
+      <c r="U55" s="4" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr"/>
+      <c r="W55" s="6" t="n">
         <v>2134</v>
       </c>
-      <c r="V54" s="7" t="n">
+      <c r="X55" s="7" t="n">
         <v>0.07161218011100895</v>
       </c>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>7608.50</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>12996.75</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>13456.25</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>13081.00</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr"/>
-      <c r="J55" s="8" t="inlineStr"/>
-      <c r="K55" s="8" t="inlineStr"/>
-      <c r="L55" s="8" t="inlineStr"/>
-      <c r="M55" s="8" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
-      <c r="O55" s="8" t="inlineStr"/>
-      <c r="P55" s="8" t="inlineStr"/>
-      <c r="Q55" s="8" t="inlineStr"/>
-      <c r="R55" s="8" t="inlineStr"/>
-      <c r="S55" s="8" t="inlineStr"/>
-      <c r="T55" s="9" t="n">
-        <v>13178</v>
-      </c>
-      <c r="U55" s="10" t="inlineStr"/>
-      <c r="V55" s="11" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>7608.50</t>
+        </is>
+      </c>
       <c r="D56" s="8" t="inlineStr"/>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>13251.25</t>
+          <t>12996.75</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>13231.50</t>
+          <t>13456.25</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>13325.50</t>
+          <t>13081.00</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr"/>
@@ -3226,108 +3372,114 @@
       <c r="Q56" s="8" t="inlineStr"/>
       <c r="R56" s="8" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr"/>
-      <c r="T56" s="9" t="n">
+      <c r="T56" s="8" t="inlineStr"/>
+      <c r="U56" s="8" t="inlineStr"/>
+      <c r="V56" s="9" t="n">
+        <v>13178</v>
+      </c>
+      <c r="W56" s="10" t="inlineStr"/>
+      <c r="X56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="1" t="n"/>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr"/>
+      <c r="D57" s="8" t="inlineStr"/>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>13251.25</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>13231.50</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>13325.50</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr"/>
+      <c r="J57" s="8" t="inlineStr"/>
+      <c r="K57" s="8" t="inlineStr"/>
+      <c r="L57" s="8" t="inlineStr"/>
+      <c r="M57" s="8" t="inlineStr"/>
+      <c r="N57" s="8" t="inlineStr"/>
+      <c r="O57" s="8" t="inlineStr"/>
+      <c r="P57" s="8" t="inlineStr"/>
+      <c r="Q57" s="8" t="inlineStr"/>
+      <c r="R57" s="8" t="inlineStr"/>
+      <c r="S57" s="8" t="inlineStr"/>
+      <c r="T57" s="8" t="inlineStr"/>
+      <c r="U57" s="8" t="inlineStr"/>
+      <c r="V57" s="9" t="n">
         <v>13269.41666666667</v>
       </c>
-      <c r="U56" s="9" t="n">
+      <c r="W57" s="9" t="n">
         <v>91.41666666666606</v>
       </c>
-      <c r="V56" s="11" t="n">
+      <c r="X57" s="11" t="n">
         <v>0.003067735144555463</v>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Jamesbond
 Random: 29.0
 Human: 302.8</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 509</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr"/>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr"/>
-      <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr"/>
-      <c r="M57" s="4" t="inlineStr"/>
-      <c r="N57" s="4" t="inlineStr"/>
-      <c r="O57" s="4" t="inlineStr"/>
-      <c r="P57" s="4" t="inlineStr"/>
-      <c r="Q57" s="4" t="inlineStr"/>
-      <c r="R57" s="4" t="inlineStr"/>
-      <c r="S57" s="4" t="inlineStr"/>
-      <c r="T57" s="5" t="inlineStr"/>
-      <c r="U57" s="6" t="n">
-        <v>-65.25</v>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>-0.2383126369612856</v>
-      </c>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>490.00</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr"/>
-      <c r="E58" s="8" t="inlineStr"/>
-      <c r="F58" s="8" t="inlineStr"/>
-      <c r="G58" s="8" t="inlineStr"/>
-      <c r="H58" s="8" t="inlineStr"/>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING, 537.50</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr"/>
-      <c r="K58" s="8" t="inlineStr"/>
-      <c r="L58" s="8" t="inlineStr"/>
-      <c r="M58" s="8" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr"/>
-      <c r="O58" s="8" t="inlineStr">
-        <is>
-          <t>522.50</t>
-        </is>
-      </c>
-      <c r="P58" s="8" t="inlineStr"/>
-      <c r="Q58" s="8" t="inlineStr"/>
-      <c r="R58" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
-        </is>
-      </c>
-      <c r="S58" s="8" t="inlineStr"/>
-      <c r="T58" s="9" t="n">
-        <v>443.75</v>
-      </c>
-      <c r="U58" s="10" t="inlineStr"/>
-      <c r="V58" s="11" t="inlineStr"/>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr"/>
+      <c r="Q58" s="4" t="inlineStr"/>
+      <c r="R58" s="4" t="inlineStr"/>
+      <c r="S58" s="4" t="inlineStr"/>
+      <c r="T58" s="4" t="inlineStr"/>
+      <c r="U58" s="4" t="inlineStr"/>
+      <c r="V58" s="5" t="inlineStr"/>
+      <c r="W58" s="6" t="n">
+        <v>-35.66666666666669</v>
+      </c>
+      <c r="X58" s="7" t="n">
+        <v>-0.1302654005356709</v>
+      </c>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>490.00</t>
+        </is>
+      </c>
       <c r="D59" s="8" t="inlineStr"/>
       <c r="E59" s="8" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr"/>
@@ -3335,7 +3487,7 @@
       <c r="H59" s="8" t="inlineStr"/>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>567.50, 660.00</t>
+          <t>532.50, 537.50</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr"/>
@@ -3345,163 +3497,159 @@
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="8" t="inlineStr">
         <is>
-          <t>665.00</t>
+          <t>522.50</t>
         </is>
       </c>
       <c r="P59" s="8" t="inlineStr"/>
       <c r="Q59" s="8" t="inlineStr"/>
-      <c r="R59" s="8" t="inlineStr">
-        <is>
-          <t>375.00</t>
-        </is>
-      </c>
+      <c r="R59" s="8" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr"/>
-      <c r="T59" s="9" t="n">
-        <v>520</v>
-      </c>
-      <c r="U59" s="9" t="n">
-        <v>76.25</v>
-      </c>
-      <c r="V59" s="11" t="n">
-        <v>0.2784879474068663</v>
-      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>365.00</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr"/>
+      <c r="V59" s="9" t="n">
+        <v>473.3333333333333</v>
+      </c>
+      <c r="W59" s="10" t="inlineStr"/>
+      <c r="X59" s="11" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Kangaroo
-Random: 52.0
-Human: 3035.0</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4208</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr"/>
-      <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr"/>
-      <c r="O60" s="4" t="inlineStr"/>
-      <c r="P60" s="4" t="inlineStr"/>
-      <c r="Q60" s="4" t="inlineStr"/>
-      <c r="R60" s="4" t="inlineStr"/>
-      <c r="S60" s="4" t="inlineStr"/>
-      <c r="T60" s="5" t="inlineStr"/>
-      <c r="U60" s="6" t="n">
-        <v>-2778</v>
-      </c>
-      <c r="V60" s="7" t="n">
-        <v>-0.9312772376801878</v>
-      </c>
+      <c r="A60" s="1" t="n"/>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr"/>
+      <c r="D60" s="8" t="inlineStr"/>
+      <c r="E60" s="8" t="inlineStr"/>
+      <c r="F60" s="8" t="inlineStr"/>
+      <c r="G60" s="8" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="8" t="inlineStr"/>
+      <c r="K60" s="8" t="inlineStr"/>
+      <c r="L60" s="8" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr"/>
+      <c r="N60" s="8" t="inlineStr"/>
+      <c r="O60" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="P60" s="8" t="inlineStr"/>
+      <c r="Q60" s="8" t="inlineStr"/>
+      <c r="R60" s="8" t="inlineStr"/>
+      <c r="S60" s="8" t="inlineStr"/>
+      <c r="T60" s="8" t="inlineStr"/>
+      <c r="U60" s="8" t="inlineStr"/>
+      <c r="V60" s="9" t="inlineStr"/>
+      <c r="W60" s="10" t="inlineStr"/>
+      <c r="X60" s="11" t="inlineStr"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr"/>
       <c r="D61" s="8" t="inlineStr"/>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>1770.00</t>
-        </is>
-      </c>
+      <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr"/>
       <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="8" t="inlineStr"/>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="J61" s="8" t="inlineStr">
-        <is>
-          <t>1730.00</t>
-        </is>
-      </c>
+          <t>567.50, 660.00</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr"/>
       <c r="K61" s="8" t="inlineStr"/>
       <c r="L61" s="8" t="inlineStr"/>
       <c r="M61" s="8" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
       <c r="O61" s="8" t="inlineStr">
         <is>
-          <t>1550.00</t>
-        </is>
-      </c>
-      <c r="P61" s="8" t="inlineStr">
-        <is>
-          <t>930.00</t>
-        </is>
-      </c>
+          <t>665.00</t>
+        </is>
+      </c>
+      <c r="P61" s="8" t="inlineStr"/>
       <c r="Q61" s="8" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr"/>
-      <c r="T61" s="9" t="n">
-        <v>1430</v>
-      </c>
-      <c r="U61" s="10" t="inlineStr"/>
-      <c r="V61" s="11" t="inlineStr"/>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr"/>
+      <c r="V61" s="9" t="n">
+        <v>535.8333333333334</v>
+      </c>
+      <c r="W61" s="9" t="n">
+        <v>62.50000000000006</v>
+      </c>
+      <c r="X61" s="11" t="n">
+        <v>0.2282688093498906</v>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="1" t="n"/>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr"/>
-      <c r="D62" s="8" t="inlineStr"/>
-      <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="8" t="inlineStr"/>
-      <c r="G62" s="8" t="inlineStr"/>
-      <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="8" t="inlineStr"/>
-      <c r="J62" s="8" t="inlineStr"/>
-      <c r="K62" s="8" t="inlineStr"/>
-      <c r="L62" s="8" t="inlineStr"/>
-      <c r="M62" s="8" t="inlineStr"/>
-      <c r="N62" s="8" t="inlineStr"/>
-      <c r="O62" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="P62" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="Q62" s="8" t="inlineStr"/>
-      <c r="R62" s="8" t="inlineStr"/>
-      <c r="S62" s="8" t="inlineStr"/>
-      <c r="T62" s="9" t="inlineStr"/>
-      <c r="U62" s="10" t="inlineStr"/>
-      <c r="V62" s="11" t="inlineStr"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Kangaroo
+Random: 52.0
+Human: 3035.0</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4208</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr"/>
+      <c r="Q62" s="4" t="inlineStr"/>
+      <c r="R62" s="4" t="inlineStr"/>
+      <c r="S62" s="4" t="inlineStr"/>
+      <c r="T62" s="4" t="inlineStr"/>
+      <c r="U62" s="4" t="inlineStr"/>
+      <c r="V62" s="5" t="inlineStr"/>
+      <c r="W62" s="6" t="n">
+        <v>-2778</v>
+      </c>
+      <c r="X62" s="7" t="n">
+        <v>-0.9312772376801878</v>
+      </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr"/>
       <c r="D63" s="8" t="inlineStr"/>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>1760.00</t>
+          <t>1770.00</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr"/>
@@ -3509,198 +3657,206 @@
       <c r="H63" s="8" t="inlineStr"/>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>1590.00</t>
-        </is>
-      </c>
-      <c r="J63" s="8" t="inlineStr"/>
+          <t>1470.00</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>1730.00</t>
+        </is>
+      </c>
       <c r="K63" s="8" t="inlineStr"/>
       <c r="L63" s="8" t="inlineStr"/>
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
       <c r="O63" s="8" t="inlineStr">
         <is>
-          <t>1670.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="P63" s="8" t="inlineStr">
         <is>
-          <t>760.00</t>
+          <t>930.00</t>
         </is>
       </c>
       <c r="Q63" s="8" t="inlineStr"/>
       <c r="R63" s="8" t="inlineStr"/>
       <c r="S63" s="8" t="inlineStr"/>
-      <c r="T63" s="9" t="n">
-        <v>1445</v>
-      </c>
-      <c r="U63" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="V63" s="11" t="n">
-        <v>0.005028494803888703</v>
-      </c>
+      <c r="T63" s="8" t="inlineStr"/>
+      <c r="U63" s="8" t="inlineStr"/>
+      <c r="V63" s="9" t="n">
+        <v>1430</v>
+      </c>
+      <c r="W63" s="10" t="inlineStr"/>
+      <c r="X63" s="11" t="inlineStr"/>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Krull
-Random: 1598.0
-Human: 2665.5</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 8413</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr"/>
-      <c r="D64" s="4" t="inlineStr"/>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="4" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr"/>
-      <c r="J64" s="4" t="inlineStr"/>
-      <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr"/>
-      <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr"/>
-      <c r="O64" s="4" t="inlineStr"/>
-      <c r="P64" s="4" t="inlineStr"/>
-      <c r="Q64" s="4" t="inlineStr"/>
-      <c r="R64" s="4" t="inlineStr"/>
-      <c r="S64" s="4" t="inlineStr"/>
-      <c r="T64" s="5" t="inlineStr"/>
-      <c r="U64" s="6" t="n">
-        <v>-2744.7</v>
-      </c>
-      <c r="V64" s="7" t="n">
-        <v>-2.571147540983606</v>
-      </c>
+      <c r="A64" s="1" t="n"/>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr"/>
+      <c r="D64" s="8" t="inlineStr"/>
+      <c r="E64" s="8" t="inlineStr"/>
+      <c r="F64" s="8" t="inlineStr"/>
+      <c r="G64" s="8" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>1310.00</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr"/>
+      <c r="K64" s="8" t="inlineStr"/>
+      <c r="L64" s="8" t="inlineStr"/>
+      <c r="M64" s="8" t="inlineStr"/>
+      <c r="N64" s="8" t="inlineStr"/>
+      <c r="O64" s="8" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="P64" s="8" t="inlineStr">
+        <is>
+          <t>1030.00</t>
+        </is>
+      </c>
+      <c r="Q64" s="8" t="inlineStr"/>
+      <c r="R64" s="8" t="inlineStr"/>
+      <c r="S64" s="8" t="inlineStr"/>
+      <c r="T64" s="8" t="inlineStr"/>
+      <c r="U64" s="8" t="inlineStr"/>
+      <c r="V64" s="9" t="inlineStr"/>
+      <c r="W64" s="10" t="inlineStr"/>
+      <c r="X64" s="11" t="inlineStr"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr"/>
       <c r="D65" s="8" t="inlineStr"/>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>6202.00</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>5689.00</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>6107.50</t>
-        </is>
-      </c>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr"/>
+      <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="12" t="inlineStr">
-        <is>
-          <t>4708.50</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>5913.50</t>
-        </is>
-      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>1590.00</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr"/>
       <c r="K65" s="8" t="inlineStr"/>
       <c r="L65" s="8" t="inlineStr"/>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="8" t="inlineStr">
         <is>
-          <t>5228.50</t>
-        </is>
-      </c>
-      <c r="P65" s="8" t="inlineStr"/>
+          <t>1670.00</t>
+        </is>
+      </c>
+      <c r="P65" s="8" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
       <c r="Q65" s="8" t="inlineStr"/>
-      <c r="R65" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
+      <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr"/>
-      <c r="T65" s="9" t="n">
-        <v>5668.3</v>
-      </c>
-      <c r="U65" s="10" t="inlineStr"/>
-      <c r="V65" s="11" t="inlineStr"/>
+      <c r="T65" s="8" t="inlineStr"/>
+      <c r="U65" s="8" t="inlineStr"/>
+      <c r="V65" s="9" t="n">
+        <v>1445</v>
+      </c>
+      <c r="W65" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="X65" s="11" t="n">
+        <v>0.005028494803888703</v>
+      </c>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="1" t="n"/>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr"/>
-      <c r="D66" s="8" t="inlineStr"/>
-      <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr"/>
-      <c r="G66" s="8" t="inlineStr"/>
-      <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="12" t="inlineStr">
-        <is>
-          <t>4851.00</t>
-        </is>
-      </c>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>6044.00</t>
-        </is>
-      </c>
-      <c r="K66" s="8" t="inlineStr"/>
-      <c r="L66" s="8" t="inlineStr"/>
-      <c r="M66" s="8" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
-      <c r="O66" s="8" t="inlineStr"/>
-      <c r="P66" s="8" t="inlineStr"/>
-      <c r="Q66" s="8" t="inlineStr"/>
-      <c r="R66" s="8" t="inlineStr">
-        <is>
-          <t>6587.00</t>
-        </is>
-      </c>
-      <c r="S66" s="8" t="inlineStr"/>
-      <c r="T66" s="9" t="inlineStr"/>
-      <c r="U66" s="10" t="inlineStr"/>
-      <c r="V66" s="11" t="inlineStr"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Krull
+Random: 1598.0
+Human: 2665.5</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 8413</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr"/>
+      <c r="Q66" s="4" t="inlineStr"/>
+      <c r="R66" s="4" t="inlineStr"/>
+      <c r="S66" s="4" t="inlineStr"/>
+      <c r="T66" s="4" t="inlineStr"/>
+      <c r="U66" s="4" t="inlineStr"/>
+      <c r="V66" s="5" t="inlineStr"/>
+      <c r="W66" s="6" t="n">
+        <v>-2744.7</v>
+      </c>
+      <c r="X66" s="7" t="n">
+        <v>-2.571147540983606</v>
+      </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr"/>
       <c r="D67" s="8" t="inlineStr"/>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>6576.50</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr"/>
-      <c r="G67" s="8" t="inlineStr"/>
+          <t>6202.00</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>5689.00</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>6107.50</t>
+        </is>
+      </c>
       <c r="H67" s="8" t="inlineStr"/>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>5279.50</t>
+          <t>4708.50</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>5889.50</t>
+          <t>5913.50</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr"/>
@@ -3709,203 +3865,227 @@
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="8" t="inlineStr">
         <is>
-          <t>6447.50</t>
+          <t>5228.50</t>
         </is>
       </c>
       <c r="P67" s="8" t="inlineStr"/>
-      <c r="Q67" s="8" t="inlineStr"/>
-      <c r="R67" s="8" t="inlineStr">
-        <is>
-          <t>6796.50</t>
-        </is>
-      </c>
+      <c r="Q67" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="R67" s="8" t="inlineStr"/>
       <c r="S67" s="8" t="inlineStr"/>
-      <c r="T67" s="9" t="n">
-        <v>6197.9</v>
-      </c>
-      <c r="U67" s="9" t="n">
-        <v>529.5999999999995</v>
-      </c>
-      <c r="V67" s="11" t="n">
-        <v>0.4961124121779855</v>
-      </c>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>6289.00</t>
+        </is>
+      </c>
+      <c r="U67" s="8" t="inlineStr"/>
+      <c r="V67" s="9" t="n">
+        <v>5668.3</v>
+      </c>
+      <c r="W67" s="10" t="inlineStr"/>
+      <c r="X67" s="11" t="inlineStr"/>
     </row>
     <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>KungFuMaster
-Random: 258.5
-Human: 22736.3</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 26182</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
-      <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr"/>
-      <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr"/>
-      <c r="O68" s="4" t="inlineStr"/>
-      <c r="P68" s="4" t="inlineStr"/>
-      <c r="Q68" s="4" t="inlineStr"/>
-      <c r="R68" s="4" t="inlineStr"/>
-      <c r="S68" s="4" t="inlineStr"/>
-      <c r="T68" s="5" t="inlineStr"/>
-      <c r="U68" s="6" t="n">
-        <v>-1044.5</v>
-      </c>
-      <c r="V68" s="7" t="n">
-        <v>-0.04646807071866464</v>
-      </c>
+      <c r="A68" s="1" t="n"/>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr"/>
+      <c r="D68" s="8" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr"/>
+      <c r="F68" s="8" t="inlineStr"/>
+      <c r="G68" s="8" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>4851.00</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>6044.00</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr"/>
+      <c r="L68" s="8" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr"/>
+      <c r="N68" s="8" t="inlineStr"/>
+      <c r="O68" s="8" t="inlineStr"/>
+      <c r="P68" s="8" t="inlineStr"/>
+      <c r="Q68" s="8" t="inlineStr"/>
+      <c r="R68" s="8" t="inlineStr"/>
+      <c r="S68" s="8" t="inlineStr"/>
+      <c r="T68" s="8" t="inlineStr">
+        <is>
+          <t>6587.00</t>
+        </is>
+      </c>
+      <c r="U68" s="8" t="inlineStr"/>
+      <c r="V68" s="9" t="inlineStr"/>
+      <c r="W68" s="10" t="inlineStr"/>
+      <c r="X68" s="11" t="inlineStr"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr"/>
       <c r="D69" s="8" t="inlineStr"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>26460.00</t>
+          <t>6576.50</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr"/>
       <c r="H69" s="8" t="inlineStr"/>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>23815.00</t>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>5279.50</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>20895.00</t>
+          <t>5889.50</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr"/>
       <c r="L69" s="8" t="inlineStr"/>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
-      <c r="O69" s="8" t="inlineStr"/>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>6447.50</t>
+        </is>
+      </c>
       <c r="P69" s="8" t="inlineStr"/>
-      <c r="Q69" s="8" t="inlineStr"/>
+      <c r="Q69" s="8" t="inlineStr">
+        <is>
+          <t>6828.50</t>
+        </is>
+      </c>
       <c r="R69" s="8" t="inlineStr"/>
       <c r="S69" s="8" t="inlineStr"/>
-      <c r="T69" s="9" t="n">
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>6796.50</t>
+        </is>
+      </c>
+      <c r="U69" s="8" t="inlineStr"/>
+      <c r="V69" s="9" t="n">
+        <v>6197.9</v>
+      </c>
+      <c r="W69" s="9" t="n">
+        <v>529.5999999999995</v>
+      </c>
+      <c r="X69" s="11" t="n">
+        <v>0.4961124121779855</v>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>KungFuMaster
+Random: 258.5
+Human: 22736.3</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 26182</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr"/>
+      <c r="Q70" s="4" t="inlineStr"/>
+      <c r="R70" s="4" t="inlineStr"/>
+      <c r="S70" s="4" t="inlineStr"/>
+      <c r="T70" s="4" t="inlineStr"/>
+      <c r="U70" s="4" t="inlineStr"/>
+      <c r="V70" s="5" t="inlineStr"/>
+      <c r="W70" s="6" t="n">
+        <v>-1044.5</v>
+      </c>
+      <c r="X70" s="7" t="n">
+        <v>-0.04646807071866464</v>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="1" t="n"/>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr"/>
+      <c r="D71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>26460.00</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>23815.00</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>20895.00</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr"/>
+      <c r="L71" s="8" t="inlineStr"/>
+      <c r="M71" s="8" t="inlineStr"/>
+      <c r="N71" s="8" t="inlineStr"/>
+      <c r="O71" s="8" t="inlineStr"/>
+      <c r="P71" s="8" t="inlineStr"/>
+      <c r="Q71" s="8" t="inlineStr"/>
+      <c r="R71" s="8" t="inlineStr"/>
+      <c r="S71" s="8" t="inlineStr"/>
+      <c r="T71" s="8" t="inlineStr"/>
+      <c r="U71" s="8" t="inlineStr"/>
+      <c r="V71" s="9" t="n">
         <v>25137.5</v>
       </c>
-      <c r="U69" s="10" t="inlineStr"/>
-      <c r="V69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr"/>
-      <c r="D70" s="8" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>30110.00</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr"/>
-      <c r="G70" s="8" t="inlineStr"/>
-      <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>20245.00</t>
-        </is>
-      </c>
-      <c r="J70" s="8" t="inlineStr"/>
-      <c r="K70" s="8" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
-      <c r="M70" s="8" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
-      <c r="O70" s="8" t="inlineStr"/>
-      <c r="P70" s="8" t="inlineStr"/>
-      <c r="Q70" s="8" t="inlineStr"/>
-      <c r="R70" s="8" t="inlineStr"/>
-      <c r="S70" s="8" t="inlineStr"/>
-      <c r="T70" s="9" t="n">
-        <v>25177.5</v>
-      </c>
-      <c r="U70" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="V70" s="11" t="n">
-        <v>0.001779533584247569</v>
-      </c>
-    </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>MsPacman
-Random: 307.3
-Human: 6951.6</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 2673</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr"/>
-      <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
-      <c r="K71" s="4" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="inlineStr"/>
-      <c r="N71" s="4" t="inlineStr"/>
-      <c r="O71" s="4" t="inlineStr"/>
-      <c r="P71" s="4" t="inlineStr"/>
-      <c r="Q71" s="4" t="inlineStr"/>
-      <c r="R71" s="4" t="inlineStr"/>
-      <c r="S71" s="4" t="inlineStr"/>
-      <c r="T71" s="5" t="inlineStr"/>
-      <c r="U71" s="6" t="n">
-        <v>-602</v>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>-0.09060397634062278</v>
-      </c>
+      <c r="W71" s="10" t="inlineStr"/>
+      <c r="X71" s="11" t="inlineStr"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>1807.50</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr"/>
       <c r="D72" s="8" t="inlineStr"/>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>2007.00</t>
+          <t>30110.00</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr"/>
@@ -3913,7 +4093,7 @@
       <c r="H72" s="8" t="inlineStr"/>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>2388.00</t>
+          <t>20245.00</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr"/>
@@ -3921,251 +4101,267 @@
       <c r="L72" s="8" t="inlineStr"/>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
-      <c r="O72" s="8" t="inlineStr">
-        <is>
-          <t>1754.00</t>
-        </is>
-      </c>
+      <c r="O72" s="8" t="inlineStr"/>
       <c r="P72" s="8" t="inlineStr"/>
       <c r="Q72" s="8" t="inlineStr"/>
       <c r="R72" s="8" t="inlineStr"/>
       <c r="S72" s="8" t="inlineStr"/>
-      <c r="T72" s="9" t="n">
+      <c r="T72" s="8" t="inlineStr"/>
+      <c r="U72" s="8" t="inlineStr"/>
+      <c r="V72" s="9" t="n">
+        <v>25177.5</v>
+      </c>
+      <c r="W72" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="X72" s="11" t="n">
+        <v>0.001779533584247569</v>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>MsPacman
+Random: 307.3
+Human: 6951.6</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 2673</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="4" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr"/>
+      <c r="Q73" s="4" t="inlineStr"/>
+      <c r="R73" s="4" t="inlineStr"/>
+      <c r="S73" s="4" t="inlineStr"/>
+      <c r="T73" s="4" t="inlineStr"/>
+      <c r="U73" s="4" t="inlineStr"/>
+      <c r="V73" s="5" t="inlineStr"/>
+      <c r="W73" s="6" t="n">
+        <v>-602</v>
+      </c>
+      <c r="X73" s="7" t="n">
+        <v>-0.09060397634062278</v>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="1" t="n"/>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>1807.50</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr"/>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>2007.00</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>2388.00</t>
+        </is>
+      </c>
+      <c r="J74" s="8" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr"/>
+      <c r="L74" s="8" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
+      <c r="N74" s="8" t="inlineStr"/>
+      <c r="O74" s="8" t="inlineStr">
+        <is>
+          <t>1754.00</t>
+        </is>
+      </c>
+      <c r="P74" s="8" t="inlineStr"/>
+      <c r="Q74" s="8" t="inlineStr"/>
+      <c r="R74" s="8" t="inlineStr"/>
+      <c r="S74" s="8" t="inlineStr"/>
+      <c r="T74" s="8" t="inlineStr"/>
+      <c r="U74" s="8" t="inlineStr"/>
+      <c r="V74" s="9" t="n">
         <v>2071</v>
       </c>
-      <c r="U72" s="10" t="inlineStr"/>
-      <c r="V72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="1" t="n"/>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr"/>
-      <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="8" t="inlineStr"/>
-      <c r="F73" s="8" t="inlineStr"/>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr"/>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>2250.00</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr"/>
-      <c r="K73" s="8" t="inlineStr"/>
-      <c r="L73" s="8" t="inlineStr"/>
-      <c r="M73" s="8" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr"/>
-      <c r="O73" s="8" t="inlineStr">
-        <is>
-          <t>1886.50</t>
-        </is>
-      </c>
-      <c r="P73" s="8" t="inlineStr"/>
-      <c r="Q73" s="8" t="inlineStr"/>
-      <c r="R73" s="8" t="inlineStr"/>
-      <c r="S73" s="8" t="inlineStr"/>
-      <c r="T73" s="9" t="n">
-        <v>2068.25</v>
-      </c>
-      <c r="U73" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V73" s="11" t="n">
-        <v>-0.0004138885962403865</v>
-      </c>
-    </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Pong
-Random: -20.7
-Human: 14.6</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr"/>
-      <c r="D74" s="4" t="inlineStr"/>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr"/>
-      <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="4" t="inlineStr"/>
-      <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr"/>
-      <c r="O74" s="4" t="inlineStr"/>
-      <c r="P74" s="4" t="inlineStr"/>
-      <c r="Q74" s="4" t="inlineStr"/>
-      <c r="R74" s="4" t="inlineStr"/>
-      <c r="S74" s="4" t="inlineStr"/>
-      <c r="T74" s="5" t="inlineStr"/>
-      <c r="U74" s="6" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="V74" s="7" t="n">
-        <v>-0.1529745042492918</v>
-      </c>
+      <c r="W74" s="10" t="inlineStr"/>
+      <c r="X74" s="11" t="inlineStr"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr"/>
       <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
+      <c r="E75" s="8" t="inlineStr"/>
+      <c r="F75" s="8" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr"/>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>5.70</t>
-        </is>
-      </c>
-      <c r="J75" s="8" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
+          <t>2250.00</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr"/>
       <c r="K75" s="8" t="inlineStr"/>
       <c r="L75" s="8" t="inlineStr"/>
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr"/>
-      <c r="O75" s="8" t="inlineStr"/>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>1886.50</t>
+        </is>
+      </c>
       <c r="P75" s="8" t="inlineStr"/>
       <c r="Q75" s="8" t="inlineStr"/>
       <c r="R75" s="8" t="inlineStr"/>
       <c r="S75" s="8" t="inlineStr"/>
-      <c r="T75" s="9" t="n">
+      <c r="T75" s="8" t="inlineStr"/>
+      <c r="U75" s="8" t="inlineStr"/>
+      <c r="V75" s="9" t="n">
+        <v>2068.25</v>
+      </c>
+      <c r="W75" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X75" s="11" t="n">
+        <v>-0.0004138885962403865</v>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Pong
+Random: -20.7
+Human: 14.6</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr"/>
+      <c r="D76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr"/>
+      <c r="L76" s="4" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr"/>
+      <c r="N76" s="4" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr"/>
+      <c r="Q76" s="4" t="inlineStr"/>
+      <c r="R76" s="4" t="inlineStr"/>
+      <c r="S76" s="4" t="inlineStr"/>
+      <c r="T76" s="4" t="inlineStr"/>
+      <c r="U76" s="4" t="inlineStr"/>
+      <c r="V76" s="5" t="inlineStr"/>
+      <c r="W76" s="6" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="X76" s="7" t="n">
+        <v>-0.1529745042492918</v>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="1" t="n"/>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr"/>
+      <c r="D77" s="8" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>13.70</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr"/>
+      <c r="L77" s="8" t="inlineStr"/>
+      <c r="M77" s="8" t="inlineStr"/>
+      <c r="N77" s="8" t="inlineStr"/>
+      <c r="O77" s="8" t="inlineStr"/>
+      <c r="P77" s="8" t="inlineStr"/>
+      <c r="Q77" s="8" t="inlineStr"/>
+      <c r="R77" s="8" t="inlineStr"/>
+      <c r="S77" s="8" t="inlineStr"/>
+      <c r="T77" s="8" t="inlineStr"/>
+      <c r="U77" s="8" t="inlineStr"/>
+      <c r="V77" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="U75" s="10" t="inlineStr"/>
-      <c r="V75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="1" t="n"/>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr"/>
-      <c r="D76" s="8" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>8.20</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr"/>
-      <c r="L76" s="8" t="inlineStr"/>
-      <c r="M76" s="8" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr"/>
-      <c r="O76" s="8" t="inlineStr"/>
-      <c r="P76" s="8" t="inlineStr"/>
-      <c r="Q76" s="8" t="inlineStr"/>
-      <c r="R76" s="8" t="inlineStr"/>
-      <c r="S76" s="8" t="inlineStr"/>
-      <c r="T76" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="U76" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V76" s="11" t="n">
-        <v>0.09631728045325781</v>
-      </c>
-    </row>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>PrivateEye
-Random: 24.9
-Human: 69571.3</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7781</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr"/>
-      <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="4" t="inlineStr"/>
-      <c r="J77" s="4" t="inlineStr"/>
-      <c r="K77" s="4" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr"/>
-      <c r="M77" s="4" t="inlineStr"/>
-      <c r="N77" s="4" t="inlineStr"/>
-      <c r="O77" s="4" t="inlineStr"/>
-      <c r="P77" s="4" t="inlineStr"/>
-      <c r="Q77" s="4" t="inlineStr"/>
-      <c r="R77" s="4" t="inlineStr"/>
-      <c r="S77" s="4" t="inlineStr"/>
-      <c r="T77" s="5" t="inlineStr"/>
-      <c r="U77" s="6" t="n">
-        <v>-7628.05</v>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>-0.1096828879711962</v>
-      </c>
+      <c r="W77" s="10" t="inlineStr"/>
+      <c r="X77" s="11" t="inlineStr"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>75.30</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr"/>
       <c r="D78" s="8" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr"/>
-      <c r="F78" s="8" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>8.20</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
       <c r="H78" s="8" t="inlineStr"/>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>199.35</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr"/>
@@ -4173,153 +4369,135 @@
       <c r="L78" s="8" t="inlineStr"/>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr"/>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="8" t="inlineStr"/>
+      <c r="P78" s="8" t="inlineStr"/>
+      <c r="Q78" s="8" t="inlineStr"/>
+      <c r="R78" s="8" t="inlineStr"/>
+      <c r="S78" s="8" t="inlineStr"/>
+      <c r="T78" s="8" t="inlineStr"/>
+      <c r="U78" s="8" t="inlineStr"/>
+      <c r="V78" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="W78" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X78" s="11" t="n">
+        <v>0.09631728045325781</v>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>PrivateEye
+Random: 24.9
+Human: 69571.3</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 7781</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr"/>
+      <c r="J79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr"/>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr"/>
+      <c r="O79" s="4" t="inlineStr"/>
+      <c r="P79" s="4" t="inlineStr"/>
+      <c r="Q79" s="4" t="inlineStr"/>
+      <c r="R79" s="4" t="inlineStr"/>
+      <c r="S79" s="4" t="inlineStr"/>
+      <c r="T79" s="4" t="inlineStr"/>
+      <c r="U79" s="4" t="inlineStr"/>
+      <c r="V79" s="5" t="inlineStr"/>
+      <c r="W79" s="6" t="n">
+        <v>-6958.88</v>
+      </c>
+      <c r="X79" s="7" t="n">
+        <v>-0.1000609664914359</v>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="1" t="n"/>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>75.30</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr"/>
+      <c r="F80" s="8" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>199.35</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr"/>
+      <c r="L80" s="8" t="inlineStr"/>
+      <c r="M80" s="8" t="inlineStr"/>
+      <c r="N80" s="8" t="inlineStr"/>
+      <c r="O80" s="8" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P78" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="Q78" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="R78" s="8" t="inlineStr">
+      <c r="P80" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>3551.75</t>
+        </is>
+      </c>
+      <c r="R80" s="8" t="inlineStr"/>
+      <c r="S80" s="8" t="inlineStr"/>
+      <c r="T80" s="8" t="inlineStr">
         <is>
           <t>159.50</t>
         </is>
       </c>
-      <c r="S78" s="8" t="inlineStr"/>
-      <c r="T78" s="9" t="n">
-        <v>152.95</v>
-      </c>
-      <c r="U78" s="10" t="inlineStr"/>
-      <c r="V78" s="11" t="inlineStr"/>
-    </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="1" t="n"/>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr"/>
-      <c r="D79" s="8" t="inlineStr"/>
-      <c r="E79" s="8" t="inlineStr"/>
-      <c r="F79" s="8" t="inlineStr"/>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr"/>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>191.95</t>
-        </is>
-      </c>
-      <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" s="8" t="inlineStr"/>
-      <c r="L79" s="8" t="inlineStr"/>
-      <c r="M79" s="8" t="inlineStr"/>
-      <c r="N79" s="8" t="inlineStr"/>
-      <c r="O79" s="8" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="P79" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q79" s="8" t="inlineStr">
-        <is>
-          <t>166.80</t>
-        </is>
-      </c>
-      <c r="R79" s="8" t="inlineStr">
-        <is>
-          <t>153.20</t>
-        </is>
-      </c>
-      <c r="S79" s="8" t="inlineStr"/>
-      <c r="T79" s="9" t="n">
-        <v>121.7166666666667</v>
-      </c>
-      <c r="U79" s="9" t="n">
-        <v>31.23333333333336</v>
-      </c>
-      <c r="V79" s="11" t="n">
-        <v>-0.0004491006483920571</v>
-      </c>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Qbert
-Random: 163.9
-Human: 13455.0</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4522</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
-      <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr"/>
-      <c r="K80" s="4" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr"/>
-      <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr"/>
-      <c r="O80" s="4" t="inlineStr"/>
-      <c r="P80" s="4" t="inlineStr"/>
-      <c r="Q80" s="4" t="inlineStr"/>
-      <c r="R80" s="4" t="inlineStr"/>
-      <c r="S80" s="4" t="inlineStr"/>
-      <c r="T80" s="5" t="inlineStr"/>
-      <c r="U80" s="6" t="n">
-        <v>-1646.75</v>
-      </c>
-      <c r="V80" s="7" t="n">
-        <v>-0.1238986991294927</v>
-      </c>
+      <c r="U80" s="8" t="inlineStr"/>
+      <c r="V80" s="9" t="n">
+        <v>822.1200000000001</v>
+      </c>
+      <c r="W80" s="10" t="inlineStr"/>
+      <c r="X80" s="11" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr"/>
       <c r="D81" s="8" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
+      <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
+      <c r="G81" s="8" t="inlineStr"/>
       <c r="H81" s="8" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>3193.75</t>
+          <t>191.95</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr"/>
@@ -4329,91 +4507,105 @@
       <c r="N81" s="8" t="inlineStr"/>
       <c r="O81" s="8" t="inlineStr">
         <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="P81" s="8" t="inlineStr"/>
-      <c r="Q81" s="8" t="inlineStr"/>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="P81" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>166.80</t>
+        </is>
+      </c>
       <c r="R81" s="8" t="inlineStr"/>
       <c r="S81" s="8" t="inlineStr"/>
-      <c r="T81" s="9" t="n">
-        <v>2875.25</v>
-      </c>
-      <c r="U81" s="10" t="inlineStr"/>
-      <c r="V81" s="11" t="inlineStr"/>
+      <c r="T81" s="8" t="inlineStr">
+        <is>
+          <t>153.20</t>
+        </is>
+      </c>
+      <c r="U81" s="8" t="inlineStr"/>
+      <c r="V81" s="9" t="n">
+        <v>126.39</v>
+      </c>
+      <c r="W81" s="9" t="n">
+        <v>695.7300000000001</v>
+      </c>
+      <c r="X81" s="11" t="n">
+        <v>-0.01000382478460424</v>
+      </c>
     </row>
     <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="1" t="n"/>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>2818.75</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr"/>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>1918.75</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr"/>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t>2553.75</t>
-        </is>
-      </c>
-      <c r="H82" s="8" t="inlineStr"/>
-      <c r="I82" s="8" t="inlineStr"/>
-      <c r="J82" s="8" t="inlineStr"/>
-      <c r="K82" s="8" t="inlineStr"/>
-      <c r="L82" s="8" t="inlineStr"/>
-      <c r="M82" s="8" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr"/>
-      <c r="O82" s="8" t="inlineStr">
-        <is>
-          <t>3782.50</t>
-        </is>
-      </c>
-      <c r="P82" s="8" t="inlineStr"/>
-      <c r="Q82" s="8" t="inlineStr"/>
-      <c r="R82" s="8" t="inlineStr"/>
-      <c r="S82" s="8" t="inlineStr"/>
-      <c r="T82" s="9" t="inlineStr"/>
-      <c r="U82" s="10" t="inlineStr"/>
-      <c r="V82" s="11" t="inlineStr"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Qbert
+Random: 163.9
+Human: 13455.0</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4522</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr"/>
+      <c r="D82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr"/>
+      <c r="P82" s="4" t="inlineStr"/>
+      <c r="Q82" s="4" t="inlineStr"/>
+      <c r="R82" s="4" t="inlineStr"/>
+      <c r="S82" s="4" t="inlineStr"/>
+      <c r="T82" s="4" t="inlineStr"/>
+      <c r="U82" s="4" t="inlineStr"/>
+      <c r="V82" s="5" t="inlineStr"/>
+      <c r="W82" s="6" t="n">
+        <v>-1646.75</v>
+      </c>
+      <c r="X82" s="7" t="n">
+        <v>-0.1238986991294927</v>
+      </c>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>2702.50</t>
+          <t>1771.25</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr"/>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>4056.25</t>
+          <t>3786.25</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr"/>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>2338.75</t>
+          <t>2940.00</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr"/>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>2608.75</t>
+          <t>3193.75</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr"/>
@@ -4423,77 +4615,95 @@
       <c r="N83" s="8" t="inlineStr"/>
       <c r="O83" s="8" t="inlineStr">
         <is>
-          <t>2895.00</t>
+          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
         </is>
       </c>
       <c r="P83" s="8" t="inlineStr"/>
       <c r="Q83" s="8" t="inlineStr"/>
       <c r="R83" s="8" t="inlineStr"/>
       <c r="S83" s="8" t="inlineStr"/>
-      <c r="T83" s="9" t="n">
-        <v>2920.25</v>
-      </c>
-      <c r="U83" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="V83" s="11" t="n">
-        <v>0.003385724281662165</v>
-      </c>
+      <c r="T83" s="8" t="inlineStr"/>
+      <c r="U83" s="8" t="inlineStr"/>
+      <c r="V83" s="9" t="n">
+        <v>2875.25</v>
+      </c>
+      <c r="W83" s="10" t="inlineStr"/>
+      <c r="X83" s="11" t="inlineStr"/>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>RoadRunner
-Random: 11.5
-Human: 7845.0</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 17564</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr"/>
-      <c r="D84" s="4" t="inlineStr"/>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
-      <c r="K84" s="4" t="inlineStr"/>
-      <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr"/>
-      <c r="O84" s="4" t="inlineStr"/>
-      <c r="P84" s="4" t="inlineStr"/>
-      <c r="Q84" s="4" t="inlineStr"/>
-      <c r="R84" s="4" t="inlineStr"/>
-      <c r="S84" s="4" t="inlineStr"/>
-      <c r="T84" s="5" t="inlineStr"/>
-      <c r="U84" s="6" t="n">
-        <v>-8627.75</v>
-      </c>
-      <c r="V84" s="7" t="n">
-        <v>-1.101391459756175</v>
-      </c>
+      <c r="A84" s="1" t="n"/>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>2818.75</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr"/>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>1918.75</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr"/>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>2553.75</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="8" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
+      <c r="N84" s="8" t="inlineStr"/>
+      <c r="O84" s="8" t="inlineStr">
+        <is>
+          <t>3782.50</t>
+        </is>
+      </c>
+      <c r="P84" s="8" t="inlineStr"/>
+      <c r="Q84" s="8" t="inlineStr"/>
+      <c r="R84" s="8" t="inlineStr"/>
+      <c r="S84" s="8" t="inlineStr"/>
+      <c r="T84" s="8" t="inlineStr"/>
+      <c r="U84" s="8" t="inlineStr"/>
+      <c r="V84" s="9" t="inlineStr"/>
+      <c r="W84" s="10" t="inlineStr"/>
+      <c r="X84" s="11" t="inlineStr"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>2702.50</t>
+        </is>
+      </c>
       <c r="D85" s="8" t="inlineStr"/>
-      <c r="E85" s="8" t="inlineStr"/>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>4056.25</t>
+        </is>
+      </c>
       <c r="F85" s="8" t="inlineStr"/>
-      <c r="G85" s="8" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>2338.75</t>
+        </is>
+      </c>
       <c r="H85" s="8" t="inlineStr"/>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>8610.00</t>
+          <t>2608.75</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr"/>
@@ -4503,72 +4713,70 @@
       <c r="N85" s="8" t="inlineStr"/>
       <c r="O85" s="8" t="inlineStr">
         <is>
-          <t>7290.00</t>
-        </is>
-      </c>
-      <c r="P85" s="8" t="inlineStr">
-        <is>
-          <t>9690.00</t>
-        </is>
-      </c>
-      <c r="Q85" s="8" t="inlineStr">
-        <is>
-          <t>10155.00</t>
-        </is>
-      </c>
+          <t>2895.00</t>
+        </is>
+      </c>
+      <c r="P85" s="8" t="inlineStr"/>
+      <c r="Q85" s="8" t="inlineStr"/>
       <c r="R85" s="8" t="inlineStr"/>
       <c r="S85" s="8" t="inlineStr"/>
-      <c r="T85" s="9" t="n">
-        <v>8936.25</v>
-      </c>
-      <c r="U85" s="10" t="inlineStr"/>
-      <c r="V85" s="11" t="inlineStr"/>
+      <c r="T85" s="8" t="inlineStr"/>
+      <c r="U85" s="8" t="inlineStr"/>
+      <c r="V85" s="9" t="n">
+        <v>2920.25</v>
+      </c>
+      <c r="W85" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="X85" s="11" t="n">
+        <v>0.003385724281662165</v>
+      </c>
     </row>
     <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="1" t="n"/>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr"/>
-      <c r="D86" s="8" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr"/>
-      <c r="F86" s="8" t="inlineStr"/>
-      <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="8" t="inlineStr"/>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr"/>
-      <c r="L86" s="8" t="inlineStr"/>
-      <c r="M86" s="8" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
-      <c r="O86" s="8" t="inlineStr">
-        <is>
-          <t>8520.00</t>
-        </is>
-      </c>
-      <c r="P86" s="8" t="inlineStr">
-        <is>
-          <t>11830.00</t>
-        </is>
-      </c>
-      <c r="Q86" s="8" t="inlineStr">
-        <is>
-          <t>16805.00</t>
-        </is>
-      </c>
-      <c r="R86" s="8" t="inlineStr"/>
-      <c r="S86" s="8" t="inlineStr"/>
-      <c r="T86" s="9" t="inlineStr"/>
-      <c r="U86" s="10" t="inlineStr"/>
-      <c r="V86" s="11" t="inlineStr"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>RoadRunner
+Random: 11.5
+Human: 7845.0</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 17564</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr"/>
+      <c r="D86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="4" t="inlineStr"/>
+      <c r="N86" s="4" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr"/>
+      <c r="P86" s="4" t="inlineStr"/>
+      <c r="Q86" s="4" t="inlineStr"/>
+      <c r="R86" s="4" t="inlineStr"/>
+      <c r="S86" s="4" t="inlineStr"/>
+      <c r="T86" s="4" t="inlineStr"/>
+      <c r="U86" s="4" t="inlineStr"/>
+      <c r="V86" s="5" t="inlineStr"/>
+      <c r="W86" s="6" t="n">
+        <v>-8627.75</v>
+      </c>
+      <c r="X86" s="7" t="n">
+        <v>-1.101391459756175</v>
+      </c>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr"/>
@@ -4579,7 +4787,7 @@
       <c r="H87" s="8" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>8195.00</t>
+          <t>8610.00</t>
         </is>
       </c>
       <c r="J87" s="8" t="inlineStr"/>
@@ -4589,81 +4797,79 @@
       <c r="N87" s="8" t="inlineStr"/>
       <c r="O87" s="8" t="inlineStr">
         <is>
-          <t>8325.00</t>
+          <t>7290.00</t>
         </is>
       </c>
       <c r="P87" s="8" t="inlineStr">
         <is>
-          <t>12890.00</t>
+          <t>9690.00</t>
         </is>
       </c>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>16980.00</t>
+          <t>10155.00</t>
         </is>
       </c>
       <c r="R87" s="8" t="inlineStr"/>
       <c r="S87" s="8" t="inlineStr"/>
-      <c r="T87" s="9" t="n">
-        <v>11597.5</v>
-      </c>
-      <c r="U87" s="9" t="n">
-        <v>2661.25</v>
-      </c>
-      <c r="V87" s="11" t="n">
-        <v>0.3397268143230995</v>
-      </c>
+      <c r="T87" s="8" t="inlineStr"/>
+      <c r="U87" s="8" t="inlineStr"/>
+      <c r="V87" s="9" t="n">
+        <v>8936.25</v>
+      </c>
+      <c r="W87" s="10" t="inlineStr"/>
+      <c r="X87" s="11" t="inlineStr"/>
     </row>
     <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Seaquest
-Random: 68.4
-Human: 42054.7</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 525</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr"/>
-      <c r="D88" s="4" t="inlineStr"/>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr"/>
-      <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="4" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr"/>
-      <c r="K88" s="4" t="inlineStr"/>
-      <c r="L88" s="4" t="inlineStr"/>
-      <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr"/>
-      <c r="O88" s="4" t="inlineStr"/>
-      <c r="P88" s="4" t="inlineStr"/>
-      <c r="Q88" s="4" t="inlineStr"/>
-      <c r="R88" s="4" t="inlineStr"/>
-      <c r="S88" s="4" t="inlineStr"/>
-      <c r="T88" s="5" t="inlineStr"/>
-      <c r="U88" s="6" t="n">
-        <v>-64.33333333333331</v>
-      </c>
-      <c r="V88" s="7" t="n">
-        <v>-0.001532245835744834</v>
-      </c>
+      <c r="A88" s="1" t="n"/>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr"/>
+      <c r="D88" s="8" t="inlineStr"/>
+      <c r="E88" s="8" t="inlineStr"/>
+      <c r="F88" s="8" t="inlineStr"/>
+      <c r="G88" s="8" t="inlineStr"/>
+      <c r="H88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr"/>
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="8" t="inlineStr"/>
+      <c r="M88" s="8" t="inlineStr"/>
+      <c r="N88" s="8" t="inlineStr"/>
+      <c r="O88" s="8" t="inlineStr">
+        <is>
+          <t>8520.00</t>
+        </is>
+      </c>
+      <c r="P88" s="8" t="inlineStr">
+        <is>
+          <t>11830.00</t>
+        </is>
+      </c>
+      <c r="Q88" s="8" t="inlineStr">
+        <is>
+          <t>16805.00</t>
+        </is>
+      </c>
+      <c r="R88" s="8" t="inlineStr"/>
+      <c r="S88" s="8" t="inlineStr"/>
+      <c r="T88" s="8" t="inlineStr"/>
+      <c r="U88" s="8" t="inlineStr"/>
+      <c r="V88" s="9" t="inlineStr"/>
+      <c r="W88" s="10" t="inlineStr"/>
+      <c r="X88" s="11" t="inlineStr"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>454.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr"/>
       <c r="D89" s="8" t="inlineStr"/>
       <c r="E89" s="8" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr"/>
@@ -4671,7 +4877,7 @@
       <c r="H89" s="8" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>494.00</t>
+          <t>8195.00</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr"/>
@@ -4681,63 +4887,85 @@
       <c r="N89" s="8" t="inlineStr"/>
       <c r="O89" s="8" t="inlineStr">
         <is>
-          <t>418.00</t>
-        </is>
-      </c>
-      <c r="P89" s="8" t="inlineStr"/>
-      <c r="Q89" s="8" t="inlineStr"/>
-      <c r="R89" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
+          <t>8325.00</t>
+        </is>
+      </c>
+      <c r="P89" s="8" t="inlineStr">
+        <is>
+          <t>12890.00</t>
+        </is>
+      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>16980.00</t>
+        </is>
+      </c>
+      <c r="R89" s="8" t="inlineStr"/>
       <c r="S89" s="8" t="inlineStr"/>
-      <c r="T89" s="9" t="n">
-        <v>460.6666666666667</v>
-      </c>
-      <c r="U89" s="10" t="inlineStr"/>
-      <c r="V89" s="11" t="inlineStr"/>
+      <c r="T89" s="8" t="inlineStr"/>
+      <c r="U89" s="8" t="inlineStr"/>
+      <c r="V89" s="9" t="n">
+        <v>11597.5</v>
+      </c>
+      <c r="W89" s="9" t="n">
+        <v>2661.25</v>
+      </c>
+      <c r="X89" s="11" t="n">
+        <v>0.3397268143230995</v>
+      </c>
     </row>
     <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="1" t="n"/>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr"/>
-      <c r="D90" s="8" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr"/>
-      <c r="F90" s="8" t="inlineStr"/>
-      <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr"/>
-      <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr"/>
-      <c r="L90" s="8" t="inlineStr"/>
-      <c r="M90" s="8" t="inlineStr"/>
-      <c r="N90" s="8" t="inlineStr"/>
-      <c r="O90" s="8" t="inlineStr"/>
-      <c r="P90" s="8" t="inlineStr"/>
-      <c r="Q90" s="8" t="inlineStr"/>
-      <c r="R90" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="S90" s="8" t="inlineStr"/>
-      <c r="T90" s="9" t="inlineStr"/>
-      <c r="U90" s="10" t="inlineStr"/>
-      <c r="V90" s="11" t="inlineStr"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Seaquest
+Random: 68.4
+Human: 42054.7</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 525</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr"/>
+      <c r="N90" s="4" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr"/>
+      <c r="P90" s="4" t="inlineStr"/>
+      <c r="Q90" s="4" t="inlineStr"/>
+      <c r="R90" s="4" t="inlineStr"/>
+      <c r="S90" s="4" t="inlineStr"/>
+      <c r="T90" s="4" t="inlineStr"/>
+      <c r="U90" s="4" t="inlineStr"/>
+      <c r="V90" s="5" t="inlineStr"/>
+      <c r="W90" s="6" t="n">
+        <v>-64.33333333333331</v>
+      </c>
+      <c r="X90" s="7" t="n">
+        <v>-0.001532245835744834</v>
+      </c>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>454.00</t>
+        </is>
+      </c>
       <c r="D91" s="8" t="inlineStr"/>
       <c r="E91" s="8" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr"/>
@@ -4745,7 +4973,7 @@
       <c r="H91" s="8" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>521.00</t>
+          <t>494.00</t>
         </is>
       </c>
       <c r="J91" s="8" t="inlineStr"/>
@@ -4755,87 +4983,77 @@
       <c r="N91" s="8" t="inlineStr"/>
       <c r="O91" s="8" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>418.00</t>
         </is>
       </c>
       <c r="P91" s="8" t="inlineStr"/>
       <c r="Q91" s="8" t="inlineStr"/>
-      <c r="R91" s="8" t="inlineStr">
-        <is>
-          <t>545.00</t>
-        </is>
-      </c>
+      <c r="R91" s="8" t="inlineStr"/>
       <c r="S91" s="8" t="inlineStr"/>
-      <c r="T91" s="9" t="n">
-        <v>505.3333333333333</v>
-      </c>
-      <c r="U91" s="9" t="n">
-        <v>44.66666666666663</v>
-      </c>
-      <c r="V91" s="11" t="n">
-        <v>0.001063839077667397</v>
-      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>470.00</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="inlineStr"/>
+      <c r="V91" s="9" t="n">
+        <v>460.6666666666667</v>
+      </c>
+      <c r="W91" s="10" t="inlineStr"/>
+      <c r="X91" s="11" t="inlineStr"/>
     </row>
     <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>UpNDown
-Random: 533.4
-Human: 11693.2</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7985</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr"/>
-      <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr"/>
-      <c r="K92" s="4" t="inlineStr"/>
-      <c r="L92" s="4" t="inlineStr"/>
-      <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr"/>
-      <c r="O92" s="4" t="inlineStr"/>
-      <c r="P92" s="4" t="inlineStr"/>
-      <c r="Q92" s="4" t="inlineStr"/>
-      <c r="R92" s="4" t="inlineStr"/>
-      <c r="S92" s="4" t="inlineStr"/>
-      <c r="T92" s="5" t="inlineStr"/>
-      <c r="U92" s="6" t="n">
-        <v>-2963</v>
-      </c>
-      <c r="V92" s="7" t="n">
-        <v>-0.2655065502966003</v>
-      </c>
+      <c r="A92" s="1" t="n"/>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr"/>
+      <c r="D92" s="8" t="inlineStr"/>
+      <c r="E92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr"/>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr"/>
+      <c r="L92" s="8" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr"/>
+      <c r="N92" s="8" t="inlineStr"/>
+      <c r="O92" s="8" t="inlineStr"/>
+      <c r="P92" s="8" t="inlineStr"/>
+      <c r="Q92" s="8" t="inlineStr"/>
+      <c r="R92" s="8" t="inlineStr"/>
+      <c r="S92" s="8" t="inlineStr"/>
+      <c r="T92" s="8" t="inlineStr">
+        <is>
+          <t>557.00</t>
+        </is>
+      </c>
+      <c r="U92" s="8" t="inlineStr"/>
+      <c r="V92" s="9" t="inlineStr"/>
+      <c r="W92" s="10" t="inlineStr"/>
+      <c r="X92" s="11" t="inlineStr"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>9044.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr"/>
       <c r="D93" s="8" t="inlineStr"/>
       <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr"/>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>5849.00</t>
-        </is>
-      </c>
+      <c r="G93" s="8" t="inlineStr"/>
       <c r="H93" s="8" t="inlineStr"/>
-      <c r="I93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>521.00</t>
+        </is>
+      </c>
       <c r="J93" s="8" t="inlineStr"/>
       <c r="K93" s="8" t="inlineStr"/>
       <c r="L93" s="8" t="inlineStr"/>
@@ -4843,79 +5061,89 @@
       <c r="N93" s="8" t="inlineStr"/>
       <c r="O93" s="8" t="inlineStr">
         <is>
-          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
-        </is>
-      </c>
-      <c r="P93" s="8" t="inlineStr">
-        <is>
-          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
-        </is>
-      </c>
-      <c r="Q93" s="8" t="inlineStr">
-        <is>
-          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
-        </is>
-      </c>
+          <t>450.00</t>
+        </is>
+      </c>
+      <c r="P93" s="8" t="inlineStr"/>
+      <c r="Q93" s="8" t="inlineStr"/>
       <c r="R93" s="8" t="inlineStr"/>
       <c r="S93" s="8" t="inlineStr"/>
-      <c r="T93" s="9" t="n">
-        <v>5022</v>
-      </c>
-      <c r="U93" s="10" t="inlineStr"/>
-      <c r="V93" s="11" t="inlineStr"/>
+      <c r="T93" s="8" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
+      <c r="U93" s="8" t="inlineStr"/>
+      <c r="V93" s="9" t="n">
+        <v>505.3333333333333</v>
+      </c>
+      <c r="W93" s="9" t="n">
+        <v>44.66666666666663</v>
+      </c>
+      <c r="X93" s="11" t="n">
+        <v>0.001063839077667397</v>
+      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="1" t="n"/>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr"/>
-      <c r="D94" s="8" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr"/>
-      <c r="F94" s="8" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr"/>
-      <c r="L94" s="8" t="inlineStr"/>
-      <c r="M94" s="8" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
-      <c r="O94" s="8" t="inlineStr">
-        <is>
-          <t>5670.00</t>
-        </is>
-      </c>
-      <c r="P94" s="8" t="inlineStr">
-        <is>
-          <t>7178.00</t>
-        </is>
-      </c>
-      <c r="Q94" s="8" t="inlineStr">
-        <is>
-          <t>3066.00</t>
-        </is>
-      </c>
-      <c r="R94" s="8" t="inlineStr"/>
-      <c r="S94" s="8" t="inlineStr"/>
-      <c r="T94" s="9" t="inlineStr"/>
-      <c r="U94" s="10" t="inlineStr"/>
-      <c r="V94" s="11" t="inlineStr"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>UpNDown
+Random: 533.4
+Human: 11693.2</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 7985</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
+      <c r="D94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr"/>
+      <c r="P94" s="4" t="inlineStr"/>
+      <c r="Q94" s="4" t="inlineStr"/>
+      <c r="R94" s="4" t="inlineStr"/>
+      <c r="S94" s="4" t="inlineStr"/>
+      <c r="T94" s="4" t="inlineStr"/>
+      <c r="U94" s="4" t="inlineStr"/>
+      <c r="V94" s="5" t="inlineStr"/>
+      <c r="W94" s="6" t="n">
+        <v>-2963</v>
+      </c>
+      <c r="X94" s="7" t="n">
+        <v>-0.2655065502966003</v>
+      </c>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>9044.00</t>
+        </is>
+      </c>
       <c r="D95" s="8" t="inlineStr"/>
       <c r="E95" s="8" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr"/>
-      <c r="G95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>5849.00</t>
+        </is>
+      </c>
       <c r="H95" s="8" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr"/>
       <c r="J95" s="8" t="inlineStr"/>
@@ -4925,59 +5153,147 @@
       <c r="N95" s="8" t="inlineStr"/>
       <c r="O95" s="8" t="inlineStr">
         <is>
-          <t>6043.00</t>
+          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
         </is>
       </c>
       <c r="P95" s="8" t="inlineStr">
         <is>
-          <t>6658.00</t>
+          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
         </is>
       </c>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>2974.50</t>
+          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
         </is>
       </c>
       <c r="R95" s="8" t="inlineStr"/>
       <c r="S95" s="8" t="inlineStr"/>
-      <c r="T95" s="9" t="n">
+      <c r="T95" s="8" t="inlineStr"/>
+      <c r="U95" s="8" t="inlineStr"/>
+      <c r="V95" s="9" t="n">
+        <v>5022</v>
+      </c>
+      <c r="W95" s="10" t="inlineStr"/>
+      <c r="X95" s="11" t="inlineStr"/>
+    </row>
+    <row r="96" ht="24" customHeight="1">
+      <c r="A96" s="1" t="n"/>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr"/>
+      <c r="D96" s="8" t="inlineStr"/>
+      <c r="E96" s="8" t="inlineStr"/>
+      <c r="F96" s="8" t="inlineStr"/>
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr"/>
+      <c r="J96" s="8" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr"/>
+      <c r="N96" s="8" t="inlineStr"/>
+      <c r="O96" s="8" t="inlineStr">
+        <is>
+          <t>5670.00</t>
+        </is>
+      </c>
+      <c r="P96" s="8" t="inlineStr">
+        <is>
+          <t>7178.00</t>
+        </is>
+      </c>
+      <c r="Q96" s="8" t="inlineStr">
+        <is>
+          <t>3066.00</t>
+        </is>
+      </c>
+      <c r="R96" s="8" t="inlineStr"/>
+      <c r="S96" s="8" t="inlineStr"/>
+      <c r="T96" s="8" t="inlineStr"/>
+      <c r="U96" s="8" t="inlineStr"/>
+      <c r="V96" s="9" t="inlineStr"/>
+      <c r="W96" s="10" t="inlineStr"/>
+      <c r="X96" s="11" t="inlineStr"/>
+    </row>
+    <row r="97" ht="24" customHeight="1">
+      <c r="A97" s="1" t="n"/>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr"/>
+      <c r="D97" s="8" t="inlineStr"/>
+      <c r="E97" s="8" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr"/>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr"/>
+      <c r="J97" s="8" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr"/>
+      <c r="L97" s="8" t="inlineStr"/>
+      <c r="M97" s="8" t="inlineStr"/>
+      <c r="N97" s="8" t="inlineStr"/>
+      <c r="O97" s="8" t="inlineStr">
+        <is>
+          <t>6043.00</t>
+        </is>
+      </c>
+      <c r="P97" s="8" t="inlineStr">
+        <is>
+          <t>6658.00</t>
+        </is>
+      </c>
+      <c r="Q97" s="8" t="inlineStr">
+        <is>
+          <t>2974.50</t>
+        </is>
+      </c>
+      <c r="R97" s="8" t="inlineStr"/>
+      <c r="S97" s="8" t="inlineStr"/>
+      <c r="T97" s="8" t="inlineStr"/>
+      <c r="U97" s="8" t="inlineStr"/>
+      <c r="V97" s="9" t="n">
         <v>5225.166666666667</v>
       </c>
-      <c r="U95" s="9" t="n">
+      <c r="W97" s="9" t="n">
         <v>203.166666666667</v>
       </c>
-      <c r="V95" s="11" t="n">
+      <c r="X97" s="11" t="n">
         <v>0.01820522470534122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A76:A78"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="A90:A93"/>
     <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="A86:A89"/>
     <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="A73:A75"/>
     <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A51:A53"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A54:A56"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A62:A65"/>
     <mergeCell ref="A47:A50"/>
-    <mergeCell ref="A74:A76"/>
     <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A58:A61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -268,13 +268,6 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E48" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
     <comment ref="E49" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
@@ -289,16 +282,9 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O52" authorId="0" shapeId="0">
+    <comment ref="E51" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="T52" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -331,9 +317,16 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I67" authorId="0" shapeId="0">
+    <comment ref="O55" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="T55" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -346,6 +339,13 @@
       </text>
     </comment>
     <comment ref="I69" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I70" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
 STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X97"/>
+  <dimension ref="A1:X98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
@@ -1625,7 +1625,11 @@
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr"/>
-      <c r="S19" s="8" t="inlineStr"/>
+      <c r="S19" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
           <t>668.50</t>
@@ -1707,7 +1711,11 @@
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr"/>
-      <c r="S21" s="8" t="inlineStr"/>
+      <c r="S21" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
           <t>565.00</t>
@@ -1964,10 +1972,10 @@
       <c r="U26" s="4" t="inlineStr"/>
       <c r="V26" s="5" t="inlineStr"/>
       <c r="W26" s="6" t="n">
-        <v>-5.549999999999997</v>
+        <v>-3</v>
       </c>
       <c r="X26" s="7" t="n">
-        <v>-0.4624999999999997</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
@@ -2015,9 +2023,9 @@
           <t>77.80</t>
         </is>
       </c>
-      <c r="Q27" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>87.20</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr"/>
@@ -2025,7 +2033,7 @@
       <c r="T27" s="8" t="inlineStr"/>
       <c r="U27" s="8" t="inlineStr"/>
       <c r="V27" s="9" t="n">
-        <v>74.45</v>
+        <v>77</v>
       </c>
       <c r="W27" s="10" t="inlineStr"/>
       <c r="X27" s="11" t="inlineStr"/>
@@ -2111,13 +2119,13 @@
       <c r="T29" s="8" t="inlineStr"/>
       <c r="U29" s="8" t="inlineStr"/>
       <c r="V29" s="9" t="n">
-        <v>72.71250000000001</v>
+        <v>75.75</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>1.737499999999997</v>
+        <v>1.25</v>
       </c>
       <c r="X29" s="11" t="n">
-        <v>-0.1447916666666664</v>
+        <v>-0.1041666666666667</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
@@ -2840,7 +2848,7 @@
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr"/>
@@ -2855,145 +2863,127 @@
       <c r="L46" s="8" t="inlineStr"/>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
-      <c r="O46" s="8" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="P46" s="8" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
+      <c r="O46" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="P46" s="8" t="inlineStr"/>
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr"/>
       <c r="T46" s="8" t="inlineStr"/>
       <c r="U46" s="8" t="inlineStr"/>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="9" t="inlineStr"/>
+      <c r="W46" s="10" t="inlineStr"/>
+      <c r="X46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr"/>
+      <c r="D47" s="8" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="inlineStr"/>
+      <c r="M47" s="8" t="inlineStr"/>
+      <c r="N47" s="8" t="inlineStr"/>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>33.55</t>
+        </is>
+      </c>
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="Q47" s="8" t="inlineStr"/>
+      <c r="R47" s="8" t="inlineStr"/>
+      <c r="S47" s="8" t="inlineStr"/>
+      <c r="T47" s="8" t="inlineStr"/>
+      <c r="U47" s="8" t="inlineStr"/>
+      <c r="V47" s="9" t="n">
         <v>33.15</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W47" s="9" t="n">
         <v>0.1499999999999986</v>
       </c>
-      <c r="X46" s="11" t="n">
+      <c r="X47" s="11" t="n">
         <v>-0.005067567567567519</v>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Frostbite
 Random: 65.2
 Human: 4334.7</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 1316</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr"/>
-      <c r="D47" s="4" t="inlineStr"/>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="4" t="inlineStr"/>
-      <c r="N47" s="4" t="inlineStr"/>
-      <c r="O47" s="4" t="inlineStr"/>
-      <c r="P47" s="4" t="inlineStr"/>
-      <c r="Q47" s="4" t="inlineStr"/>
-      <c r="R47" s="4" t="inlineStr"/>
-      <c r="S47" s="4" t="inlineStr"/>
-      <c r="T47" s="4" t="inlineStr"/>
-      <c r="U47" s="4" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr"/>
-      <c r="W47" s="6" t="n">
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr"/>
+      <c r="Q48" s="4" t="inlineStr"/>
+      <c r="R48" s="4" t="inlineStr"/>
+      <c r="S48" s="4" t="inlineStr"/>
+      <c r="T48" s="4" t="inlineStr"/>
+      <c r="U48" s="4" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr"/>
+      <c r="W48" s="6" t="n">
         <v>491.5</v>
       </c>
-      <c r="X47" s="7" t="n">
+      <c r="X48" s="7" t="n">
         <v>0.115118866377796</v>
       </c>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr"/>
-      <c r="D48" s="8" t="inlineStr"/>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>2068.00</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>2270.50</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>1904.00</t>
-        </is>
-      </c>
-      <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="8" t="inlineStr"/>
-      <c r="J48" s="8" t="inlineStr"/>
-      <c r="K48" s="8" t="inlineStr"/>
-      <c r="L48" s="8" t="inlineStr"/>
-      <c r="M48" s="8" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
-      <c r="O48" s="8" t="inlineStr">
-        <is>
-          <t>2544.50, 2833.50, 2600.50, 2639.00</t>
-        </is>
-      </c>
-      <c r="P48" s="8" t="inlineStr">
-        <is>
-          <t>250.50, 252.50, 255.00, 255.00</t>
-        </is>
-      </c>
-      <c r="Q48" s="8" t="inlineStr"/>
-      <c r="R48" s="8" t="inlineStr"/>
-      <c r="S48" s="8" t="inlineStr"/>
-      <c r="T48" s="8" t="inlineStr"/>
-      <c r="U48" s="8" t="inlineStr"/>
-      <c r="V48" s="9" t="n">
-        <v>1807.5</v>
-      </c>
-      <c r="W48" s="10" t="inlineStr"/>
-      <c r="X48" s="11" t="inlineStr"/>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr"/>
       <c r="D49" s="8" t="inlineStr"/>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>2301.00</t>
+          <t>2068.00</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>2609.00</t>
+          <t>2270.50</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>3242.50</t>
+          <t>1904.00</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr"/>
@@ -3005,12 +2995,12 @@
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="8" t="inlineStr">
         <is>
-          <t>2119.50</t>
+          <t>2544.50, 2833.50, 2600.50, 2639.00</t>
         </is>
       </c>
       <c r="P49" s="8" t="inlineStr">
         <is>
-          <t>261.50</t>
+          <t>250.50, 252.50, 255.00, 255.00</t>
         </is>
       </c>
       <c r="Q49" s="8" t="inlineStr"/>
@@ -3018,7 +3008,9 @@
       <c r="S49" s="8" t="inlineStr"/>
       <c r="T49" s="8" t="inlineStr"/>
       <c r="U49" s="8" t="inlineStr"/>
-      <c r="V49" s="9" t="inlineStr"/>
+      <c r="V49" s="9" t="n">
+        <v>1807.5</v>
+      </c>
       <c r="W49" s="10" t="inlineStr"/>
       <c r="X49" s="11" t="inlineStr"/>
     </row>
@@ -3026,24 +3018,24 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr"/>
       <c r="D50" s="8" t="inlineStr"/>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>2113.50, 2350.50</t>
+          <t>2301.00</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>2443.00</t>
+          <t>2609.00</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>2779.00</t>
+          <t>3242.50</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr"/>
@@ -3051,24 +3043,16 @@
       <c r="J50" s="8" t="inlineStr"/>
       <c r="K50" s="8" t="inlineStr"/>
       <c r="L50" s="8" t="inlineStr"/>
-      <c r="M50" s="8" t="inlineStr">
-        <is>
-          <t>283.50</t>
-        </is>
-      </c>
-      <c r="N50" s="8" t="inlineStr">
-        <is>
-          <t>252.00</t>
-        </is>
-      </c>
+      <c r="M50" s="8" t="inlineStr"/>
+      <c r="N50" s="8" t="inlineStr"/>
       <c r="O50" s="8" t="inlineStr">
         <is>
-          <t>2474.00</t>
+          <t>2119.50</t>
         </is>
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>251.00</t>
+          <t>261.50</t>
         </is>
       </c>
       <c r="Q50" s="8" t="inlineStr"/>
@@ -3076,136 +3060,146 @@
       <c r="S50" s="8" t="inlineStr"/>
       <c r="T50" s="8" t="inlineStr"/>
       <c r="U50" s="8" t="inlineStr"/>
-      <c r="V50" s="9" t="n">
+      <c r="V50" s="9" t="inlineStr"/>
+      <c r="W50" s="10" t="inlineStr"/>
+      <c r="X50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr"/>
+      <c r="D51" s="8" t="inlineStr"/>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>2113.50, 2350.50</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>2443.00</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>2779.00</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr"/>
+      <c r="J51" s="8" t="inlineStr"/>
+      <c r="K51" s="8" t="inlineStr"/>
+      <c r="L51" s="8" t="inlineStr"/>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>283.50</t>
+        </is>
+      </c>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>252.00</t>
+        </is>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>2474.00</t>
+        </is>
+      </c>
+      <c r="P51" s="8" t="inlineStr">
+        <is>
+          <t>251.00</t>
+        </is>
+      </c>
+      <c r="Q51" s="8" t="inlineStr"/>
+      <c r="R51" s="8" t="inlineStr"/>
+      <c r="S51" s="8" t="inlineStr"/>
+      <c r="T51" s="8" t="inlineStr"/>
+      <c r="U51" s="8" t="inlineStr"/>
+      <c r="V51" s="9" t="n">
         <v>2012.1</v>
       </c>
-      <c r="W50" s="9" t="n">
+      <c r="W51" s="9" t="n">
         <v>204.5999999999999</v>
       </c>
-      <c r="X50" s="11" t="n">
+      <c r="X51" s="11" t="n">
         <v>0.0479213022602178</v>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Gopher
 Random: 257.6
 Human: 2412.5</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 8240</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr"/>
-      <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="4" t="inlineStr"/>
-      <c r="K51" s="4" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="4" t="inlineStr"/>
-      <c r="N51" s="4" t="inlineStr"/>
-      <c r="O51" s="4" t="inlineStr"/>
-      <c r="P51" s="4" t="inlineStr"/>
-      <c r="Q51" s="4" t="inlineStr"/>
-      <c r="R51" s="4" t="inlineStr"/>
-      <c r="S51" s="4" t="inlineStr"/>
-      <c r="T51" s="4" t="inlineStr"/>
-      <c r="U51" s="4" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr"/>
-      <c r="W51" s="6" t="n">
-        <v>-5475.2</v>
-      </c>
-      <c r="X51" s="7" t="n">
-        <v>-2.540813958884403</v>
-      </c>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>5968.00</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>3752.00</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>3275.00</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>3914.00</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>4219.00</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="8" t="inlineStr"/>
-      <c r="J52" s="8" t="inlineStr"/>
-      <c r="K52" s="8" t="inlineStr"/>
-      <c r="L52" s="8" t="inlineStr"/>
-      <c r="M52" s="8" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
-      <c r="O52" s="12" t="inlineStr">
-        <is>
-          <t>2486.00</t>
-        </is>
-      </c>
-      <c r="P52" s="8" t="inlineStr">
-        <is>
-          <t>1250.00</t>
-        </is>
-      </c>
-      <c r="Q52" s="8" t="inlineStr"/>
-      <c r="R52" s="8" t="inlineStr"/>
-      <c r="S52" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="T52" s="12" t="inlineStr">
-        <is>
-          <t>2594.00</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr"/>
-      <c r="V52" s="9" t="n">
-        <v>2764.8</v>
-      </c>
-      <c r="W52" s="10" t="inlineStr"/>
-      <c r="X52" s="11" t="inlineStr"/>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr"/>
+      <c r="P52" s="4" t="inlineStr"/>
+      <c r="Q52" s="4" t="inlineStr"/>
+      <c r="R52" s="4" t="inlineStr"/>
+      <c r="S52" s="4" t="inlineStr"/>
+      <c r="T52" s="4" t="inlineStr"/>
+      <c r="U52" s="4" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr"/>
+      <c r="W52" s="6" t="n">
+        <v>-5338.5</v>
+      </c>
+      <c r="X52" s="7" t="n">
+        <v>-2.477377140470555</v>
+      </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr"/>
-      <c r="D53" s="8" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr"/>
-      <c r="F53" s="8" t="inlineStr"/>
-      <c r="G53" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>5968.00</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>3752.00</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>3275.00</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>3914.00</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>4219.00</t>
+        </is>
+      </c>
       <c r="H53" s="8" t="inlineStr"/>
       <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr"/>
@@ -3213,18 +3207,32 @@
       <c r="L53" s="8" t="inlineStr"/>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
-      <c r="O53" s="12" t="inlineStr"/>
-      <c r="P53" s="8" t="inlineStr"/>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>2486.00</t>
+        </is>
+      </c>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
       <c r="Q53" s="8" t="inlineStr"/>
-      <c r="R53" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="S53" s="8" t="inlineStr"/>
-      <c r="T53" s="12" t="inlineStr"/>
+      <c r="R53" s="8" t="inlineStr"/>
+      <c r="S53" s="8" t="inlineStr">
+        <is>
+          <t>3585.00</t>
+        </is>
+      </c>
+      <c r="T53" s="12" t="inlineStr">
+        <is>
+          <t>2594.00</t>
+        </is>
+      </c>
       <c r="U53" s="8" t="inlineStr"/>
-      <c r="V53" s="9" t="inlineStr"/>
+      <c r="V53" s="9" t="n">
+        <v>2901.5</v>
+      </c>
       <c r="W53" s="10" t="inlineStr"/>
       <c r="X53" s="11" t="inlineStr"/>
     </row>
@@ -3232,22 +3240,14 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr"/>
       <c r="D54" s="8" t="inlineStr"/>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>3327.00</t>
-        </is>
-      </c>
+      <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr"/>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>3829.00</t>
-        </is>
-      </c>
+      <c r="G54" s="8" t="inlineStr"/>
       <c r="H54" s="8" t="inlineStr"/>
       <c r="I54" s="8" t="inlineStr"/>
       <c r="J54" s="8" t="inlineStr"/>
@@ -3255,153 +3255,147 @@
       <c r="L54" s="8" t="inlineStr"/>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
-      <c r="O54" s="12" t="inlineStr">
+      <c r="O54" s="12" t="inlineStr"/>
+      <c r="P54" s="8" t="inlineStr"/>
+      <c r="Q54" s="8" t="inlineStr"/>
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="S54" s="8" t="inlineStr"/>
+      <c r="T54" s="12" t="inlineStr"/>
+      <c r="U54" s="8" t="inlineStr"/>
+      <c r="V54" s="9" t="inlineStr"/>
+      <c r="W54" s="10" t="inlineStr"/>
+      <c r="X54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr"/>
+      <c r="D55" s="8" t="inlineStr"/>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>3327.00</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr"/>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>3829.00</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr"/>
+      <c r="J55" s="8" t="inlineStr"/>
+      <c r="K55" s="8" t="inlineStr"/>
+      <c r="L55" s="8" t="inlineStr"/>
+      <c r="M55" s="8" t="inlineStr"/>
+      <c r="N55" s="8" t="inlineStr"/>
+      <c r="O55" s="12" t="inlineStr">
         <is>
           <t>1024.00</t>
         </is>
       </c>
-      <c r="P54" s="8" t="inlineStr">
+      <c r="P55" s="8" t="inlineStr">
         <is>
           <t>927.00</t>
         </is>
       </c>
-      <c r="Q54" s="8" t="inlineStr">
-        <is>
-          <t>972.00</t>
-        </is>
-      </c>
-      <c r="R54" s="8" t="inlineStr"/>
-      <c r="S54" s="8" t="inlineStr">
+      <c r="Q55" s="8" t="inlineStr"/>
+      <c r="R55" s="8" t="inlineStr"/>
+      <c r="S55" s="8" t="inlineStr">
         <is>
           <t>7531.00</t>
         </is>
       </c>
-      <c r="T54" s="12" t="inlineStr">
+      <c r="T55" s="12" t="inlineStr">
         <is>
           <t>1005.00</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr"/>
-      <c r="V54" s="9" t="n">
-        <v>2022.4</v>
-      </c>
-      <c r="W54" s="9" t="n">
-        <v>742.4000000000001</v>
-      </c>
-      <c r="X54" s="11" t="n">
-        <v>-0.3445171469673767</v>
-      </c>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="U55" s="8" t="inlineStr"/>
+      <c r="V55" s="9" t="n">
+        <v>2940.5</v>
+      </c>
+      <c r="W55" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="X55" s="11" t="n">
+        <v>0.01809828762355562</v>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Hero
 Random: 1027.0
 Human: 30826.4</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 11044</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr"/>
-      <c r="D55" s="4" t="inlineStr"/>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr"/>
-      <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr"/>
-      <c r="M55" s="4" t="inlineStr"/>
-      <c r="N55" s="4" t="inlineStr"/>
-      <c r="O55" s="4" t="inlineStr"/>
-      <c r="P55" s="4" t="inlineStr"/>
-      <c r="Q55" s="4" t="inlineStr"/>
-      <c r="R55" s="4" t="inlineStr"/>
-      <c r="S55" s="4" t="inlineStr"/>
-      <c r="T55" s="4" t="inlineStr"/>
-      <c r="U55" s="4" t="inlineStr"/>
-      <c r="V55" s="5" t="inlineStr"/>
-      <c r="W55" s="6" t="n">
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr"/>
+      <c r="P56" s="4" t="inlineStr"/>
+      <c r="Q56" s="4" t="inlineStr"/>
+      <c r="R56" s="4" t="inlineStr"/>
+      <c r="S56" s="4" t="inlineStr"/>
+      <c r="T56" s="4" t="inlineStr"/>
+      <c r="U56" s="4" t="inlineStr"/>
+      <c r="V56" s="5" t="inlineStr"/>
+      <c r="W56" s="6" t="n">
         <v>2134</v>
       </c>
-      <c r="X55" s="7" t="n">
+      <c r="X56" s="7" t="n">
         <v>0.07161218011100895</v>
       </c>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>7608.50</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr"/>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>12996.75</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>13456.25</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
-        <is>
-          <t>13081.00</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="inlineStr"/>
-      <c r="I56" s="8" t="inlineStr"/>
-      <c r="J56" s="8" t="inlineStr"/>
-      <c r="K56" s="8" t="inlineStr"/>
-      <c r="L56" s="8" t="inlineStr"/>
-      <c r="M56" s="8" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr"/>
-      <c r="O56" s="8" t="inlineStr"/>
-      <c r="P56" s="8" t="inlineStr"/>
-      <c r="Q56" s="8" t="inlineStr"/>
-      <c r="R56" s="8" t="inlineStr"/>
-      <c r="S56" s="8" t="inlineStr"/>
-      <c r="T56" s="8" t="inlineStr"/>
-      <c r="U56" s="8" t="inlineStr"/>
-      <c r="V56" s="9" t="n">
-        <v>13178</v>
-      </c>
-      <c r="W56" s="10" t="inlineStr"/>
-      <c r="X56" s="11" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>7608.50</t>
+        </is>
+      </c>
       <c r="D57" s="8" t="inlineStr"/>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>13251.25</t>
+          <t>12996.75</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>13231.50</t>
+          <t>13456.25</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>13325.50</t>
+          <t>13081.00</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr"/>
@@ -3419,134 +3413,144 @@
       <c r="T57" s="8" t="inlineStr"/>
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="9" t="n">
+        <v>13178</v>
+      </c>
+      <c r="W57" s="10" t="inlineStr"/>
+      <c r="X57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr"/>
+      <c r="D58" s="8" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>13251.25</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>13231.50</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>13325.50</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr"/>
+      <c r="J58" s="8" t="inlineStr"/>
+      <c r="K58" s="8" t="inlineStr"/>
+      <c r="L58" s="8" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
+      <c r="N58" s="8" t="inlineStr"/>
+      <c r="O58" s="8" t="inlineStr"/>
+      <c r="P58" s="8" t="inlineStr"/>
+      <c r="Q58" s="8" t="inlineStr"/>
+      <c r="R58" s="8" t="inlineStr"/>
+      <c r="S58" s="8" t="inlineStr"/>
+      <c r="T58" s="8" t="inlineStr"/>
+      <c r="U58" s="8" t="inlineStr"/>
+      <c r="V58" s="9" t="n">
         <v>13269.41666666667</v>
       </c>
-      <c r="W57" s="9" t="n">
+      <c r="W58" s="9" t="n">
         <v>91.41666666666606</v>
       </c>
-      <c r="X57" s="11" t="n">
+      <c r="X58" s="11" t="n">
         <v>0.003067735144555463</v>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Jamesbond
 Random: 29.0
 Human: 302.8</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 509</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr"/>
-      <c r="O58" s="4" t="inlineStr"/>
-      <c r="P58" s="4" t="inlineStr"/>
-      <c r="Q58" s="4" t="inlineStr"/>
-      <c r="R58" s="4" t="inlineStr"/>
-      <c r="S58" s="4" t="inlineStr"/>
-      <c r="T58" s="4" t="inlineStr"/>
-      <c r="U58" s="4" t="inlineStr"/>
-      <c r="V58" s="5" t="inlineStr"/>
-      <c r="W58" s="6" t="n">
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="4" t="inlineStr"/>
+      <c r="Q59" s="4" t="inlineStr"/>
+      <c r="R59" s="4" t="inlineStr"/>
+      <c r="S59" s="4" t="inlineStr"/>
+      <c r="T59" s="4" t="inlineStr"/>
+      <c r="U59" s="4" t="inlineStr"/>
+      <c r="V59" s="5" t="inlineStr"/>
+      <c r="W59" s="6" t="n">
         <v>-35.66666666666669</v>
       </c>
-      <c r="X58" s="7" t="n">
+      <c r="X59" s="7" t="n">
         <v>-0.1302654005356709</v>
       </c>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="1" t="n"/>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>490.00</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr"/>
-      <c r="F59" s="8" t="inlineStr"/>
-      <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="8" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>532.50, 537.50</t>
-        </is>
-      </c>
-      <c r="J59" s="8" t="inlineStr"/>
-      <c r="K59" s="8" t="inlineStr"/>
-      <c r="L59" s="8" t="inlineStr"/>
-      <c r="M59" s="8" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr"/>
-      <c r="O59" s="8" t="inlineStr">
-        <is>
-          <t>522.50</t>
-        </is>
-      </c>
-      <c r="P59" s="8" t="inlineStr"/>
-      <c r="Q59" s="8" t="inlineStr"/>
-      <c r="R59" s="8" t="inlineStr"/>
-      <c r="S59" s="8" t="inlineStr"/>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr"/>
-      <c r="V59" s="9" t="n">
-        <v>473.3333333333333</v>
-      </c>
-      <c r="W59" s="10" t="inlineStr"/>
-      <c r="X59" s="11" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>490.00</t>
+        </is>
+      </c>
       <c r="D60" s="8" t="inlineStr"/>
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr"/>
       <c r="G60" s="8" t="inlineStr"/>
       <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>532.50, 537.50</t>
+        </is>
+      </c>
       <c r="J60" s="8" t="inlineStr"/>
       <c r="K60" s="8" t="inlineStr"/>
       <c r="L60" s="8" t="inlineStr"/>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
-      <c r="O60" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="O60" s="8" t="inlineStr">
+        <is>
+          <t>522.50</t>
         </is>
       </c>
       <c r="P60" s="8" t="inlineStr"/>
       <c r="Q60" s="8" t="inlineStr"/>
       <c r="R60" s="8" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr"/>
-      <c r="T60" s="8" t="inlineStr"/>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>365.00</t>
+        </is>
+      </c>
       <c r="U60" s="8" t="inlineStr"/>
-      <c r="V60" s="9" t="inlineStr"/>
+      <c r="V60" s="9" t="n">
+        <v>473.3333333333333</v>
+      </c>
       <c r="W60" s="10" t="inlineStr"/>
       <c r="X60" s="11" t="inlineStr"/>
     </row>
@@ -3554,7 +3558,7 @@
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr"/>
@@ -3563,164 +3567,154 @@
       <c r="F61" s="8" t="inlineStr"/>
       <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="8" t="inlineStr"/>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>567.50, 660.00</t>
-        </is>
-      </c>
+      <c r="I61" s="8" t="inlineStr"/>
       <c r="J61" s="8" t="inlineStr"/>
       <c r="K61" s="8" t="inlineStr"/>
       <c r="L61" s="8" t="inlineStr"/>
       <c r="M61" s="8" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="8" t="inlineStr">
-        <is>
-          <t>665.00</t>
+      <c r="O61" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
         </is>
       </c>
       <c r="P61" s="8" t="inlineStr"/>
       <c r="Q61" s="8" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr"/>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="T61" s="8" t="inlineStr"/>
+      <c r="U61" s="8" t="inlineStr"/>
+      <c r="V61" s="9" t="inlineStr"/>
+      <c r="W61" s="10" t="inlineStr"/>
+      <c r="X61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="1" t="n"/>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr"/>
+      <c r="D62" s="8" t="inlineStr"/>
+      <c r="E62" s="8" t="inlineStr"/>
+      <c r="F62" s="8" t="inlineStr"/>
+      <c r="G62" s="8" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>567.50, 660.00</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr"/>
+      <c r="K62" s="8" t="inlineStr"/>
+      <c r="L62" s="8" t="inlineStr"/>
+      <c r="M62" s="8" t="inlineStr"/>
+      <c r="N62" s="8" t="inlineStr"/>
+      <c r="O62" s="8" t="inlineStr">
+        <is>
+          <t>665.00</t>
+        </is>
+      </c>
+      <c r="P62" s="8" t="inlineStr"/>
+      <c r="Q62" s="8" t="inlineStr"/>
+      <c r="R62" s="8" t="inlineStr"/>
+      <c r="S62" s="8" t="inlineStr"/>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>375.00</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr"/>
-      <c r="V61" s="9" t="n">
+      <c r="U62" s="8" t="inlineStr"/>
+      <c r="V62" s="9" t="n">
         <v>535.8333333333334</v>
       </c>
-      <c r="W61" s="9" t="n">
+      <c r="W62" s="9" t="n">
         <v>62.50000000000006</v>
       </c>
-      <c r="X61" s="11" t="n">
+      <c r="X62" s="11" t="n">
         <v>0.2282688093498906</v>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Kangaroo
 Random: 52.0
 Human: 3035.0</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 4208</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr"/>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr"/>
-      <c r="O62" s="4" t="inlineStr"/>
-      <c r="P62" s="4" t="inlineStr"/>
-      <c r="Q62" s="4" t="inlineStr"/>
-      <c r="R62" s="4" t="inlineStr"/>
-      <c r="S62" s="4" t="inlineStr"/>
-      <c r="T62" s="4" t="inlineStr"/>
-      <c r="U62" s="4" t="inlineStr"/>
-      <c r="V62" s="5" t="inlineStr"/>
-      <c r="W62" s="6" t="n">
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
+      <c r="J63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr"/>
+      <c r="L63" s="4" t="inlineStr"/>
+      <c r="M63" s="4" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr"/>
+      <c r="Q63" s="4" t="inlineStr"/>
+      <c r="R63" s="4" t="inlineStr"/>
+      <c r="S63" s="4" t="inlineStr"/>
+      <c r="T63" s="4" t="inlineStr"/>
+      <c r="U63" s="4" t="inlineStr"/>
+      <c r="V63" s="5" t="inlineStr"/>
+      <c r="W63" s="6" t="n">
         <v>-2778</v>
       </c>
-      <c r="X62" s="7" t="n">
+      <c r="X63" s="7" t="n">
         <v>-0.9312772376801878</v>
       </c>
-    </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="1" t="n"/>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr"/>
-      <c r="D63" s="8" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>1770.00</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr"/>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr"/>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="J63" s="8" t="inlineStr">
-        <is>
-          <t>1730.00</t>
-        </is>
-      </c>
-      <c r="K63" s="8" t="inlineStr"/>
-      <c r="L63" s="8" t="inlineStr"/>
-      <c r="M63" s="8" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
-      <c r="O63" s="8" t="inlineStr">
-        <is>
-          <t>1550.00</t>
-        </is>
-      </c>
-      <c r="P63" s="8" t="inlineStr">
-        <is>
-          <t>930.00</t>
-        </is>
-      </c>
-      <c r="Q63" s="8" t="inlineStr"/>
-      <c r="R63" s="8" t="inlineStr"/>
-      <c r="S63" s="8" t="inlineStr"/>
-      <c r="T63" s="8" t="inlineStr"/>
-      <c r="U63" s="8" t="inlineStr"/>
-      <c r="V63" s="9" t="n">
-        <v>1430</v>
-      </c>
-      <c r="W63" s="10" t="inlineStr"/>
-      <c r="X63" s="11" t="inlineStr"/>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr"/>
       <c r="D64" s="8" t="inlineStr"/>
-      <c r="E64" s="8" t="inlineStr"/>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>1770.00</t>
+        </is>
+      </c>
       <c r="F64" s="8" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr"/>
       <c r="H64" s="8" t="inlineStr"/>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>1310.00</t>
-        </is>
-      </c>
-      <c r="J64" s="8" t="inlineStr"/>
+          <t>1470.00</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>1730.00</t>
+        </is>
+      </c>
       <c r="K64" s="8" t="inlineStr"/>
       <c r="L64" s="8" t="inlineStr"/>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
       <c r="O64" s="8" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="P64" s="8" t="inlineStr">
         <is>
-          <t>1030.00</t>
+          <t>930.00</t>
         </is>
       </c>
       <c r="Q64" s="8" t="inlineStr"/>
@@ -3728,7 +3722,9 @@
       <c r="S64" s="8" t="inlineStr"/>
       <c r="T64" s="8" t="inlineStr"/>
       <c r="U64" s="8" t="inlineStr"/>
-      <c r="V64" s="9" t="inlineStr"/>
+      <c r="V64" s="9" t="n">
+        <v>1430</v>
+      </c>
       <c r="W64" s="10" t="inlineStr"/>
       <c r="X64" s="11" t="inlineStr"/>
     </row>
@@ -3736,22 +3732,18 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr"/>
       <c r="D65" s="8" t="inlineStr"/>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>1760.00</t>
-        </is>
-      </c>
+      <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr"/>
       <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="8" t="inlineStr"/>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr"/>
@@ -3761,12 +3753,12 @@
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="8" t="inlineStr">
         <is>
-          <t>1670.00</t>
+          <t>1500.00</t>
         </is>
       </c>
       <c r="P65" s="8" t="inlineStr">
         <is>
-          <t>760.00</t>
+          <t>1030.00</t>
         </is>
       </c>
       <c r="Q65" s="8" t="inlineStr"/>
@@ -3774,159 +3766,163 @@
       <c r="S65" s="8" t="inlineStr"/>
       <c r="T65" s="8" t="inlineStr"/>
       <c r="U65" s="8" t="inlineStr"/>
-      <c r="V65" s="9" t="n">
+      <c r="V65" s="9" t="inlineStr"/>
+      <c r="W65" s="10" t="inlineStr"/>
+      <c r="X65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="1" t="n"/>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr"/>
+      <c r="D66" s="8" t="inlineStr"/>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr"/>
+      <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>1590.00</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr"/>
+      <c r="K66" s="8" t="inlineStr"/>
+      <c r="L66" s="8" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr"/>
+      <c r="N66" s="8" t="inlineStr"/>
+      <c r="O66" s="8" t="inlineStr">
+        <is>
+          <t>1670.00</t>
+        </is>
+      </c>
+      <c r="P66" s="8" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
+      <c r="Q66" s="8" t="inlineStr"/>
+      <c r="R66" s="8" t="inlineStr"/>
+      <c r="S66" s="8" t="inlineStr"/>
+      <c r="T66" s="8" t="inlineStr"/>
+      <c r="U66" s="8" t="inlineStr"/>
+      <c r="V66" s="9" t="n">
         <v>1445</v>
       </c>
-      <c r="W65" s="9" t="n">
+      <c r="W66" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="X65" s="11" t="n">
+      <c r="X66" s="11" t="n">
         <v>0.005028494803888703</v>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Krull
 Random: 1598.0
 Human: 2665.5</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 8413</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr"/>
-      <c r="D66" s="4" t="inlineStr"/>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr"/>
-      <c r="K66" s="4" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr"/>
-      <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr"/>
-      <c r="O66" s="4" t="inlineStr"/>
-      <c r="P66" s="4" t="inlineStr"/>
-      <c r="Q66" s="4" t="inlineStr"/>
-      <c r="R66" s="4" t="inlineStr"/>
-      <c r="S66" s="4" t="inlineStr"/>
-      <c r="T66" s="4" t="inlineStr"/>
-      <c r="U66" s="4" t="inlineStr"/>
-      <c r="V66" s="5" t="inlineStr"/>
-      <c r="W66" s="6" t="n">
-        <v>-2744.7</v>
-      </c>
-      <c r="X66" s="7" t="n">
-        <v>-2.571147540983606</v>
-      </c>
-    </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="1" t="n"/>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr"/>
-      <c r="D67" s="8" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>6202.00</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>5689.00</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>6107.50</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr"/>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>4708.50</t>
-        </is>
-      </c>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>5913.50</t>
-        </is>
-      </c>
-      <c r="K67" s="8" t="inlineStr"/>
-      <c r="L67" s="8" t="inlineStr"/>
-      <c r="M67" s="8" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
-      <c r="O67" s="8" t="inlineStr">
-        <is>
-          <t>5228.50</t>
-        </is>
-      </c>
-      <c r="P67" s="8" t="inlineStr"/>
-      <c r="Q67" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="R67" s="8" t="inlineStr"/>
-      <c r="S67" s="8" t="inlineStr"/>
-      <c r="T67" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
-      <c r="U67" s="8" t="inlineStr"/>
-      <c r="V67" s="9" t="n">
-        <v>5668.3</v>
-      </c>
-      <c r="W67" s="10" t="inlineStr"/>
-      <c r="X67" s="11" t="inlineStr"/>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="4" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr"/>
+      <c r="O67" s="4" t="inlineStr"/>
+      <c r="P67" s="4" t="inlineStr"/>
+      <c r="Q67" s="4" t="inlineStr"/>
+      <c r="R67" s="4" t="inlineStr"/>
+      <c r="S67" s="4" t="inlineStr"/>
+      <c r="T67" s="4" t="inlineStr"/>
+      <c r="U67" s="4" t="inlineStr"/>
+      <c r="V67" s="5" t="inlineStr"/>
+      <c r="W67" s="6" t="n">
+        <v>-2756.25</v>
+      </c>
+      <c r="X67" s="7" t="n">
+        <v>-2.581967213114754</v>
+      </c>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr"/>
       <c r="D68" s="8" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr"/>
-      <c r="G68" s="8" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>6202.00</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>5689.00</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>6107.50</t>
+        </is>
+      </c>
       <c r="H68" s="8" t="inlineStr"/>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>4851.00</t>
+          <t>4708.50</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>6044.00</t>
+          <t>5913.50</t>
         </is>
       </c>
       <c r="K68" s="8" t="inlineStr"/>
       <c r="L68" s="8" t="inlineStr"/>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
-      <c r="O68" s="8" t="inlineStr"/>
+      <c r="O68" s="8" t="inlineStr">
+        <is>
+          <t>5228.50</t>
+        </is>
+      </c>
       <c r="P68" s="8" t="inlineStr"/>
-      <c r="Q68" s="8" t="inlineStr"/>
+      <c r="Q68" s="8" t="inlineStr">
+        <is>
+          <t>5599.00</t>
+        </is>
+      </c>
       <c r="R68" s="8" t="inlineStr"/>
       <c r="S68" s="8" t="inlineStr"/>
       <c r="T68" s="8" t="inlineStr">
         <is>
-          <t>6587.00</t>
+          <t>6289.00</t>
         </is>
       </c>
       <c r="U68" s="8" t="inlineStr"/>
-      <c r="V68" s="9" t="inlineStr"/>
+      <c r="V68" s="9" t="n">
+        <v>5656.75</v>
+      </c>
       <c r="W68" s="10" t="inlineStr"/>
       <c r="X68" s="11" t="inlineStr"/>
     </row>
@@ -3934,158 +3930,156 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr"/>
       <c r="D69" s="8" t="inlineStr"/>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>6576.50</t>
-        </is>
-      </c>
+      <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr"/>
       <c r="H69" s="8" t="inlineStr"/>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>5279.50</t>
+          <t>4851.00</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>5889.50</t>
+          <t>6044.00</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr"/>
       <c r="L69" s="8" t="inlineStr"/>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
-      <c r="O69" s="8" t="inlineStr">
-        <is>
-          <t>6447.50</t>
-        </is>
-      </c>
+      <c r="O69" s="8" t="inlineStr"/>
       <c r="P69" s="8" t="inlineStr"/>
-      <c r="Q69" s="8" t="inlineStr">
-        <is>
-          <t>6828.50</t>
-        </is>
-      </c>
+      <c r="Q69" s="8" t="inlineStr"/>
       <c r="R69" s="8" t="inlineStr"/>
       <c r="S69" s="8" t="inlineStr"/>
       <c r="T69" s="8" t="inlineStr">
         <is>
+          <t>6587.00</t>
+        </is>
+      </c>
+      <c r="U69" s="8" t="inlineStr"/>
+      <c r="V69" s="9" t="inlineStr"/>
+      <c r="W69" s="10" t="inlineStr"/>
+      <c r="X69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="1" t="n"/>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr"/>
+      <c r="D70" s="8" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>6576.50</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>5279.50</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
+        <is>
+          <t>5889.50</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr"/>
+      <c r="L70" s="8" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
+      <c r="N70" s="8" t="inlineStr"/>
+      <c r="O70" s="8" t="inlineStr">
+        <is>
+          <t>6447.50</t>
+        </is>
+      </c>
+      <c r="P70" s="8" t="inlineStr"/>
+      <c r="Q70" s="8" t="inlineStr">
+        <is>
+          <t>6828.50</t>
+        </is>
+      </c>
+      <c r="R70" s="8" t="inlineStr"/>
+      <c r="S70" s="8" t="inlineStr"/>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
           <t>6796.50</t>
         </is>
       </c>
-      <c r="U69" s="8" t="inlineStr"/>
-      <c r="V69" s="9" t="n">
-        <v>6197.9</v>
-      </c>
-      <c r="W69" s="9" t="n">
-        <v>529.5999999999995</v>
-      </c>
-      <c r="X69" s="11" t="n">
-        <v>0.4961124121779855</v>
-      </c>
-    </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="U70" s="8" t="inlineStr"/>
+      <c r="V70" s="9" t="n">
+        <v>6303</v>
+      </c>
+      <c r="W70" s="9" t="n">
+        <v>646.25</v>
+      </c>
+      <c r="X70" s="11" t="n">
+        <v>0.6053864168618267</v>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>KungFuMaster
 Random: 258.5
 Human: 22736.3</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 26182</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr"/>
-      <c r="D70" s="4" t="inlineStr"/>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr"/>
-      <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="4" t="inlineStr"/>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr"/>
-      <c r="O70" s="4" t="inlineStr"/>
-      <c r="P70" s="4" t="inlineStr"/>
-      <c r="Q70" s="4" t="inlineStr"/>
-      <c r="R70" s="4" t="inlineStr"/>
-      <c r="S70" s="4" t="inlineStr"/>
-      <c r="T70" s="4" t="inlineStr"/>
-      <c r="U70" s="4" t="inlineStr"/>
-      <c r="V70" s="5" t="inlineStr"/>
-      <c r="W70" s="6" t="n">
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr"/>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr"/>
+      <c r="Q71" s="4" t="inlineStr"/>
+      <c r="R71" s="4" t="inlineStr"/>
+      <c r="S71" s="4" t="inlineStr"/>
+      <c r="T71" s="4" t="inlineStr"/>
+      <c r="U71" s="4" t="inlineStr"/>
+      <c r="V71" s="5" t="inlineStr"/>
+      <c r="W71" s="6" t="n">
         <v>-1044.5</v>
       </c>
-      <c r="X70" s="7" t="n">
+      <c r="X71" s="7" t="n">
         <v>-0.04646807071866464</v>
       </c>
-    </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="1" t="n"/>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr"/>
-      <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>26460.00</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr"/>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="inlineStr"/>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>23815.00</t>
-        </is>
-      </c>
-      <c r="J71" s="8" t="inlineStr">
-        <is>
-          <t>20895.00</t>
-        </is>
-      </c>
-      <c r="K71" s="8" t="inlineStr"/>
-      <c r="L71" s="8" t="inlineStr"/>
-      <c r="M71" s="8" t="inlineStr"/>
-      <c r="N71" s="8" t="inlineStr"/>
-      <c r="O71" s="8" t="inlineStr"/>
-      <c r="P71" s="8" t="inlineStr"/>
-      <c r="Q71" s="8" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
-      <c r="S71" s="8" t="inlineStr"/>
-      <c r="T71" s="8" t="inlineStr"/>
-      <c r="U71" s="8" t="inlineStr"/>
-      <c r="V71" s="9" t="n">
-        <v>25137.5</v>
-      </c>
-      <c r="W71" s="10" t="inlineStr"/>
-      <c r="X71" s="11" t="inlineStr"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr"/>
       <c r="D72" s="8" t="inlineStr"/>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>30110.00</t>
+          <t>26460.00</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr"/>
@@ -4093,10 +4087,14 @@
       <c r="H72" s="8" t="inlineStr"/>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>20245.00</t>
-        </is>
-      </c>
-      <c r="J72" s="8" t="inlineStr"/>
+          <t>23815.00</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>20895.00</t>
+        </is>
+      </c>
       <c r="K72" s="8" t="inlineStr"/>
       <c r="L72" s="8" t="inlineStr"/>
       <c r="M72" s="8" t="inlineStr"/>
@@ -4109,119 +4107,119 @@
       <c r="T72" s="8" t="inlineStr"/>
       <c r="U72" s="8" t="inlineStr"/>
       <c r="V72" s="9" t="n">
+        <v>25137.5</v>
+      </c>
+      <c r="W72" s="10" t="inlineStr"/>
+      <c r="X72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="1" t="n"/>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr"/>
+      <c r="D73" s="8" t="inlineStr"/>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>30110.00</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>20245.00</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr"/>
+      <c r="K73" s="8" t="inlineStr"/>
+      <c r="L73" s="8" t="inlineStr"/>
+      <c r="M73" s="8" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr"/>
+      <c r="O73" s="8" t="inlineStr"/>
+      <c r="P73" s="8" t="inlineStr"/>
+      <c r="Q73" s="8" t="inlineStr"/>
+      <c r="R73" s="8" t="inlineStr"/>
+      <c r="S73" s="8" t="inlineStr"/>
+      <c r="T73" s="8" t="inlineStr"/>
+      <c r="U73" s="8" t="inlineStr"/>
+      <c r="V73" s="9" t="n">
         <v>25177.5</v>
       </c>
-      <c r="W72" s="9" t="n">
+      <c r="W73" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="X72" s="11" t="n">
+      <c r="X73" s="11" t="n">
         <v>0.001779533584247569</v>
       </c>
     </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>MsPacman
 Random: 307.3
 Human: 6951.6</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 2673</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
-      <c r="G73" s="4" t="inlineStr"/>
-      <c r="H73" s="4" t="inlineStr"/>
-      <c r="I73" s="4" t="inlineStr"/>
-      <c r="J73" s="4" t="inlineStr"/>
-      <c r="K73" s="4" t="inlineStr"/>
-      <c r="L73" s="4" t="inlineStr"/>
-      <c r="M73" s="4" t="inlineStr"/>
-      <c r="N73" s="4" t="inlineStr"/>
-      <c r="O73" s="4" t="inlineStr"/>
-      <c r="P73" s="4" t="inlineStr"/>
-      <c r="Q73" s="4" t="inlineStr"/>
-      <c r="R73" s="4" t="inlineStr"/>
-      <c r="S73" s="4" t="inlineStr"/>
-      <c r="T73" s="4" t="inlineStr"/>
-      <c r="U73" s="4" t="inlineStr"/>
-      <c r="V73" s="5" t="inlineStr"/>
-      <c r="W73" s="6" t="n">
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr"/>
+      <c r="L74" s="4" t="inlineStr"/>
+      <c r="M74" s="4" t="inlineStr"/>
+      <c r="N74" s="4" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr"/>
+      <c r="P74" s="4" t="inlineStr"/>
+      <c r="Q74" s="4" t="inlineStr"/>
+      <c r="R74" s="4" t="inlineStr"/>
+      <c r="S74" s="4" t="inlineStr"/>
+      <c r="T74" s="4" t="inlineStr"/>
+      <c r="U74" s="4" t="inlineStr"/>
+      <c r="V74" s="5" t="inlineStr"/>
+      <c r="W74" s="6" t="n">
         <v>-602</v>
       </c>
-      <c r="X73" s="7" t="n">
+      <c r="X74" s="7" t="n">
         <v>-0.09060397634062278</v>
       </c>
-    </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="1" t="n"/>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>1807.50</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr"/>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>2007.00</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr"/>
-      <c r="G74" s="8" t="inlineStr"/>
-      <c r="H74" s="8" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>2388.00</t>
-        </is>
-      </c>
-      <c r="J74" s="8" t="inlineStr"/>
-      <c r="K74" s="8" t="inlineStr"/>
-      <c r="L74" s="8" t="inlineStr"/>
-      <c r="M74" s="8" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr"/>
-      <c r="O74" s="8" t="inlineStr">
-        <is>
-          <t>1754.00</t>
-        </is>
-      </c>
-      <c r="P74" s="8" t="inlineStr"/>
-      <c r="Q74" s="8" t="inlineStr"/>
-      <c r="R74" s="8" t="inlineStr"/>
-      <c r="S74" s="8" t="inlineStr"/>
-      <c r="T74" s="8" t="inlineStr"/>
-      <c r="U74" s="8" t="inlineStr"/>
-      <c r="V74" s="9" t="n">
-        <v>2071</v>
-      </c>
-      <c r="W74" s="10" t="inlineStr"/>
-      <c r="X74" s="11" t="inlineStr"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>1807.50</t>
+        </is>
+      </c>
       <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr"/>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>2007.00</t>
+        </is>
+      </c>
       <c r="F75" s="8" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr"/>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>2250.00</t>
+          <t>2388.00</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr"/>
@@ -4231,7 +4229,7 @@
       <c r="N75" s="8" t="inlineStr"/>
       <c r="O75" s="8" t="inlineStr">
         <is>
-          <t>1886.50</t>
+          <t>1754.00</t>
         </is>
       </c>
       <c r="P75" s="8" t="inlineStr"/>
@@ -4241,130 +4239,126 @@
       <c r="T75" s="8" t="inlineStr"/>
       <c r="U75" s="8" t="inlineStr"/>
       <c r="V75" s="9" t="n">
+        <v>2071</v>
+      </c>
+      <c r="W75" s="10" t="inlineStr"/>
+      <c r="X75" s="11" t="inlineStr"/>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="1" t="n"/>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr"/>
+      <c r="D76" s="8" t="inlineStr"/>
+      <c r="E76" s="8" t="inlineStr"/>
+      <c r="F76" s="8" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>2250.00</t>
+        </is>
+      </c>
+      <c r="J76" s="8" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr"/>
+      <c r="L76" s="8" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr"/>
+      <c r="N76" s="8" t="inlineStr"/>
+      <c r="O76" s="8" t="inlineStr">
+        <is>
+          <t>1886.50</t>
+        </is>
+      </c>
+      <c r="P76" s="8" t="inlineStr"/>
+      <c r="Q76" s="8" t="inlineStr"/>
+      <c r="R76" s="8" t="inlineStr"/>
+      <c r="S76" s="8" t="inlineStr"/>
+      <c r="T76" s="8" t="inlineStr"/>
+      <c r="U76" s="8" t="inlineStr"/>
+      <c r="V76" s="9" t="n">
         <v>2068.25</v>
       </c>
-      <c r="W75" s="9" t="n">
+      <c r="W76" s="9" t="n">
         <v>2.75</v>
       </c>
-      <c r="X75" s="11" t="n">
+      <c r="X76" s="11" t="n">
         <v>-0.0004138885962403865</v>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Pong
 Random: -20.7
 Human: 14.6</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 11</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr"/>
-      <c r="D76" s="4" t="inlineStr"/>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr"/>
-      <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="4" t="inlineStr"/>
-      <c r="J76" s="4" t="inlineStr"/>
-      <c r="K76" s="4" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr"/>
-      <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr"/>
-      <c r="O76" s="4" t="inlineStr"/>
-      <c r="P76" s="4" t="inlineStr"/>
-      <c r="Q76" s="4" t="inlineStr"/>
-      <c r="R76" s="4" t="inlineStr"/>
-      <c r="S76" s="4" t="inlineStr"/>
-      <c r="T76" s="4" t="inlineStr"/>
-      <c r="U76" s="4" t="inlineStr"/>
-      <c r="V76" s="5" t="inlineStr"/>
-      <c r="W76" s="6" t="n">
+      <c r="C77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr"/>
+      <c r="M77" s="4" t="inlineStr"/>
+      <c r="N77" s="4" t="inlineStr"/>
+      <c r="O77" s="4" t="inlineStr"/>
+      <c r="P77" s="4" t="inlineStr"/>
+      <c r="Q77" s="4" t="inlineStr"/>
+      <c r="R77" s="4" t="inlineStr"/>
+      <c r="S77" s="4" t="inlineStr"/>
+      <c r="T77" s="4" t="inlineStr"/>
+      <c r="U77" s="4" t="inlineStr"/>
+      <c r="V77" s="5" t="inlineStr"/>
+      <c r="W77" s="6" t="n">
         <v>-5.4</v>
       </c>
-      <c r="X76" s="7" t="n">
+      <c r="X77" s="7" t="n">
         <v>-0.1529745042492918</v>
       </c>
-    </row>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="1" t="n"/>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr"/>
-      <c r="D77" s="8" t="inlineStr"/>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr"/>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
-      <c r="K77" s="8" t="inlineStr"/>
-      <c r="L77" s="8" t="inlineStr"/>
-      <c r="M77" s="8" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr"/>
-      <c r="O77" s="8" t="inlineStr"/>
-      <c r="P77" s="8" t="inlineStr"/>
-      <c r="Q77" s="8" t="inlineStr"/>
-      <c r="R77" s="8" t="inlineStr"/>
-      <c r="S77" s="8" t="inlineStr"/>
-      <c r="T77" s="8" t="inlineStr"/>
-      <c r="U77" s="8" t="inlineStr"/>
-      <c r="V77" s="9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W77" s="10" t="inlineStr"/>
-      <c r="X77" s="11" t="inlineStr"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr"/>
       <c r="D78" s="8" t="inlineStr"/>
-      <c r="E78" s="8" t="inlineStr"/>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>8.20</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr"/>
       <c r="H78" s="8" t="inlineStr"/>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="J78" s="8" t="inlineStr"/>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>13.70</t>
+        </is>
+      </c>
       <c r="K78" s="8" t="inlineStr"/>
       <c r="L78" s="8" t="inlineStr"/>
       <c r="M78" s="8" t="inlineStr"/>
@@ -4377,119 +4371,111 @@
       <c r="T78" s="8" t="inlineStr"/>
       <c r="U78" s="8" t="inlineStr"/>
       <c r="V78" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W78" s="10" t="inlineStr"/>
+      <c r="X78" s="11" t="inlineStr"/>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="1" t="n"/>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr"/>
+      <c r="D79" s="8" t="inlineStr"/>
+      <c r="E79" s="8" t="inlineStr"/>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>8.20</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>9.80</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr"/>
+      <c r="K79" s="8" t="inlineStr"/>
+      <c r="L79" s="8" t="inlineStr"/>
+      <c r="M79" s="8" t="inlineStr"/>
+      <c r="N79" s="8" t="inlineStr"/>
+      <c r="O79" s="8" t="inlineStr"/>
+      <c r="P79" s="8" t="inlineStr"/>
+      <c r="Q79" s="8" t="inlineStr"/>
+      <c r="R79" s="8" t="inlineStr"/>
+      <c r="S79" s="8" t="inlineStr"/>
+      <c r="T79" s="8" t="inlineStr"/>
+      <c r="U79" s="8" t="inlineStr"/>
+      <c r="V79" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="W78" s="9" t="n">
+      <c r="W79" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="X78" s="11" t="n">
+      <c r="X79" s="11" t="n">
         <v>0.09631728045325781</v>
       </c>
     </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>PrivateEye
 Random: 24.9
 Human: 69571.3</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 7781</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr"/>
-      <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="4" t="inlineStr"/>
-      <c r="K79" s="4" t="inlineStr"/>
-      <c r="L79" s="4" t="inlineStr"/>
-      <c r="M79" s="4" t="inlineStr"/>
-      <c r="N79" s="4" t="inlineStr"/>
-      <c r="O79" s="4" t="inlineStr"/>
-      <c r="P79" s="4" t="inlineStr"/>
-      <c r="Q79" s="4" t="inlineStr"/>
-      <c r="R79" s="4" t="inlineStr"/>
-      <c r="S79" s="4" t="inlineStr"/>
-      <c r="T79" s="4" t="inlineStr"/>
-      <c r="U79" s="4" t="inlineStr"/>
-      <c r="V79" s="5" t="inlineStr"/>
-      <c r="W79" s="6" t="n">
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr"/>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr"/>
+      <c r="P80" s="4" t="inlineStr"/>
+      <c r="Q80" s="4" t="inlineStr"/>
+      <c r="R80" s="4" t="inlineStr"/>
+      <c r="S80" s="4" t="inlineStr"/>
+      <c r="T80" s="4" t="inlineStr"/>
+      <c r="U80" s="4" t="inlineStr"/>
+      <c r="V80" s="5" t="inlineStr"/>
+      <c r="W80" s="6" t="n">
         <v>-6958.88</v>
       </c>
-      <c r="X79" s="7" t="n">
+      <c r="X80" s="7" t="n">
         <v>-0.1000609664914359</v>
       </c>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="1" t="n"/>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>75.30</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr"/>
-      <c r="F80" s="8" t="inlineStr"/>
-      <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>199.35</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="inlineStr"/>
-      <c r="K80" s="8" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr"/>
-      <c r="M80" s="8" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
-      <c r="O80" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="P80" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q80" s="8" t="inlineStr">
-        <is>
-          <t>3551.75</t>
-        </is>
-      </c>
-      <c r="R80" s="8" t="inlineStr"/>
-      <c r="S80" s="8" t="inlineStr"/>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>159.50</t>
-        </is>
-      </c>
-      <c r="U80" s="8" t="inlineStr"/>
-      <c r="V80" s="9" t="n">
-        <v>822.1200000000001</v>
-      </c>
-      <c r="W80" s="10" t="inlineStr"/>
-      <c r="X80" s="11" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>75.30</t>
+        </is>
+      </c>
       <c r="D81" s="8" t="inlineStr"/>
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr"/>
@@ -4497,7 +4483,7 @@
       <c r="H81" s="8" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>191.95</t>
+          <t>199.35</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr"/>
@@ -4507,7 +4493,7 @@
       <c r="N81" s="8" t="inlineStr"/>
       <c r="O81" s="8" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P81" s="8" t="inlineStr">
@@ -4517,145 +4503,149 @@
       </c>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>166.80</t>
+          <t>3551.75</t>
         </is>
       </c>
       <c r="R81" s="8" t="inlineStr"/>
       <c r="S81" s="8" t="inlineStr"/>
       <c r="T81" s="8" t="inlineStr">
         <is>
-          <t>153.20</t>
+          <t>159.50</t>
         </is>
       </c>
       <c r="U81" s="8" t="inlineStr"/>
       <c r="V81" s="9" t="n">
+        <v>822.1200000000001</v>
+      </c>
+      <c r="W81" s="10" t="inlineStr"/>
+      <c r="X81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="1" t="n"/>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr"/>
+      <c r="D82" s="8" t="inlineStr"/>
+      <c r="E82" s="8" t="inlineStr"/>
+      <c r="F82" s="8" t="inlineStr"/>
+      <c r="G82" s="8" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>191.95</t>
+        </is>
+      </c>
+      <c r="J82" s="8" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr"/>
+      <c r="L82" s="8" t="inlineStr"/>
+      <c r="M82" s="8" t="inlineStr"/>
+      <c r="N82" s="8" t="inlineStr"/>
+      <c r="O82" s="8" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="P82" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q82" s="8" t="inlineStr">
+        <is>
+          <t>166.80</t>
+        </is>
+      </c>
+      <c r="R82" s="8" t="inlineStr"/>
+      <c r="S82" s="8" t="inlineStr"/>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>153.20</t>
+        </is>
+      </c>
+      <c r="U82" s="8" t="inlineStr"/>
+      <c r="V82" s="9" t="n">
         <v>126.39</v>
       </c>
-      <c r="W81" s="9" t="n">
+      <c r="W82" s="9" t="n">
         <v>695.7300000000001</v>
       </c>
-      <c r="X81" s="11" t="n">
+      <c r="X82" s="11" t="n">
         <v>-0.01000382478460424</v>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Qbert
 Random: 163.9
 Human: 13455.0</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 4522</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr"/>
-      <c r="D82" s="4" t="inlineStr"/>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr"/>
-      <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr"/>
-      <c r="O82" s="4" t="inlineStr"/>
-      <c r="P82" s="4" t="inlineStr"/>
-      <c r="Q82" s="4" t="inlineStr"/>
-      <c r="R82" s="4" t="inlineStr"/>
-      <c r="S82" s="4" t="inlineStr"/>
-      <c r="T82" s="4" t="inlineStr"/>
-      <c r="U82" s="4" t="inlineStr"/>
-      <c r="V82" s="5" t="inlineStr"/>
-      <c r="W82" s="6" t="n">
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr"/>
+      <c r="O83" s="4" t="inlineStr"/>
+      <c r="P83" s="4" t="inlineStr"/>
+      <c r="Q83" s="4" t="inlineStr"/>
+      <c r="R83" s="4" t="inlineStr"/>
+      <c r="S83" s="4" t="inlineStr"/>
+      <c r="T83" s="4" t="inlineStr"/>
+      <c r="U83" s="4" t="inlineStr"/>
+      <c r="V83" s="5" t="inlineStr"/>
+      <c r="W83" s="6" t="n">
         <v>-1646.75</v>
       </c>
-      <c r="X82" s="7" t="n">
+      <c r="X83" s="7" t="n">
         <v>-0.1238986991294927</v>
       </c>
-    </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="1" t="n"/>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr"/>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
-      <c r="H83" s="8" t="inlineStr"/>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>3193.75</t>
-        </is>
-      </c>
-      <c r="J83" s="8" t="inlineStr"/>
-      <c r="K83" s="8" t="inlineStr"/>
-      <c r="L83" s="8" t="inlineStr"/>
-      <c r="M83" s="8" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
-      <c r="O83" s="8" t="inlineStr">
-        <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="P83" s="8" t="inlineStr"/>
-      <c r="Q83" s="8" t="inlineStr"/>
-      <c r="R83" s="8" t="inlineStr"/>
-      <c r="S83" s="8" t="inlineStr"/>
-      <c r="T83" s="8" t="inlineStr"/>
-      <c r="U83" s="8" t="inlineStr"/>
-      <c r="V83" s="9" t="n">
-        <v>2875.25</v>
-      </c>
-      <c r="W83" s="10" t="inlineStr"/>
-      <c r="X83" s="11" t="inlineStr"/>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>2818.75</t>
+          <t>1771.25</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>1918.75</t>
+          <t>3786.25</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr"/>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>2553.75</t>
+          <t>2940.00</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" s="8" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>3193.75</t>
+        </is>
+      </c>
       <c r="J84" s="8" t="inlineStr"/>
       <c r="K84" s="8" t="inlineStr"/>
       <c r="L84" s="8" t="inlineStr"/>
@@ -4663,7 +4653,7 @@
       <c r="N84" s="8" t="inlineStr"/>
       <c r="O84" s="8" t="inlineStr">
         <is>
-          <t>3782.50</t>
+          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
         </is>
       </c>
       <c r="P84" s="8" t="inlineStr"/>
@@ -4672,7 +4662,9 @@
       <c r="S84" s="8" t="inlineStr"/>
       <c r="T84" s="8" t="inlineStr"/>
       <c r="U84" s="8" t="inlineStr"/>
-      <c r="V84" s="9" t="inlineStr"/>
+      <c r="V84" s="9" t="n">
+        <v>2875.25</v>
+      </c>
       <c r="W84" s="10" t="inlineStr"/>
       <c r="X84" s="11" t="inlineStr"/>
     </row>
@@ -4680,32 +4672,28 @@
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>2702.50</t>
+          <t>2818.75</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>4056.25</t>
+          <t>1918.75</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr"/>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>2338.75</t>
+          <t>2553.75</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr"/>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>2608.75</t>
-        </is>
-      </c>
+      <c r="I85" s="8" t="inlineStr"/>
       <c r="J85" s="8" t="inlineStr"/>
       <c r="K85" s="8" t="inlineStr"/>
       <c r="L85" s="8" t="inlineStr"/>
@@ -4713,7 +4701,7 @@
       <c r="N85" s="8" t="inlineStr"/>
       <c r="O85" s="8" t="inlineStr">
         <is>
-          <t>2895.00</t>
+          <t>3782.50</t>
         </is>
       </c>
       <c r="P85" s="8" t="inlineStr"/>
@@ -4722,109 +4710,111 @@
       <c r="S85" s="8" t="inlineStr"/>
       <c r="T85" s="8" t="inlineStr"/>
       <c r="U85" s="8" t="inlineStr"/>
-      <c r="V85" s="9" t="n">
+      <c r="V85" s="9" t="inlineStr"/>
+      <c r="W85" s="10" t="inlineStr"/>
+      <c r="X85" s="11" t="inlineStr"/>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="1" t="n"/>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>2702.50</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr"/>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>4056.25</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr"/>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>2338.75</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr"/>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>2608.75</t>
+        </is>
+      </c>
+      <c r="J86" s="8" t="inlineStr"/>
+      <c r="K86" s="8" t="inlineStr"/>
+      <c r="L86" s="8" t="inlineStr"/>
+      <c r="M86" s="8" t="inlineStr"/>
+      <c r="N86" s="8" t="inlineStr"/>
+      <c r="O86" s="8" t="inlineStr">
+        <is>
+          <t>2895.00</t>
+        </is>
+      </c>
+      <c r="P86" s="8" t="inlineStr"/>
+      <c r="Q86" s="8" t="inlineStr"/>
+      <c r="R86" s="8" t="inlineStr"/>
+      <c r="S86" s="8" t="inlineStr"/>
+      <c r="T86" s="8" t="inlineStr"/>
+      <c r="U86" s="8" t="inlineStr"/>
+      <c r="V86" s="9" t="n">
         <v>2920.25</v>
       </c>
-      <c r="W85" s="9" t="n">
+      <c r="W86" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="X85" s="11" t="n">
+      <c r="X86" s="11" t="n">
         <v>0.003385724281662165</v>
       </c>
     </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>RoadRunner
 Random: 11.5
 Human: 7845.0</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 17564</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr"/>
-      <c r="D86" s="4" t="inlineStr"/>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="4" t="inlineStr"/>
-      <c r="K86" s="4" t="inlineStr"/>
-      <c r="L86" s="4" t="inlineStr"/>
-      <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr"/>
-      <c r="O86" s="4" t="inlineStr"/>
-      <c r="P86" s="4" t="inlineStr"/>
-      <c r="Q86" s="4" t="inlineStr"/>
-      <c r="R86" s="4" t="inlineStr"/>
-      <c r="S86" s="4" t="inlineStr"/>
-      <c r="T86" s="4" t="inlineStr"/>
-      <c r="U86" s="4" t="inlineStr"/>
-      <c r="V86" s="5" t="inlineStr"/>
-      <c r="W86" s="6" t="n">
+      <c r="C87" s="4" t="inlineStr"/>
+      <c r="D87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
+      <c r="M87" s="4" t="inlineStr"/>
+      <c r="N87" s="4" t="inlineStr"/>
+      <c r="O87" s="4" t="inlineStr"/>
+      <c r="P87" s="4" t="inlineStr"/>
+      <c r="Q87" s="4" t="inlineStr"/>
+      <c r="R87" s="4" t="inlineStr"/>
+      <c r="S87" s="4" t="inlineStr"/>
+      <c r="T87" s="4" t="inlineStr"/>
+      <c r="U87" s="4" t="inlineStr"/>
+      <c r="V87" s="5" t="inlineStr"/>
+      <c r="W87" s="6" t="n">
         <v>-8627.75</v>
       </c>
-      <c r="X86" s="7" t="n">
+      <c r="X87" s="7" t="n">
         <v>-1.101391459756175</v>
       </c>
-    </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="1" t="n"/>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr"/>
-      <c r="D87" s="8" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr"/>
-      <c r="F87" s="8" t="inlineStr"/>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr"/>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>8610.00</t>
-        </is>
-      </c>
-      <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="8" t="inlineStr"/>
-      <c r="L87" s="8" t="inlineStr"/>
-      <c r="M87" s="8" t="inlineStr"/>
-      <c r="N87" s="8" t="inlineStr"/>
-      <c r="O87" s="8" t="inlineStr">
-        <is>
-          <t>7290.00</t>
-        </is>
-      </c>
-      <c r="P87" s="8" t="inlineStr">
-        <is>
-          <t>9690.00</t>
-        </is>
-      </c>
-      <c r="Q87" s="8" t="inlineStr">
-        <is>
-          <t>10155.00</t>
-        </is>
-      </c>
-      <c r="R87" s="8" t="inlineStr"/>
-      <c r="S87" s="8" t="inlineStr"/>
-      <c r="T87" s="8" t="inlineStr"/>
-      <c r="U87" s="8" t="inlineStr"/>
-      <c r="V87" s="9" t="n">
-        <v>8936.25</v>
-      </c>
-      <c r="W87" s="10" t="inlineStr"/>
-      <c r="X87" s="11" t="inlineStr"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr"/>
@@ -4833,7 +4823,11 @@
       <c r="F88" s="8" t="inlineStr"/>
       <c r="G88" s="8" t="inlineStr"/>
       <c r="H88" s="8" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>8610.00</t>
+        </is>
+      </c>
       <c r="J88" s="8" t="inlineStr"/>
       <c r="K88" s="8" t="inlineStr"/>
       <c r="L88" s="8" t="inlineStr"/>
@@ -4841,24 +4835,26 @@
       <c r="N88" s="8" t="inlineStr"/>
       <c r="O88" s="8" t="inlineStr">
         <is>
-          <t>8520.00</t>
+          <t>7290.00</t>
         </is>
       </c>
       <c r="P88" s="8" t="inlineStr">
         <is>
-          <t>11830.00</t>
+          <t>9690.00</t>
         </is>
       </c>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>16805.00</t>
+          <t>10155.00</t>
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr"/>
       <c r="S88" s="8" t="inlineStr"/>
       <c r="T88" s="8" t="inlineStr"/>
       <c r="U88" s="8" t="inlineStr"/>
-      <c r="V88" s="9" t="inlineStr"/>
+      <c r="V88" s="9" t="n">
+        <v>8936.25</v>
+      </c>
       <c r="W88" s="10" t="inlineStr"/>
       <c r="X88" s="11" t="inlineStr"/>
     </row>
@@ -4866,7 +4862,7 @@
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr"/>
@@ -4875,11 +4871,7 @@
       <c r="F89" s="8" t="inlineStr"/>
       <c r="G89" s="8" t="inlineStr"/>
       <c r="H89" s="8" t="inlineStr"/>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>8195.00</t>
-        </is>
-      </c>
+      <c r="I89" s="8" t="inlineStr"/>
       <c r="J89" s="8" t="inlineStr"/>
       <c r="K89" s="8" t="inlineStr"/>
       <c r="L89" s="8" t="inlineStr"/>
@@ -4887,152 +4879,164 @@
       <c r="N89" s="8" t="inlineStr"/>
       <c r="O89" s="8" t="inlineStr">
         <is>
-          <t>8325.00</t>
+          <t>8520.00</t>
         </is>
       </c>
       <c r="P89" s="8" t="inlineStr">
         <is>
-          <t>12890.00</t>
+          <t>11830.00</t>
         </is>
       </c>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>16980.00</t>
+          <t>16805.00</t>
         </is>
       </c>
       <c r="R89" s="8" t="inlineStr"/>
       <c r="S89" s="8" t="inlineStr"/>
       <c r="T89" s="8" t="inlineStr"/>
       <c r="U89" s="8" t="inlineStr"/>
-      <c r="V89" s="9" t="n">
+      <c r="V89" s="9" t="inlineStr"/>
+      <c r="W89" s="10" t="inlineStr"/>
+      <c r="X89" s="11" t="inlineStr"/>
+    </row>
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="1" t="n"/>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr"/>
+      <c r="D90" s="8" t="inlineStr"/>
+      <c r="E90" s="8" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>8195.00</t>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="8" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr"/>
+      <c r="N90" s="8" t="inlineStr"/>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>8325.00</t>
+        </is>
+      </c>
+      <c r="P90" s="8" t="inlineStr">
+        <is>
+          <t>12890.00</t>
+        </is>
+      </c>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>16980.00</t>
+        </is>
+      </c>
+      <c r="R90" s="8" t="inlineStr"/>
+      <c r="S90" s="8" t="inlineStr"/>
+      <c r="T90" s="8" t="inlineStr"/>
+      <c r="U90" s="8" t="inlineStr"/>
+      <c r="V90" s="9" t="n">
         <v>11597.5</v>
       </c>
-      <c r="W89" s="9" t="n">
+      <c r="W90" s="9" t="n">
         <v>2661.25</v>
       </c>
-      <c r="X89" s="11" t="n">
+      <c r="X90" s="11" t="n">
         <v>0.3397268143230995</v>
       </c>
     </row>
-    <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Seaquest
 Random: 68.4
 Human: 42054.7</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 525</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr"/>
-      <c r="D90" s="4" t="inlineStr"/>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="4" t="inlineStr"/>
-      <c r="H90" s="4" t="inlineStr"/>
-      <c r="I90" s="4" t="inlineStr"/>
-      <c r="J90" s="4" t="inlineStr"/>
-      <c r="K90" s="4" t="inlineStr"/>
-      <c r="L90" s="4" t="inlineStr"/>
-      <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr"/>
-      <c r="O90" s="4" t="inlineStr"/>
-      <c r="P90" s="4" t="inlineStr"/>
-      <c r="Q90" s="4" t="inlineStr"/>
-      <c r="R90" s="4" t="inlineStr"/>
-      <c r="S90" s="4" t="inlineStr"/>
-      <c r="T90" s="4" t="inlineStr"/>
-      <c r="U90" s="4" t="inlineStr"/>
-      <c r="V90" s="5" t="inlineStr"/>
-      <c r="W90" s="6" t="n">
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="inlineStr"/>
+      <c r="N91" s="4" t="inlineStr"/>
+      <c r="O91" s="4" t="inlineStr"/>
+      <c r="P91" s="4" t="inlineStr"/>
+      <c r="Q91" s="4" t="inlineStr"/>
+      <c r="R91" s="4" t="inlineStr"/>
+      <c r="S91" s="4" t="inlineStr"/>
+      <c r="T91" s="4" t="inlineStr"/>
+      <c r="U91" s="4" t="inlineStr"/>
+      <c r="V91" s="5" t="inlineStr"/>
+      <c r="W91" s="6" t="n">
         <v>-64.33333333333331</v>
       </c>
-      <c r="X90" s="7" t="n">
+      <c r="X91" s="7" t="n">
         <v>-0.001532245835744834</v>
       </c>
-    </row>
-    <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="1" t="n"/>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>454.00</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr"/>
-      <c r="E91" s="8" t="inlineStr"/>
-      <c r="F91" s="8" t="inlineStr"/>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr"/>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>494.00</t>
-        </is>
-      </c>
-      <c r="J91" s="8" t="inlineStr"/>
-      <c r="K91" s="8" t="inlineStr"/>
-      <c r="L91" s="8" t="inlineStr"/>
-      <c r="M91" s="8" t="inlineStr"/>
-      <c r="N91" s="8" t="inlineStr"/>
-      <c r="O91" s="8" t="inlineStr">
-        <is>
-          <t>418.00</t>
-        </is>
-      </c>
-      <c r="P91" s="8" t="inlineStr"/>
-      <c r="Q91" s="8" t="inlineStr"/>
-      <c r="R91" s="8" t="inlineStr"/>
-      <c r="S91" s="8" t="inlineStr"/>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
-      <c r="U91" s="8" t="inlineStr"/>
-      <c r="V91" s="9" t="n">
-        <v>460.6666666666667</v>
-      </c>
-      <c r="W91" s="10" t="inlineStr"/>
-      <c r="X91" s="11" t="inlineStr"/>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>454.00</t>
+        </is>
+      </c>
       <c r="D92" s="8" t="inlineStr"/>
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" s="8" t="inlineStr"/>
       <c r="G92" s="8" t="inlineStr"/>
       <c r="H92" s="8" t="inlineStr"/>
-      <c r="I92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>494.00</t>
+        </is>
+      </c>
       <c r="J92" s="8" t="inlineStr"/>
       <c r="K92" s="8" t="inlineStr"/>
       <c r="L92" s="8" t="inlineStr"/>
       <c r="M92" s="8" t="inlineStr"/>
       <c r="N92" s="8" t="inlineStr"/>
-      <c r="O92" s="8" t="inlineStr"/>
+      <c r="O92" s="8" t="inlineStr">
+        <is>
+          <t>418.00</t>
+        </is>
+      </c>
       <c r="P92" s="8" t="inlineStr"/>
       <c r="Q92" s="8" t="inlineStr"/>
       <c r="R92" s="8" t="inlineStr"/>
       <c r="S92" s="8" t="inlineStr"/>
       <c r="T92" s="8" t="inlineStr">
         <is>
-          <t>557.00</t>
+          <t>470.00</t>
         </is>
       </c>
       <c r="U92" s="8" t="inlineStr"/>
-      <c r="V92" s="9" t="inlineStr"/>
+      <c r="V92" s="9" t="n">
+        <v>460.6666666666667</v>
+      </c>
       <c r="W92" s="10" t="inlineStr"/>
       <c r="X92" s="11" t="inlineStr"/>
     </row>
@@ -5040,7 +5044,7 @@
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr"/>
@@ -5049,19 +5053,15 @@
       <c r="F93" s="8" t="inlineStr"/>
       <c r="G93" s="8" t="inlineStr"/>
       <c r="H93" s="8" t="inlineStr"/>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>521.00</t>
-        </is>
-      </c>
+      <c r="I93" s="8" t="inlineStr"/>
       <c r="J93" s="8" t="inlineStr"/>
       <c r="K93" s="8" t="inlineStr"/>
       <c r="L93" s="8" t="inlineStr"/>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
-      <c r="O93" s="8" t="inlineStr">
-        <is>
-          <t>450.00</t>
+      <c r="O93" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
         </is>
       </c>
       <c r="P93" s="8" t="inlineStr"/>
@@ -5070,124 +5070,122 @@
       <c r="S93" s="8" t="inlineStr"/>
       <c r="T93" s="8" t="inlineStr">
         <is>
+          <t>557.00</t>
+        </is>
+      </c>
+      <c r="U93" s="8" t="inlineStr"/>
+      <c r="V93" s="9" t="inlineStr"/>
+      <c r="W93" s="10" t="inlineStr"/>
+      <c r="X93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="1" t="n"/>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr"/>
+      <c r="D94" s="8" t="inlineStr"/>
+      <c r="E94" s="8" t="inlineStr"/>
+      <c r="F94" s="8" t="inlineStr"/>
+      <c r="G94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>521.00</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr"/>
+      <c r="L94" s="8" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr"/>
+      <c r="N94" s="8" t="inlineStr"/>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
+      <c r="P94" s="8" t="inlineStr"/>
+      <c r="Q94" s="8" t="inlineStr"/>
+      <c r="R94" s="8" t="inlineStr"/>
+      <c r="S94" s="8" t="inlineStr"/>
+      <c r="T94" s="8" t="inlineStr">
+        <is>
           <t>545.00</t>
         </is>
       </c>
-      <c r="U93" s="8" t="inlineStr"/>
-      <c r="V93" s="9" t="n">
+      <c r="U94" s="8" t="inlineStr"/>
+      <c r="V94" s="9" t="n">
         <v>505.3333333333333</v>
       </c>
-      <c r="W93" s="9" t="n">
+      <c r="W94" s="9" t="n">
         <v>44.66666666666663</v>
       </c>
-      <c r="X93" s="11" t="n">
+      <c r="X94" s="11" t="n">
         <v>0.001063839077667397</v>
       </c>
     </row>
-    <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95" ht="24" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>UpNDown
 Random: 533.4
 Human: 11693.2</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 7985</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr"/>
-      <c r="D94" s="4" t="inlineStr"/>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr"/>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
-      <c r="K94" s="4" t="inlineStr"/>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr"/>
-      <c r="O94" s="4" t="inlineStr"/>
-      <c r="P94" s="4" t="inlineStr"/>
-      <c r="Q94" s="4" t="inlineStr"/>
-      <c r="R94" s="4" t="inlineStr"/>
-      <c r="S94" s="4" t="inlineStr"/>
-      <c r="T94" s="4" t="inlineStr"/>
-      <c r="U94" s="4" t="inlineStr"/>
-      <c r="V94" s="5" t="inlineStr"/>
-      <c r="W94" s="6" t="n">
+      <c r="C95" s="4" t="inlineStr"/>
+      <c r="D95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="inlineStr"/>
+      <c r="N95" s="4" t="inlineStr"/>
+      <c r="O95" s="4" t="inlineStr"/>
+      <c r="P95" s="4" t="inlineStr"/>
+      <c r="Q95" s="4" t="inlineStr"/>
+      <c r="R95" s="4" t="inlineStr"/>
+      <c r="S95" s="4" t="inlineStr"/>
+      <c r="T95" s="4" t="inlineStr"/>
+      <c r="U95" s="4" t="inlineStr"/>
+      <c r="V95" s="5" t="inlineStr"/>
+      <c r="W95" s="6" t="n">
         <v>-2963</v>
       </c>
-      <c r="X94" s="7" t="n">
+      <c r="X95" s="7" t="n">
         <v>-0.2655065502966003</v>
       </c>
-    </row>
-    <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="1" t="n"/>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>9044.00</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="inlineStr"/>
-      <c r="E95" s="8" t="inlineStr"/>
-      <c r="F95" s="8" t="inlineStr"/>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>5849.00</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr"/>
-      <c r="I95" s="8" t="inlineStr"/>
-      <c r="J95" s="8" t="inlineStr"/>
-      <c r="K95" s="8" t="inlineStr"/>
-      <c r="L95" s="8" t="inlineStr"/>
-      <c r="M95" s="8" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr"/>
-      <c r="O95" s="8" t="inlineStr">
-        <is>
-          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
-        </is>
-      </c>
-      <c r="P95" s="8" t="inlineStr">
-        <is>
-          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
-        </is>
-      </c>
-      <c r="Q95" s="8" t="inlineStr">
-        <is>
-          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="R95" s="8" t="inlineStr"/>
-      <c r="S95" s="8" t="inlineStr"/>
-      <c r="T95" s="8" t="inlineStr"/>
-      <c r="U95" s="8" t="inlineStr"/>
-      <c r="V95" s="9" t="n">
-        <v>5022</v>
-      </c>
-      <c r="W95" s="10" t="inlineStr"/>
-      <c r="X95" s="11" t="inlineStr"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>9044.00</t>
+        </is>
+      </c>
       <c r="D96" s="8" t="inlineStr"/>
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr"/>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>5849.00</t>
+        </is>
+      </c>
       <c r="H96" s="8" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr"/>
       <c r="J96" s="8" t="inlineStr"/>
@@ -5197,24 +5195,26 @@
       <c r="N96" s="8" t="inlineStr"/>
       <c r="O96" s="8" t="inlineStr">
         <is>
-          <t>5670.00</t>
+          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
         </is>
       </c>
       <c r="P96" s="8" t="inlineStr">
         <is>
-          <t>7178.00</t>
+          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
         </is>
       </c>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>3066.00</t>
+          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
         </is>
       </c>
       <c r="R96" s="8" t="inlineStr"/>
       <c r="S96" s="8" t="inlineStr"/>
       <c r="T96" s="8" t="inlineStr"/>
       <c r="U96" s="8" t="inlineStr"/>
-      <c r="V96" s="9" t="inlineStr"/>
+      <c r="V96" s="9" t="n">
+        <v>5022</v>
+      </c>
       <c r="W96" s="10" t="inlineStr"/>
       <c r="X96" s="11" t="inlineStr"/>
     </row>
@@ -5222,7 +5222,7 @@
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
@@ -5239,61 +5239,103 @@
       <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="8" t="inlineStr">
         <is>
-          <t>6043.00</t>
+          <t>5670.00</t>
         </is>
       </c>
       <c r="P97" s="8" t="inlineStr">
         <is>
-          <t>6658.00</t>
+          <t>7178.00</t>
         </is>
       </c>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>2974.50</t>
+          <t>3066.00</t>
         </is>
       </c>
       <c r="R97" s="8" t="inlineStr"/>
       <c r="S97" s="8" t="inlineStr"/>
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
-      <c r="V97" s="9" t="n">
+      <c r="V97" s="9" t="inlineStr"/>
+      <c r="W97" s="10" t="inlineStr"/>
+      <c r="X97" s="11" t="inlineStr"/>
+    </row>
+    <row r="98" ht="24" customHeight="1">
+      <c r="A98" s="1" t="n"/>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr"/>
+      <c r="D98" s="8" t="inlineStr"/>
+      <c r="E98" s="8" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr"/>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
+      <c r="J98" s="8" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr"/>
+      <c r="L98" s="8" t="inlineStr"/>
+      <c r="M98" s="8" t="inlineStr"/>
+      <c r="N98" s="8" t="inlineStr"/>
+      <c r="O98" s="8" t="inlineStr">
+        <is>
+          <t>6043.00</t>
+        </is>
+      </c>
+      <c r="P98" s="8" t="inlineStr">
+        <is>
+          <t>6658.00</t>
+        </is>
+      </c>
+      <c r="Q98" s="8" t="inlineStr">
+        <is>
+          <t>2974.50</t>
+        </is>
+      </c>
+      <c r="R98" s="8" t="inlineStr"/>
+      <c r="S98" s="8" t="inlineStr"/>
+      <c r="T98" s="8" t="inlineStr"/>
+      <c r="U98" s="8" t="inlineStr"/>
+      <c r="V98" s="9" t="n">
         <v>5225.166666666667</v>
       </c>
-      <c r="W97" s="9" t="n">
+      <c r="W98" s="9" t="n">
         <v>203.166666666667</v>
       </c>
-      <c r="X97" s="11" t="n">
+      <c r="X98" s="11" t="n">
         <v>0.01820522470534122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A48:A51"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A87:A90"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A79:A81"/>
-    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A95:A98"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="A73:A75"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A91:A94"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A63:A66"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="A74:A76"/>
     <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A52:A55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -296,6 +296,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="P53" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="T53" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
@@ -310,6 +317,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="P54" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="T54" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
@@ -320,6 +334,13 @@
     <comment ref="O55" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P55" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -3212,7 +3233,7 @@
           <t>2486.00</t>
         </is>
       </c>
-      <c r="P53" s="8" t="inlineStr">
+      <c r="P53" s="12" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
@@ -3256,7 +3277,7 @@
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
       <c r="O54" s="12" t="inlineStr"/>
-      <c r="P54" s="8" t="inlineStr"/>
+      <c r="P54" s="12" t="inlineStr"/>
       <c r="Q54" s="8" t="inlineStr"/>
       <c r="R54" s="13" t="inlineStr">
         <is>
@@ -3302,7 +3323,7 @@
           <t>1024.00</t>
         </is>
       </c>
-      <c r="P55" s="8" t="inlineStr">
+      <c r="P55" s="12" t="inlineStr">
         <is>
           <t>927.00</t>
         </is>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -145,8 +145,8 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -229,147 +229,245 @@
     <author>STORM</author>
   </authors>
   <commentList>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>Retrieval 미사용과 target: 16 양쪽에 유효한 점수가 있는 공통 시드만 사용합니다. 각 시드에 여러 결과가 있으면 첫 번째 점수를 사용합니다.</t>
+        <t>Retrieval 미사용과 target: 16 양쪽에 유효한 점수가 있는 공통 시드만 사용합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드는 제외합니다. 각 시드에 여러 결과가 있으면 첫 번째 점수를 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: Retrieval 미사용의 공통 시드 평균 − STORM 논문 점수.
 target: 16 행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: (Retrieval 미사용 평균 − STORM 논문 점수) / (Human − Random).
 target: 16 행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
-모든 평균은 공통 시드 기준이며 HNS 차이는 부호를 유지합니다. 백분율이 아닙니다.</t>
+모든 평균은 EXCLUDED_SEEDS를 제외한 공통 시드 기준이며 HNS 차이는 부호를 유지합니다. 백분율이 아닙니다.</t>
       </text>
     </comment>
     <comment ref="Q19" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="Q20" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P23" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P24" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P25" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O27" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O28" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O29" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="E49" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="O53" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="P53" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="T53" authorId="0" shapeId="0">
+    <comment ref="U53" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="O54" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="P54" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="T54" authorId="0" shapeId="0">
+    <comment ref="U54" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="O55" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="P55" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="T55" authorId="0" shapeId="0">
+    <comment ref="U55" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I68" authorId="0" shapeId="0">
+    <comment ref="K68" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I69" authorId="0" shapeId="0">
+    <comment ref="L68" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I70" authorId="0" shapeId="0">
+    <comment ref="K69" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM-1/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 LaTeX 결과 집계에서 제외되는 시드입니다.
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L69" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K70" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L70" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I84" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I85" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I86" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
@@ -666,15 +764,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X98"/>
+  <dimension ref="A1:Y98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
     <col width="41.1" customWidth="1" min="2" max="2"/>
-    <col width="3" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="46" customWidth="1" min="23" max="23"/>
-    <col width="32" customWidth="1" min="24" max="24"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="19" max="19"/>
+    <col width="3" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="46" customWidth="1" min="24" max="24"/>
+    <col width="32" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,32 +802,32 @@
         <v>710</v>
       </c>
       <c r="G1" s="1" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>2710</v>
+      </c>
+      <c r="I1" s="1" t="n">
         <v>3710</v>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>  </t>
         </is>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>5090</v>
-      </c>
-      <c r="M1" s="1" t="n">
-        <v>1710</v>
-      </c>
-      <c r="N1" s="1" t="n">
-        <v>2710</v>
       </c>
       <c r="O1" s="1" t="n">
         <v>6000</v>
@@ -740,28 +841,33 @@
       <c r="R1" s="1" t="n">
         <v>6030</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>    </t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="n">
         <v>9998</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>9999</v>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>   </t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -799,11 +905,12 @@
       <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr"/>
-      <c r="W2" s="6" t="n">
+      <c r="V2" s="4" t="inlineStr"/>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="6" t="n">
         <v>57.79999999999995</v>
       </c>
-      <c r="X2" s="7" t="n">
+      <c r="Y2" s="7" t="n">
         <v>0.008376932999028966</v>
       </c>
     </row>
@@ -824,24 +931,24 @@
       <c r="F3" s="8" t="inlineStr"/>
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>688.50</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>817.00</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>842.50</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="8" t="inlineStr">
         <is>
           <t>1397.50, 1426.50, 1411.00</t>
@@ -857,11 +964,12 @@
       <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="8" t="inlineStr"/>
-      <c r="V3" s="9" t="n">
+      <c r="V3" s="8" t="inlineStr"/>
+      <c r="W3" s="9" t="n">
         <v>1041.8</v>
       </c>
-      <c r="W3" s="10" t="inlineStr"/>
-      <c r="X3" s="11" t="inlineStr"/>
+      <c r="X3" s="10" t="inlineStr"/>
+      <c r="Y3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -880,13 +988,13 @@
       <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>641.00</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
       <c r="L4" s="8" t="inlineStr"/>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
@@ -905,9 +1013,10 @@
       <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="8" t="inlineStr"/>
-      <c r="V4" s="9" t="inlineStr"/>
-      <c r="W4" s="10" t="inlineStr"/>
-      <c r="X4" s="11" t="inlineStr"/>
+      <c r="V4" s="8" t="inlineStr"/>
+      <c r="W4" s="9" t="inlineStr"/>
+      <c r="X4" s="10" t="inlineStr"/>
+      <c r="Y4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -926,20 +1035,20 @@
       <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>743.50</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>864.00</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr">
         <is>
           <t>1400.00</t>
@@ -955,13 +1064,14 @@
       <c r="S5" s="8" t="inlineStr"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="8" t="inlineStr"/>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="inlineStr"/>
+      <c r="W5" s="9" t="n">
         <v>1091.1</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="X5" s="9" t="n">
         <v>49.29999999999995</v>
       </c>
-      <c r="X5" s="11" t="n">
+      <c r="Y5" s="11" t="n">
         <v>0.007145031087407058</v>
       </c>
     </row>
@@ -997,12 +1107,13 @@
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr"/>
-      <c r="W6" s="6" t="n">
-        <v>2.849999999999994</v>
-      </c>
-      <c r="X6" s="7" t="n">
-        <v>0.001663068214973446</v>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="6" t="n">
+        <v>-29.0625</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>-0.01695891929742662</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
@@ -1022,20 +1133,20 @@
       <c r="F7" s="8" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>177.55</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>204.85</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="8" t="inlineStr">
         <is>
           <t>126.40, 128.45, 130.35</t>
@@ -1055,11 +1166,12 @@
       <c r="S7" s="8" t="inlineStr"/>
       <c r="T7" s="8" t="inlineStr"/>
       <c r="U7" s="8" t="inlineStr"/>
-      <c r="V7" s="9" t="n">
-        <v>207.85</v>
-      </c>
-      <c r="W7" s="10" t="inlineStr"/>
-      <c r="X7" s="11" t="inlineStr"/>
+      <c r="V7" s="8" t="inlineStr"/>
+      <c r="W7" s="9" t="n">
+        <v>175.9375</v>
+      </c>
+      <c r="X7" s="10" t="inlineStr"/>
+      <c r="Y7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="1" t="n"/>
@@ -1103,9 +1215,10 @@
       <c r="S8" s="8" t="inlineStr"/>
       <c r="T8" s="8" t="inlineStr"/>
       <c r="U8" s="8" t="inlineStr"/>
-      <c r="V8" s="9" t="inlineStr"/>
-      <c r="W8" s="10" t="inlineStr"/>
-      <c r="X8" s="11" t="inlineStr"/>
+      <c r="V8" s="8" t="inlineStr"/>
+      <c r="W8" s="9" t="inlineStr"/>
+      <c r="X8" s="10" t="inlineStr"/>
+      <c r="Y8" s="11" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="1" t="n"/>
@@ -1124,43 +1237,44 @@
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>129.40</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr">
         <is>
           <t>147.80</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="8" t="inlineStr">
         <is>
           <t>155.25</t>
         </is>
       </c>
       <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr">
-        <is>
-          <t>222.50</t>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING, 236.55, 222.50</t>
         </is>
       </c>
       <c r="R9" s="8" t="inlineStr"/>
       <c r="S9" s="8" t="inlineStr"/>
       <c r="T9" s="8" t="inlineStr"/>
       <c r="U9" s="8" t="inlineStr"/>
-      <c r="V9" s="9" t="n">
-        <v>164.88</v>
-      </c>
+      <c r="V9" s="8" t="inlineStr"/>
       <c r="W9" s="9" t="n">
-        <v>42.96999999999997</v>
-      </c>
-      <c r="X9" s="11" t="n">
-        <v>-0.02507440042014353</v>
+        <v>150.475</v>
+      </c>
+      <c r="X9" s="9" t="n">
+        <v>25.46249999999998</v>
+      </c>
+      <c r="Y9" s="11" t="n">
+        <v>-0.01485820155219699</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -1195,12 +1309,13 @@
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="4" t="inlineStr"/>
       <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="5" t="inlineStr"/>
-      <c r="W10" s="6" t="n">
-        <v>-22.95000000000005</v>
-      </c>
-      <c r="X10" s="7" t="n">
-        <v>-0.04416859122401856</v>
+      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="6" t="n">
+        <v>-36.5625</v>
+      </c>
+      <c r="Y10" s="7" t="n">
+        <v>-0.07036662817551963</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
@@ -1220,24 +1335,24 @@
       <c r="F11" s="8" t="inlineStr"/>
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>620.40</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>605.80</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr">
         <is>
           <t>662.40</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="8" t="inlineStr">
         <is>
           <t>1126.55</t>
@@ -1253,11 +1368,12 @@
       <c r="S11" s="8" t="inlineStr"/>
       <c r="T11" s="8" t="inlineStr"/>
       <c r="U11" s="8" t="inlineStr"/>
-      <c r="V11" s="9" t="n">
-        <v>778.05</v>
-      </c>
-      <c r="W11" s="10" t="inlineStr"/>
-      <c r="X11" s="11" t="inlineStr"/>
+      <c r="V11" s="8" t="inlineStr"/>
+      <c r="W11" s="9" t="n">
+        <v>764.4375</v>
+      </c>
+      <c r="X11" s="10" t="inlineStr"/>
+      <c r="Y11" s="11" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="1" t="n"/>
@@ -1276,13 +1392,13 @@
       <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr"/>
       <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>693.30</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
       <c r="L12" s="8" t="inlineStr"/>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
@@ -1301,9 +1417,10 @@
       <c r="S12" s="8" t="inlineStr"/>
       <c r="T12" s="8" t="inlineStr"/>
       <c r="U12" s="8" t="inlineStr"/>
-      <c r="V12" s="9" t="inlineStr"/>
-      <c r="W12" s="10" t="inlineStr"/>
-      <c r="X12" s="11" t="inlineStr"/>
+      <c r="V12" s="8" t="inlineStr"/>
+      <c r="W12" s="9" t="inlineStr"/>
+      <c r="X12" s="10" t="inlineStr"/>
+      <c r="Y12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -1328,24 +1445,24 @@
           <t>548.60</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>720.25</t>
-        </is>
-      </c>
+      <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="8" t="inlineStr">
         <is>
+          <t>720.25</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
           <t>666.55</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>633.05</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="8" t="inlineStr">
@@ -1353,9 +1470,9 @@
           <t>724.80</t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>723.85</t>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING, 723.85</t>
         </is>
       </c>
       <c r="Q13" s="8" t="inlineStr"/>
@@ -1363,14 +1480,15 @@
       <c r="S13" s="8" t="inlineStr"/>
       <c r="T13" s="8" t="inlineStr"/>
       <c r="U13" s="8" t="inlineStr"/>
-      <c r="V13" s="9" t="n">
-        <v>705.5400000000001</v>
-      </c>
+      <c r="V13" s="8" t="inlineStr"/>
       <c r="W13" s="9" t="n">
-        <v>72.50999999999988</v>
-      </c>
-      <c r="X13" s="11" t="n">
-        <v>-0.1395496535796764</v>
+        <v>700.9625000000001</v>
+      </c>
+      <c r="X13" s="9" t="n">
+        <v>63.47499999999991</v>
+      </c>
+      <c r="Y13" s="11" t="n">
+        <v>-0.1221612779060814</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
@@ -1405,12 +1523,13 @@
       <c r="S14" s="4" t="inlineStr"/>
       <c r="T14" s="4" t="inlineStr"/>
       <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="5" t="inlineStr"/>
-      <c r="W14" s="6" t="n">
-        <v>-350.5</v>
-      </c>
-      <c r="X14" s="7" t="n">
-        <v>-0.04226303160382478</v>
+      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="6" t="n">
+        <v>-349.6666666666666</v>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>-0.04216254888484278</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
@@ -1432,13 +1551,13 @@
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>562.50</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr"/>
       <c r="K15" s="8" t="inlineStr"/>
       <c r="L15" s="8" t="inlineStr"/>
@@ -1459,11 +1578,12 @@
       <c r="S15" s="8" t="inlineStr"/>
       <c r="T15" s="8" t="inlineStr"/>
       <c r="U15" s="8" t="inlineStr"/>
-      <c r="V15" s="9" t="n">
-        <v>677.5</v>
-      </c>
-      <c r="W15" s="10" t="inlineStr"/>
-      <c r="X15" s="11" t="inlineStr"/>
+      <c r="V15" s="8" t="inlineStr"/>
+      <c r="W15" s="9" t="n">
+        <v>678.3333333333334</v>
+      </c>
+      <c r="X15" s="10" t="inlineStr"/>
+      <c r="Y15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -1480,13 +1600,13 @@
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>677.50</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="8" t="inlineStr"/>
       <c r="L16" s="8" t="inlineStr"/>
@@ -1503,9 +1623,10 @@
       <c r="S16" s="8" t="inlineStr"/>
       <c r="T16" s="8" t="inlineStr"/>
       <c r="U16" s="8" t="inlineStr"/>
-      <c r="V16" s="9" t="inlineStr"/>
-      <c r="W16" s="10" t="inlineStr"/>
-      <c r="X16" s="11" t="inlineStr"/>
+      <c r="V16" s="8" t="inlineStr"/>
+      <c r="W16" s="9" t="inlineStr"/>
+      <c r="X16" s="10" t="inlineStr"/>
+      <c r="Y16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -1522,13 +1643,13 @@
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>545.00</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="inlineStr"/>
       <c r="K17" s="8" t="inlineStr"/>
       <c r="L17" s="8" t="inlineStr"/>
@@ -1539,9 +1660,9 @@
           <t>887.50</t>
         </is>
       </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>1005.00</t>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING, 1005.00</t>
         </is>
       </c>
       <c r="Q17" s="8" t="inlineStr"/>
@@ -1549,14 +1670,15 @@
       <c r="S17" s="8" t="inlineStr"/>
       <c r="T17" s="8" t="inlineStr"/>
       <c r="U17" s="8" t="inlineStr"/>
-      <c r="V17" s="9" t="n">
-        <v>759.375</v>
-      </c>
+      <c r="V17" s="8" t="inlineStr"/>
       <c r="W17" s="9" t="n">
-        <v>81.875</v>
-      </c>
-      <c r="X17" s="11" t="n">
-        <v>0.009872427139980468</v>
+        <v>677.5</v>
+      </c>
+      <c r="X17" s="9" t="n">
+        <v>0.8333333333333712</v>
+      </c>
+      <c r="Y17" s="11" t="n">
+        <v>-0.000100482718981994</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
@@ -1591,12 +1713,13 @@
       <c r="S18" s="4" t="inlineStr"/>
       <c r="T18" s="4" t="inlineStr"/>
       <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="5" t="inlineStr"/>
-      <c r="W18" s="6" t="n">
-        <v>-89.125</v>
-      </c>
-      <c r="X18" s="7" t="n">
-        <v>-0.120618486940046</v>
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="5" t="inlineStr"/>
+      <c r="X18" s="6" t="n">
+        <v>-84.75</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>-0.1146975233455136</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
@@ -1612,24 +1735,24 @@
       <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>163.00</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>699.00</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr">
         <is>
           <t>521.00</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="8" t="inlineStr">
         <is>
           <t>246.00</t>
@@ -1640,28 +1763,29 @@
           <t>170.00</t>
         </is>
       </c>
-      <c r="Q19" s="12" t="inlineStr">
+      <c r="Q19" s="13" t="inlineStr">
         <is>
           <t>677.00</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr"/>
-      <c r="S19" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="S19" s="8" t="inlineStr"/>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>694.50</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>668.50</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr"/>
-      <c r="V19" s="9" t="n">
-        <v>551.875</v>
-      </c>
-      <c r="W19" s="10" t="inlineStr"/>
-      <c r="X19" s="11" t="inlineStr"/>
+      <c r="V19" s="8" t="inlineStr"/>
+      <c r="W19" s="9" t="n">
+        <v>556.25</v>
+      </c>
+      <c r="X19" s="10" t="inlineStr"/>
+      <c r="Y19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="1" t="n"/>
@@ -1684,18 +1808,19 @@
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="8" t="inlineStr"/>
       <c r="P20" s="8" t="inlineStr"/>
-      <c r="Q20" s="12" t="inlineStr"/>
+      <c r="Q20" s="13" t="inlineStr"/>
       <c r="R20" s="8" t="inlineStr"/>
       <c r="S20" s="8" t="inlineStr"/>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="T20" s="8" t="inlineStr"/>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>507.50</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr"/>
-      <c r="V20" s="9" t="inlineStr"/>
-      <c r="W20" s="10" t="inlineStr"/>
-      <c r="X20" s="11" t="inlineStr"/>
+      <c r="V20" s="8" t="inlineStr"/>
+      <c r="W20" s="9" t="inlineStr"/>
+      <c r="X20" s="10" t="inlineStr"/>
+      <c r="Y20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="1" t="n"/>
@@ -1710,47 +1835,48 @@
       <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr"/>
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>169.50</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>633.50</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="8" t="inlineStr"/>
       <c r="P21" s="8" t="inlineStr"/>
-      <c r="Q21" s="12" t="inlineStr">
+      <c r="Q21" s="13" t="inlineStr">
         <is>
           <t>114.00</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr"/>
-      <c r="S21" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="S21" s="8" t="inlineStr"/>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>566.00</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>565.00</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr"/>
-      <c r="V21" s="9" t="n">
-        <v>370.5</v>
-      </c>
+      <c r="V21" s="8" t="inlineStr"/>
       <c r="W21" s="9" t="n">
-        <v>181.375</v>
-      </c>
-      <c r="X21" s="11" t="n">
-        <v>-0.2454662335904723</v>
+        <v>483.5</v>
+      </c>
+      <c r="X21" s="9" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="Y21" s="11" t="n">
+        <v>-0.09845716605765327</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
@@ -1785,12 +1911,13 @@
       <c r="S22" s="4" t="inlineStr"/>
       <c r="T22" s="4" t="inlineStr"/>
       <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="5" t="inlineStr"/>
-      <c r="W22" s="6" t="n">
-        <v>-2965</v>
-      </c>
-      <c r="X22" s="7" t="n">
-        <v>-0.08513387409374776</v>
+      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="5" t="inlineStr"/>
+      <c r="X22" s="6" t="n">
+        <v>-3777.5</v>
+      </c>
+      <c r="Y22" s="7" t="n">
+        <v>-0.1084631397602469</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
@@ -1806,30 +1933,30 @@
       <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>5300.00</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>15900.00</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr"/>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr">
         <is>
           <t>9650.00</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="8" t="inlineStr">
         <is>
           <t>15100.00, 16150.00, 14200.00, 14800.00</t>
         </is>
       </c>
-      <c r="P23" s="8" t="inlineStr">
+      <c r="P23" s="13" t="inlineStr">
         <is>
           <t>9300.00, 8850.00, 8250.00, 9250.00</t>
         </is>
@@ -1843,11 +1970,12 @@
       <c r="S23" s="8" t="inlineStr"/>
       <c r="T23" s="8" t="inlineStr"/>
       <c r="U23" s="8" t="inlineStr"/>
-      <c r="V23" s="9" t="n">
-        <v>10575</v>
-      </c>
-      <c r="W23" s="10" t="inlineStr"/>
-      <c r="X23" s="11" t="inlineStr"/>
+      <c r="V23" s="8" t="inlineStr"/>
+      <c r="W23" s="9" t="n">
+        <v>9762.5</v>
+      </c>
+      <c r="X23" s="10" t="inlineStr"/>
+      <c r="Y23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="1" t="n"/>
@@ -1862,18 +1990,18 @@
       <c r="F24" s="8" t="inlineStr"/>
       <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr"/>
+      <c r="J24" s="8" t="inlineStr"/>
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>5550.00</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr">
         <is>
           <t>13900.00</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="8" t="inlineStr"/>
       <c r="O24" s="8" t="inlineStr">
@@ -1881,7 +2009,7 @@
           <t>10950.00</t>
         </is>
       </c>
-      <c r="P24" s="8" t="inlineStr">
+      <c r="P24" s="13" t="inlineStr">
         <is>
           <t>5900.00</t>
         </is>
@@ -1895,9 +2023,10 @@
       <c r="S24" s="8" t="inlineStr"/>
       <c r="T24" s="8" t="inlineStr"/>
       <c r="U24" s="8" t="inlineStr"/>
-      <c r="V24" s="9" t="inlineStr"/>
-      <c r="W24" s="10" t="inlineStr"/>
-      <c r="X24" s="11" t="inlineStr"/>
+      <c r="V24" s="8" t="inlineStr"/>
+      <c r="W24" s="9" t="inlineStr"/>
+      <c r="X24" s="10" t="inlineStr"/>
+      <c r="Y24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -1912,30 +2041,30 @@
       <c r="F25" s="8" t="inlineStr"/>
       <c r="G25" s="8" t="inlineStr"/>
       <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>5500.00</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>14250.00</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr"/>
+      <c r="N25" s="8" t="inlineStr">
         <is>
           <t>13050.00</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>14350.00</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING, 14350.00</t>
+        </is>
+      </c>
+      <c r="P25" s="13" t="inlineStr">
         <is>
           <t>5650.00</t>
         </is>
@@ -1949,14 +2078,15 @@
       <c r="S25" s="8" t="inlineStr"/>
       <c r="T25" s="8" t="inlineStr"/>
       <c r="U25" s="8" t="inlineStr"/>
-      <c r="V25" s="9" t="n">
-        <v>10608.33333333333</v>
-      </c>
+      <c r="V25" s="8" t="inlineStr"/>
       <c r="W25" s="9" t="n">
-        <v>33.33333333333394</v>
-      </c>
-      <c r="X25" s="11" t="n">
-        <v>0.0009570980786256245</v>
+        <v>10912.5</v>
+      </c>
+      <c r="X25" s="9" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Y25" s="11" t="n">
+        <v>0.03301988371258345</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
@@ -1991,12 +2121,13 @@
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="4" t="inlineStr"/>
       <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="5" t="inlineStr"/>
-      <c r="W26" s="6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X26" s="7" t="n">
-        <v>-0.25</v>
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="5" t="inlineStr"/>
+      <c r="X26" s="6" t="n">
+        <v>-1.350000000000009</v>
+      </c>
+      <c r="Y26" s="7" t="n">
+        <v>-0.1125000000000007</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
@@ -2014,27 +2145,27 @@
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>73.80</t>
-        </is>
-      </c>
+      <c r="G27" s="8" t="inlineStr"/>
       <c r="H27" s="8" t="inlineStr"/>
       <c r="I27" s="8" t="inlineStr">
         <is>
+          <t>73.80</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
           <t>81.00</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr">
         <is>
           <t>88.60</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="13" t="inlineStr">
         <is>
           <t>70.40</t>
         </is>
@@ -2053,11 +2184,12 @@
       <c r="S27" s="8" t="inlineStr"/>
       <c r="T27" s="8" t="inlineStr"/>
       <c r="U27" s="8" t="inlineStr"/>
-      <c r="V27" s="9" t="n">
-        <v>77</v>
-      </c>
-      <c r="W27" s="10" t="inlineStr"/>
-      <c r="X27" s="11" t="inlineStr"/>
+      <c r="V27" s="8" t="inlineStr"/>
+      <c r="W27" s="9" t="n">
+        <v>78.64999999999999</v>
+      </c>
+      <c r="X27" s="10" t="inlineStr"/>
+      <c r="Y27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -2082,16 +2214,17 @@
       <c r="L28" s="8" t="inlineStr"/>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="8" t="inlineStr"/>
-      <c r="O28" s="8" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr"/>
       <c r="P28" s="8" t="inlineStr"/>
       <c r="Q28" s="8" t="inlineStr"/>
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr"/>
       <c r="T28" s="8" t="inlineStr"/>
       <c r="U28" s="8" t="inlineStr"/>
-      <c r="V28" s="9" t="inlineStr"/>
-      <c r="W28" s="10" t="inlineStr"/>
-      <c r="X28" s="11" t="inlineStr"/>
+      <c r="V28" s="8" t="inlineStr"/>
+      <c r="W28" s="9" t="inlineStr"/>
+      <c r="X28" s="10" t="inlineStr"/>
+      <c r="Y28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -2110,17 +2243,17 @@
       <c r="F29" s="8" t="inlineStr"/>
       <c r="G29" s="8" t="inlineStr"/>
       <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>78.50</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr"/>
-      <c r="K29" s="8" t="inlineStr"/>
       <c r="L29" s="8" t="inlineStr"/>
       <c r="M29" s="8" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="13" t="inlineStr">
         <is>
           <t>51.15</t>
         </is>
@@ -2139,14 +2272,15 @@
       <c r="S29" s="8" t="inlineStr"/>
       <c r="T29" s="8" t="inlineStr"/>
       <c r="U29" s="8" t="inlineStr"/>
-      <c r="V29" s="9" t="n">
-        <v>75.75</v>
-      </c>
+      <c r="V29" s="8" t="inlineStr"/>
       <c r="W29" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X29" s="11" t="n">
-        <v>-0.1041666666666667</v>
+        <v>81.90000000000001</v>
+      </c>
+      <c r="X29" s="9" t="n">
+        <v>3.250000000000014</v>
+      </c>
+      <c r="Y29" s="11" t="n">
+        <v>0.2708333333333345</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
@@ -2181,11 +2315,12 @@
       <c r="S30" s="4" t="inlineStr"/>
       <c r="T30" s="4" t="inlineStr"/>
       <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="5" t="inlineStr"/>
-      <c r="W30" s="6" t="n">
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="5" t="inlineStr"/>
+      <c r="X30" s="6" t="n">
         <v>-4.266666666666666</v>
       </c>
-      <c r="X30" s="7" t="n">
+      <c r="Y30" s="7" t="n">
         <v>-0.1481481481481481</v>
       </c>
     </row>
@@ -2212,19 +2347,19 @@
           <t>9.60</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
-      </c>
+      <c r="G31" s="8" t="inlineStr"/>
       <c r="H31" s="8" t="inlineStr"/>
       <c r="I31" s="8" t="inlineStr">
         <is>
+          <t>14.00</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
           <t>9.80</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr"/>
       <c r="L31" s="8" t="inlineStr"/>
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
@@ -2235,11 +2370,12 @@
       <c r="S31" s="8" t="inlineStr"/>
       <c r="T31" s="8" t="inlineStr"/>
       <c r="U31" s="8" t="inlineStr"/>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="inlineStr"/>
+      <c r="W31" s="9" t="n">
         <v>11.73333333333333</v>
       </c>
-      <c r="W31" s="10" t="inlineStr"/>
-      <c r="X31" s="11" t="inlineStr"/>
+      <c r="X31" s="10" t="inlineStr"/>
+      <c r="Y31" s="11" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="1" t="n"/>
@@ -2256,19 +2392,19 @@
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>15.60</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
       <c r="J32" s="8" t="inlineStr"/>
-      <c r="K32" s="8" t="inlineStr"/>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
       <c r="L32" s="8" t="inlineStr"/>
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="8" t="inlineStr"/>
@@ -2279,9 +2415,10 @@
       <c r="S32" s="8" t="inlineStr"/>
       <c r="T32" s="8" t="inlineStr"/>
       <c r="U32" s="8" t="inlineStr"/>
-      <c r="V32" s="9" t="inlineStr"/>
-      <c r="W32" s="10" t="inlineStr"/>
-      <c r="X32" s="11" t="inlineStr"/>
+      <c r="V32" s="8" t="inlineStr"/>
+      <c r="W32" s="9" t="inlineStr"/>
+      <c r="X32" s="10" t="inlineStr"/>
+      <c r="Y32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="1" t="n"/>
@@ -2298,19 +2435,19 @@
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr"/>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
+      <c r="G33" s="8" t="inlineStr"/>
       <c r="H33" s="8" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr">
         <is>
+          <t>15.10</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
           <t>9.30</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr"/>
       <c r="L33" s="8" t="inlineStr"/>
       <c r="M33" s="8" t="inlineStr"/>
       <c r="N33" s="8" t="inlineStr"/>
@@ -2321,13 +2458,14 @@
       <c r="S33" s="8" t="inlineStr"/>
       <c r="T33" s="8" t="inlineStr"/>
       <c r="U33" s="8" t="inlineStr"/>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="inlineStr"/>
+      <c r="W33" s="9" t="n">
         <v>12.36666666666667</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="X33" s="9" t="n">
         <v>0.6333333333333311</v>
       </c>
-      <c r="X33" s="11" t="n">
+      <c r="Y33" s="11" t="n">
         <v>0.02199074074074066</v>
       </c>
     </row>
@@ -2363,12 +2501,13 @@
       <c r="S34" s="4" t="inlineStr"/>
       <c r="T34" s="4" t="inlineStr"/>
       <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr"/>
-      <c r="W34" s="6" t="n">
-        <v>-289.6666666666667</v>
-      </c>
-      <c r="X34" s="7" t="n">
-        <v>-0.04404370920001623</v>
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="5" t="inlineStr"/>
+      <c r="X34" s="6" t="n">
+        <v>-480.5</v>
+      </c>
+      <c r="Y34" s="7" t="n">
+        <v>-0.07305984673397396</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
@@ -2394,19 +2533,19 @@
           <t>1980.00</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>1345.00</t>
-        </is>
-      </c>
+      <c r="G35" s="8" t="inlineStr"/>
       <c r="H35" s="8" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr">
         <is>
+          <t>1345.00</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
           <t>1470.00</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
       <c r="L35" s="8" t="inlineStr"/>
       <c r="M35" s="8" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
@@ -2417,11 +2556,12 @@
       <c r="S35" s="8" t="inlineStr"/>
       <c r="T35" s="8" t="inlineStr"/>
       <c r="U35" s="8" t="inlineStr"/>
-      <c r="V35" s="9" t="n">
-        <v>1598.333333333333</v>
-      </c>
-      <c r="W35" s="10" t="inlineStr"/>
-      <c r="X35" s="11" t="inlineStr"/>
+      <c r="V35" s="8" t="inlineStr"/>
+      <c r="W35" s="9" t="n">
+        <v>1407.5</v>
+      </c>
+      <c r="X35" s="10" t="inlineStr"/>
+      <c r="Y35" s="11" t="inlineStr"/>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="1" t="n"/>
@@ -2453,9 +2593,10 @@
       <c r="S36" s="8" t="inlineStr"/>
       <c r="T36" s="8" t="inlineStr"/>
       <c r="U36" s="8" t="inlineStr"/>
-      <c r="V36" s="9" t="inlineStr"/>
-      <c r="W36" s="10" t="inlineStr"/>
-      <c r="X36" s="11" t="inlineStr"/>
+      <c r="V36" s="8" t="inlineStr"/>
+      <c r="W36" s="9" t="inlineStr"/>
+      <c r="X36" s="10" t="inlineStr"/>
+      <c r="Y36" s="11" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="1" t="n"/>
@@ -2467,24 +2608,24 @@
       <c r="C37" s="8" t="inlineStr"/>
       <c r="D37" s="8" t="inlineStr"/>
       <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>970.00</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>1445.00</t>
-        </is>
-      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING, 1125.00, 970.00</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr"/>
       <c r="H37" s="8" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
+          <t>1445.00</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
           <t>1260.00</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr"/>
       <c r="L37" s="8" t="inlineStr"/>
       <c r="M37" s="8" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
@@ -2495,14 +2636,15 @@
       <c r="S37" s="8" t="inlineStr"/>
       <c r="T37" s="8" t="inlineStr"/>
       <c r="U37" s="8" t="inlineStr"/>
-      <c r="V37" s="9" t="n">
-        <v>1225</v>
-      </c>
+      <c r="V37" s="8" t="inlineStr"/>
       <c r="W37" s="9" t="n">
-        <v>373.3333333333333</v>
-      </c>
-      <c r="X37" s="11" t="n">
-        <v>-0.05676519482625794</v>
+        <v>1352.5</v>
+      </c>
+      <c r="X37" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y37" s="11" t="n">
+        <v>-0.008362729594939788</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
@@ -2537,11 +2679,12 @@
       <c r="S38" s="4" t="inlineStr"/>
       <c r="T38" s="4" t="inlineStr"/>
       <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="5" t="inlineStr"/>
-      <c r="W38" s="6" t="n">
+      <c r="V38" s="4" t="inlineStr"/>
+      <c r="W38" s="5" t="inlineStr"/>
+      <c r="X38" s="6" t="n">
         <v>-9204.333333333336</v>
       </c>
-      <c r="X38" s="7" t="n">
+      <c r="Y38" s="7" t="n">
         <v>-0.3674545921510859</v>
       </c>
     </row>
@@ -2568,19 +2711,19 @@
           <t>49810.00</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>66125.00</t>
-        </is>
-      </c>
+      <c r="G39" s="8" t="inlineStr"/>
       <c r="H39" s="8" t="inlineStr"/>
       <c r="I39" s="8" t="inlineStr">
         <is>
+          <t>66125.00</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr"/>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
           <t>59970.00</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr"/>
       <c r="L39" s="8" t="inlineStr"/>
       <c r="M39" s="8" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
@@ -2591,40 +2734,33 @@
       <c r="S39" s="8" t="inlineStr"/>
       <c r="T39" s="8" t="inlineStr"/>
       <c r="U39" s="8" t="inlineStr"/>
-      <c r="V39" s="9" t="n">
+      <c r="V39" s="8" t="inlineStr"/>
+      <c r="W39" s="9" t="n">
         <v>57571.66666666666</v>
       </c>
-      <c r="W39" s="10" t="inlineStr"/>
-      <c r="X39" s="11" t="inlineStr"/>
+      <c r="X39" s="10" t="inlineStr"/>
+      <c r="Y39" s="11" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr"/>
       <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>56795.00</t>
-        </is>
-      </c>
+      <c r="E40" s="8" t="inlineStr"/>
       <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>53655.00</t>
-        </is>
-      </c>
+      <c r="G40" s="8" t="inlineStr"/>
       <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>63275.00</t>
-        </is>
-      </c>
+      <c r="I40" s="8" t="inlineStr"/>
       <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="L40" s="8" t="inlineStr"/>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
@@ -2635,135 +2771,140 @@
       <c r="S40" s="8" t="inlineStr"/>
       <c r="T40" s="8" t="inlineStr"/>
       <c r="U40" s="8" t="inlineStr"/>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="inlineStr"/>
+      <c r="W40" s="9" t="inlineStr"/>
+      <c r="X40" s="10" t="inlineStr"/>
+      <c r="Y40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr"/>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>56795.00</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>53655.00</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr"/>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>63275.00</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
+      <c r="N41" s="8" t="inlineStr"/>
+      <c r="O41" s="8" t="inlineStr"/>
+      <c r="P41" s="8" t="inlineStr"/>
+      <c r="Q41" s="8" t="inlineStr"/>
+      <c r="R41" s="8" t="inlineStr"/>
+      <c r="S41" s="8" t="inlineStr"/>
+      <c r="T41" s="8" t="inlineStr"/>
+      <c r="U41" s="8" t="inlineStr"/>
+      <c r="V41" s="8" t="inlineStr"/>
+      <c r="W41" s="9" t="n">
         <v>57908.33333333334</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="X41" s="9" t="n">
         <v>336.6666666666715</v>
       </c>
-      <c r="X40" s="11" t="n">
+      <c r="Y41" s="11" t="n">
         <v>0.01344037728869018</v>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>DemonAttack
 Random: 152.1
 Human: 1971.0</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 165</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="4" t="inlineStr"/>
-      <c r="M41" s="4" t="inlineStr"/>
-      <c r="N41" s="4" t="inlineStr"/>
-      <c r="O41" s="4" t="inlineStr"/>
-      <c r="P41" s="4" t="inlineStr"/>
-      <c r="Q41" s="4" t="inlineStr"/>
-      <c r="R41" s="4" t="inlineStr"/>
-      <c r="S41" s="4" t="inlineStr"/>
-      <c r="T41" s="4" t="inlineStr"/>
-      <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="5" t="inlineStr"/>
-      <c r="W41" s="6" t="n">
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr"/>
+      <c r="Q42" s="4" t="inlineStr"/>
+      <c r="R42" s="4" t="inlineStr"/>
+      <c r="S42" s="4" t="inlineStr"/>
+      <c r="T42" s="4" t="inlineStr"/>
+      <c r="U42" s="4" t="inlineStr"/>
+      <c r="V42" s="4" t="inlineStr"/>
+      <c r="W42" s="5" t="inlineStr"/>
+      <c r="X42" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="X41" s="7" t="n">
+      <c r="Y42" s="7" t="n">
         <v>0.01539391940183627</v>
       </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr"/>
-      <c r="D42" s="8" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>214.25</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>139.75</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>200.75</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>171.75</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr"/>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>188.00</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
-      <c r="O42" s="8" t="inlineStr"/>
-      <c r="P42" s="8" t="inlineStr"/>
-      <c r="Q42" s="8" t="inlineStr"/>
-      <c r="R42" s="8" t="inlineStr"/>
-      <c r="S42" s="8" t="inlineStr"/>
-      <c r="T42" s="8" t="inlineStr"/>
-      <c r="U42" s="8" t="inlineStr"/>
-      <c r="V42" s="9" t="n">
-        <v>193</v>
-      </c>
-      <c r="W42" s="10" t="inlineStr"/>
-      <c r="X42" s="11" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr"/>
       <c r="D43" s="8" t="inlineStr"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>150.75</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr"/>
+          <t>214.25</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>139.75</t>
+        </is>
+      </c>
       <c r="G43" s="8" t="inlineStr"/>
       <c r="H43" s="8" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>192.25</t>
+          <t>200.75</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr"/>
-      <c r="K43" s="8" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>171.75</t>
+        </is>
+      </c>
       <c r="L43" s="8" t="inlineStr"/>
       <c r="M43" s="8" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>188.00</t>
+        </is>
+      </c>
       <c r="O43" s="8" t="inlineStr"/>
       <c r="P43" s="8" t="inlineStr"/>
       <c r="Q43" s="8" t="inlineStr"/>
@@ -2771,105 +2912,104 @@
       <c r="S43" s="8" t="inlineStr"/>
       <c r="T43" s="8" t="inlineStr"/>
       <c r="U43" s="8" t="inlineStr"/>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="inlineStr"/>
+      <c r="W43" s="9" t="n">
+        <v>193</v>
+      </c>
+      <c r="X43" s="10" t="inlineStr"/>
+      <c r="Y43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="1" t="n"/>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>150.75</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr"/>
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
+      <c r="J44" s="8" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>192.25</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
+      <c r="N44" s="8" t="inlineStr"/>
+      <c r="O44" s="8" t="inlineStr"/>
+      <c r="P44" s="8" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
+      <c r="S44" s="8" t="inlineStr"/>
+      <c r="T44" s="8" t="inlineStr"/>
+      <c r="U44" s="8" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="9" t="n">
         <v>171.5</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="X44" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="X43" s="11" t="n">
+      <c r="Y44" s="11" t="n">
         <v>-0.01182033096926714</v>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Freeway
 Random: 0.0
 Human: 29.6</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 34</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
-      <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr"/>
-      <c r="O44" s="4" t="inlineStr"/>
-      <c r="P44" s="4" t="inlineStr"/>
-      <c r="Q44" s="4" t="inlineStr"/>
-      <c r="R44" s="4" t="inlineStr"/>
-      <c r="S44" s="4" t="inlineStr"/>
-      <c r="T44" s="4" t="inlineStr"/>
-      <c r="U44" s="4" t="inlineStr"/>
-      <c r="V44" s="5" t="inlineStr"/>
-      <c r="W44" s="6" t="n">
-        <v>-0.7000000000000028</v>
-      </c>
-      <c r="X44" s="7" t="n">
-        <v>-0.02364864864864874</v>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr"/>
-      <c r="D45" s="8" t="inlineStr"/>
-      <c r="E45" s="8" t="inlineStr"/>
-      <c r="F45" s="8" t="inlineStr"/>
-      <c r="G45" s="8" t="inlineStr"/>
-      <c r="H45" s="8" t="inlineStr"/>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J45" s="8" t="inlineStr"/>
-      <c r="K45" s="8" t="inlineStr"/>
-      <c r="L45" s="8" t="inlineStr"/>
-      <c r="M45" s="8" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
-      <c r="O45" s="8" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
-      </c>
-      <c r="P45" s="8" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="Q45" s="8" t="inlineStr"/>
-      <c r="R45" s="8" t="inlineStr"/>
-      <c r="S45" s="8" t="inlineStr"/>
-      <c r="T45" s="8" t="inlineStr"/>
-      <c r="U45" s="8" t="inlineStr"/>
-      <c r="V45" s="9" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="W45" s="10" t="inlineStr"/>
-      <c r="X45" s="11" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr"/>
+      <c r="P45" s="4" t="inlineStr"/>
+      <c r="Q45" s="4" t="inlineStr"/>
+      <c r="R45" s="4" t="inlineStr"/>
+      <c r="S45" s="4" t="inlineStr"/>
+      <c r="T45" s="4" t="inlineStr"/>
+      <c r="U45" s="4" t="inlineStr"/>
+      <c r="V45" s="4" t="inlineStr"/>
+      <c r="W45" s="5" t="inlineStr"/>
+      <c r="X45" s="6" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Y45" s="7" t="n">
+        <v>-0.04222972972972973</v>
+      </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr"/>
@@ -2880,24 +3020,35 @@
       <c r="H46" s="8" t="inlineStr"/>
       <c r="I46" s="8" t="inlineStr"/>
       <c r="J46" s="8" t="inlineStr"/>
-      <c r="K46" s="8" t="inlineStr"/>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="L46" s="8" t="inlineStr"/>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
-      <c r="O46" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="P46" s="8" t="inlineStr"/>
+      <c r="O46" s="8" t="inlineStr">
+        <is>
+          <t>33.85</t>
+        </is>
+      </c>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr"/>
       <c r="T46" s="8" t="inlineStr"/>
       <c r="U46" s="8" t="inlineStr"/>
-      <c r="V46" s="9" t="inlineStr"/>
-      <c r="W46" s="10" t="inlineStr"/>
-      <c r="X46" s="11" t="inlineStr"/>
+      <c r="V46" s="8" t="inlineStr"/>
+      <c r="W46" s="9" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="X46" s="10" t="inlineStr"/>
+      <c r="Y46" s="11" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="1" t="n"/>
@@ -2918,9 +3069,9 @@
       <c r="L47" s="8" t="inlineStr"/>
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
-      <c r="O47" s="8" t="inlineStr">
-        <is>
-          <t>33.55</t>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING, 33.55</t>
         </is>
       </c>
       <c r="P47" s="8" t="inlineStr">
@@ -2933,14 +3084,15 @@
       <c r="S47" s="8" t="inlineStr"/>
       <c r="T47" s="8" t="inlineStr"/>
       <c r="U47" s="8" t="inlineStr"/>
-      <c r="V47" s="9" t="n">
-        <v>33.15</v>
-      </c>
+      <c r="V47" s="8" t="inlineStr"/>
       <c r="W47" s="9" t="n">
-        <v>0.1499999999999986</v>
-      </c>
-      <c r="X47" s="11" t="n">
-        <v>-0.005067567567567519</v>
+        <v>32.75</v>
+      </c>
+      <c r="X47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
@@ -2975,12 +3127,13 @@
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="4" t="inlineStr"/>
       <c r="U48" s="4" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr"/>
-      <c r="W48" s="6" t="n">
-        <v>491.5</v>
-      </c>
-      <c r="X48" s="7" t="n">
-        <v>0.115118866377796</v>
+      <c r="V48" s="4" t="inlineStr"/>
+      <c r="W48" s="5" t="inlineStr"/>
+      <c r="X48" s="6" t="n">
+        <v>426.375</v>
+      </c>
+      <c r="Y48" s="7" t="n">
+        <v>0.09986532380840848</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
@@ -2992,7 +3145,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr"/>
       <c r="D49" s="8" t="inlineStr"/>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>2068.00</t>
         </is>
@@ -3002,13 +3155,13 @@
           <t>2270.50</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>1904.00</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="8" t="inlineStr"/>
       <c r="J49" s="8" t="inlineStr"/>
       <c r="K49" s="8" t="inlineStr"/>
       <c r="L49" s="8" t="inlineStr"/>
@@ -3029,11 +3182,12 @@
       <c r="S49" s="8" t="inlineStr"/>
       <c r="T49" s="8" t="inlineStr"/>
       <c r="U49" s="8" t="inlineStr"/>
-      <c r="V49" s="9" t="n">
-        <v>1807.5</v>
-      </c>
-      <c r="W49" s="10" t="inlineStr"/>
-      <c r="X49" s="11" t="inlineStr"/>
+      <c r="V49" s="8" t="inlineStr"/>
+      <c r="W49" s="9" t="n">
+        <v>1742.375</v>
+      </c>
+      <c r="X49" s="10" t="inlineStr"/>
+      <c r="Y49" s="11" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="1" t="n"/>
@@ -3044,7 +3198,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr"/>
       <c r="D50" s="8" t="inlineStr"/>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>2301.00</t>
         </is>
@@ -3054,13 +3208,13 @@
           <t>2609.00</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>3242.50</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr"/>
-      <c r="I50" s="8" t="inlineStr"/>
       <c r="J50" s="8" t="inlineStr"/>
       <c r="K50" s="8" t="inlineStr"/>
       <c r="L50" s="8" t="inlineStr"/>
@@ -3081,9 +3235,10 @@
       <c r="S50" s="8" t="inlineStr"/>
       <c r="T50" s="8" t="inlineStr"/>
       <c r="U50" s="8" t="inlineStr"/>
-      <c r="V50" s="9" t="inlineStr"/>
-      <c r="W50" s="10" t="inlineStr"/>
-      <c r="X50" s="11" t="inlineStr"/>
+      <c r="V50" s="8" t="inlineStr"/>
+      <c r="W50" s="9" t="inlineStr"/>
+      <c r="X50" s="10" t="inlineStr"/>
+      <c r="Y50" s="11" t="inlineStr"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="1" t="n"/>
@@ -3094,7 +3249,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr"/>
       <c r="D51" s="8" t="inlineStr"/>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>2113.50, 2350.50</t>
         </is>
@@ -3106,24 +3261,24 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
+          <t>283.50</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>252.00</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
           <t>2779.00</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr"/>
-      <c r="I51" s="8" t="inlineStr"/>
       <c r="J51" s="8" t="inlineStr"/>
       <c r="K51" s="8" t="inlineStr"/>
       <c r="L51" s="8" t="inlineStr"/>
-      <c r="M51" s="8" t="inlineStr">
-        <is>
-          <t>283.50</t>
-        </is>
-      </c>
-      <c r="N51" s="8" t="inlineStr">
-        <is>
-          <t>252.00</t>
-        </is>
-      </c>
+      <c r="M51" s="8" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr"/>
       <c r="O51" s="8" t="inlineStr">
         <is>
           <t>2474.00</t>
@@ -3139,14 +3294,15 @@
       <c r="S51" s="8" t="inlineStr"/>
       <c r="T51" s="8" t="inlineStr"/>
       <c r="U51" s="8" t="inlineStr"/>
-      <c r="V51" s="9" t="n">
-        <v>2012.1</v>
-      </c>
+      <c r="V51" s="8" t="inlineStr"/>
       <c r="W51" s="9" t="n">
-        <v>204.5999999999999</v>
-      </c>
-      <c r="X51" s="11" t="n">
-        <v>0.0479213022602178</v>
+        <v>1986.75</v>
+      </c>
+      <c r="X51" s="9" t="n">
+        <v>244.375</v>
+      </c>
+      <c r="Y51" s="11" t="n">
+        <v>0.05723738142639653</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
@@ -3181,12 +3337,13 @@
       <c r="S52" s="4" t="inlineStr"/>
       <c r="T52" s="4" t="inlineStr"/>
       <c r="U52" s="4" t="inlineStr"/>
-      <c r="V52" s="5" t="inlineStr"/>
-      <c r="W52" s="6" t="n">
-        <v>-5338.5</v>
-      </c>
-      <c r="X52" s="7" t="n">
-        <v>-2.477377140470555</v>
+      <c r="V52" s="4" t="inlineStr"/>
+      <c r="W52" s="5" t="inlineStr"/>
+      <c r="X52" s="6" t="n">
+        <v>-4547</v>
+      </c>
+      <c r="Y52" s="7" t="n">
+        <v>-2.110074713443779</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
@@ -3216,46 +3373,47 @@
           <t>3914.00</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>4219.00</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr"/>
-      <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr"/>
       <c r="K53" s="8" t="inlineStr"/>
       <c r="L53" s="8" t="inlineStr"/>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
-      <c r="O53" s="12" t="inlineStr">
+      <c r="O53" s="13" t="inlineStr">
         <is>
           <t>2486.00</t>
         </is>
       </c>
-      <c r="P53" s="12" t="inlineStr">
+      <c r="P53" s="13" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr"/>
       <c r="R53" s="8" t="inlineStr"/>
-      <c r="S53" s="8" t="inlineStr">
+      <c r="S53" s="8" t="inlineStr"/>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>3585.00</t>
         </is>
       </c>
-      <c r="T53" s="12" t="inlineStr">
+      <c r="U53" s="13" t="inlineStr">
         <is>
           <t>2594.00</t>
         </is>
       </c>
-      <c r="U53" s="8" t="inlineStr"/>
-      <c r="V53" s="9" t="n">
-        <v>2901.5</v>
-      </c>
-      <c r="W53" s="10" t="inlineStr"/>
-      <c r="X53" s="11" t="inlineStr"/>
+      <c r="V53" s="8" t="inlineStr"/>
+      <c r="W53" s="9" t="n">
+        <v>3693</v>
+      </c>
+      <c r="X53" s="10" t="inlineStr"/>
+      <c r="Y53" s="11" t="inlineStr"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="1" t="n"/>
@@ -3276,20 +3434,21 @@
       <c r="L54" s="8" t="inlineStr"/>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
-      <c r="O54" s="12" t="inlineStr"/>
-      <c r="P54" s="12" t="inlineStr"/>
+      <c r="O54" s="13" t="inlineStr"/>
+      <c r="P54" s="13" t="inlineStr"/>
       <c r="Q54" s="8" t="inlineStr"/>
-      <c r="R54" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="R54" s="8" t="inlineStr">
+        <is>
+          <t>2533.00</t>
         </is>
       </c>
       <c r="S54" s="8" t="inlineStr"/>
-      <c r="T54" s="12" t="inlineStr"/>
-      <c r="U54" s="8" t="inlineStr"/>
-      <c r="V54" s="9" t="inlineStr"/>
-      <c r="W54" s="10" t="inlineStr"/>
-      <c r="X54" s="11" t="inlineStr"/>
+      <c r="T54" s="8" t="inlineStr"/>
+      <c r="U54" s="13" t="inlineStr"/>
+      <c r="V54" s="8" t="inlineStr"/>
+      <c r="W54" s="9" t="inlineStr"/>
+      <c r="X54" s="10" t="inlineStr"/>
+      <c r="Y54" s="11" t="inlineStr"/>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="1" t="n"/>
@@ -3306,49 +3465,50 @@
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr"/>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>3829.00</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr"/>
       <c r="J55" s="8" t="inlineStr"/>
       <c r="K55" s="8" t="inlineStr"/>
       <c r="L55" s="8" t="inlineStr"/>
       <c r="M55" s="8" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
-      <c r="O55" s="12" t="inlineStr">
+      <c r="O55" s="13" t="inlineStr">
         <is>
           <t>1024.00</t>
         </is>
       </c>
-      <c r="P55" s="12" t="inlineStr">
+      <c r="P55" s="13" t="inlineStr">
         <is>
           <t>927.00</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr"/>
       <c r="R55" s="8" t="inlineStr"/>
-      <c r="S55" s="8" t="inlineStr">
+      <c r="S55" s="8" t="inlineStr"/>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>7531.00</t>
         </is>
       </c>
-      <c r="T55" s="12" t="inlineStr">
+      <c r="U55" s="13" t="inlineStr">
         <is>
           <t>1005.00</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr"/>
-      <c r="V55" s="9" t="n">
-        <v>2940.5</v>
-      </c>
+      <c r="V55" s="8" t="inlineStr"/>
       <c r="W55" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="X55" s="11" t="n">
-        <v>0.01809828762355562</v>
+        <v>4895.666666666667</v>
+      </c>
+      <c r="X55" s="9" t="n">
+        <v>1202.666666666667</v>
+      </c>
+      <c r="Y55" s="11" t="n">
+        <v>0.558107878169134</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
@@ -3383,11 +3543,12 @@
       <c r="S56" s="4" t="inlineStr"/>
       <c r="T56" s="4" t="inlineStr"/>
       <c r="U56" s="4" t="inlineStr"/>
-      <c r="V56" s="5" t="inlineStr"/>
-      <c r="W56" s="6" t="n">
+      <c r="V56" s="4" t="inlineStr"/>
+      <c r="W56" s="5" t="inlineStr"/>
+      <c r="X56" s="6" t="n">
         <v>2134</v>
       </c>
-      <c r="X56" s="7" t="n">
+      <c r="Y56" s="7" t="n">
         <v>0.07161218011100895</v>
       </c>
     </row>
@@ -3414,13 +3575,13 @@
           <t>13456.25</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>13081.00</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr"/>
-      <c r="I57" s="8" t="inlineStr"/>
       <c r="J57" s="8" t="inlineStr"/>
       <c r="K57" s="8" t="inlineStr"/>
       <c r="L57" s="8" t="inlineStr"/>
@@ -3433,11 +3594,12 @@
       <c r="S57" s="8" t="inlineStr"/>
       <c r="T57" s="8" t="inlineStr"/>
       <c r="U57" s="8" t="inlineStr"/>
-      <c r="V57" s="9" t="n">
+      <c r="V57" s="8" t="inlineStr"/>
+      <c r="W57" s="9" t="n">
         <v>13178</v>
       </c>
-      <c r="W57" s="10" t="inlineStr"/>
-      <c r="X57" s="11" t="inlineStr"/>
+      <c r="X57" s="10" t="inlineStr"/>
+      <c r="Y57" s="11" t="inlineStr"/>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="1" t="n"/>
@@ -3458,13 +3620,13 @@
           <t>13231.50</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>13325.50</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr"/>
-      <c r="I58" s="8" t="inlineStr"/>
       <c r="J58" s="8" t="inlineStr"/>
       <c r="K58" s="8" t="inlineStr"/>
       <c r="L58" s="8" t="inlineStr"/>
@@ -3477,13 +3639,14 @@
       <c r="S58" s="8" t="inlineStr"/>
       <c r="T58" s="8" t="inlineStr"/>
       <c r="U58" s="8" t="inlineStr"/>
-      <c r="V58" s="9" t="n">
+      <c r="V58" s="8" t="inlineStr"/>
+      <c r="W58" s="9" t="n">
         <v>13269.41666666667</v>
       </c>
-      <c r="W58" s="9" t="n">
+      <c r="X58" s="9" t="n">
         <v>91.41666666666606</v>
       </c>
-      <c r="X58" s="11" t="n">
+      <c r="Y58" s="11" t="n">
         <v>0.003067735144555463</v>
       </c>
     </row>
@@ -3519,11 +3682,12 @@
       <c r="S59" s="4" t="inlineStr"/>
       <c r="T59" s="4" t="inlineStr"/>
       <c r="U59" s="4" t="inlineStr"/>
-      <c r="V59" s="5" t="inlineStr"/>
-      <c r="W59" s="6" t="n">
+      <c r="V59" s="4" t="inlineStr"/>
+      <c r="W59" s="5" t="inlineStr"/>
+      <c r="X59" s="6" t="n">
         <v>-35.66666666666669</v>
       </c>
-      <c r="X59" s="7" t="n">
+      <c r="Y59" s="7" t="n">
         <v>-0.1302654005356709</v>
       </c>
     </row>
@@ -3544,13 +3708,13 @@
       <c r="F60" s="8" t="inlineStr"/>
       <c r="G60" s="8" t="inlineStr"/>
       <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="8" t="inlineStr"/>
+      <c r="K60" s="8" t="inlineStr">
         <is>
           <t>532.50, 537.50</t>
         </is>
       </c>
-      <c r="J60" s="8" t="inlineStr"/>
-      <c r="K60" s="8" t="inlineStr"/>
       <c r="L60" s="8" t="inlineStr"/>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
@@ -3563,17 +3727,18 @@
       <c r="Q60" s="8" t="inlineStr"/>
       <c r="R60" s="8" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr"/>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="T60" s="8" t="inlineStr"/>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>365.00</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr"/>
-      <c r="V60" s="9" t="n">
+      <c r="V60" s="8" t="inlineStr"/>
+      <c r="W60" s="9" t="n">
         <v>473.3333333333333</v>
       </c>
-      <c r="W60" s="10" t="inlineStr"/>
-      <c r="X60" s="11" t="inlineStr"/>
+      <c r="X60" s="10" t="inlineStr"/>
+      <c r="Y60" s="11" t="inlineStr"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="1" t="n"/>
@@ -3594,9 +3759,9 @@
       <c r="L61" s="8" t="inlineStr"/>
       <c r="M61" s="8" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>575.00</t>
         </is>
       </c>
       <c r="P61" s="8" t="inlineStr"/>
@@ -3605,9 +3770,10 @@
       <c r="S61" s="8" t="inlineStr"/>
       <c r="T61" s="8" t="inlineStr"/>
       <c r="U61" s="8" t="inlineStr"/>
-      <c r="V61" s="9" t="inlineStr"/>
-      <c r="W61" s="10" t="inlineStr"/>
-      <c r="X61" s="11" t="inlineStr"/>
+      <c r="V61" s="8" t="inlineStr"/>
+      <c r="W61" s="9" t="inlineStr"/>
+      <c r="X61" s="10" t="inlineStr"/>
+      <c r="Y61" s="11" t="inlineStr"/>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="1" t="n"/>
@@ -3622,13 +3788,13 @@
       <c r="F62" s="8" t="inlineStr"/>
       <c r="G62" s="8" t="inlineStr"/>
       <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr"/>
+      <c r="J62" s="8" t="inlineStr"/>
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>567.50, 660.00</t>
         </is>
       </c>
-      <c r="J62" s="8" t="inlineStr"/>
-      <c r="K62" s="8" t="inlineStr"/>
       <c r="L62" s="8" t="inlineStr"/>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
@@ -3641,19 +3807,20 @@
       <c r="Q62" s="8" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr"/>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr"/>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>375.00</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr"/>
-      <c r="V62" s="9" t="n">
+      <c r="V62" s="8" t="inlineStr"/>
+      <c r="W62" s="9" t="n">
         <v>535.8333333333334</v>
       </c>
-      <c r="W62" s="9" t="n">
+      <c r="X62" s="9" t="n">
         <v>62.50000000000006</v>
       </c>
-      <c r="X62" s="11" t="n">
+      <c r="Y62" s="11" t="n">
         <v>0.2282688093498906</v>
       </c>
     </row>
@@ -3689,11 +3856,12 @@
       <c r="S63" s="4" t="inlineStr"/>
       <c r="T63" s="4" t="inlineStr"/>
       <c r="U63" s="4" t="inlineStr"/>
-      <c r="V63" s="5" t="inlineStr"/>
-      <c r="W63" s="6" t="n">
+      <c r="V63" s="4" t="inlineStr"/>
+      <c r="W63" s="5" t="inlineStr"/>
+      <c r="X63" s="6" t="n">
         <v>-2778</v>
       </c>
-      <c r="X63" s="7" t="n">
+      <c r="Y63" s="7" t="n">
         <v>-0.9312772376801878</v>
       </c>
     </row>
@@ -3714,18 +3882,18 @@
       <c r="F64" s="8" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr"/>
       <c r="H64" s="8" t="inlineStr"/>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr"/>
+      <c r="J64" s="8" t="inlineStr"/>
+      <c r="K64" s="8" t="inlineStr">
         <is>
           <t>1470.00</t>
         </is>
       </c>
-      <c r="J64" s="8" t="inlineStr">
+      <c r="L64" s="8" t="inlineStr">
         <is>
           <t>1730.00</t>
         </is>
       </c>
-      <c r="K64" s="8" t="inlineStr"/>
-      <c r="L64" s="8" t="inlineStr"/>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
       <c r="O64" s="8" t="inlineStr">
@@ -3743,11 +3911,12 @@
       <c r="S64" s="8" t="inlineStr"/>
       <c r="T64" s="8" t="inlineStr"/>
       <c r="U64" s="8" t="inlineStr"/>
-      <c r="V64" s="9" t="n">
+      <c r="V64" s="8" t="inlineStr"/>
+      <c r="W64" s="9" t="n">
         <v>1430</v>
       </c>
-      <c r="W64" s="10" t="inlineStr"/>
-      <c r="X64" s="11" t="inlineStr"/>
+      <c r="X64" s="10" t="inlineStr"/>
+      <c r="Y64" s="11" t="inlineStr"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="1" t="n"/>
@@ -3762,13 +3931,13 @@
       <c r="F65" s="8" t="inlineStr"/>
       <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr"/>
+      <c r="J65" s="8" t="inlineStr"/>
+      <c r="K65" s="8" t="inlineStr">
         <is>
           <t>1310.00</t>
         </is>
       </c>
-      <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr"/>
       <c r="L65" s="8" t="inlineStr"/>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
@@ -3787,9 +3956,10 @@
       <c r="S65" s="8" t="inlineStr"/>
       <c r="T65" s="8" t="inlineStr"/>
       <c r="U65" s="8" t="inlineStr"/>
-      <c r="V65" s="9" t="inlineStr"/>
-      <c r="W65" s="10" t="inlineStr"/>
-      <c r="X65" s="11" t="inlineStr"/>
+      <c r="V65" s="8" t="inlineStr"/>
+      <c r="W65" s="9" t="inlineStr"/>
+      <c r="X65" s="10" t="inlineStr"/>
+      <c r="Y65" s="11" t="inlineStr"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="1" t="n"/>
@@ -3808,13 +3978,13 @@
       <c r="F66" s="8" t="inlineStr"/>
       <c r="G66" s="8" t="inlineStr"/>
       <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr"/>
+      <c r="J66" s="8" t="inlineStr"/>
+      <c r="K66" s="8" t="inlineStr">
         <is>
           <t>1590.00</t>
         </is>
       </c>
-      <c r="J66" s="8" t="inlineStr"/>
-      <c r="K66" s="8" t="inlineStr"/>
       <c r="L66" s="8" t="inlineStr"/>
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="8" t="inlineStr"/>
@@ -3833,13 +4003,14 @@
       <c r="S66" s="8" t="inlineStr"/>
       <c r="T66" s="8" t="inlineStr"/>
       <c r="U66" s="8" t="inlineStr"/>
-      <c r="V66" s="9" t="n">
+      <c r="V66" s="8" t="inlineStr"/>
+      <c r="W66" s="9" t="n">
         <v>1445</v>
       </c>
-      <c r="W66" s="9" t="n">
+      <c r="X66" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="X66" s="11" t="n">
+      <c r="Y66" s="11" t="n">
         <v>0.005028494803888703</v>
       </c>
     </row>
@@ -3875,12 +4046,13 @@
       <c r="S67" s="4" t="inlineStr"/>
       <c r="T67" s="4" t="inlineStr"/>
       <c r="U67" s="4" t="inlineStr"/>
-      <c r="V67" s="5" t="inlineStr"/>
-      <c r="W67" s="6" t="n">
-        <v>-2756.25</v>
-      </c>
-      <c r="X67" s="7" t="n">
-        <v>-2.581967213114754</v>
+      <c r="V67" s="4" t="inlineStr"/>
+      <c r="W67" s="5" t="inlineStr"/>
+      <c r="X67" s="6" t="n">
+        <v>-2583.375</v>
+      </c>
+      <c r="Y67" s="7" t="n">
+        <v>-2.420023419203747</v>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1">
@@ -3902,24 +4074,24 @@
           <t>5689.00</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>6107.50</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="12" t="inlineStr">
+      <c r="J68" s="8" t="inlineStr"/>
+      <c r="K68" s="13" t="inlineStr">
         <is>
           <t>4708.50</t>
         </is>
       </c>
-      <c r="J68" s="8" t="inlineStr">
+      <c r="L68" s="13" t="inlineStr">
         <is>
           <t>5913.50</t>
         </is>
       </c>
-      <c r="K68" s="8" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr"/>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
       <c r="O68" s="8" t="inlineStr">
@@ -3935,17 +4107,18 @@
       </c>
       <c r="R68" s="8" t="inlineStr"/>
       <c r="S68" s="8" t="inlineStr"/>
-      <c r="T68" s="8" t="inlineStr">
+      <c r="T68" s="8" t="inlineStr"/>
+      <c r="U68" s="8" t="inlineStr">
         <is>
           <t>6289.00</t>
         </is>
       </c>
-      <c r="U68" s="8" t="inlineStr"/>
-      <c r="V68" s="9" t="n">
-        <v>5656.75</v>
-      </c>
-      <c r="W68" s="10" t="inlineStr"/>
-      <c r="X68" s="11" t="inlineStr"/>
+      <c r="V68" s="8" t="inlineStr"/>
+      <c r="W68" s="9" t="n">
+        <v>5829.625</v>
+      </c>
+      <c r="X68" s="10" t="inlineStr"/>
+      <c r="Y68" s="11" t="inlineStr"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
@@ -3960,18 +4133,18 @@
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr"/>
       <c r="H69" s="8" t="inlineStr"/>
-      <c r="I69" s="12" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr"/>
+      <c r="K69" s="13" t="inlineStr">
         <is>
           <t>4851.00</t>
         </is>
       </c>
-      <c r="J69" s="8" t="inlineStr">
+      <c r="L69" s="13" t="inlineStr">
         <is>
           <t>6044.00</t>
         </is>
       </c>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="8" t="inlineStr"/>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
       <c r="O69" s="8" t="inlineStr"/>
@@ -3979,15 +4152,16 @@
       <c r="Q69" s="8" t="inlineStr"/>
       <c r="R69" s="8" t="inlineStr"/>
       <c r="S69" s="8" t="inlineStr"/>
-      <c r="T69" s="8" t="inlineStr">
+      <c r="T69" s="8" t="inlineStr"/>
+      <c r="U69" s="8" t="inlineStr">
         <is>
           <t>6587.00</t>
         </is>
       </c>
-      <c r="U69" s="8" t="inlineStr"/>
-      <c r="V69" s="9" t="inlineStr"/>
-      <c r="W69" s="10" t="inlineStr"/>
-      <c r="X69" s="11" t="inlineStr"/>
+      <c r="V69" s="8" t="inlineStr"/>
+      <c r="W69" s="9" t="inlineStr"/>
+      <c r="X69" s="10" t="inlineStr"/>
+      <c r="Y69" s="11" t="inlineStr"/>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="1" t="n"/>
@@ -4006,18 +4180,18 @@
       <c r="F70" s="8" t="inlineStr"/>
       <c r="G70" s="8" t="inlineStr"/>
       <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="12" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr"/>
+      <c r="K70" s="13" t="inlineStr">
         <is>
           <t>5279.50</t>
         </is>
       </c>
-      <c r="J70" s="8" t="inlineStr">
+      <c r="L70" s="13" t="inlineStr">
         <is>
           <t>5889.50</t>
         </is>
       </c>
-      <c r="K70" s="8" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
       <c r="O70" s="8" t="inlineStr">
@@ -4033,20 +4207,21 @@
       </c>
       <c r="R70" s="8" t="inlineStr"/>
       <c r="S70" s="8" t="inlineStr"/>
-      <c r="T70" s="8" t="inlineStr">
+      <c r="T70" s="8" t="inlineStr"/>
+      <c r="U70" s="8" t="inlineStr">
         <is>
           <t>6796.50</t>
         </is>
       </c>
-      <c r="U70" s="8" t="inlineStr"/>
-      <c r="V70" s="9" t="n">
-        <v>6303</v>
-      </c>
+      <c r="V70" s="8" t="inlineStr"/>
       <c r="W70" s="9" t="n">
-        <v>646.25</v>
-      </c>
-      <c r="X70" s="11" t="n">
-        <v>0.6053864168618267</v>
+        <v>6662.25</v>
+      </c>
+      <c r="X70" s="9" t="n">
+        <v>832.625</v>
+      </c>
+      <c r="Y70" s="11" t="n">
+        <v>0.779976580796253</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1">
@@ -4081,11 +4256,12 @@
       <c r="S71" s="4" t="inlineStr"/>
       <c r="T71" s="4" t="inlineStr"/>
       <c r="U71" s="4" t="inlineStr"/>
-      <c r="V71" s="5" t="inlineStr"/>
-      <c r="W71" s="6" t="n">
+      <c r="V71" s="4" t="inlineStr"/>
+      <c r="W71" s="5" t="inlineStr"/>
+      <c r="X71" s="6" t="n">
         <v>-1044.5</v>
       </c>
-      <c r="X71" s="7" t="n">
+      <c r="Y71" s="7" t="n">
         <v>-0.04646807071866464</v>
       </c>
     </row>
@@ -4106,18 +4282,18 @@
       <c r="F72" s="8" t="inlineStr"/>
       <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr"/>
+      <c r="J72" s="8" t="inlineStr"/>
+      <c r="K72" s="8" t="inlineStr">
         <is>
           <t>23815.00</t>
         </is>
       </c>
-      <c r="J72" s="8" t="inlineStr">
+      <c r="L72" s="8" t="inlineStr">
         <is>
           <t>20895.00</t>
         </is>
       </c>
-      <c r="K72" s="8" t="inlineStr"/>
-      <c r="L72" s="8" t="inlineStr"/>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
       <c r="O72" s="8" t="inlineStr"/>
@@ -4127,11 +4303,12 @@
       <c r="S72" s="8" t="inlineStr"/>
       <c r="T72" s="8" t="inlineStr"/>
       <c r="U72" s="8" t="inlineStr"/>
-      <c r="V72" s="9" t="n">
+      <c r="V72" s="8" t="inlineStr"/>
+      <c r="W72" s="9" t="n">
         <v>25137.5</v>
       </c>
-      <c r="W72" s="10" t="inlineStr"/>
-      <c r="X72" s="11" t="inlineStr"/>
+      <c r="X72" s="10" t="inlineStr"/>
+      <c r="Y72" s="11" t="inlineStr"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="1" t="n"/>
@@ -4150,13 +4327,13 @@
       <c r="F73" s="8" t="inlineStr"/>
       <c r="G73" s="8" t="inlineStr"/>
       <c r="H73" s="8" t="inlineStr"/>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr"/>
+      <c r="J73" s="8" t="inlineStr"/>
+      <c r="K73" s="8" t="inlineStr">
         <is>
           <t>20245.00</t>
         </is>
       </c>
-      <c r="J73" s="8" t="inlineStr"/>
-      <c r="K73" s="8" t="inlineStr"/>
       <c r="L73" s="8" t="inlineStr"/>
       <c r="M73" s="8" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
@@ -4167,13 +4344,14 @@
       <c r="S73" s="8" t="inlineStr"/>
       <c r="T73" s="8" t="inlineStr"/>
       <c r="U73" s="8" t="inlineStr"/>
-      <c r="V73" s="9" t="n">
+      <c r="V73" s="8" t="inlineStr"/>
+      <c r="W73" s="9" t="n">
         <v>25177.5</v>
       </c>
-      <c r="W73" s="9" t="n">
+      <c r="X73" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="X73" s="11" t="n">
+      <c r="Y73" s="11" t="n">
         <v>0.001779533584247569</v>
       </c>
     </row>
@@ -4209,11 +4387,12 @@
       <c r="S74" s="4" t="inlineStr"/>
       <c r="T74" s="4" t="inlineStr"/>
       <c r="U74" s="4" t="inlineStr"/>
-      <c r="V74" s="5" t="inlineStr"/>
-      <c r="W74" s="6" t="n">
+      <c r="V74" s="4" t="inlineStr"/>
+      <c r="W74" s="5" t="inlineStr"/>
+      <c r="X74" s="6" t="n">
         <v>-602</v>
       </c>
-      <c r="X74" s="7" t="n">
+      <c r="Y74" s="7" t="n">
         <v>-0.09060397634062278</v>
       </c>
     </row>
@@ -4238,13 +4417,13 @@
       <c r="F75" s="8" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr"/>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="8" t="inlineStr">
         <is>
           <t>2388.00</t>
         </is>
       </c>
-      <c r="J75" s="8" t="inlineStr"/>
-      <c r="K75" s="8" t="inlineStr"/>
       <c r="L75" s="8" t="inlineStr"/>
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr"/>
@@ -4259,11 +4438,12 @@
       <c r="S75" s="8" t="inlineStr"/>
       <c r="T75" s="8" t="inlineStr"/>
       <c r="U75" s="8" t="inlineStr"/>
-      <c r="V75" s="9" t="n">
+      <c r="V75" s="8" t="inlineStr"/>
+      <c r="W75" s="9" t="n">
         <v>2071</v>
       </c>
-      <c r="W75" s="10" t="inlineStr"/>
-      <c r="X75" s="11" t="inlineStr"/>
+      <c r="X75" s="10" t="inlineStr"/>
+      <c r="Y75" s="11" t="inlineStr"/>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="1" t="n"/>
@@ -4278,13 +4458,13 @@
       <c r="F76" s="8" t="inlineStr"/>
       <c r="G76" s="8" t="inlineStr"/>
       <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="8" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr">
         <is>
           <t>2250.00</t>
         </is>
       </c>
-      <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr"/>
       <c r="L76" s="8" t="inlineStr"/>
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr"/>
@@ -4299,13 +4479,14 @@
       <c r="S76" s="8" t="inlineStr"/>
       <c r="T76" s="8" t="inlineStr"/>
       <c r="U76" s="8" t="inlineStr"/>
-      <c r="V76" s="9" t="n">
+      <c r="V76" s="8" t="inlineStr"/>
+      <c r="W76" s="9" t="n">
         <v>2068.25</v>
       </c>
-      <c r="W76" s="9" t="n">
+      <c r="X76" s="9" t="n">
         <v>2.75</v>
       </c>
-      <c r="X76" s="11" t="n">
+      <c r="Y76" s="11" t="n">
         <v>-0.0004138885962403865</v>
       </c>
     </row>
@@ -4341,11 +4522,12 @@
       <c r="S77" s="4" t="inlineStr"/>
       <c r="T77" s="4" t="inlineStr"/>
       <c r="U77" s="4" t="inlineStr"/>
-      <c r="V77" s="5" t="inlineStr"/>
-      <c r="W77" s="6" t="n">
+      <c r="V77" s="4" t="inlineStr"/>
+      <c r="W77" s="5" t="inlineStr"/>
+      <c r="X77" s="6" t="n">
         <v>-5.4</v>
       </c>
-      <c r="X77" s="7" t="n">
+      <c r="Y77" s="7" t="n">
         <v>-0.1529745042492918</v>
       </c>
     </row>
@@ -4370,18 +4552,18 @@
       </c>
       <c r="G78" s="8" t="inlineStr"/>
       <c r="H78" s="8" t="inlineStr"/>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr"/>
+      <c r="J78" s="8" t="inlineStr"/>
+      <c r="K78" s="8" t="inlineStr">
         <is>
           <t>5.70</t>
         </is>
       </c>
-      <c r="J78" s="8" t="inlineStr">
+      <c r="L78" s="8" t="inlineStr">
         <is>
           <t>13.70</t>
         </is>
       </c>
-      <c r="K78" s="8" t="inlineStr"/>
-      <c r="L78" s="8" t="inlineStr"/>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr"/>
       <c r="O78" s="8" t="inlineStr"/>
@@ -4391,11 +4573,12 @@
       <c r="S78" s="8" t="inlineStr"/>
       <c r="T78" s="8" t="inlineStr"/>
       <c r="U78" s="8" t="inlineStr"/>
-      <c r="V78" s="9" t="n">
+      <c r="V78" s="8" t="inlineStr"/>
+      <c r="W78" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="W78" s="10" t="inlineStr"/>
-      <c r="X78" s="11" t="inlineStr"/>
+      <c r="X78" s="10" t="inlineStr"/>
+      <c r="Y78" s="11" t="inlineStr"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="1" t="n"/>
@@ -4412,19 +4595,19 @@
           <t>8.20</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
+      <c r="G79" s="8" t="inlineStr"/>
       <c r="H79" s="8" t="inlineStr"/>
       <c r="I79" s="8" t="inlineStr">
         <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr"/>
+      <c r="K79" s="8" t="inlineStr">
+        <is>
           <t>9.80</t>
         </is>
       </c>
-      <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" s="8" t="inlineStr"/>
       <c r="L79" s="8" t="inlineStr"/>
       <c r="M79" s="8" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr"/>
@@ -4435,13 +4618,14 @@
       <c r="S79" s="8" t="inlineStr"/>
       <c r="T79" s="8" t="inlineStr"/>
       <c r="U79" s="8" t="inlineStr"/>
-      <c r="V79" s="9" t="n">
+      <c r="V79" s="8" t="inlineStr"/>
+      <c r="W79" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="W79" s="9" t="n">
+      <c r="X79" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="X79" s="11" t="n">
+      <c r="Y79" s="11" t="n">
         <v>0.09631728045325781</v>
       </c>
     </row>
@@ -4477,12 +4661,13 @@
       <c r="S80" s="4" t="inlineStr"/>
       <c r="T80" s="4" t="inlineStr"/>
       <c r="U80" s="4" t="inlineStr"/>
-      <c r="V80" s="5" t="inlineStr"/>
-      <c r="W80" s="6" t="n">
-        <v>-6958.88</v>
-      </c>
-      <c r="X80" s="7" t="n">
-        <v>-0.1000609664914359</v>
+      <c r="V80" s="4" t="inlineStr"/>
+      <c r="W80" s="5" t="inlineStr"/>
+      <c r="X80" s="6" t="n">
+        <v>-6778.35</v>
+      </c>
+      <c r="Y80" s="7" t="n">
+        <v>-0.09746514557187719</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1">
@@ -4502,17 +4687,17 @@
       <c r="F81" s="8" t="inlineStr"/>
       <c r="G81" s="8" t="inlineStr"/>
       <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr">
         <is>
           <t>199.35</t>
         </is>
       </c>
-      <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr"/>
       <c r="L81" s="8" t="inlineStr"/>
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="8" t="inlineStr"/>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="13" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
@@ -4529,17 +4714,18 @@
       </c>
       <c r="R81" s="8" t="inlineStr"/>
       <c r="S81" s="8" t="inlineStr"/>
-      <c r="T81" s="8" t="inlineStr">
+      <c r="T81" s="8" t="inlineStr"/>
+      <c r="U81" s="8" t="inlineStr">
         <is>
           <t>159.50</t>
         </is>
       </c>
-      <c r="U81" s="8" t="inlineStr"/>
-      <c r="V81" s="9" t="n">
-        <v>822.1200000000001</v>
-      </c>
-      <c r="W81" s="10" t="inlineStr"/>
-      <c r="X81" s="11" t="inlineStr"/>
+      <c r="V81" s="8" t="inlineStr"/>
+      <c r="W81" s="9" t="n">
+        <v>1002.65</v>
+      </c>
+      <c r="X81" s="10" t="inlineStr"/>
+      <c r="Y81" s="11" t="inlineStr"/>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="1" t="n"/>
@@ -4554,17 +4740,17 @@
       <c r="F82" s="8" t="inlineStr"/>
       <c r="G82" s="8" t="inlineStr"/>
       <c r="H82" s="8" t="inlineStr"/>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr"/>
+      <c r="J82" s="8" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr">
         <is>
           <t>191.95</t>
         </is>
       </c>
-      <c r="J82" s="8" t="inlineStr"/>
-      <c r="K82" s="8" t="inlineStr"/>
       <c r="L82" s="8" t="inlineStr"/>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="13" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
@@ -4581,20 +4767,21 @@
       </c>
       <c r="R82" s="8" t="inlineStr"/>
       <c r="S82" s="8" t="inlineStr"/>
-      <c r="T82" s="8" t="inlineStr">
+      <c r="T82" s="8" t="inlineStr"/>
+      <c r="U82" s="8" t="inlineStr">
         <is>
           <t>153.20</t>
         </is>
       </c>
-      <c r="U82" s="8" t="inlineStr"/>
-      <c r="V82" s="9" t="n">
-        <v>126.39</v>
-      </c>
+      <c r="V82" s="8" t="inlineStr"/>
       <c r="W82" s="9" t="n">
-        <v>695.7300000000001</v>
-      </c>
-      <c r="X82" s="11" t="n">
-        <v>-0.01000382478460424</v>
+        <v>152.9875</v>
+      </c>
+      <c r="X82" s="9" t="n">
+        <v>849.6624999999999</v>
+      </c>
+      <c r="Y82" s="11" t="n">
+        <v>-0.01221720319096315</v>
       </c>
     </row>
     <row r="83" ht="24" customHeight="1">
@@ -4629,12 +4816,13 @@
       <c r="S83" s="4" t="inlineStr"/>
       <c r="T83" s="4" t="inlineStr"/>
       <c r="U83" s="4" t="inlineStr"/>
-      <c r="V83" s="5" t="inlineStr"/>
-      <c r="W83" s="6" t="n">
-        <v>-1646.75</v>
-      </c>
-      <c r="X83" s="7" t="n">
-        <v>-0.1238986991294927</v>
+      <c r="V83" s="4" t="inlineStr"/>
+      <c r="W83" s="5" t="inlineStr"/>
+      <c r="X83" s="6" t="n">
+        <v>-1662.9375</v>
+      </c>
+      <c r="Y83" s="7" t="n">
+        <v>-0.1251166193919239</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1">
@@ -4656,19 +4844,19 @@
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr"/>
+      <c r="H84" s="8" t="inlineStr"/>
+      <c r="I84" s="13" t="inlineStr">
         <is>
           <t>2940.00</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" s="8" t="inlineStr">
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr">
         <is>
           <t>3193.75</t>
         </is>
       </c>
-      <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr"/>
       <c r="L84" s="8" t="inlineStr"/>
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="8" t="inlineStr"/>
@@ -4683,11 +4871,12 @@
       <c r="S84" s="8" t="inlineStr"/>
       <c r="T84" s="8" t="inlineStr"/>
       <c r="U84" s="8" t="inlineStr"/>
-      <c r="V84" s="9" t="n">
-        <v>2875.25</v>
-      </c>
-      <c r="W84" s="10" t="inlineStr"/>
-      <c r="X84" s="11" t="inlineStr"/>
+      <c r="V84" s="8" t="inlineStr"/>
+      <c r="W84" s="9" t="n">
+        <v>2859.0625</v>
+      </c>
+      <c r="X84" s="10" t="inlineStr"/>
+      <c r="Y84" s="11" t="inlineStr"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
@@ -4708,13 +4897,13 @@
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr"/>
-      <c r="G85" s="8" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr"/>
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>2553.75</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr"/>
-      <c r="I85" s="8" t="inlineStr"/>
       <c r="J85" s="8" t="inlineStr"/>
       <c r="K85" s="8" t="inlineStr"/>
       <c r="L85" s="8" t="inlineStr"/>
@@ -4731,9 +4920,10 @@
       <c r="S85" s="8" t="inlineStr"/>
       <c r="T85" s="8" t="inlineStr"/>
       <c r="U85" s="8" t="inlineStr"/>
-      <c r="V85" s="9" t="inlineStr"/>
-      <c r="W85" s="10" t="inlineStr"/>
-      <c r="X85" s="11" t="inlineStr"/>
+      <c r="V85" s="8" t="inlineStr"/>
+      <c r="W85" s="9" t="inlineStr"/>
+      <c r="X85" s="10" t="inlineStr"/>
+      <c r="Y85" s="11" t="inlineStr"/>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="1" t="n"/>
@@ -4754,19 +4944,19 @@
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr"/>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr"/>
+      <c r="I86" s="13" t="inlineStr">
         <is>
           <t>2338.75</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="J86" s="8" t="inlineStr"/>
+      <c r="K86" s="8" t="inlineStr">
         <is>
           <t>2608.75</t>
         </is>
       </c>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr"/>
       <c r="L86" s="8" t="inlineStr"/>
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr"/>
@@ -4781,14 +4971,15 @@
       <c r="S86" s="8" t="inlineStr"/>
       <c r="T86" s="8" t="inlineStr"/>
       <c r="U86" s="8" t="inlineStr"/>
-      <c r="V86" s="9" t="n">
-        <v>2920.25</v>
-      </c>
+      <c r="V86" s="8" t="inlineStr"/>
       <c r="W86" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="X86" s="11" t="n">
-        <v>0.003385724281662165</v>
+        <v>3065.625</v>
+      </c>
+      <c r="X86" s="9" t="n">
+        <v>206.5625</v>
+      </c>
+      <c r="Y86" s="11" t="n">
+        <v>0.01554141493179646</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1">
@@ -4823,11 +5014,12 @@
       <c r="S87" s="4" t="inlineStr"/>
       <c r="T87" s="4" t="inlineStr"/>
       <c r="U87" s="4" t="inlineStr"/>
-      <c r="V87" s="5" t="inlineStr"/>
-      <c r="W87" s="6" t="n">
+      <c r="V87" s="4" t="inlineStr"/>
+      <c r="W87" s="5" t="inlineStr"/>
+      <c r="X87" s="6" t="n">
         <v>-8627.75</v>
       </c>
-      <c r="X87" s="7" t="n">
+      <c r="Y87" s="7" t="n">
         <v>-1.101391459756175</v>
       </c>
     </row>
@@ -4844,13 +5036,13 @@
       <c r="F88" s="8" t="inlineStr"/>
       <c r="G88" s="8" t="inlineStr"/>
       <c r="H88" s="8" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr"/>
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr">
         <is>
           <t>8610.00</t>
         </is>
       </c>
-      <c r="J88" s="8" t="inlineStr"/>
-      <c r="K88" s="8" t="inlineStr"/>
       <c r="L88" s="8" t="inlineStr"/>
       <c r="M88" s="8" t="inlineStr"/>
       <c r="N88" s="8" t="inlineStr"/>
@@ -4873,11 +5065,12 @@
       <c r="S88" s="8" t="inlineStr"/>
       <c r="T88" s="8" t="inlineStr"/>
       <c r="U88" s="8" t="inlineStr"/>
-      <c r="V88" s="9" t="n">
+      <c r="V88" s="8" t="inlineStr"/>
+      <c r="W88" s="9" t="n">
         <v>8936.25</v>
       </c>
-      <c r="W88" s="10" t="inlineStr"/>
-      <c r="X88" s="11" t="inlineStr"/>
+      <c r="X88" s="10" t="inlineStr"/>
+      <c r="Y88" s="11" t="inlineStr"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="1" t="n"/>
@@ -4917,9 +5110,10 @@
       <c r="S89" s="8" t="inlineStr"/>
       <c r="T89" s="8" t="inlineStr"/>
       <c r="U89" s="8" t="inlineStr"/>
-      <c r="V89" s="9" t="inlineStr"/>
-      <c r="W89" s="10" t="inlineStr"/>
-      <c r="X89" s="11" t="inlineStr"/>
+      <c r="V89" s="8" t="inlineStr"/>
+      <c r="W89" s="9" t="inlineStr"/>
+      <c r="X89" s="10" t="inlineStr"/>
+      <c r="Y89" s="11" t="inlineStr"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="1" t="n"/>
@@ -4934,13 +5128,13 @@
       <c r="F90" s="8" t="inlineStr"/>
       <c r="G90" s="8" t="inlineStr"/>
       <c r="H90" s="8" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr"/>
+      <c r="J90" s="8" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr">
         <is>
           <t>8195.00</t>
         </is>
       </c>
-      <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr"/>
       <c r="L90" s="8" t="inlineStr"/>
       <c r="M90" s="8" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr"/>
@@ -4963,13 +5157,14 @@
       <c r="S90" s="8" t="inlineStr"/>
       <c r="T90" s="8" t="inlineStr"/>
       <c r="U90" s="8" t="inlineStr"/>
-      <c r="V90" s="9" t="n">
+      <c r="V90" s="8" t="inlineStr"/>
+      <c r="W90" s="9" t="n">
         <v>11597.5</v>
       </c>
-      <c r="W90" s="9" t="n">
+      <c r="X90" s="9" t="n">
         <v>2661.25</v>
       </c>
-      <c r="X90" s="11" t="n">
+      <c r="Y90" s="11" t="n">
         <v>0.3397268143230995</v>
       </c>
     </row>
@@ -5005,12 +5200,13 @@
       <c r="S91" s="4" t="inlineStr"/>
       <c r="T91" s="4" t="inlineStr"/>
       <c r="U91" s="4" t="inlineStr"/>
-      <c r="V91" s="5" t="inlineStr"/>
-      <c r="W91" s="6" t="n">
-        <v>-64.33333333333331</v>
-      </c>
-      <c r="X91" s="7" t="n">
-        <v>-0.001532245835744834</v>
+      <c r="V91" s="4" t="inlineStr"/>
+      <c r="W91" s="5" t="inlineStr"/>
+      <c r="X91" s="6" t="n">
+        <v>-69</v>
+      </c>
+      <c r="Y91" s="7" t="n">
+        <v>-0.001643393202068294</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1">
@@ -5030,13 +5226,13 @@
       <c r="F92" s="8" t="inlineStr"/>
       <c r="G92" s="8" t="inlineStr"/>
       <c r="H92" s="8" t="inlineStr"/>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr"/>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr">
         <is>
           <t>494.00</t>
         </is>
       </c>
-      <c r="J92" s="8" t="inlineStr"/>
-      <c r="K92" s="8" t="inlineStr"/>
       <c r="L92" s="8" t="inlineStr"/>
       <c r="M92" s="8" t="inlineStr"/>
       <c r="N92" s="8" t="inlineStr"/>
@@ -5049,17 +5245,18 @@
       <c r="Q92" s="8" t="inlineStr"/>
       <c r="R92" s="8" t="inlineStr"/>
       <c r="S92" s="8" t="inlineStr"/>
-      <c r="T92" s="8" t="inlineStr">
+      <c r="T92" s="8" t="inlineStr"/>
+      <c r="U92" s="8" t="inlineStr">
         <is>
           <t>470.00</t>
         </is>
       </c>
-      <c r="U92" s="8" t="inlineStr"/>
-      <c r="V92" s="9" t="n">
-        <v>460.6666666666667</v>
-      </c>
-      <c r="W92" s="10" t="inlineStr"/>
-      <c r="X92" s="11" t="inlineStr"/>
+      <c r="V92" s="8" t="inlineStr"/>
+      <c r="W92" s="9" t="n">
+        <v>456</v>
+      </c>
+      <c r="X92" s="10" t="inlineStr"/>
+      <c r="Y92" s="11" t="inlineStr"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
@@ -5080,24 +5277,25 @@
       <c r="L93" s="8" t="inlineStr"/>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
-      <c r="O93" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="O93" s="8" t="inlineStr">
+        <is>
+          <t>476.00</t>
         </is>
       </c>
       <c r="P93" s="8" t="inlineStr"/>
       <c r="Q93" s="8" t="inlineStr"/>
       <c r="R93" s="8" t="inlineStr"/>
       <c r="S93" s="8" t="inlineStr"/>
-      <c r="T93" s="8" t="inlineStr">
+      <c r="T93" s="8" t="inlineStr"/>
+      <c r="U93" s="8" t="inlineStr">
         <is>
           <t>557.00</t>
         </is>
       </c>
-      <c r="U93" s="8" t="inlineStr"/>
-      <c r="V93" s="9" t="inlineStr"/>
-      <c r="W93" s="10" t="inlineStr"/>
-      <c r="X93" s="11" t="inlineStr"/>
+      <c r="V93" s="8" t="inlineStr"/>
+      <c r="W93" s="9" t="inlineStr"/>
+      <c r="X93" s="10" t="inlineStr"/>
+      <c r="Y93" s="11" t="inlineStr"/>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="1" t="n"/>
@@ -5112,13 +5310,13 @@
       <c r="F94" s="8" t="inlineStr"/>
       <c r="G94" s="8" t="inlineStr"/>
       <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr"/>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr">
         <is>
           <t>521.00</t>
         </is>
       </c>
-      <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr"/>
       <c r="L94" s="8" t="inlineStr"/>
       <c r="M94" s="8" t="inlineStr"/>
       <c r="N94" s="8" t="inlineStr"/>
@@ -5131,20 +5329,21 @@
       <c r="Q94" s="8" t="inlineStr"/>
       <c r="R94" s="8" t="inlineStr"/>
       <c r="S94" s="8" t="inlineStr"/>
-      <c r="T94" s="8" t="inlineStr">
-        <is>
-          <t>545.00</t>
-        </is>
-      </c>
-      <c r="U94" s="8" t="inlineStr"/>
-      <c r="V94" s="9" t="n">
-        <v>505.3333333333333</v>
-      </c>
+      <c r="T94" s="8" t="inlineStr"/>
+      <c r="U94" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING, 545.00</t>
+        </is>
+      </c>
+      <c r="V94" s="8" t="inlineStr"/>
       <c r="W94" s="9" t="n">
-        <v>44.66666666666663</v>
-      </c>
-      <c r="X94" s="11" t="n">
-        <v>0.001063839077667397</v>
+        <v>485.5</v>
+      </c>
+      <c r="X94" s="9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Y94" s="11" t="n">
+        <v>0.0007026101371161546</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1">
@@ -5179,11 +5378,12 @@
       <c r="S95" s="4" t="inlineStr"/>
       <c r="T95" s="4" t="inlineStr"/>
       <c r="U95" s="4" t="inlineStr"/>
-      <c r="V95" s="5" t="inlineStr"/>
-      <c r="W95" s="6" t="n">
+      <c r="V95" s="4" t="inlineStr"/>
+      <c r="W95" s="5" t="inlineStr"/>
+      <c r="X95" s="6" t="n">
         <v>-2963</v>
       </c>
-      <c r="X95" s="7" t="n">
+      <c r="Y95" s="7" t="n">
         <v>-0.2655065502966003</v>
       </c>
     </row>
@@ -5202,13 +5402,13 @@
       <c r="D96" s="8" t="inlineStr"/>
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>5849.00</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr"/>
       <c r="J96" s="8" t="inlineStr"/>
       <c r="K96" s="8" t="inlineStr"/>
       <c r="L96" s="8" t="inlineStr"/>
@@ -5233,11 +5433,12 @@
       <c r="S96" s="8" t="inlineStr"/>
       <c r="T96" s="8" t="inlineStr"/>
       <c r="U96" s="8" t="inlineStr"/>
-      <c r="V96" s="9" t="n">
+      <c r="V96" s="8" t="inlineStr"/>
+      <c r="W96" s="9" t="n">
         <v>5022</v>
       </c>
-      <c r="W96" s="10" t="inlineStr"/>
-      <c r="X96" s="11" t="inlineStr"/>
+      <c r="X96" s="10" t="inlineStr"/>
+      <c r="Y96" s="11" t="inlineStr"/>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="1" t="n"/>
@@ -5277,9 +5478,10 @@
       <c r="S97" s="8" t="inlineStr"/>
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
-      <c r="V97" s="9" t="inlineStr"/>
-      <c r="W97" s="10" t="inlineStr"/>
-      <c r="X97" s="11" t="inlineStr"/>
+      <c r="V97" s="8" t="inlineStr"/>
+      <c r="W97" s="9" t="inlineStr"/>
+      <c r="X97" s="10" t="inlineStr"/>
+      <c r="Y97" s="11" t="inlineStr"/>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="1" t="n"/>
@@ -5319,13 +5521,14 @@
       <c r="S98" s="8" t="inlineStr"/>
       <c r="T98" s="8" t="inlineStr"/>
       <c r="U98" s="8" t="inlineStr"/>
-      <c r="V98" s="9" t="n">
+      <c r="V98" s="8" t="inlineStr"/>
+      <c r="W98" s="9" t="n">
         <v>5225.166666666667</v>
       </c>
-      <c r="W98" s="9" t="n">
+      <c r="X98" s="9" t="n">
         <v>203.166666666667</v>
       </c>
-      <c r="X98" s="11" t="n">
+      <c r="Y98" s="11" t="n">
         <v>0.01820522470534122</v>
       </c>
     </row>
@@ -5334,27 +5537,27 @@
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="A48:A51"/>
     <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A38:A40"/>
     <mergeCell ref="A87:A90"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A45:A47"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A91:A94"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A41:A43"/>
     <mergeCell ref="A63:A66"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A44:A47"/>
     <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A38:A41"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="A80:A82"/>
     <mergeCell ref="A59:A62"/>
     <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A42:A44"/>
     <mergeCell ref="A56:A58"/>
     <mergeCell ref="A52:A55"/>
   </mergeCells>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -247,224 +247,231 @@
 모든 평균은 EXCLUDED_SEEDS를 제외한 공통 시드 기준이며 HNS 차이는 부호를 유지합니다. 백분율이 아닙니다.</t>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0">
+    <comment ref="Q23" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q20" authorId="0" shapeId="0">
+    <comment ref="Q24" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q21" authorId="0" shapeId="0">
+    <comment ref="Q25" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P23" authorId="0" shapeId="0">
+    <comment ref="P27" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P28" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P25" authorId="0" shapeId="0">
+    <comment ref="P29" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O27" authorId="0" shapeId="0">
+    <comment ref="P30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O32" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O28" authorId="0" shapeId="0">
+    <comment ref="O33" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O29" authorId="0" shapeId="0">
+    <comment ref="O34" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0">
+    <comment ref="E56" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E50" authorId="0" shapeId="0">
+    <comment ref="E57" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0">
+    <comment ref="E58" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O53" authorId="0" shapeId="0">
+    <comment ref="O60" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P53" authorId="0" shapeId="0">
+    <comment ref="P60" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="U53" authorId="0" shapeId="0">
+    <comment ref="U60" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0">
+    <comment ref="O61" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P54" authorId="0" shapeId="0">
+    <comment ref="P61" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="U54" authorId="0" shapeId="0">
+    <comment ref="U61" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0">
+    <comment ref="O62" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P55" authorId="0" shapeId="0">
+    <comment ref="P62" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="U55" authorId="0" shapeId="0">
+    <comment ref="U62" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K68" authorId="0" shapeId="0">
+    <comment ref="K75" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L68" authorId="0" shapeId="0">
+    <comment ref="L75" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K69" authorId="0" shapeId="0">
+    <comment ref="K76" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L69" authorId="0" shapeId="0">
+    <comment ref="L76" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K70" authorId="0" shapeId="0">
+    <comment ref="K77" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L70" authorId="0" shapeId="0">
+    <comment ref="L77" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O81" authorId="0" shapeId="0">
+    <comment ref="O88" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O82" authorId="0" shapeId="0">
+    <comment ref="O89" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I84" authorId="0" shapeId="0">
+    <comment ref="I91" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I85" authorId="0" shapeId="0">
+    <comment ref="I92" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I86" authorId="0" shapeId="0">
+    <comment ref="I93" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -764,11 +771,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y98"/>
+  <dimension ref="A1:Y107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
-    <col width="41.1" customWidth="1" min="2" max="2"/>
+    <col width="54.7" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="13" max="13"/>
     <col width="3" customWidth="1" min="19" max="19"/>
@@ -1110,10 +1117,10 @@
       <c r="V6" s="4" t="inlineStr"/>
       <c r="W6" s="5" t="inlineStr"/>
       <c r="X6" s="6" t="n">
-        <v>-29.0625</v>
+        <v>2.849999999999994</v>
       </c>
       <c r="Y6" s="7" t="n">
-        <v>-0.01695891929742662</v>
+        <v>0.001663068214973446</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
@@ -1168,7 +1175,7 @@
       <c r="U7" s="8" t="inlineStr"/>
       <c r="V7" s="8" t="inlineStr"/>
       <c r="W7" s="9" t="n">
-        <v>175.9375</v>
+        <v>207.85</v>
       </c>
       <c r="X7" s="10" t="inlineStr"/>
       <c r="Y7" s="11" t="inlineStr"/>
@@ -1257,9 +1264,9 @@
         </is>
       </c>
       <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING, 236.55, 222.50</t>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>222.50</t>
         </is>
       </c>
       <c r="R9" s="8" t="inlineStr"/>
@@ -1268,68 +1275,58 @@
       <c r="U9" s="8" t="inlineStr"/>
       <c r="V9" s="8" t="inlineStr"/>
       <c r="W9" s="9" t="n">
-        <v>150.475</v>
+        <v>164.88</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>25.46249999999998</v>
+        <v>42.96999999999997</v>
       </c>
       <c r="Y9" s="11" t="n">
-        <v>-0.01485820155219699</v>
+        <v>-0.02507440042014353</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Assault
-Random: 222.4
-Human: 742.0</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 801</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="5" t="inlineStr"/>
-      <c r="X10" s="6" t="n">
-        <v>-36.5625</v>
-      </c>
-      <c r="Y10" s="7" t="n">
-        <v>-0.07036662817551963</v>
-      </c>
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr"/>
+      <c r="K10" s="8" t="inlineStr"/>
+      <c r="L10" s="8" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr"/>
+      <c r="O10" s="8" t="inlineStr"/>
+      <c r="P10" s="8" t="inlineStr"/>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>236.55</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr"/>
+      <c r="S10" s="8" t="inlineStr"/>
+      <c r="T10" s="8" t="inlineStr"/>
+      <c r="U10" s="8" t="inlineStr"/>
+      <c r="V10" s="8" t="inlineStr"/>
+      <c r="W10" s="9" t="inlineStr"/>
+      <c r="X10" s="10" t="inlineStr"/>
+      <c r="Y10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>705.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr"/>
       <c r="D11" s="8" t="inlineStr"/>
       <c r="E11" s="8" t="inlineStr"/>
       <c r="F11" s="8" t="inlineStr"/>
@@ -1337,142 +1334,110 @@
       <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>620.40</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>605.80</t>
-        </is>
-      </c>
+      <c r="K11" s="8" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr"/>
       <c r="M11" s="8" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>662.40</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>1126.55</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>832.50</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="8" t="inlineStr"/>
+      <c r="P11" s="8" t="inlineStr"/>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="R11" s="8" t="inlineStr"/>
       <c r="S11" s="8" t="inlineStr"/>
       <c r="T11" s="8" t="inlineStr"/>
       <c r="U11" s="8" t="inlineStr"/>
       <c r="V11" s="8" t="inlineStr"/>
-      <c r="W11" s="9" t="n">
-        <v>764.4375</v>
-      </c>
+      <c r="W11" s="9" t="inlineStr"/>
       <c r="X11" s="10" t="inlineStr"/>
       <c r="Y11" s="11" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>740.75</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>693.30</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>1033.70</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>867.85</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
-      <c r="S12" s="8" t="inlineStr"/>
-      <c r="T12" s="8" t="inlineStr"/>
-      <c r="U12" s="8" t="inlineStr"/>
-      <c r="V12" s="8" t="inlineStr"/>
-      <c r="W12" s="9" t="inlineStr"/>
-      <c r="X12" s="10" t="inlineStr"/>
-      <c r="Y12" s="11" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Assault
+Random: 222.4
+Human: 742.0</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 801</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr"/>
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="6" t="n">
+        <v>-22.95000000000005</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>-0.04416859122401856</v>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>779.45</t>
+          <t>705.00</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>738.60</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>548.60</t>
-        </is>
-      </c>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>720.25</t>
-        </is>
-      </c>
+      <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="8" t="inlineStr"/>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>666.55</t>
+          <t>620.40</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>633.05</t>
+          <t>605.80</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>662.40</t>
+        </is>
+      </c>
       <c r="O13" s="8" t="inlineStr">
         <is>
-          <t>724.80</t>
-        </is>
-      </c>
-      <c r="P13" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING, 723.85</t>
+          <t>1126.55</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>832.50</t>
         </is>
       </c>
       <c r="Q13" s="8" t="inlineStr"/>
@@ -1482,95 +1447,109 @@
       <c r="U13" s="8" t="inlineStr"/>
       <c r="V13" s="8" t="inlineStr"/>
       <c r="W13" s="9" t="n">
-        <v>700.9625000000001</v>
-      </c>
-      <c r="X13" s="9" t="n">
-        <v>63.47499999999991</v>
-      </c>
-      <c r="Y13" s="11" t="n">
-        <v>-0.1221612779060814</v>
-      </c>
+        <v>778.05</v>
+      </c>
+      <c r="X13" s="10" t="inlineStr"/>
+      <c r="Y13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Asterix
-Random: 210.0
-Human: 8503.3</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 1028</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="5" t="inlineStr"/>
-      <c r="X14" s="6" t="n">
-        <v>-349.6666666666666</v>
-      </c>
-      <c r="Y14" s="7" t="n">
-        <v>-0.04216254888484278</v>
-      </c>
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>740.75</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr"/>
+      <c r="J14" s="8" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>693.30</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr"/>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>1033.70</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>867.85</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr"/>
+      <c r="R14" s="8" t="inlineStr"/>
+      <c r="S14" s="8" t="inlineStr"/>
+      <c r="T14" s="8" t="inlineStr"/>
+      <c r="U14" s="8" t="inlineStr"/>
+      <c r="V14" s="8" t="inlineStr"/>
+      <c r="W14" s="9" t="inlineStr"/>
+      <c r="X14" s="10" t="inlineStr"/>
+      <c r="Y14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>515.00</t>
+          <t>779.45</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>530.00</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr"/>
+          <t>738.60</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>548.60</t>
+        </is>
+      </c>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>562.50</t>
+          <t>720.25</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>666.55</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>633.05</t>
+        </is>
+      </c>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="8" t="inlineStr">
         <is>
-          <t>942.50</t>
+          <t>724.80</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>675.00</t>
+          <t>723.85</t>
         </is>
       </c>
       <c r="Q15" s="8" t="inlineStr"/>
@@ -1580,33 +1559,29 @@
       <c r="U15" s="8" t="inlineStr"/>
       <c r="V15" s="8" t="inlineStr"/>
       <c r="W15" s="9" t="n">
-        <v>678.3333333333334</v>
-      </c>
-      <c r="X15" s="10" t="inlineStr"/>
-      <c r="Y15" s="11" t="inlineStr"/>
+        <v>705.5400000000001</v>
+      </c>
+      <c r="X15" s="9" t="n">
+        <v>72.50999999999988</v>
+      </c>
+      <c r="Y15" s="11" t="n">
+        <v>-0.1395496535796764</v>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr"/>
       <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>467.50</t>
-        </is>
-      </c>
+      <c r="E16" s="8" t="inlineStr"/>
       <c r="F16" s="8" t="inlineStr"/>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>677.50</t>
-        </is>
-      </c>
+      <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="8" t="inlineStr"/>
       <c r="L16" s="8" t="inlineStr"/>
@@ -1615,7 +1590,7 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>860.00</t>
+          <t>714.00</t>
         </is>
       </c>
       <c r="Q16" s="8" t="inlineStr"/>
@@ -1629,161 +1604,139 @@
       <c r="Y16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>600.00</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>545.00</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>887.50</t>
-        </is>
-      </c>
-      <c r="P17" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING, 1005.00</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr"/>
-      <c r="R17" s="8" t="inlineStr"/>
-      <c r="S17" s="8" t="inlineStr"/>
-      <c r="T17" s="8" t="inlineStr"/>
-      <c r="U17" s="8" t="inlineStr"/>
-      <c r="V17" s="8" t="inlineStr"/>
-      <c r="W17" s="9" t="n">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Asterix
+Random: 210.0
+Human: 8503.3</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 1028</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="6" t="n">
+        <v>-350.5</v>
+      </c>
+      <c r="Y17" s="7" t="n">
+        <v>-0.04226303160382478</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>515.00</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>530.00</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>562.50</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr"/>
+      <c r="L18" s="8" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr"/>
+      <c r="N18" s="8" t="inlineStr"/>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>942.50</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>675.00</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr"/>
+      <c r="R18" s="8" t="inlineStr"/>
+      <c r="S18" s="8" t="inlineStr"/>
+      <c r="T18" s="8" t="inlineStr"/>
+      <c r="U18" s="8" t="inlineStr"/>
+      <c r="V18" s="8" t="inlineStr"/>
+      <c r="W18" s="9" t="n">
         <v>677.5</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>0.8333333333333712</v>
-      </c>
-      <c r="Y17" s="11" t="n">
-        <v>-0.000100482718981994</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>BankHeist
-Random: 14.2
-Human: 753.1</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 641</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr"/>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="5" t="inlineStr"/>
-      <c r="X18" s="6" t="n">
-        <v>-84.75</v>
-      </c>
-      <c r="Y18" s="7" t="n">
-        <v>-0.1146975233455136</v>
-      </c>
+      <c r="X18" s="10" t="inlineStr"/>
+      <c r="Y18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr"/>
       <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>467.50</t>
+        </is>
+      </c>
       <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>677.50</t>
+        </is>
+      </c>
       <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>163.00</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>699.00</t>
-        </is>
-      </c>
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="8" t="inlineStr"/>
       <c r="M19" s="8" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>521.00</t>
-        </is>
-      </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>246.00</t>
-        </is>
-      </c>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr"/>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>170.00</t>
-        </is>
-      </c>
-      <c r="Q19" s="13" t="inlineStr">
-        <is>
-          <t>677.00</t>
-        </is>
-      </c>
+          <t>860.00</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr"/>
       <c r="R19" s="8" t="inlineStr"/>
       <c r="S19" s="8" t="inlineStr"/>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>694.50</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>668.50</t>
-        </is>
-      </c>
+      <c r="T19" s="8" t="inlineStr"/>
+      <c r="U19" s="8" t="inlineStr"/>
       <c r="V19" s="8" t="inlineStr"/>
-      <c r="W19" s="9" t="n">
-        <v>556.25</v>
-      </c>
+      <c r="W19" s="9" t="inlineStr"/>
       <c r="X19" s="10" t="inlineStr"/>
       <c r="Y19" s="11" t="inlineStr"/>
     </row>
@@ -1791,42 +1744,60 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr"/>
       <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
       <c r="F20" s="8" t="inlineStr"/>
       <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
       <c r="J20" s="8" t="inlineStr"/>
       <c r="K20" s="8" t="inlineStr"/>
       <c r="L20" s="8" t="inlineStr"/>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="8" t="inlineStr"/>
-      <c r="P20" s="8" t="inlineStr"/>
-      <c r="Q20" s="13" t="inlineStr"/>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>887.50</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>1005.00</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr"/>
       <c r="R20" s="8" t="inlineStr"/>
       <c r="S20" s="8" t="inlineStr"/>
       <c r="T20" s="8" t="inlineStr"/>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>507.50</t>
-        </is>
-      </c>
+      <c r="U20" s="8" t="inlineStr"/>
       <c r="V20" s="8" t="inlineStr"/>
-      <c r="W20" s="9" t="inlineStr"/>
-      <c r="X20" s="10" t="inlineStr"/>
-      <c r="Y20" s="11" t="inlineStr"/>
+      <c r="W20" s="9" t="n">
+        <v>759.375</v>
+      </c>
+      <c r="X20" s="9" t="n">
+        <v>81.875</v>
+      </c>
+      <c r="Y20" s="11" t="n">
+        <v>0.009872427139980468</v>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr"/>
@@ -1837,59 +1808,37 @@
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>169.50</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>633.50</t>
-        </is>
-      </c>
+      <c r="K21" s="8" t="inlineStr"/>
+      <c r="L21" s="8" t="inlineStr"/>
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="8" t="inlineStr"/>
-      <c r="P21" s="8" t="inlineStr"/>
-      <c r="Q21" s="13" t="inlineStr">
-        <is>
-          <t>114.00</t>
-        </is>
-      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr"/>
       <c r="R21" s="8" t="inlineStr"/>
       <c r="S21" s="8" t="inlineStr"/>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>566.00</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>565.00</t>
-        </is>
-      </c>
+      <c r="T21" s="8" t="inlineStr"/>
+      <c r="U21" s="8" t="inlineStr"/>
       <c r="V21" s="8" t="inlineStr"/>
-      <c r="W21" s="9" t="n">
-        <v>483.5</v>
-      </c>
-      <c r="X21" s="9" t="n">
-        <v>72.75</v>
-      </c>
-      <c r="Y21" s="11" t="n">
-        <v>-0.09845716605765327</v>
-      </c>
+      <c r="W21" s="9" t="inlineStr"/>
+      <c r="X21" s="10" t="inlineStr"/>
+      <c r="Y21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BattleZone
-Random: 2360.0
-Human: 37187.5</t>
+          <t>BankHeist
+Random: 14.2
+Human: 753.1</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 13540</t>
+          <t>STORM (논문): 641</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1914,10 +1863,10 @@
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="5" t="inlineStr"/>
       <c r="X22" s="6" t="n">
-        <v>-3777.5</v>
+        <v>-84.75</v>
       </c>
       <c r="Y22" s="7" t="n">
-        <v>-0.1084631397602469</v>
+        <v>-0.1146975233455136</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
@@ -1937,42 +1886,50 @@
       <c r="J23" s="8" t="inlineStr"/>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>5300.00</t>
+          <t>163.00</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>15900.00</t>
+          <t>699.00</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>9650.00</t>
+          <t>521.00</t>
         </is>
       </c>
       <c r="O23" s="8" t="inlineStr">
         <is>
-          <t>15100.00, 16150.00, 14200.00, 14800.00</t>
-        </is>
-      </c>
-      <c r="P23" s="13" t="inlineStr">
-        <is>
-          <t>9300.00, 8850.00, 8250.00, 9250.00</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>8200.00, 8400.00, 8550.00, 7950.00</t>
+          <t>246.00</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>170.00</t>
+        </is>
+      </c>
+      <c r="Q23" s="13" t="inlineStr">
+        <is>
+          <t>677.00</t>
         </is>
       </c>
       <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="8" t="inlineStr"/>
-      <c r="T23" s="8" t="inlineStr"/>
-      <c r="U23" s="8" t="inlineStr"/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>694.50</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>668.50</t>
+        </is>
+      </c>
       <c r="V23" s="8" t="inlineStr"/>
       <c r="W23" s="9" t="n">
-        <v>9762.5</v>
+        <v>556.25</v>
       </c>
       <c r="X23" s="10" t="inlineStr"/>
       <c r="Y23" s="11" t="inlineStr"/>
@@ -1992,37 +1949,21 @@
       <c r="H24" s="8" t="inlineStr"/>
       <c r="I24" s="8" t="inlineStr"/>
       <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>5550.00</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>13900.00</t>
-        </is>
-      </c>
+      <c r="K24" s="8" t="inlineStr"/>
+      <c r="L24" s="8" t="inlineStr"/>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>10950.00</t>
-        </is>
-      </c>
-      <c r="P24" s="13" t="inlineStr">
-        <is>
-          <t>5900.00</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t>7450.00</t>
-        </is>
-      </c>
+      <c r="O24" s="8" t="inlineStr"/>
+      <c r="P24" s="8" t="inlineStr"/>
+      <c r="Q24" s="13" t="inlineStr"/>
       <c r="R24" s="8" t="inlineStr"/>
       <c r="S24" s="8" t="inlineStr"/>
       <c r="T24" s="8" t="inlineStr"/>
-      <c r="U24" s="8" t="inlineStr"/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>507.50</t>
+        </is>
+      </c>
       <c r="V24" s="8" t="inlineStr"/>
       <c r="W24" s="9" t="inlineStr"/>
       <c r="X24" s="10" t="inlineStr"/>
@@ -2045,61 +1986,57 @@
       <c r="J25" s="8" t="inlineStr"/>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>169.50</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>14250.00</t>
+          <t>633.50</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>13050.00</t>
-        </is>
-      </c>
-      <c r="O25" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING, 14350.00</t>
-        </is>
-      </c>
-      <c r="P25" s="13" t="inlineStr">
-        <is>
-          <t>5650.00</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t>10850.00</t>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="8" t="inlineStr"/>
+      <c r="P25" s="8" t="inlineStr"/>
+      <c r="Q25" s="13" t="inlineStr">
+        <is>
+          <t>114.00</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="8" t="inlineStr"/>
-      <c r="T25" s="8" t="inlineStr"/>
-      <c r="U25" s="8" t="inlineStr"/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>566.00</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>565.00</t>
+        </is>
+      </c>
       <c r="V25" s="8" t="inlineStr"/>
       <c r="W25" s="9" t="n">
-        <v>10912.5</v>
+        <v>483.5</v>
       </c>
       <c r="X25" s="9" t="n">
-        <v>1150</v>
+        <v>72.75</v>
       </c>
       <c r="Y25" s="11" t="n">
-        <v>0.03301988371258345</v>
+        <v>-0.09845716605765327</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Boxing
-Random: 0.1
-Human: 12.1</t>
+          <t>BattleZone
+Random: 2360.0
+Human: 37187.5</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 80</t>
+          <t>STORM (논문): 13540</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -2124,10 +2061,10 @@
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="5" t="inlineStr"/>
       <c r="X26" s="6" t="n">
-        <v>-1.350000000000009</v>
+        <v>-2710</v>
       </c>
       <c r="Y26" s="7" t="n">
-        <v>-0.1125000000000007</v>
+        <v>-0.07781207379226186</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
@@ -2139,45 +2076,41 @@
       </c>
       <c r="C27" s="8" t="inlineStr"/>
       <c r="D27" s="8" t="inlineStr"/>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>68.60</t>
-        </is>
-      </c>
+      <c r="E27" s="8" t="inlineStr"/>
       <c r="F27" s="8" t="inlineStr"/>
       <c r="G27" s="8" t="inlineStr"/>
       <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>73.80</t>
-        </is>
-      </c>
+      <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="8" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>81.00</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr"/>
+          <t>5300.00</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>15900.00</t>
+        </is>
+      </c>
       <c r="M27" s="8" t="inlineStr"/>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>88.60</t>
-        </is>
-      </c>
-      <c r="O27" s="13" t="inlineStr">
-        <is>
-          <t>70.40</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>77.80</t>
+          <t>9650.00</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>15100.00, 16150.00, 14200.00, 14800.00</t>
+        </is>
+      </c>
+      <c r="P27" s="13" t="inlineStr">
+        <is>
+          <t>9300.00, 8850.00, 8250.00, 9250.00</t>
         </is>
       </c>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>87.20</t>
+          <t>8200.00, 8400.00, 8550.00, 7950.00</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr"/>
@@ -2186,7 +2119,7 @@
       <c r="U27" s="8" t="inlineStr"/>
       <c r="V27" s="8" t="inlineStr"/>
       <c r="W27" s="9" t="n">
-        <v>78.64999999999999</v>
+        <v>10830</v>
       </c>
       <c r="X27" s="10" t="inlineStr"/>
       <c r="Y27" s="11" t="inlineStr"/>
@@ -2200,23 +2133,39 @@
       </c>
       <c r="C28" s="8" t="inlineStr"/>
       <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>74.85</t>
-        </is>
-      </c>
+      <c r="E28" s="8" t="inlineStr"/>
       <c r="F28" s="8" t="inlineStr"/>
       <c r="G28" s="8" t="inlineStr"/>
       <c r="H28" s="8" t="inlineStr"/>
       <c r="I28" s="8" t="inlineStr"/>
       <c r="J28" s="8" t="inlineStr"/>
-      <c r="K28" s="8" t="inlineStr"/>
-      <c r="L28" s="8" t="inlineStr"/>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>5550.00</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>13900.00</t>
+        </is>
+      </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="8" t="inlineStr"/>
-      <c r="O28" s="13" t="inlineStr"/>
-      <c r="P28" s="8" t="inlineStr"/>
-      <c r="Q28" s="8" t="inlineStr"/>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>10950.00</t>
+        </is>
+      </c>
+      <c r="P28" s="13" t="inlineStr">
+        <is>
+          <t>5900.00</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>7450.00</t>
+        </is>
+      </c>
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr"/>
       <c r="T28" s="8" t="inlineStr"/>
@@ -2235,11 +2184,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr"/>
       <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>76.15</t>
-        </is>
-      </c>
+      <c r="E29" s="8" t="inlineStr"/>
       <c r="F29" s="8" t="inlineStr"/>
       <c r="G29" s="8" t="inlineStr"/>
       <c r="H29" s="8" t="inlineStr"/>
@@ -2247,25 +2192,33 @@
       <c r="J29" s="8" t="inlineStr"/>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>78.50</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr"/>
+          <t>5500.00</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>14250.00</t>
+        </is>
+      </c>
       <c r="M29" s="8" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
-      <c r="O29" s="13" t="inlineStr">
-        <is>
-          <t>51.15</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="inlineStr">
-        <is>
-          <t>85.05</t>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>13050.00</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>14350.00</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t>5650.00</t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>87.90</t>
+          <t>10850.00</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr"/>
@@ -2274,121 +2227,103 @@
       <c r="U29" s="8" t="inlineStr"/>
       <c r="V29" s="8" t="inlineStr"/>
       <c r="W29" s="9" t="n">
-        <v>81.90000000000001</v>
+        <v>11600</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>3.250000000000014</v>
+        <v>770</v>
       </c>
       <c r="Y29" s="11" t="n">
-        <v>0.2708333333333345</v>
+        <v>0.02210896561625153</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Breakout
-Random: 1.7
-Human: 30.5</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 16</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr"/>
-      <c r="O30" s="4" t="inlineStr"/>
-      <c r="P30" s="4" t="inlineStr"/>
-      <c r="Q30" s="4" t="inlineStr"/>
-      <c r="R30" s="4" t="inlineStr"/>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="5" t="inlineStr"/>
-      <c r="X30" s="6" t="n">
-        <v>-4.266666666666666</v>
-      </c>
-      <c r="Y30" s="7" t="n">
-        <v>-0.1481481481481481</v>
-      </c>
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
+      <c r="J30" s="8" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr"/>
+      <c r="L30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
+      <c r="N30" s="8" t="inlineStr"/>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="P30" s="13" t="inlineStr"/>
+      <c r="Q30" s="8" t="inlineStr"/>
+      <c r="R30" s="8" t="inlineStr"/>
+      <c r="S30" s="8" t="inlineStr"/>
+      <c r="T30" s="8" t="inlineStr"/>
+      <c r="U30" s="8" t="inlineStr"/>
+      <c r="V30" s="8" t="inlineStr"/>
+      <c r="W30" s="9" t="inlineStr"/>
+      <c r="X30" s="10" t="inlineStr"/>
+      <c r="Y30" s="11" t="inlineStr"/>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>11.40</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>9.60</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr"/>
-      <c r="M31" s="8" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
-      <c r="O31" s="8" t="inlineStr"/>
-      <c r="P31" s="8" t="inlineStr"/>
-      <c r="Q31" s="8" t="inlineStr"/>
-      <c r="R31" s="8" t="inlineStr"/>
-      <c r="S31" s="8" t="inlineStr"/>
-      <c r="T31" s="8" t="inlineStr"/>
-      <c r="U31" s="8" t="inlineStr"/>
-      <c r="V31" s="8" t="inlineStr"/>
-      <c r="W31" s="9" t="n">
-        <v>11.73333333333333</v>
-      </c>
-      <c r="X31" s="10" t="inlineStr"/>
-      <c r="Y31" s="11" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Boxing
+Random: 0.1
+Human: 12.1</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 80</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr"/>
+      <c r="Q31" s="4" t="inlineStr"/>
+      <c r="R31" s="4" t="inlineStr"/>
+      <c r="S31" s="4" t="inlineStr"/>
+      <c r="T31" s="4" t="inlineStr"/>
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="5" t="inlineStr"/>
+      <c r="X31" s="6" t="n">
+        <v>-1.350000000000009</v>
+      </c>
+      <c r="Y31" s="7" t="n">
+        <v>-0.1125000000000007</v>
+      </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr"/>
       <c r="D32" s="8" t="inlineStr"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>68.60</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr"/>
@@ -2396,27 +2331,45 @@
       <c r="H32" s="8" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>73.80</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr"/>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr"/>
       <c r="M32" s="8" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
-      <c r="O32" s="8" t="inlineStr"/>
-      <c r="P32" s="8" t="inlineStr"/>
-      <c r="Q32" s="8" t="inlineStr"/>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>88.60</t>
+        </is>
+      </c>
+      <c r="O32" s="13" t="inlineStr">
+        <is>
+          <t>70.40</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>77.80</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>87.20</t>
+        </is>
+      </c>
       <c r="R32" s="8" t="inlineStr"/>
       <c r="S32" s="8" t="inlineStr"/>
       <c r="T32" s="8" t="inlineStr"/>
       <c r="U32" s="8" t="inlineStr"/>
       <c r="V32" s="8" t="inlineStr"/>
-      <c r="W32" s="9" t="inlineStr"/>
+      <c r="W32" s="9" t="n">
+        <v>78.64999999999999</v>
+      </c>
       <c r="X32" s="10" t="inlineStr"/>
       <c r="Y32" s="11" t="inlineStr"/>
     </row>
@@ -2424,34 +2377,26 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr"/>
       <c r="D33" s="8" t="inlineStr"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>74.85</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr"/>
       <c r="G33" s="8" t="inlineStr"/>
       <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
+      <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="8" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>9.30</t>
-        </is>
-      </c>
+      <c r="K33" s="8" t="inlineStr"/>
       <c r="L33" s="8" t="inlineStr"/>
       <c r="M33" s="8" t="inlineStr"/>
       <c r="N33" s="8" t="inlineStr"/>
-      <c r="O33" s="8" t="inlineStr"/>
+      <c r="O33" s="13" t="inlineStr"/>
       <c r="P33" s="8" t="inlineStr"/>
       <c r="Q33" s="8" t="inlineStr"/>
       <c r="R33" s="8" t="inlineStr"/>
@@ -2459,130 +2404,144 @@
       <c r="T33" s="8" t="inlineStr"/>
       <c r="U33" s="8" t="inlineStr"/>
       <c r="V33" s="8" t="inlineStr"/>
-      <c r="W33" s="9" t="n">
-        <v>12.36666666666667</v>
-      </c>
-      <c r="X33" s="9" t="n">
-        <v>0.6333333333333311</v>
-      </c>
-      <c r="Y33" s="11" t="n">
-        <v>0.02199074074074066</v>
-      </c>
+      <c r="W33" s="9" t="inlineStr"/>
+      <c r="X33" s="10" t="inlineStr"/>
+      <c r="Y33" s="11" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ChopperCommand
-Random: 811.0
-Human: 7387.8</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 1888</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr"/>
-      <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr"/>
-      <c r="O34" s="4" t="inlineStr"/>
-      <c r="P34" s="4" t="inlineStr"/>
-      <c r="Q34" s="4" t="inlineStr"/>
-      <c r="R34" s="4" t="inlineStr"/>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="5" t="inlineStr"/>
-      <c r="X34" s="6" t="n">
-        <v>-480.5</v>
-      </c>
-      <c r="Y34" s="7" t="n">
-        <v>-0.07305984673397396</v>
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr"/>
+      <c r="D34" s="8" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>76.15</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr"/>
+      <c r="J34" s="8" t="inlineStr"/>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>78.50</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
+      <c r="N34" s="8" t="inlineStr"/>
+      <c r="O34" s="13" t="inlineStr">
+        <is>
+          <t>51.15</t>
+        </is>
+      </c>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>85.05</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>87.90</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr"/>
+      <c r="S34" s="8" t="inlineStr"/>
+      <c r="T34" s="8" t="inlineStr"/>
+      <c r="U34" s="8" t="inlineStr"/>
+      <c r="V34" s="8" t="inlineStr"/>
+      <c r="W34" s="9" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="X34" s="9" t="n">
+        <v>3.250000000000014</v>
+      </c>
+      <c r="Y34" s="11" t="n">
+        <v>0.2708333333333345</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>1530.00</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>1960.00</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>1980.00</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>1345.00</t>
-        </is>
-      </c>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
-      <c r="O35" s="8" t="inlineStr"/>
-      <c r="P35" s="8" t="inlineStr"/>
-      <c r="Q35" s="8" t="inlineStr"/>
-      <c r="R35" s="8" t="inlineStr"/>
-      <c r="S35" s="8" t="inlineStr"/>
-      <c r="T35" s="8" t="inlineStr"/>
-      <c r="U35" s="8" t="inlineStr"/>
-      <c r="V35" s="8" t="inlineStr"/>
-      <c r="W35" s="9" t="n">
-        <v>1407.5</v>
-      </c>
-      <c r="X35" s="10" t="inlineStr"/>
-      <c r="Y35" s="11" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Breakout
+Random: 1.7
+Human: 30.5</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 16</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="inlineStr"/>
+      <c r="Q35" s="4" t="inlineStr"/>
+      <c r="R35" s="4" t="inlineStr"/>
+      <c r="S35" s="4" t="inlineStr"/>
+      <c r="T35" s="4" t="inlineStr"/>
+      <c r="U35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="5" t="inlineStr"/>
+      <c r="X35" s="6" t="n">
+        <v>-4.266666666666666</v>
+      </c>
+      <c r="Y35" s="7" t="n">
+        <v>-0.1481481481481481</v>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr"/>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>14.35</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>11.40</t>
+        </is>
+      </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr"/>
       <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>14.00</t>
+        </is>
+      </c>
       <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>9.80</t>
+        </is>
+      </c>
       <c r="L36" s="8" t="inlineStr"/>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
@@ -2594,7 +2553,9 @@
       <c r="T36" s="8" t="inlineStr"/>
       <c r="U36" s="8" t="inlineStr"/>
       <c r="V36" s="8" t="inlineStr"/>
-      <c r="W36" s="9" t="inlineStr"/>
+      <c r="W36" s="9" t="n">
+        <v>11.73333333333333</v>
+      </c>
       <c r="X36" s="10" t="inlineStr"/>
       <c r="Y36" s="11" t="inlineStr"/>
     </row>
@@ -2602,28 +2563,28 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr"/>
       <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING, 1125.00, 970.00</t>
-        </is>
-      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>12.10</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="8" t="inlineStr"/>
       <c r="H37" s="8" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr"/>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr"/>
@@ -2637,128 +2598,134 @@
       <c r="T37" s="8" t="inlineStr"/>
       <c r="U37" s="8" t="inlineStr"/>
       <c r="V37" s="8" t="inlineStr"/>
-      <c r="W37" s="9" t="n">
-        <v>1352.5</v>
-      </c>
-      <c r="X37" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y37" s="11" t="n">
-        <v>-0.008362729594939788</v>
-      </c>
+      <c r="W37" s="9" t="inlineStr"/>
+      <c r="X37" s="10" t="inlineStr"/>
+      <c r="Y37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CrazyClimber
-Random: 10780.5
-Human: 35829.4</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 66776</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr"/>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr"/>
-      <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr"/>
-      <c r="O38" s="4" t="inlineStr"/>
-      <c r="P38" s="4" t="inlineStr"/>
-      <c r="Q38" s="4" t="inlineStr"/>
-      <c r="R38" s="4" t="inlineStr"/>
-      <c r="S38" s="4" t="inlineStr"/>
-      <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="4" t="inlineStr"/>
-      <c r="W38" s="5" t="inlineStr"/>
-      <c r="X38" s="6" t="n">
-        <v>-9204.333333333336</v>
-      </c>
-      <c r="Y38" s="7" t="n">
-        <v>-0.3674545921510859</v>
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr"/>
+      <c r="D38" s="8" t="inlineStr"/>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>12.70</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr"/>
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>15.10</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr"/>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>9.30</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
+      <c r="N38" s="8" t="inlineStr"/>
+      <c r="O38" s="8" t="inlineStr"/>
+      <c r="P38" s="8" t="inlineStr"/>
+      <c r="Q38" s="8" t="inlineStr"/>
+      <c r="R38" s="8" t="inlineStr"/>
+      <c r="S38" s="8" t="inlineStr"/>
+      <c r="T38" s="8" t="inlineStr"/>
+      <c r="U38" s="8" t="inlineStr"/>
+      <c r="V38" s="8" t="inlineStr"/>
+      <c r="W38" s="9" t="n">
+        <v>12.36666666666667</v>
+      </c>
+      <c r="X38" s="9" t="n">
+        <v>0.6333333333333311</v>
+      </c>
+      <c r="Y38" s="11" t="n">
+        <v>0.02199074074074066</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>63125.00</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>46620.00</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>49810.00</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr"/>
-      <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>66125.00</t>
-        </is>
-      </c>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr">
-        <is>
-          <t>59970.00</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr"/>
-      <c r="M39" s="8" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
-      <c r="O39" s="8" t="inlineStr"/>
-      <c r="P39" s="8" t="inlineStr"/>
-      <c r="Q39" s="8" t="inlineStr"/>
-      <c r="R39" s="8" t="inlineStr"/>
-      <c r="S39" s="8" t="inlineStr"/>
-      <c r="T39" s="8" t="inlineStr"/>
-      <c r="U39" s="8" t="inlineStr"/>
-      <c r="V39" s="8" t="inlineStr"/>
-      <c r="W39" s="9" t="n">
-        <v>57571.66666666666</v>
-      </c>
-      <c r="X39" s="10" t="inlineStr"/>
-      <c r="Y39" s="11" t="inlineStr"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ChopperCommand
+Random: 811.0
+Human: 7387.8</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 1888</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="inlineStr"/>
+      <c r="Q39" s="4" t="inlineStr"/>
+      <c r="R39" s="4" t="inlineStr"/>
+      <c r="S39" s="4" t="inlineStr"/>
+      <c r="T39" s="4" t="inlineStr"/>
+      <c r="U39" s="4" t="inlineStr"/>
+      <c r="V39" s="4" t="inlineStr"/>
+      <c r="W39" s="5" t="inlineStr"/>
+      <c r="X39" s="6" t="n">
+        <v>-289.6666666666667</v>
+      </c>
+      <c r="Y39" s="7" t="n">
+        <v>-0.04404370920001623</v>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>1530.00</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>1960.00</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>1980.00</t>
+        </is>
+      </c>
       <c r="G40" s="8" t="inlineStr"/>
       <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>1345.00</t>
+        </is>
+      </c>
       <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr"/>
@@ -2772,7 +2739,9 @@
       <c r="T40" s="8" t="inlineStr"/>
       <c r="U40" s="8" t="inlineStr"/>
       <c r="V40" s="8" t="inlineStr"/>
-      <c r="W40" s="9" t="inlineStr"/>
+      <c r="W40" s="9" t="n">
+        <v>1598.333333333333</v>
+      </c>
       <c r="X40" s="10" t="inlineStr"/>
       <c r="Y40" s="11" t="inlineStr"/>
     </row>
@@ -2780,30 +2749,22 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr"/>
       <c r="D41" s="8" t="inlineStr"/>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>56795.00</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr"/>
+      <c r="E41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>1360.00</t>
+        </is>
+      </c>
       <c r="G41" s="8" t="inlineStr"/>
       <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>53655.00</t>
-        </is>
-      </c>
+      <c r="I41" s="8" t="inlineStr"/>
       <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>63275.00</t>
-        </is>
-      </c>
+      <c r="K41" s="8" t="inlineStr"/>
       <c r="L41" s="8" t="inlineStr"/>
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
@@ -2815,96 +2776,82 @@
       <c r="T41" s="8" t="inlineStr"/>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
-      <c r="W41" s="9" t="n">
-        <v>57908.33333333334</v>
-      </c>
-      <c r="X41" s="9" t="n">
-        <v>336.6666666666715</v>
-      </c>
-      <c r="Y41" s="11" t="n">
-        <v>0.01344037728869018</v>
-      </c>
+      <c r="W41" s="9" t="inlineStr"/>
+      <c r="X41" s="10" t="inlineStr"/>
+      <c r="Y41" s="11" t="inlineStr"/>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>DemonAttack
-Random: 152.1
-Human: 1971.0</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 165</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="inlineStr"/>
-      <c r="P42" s="4" t="inlineStr"/>
-      <c r="Q42" s="4" t="inlineStr"/>
-      <c r="R42" s="4" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr"/>
-      <c r="T42" s="4" t="inlineStr"/>
-      <c r="U42" s="4" t="inlineStr"/>
-      <c r="V42" s="4" t="inlineStr"/>
-      <c r="W42" s="5" t="inlineStr"/>
-      <c r="X42" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y42" s="7" t="n">
-        <v>0.01539391940183627</v>
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr"/>
+      <c r="D42" s="8" t="inlineStr"/>
+      <c r="E42" s="8" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>970.00</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>1445.00</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr"/>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>1260.00</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="8" t="inlineStr"/>
+      <c r="O42" s="8" t="inlineStr"/>
+      <c r="P42" s="8" t="inlineStr"/>
+      <c r="Q42" s="8" t="inlineStr"/>
+      <c r="R42" s="8" t="inlineStr"/>
+      <c r="S42" s="8" t="inlineStr"/>
+      <c r="T42" s="8" t="inlineStr"/>
+      <c r="U42" s="8" t="inlineStr"/>
+      <c r="V42" s="8" t="inlineStr"/>
+      <c r="W42" s="9" t="n">
+        <v>1225</v>
+      </c>
+      <c r="X42" s="9" t="n">
+        <v>373.3333333333333</v>
+      </c>
+      <c r="Y42" s="11" t="n">
+        <v>-0.05676519482625794</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr"/>
       <c r="D43" s="8" t="inlineStr"/>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>214.25</t>
-        </is>
-      </c>
+      <c r="E43" s="8" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>139.75</t>
+          <t>1125.00</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr"/>
       <c r="H43" s="8" t="inlineStr"/>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>200.75</t>
-        </is>
-      </c>
+      <c r="I43" s="8" t="inlineStr"/>
       <c r="J43" s="8" t="inlineStr"/>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>171.75</t>
-        </is>
-      </c>
+      <c r="K43" s="8" t="inlineStr"/>
       <c r="L43" s="8" t="inlineStr"/>
       <c r="M43" s="8" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t>188.00</t>
-        </is>
-      </c>
+      <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="8" t="inlineStr"/>
       <c r="P43" s="8" t="inlineStr"/>
       <c r="Q43" s="8" t="inlineStr"/>
@@ -2913,9 +2860,7 @@
       <c r="T43" s="8" t="inlineStr"/>
       <c r="U43" s="8" t="inlineStr"/>
       <c r="V43" s="8" t="inlineStr"/>
-      <c r="W43" s="9" t="n">
-        <v>193</v>
-      </c>
+      <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="10" t="inlineStr"/>
       <c r="Y43" s="11" t="inlineStr"/>
     </row>
@@ -2923,26 +2868,22 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr"/>
       <c r="D44" s="8" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>150.75</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="G44" s="8" t="inlineStr"/>
       <c r="H44" s="8" t="inlineStr"/>
       <c r="I44" s="8" t="inlineStr"/>
       <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="8" t="inlineStr">
-        <is>
-          <t>192.25</t>
-        </is>
-      </c>
+      <c r="K44" s="8" t="inlineStr"/>
       <c r="L44" s="8" t="inlineStr"/>
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
@@ -2954,27 +2895,21 @@
       <c r="T44" s="8" t="inlineStr"/>
       <c r="U44" s="8" t="inlineStr"/>
       <c r="V44" s="8" t="inlineStr"/>
-      <c r="W44" s="9" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="X44" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="Y44" s="11" t="n">
-        <v>-0.01182033096926714</v>
-      </c>
+      <c r="W44" s="9" t="inlineStr"/>
+      <c r="X44" s="10" t="inlineStr"/>
+      <c r="Y44" s="11" t="inlineStr"/>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Freeway
-Random: 0.0
-Human: 29.6</t>
+          <t>CrazyClimber
+Random: 10780.5
+Human: 35829.4</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 34</t>
+          <t>STORM (논문): 66776</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -2999,10 +2934,10 @@
       <c r="V45" s="4" t="inlineStr"/>
       <c r="W45" s="5" t="inlineStr"/>
       <c r="X45" s="6" t="n">
-        <v>-1.25</v>
+        <v>-9204.333333333336</v>
       </c>
       <c r="Y45" s="7" t="n">
-        <v>-0.04222972972972973</v>
+        <v>-0.3674545921510859</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
@@ -3013,31 +2948,39 @@
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr"/>
-      <c r="D46" s="8" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr"/>
-      <c r="F46" s="8" t="inlineStr"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>63125.00</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>46620.00</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>49810.00</t>
+        </is>
+      </c>
       <c r="G46" s="8" t="inlineStr"/>
       <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>66125.00</t>
+        </is>
+      </c>
       <c r="J46" s="8" t="inlineStr"/>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>59970.00</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr"/>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
-      <c r="O46" s="8" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
-      </c>
-      <c r="P46" s="8" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
+      <c r="O46" s="8" t="inlineStr"/>
+      <c r="P46" s="8" t="inlineStr"/>
       <c r="Q46" s="8" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr"/>
@@ -3045,7 +2988,7 @@
       <c r="U46" s="8" t="inlineStr"/>
       <c r="V46" s="8" t="inlineStr"/>
       <c r="W46" s="9" t="n">
-        <v>32.75</v>
+        <v>57571.66666666666</v>
       </c>
       <c r="X46" s="10" t="inlineStr"/>
       <c r="Y46" s="11" t="inlineStr"/>
@@ -3054,7 +2997,7 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr"/>
@@ -3065,178 +3008,166 @@
       <c r="H47" s="8" t="inlineStr"/>
       <c r="I47" s="8" t="inlineStr"/>
       <c r="J47" s="8" t="inlineStr"/>
-      <c r="K47" s="8" t="inlineStr"/>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="L47" s="8" t="inlineStr"/>
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
-      <c r="O47" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING, 33.55</t>
-        </is>
-      </c>
-      <c r="P47" s="8" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
+      <c r="O47" s="8" t="inlineStr"/>
+      <c r="P47" s="8" t="inlineStr"/>
       <c r="Q47" s="8" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
       <c r="S47" s="8" t="inlineStr"/>
       <c r="T47" s="8" t="inlineStr"/>
       <c r="U47" s="8" t="inlineStr"/>
       <c r="V47" s="8" t="inlineStr"/>
-      <c r="W47" s="9" t="n">
-        <v>32.75</v>
-      </c>
-      <c r="X47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="W47" s="9" t="inlineStr"/>
+      <c r="X47" s="10" t="inlineStr"/>
+      <c r="Y47" s="11" t="inlineStr"/>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Frostbite
-Random: 65.2
-Human: 4334.7</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 1316</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="4" t="inlineStr"/>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr"/>
-      <c r="J48" s="4" t="inlineStr"/>
-      <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr"/>
-      <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr"/>
-      <c r="O48" s="4" t="inlineStr"/>
-      <c r="P48" s="4" t="inlineStr"/>
-      <c r="Q48" s="4" t="inlineStr"/>
-      <c r="R48" s="4" t="inlineStr"/>
-      <c r="S48" s="4" t="inlineStr"/>
-      <c r="T48" s="4" t="inlineStr"/>
-      <c r="U48" s="4" t="inlineStr"/>
-      <c r="V48" s="4" t="inlineStr"/>
-      <c r="W48" s="5" t="inlineStr"/>
-      <c r="X48" s="6" t="n">
-        <v>426.375</v>
-      </c>
-      <c r="Y48" s="7" t="n">
-        <v>0.09986532380840848</v>
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr"/>
+      <c r="D48" s="8" t="inlineStr"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>56795.00</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>53655.00</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr"/>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>63275.00</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr"/>
+      <c r="M48" s="8" t="inlineStr"/>
+      <c r="N48" s="8" t="inlineStr"/>
+      <c r="O48" s="8" t="inlineStr"/>
+      <c r="P48" s="8" t="inlineStr"/>
+      <c r="Q48" s="8" t="inlineStr"/>
+      <c r="R48" s="8" t="inlineStr"/>
+      <c r="S48" s="8" t="inlineStr"/>
+      <c r="T48" s="8" t="inlineStr"/>
+      <c r="U48" s="8" t="inlineStr"/>
+      <c r="V48" s="8" t="inlineStr"/>
+      <c r="W48" s="9" t="n">
+        <v>57908.33333333334</v>
+      </c>
+      <c r="X48" s="9" t="n">
+        <v>336.6666666666715</v>
+      </c>
+      <c r="Y48" s="11" t="n">
+        <v>0.01344037728869018</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr"/>
-      <c r="D49" s="8" t="inlineStr"/>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>2068.00</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>2270.50</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr"/>
-      <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>1904.00</t>
-        </is>
-      </c>
-      <c r="J49" s="8" t="inlineStr"/>
-      <c r="K49" s="8" t="inlineStr"/>
-      <c r="L49" s="8" t="inlineStr"/>
-      <c r="M49" s="8" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
-      <c r="O49" s="8" t="inlineStr">
-        <is>
-          <t>2544.50, 2833.50, 2600.50, 2639.00</t>
-        </is>
-      </c>
-      <c r="P49" s="8" t="inlineStr">
-        <is>
-          <t>250.50, 252.50, 255.00, 255.00</t>
-        </is>
-      </c>
-      <c r="Q49" s="8" t="inlineStr"/>
-      <c r="R49" s="8" t="inlineStr"/>
-      <c r="S49" s="8" t="inlineStr"/>
-      <c r="T49" s="8" t="inlineStr"/>
-      <c r="U49" s="8" t="inlineStr"/>
-      <c r="V49" s="8" t="inlineStr"/>
-      <c r="W49" s="9" t="n">
-        <v>1742.375</v>
-      </c>
-      <c r="X49" s="10" t="inlineStr"/>
-      <c r="Y49" s="11" t="inlineStr"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>DemonAttack
+Random: 152.1
+Human: 1971.0</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 165</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr"/>
+      <c r="Q49" s="4" t="inlineStr"/>
+      <c r="R49" s="4" t="inlineStr"/>
+      <c r="S49" s="4" t="inlineStr"/>
+      <c r="T49" s="4" t="inlineStr"/>
+      <c r="U49" s="4" t="inlineStr"/>
+      <c r="V49" s="4" t="inlineStr"/>
+      <c r="W49" s="5" t="inlineStr"/>
+      <c r="X49" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y49" s="7" t="n">
+        <v>0.01539391940183627</v>
+      </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr"/>
       <c r="D50" s="8" t="inlineStr"/>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>2301.00</t>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>214.25</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>2609.00</t>
+          <t>139.75</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr"/>
       <c r="H50" s="8" t="inlineStr"/>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>3242.50</t>
+          <t>200.75</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr"/>
-      <c r="K50" s="8" t="inlineStr"/>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>171.75</t>
+        </is>
+      </c>
       <c r="L50" s="8" t="inlineStr"/>
       <c r="M50" s="8" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
-      <c r="O50" s="8" t="inlineStr">
-        <is>
-          <t>2119.50</t>
-        </is>
-      </c>
-      <c r="P50" s="8" t="inlineStr">
-        <is>
-          <t>261.50</t>
-        </is>
-      </c>
+      <c r="N50" s="8" t="inlineStr">
+        <is>
+          <t>188.00</t>
+        </is>
+      </c>
+      <c r="O50" s="8" t="inlineStr"/>
+      <c r="P50" s="8" t="inlineStr"/>
       <c r="Q50" s="8" t="inlineStr"/>
       <c r="R50" s="8" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr"/>
       <c r="T50" s="8" t="inlineStr"/>
       <c r="U50" s="8" t="inlineStr"/>
       <c r="V50" s="8" t="inlineStr"/>
-      <c r="W50" s="9" t="inlineStr"/>
+      <c r="W50" s="9" t="n">
+        <v>193</v>
+      </c>
       <c r="X50" s="10" t="inlineStr"/>
       <c r="Y50" s="11" t="inlineStr"/>
     </row>
@@ -3249,46 +3180,26 @@
       </c>
       <c r="C51" s="8" t="inlineStr"/>
       <c r="D51" s="8" t="inlineStr"/>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>2113.50, 2350.50</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>2443.00</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>283.50</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>252.00</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>2779.00</t>
-        </is>
-      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>150.75</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr"/>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr"/>
       <c r="J51" s="8" t="inlineStr"/>
-      <c r="K51" s="8" t="inlineStr"/>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>192.25</t>
+        </is>
+      </c>
       <c r="L51" s="8" t="inlineStr"/>
       <c r="M51" s="8" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
-      <c r="O51" s="8" t="inlineStr">
-        <is>
-          <t>2474.00</t>
-        </is>
-      </c>
-      <c r="P51" s="8" t="inlineStr">
-        <is>
-          <t>251.00</t>
-        </is>
-      </c>
+      <c r="O51" s="8" t="inlineStr"/>
+      <c r="P51" s="8" t="inlineStr"/>
       <c r="Q51" s="8" t="inlineStr"/>
       <c r="R51" s="8" t="inlineStr"/>
       <c r="S51" s="8" t="inlineStr"/>
@@ -3296,26 +3207,26 @@
       <c r="U51" s="8" t="inlineStr"/>
       <c r="V51" s="8" t="inlineStr"/>
       <c r="W51" s="9" t="n">
-        <v>1986.75</v>
+        <v>171.5</v>
       </c>
       <c r="X51" s="9" t="n">
-        <v>244.375</v>
+        <v>21.5</v>
       </c>
       <c r="Y51" s="11" t="n">
-        <v>0.05723738142639653</v>
+        <v>-0.01182033096926714</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Gopher
-Random: 257.6
-Human: 2412.5</t>
+          <t>Freeway
+Random: 0.0
+Human: 29.6</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 8240</t>
+          <t>STORM (논문): 34</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -3340,10 +3251,10 @@
       <c r="V52" s="4" t="inlineStr"/>
       <c r="W52" s="5" t="inlineStr"/>
       <c r="X52" s="6" t="n">
-        <v>-4547</v>
+        <v>-0.7000000000000028</v>
       </c>
       <c r="Y52" s="7" t="n">
-        <v>-2.110074713443779</v>
+        <v>-0.02364864864864874</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
@@ -3353,64 +3264,40 @@
           <t>Retrieval 미사용</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>5968.00</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>3752.00</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>3275.00</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>3914.00</t>
-        </is>
-      </c>
+      <c r="C53" s="8" t="inlineStr"/>
+      <c r="D53" s="8" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr"/>
       <c r="G53" s="8" t="inlineStr"/>
       <c r="H53" s="8" t="inlineStr"/>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>4219.00</t>
-        </is>
-      </c>
+      <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr"/>
-      <c r="K53" s="8" t="inlineStr"/>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="L53" s="8" t="inlineStr"/>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
-      <c r="O53" s="13" t="inlineStr">
-        <is>
-          <t>2486.00</t>
-        </is>
-      </c>
-      <c r="P53" s="13" t="inlineStr">
-        <is>
-          <t>1250.00</t>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>33.85</t>
+        </is>
+      </c>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t>32.75</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr"/>
       <c r="R53" s="8" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr"/>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>3585.00</t>
-        </is>
-      </c>
-      <c r="U53" s="13" t="inlineStr">
-        <is>
-          <t>2594.00</t>
-        </is>
-      </c>
+      <c r="T53" s="8" t="inlineStr"/>
+      <c r="U53" s="8" t="inlineStr"/>
       <c r="V53" s="8" t="inlineStr"/>
       <c r="W53" s="9" t="n">
-        <v>3693</v>
+        <v>33.3</v>
       </c>
       <c r="X53" s="10" t="inlineStr"/>
       <c r="Y53" s="11" t="inlineStr"/>
@@ -3419,7 +3306,7 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr"/>
@@ -3434,152 +3321,150 @@
       <c r="L54" s="8" t="inlineStr"/>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
-      <c r="O54" s="13" t="inlineStr"/>
-      <c r="P54" s="13" t="inlineStr"/>
+      <c r="O54" s="8" t="inlineStr">
+        <is>
+          <t>33.55</t>
+        </is>
+      </c>
+      <c r="P54" s="8" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
       <c r="Q54" s="8" t="inlineStr"/>
-      <c r="R54" s="8" t="inlineStr">
-        <is>
-          <t>2533.00</t>
-        </is>
-      </c>
+      <c r="R54" s="8" t="inlineStr"/>
       <c r="S54" s="8" t="inlineStr"/>
       <c r="T54" s="8" t="inlineStr"/>
-      <c r="U54" s="13" t="inlineStr"/>
+      <c r="U54" s="8" t="inlineStr"/>
       <c r="V54" s="8" t="inlineStr"/>
-      <c r="W54" s="9" t="inlineStr"/>
-      <c r="X54" s="10" t="inlineStr"/>
-      <c r="Y54" s="11" t="inlineStr"/>
+      <c r="W54" s="9" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="X54" s="9" t="n">
+        <v>0.1499999999999986</v>
+      </c>
+      <c r="Y54" s="11" t="n">
+        <v>-0.005067567567567519</v>
+      </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>3327.00</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr"/>
-      <c r="G55" s="8" t="inlineStr"/>
-      <c r="H55" s="8" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>3829.00</t>
-        </is>
-      </c>
-      <c r="J55" s="8" t="inlineStr"/>
-      <c r="K55" s="8" t="inlineStr"/>
-      <c r="L55" s="8" t="inlineStr"/>
-      <c r="M55" s="8" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
-      <c r="O55" s="13" t="inlineStr">
-        <is>
-          <t>1024.00</t>
-        </is>
-      </c>
-      <c r="P55" s="13" t="inlineStr">
-        <is>
-          <t>927.00</t>
-        </is>
-      </c>
-      <c r="Q55" s="8" t="inlineStr"/>
-      <c r="R55" s="8" t="inlineStr"/>
-      <c r="S55" s="8" t="inlineStr"/>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>7531.00</t>
-        </is>
-      </c>
-      <c r="U55" s="13" t="inlineStr">
-        <is>
-          <t>1005.00</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr"/>
-      <c r="W55" s="9" t="n">
-        <v>4895.666666666667</v>
-      </c>
-      <c r="X55" s="9" t="n">
-        <v>1202.666666666667</v>
-      </c>
-      <c r="Y55" s="11" t="n">
-        <v>0.558107878169134</v>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Frostbite
+Random: 65.2
+Human: 4334.7</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 1316</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
+      <c r="P55" s="4" t="inlineStr"/>
+      <c r="Q55" s="4" t="inlineStr"/>
+      <c r="R55" s="4" t="inlineStr"/>
+      <c r="S55" s="4" t="inlineStr"/>
+      <c r="T55" s="4" t="inlineStr"/>
+      <c r="U55" s="4" t="inlineStr"/>
+      <c r="V55" s="4" t="inlineStr"/>
+      <c r="W55" s="5" t="inlineStr"/>
+      <c r="X55" s="6" t="n">
+        <v>426.375</v>
+      </c>
+      <c r="Y55" s="7" t="n">
+        <v>0.09986532380840848</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Hero
-Random: 1027.0
-Human: 30826.4</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11044</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr"/>
-      <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
-      <c r="H56" s="4" t="inlineStr"/>
-      <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr"/>
-      <c r="K56" s="4" t="inlineStr"/>
-      <c r="L56" s="4" t="inlineStr"/>
-      <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr"/>
-      <c r="O56" s="4" t="inlineStr"/>
-      <c r="P56" s="4" t="inlineStr"/>
-      <c r="Q56" s="4" t="inlineStr"/>
-      <c r="R56" s="4" t="inlineStr"/>
-      <c r="S56" s="4" t="inlineStr"/>
-      <c r="T56" s="4" t="inlineStr"/>
-      <c r="U56" s="4" t="inlineStr"/>
-      <c r="V56" s="4" t="inlineStr"/>
-      <c r="W56" s="5" t="inlineStr"/>
-      <c r="X56" s="6" t="n">
-        <v>2134</v>
-      </c>
-      <c r="Y56" s="7" t="n">
-        <v>0.07161218011100895</v>
-      </c>
+      <c r="A56" s="1" t="n"/>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr"/>
+      <c r="D56" s="8" t="inlineStr"/>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>2068.00</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>2270.50</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr"/>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>1904.00</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr"/>
+      <c r="K56" s="8" t="inlineStr"/>
+      <c r="L56" s="8" t="inlineStr"/>
+      <c r="M56" s="8" t="inlineStr"/>
+      <c r="N56" s="8" t="inlineStr"/>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>2544.50, 2833.50, 2600.50, 2639.00</t>
+        </is>
+      </c>
+      <c r="P56" s="8" t="inlineStr">
+        <is>
+          <t>250.50, 252.50, 255.00, 255.00</t>
+        </is>
+      </c>
+      <c r="Q56" s="8" t="inlineStr"/>
+      <c r="R56" s="8" t="inlineStr"/>
+      <c r="S56" s="8" t="inlineStr"/>
+      <c r="T56" s="8" t="inlineStr"/>
+      <c r="U56" s="8" t="inlineStr"/>
+      <c r="V56" s="8" t="inlineStr"/>
+      <c r="W56" s="9" t="n">
+        <v>1742.375</v>
+      </c>
+      <c r="X56" s="10" t="inlineStr"/>
+      <c r="Y56" s="11" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>7608.50</t>
-        </is>
-      </c>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr"/>
       <c r="D57" s="8" t="inlineStr"/>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>12996.75</t>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>2301.00</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>13456.25</t>
+          <t>2609.00</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr"/>
       <c r="H57" s="8" t="inlineStr"/>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>13081.00</t>
+          <t>3242.50</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr"/>
@@ -3587,17 +3472,23 @@
       <c r="L57" s="8" t="inlineStr"/>
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
-      <c r="O57" s="8" t="inlineStr"/>
-      <c r="P57" s="8" t="inlineStr"/>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>2119.50</t>
+        </is>
+      </c>
+      <c r="P57" s="8" t="inlineStr">
+        <is>
+          <t>261.50</t>
+        </is>
+      </c>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr"/>
       <c r="T57" s="8" t="inlineStr"/>
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr"/>
-      <c r="W57" s="9" t="n">
-        <v>13178</v>
-      </c>
+      <c r="W57" s="9" t="inlineStr"/>
       <c r="X57" s="10" t="inlineStr"/>
       <c r="Y57" s="11" t="inlineStr"/>
     </row>
@@ -3610,21 +3501,29 @@
       </c>
       <c r="C58" s="8" t="inlineStr"/>
       <c r="D58" s="8" t="inlineStr"/>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>13251.25</t>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>2113.50, 2350.50</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>13231.50</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr"/>
-      <c r="H58" s="8" t="inlineStr"/>
+          <t>2443.00</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>283.50</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>252.00</t>
+        </is>
+      </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>13325.50</t>
+          <t>2779.00</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr"/>
@@ -3632,8 +3531,16 @@
       <c r="L58" s="8" t="inlineStr"/>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
-      <c r="O58" s="8" t="inlineStr"/>
-      <c r="P58" s="8" t="inlineStr"/>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>2474.00</t>
+        </is>
+      </c>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>251.00</t>
+        </is>
+      </c>
       <c r="Q58" s="8" t="inlineStr"/>
       <c r="R58" s="8" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr"/>
@@ -3641,26 +3548,26 @@
       <c r="U58" s="8" t="inlineStr"/>
       <c r="V58" s="8" t="inlineStr"/>
       <c r="W58" s="9" t="n">
-        <v>13269.41666666667</v>
+        <v>1986.75</v>
       </c>
       <c r="X58" s="9" t="n">
-        <v>91.41666666666606</v>
+        <v>244.375</v>
       </c>
       <c r="Y58" s="11" t="n">
-        <v>0.003067735144555463</v>
+        <v>0.05723738142639653</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Jamesbond
-Random: 29.0
-Human: 302.8</t>
+          <t>Gopher
+Random: 257.6
+Human: 2412.5</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 509</t>
+          <t>STORM (논문): 8240</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -3685,10 +3592,10 @@
       <c r="V59" s="4" t="inlineStr"/>
       <c r="W59" s="5" t="inlineStr"/>
       <c r="X59" s="6" t="n">
-        <v>-35.66666666666669</v>
+        <v>-4547</v>
       </c>
       <c r="Y59" s="7" t="n">
-        <v>-0.1302654005356709</v>
+        <v>-2.110074713443779</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
@@ -3700,42 +3607,62 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>490.00</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr"/>
-      <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="8" t="inlineStr"/>
+          <t>5968.00</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>3752.00</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>3275.00</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>3914.00</t>
+        </is>
+      </c>
       <c r="G60" s="8" t="inlineStr"/>
       <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>4219.00</t>
+        </is>
+      </c>
       <c r="J60" s="8" t="inlineStr"/>
-      <c r="K60" s="8" t="inlineStr">
-        <is>
-          <t>532.50, 537.50</t>
-        </is>
-      </c>
+      <c r="K60" s="8" t="inlineStr"/>
       <c r="L60" s="8" t="inlineStr"/>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
-      <c r="O60" s="8" t="inlineStr">
-        <is>
-          <t>522.50</t>
-        </is>
-      </c>
-      <c r="P60" s="8" t="inlineStr"/>
+      <c r="O60" s="13" t="inlineStr">
+        <is>
+          <t>2486.00</t>
+        </is>
+      </c>
+      <c r="P60" s="13" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
       <c r="Q60" s="8" t="inlineStr"/>
       <c r="R60" s="8" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr"/>
-      <c r="T60" s="8" t="inlineStr"/>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>3585.00</t>
+        </is>
+      </c>
+      <c r="U60" s="13" t="inlineStr">
+        <is>
+          <t>2594.00</t>
         </is>
       </c>
       <c r="V60" s="8" t="inlineStr"/>
       <c r="W60" s="9" t="n">
-        <v>473.3333333333333</v>
+        <v>3693</v>
       </c>
       <c r="X60" s="10" t="inlineStr"/>
       <c r="Y60" s="11" t="inlineStr"/>
@@ -3759,17 +3686,17 @@
       <c r="L61" s="8" t="inlineStr"/>
       <c r="M61" s="8" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="8" t="inlineStr">
-        <is>
-          <t>575.00</t>
-        </is>
-      </c>
-      <c r="P61" s="8" t="inlineStr"/>
+      <c r="O61" s="13" t="inlineStr"/>
+      <c r="P61" s="13" t="inlineStr"/>
       <c r="Q61" s="8" t="inlineStr"/>
-      <c r="R61" s="8" t="inlineStr"/>
+      <c r="R61" s="8" t="inlineStr">
+        <is>
+          <t>2533.00</t>
+        </is>
+      </c>
       <c r="S61" s="8" t="inlineStr"/>
       <c r="T61" s="8" t="inlineStr"/>
-      <c r="U61" s="8" t="inlineStr"/>
+      <c r="U61" s="13" t="inlineStr"/>
       <c r="V61" s="8" t="inlineStr"/>
       <c r="W61" s="9" t="inlineStr"/>
       <c r="X61" s="10" t="inlineStr"/>
@@ -3784,57 +3711,69 @@
       </c>
       <c r="C62" s="8" t="inlineStr"/>
       <c r="D62" s="8" t="inlineStr"/>
-      <c r="E62" s="8" t="inlineStr"/>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>3327.00</t>
+        </is>
+      </c>
       <c r="F62" s="8" t="inlineStr"/>
       <c r="G62" s="8" t="inlineStr"/>
       <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>3829.00</t>
+        </is>
+      </c>
       <c r="J62" s="8" t="inlineStr"/>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>567.50, 660.00</t>
-        </is>
-      </c>
+      <c r="K62" s="8" t="inlineStr"/>
       <c r="L62" s="8" t="inlineStr"/>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
-      <c r="O62" s="8" t="inlineStr">
-        <is>
-          <t>665.00</t>
-        </is>
-      </c>
-      <c r="P62" s="8" t="inlineStr"/>
+      <c r="O62" s="13" t="inlineStr">
+        <is>
+          <t>1024.00</t>
+        </is>
+      </c>
+      <c r="P62" s="13" t="inlineStr">
+        <is>
+          <t>927.00</t>
+        </is>
+      </c>
       <c r="Q62" s="8" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr"/>
-      <c r="T62" s="8" t="inlineStr"/>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>375.00</t>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>7531.00</t>
+        </is>
+      </c>
+      <c r="U62" s="13" t="inlineStr">
+        <is>
+          <t>1005.00</t>
         </is>
       </c>
       <c r="V62" s="8" t="inlineStr"/>
       <c r="W62" s="9" t="n">
-        <v>535.8333333333334</v>
+        <v>4895.666666666667</v>
       </c>
       <c r="X62" s="9" t="n">
-        <v>62.50000000000006</v>
+        <v>1202.666666666667</v>
       </c>
       <c r="Y62" s="11" t="n">
-        <v>0.2282688093498906</v>
+        <v>0.558107878169134</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Kangaroo
-Random: 52.0
-Human: 3035.0</t>
+          <t>Hero
+Random: 1027.0
+Human: 30826.4</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 4208</t>
+          <t>STORM (논문): 11044</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -3859,10 +3798,10 @@
       <c r="V63" s="4" t="inlineStr"/>
       <c r="W63" s="5" t="inlineStr"/>
       <c r="X63" s="6" t="n">
-        <v>-2778</v>
+        <v>2134</v>
       </c>
       <c r="Y63" s="7" t="n">
-        <v>-0.9312772376801878</v>
+        <v>0.07161218011100895</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
@@ -3872,40 +3811,36 @@
           <t>Retrieval 미사용</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr"/>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>7608.50</t>
+        </is>
+      </c>
       <c r="D64" s="8" t="inlineStr"/>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>1770.00</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr"/>
+          <t>12996.75</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>13456.25</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="inlineStr"/>
       <c r="H64" s="8" t="inlineStr"/>
-      <c r="I64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>13081.00</t>
+        </is>
+      </c>
       <c r="J64" s="8" t="inlineStr"/>
-      <c r="K64" s="8" t="inlineStr">
-        <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="L64" s="8" t="inlineStr">
-        <is>
-          <t>1730.00</t>
-        </is>
-      </c>
+      <c r="K64" s="8" t="inlineStr"/>
+      <c r="L64" s="8" t="inlineStr"/>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
-      <c r="O64" s="8" t="inlineStr">
-        <is>
-          <t>1550.00</t>
-        </is>
-      </c>
-      <c r="P64" s="8" t="inlineStr">
-        <is>
-          <t>930.00</t>
-        </is>
-      </c>
+      <c r="O64" s="8" t="inlineStr"/>
+      <c r="P64" s="8" t="inlineStr"/>
       <c r="Q64" s="8" t="inlineStr"/>
       <c r="R64" s="8" t="inlineStr"/>
       <c r="S64" s="8" t="inlineStr"/>
@@ -3913,7 +3848,7 @@
       <c r="U64" s="8" t="inlineStr"/>
       <c r="V64" s="8" t="inlineStr"/>
       <c r="W64" s="9" t="n">
-        <v>1430</v>
+        <v>13178</v>
       </c>
       <c r="X64" s="10" t="inlineStr"/>
       <c r="Y64" s="11" t="inlineStr"/>
@@ -3922,201 +3857,173 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr"/>
       <c r="D65" s="8" t="inlineStr"/>
-      <c r="E65" s="8" t="inlineStr"/>
-      <c r="F65" s="8" t="inlineStr"/>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>13251.25</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>13231.50</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>13325.50</t>
+        </is>
+      </c>
       <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr">
-        <is>
-          <t>1310.00</t>
-        </is>
-      </c>
+      <c r="K65" s="8" t="inlineStr"/>
       <c r="L65" s="8" t="inlineStr"/>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
-      <c r="O65" s="8" t="inlineStr">
-        <is>
-          <t>1500.00</t>
-        </is>
-      </c>
-      <c r="P65" s="8" t="inlineStr">
-        <is>
-          <t>1030.00</t>
-        </is>
-      </c>
+      <c r="O65" s="8" t="inlineStr"/>
+      <c r="P65" s="8" t="inlineStr"/>
       <c r="Q65" s="8" t="inlineStr"/>
       <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr"/>
       <c r="T65" s="8" t="inlineStr"/>
       <c r="U65" s="8" t="inlineStr"/>
       <c r="V65" s="8" t="inlineStr"/>
-      <c r="W65" s="9" t="inlineStr"/>
-      <c r="X65" s="10" t="inlineStr"/>
-      <c r="Y65" s="11" t="inlineStr"/>
+      <c r="W65" s="9" t="n">
+        <v>13269.41666666667</v>
+      </c>
+      <c r="X65" s="9" t="n">
+        <v>91.41666666666606</v>
+      </c>
+      <c r="Y65" s="11" t="n">
+        <v>0.003067735144555463</v>
+      </c>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="1" t="n"/>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr"/>
-      <c r="D66" s="8" t="inlineStr"/>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>1760.00</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr"/>
-      <c r="G66" s="8" t="inlineStr"/>
-      <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="8" t="inlineStr"/>
-      <c r="J66" s="8" t="inlineStr"/>
-      <c r="K66" s="8" t="inlineStr">
-        <is>
-          <t>1590.00</t>
-        </is>
-      </c>
-      <c r="L66" s="8" t="inlineStr"/>
-      <c r="M66" s="8" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
-      <c r="O66" s="8" t="inlineStr">
-        <is>
-          <t>1670.00</t>
-        </is>
-      </c>
-      <c r="P66" s="8" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
-      </c>
-      <c r="Q66" s="8" t="inlineStr"/>
-      <c r="R66" s="8" t="inlineStr"/>
-      <c r="S66" s="8" t="inlineStr"/>
-      <c r="T66" s="8" t="inlineStr"/>
-      <c r="U66" s="8" t="inlineStr"/>
-      <c r="V66" s="8" t="inlineStr"/>
-      <c r="W66" s="9" t="n">
-        <v>1445</v>
-      </c>
-      <c r="X66" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y66" s="11" t="n">
-        <v>0.005028494803888703</v>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Jamesbond
+Random: 29.0
+Human: 302.8</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 509</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr"/>
+      <c r="Q66" s="4" t="inlineStr"/>
+      <c r="R66" s="4" t="inlineStr"/>
+      <c r="S66" s="4" t="inlineStr"/>
+      <c r="T66" s="4" t="inlineStr"/>
+      <c r="U66" s="4" t="inlineStr"/>
+      <c r="V66" s="4" t="inlineStr"/>
+      <c r="W66" s="5" t="inlineStr"/>
+      <c r="X66" s="6" t="n">
+        <v>-35.66666666666669</v>
+      </c>
+      <c r="Y66" s="7" t="n">
+        <v>-0.1302654005356709</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Krull
-Random: 1598.0
-Human: 2665.5</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 8413</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr"/>
-      <c r="D67" s="4" t="inlineStr"/>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="4" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="4" t="inlineStr"/>
-      <c r="K67" s="4" t="inlineStr"/>
-      <c r="L67" s="4" t="inlineStr"/>
-      <c r="M67" s="4" t="inlineStr"/>
-      <c r="N67" s="4" t="inlineStr"/>
-      <c r="O67" s="4" t="inlineStr"/>
-      <c r="P67" s="4" t="inlineStr"/>
-      <c r="Q67" s="4" t="inlineStr"/>
-      <c r="R67" s="4" t="inlineStr"/>
-      <c r="S67" s="4" t="inlineStr"/>
-      <c r="T67" s="4" t="inlineStr"/>
-      <c r="U67" s="4" t="inlineStr"/>
-      <c r="V67" s="4" t="inlineStr"/>
-      <c r="W67" s="5" t="inlineStr"/>
-      <c r="X67" s="6" t="n">
-        <v>-2583.375</v>
-      </c>
-      <c r="Y67" s="7" t="n">
-        <v>-2.420023419203747</v>
-      </c>
+      <c r="A67" s="1" t="n"/>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>490.00</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr"/>
+      <c r="F67" s="8" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr"/>
+      <c r="J67" s="8" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>532.50, 537.50</t>
+        </is>
+      </c>
+      <c r="L67" s="8" t="inlineStr"/>
+      <c r="M67" s="8" t="inlineStr"/>
+      <c r="N67" s="8" t="inlineStr"/>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>522.50</t>
+        </is>
+      </c>
+      <c r="P67" s="8" t="inlineStr"/>
+      <c r="Q67" s="8" t="inlineStr"/>
+      <c r="R67" s="8" t="inlineStr"/>
+      <c r="S67" s="8" t="inlineStr"/>
+      <c r="T67" s="8" t="inlineStr"/>
+      <c r="U67" s="8" t="inlineStr">
+        <is>
+          <t>365.00</t>
+        </is>
+      </c>
+      <c r="V67" s="8" t="inlineStr"/>
+      <c r="W67" s="9" t="n">
+        <v>473.3333333333333</v>
+      </c>
+      <c r="X67" s="10" t="inlineStr"/>
+      <c r="Y67" s="11" t="inlineStr"/>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr"/>
       <c r="D68" s="8" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>6202.00</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>5689.00</t>
-        </is>
-      </c>
+      <c r="E68" s="8" t="inlineStr"/>
+      <c r="F68" s="8" t="inlineStr"/>
       <c r="G68" s="8" t="inlineStr"/>
       <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>6107.50</t>
-        </is>
-      </c>
+      <c r="I68" s="8" t="inlineStr"/>
       <c r="J68" s="8" t="inlineStr"/>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>4708.50</t>
-        </is>
-      </c>
-      <c r="L68" s="13" t="inlineStr">
-        <is>
-          <t>5913.50</t>
-        </is>
-      </c>
+      <c r="K68" s="8" t="inlineStr"/>
+      <c r="L68" s="8" t="inlineStr"/>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
       <c r="O68" s="8" t="inlineStr">
         <is>
-          <t>5228.50</t>
+          <t>575.00</t>
         </is>
       </c>
       <c r="P68" s="8" t="inlineStr"/>
-      <c r="Q68" s="8" t="inlineStr">
-        <is>
-          <t>5599.00</t>
-        </is>
-      </c>
+      <c r="Q68" s="8" t="inlineStr"/>
       <c r="R68" s="8" t="inlineStr"/>
       <c r="S68" s="8" t="inlineStr"/>
       <c r="T68" s="8" t="inlineStr"/>
-      <c r="U68" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
+      <c r="U68" s="8" t="inlineStr"/>
       <c r="V68" s="8" t="inlineStr"/>
-      <c r="W68" s="9" t="n">
-        <v>5829.625</v>
-      </c>
+      <c r="W68" s="9" t="inlineStr"/>
       <c r="X68" s="10" t="inlineStr"/>
       <c r="Y68" s="11" t="inlineStr"/>
     </row>
@@ -4124,7 +4031,7 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr"/>
@@ -4135,19 +4042,19 @@
       <c r="H69" s="8" t="inlineStr"/>
       <c r="I69" s="8" t="inlineStr"/>
       <c r="J69" s="8" t="inlineStr"/>
-      <c r="K69" s="13" t="inlineStr">
-        <is>
-          <t>4851.00</t>
-        </is>
-      </c>
-      <c r="L69" s="13" t="inlineStr">
-        <is>
-          <t>6044.00</t>
-        </is>
-      </c>
+      <c r="K69" s="8" t="inlineStr">
+        <is>
+          <t>567.50, 660.00</t>
+        </is>
+      </c>
+      <c r="L69" s="8" t="inlineStr"/>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
-      <c r="O69" s="8" t="inlineStr"/>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>665.00</t>
+        </is>
+      </c>
       <c r="P69" s="8" t="inlineStr"/>
       <c r="Q69" s="8" t="inlineStr"/>
       <c r="R69" s="8" t="inlineStr"/>
@@ -4155,130 +4062,124 @@
       <c r="T69" s="8" t="inlineStr"/>
       <c r="U69" s="8" t="inlineStr">
         <is>
-          <t>6587.00</t>
+          <t>375.00</t>
         </is>
       </c>
       <c r="V69" s="8" t="inlineStr"/>
-      <c r="W69" s="9" t="inlineStr"/>
-      <c r="X69" s="10" t="inlineStr"/>
-      <c r="Y69" s="11" t="inlineStr"/>
+      <c r="W69" s="9" t="n">
+        <v>535.8333333333334</v>
+      </c>
+      <c r="X69" s="9" t="n">
+        <v>62.50000000000006</v>
+      </c>
+      <c r="Y69" s="11" t="n">
+        <v>0.2282688093498906</v>
+      </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr"/>
-      <c r="D70" s="8" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>6576.50</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr"/>
-      <c r="G70" s="8" t="inlineStr"/>
-      <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr"/>
-      <c r="J70" s="8" t="inlineStr"/>
-      <c r="K70" s="13" t="inlineStr">
-        <is>
-          <t>5279.50</t>
-        </is>
-      </c>
-      <c r="L70" s="13" t="inlineStr">
-        <is>
-          <t>5889.50</t>
-        </is>
-      </c>
-      <c r="M70" s="8" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
-      <c r="O70" s="8" t="inlineStr">
-        <is>
-          <t>6447.50</t>
-        </is>
-      </c>
-      <c r="P70" s="8" t="inlineStr"/>
-      <c r="Q70" s="8" t="inlineStr">
-        <is>
-          <t>6828.50</t>
-        </is>
-      </c>
-      <c r="R70" s="8" t="inlineStr"/>
-      <c r="S70" s="8" t="inlineStr"/>
-      <c r="T70" s="8" t="inlineStr"/>
-      <c r="U70" s="8" t="inlineStr">
-        <is>
-          <t>6796.50</t>
-        </is>
-      </c>
-      <c r="V70" s="8" t="inlineStr"/>
-      <c r="W70" s="9" t="n">
-        <v>6662.25</v>
-      </c>
-      <c r="X70" s="9" t="n">
-        <v>832.625</v>
-      </c>
-      <c r="Y70" s="11" t="n">
-        <v>0.779976580796253</v>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Kangaroo
+Random: 52.0
+Human: 3035.0</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4208</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr"/>
+      <c r="Q70" s="4" t="inlineStr"/>
+      <c r="R70" s="4" t="inlineStr"/>
+      <c r="S70" s="4" t="inlineStr"/>
+      <c r="T70" s="4" t="inlineStr"/>
+      <c r="U70" s="4" t="inlineStr"/>
+      <c r="V70" s="4" t="inlineStr"/>
+      <c r="W70" s="5" t="inlineStr"/>
+      <c r="X70" s="6" t="n">
+        <v>-2778</v>
+      </c>
+      <c r="Y70" s="7" t="n">
+        <v>-0.9312772376801878</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>KungFuMaster
-Random: 258.5
-Human: 22736.3</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 26182</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr"/>
-      <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
-      <c r="K71" s="4" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="inlineStr"/>
-      <c r="N71" s="4" t="inlineStr"/>
-      <c r="O71" s="4" t="inlineStr"/>
-      <c r="P71" s="4" t="inlineStr"/>
-      <c r="Q71" s="4" t="inlineStr"/>
-      <c r="R71" s="4" t="inlineStr"/>
-      <c r="S71" s="4" t="inlineStr"/>
-      <c r="T71" s="4" t="inlineStr"/>
-      <c r="U71" s="4" t="inlineStr"/>
-      <c r="V71" s="4" t="inlineStr"/>
-      <c r="W71" s="5" t="inlineStr"/>
-      <c r="X71" s="6" t="n">
-        <v>-1044.5</v>
-      </c>
-      <c r="Y71" s="7" t="n">
-        <v>-0.04646807071866464</v>
-      </c>
+      <c r="A71" s="1" t="n"/>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr"/>
+      <c r="D71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>1770.00</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr"/>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>1470.00</t>
+        </is>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>1730.00</t>
+        </is>
+      </c>
+      <c r="M71" s="8" t="inlineStr"/>
+      <c r="N71" s="8" t="inlineStr"/>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>1550.00</t>
+        </is>
+      </c>
+      <c r="P71" s="8" t="inlineStr">
+        <is>
+          <t>930.00</t>
+        </is>
+      </c>
+      <c r="Q71" s="8" t="inlineStr"/>
+      <c r="R71" s="8" t="inlineStr"/>
+      <c r="S71" s="8" t="inlineStr"/>
+      <c r="T71" s="8" t="inlineStr"/>
+      <c r="U71" s="8" t="inlineStr"/>
+      <c r="V71" s="8" t="inlineStr"/>
+      <c r="W71" s="9" t="n">
+        <v>1430</v>
+      </c>
+      <c r="X71" s="10" t="inlineStr"/>
+      <c r="Y71" s="11" t="inlineStr"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr"/>
       <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>26460.00</t>
-        </is>
-      </c>
+      <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr"/>
       <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="8" t="inlineStr"/>
@@ -4286,27 +4187,29 @@
       <c r="J72" s="8" t="inlineStr"/>
       <c r="K72" s="8" t="inlineStr">
         <is>
-          <t>23815.00</t>
-        </is>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
-        <is>
-          <t>20895.00</t>
-        </is>
-      </c>
+          <t>1310.00</t>
+        </is>
+      </c>
+      <c r="L72" s="8" t="inlineStr"/>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
-      <c r="O72" s="8" t="inlineStr"/>
-      <c r="P72" s="8" t="inlineStr"/>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="P72" s="8" t="inlineStr">
+        <is>
+          <t>1030.00</t>
+        </is>
+      </c>
       <c r="Q72" s="8" t="inlineStr"/>
       <c r="R72" s="8" t="inlineStr"/>
       <c r="S72" s="8" t="inlineStr"/>
       <c r="T72" s="8" t="inlineStr"/>
       <c r="U72" s="8" t="inlineStr"/>
       <c r="V72" s="8" t="inlineStr"/>
-      <c r="W72" s="9" t="n">
-        <v>25137.5</v>
-      </c>
+      <c r="W72" s="9" t="inlineStr"/>
       <c r="X72" s="10" t="inlineStr"/>
       <c r="Y72" s="11" t="inlineStr"/>
     </row>
@@ -4321,7 +4224,7 @@
       <c r="D73" s="8" t="inlineStr"/>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>30110.00</t>
+          <t>1760.00</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr"/>
@@ -4331,14 +4234,22 @@
       <c r="J73" s="8" t="inlineStr"/>
       <c r="K73" s="8" t="inlineStr">
         <is>
-          <t>20245.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="L73" s="8" t="inlineStr"/>
       <c r="M73" s="8" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
-      <c r="O73" s="8" t="inlineStr"/>
-      <c r="P73" s="8" t="inlineStr"/>
+      <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>1670.00</t>
+        </is>
+      </c>
+      <c r="P73" s="8" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
       <c r="Q73" s="8" t="inlineStr"/>
       <c r="R73" s="8" t="inlineStr"/>
       <c r="S73" s="8" t="inlineStr"/>
@@ -4346,26 +4257,26 @@
       <c r="U73" s="8" t="inlineStr"/>
       <c r="V73" s="8" t="inlineStr"/>
       <c r="W73" s="9" t="n">
-        <v>25177.5</v>
+        <v>1445</v>
       </c>
       <c r="X73" s="9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="Y73" s="11" t="n">
-        <v>0.001779533584247569</v>
+        <v>0.005028494803888703</v>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MsPacman
-Random: 307.3
-Human: 6951.6</t>
+          <t>Krull
+Random: 1598.0
+Human: 2665.5</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 2673</t>
+          <t>STORM (논문): 8413</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -4390,10 +4301,10 @@
       <c r="V74" s="4" t="inlineStr"/>
       <c r="W74" s="5" t="inlineStr"/>
       <c r="X74" s="6" t="n">
-        <v>-602</v>
+        <v>-2583.375</v>
       </c>
       <c r="Y74" s="7" t="n">
-        <v>-0.09060397634062278</v>
+        <v>-2.420023419203747</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
@@ -4403,44 +4314,60 @@
           <t>Retrieval 미사용</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>1807.50</t>
-        </is>
-      </c>
+      <c r="C75" s="8" t="inlineStr"/>
       <c r="D75" s="8" t="inlineStr"/>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>2007.00</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr"/>
+          <t>6202.00</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>5689.00</t>
+        </is>
+      </c>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>6107.50</t>
+        </is>
+      </c>
       <c r="J75" s="8" t="inlineStr"/>
-      <c r="K75" s="8" t="inlineStr">
-        <is>
-          <t>2388.00</t>
-        </is>
-      </c>
-      <c r="L75" s="8" t="inlineStr"/>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>4708.50</t>
+        </is>
+      </c>
+      <c r="L75" s="13" t="inlineStr">
+        <is>
+          <t>5913.50</t>
+        </is>
+      </c>
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr"/>
       <c r="O75" s="8" t="inlineStr">
         <is>
-          <t>1754.00</t>
+          <t>5228.50</t>
         </is>
       </c>
       <c r="P75" s="8" t="inlineStr"/>
-      <c r="Q75" s="8" t="inlineStr"/>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>5599.00</t>
+        </is>
+      </c>
       <c r="R75" s="8" t="inlineStr"/>
       <c r="S75" s="8" t="inlineStr"/>
       <c r="T75" s="8" t="inlineStr"/>
-      <c r="U75" s="8" t="inlineStr"/>
+      <c r="U75" s="8" t="inlineStr">
+        <is>
+          <t>6289.00</t>
+        </is>
+      </c>
       <c r="V75" s="8" t="inlineStr"/>
       <c r="W75" s="9" t="n">
-        <v>2071</v>
+        <v>5829.625</v>
       </c>
       <c r="X75" s="10" t="inlineStr"/>
       <c r="Y75" s="11" t="inlineStr"/>
@@ -4449,7 +4376,7 @@
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr"/>
@@ -4460,155 +4387,165 @@
       <c r="H76" s="8" t="inlineStr"/>
       <c r="I76" s="8" t="inlineStr"/>
       <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr">
-        <is>
-          <t>2250.00</t>
-        </is>
-      </c>
-      <c r="L76" s="8" t="inlineStr"/>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>4851.00</t>
+        </is>
+      </c>
+      <c r="L76" s="13" t="inlineStr">
+        <is>
+          <t>6044.00</t>
+        </is>
+      </c>
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr"/>
-      <c r="O76" s="8" t="inlineStr">
-        <is>
-          <t>1886.50</t>
-        </is>
-      </c>
+      <c r="O76" s="8" t="inlineStr"/>
       <c r="P76" s="8" t="inlineStr"/>
       <c r="Q76" s="8" t="inlineStr"/>
       <c r="R76" s="8" t="inlineStr"/>
       <c r="S76" s="8" t="inlineStr"/>
       <c r="T76" s="8" t="inlineStr"/>
-      <c r="U76" s="8" t="inlineStr"/>
+      <c r="U76" s="8" t="inlineStr">
+        <is>
+          <t>6587.00</t>
+        </is>
+      </c>
       <c r="V76" s="8" t="inlineStr"/>
-      <c r="W76" s="9" t="n">
-        <v>2068.25</v>
-      </c>
-      <c r="X76" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y76" s="11" t="n">
-        <v>-0.0004138885962403865</v>
-      </c>
+      <c r="W76" s="9" t="inlineStr"/>
+      <c r="X76" s="10" t="inlineStr"/>
+      <c r="Y76" s="11" t="inlineStr"/>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Pong
-Random: -20.7
-Human: 14.6</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr"/>
-      <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="4" t="inlineStr"/>
-      <c r="J77" s="4" t="inlineStr"/>
-      <c r="K77" s="4" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr"/>
-      <c r="M77" s="4" t="inlineStr"/>
-      <c r="N77" s="4" t="inlineStr"/>
-      <c r="O77" s="4" t="inlineStr"/>
-      <c r="P77" s="4" t="inlineStr"/>
-      <c r="Q77" s="4" t="inlineStr"/>
-      <c r="R77" s="4" t="inlineStr"/>
-      <c r="S77" s="4" t="inlineStr"/>
-      <c r="T77" s="4" t="inlineStr"/>
-      <c r="U77" s="4" t="inlineStr"/>
-      <c r="V77" s="4" t="inlineStr"/>
-      <c r="W77" s="5" t="inlineStr"/>
-      <c r="X77" s="6" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="Y77" s="7" t="n">
-        <v>-0.1529745042492918</v>
+      <c r="A77" s="1" t="n"/>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr"/>
+      <c r="D77" s="8" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>6576.50</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr"/>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr"/>
+      <c r="J77" s="8" t="inlineStr"/>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>5279.50</t>
+        </is>
+      </c>
+      <c r="L77" s="13" t="inlineStr">
+        <is>
+          <t>5889.50</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="inlineStr"/>
+      <c r="N77" s="8" t="inlineStr"/>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>6447.50</t>
+        </is>
+      </c>
+      <c r="P77" s="8" t="inlineStr"/>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
+          <t>6828.50</t>
+        </is>
+      </c>
+      <c r="R77" s="8" t="inlineStr"/>
+      <c r="S77" s="8" t="inlineStr"/>
+      <c r="T77" s="8" t="inlineStr"/>
+      <c r="U77" s="8" t="inlineStr">
+        <is>
+          <t>6796.50</t>
+        </is>
+      </c>
+      <c r="V77" s="8" t="inlineStr"/>
+      <c r="W77" s="9" t="n">
+        <v>6662.25</v>
+      </c>
+      <c r="X77" s="9" t="n">
+        <v>832.625</v>
+      </c>
+      <c r="Y77" s="11" t="n">
+        <v>0.779976580796253</v>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="1" t="n"/>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr"/>
-      <c r="D78" s="8" t="inlineStr"/>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="8" t="inlineStr"/>
-      <c r="I78" s="8" t="inlineStr"/>
-      <c r="J78" s="8" t="inlineStr"/>
-      <c r="K78" s="8" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
-      <c r="M78" s="8" t="inlineStr"/>
-      <c r="N78" s="8" t="inlineStr"/>
-      <c r="O78" s="8" t="inlineStr"/>
-      <c r="P78" s="8" t="inlineStr"/>
-      <c r="Q78" s="8" t="inlineStr"/>
-      <c r="R78" s="8" t="inlineStr"/>
-      <c r="S78" s="8" t="inlineStr"/>
-      <c r="T78" s="8" t="inlineStr"/>
-      <c r="U78" s="8" t="inlineStr"/>
-      <c r="V78" s="8" t="inlineStr"/>
-      <c r="W78" s="9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="X78" s="10" t="inlineStr"/>
-      <c r="Y78" s="11" t="inlineStr"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>KungFuMaster
+Random: 258.5
+Human: 22736.3</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 26182</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr"/>
+      <c r="J78" s="4" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr"/>
+      <c r="M78" s="4" t="inlineStr"/>
+      <c r="N78" s="4" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr"/>
+      <c r="P78" s="4" t="inlineStr"/>
+      <c r="Q78" s="4" t="inlineStr"/>
+      <c r="R78" s="4" t="inlineStr"/>
+      <c r="S78" s="4" t="inlineStr"/>
+      <c r="T78" s="4" t="inlineStr"/>
+      <c r="U78" s="4" t="inlineStr"/>
+      <c r="V78" s="4" t="inlineStr"/>
+      <c r="W78" s="5" t="inlineStr"/>
+      <c r="X78" s="6" t="n">
+        <v>-1044.5</v>
+      </c>
+      <c r="Y78" s="7" t="n">
+        <v>-0.04646807071866464</v>
+      </c>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr"/>
       <c r="D79" s="8" t="inlineStr"/>
-      <c r="E79" s="8" t="inlineStr"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>8.20</t>
-        </is>
-      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>26460.00</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr"/>
       <c r="G79" s="8" t="inlineStr"/>
       <c r="H79" s="8" t="inlineStr"/>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
+      <c r="I79" s="8" t="inlineStr"/>
       <c r="J79" s="8" t="inlineStr"/>
       <c r="K79" s="8" t="inlineStr">
         <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="L79" s="8" t="inlineStr"/>
+          <t>23815.00</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>20895.00</t>
+        </is>
+      </c>
       <c r="M79" s="8" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr"/>
       <c r="O79" s="8" t="inlineStr"/>
@@ -4620,123 +4557,115 @@
       <c r="U79" s="8" t="inlineStr"/>
       <c r="V79" s="8" t="inlineStr"/>
       <c r="W79" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="X79" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y79" s="11" t="n">
-        <v>0.09631728045325781</v>
-      </c>
+        <v>25137.5</v>
+      </c>
+      <c r="X79" s="10" t="inlineStr"/>
+      <c r="Y79" s="11" t="inlineStr"/>
     </row>
     <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>PrivateEye
-Random: 24.9
-Human: 69571.3</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7781</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
-      <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr"/>
-      <c r="K80" s="4" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr"/>
-      <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr"/>
-      <c r="O80" s="4" t="inlineStr"/>
-      <c r="P80" s="4" t="inlineStr"/>
-      <c r="Q80" s="4" t="inlineStr"/>
-      <c r="R80" s="4" t="inlineStr"/>
-      <c r="S80" s="4" t="inlineStr"/>
-      <c r="T80" s="4" t="inlineStr"/>
-      <c r="U80" s="4" t="inlineStr"/>
-      <c r="V80" s="4" t="inlineStr"/>
-      <c r="W80" s="5" t="inlineStr"/>
-      <c r="X80" s="6" t="n">
-        <v>-6778.35</v>
-      </c>
-      <c r="Y80" s="7" t="n">
-        <v>-0.09746514557187719</v>
+      <c r="A80" s="1" t="n"/>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr"/>
+      <c r="D80" s="8" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>30110.00</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr"/>
+      <c r="J80" s="8" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>20245.00</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="inlineStr"/>
+      <c r="M80" s="8" t="inlineStr"/>
+      <c r="N80" s="8" t="inlineStr"/>
+      <c r="O80" s="8" t="inlineStr"/>
+      <c r="P80" s="8" t="inlineStr"/>
+      <c r="Q80" s="8" t="inlineStr"/>
+      <c r="R80" s="8" t="inlineStr"/>
+      <c r="S80" s="8" t="inlineStr"/>
+      <c r="T80" s="8" t="inlineStr"/>
+      <c r="U80" s="8" t="inlineStr"/>
+      <c r="V80" s="8" t="inlineStr"/>
+      <c r="W80" s="9" t="n">
+        <v>25177.5</v>
+      </c>
+      <c r="X80" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y80" s="11" t="n">
+        <v>0.001779533584247569</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="1" t="n"/>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>75.30</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr"/>
-      <c r="F81" s="8" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr"/>
-      <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr">
-        <is>
-          <t>199.35</t>
-        </is>
-      </c>
-      <c r="L81" s="8" t="inlineStr"/>
-      <c r="M81" s="8" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
-      <c r="O81" s="13" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="P81" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q81" s="8" t="inlineStr">
-        <is>
-          <t>3551.75</t>
-        </is>
-      </c>
-      <c r="R81" s="8" t="inlineStr"/>
-      <c r="S81" s="8" t="inlineStr"/>
-      <c r="T81" s="8" t="inlineStr"/>
-      <c r="U81" s="8" t="inlineStr">
-        <is>
-          <t>159.50</t>
-        </is>
-      </c>
-      <c r="V81" s="8" t="inlineStr"/>
-      <c r="W81" s="9" t="n">
-        <v>1002.65</v>
-      </c>
-      <c r="X81" s="10" t="inlineStr"/>
-      <c r="Y81" s="11" t="inlineStr"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>MsPacman
+Random: 307.3
+Human: 6951.6</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 2673</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
+      <c r="D81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr"/>
+      <c r="L81" s="4" t="inlineStr"/>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="inlineStr"/>
+      <c r="O81" s="4" t="inlineStr"/>
+      <c r="P81" s="4" t="inlineStr"/>
+      <c r="Q81" s="4" t="inlineStr"/>
+      <c r="R81" s="4" t="inlineStr"/>
+      <c r="S81" s="4" t="inlineStr"/>
+      <c r="T81" s="4" t="inlineStr"/>
+      <c r="U81" s="4" t="inlineStr"/>
+      <c r="V81" s="4" t="inlineStr"/>
+      <c r="W81" s="5" t="inlineStr"/>
+      <c r="X81" s="6" t="n">
+        <v>-602</v>
+      </c>
+      <c r="Y81" s="7" t="n">
+        <v>-0.09060397634062278</v>
+      </c>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>1807.50</t>
+        </is>
+      </c>
       <c r="D82" s="8" t="inlineStr"/>
-      <c r="E82" s="8" t="inlineStr"/>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>2007.00</t>
+        </is>
+      </c>
       <c r="F82" s="8" t="inlineStr"/>
       <c r="G82" s="8" t="inlineStr"/>
       <c r="H82" s="8" t="inlineStr"/>
@@ -4744,176 +4673,152 @@
       <c r="J82" s="8" t="inlineStr"/>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>191.95</t>
+          <t>2388.00</t>
         </is>
       </c>
       <c r="L82" s="8" t="inlineStr"/>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
-      <c r="O82" s="13" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="P82" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q82" s="8" t="inlineStr">
-        <is>
-          <t>166.80</t>
-        </is>
-      </c>
+      <c r="O82" s="8" t="inlineStr">
+        <is>
+          <t>1754.00</t>
+        </is>
+      </c>
+      <c r="P82" s="8" t="inlineStr"/>
+      <c r="Q82" s="8" t="inlineStr"/>
       <c r="R82" s="8" t="inlineStr"/>
       <c r="S82" s="8" t="inlineStr"/>
       <c r="T82" s="8" t="inlineStr"/>
-      <c r="U82" s="8" t="inlineStr">
-        <is>
-          <t>153.20</t>
-        </is>
-      </c>
+      <c r="U82" s="8" t="inlineStr"/>
       <c r="V82" s="8" t="inlineStr"/>
       <c r="W82" s="9" t="n">
-        <v>152.9875</v>
-      </c>
-      <c r="X82" s="9" t="n">
-        <v>849.6624999999999</v>
-      </c>
-      <c r="Y82" s="11" t="n">
-        <v>-0.01221720319096315</v>
-      </c>
+        <v>2071</v>
+      </c>
+      <c r="X82" s="10" t="inlineStr"/>
+      <c r="Y82" s="11" t="inlineStr"/>
     </row>
     <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Qbert
-Random: 163.9
-Human: 13455.0</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4522</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr"/>
-      <c r="D83" s="4" t="inlineStr"/>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr"/>
-      <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
-      <c r="K83" s="4" t="inlineStr"/>
-      <c r="L83" s="4" t="inlineStr"/>
-      <c r="M83" s="4" t="inlineStr"/>
-      <c r="N83" s="4" t="inlineStr"/>
-      <c r="O83" s="4" t="inlineStr"/>
-      <c r="P83" s="4" t="inlineStr"/>
-      <c r="Q83" s="4" t="inlineStr"/>
-      <c r="R83" s="4" t="inlineStr"/>
-      <c r="S83" s="4" t="inlineStr"/>
-      <c r="T83" s="4" t="inlineStr"/>
-      <c r="U83" s="4" t="inlineStr"/>
-      <c r="V83" s="4" t="inlineStr"/>
-      <c r="W83" s="5" t="inlineStr"/>
-      <c r="X83" s="6" t="n">
-        <v>-1662.9375</v>
-      </c>
-      <c r="Y83" s="7" t="n">
-        <v>-0.1251166193919239</v>
+      <c r="A83" s="1" t="n"/>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr"/>
+      <c r="D83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr"/>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr"/>
+      <c r="J83" s="8" t="inlineStr"/>
+      <c r="K83" s="8" t="inlineStr">
+        <is>
+          <t>2250.00</t>
+        </is>
+      </c>
+      <c r="L83" s="8" t="inlineStr"/>
+      <c r="M83" s="8" t="inlineStr"/>
+      <c r="N83" s="8" t="inlineStr"/>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>1886.50</t>
+        </is>
+      </c>
+      <c r="P83" s="8" t="inlineStr"/>
+      <c r="Q83" s="8" t="inlineStr"/>
+      <c r="R83" s="8" t="inlineStr"/>
+      <c r="S83" s="8" t="inlineStr"/>
+      <c r="T83" s="8" t="inlineStr"/>
+      <c r="U83" s="8" t="inlineStr"/>
+      <c r="V83" s="8" t="inlineStr"/>
+      <c r="W83" s="9" t="n">
+        <v>2068.25</v>
+      </c>
+      <c r="X83" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y83" s="11" t="n">
+        <v>-0.0004138885962403865</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="1" t="n"/>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr"/>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
-      <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr">
-        <is>
-          <t>3193.75</t>
-        </is>
-      </c>
-      <c r="L84" s="8" t="inlineStr"/>
-      <c r="M84" s="8" t="inlineStr"/>
-      <c r="N84" s="8" t="inlineStr"/>
-      <c r="O84" s="8" t="inlineStr">
-        <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="P84" s="8" t="inlineStr"/>
-      <c r="Q84" s="8" t="inlineStr"/>
-      <c r="R84" s="8" t="inlineStr"/>
-      <c r="S84" s="8" t="inlineStr"/>
-      <c r="T84" s="8" t="inlineStr"/>
-      <c r="U84" s="8" t="inlineStr"/>
-      <c r="V84" s="8" t="inlineStr"/>
-      <c r="W84" s="9" t="n">
-        <v>2859.0625</v>
-      </c>
-      <c r="X84" s="10" t="inlineStr"/>
-      <c r="Y84" s="11" t="inlineStr"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Pong
+Random: -20.7
+Human: 14.6</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr"/>
+      <c r="N84" s="4" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr"/>
+      <c r="P84" s="4" t="inlineStr"/>
+      <c r="Q84" s="4" t="inlineStr"/>
+      <c r="R84" s="4" t="inlineStr"/>
+      <c r="S84" s="4" t="inlineStr"/>
+      <c r="T84" s="4" t="inlineStr"/>
+      <c r="U84" s="4" t="inlineStr"/>
+      <c r="V84" s="4" t="inlineStr"/>
+      <c r="W84" s="5" t="inlineStr"/>
+      <c r="X84" s="6" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="Y84" s="7" t="n">
+        <v>-0.1529745042492918</v>
+      </c>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>2818.75</t>
-        </is>
-      </c>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr"/>
       <c r="D85" s="8" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>1918.75</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr"/>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="inlineStr"/>
       <c r="H85" s="8" t="inlineStr"/>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>2553.75</t>
-        </is>
-      </c>
+      <c r="I85" s="8" t="inlineStr"/>
       <c r="J85" s="8" t="inlineStr"/>
-      <c r="K85" s="8" t="inlineStr"/>
-      <c r="L85" s="8" t="inlineStr"/>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>13.70</t>
+        </is>
+      </c>
       <c r="M85" s="8" t="inlineStr"/>
       <c r="N85" s="8" t="inlineStr"/>
-      <c r="O85" s="8" t="inlineStr">
-        <is>
-          <t>3782.50</t>
-        </is>
-      </c>
+      <c r="O85" s="8" t="inlineStr"/>
       <c r="P85" s="8" t="inlineStr"/>
       <c r="Q85" s="8" t="inlineStr"/>
       <c r="R85" s="8" t="inlineStr"/>
@@ -4921,7 +4826,9 @@
       <c r="T85" s="8" t="inlineStr"/>
       <c r="U85" s="8" t="inlineStr"/>
       <c r="V85" s="8" t="inlineStr"/>
-      <c r="W85" s="9" t="inlineStr"/>
+      <c r="W85" s="9" t="n">
+        <v>5.6</v>
+      </c>
       <c r="X85" s="10" t="inlineStr"/>
       <c r="Y85" s="11" t="inlineStr"/>
     </row>
@@ -4932,39 +4839,31 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>2702.50</t>
-        </is>
-      </c>
+      <c r="C86" s="8" t="inlineStr"/>
       <c r="D86" s="8" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>4056.25</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr"/>
+      <c r="E86" s="8" t="inlineStr"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>8.20</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="inlineStr"/>
       <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>2338.75</t>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>14.45</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr"/>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>2608.75</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="L86" s="8" t="inlineStr"/>
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr"/>
-      <c r="O86" s="8" t="inlineStr">
-        <is>
-          <t>2895.00</t>
-        </is>
-      </c>
+      <c r="O86" s="8" t="inlineStr"/>
       <c r="P86" s="8" t="inlineStr"/>
       <c r="Q86" s="8" t="inlineStr"/>
       <c r="R86" s="8" t="inlineStr"/>
@@ -4973,26 +4872,26 @@
       <c r="U86" s="8" t="inlineStr"/>
       <c r="V86" s="8" t="inlineStr"/>
       <c r="W86" s="9" t="n">
-        <v>3065.625</v>
+        <v>9</v>
       </c>
       <c r="X86" s="9" t="n">
-        <v>206.5625</v>
+        <v>3.4</v>
       </c>
       <c r="Y86" s="11" t="n">
-        <v>0.01554141493179646</v>
+        <v>0.09631728045325781</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RoadRunner
-Random: 11.5
-Human: 7845.0</t>
+          <t>PrivateEye
+Random: 24.9
+Human: 69571.3</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 17564</t>
+          <t>STORM (논문): 7781</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -5017,10 +4916,10 @@
       <c r="V87" s="4" t="inlineStr"/>
       <c r="W87" s="5" t="inlineStr"/>
       <c r="X87" s="6" t="n">
-        <v>-8627.75</v>
+        <v>-6778.35</v>
       </c>
       <c r="Y87" s="7" t="n">
-        <v>-1.101391459756175</v>
+        <v>-0.09746514557187719</v>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1">
@@ -5030,7 +4929,11 @@
           <t>Retrieval 미사용</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr"/>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>75.30</t>
+        </is>
+      </c>
       <c r="D88" s="8" t="inlineStr"/>
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" s="8" t="inlineStr"/>
@@ -5040,34 +4943,38 @@
       <c r="J88" s="8" t="inlineStr"/>
       <c r="K88" s="8" t="inlineStr">
         <is>
-          <t>8610.00</t>
+          <t>199.35</t>
         </is>
       </c>
       <c r="L88" s="8" t="inlineStr"/>
       <c r="M88" s="8" t="inlineStr"/>
       <c r="N88" s="8" t="inlineStr"/>
-      <c r="O88" s="8" t="inlineStr">
-        <is>
-          <t>7290.00</t>
+      <c r="O88" s="13" t="inlineStr">
+        <is>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P88" s="8" t="inlineStr">
         <is>
-          <t>9690.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>10155.00</t>
+          <t>3551.75</t>
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr"/>
       <c r="S88" s="8" t="inlineStr"/>
       <c r="T88" s="8" t="inlineStr"/>
-      <c r="U88" s="8" t="inlineStr"/>
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>159.50</t>
+        </is>
+      </c>
       <c r="V88" s="8" t="inlineStr"/>
       <c r="W88" s="9" t="n">
-        <v>8936.25</v>
+        <v>1002.65</v>
       </c>
       <c r="X88" s="10" t="inlineStr"/>
       <c r="Y88" s="11" t="inlineStr"/>
@@ -5076,7 +4983,7 @@
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr"/>
@@ -5087,158 +4994,176 @@
       <c r="H89" s="8" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr"/>
       <c r="J89" s="8" t="inlineStr"/>
-      <c r="K89" s="8" t="inlineStr"/>
+      <c r="K89" s="8" t="inlineStr">
+        <is>
+          <t>191.95</t>
+        </is>
+      </c>
       <c r="L89" s="8" t="inlineStr"/>
       <c r="M89" s="8" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr"/>
-      <c r="O89" s="8" t="inlineStr">
-        <is>
-          <t>8520.00</t>
+      <c r="O89" s="13" t="inlineStr">
+        <is>
+          <t>20.00</t>
         </is>
       </c>
       <c r="P89" s="8" t="inlineStr">
         <is>
-          <t>11830.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>16805.00</t>
+          <t>166.80</t>
         </is>
       </c>
       <c r="R89" s="8" t="inlineStr"/>
       <c r="S89" s="8" t="inlineStr"/>
       <c r="T89" s="8" t="inlineStr"/>
-      <c r="U89" s="8" t="inlineStr"/>
+      <c r="U89" s="8" t="inlineStr">
+        <is>
+          <t>153.20</t>
+        </is>
+      </c>
       <c r="V89" s="8" t="inlineStr"/>
-      <c r="W89" s="9" t="inlineStr"/>
-      <c r="X89" s="10" t="inlineStr"/>
-      <c r="Y89" s="11" t="inlineStr"/>
+      <c r="W89" s="9" t="n">
+        <v>152.9875</v>
+      </c>
+      <c r="X89" s="9" t="n">
+        <v>849.6624999999999</v>
+      </c>
+      <c r="Y89" s="11" t="n">
+        <v>-0.01221720319096315</v>
+      </c>
     </row>
     <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="1" t="n"/>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr"/>
-      <c r="D90" s="8" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr"/>
-      <c r="F90" s="8" t="inlineStr"/>
-      <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr"/>
-      <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr">
-        <is>
-          <t>8195.00</t>
-        </is>
-      </c>
-      <c r="L90" s="8" t="inlineStr"/>
-      <c r="M90" s="8" t="inlineStr"/>
-      <c r="N90" s="8" t="inlineStr"/>
-      <c r="O90" s="8" t="inlineStr">
-        <is>
-          <t>8325.00</t>
-        </is>
-      </c>
-      <c r="P90" s="8" t="inlineStr">
-        <is>
-          <t>12890.00</t>
-        </is>
-      </c>
-      <c r="Q90" s="8" t="inlineStr">
-        <is>
-          <t>16980.00</t>
-        </is>
-      </c>
-      <c r="R90" s="8" t="inlineStr"/>
-      <c r="S90" s="8" t="inlineStr"/>
-      <c r="T90" s="8" t="inlineStr"/>
-      <c r="U90" s="8" t="inlineStr"/>
-      <c r="V90" s="8" t="inlineStr"/>
-      <c r="W90" s="9" t="n">
-        <v>11597.5</v>
-      </c>
-      <c r="X90" s="9" t="n">
-        <v>2661.25</v>
-      </c>
-      <c r="Y90" s="11" t="n">
-        <v>0.3397268143230995</v>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Qbert
+Random: 163.9
+Human: 13455.0</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4522</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr"/>
+      <c r="N90" s="4" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr"/>
+      <c r="P90" s="4" t="inlineStr"/>
+      <c r="Q90" s="4" t="inlineStr"/>
+      <c r="R90" s="4" t="inlineStr"/>
+      <c r="S90" s="4" t="inlineStr"/>
+      <c r="T90" s="4" t="inlineStr"/>
+      <c r="U90" s="4" t="inlineStr"/>
+      <c r="V90" s="4" t="inlineStr"/>
+      <c r="W90" s="5" t="inlineStr"/>
+      <c r="X90" s="6" t="n">
+        <v>-1662.9375</v>
+      </c>
+      <c r="Y90" s="7" t="n">
+        <v>-0.1251166193919239</v>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Seaquest
-Random: 68.4
-Human: 42054.7</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 525</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="4" t="inlineStr"/>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr"/>
-      <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="4" t="inlineStr"/>
-      <c r="J91" s="4" t="inlineStr"/>
-      <c r="K91" s="4" t="inlineStr"/>
-      <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="4" t="inlineStr"/>
-      <c r="N91" s="4" t="inlineStr"/>
-      <c r="O91" s="4" t="inlineStr"/>
-      <c r="P91" s="4" t="inlineStr"/>
-      <c r="Q91" s="4" t="inlineStr"/>
-      <c r="R91" s="4" t="inlineStr"/>
-      <c r="S91" s="4" t="inlineStr"/>
-      <c r="T91" s="4" t="inlineStr"/>
-      <c r="U91" s="4" t="inlineStr"/>
-      <c r="V91" s="4" t="inlineStr"/>
-      <c r="W91" s="5" t="inlineStr"/>
-      <c r="X91" s="6" t="n">
-        <v>-69</v>
-      </c>
-      <c r="Y91" s="7" t="n">
-        <v>-0.001643393202068294</v>
-      </c>
+      <c r="A91" s="1" t="n"/>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>1771.25</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>3786.25</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>2940.00</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr"/>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>3193.75</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="inlineStr"/>
+      <c r="M91" s="8" t="inlineStr"/>
+      <c r="N91" s="8" t="inlineStr"/>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
+        </is>
+      </c>
+      <c r="P91" s="8" t="inlineStr"/>
+      <c r="Q91" s="8" t="inlineStr"/>
+      <c r="R91" s="8" t="inlineStr"/>
+      <c r="S91" s="8" t="inlineStr"/>
+      <c r="T91" s="8" t="inlineStr"/>
+      <c r="U91" s="8" t="inlineStr"/>
+      <c r="V91" s="8" t="inlineStr"/>
+      <c r="W91" s="9" t="n">
+        <v>2859.0625</v>
+      </c>
+      <c r="X91" s="10" t="inlineStr"/>
+      <c r="Y91" s="11" t="inlineStr"/>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>454.00</t>
+          <t>2818.75</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr"/>
-      <c r="E92" s="8" t="inlineStr"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>1918.75</t>
+        </is>
+      </c>
       <c r="F92" s="8" t="inlineStr"/>
       <c r="G92" s="8" t="inlineStr"/>
       <c r="H92" s="8" t="inlineStr"/>
-      <c r="I92" s="8" t="inlineStr"/>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>2553.75</t>
+        </is>
+      </c>
       <c r="J92" s="8" t="inlineStr"/>
-      <c r="K92" s="8" t="inlineStr">
-        <is>
-          <t>494.00</t>
-        </is>
-      </c>
+      <c r="K92" s="8" t="inlineStr"/>
       <c r="L92" s="8" t="inlineStr"/>
       <c r="M92" s="8" t="inlineStr"/>
       <c r="N92" s="8" t="inlineStr"/>
       <c r="O92" s="8" t="inlineStr">
         <is>
-          <t>418.00</t>
+          <t>3782.50</t>
         </is>
       </c>
       <c r="P92" s="8" t="inlineStr"/>
@@ -5246,15 +5171,9 @@
       <c r="R92" s="8" t="inlineStr"/>
       <c r="S92" s="8" t="inlineStr"/>
       <c r="T92" s="8" t="inlineStr"/>
-      <c r="U92" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
+      <c r="U92" s="8" t="inlineStr"/>
       <c r="V92" s="8" t="inlineStr"/>
-      <c r="W92" s="9" t="n">
-        <v>456</v>
-      </c>
+      <c r="W92" s="9" t="inlineStr"/>
       <c r="X92" s="10" t="inlineStr"/>
       <c r="Y92" s="11" t="inlineStr"/>
     </row>
@@ -5262,24 +5181,40 @@
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>2702.50</t>
+        </is>
+      </c>
       <c r="D93" s="8" t="inlineStr"/>
-      <c r="E93" s="8" t="inlineStr"/>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>4056.25</t>
+        </is>
+      </c>
       <c r="F93" s="8" t="inlineStr"/>
       <c r="G93" s="8" t="inlineStr"/>
       <c r="H93" s="8" t="inlineStr"/>
-      <c r="I93" s="8" t="inlineStr"/>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>2338.75</t>
+        </is>
+      </c>
       <c r="J93" s="8" t="inlineStr"/>
-      <c r="K93" s="8" t="inlineStr"/>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>2608.75</t>
+        </is>
+      </c>
       <c r="L93" s="8" t="inlineStr"/>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
       <c r="O93" s="8" t="inlineStr">
         <is>
-          <t>476.00</t>
+          <t>2895.00</t>
         </is>
       </c>
       <c r="P93" s="8" t="inlineStr"/>
@@ -5287,128 +5222,122 @@
       <c r="R93" s="8" t="inlineStr"/>
       <c r="S93" s="8" t="inlineStr"/>
       <c r="T93" s="8" t="inlineStr"/>
-      <c r="U93" s="8" t="inlineStr">
-        <is>
-          <t>557.00</t>
-        </is>
-      </c>
+      <c r="U93" s="8" t="inlineStr"/>
       <c r="V93" s="8" t="inlineStr"/>
-      <c r="W93" s="9" t="inlineStr"/>
-      <c r="X93" s="10" t="inlineStr"/>
-      <c r="Y93" s="11" t="inlineStr"/>
+      <c r="W93" s="9" t="n">
+        <v>3065.625</v>
+      </c>
+      <c r="X93" s="9" t="n">
+        <v>206.5625</v>
+      </c>
+      <c r="Y93" s="11" t="n">
+        <v>0.01554141493179646</v>
+      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="1" t="n"/>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr"/>
-      <c r="D94" s="8" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr"/>
-      <c r="F94" s="8" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr">
-        <is>
-          <t>521.00</t>
-        </is>
-      </c>
-      <c r="L94" s="8" t="inlineStr"/>
-      <c r="M94" s="8" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
-      <c r="O94" s="8" t="inlineStr">
-        <is>
-          <t>450.00</t>
-        </is>
-      </c>
-      <c r="P94" s="8" t="inlineStr"/>
-      <c r="Q94" s="8" t="inlineStr"/>
-      <c r="R94" s="8" t="inlineStr"/>
-      <c r="S94" s="8" t="inlineStr"/>
-      <c r="T94" s="8" t="inlineStr"/>
-      <c r="U94" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING, 545.00</t>
-        </is>
-      </c>
-      <c r="V94" s="8" t="inlineStr"/>
-      <c r="W94" s="9" t="n">
-        <v>485.5</v>
-      </c>
-      <c r="X94" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="Y94" s="11" t="n">
-        <v>0.0007026101371161546</v>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>RoadRunner
+Random: 11.5
+Human: 7845.0</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 17564</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
+      <c r="D94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr"/>
+      <c r="P94" s="4" t="inlineStr"/>
+      <c r="Q94" s="4" t="inlineStr"/>
+      <c r="R94" s="4" t="inlineStr"/>
+      <c r="S94" s="4" t="inlineStr"/>
+      <c r="T94" s="4" t="inlineStr"/>
+      <c r="U94" s="4" t="inlineStr"/>
+      <c r="V94" s="4" t="inlineStr"/>
+      <c r="W94" s="5" t="inlineStr"/>
+      <c r="X94" s="6" t="n">
+        <v>-8627.75</v>
+      </c>
+      <c r="Y94" s="7" t="n">
+        <v>-1.101391459756175</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>UpNDown
-Random: 533.4
-Human: 11693.2</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7985</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr"/>
-      <c r="D95" s="4" t="inlineStr"/>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr"/>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
-      <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="inlineStr"/>
-      <c r="N95" s="4" t="inlineStr"/>
-      <c r="O95" s="4" t="inlineStr"/>
-      <c r="P95" s="4" t="inlineStr"/>
-      <c r="Q95" s="4" t="inlineStr"/>
-      <c r="R95" s="4" t="inlineStr"/>
-      <c r="S95" s="4" t="inlineStr"/>
-      <c r="T95" s="4" t="inlineStr"/>
-      <c r="U95" s="4" t="inlineStr"/>
-      <c r="V95" s="4" t="inlineStr"/>
-      <c r="W95" s="5" t="inlineStr"/>
-      <c r="X95" s="6" t="n">
-        <v>-2963</v>
-      </c>
-      <c r="Y95" s="7" t="n">
-        <v>-0.2655065502966003</v>
-      </c>
+      <c r="A95" s="1" t="n"/>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr"/>
+      <c r="D95" s="8" t="inlineStr"/>
+      <c r="E95" s="8" t="inlineStr"/>
+      <c r="F95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>8610.00</t>
+        </is>
+      </c>
+      <c r="L95" s="8" t="inlineStr"/>
+      <c r="M95" s="8" t="inlineStr"/>
+      <c r="N95" s="8" t="inlineStr"/>
+      <c r="O95" s="8" t="inlineStr">
+        <is>
+          <t>7290.00</t>
+        </is>
+      </c>
+      <c r="P95" s="8" t="inlineStr">
+        <is>
+          <t>9690.00</t>
+        </is>
+      </c>
+      <c r="Q95" s="8" t="inlineStr">
+        <is>
+          <t>10155.00</t>
+        </is>
+      </c>
+      <c r="R95" s="8" t="inlineStr"/>
+      <c r="S95" s="8" t="inlineStr"/>
+      <c r="T95" s="8" t="inlineStr"/>
+      <c r="U95" s="8" t="inlineStr"/>
+      <c r="V95" s="8" t="inlineStr"/>
+      <c r="W95" s="9" t="n">
+        <v>8936.25</v>
+      </c>
+      <c r="X95" s="10" t="inlineStr"/>
+      <c r="Y95" s="11" t="inlineStr"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr">
-        <is>
-          <t>9044.00</t>
-        </is>
-      </c>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr"/>
       <c r="D96" s="8" t="inlineStr"/>
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr"/>
       <c r="G96" s="8" t="inlineStr"/>
       <c r="H96" s="8" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>5849.00</t>
-        </is>
-      </c>
+      <c r="I96" s="8" t="inlineStr"/>
       <c r="J96" s="8" t="inlineStr"/>
       <c r="K96" s="8" t="inlineStr"/>
       <c r="L96" s="8" t="inlineStr"/>
@@ -5416,17 +5345,17 @@
       <c r="N96" s="8" t="inlineStr"/>
       <c r="O96" s="8" t="inlineStr">
         <is>
-          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
+          <t>8520.00</t>
         </is>
       </c>
       <c r="P96" s="8" t="inlineStr">
         <is>
-          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
+          <t>11830.00</t>
         </is>
       </c>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
+          <t>16805.00</t>
         </is>
       </c>
       <c r="R96" s="8" t="inlineStr"/>
@@ -5434,9 +5363,7 @@
       <c r="T96" s="8" t="inlineStr"/>
       <c r="U96" s="8" t="inlineStr"/>
       <c r="V96" s="8" t="inlineStr"/>
-      <c r="W96" s="9" t="n">
-        <v>5022</v>
-      </c>
+      <c r="W96" s="9" t="inlineStr"/>
       <c r="X96" s="10" t="inlineStr"/>
       <c r="Y96" s="11" t="inlineStr"/>
     </row>
@@ -5444,7 +5371,7 @@
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
@@ -5455,23 +5382,27 @@
       <c r="H97" s="8" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr"/>
       <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>8195.00</t>
+        </is>
+      </c>
       <c r="L97" s="8" t="inlineStr"/>
       <c r="M97" s="8" t="inlineStr"/>
       <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="8" t="inlineStr">
         <is>
-          <t>5670.00</t>
+          <t>8325.00</t>
         </is>
       </c>
       <c r="P97" s="8" t="inlineStr">
         <is>
-          <t>7178.00</t>
+          <t>12890.00</t>
         </is>
       </c>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>3066.00</t>
+          <t>16980.00</t>
         </is>
       </c>
       <c r="R97" s="8" t="inlineStr"/>
@@ -5479,87 +5410,478 @@
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
-      <c r="W97" s="9" t="inlineStr"/>
-      <c r="X97" s="10" t="inlineStr"/>
-      <c r="Y97" s="11" t="inlineStr"/>
+      <c r="W97" s="9" t="n">
+        <v>11597.5</v>
+      </c>
+      <c r="X97" s="9" t="n">
+        <v>2661.25</v>
+      </c>
+      <c r="Y97" s="11" t="n">
+        <v>0.3397268143230995</v>
+      </c>
     </row>
     <row r="98" ht="24" customHeight="1">
-      <c r="A98" s="1" t="n"/>
-      <c r="B98" s="1" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Seaquest
+Random: 68.4
+Human: 42054.7</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 525</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr"/>
+      <c r="D98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr"/>
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="inlineStr"/>
+      <c r="N98" s="4" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr"/>
+      <c r="P98" s="4" t="inlineStr"/>
+      <c r="Q98" s="4" t="inlineStr"/>
+      <c r="R98" s="4" t="inlineStr"/>
+      <c r="S98" s="4" t="inlineStr"/>
+      <c r="T98" s="4" t="inlineStr"/>
+      <c r="U98" s="4" t="inlineStr"/>
+      <c r="V98" s="4" t="inlineStr"/>
+      <c r="W98" s="5" t="inlineStr"/>
+      <c r="X98" s="6" t="n">
+        <v>-64.33333333333331</v>
+      </c>
+      <c r="Y98" s="7" t="n">
+        <v>-0.001532245835744834</v>
+      </c>
+    </row>
+    <row r="99" ht="24" customHeight="1">
+      <c r="A99" s="1" t="n"/>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>454.00</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr"/>
+      <c r="E99" s="8" t="inlineStr"/>
+      <c r="F99" s="8" t="inlineStr"/>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr"/>
+      <c r="J99" s="8" t="inlineStr"/>
+      <c r="K99" s="8" t="inlineStr">
+        <is>
+          <t>494.00</t>
+        </is>
+      </c>
+      <c r="L99" s="8" t="inlineStr"/>
+      <c r="M99" s="8" t="inlineStr"/>
+      <c r="N99" s="8" t="inlineStr"/>
+      <c r="O99" s="8" t="inlineStr">
+        <is>
+          <t>418.00</t>
+        </is>
+      </c>
+      <c r="P99" s="8" t="inlineStr"/>
+      <c r="Q99" s="8" t="inlineStr"/>
+      <c r="R99" s="8" t="inlineStr"/>
+      <c r="S99" s="8" t="inlineStr"/>
+      <c r="T99" s="8" t="inlineStr"/>
+      <c r="U99" s="8" t="inlineStr">
+        <is>
+          <t>470.00</t>
+        </is>
+      </c>
+      <c r="V99" s="8" t="inlineStr"/>
+      <c r="W99" s="9" t="n">
+        <v>460.6666666666667</v>
+      </c>
+      <c r="X99" s="10" t="inlineStr"/>
+      <c r="Y99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="1" t="n"/>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr"/>
+      <c r="D100" s="8" t="inlineStr"/>
+      <c r="E100" s="8" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr"/>
+      <c r="G100" s="8" t="inlineStr"/>
+      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr"/>
+      <c r="J100" s="8" t="inlineStr"/>
+      <c r="K100" s="8" t="inlineStr"/>
+      <c r="L100" s="8" t="inlineStr"/>
+      <c r="M100" s="8" t="inlineStr"/>
+      <c r="N100" s="8" t="inlineStr"/>
+      <c r="O100" s="8" t="inlineStr">
+        <is>
+          <t>476.00</t>
+        </is>
+      </c>
+      <c r="P100" s="8" t="inlineStr"/>
+      <c r="Q100" s="8" t="inlineStr"/>
+      <c r="R100" s="8" t="inlineStr"/>
+      <c r="S100" s="8" t="inlineStr"/>
+      <c r="T100" s="8" t="inlineStr"/>
+      <c r="U100" s="8" t="inlineStr">
+        <is>
+          <t>557.00</t>
+        </is>
+      </c>
+      <c r="V100" s="8" t="inlineStr"/>
+      <c r="W100" s="9" t="inlineStr"/>
+      <c r="X100" s="10" t="inlineStr"/>
+      <c r="Y100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101" ht="24" customHeight="1">
+      <c r="A101" s="1" t="n"/>
+      <c r="B101" s="1" t="inlineStr">
         <is>
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr"/>
-      <c r="D98" s="8" t="inlineStr"/>
-      <c r="E98" s="8" t="inlineStr"/>
-      <c r="F98" s="8" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr"/>
-      <c r="H98" s="8" t="inlineStr"/>
-      <c r="I98" s="8" t="inlineStr"/>
-      <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="8" t="inlineStr"/>
-      <c r="L98" s="8" t="inlineStr"/>
-      <c r="M98" s="8" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr"/>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr"/>
+      <c r="D101" s="8" t="inlineStr"/>
+      <c r="E101" s="8" t="inlineStr"/>
+      <c r="F101" s="8" t="inlineStr"/>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="inlineStr"/>
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>521.00</t>
+        </is>
+      </c>
+      <c r="L101" s="8" t="inlineStr"/>
+      <c r="M101" s="8" t="inlineStr"/>
+      <c r="N101" s="8" t="inlineStr"/>
+      <c r="O101" s="8" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
+      <c r="P101" s="8" t="inlineStr"/>
+      <c r="Q101" s="8" t="inlineStr"/>
+      <c r="R101" s="8" t="inlineStr"/>
+      <c r="S101" s="8" t="inlineStr"/>
+      <c r="T101" s="8" t="inlineStr"/>
+      <c r="U101" s="8" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
+      <c r="V101" s="8" t="inlineStr"/>
+      <c r="W101" s="9" t="n">
+        <v>505.3333333333333</v>
+      </c>
+      <c r="X101" s="9" t="n">
+        <v>44.66666666666663</v>
+      </c>
+      <c r="Y101" s="11" t="n">
+        <v>0.001063839077667397</v>
+      </c>
+    </row>
+    <row r="102" ht="24" customHeight="1">
+      <c r="A102" s="1" t="n"/>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr"/>
+      <c r="D102" s="8" t="inlineStr"/>
+      <c r="E102" s="8" t="inlineStr"/>
+      <c r="F102" s="8" t="inlineStr"/>
+      <c r="G102" s="8" t="inlineStr"/>
+      <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="8" t="inlineStr"/>
+      <c r="J102" s="8" t="inlineStr"/>
+      <c r="K102" s="8" t="inlineStr"/>
+      <c r="L102" s="8" t="inlineStr"/>
+      <c r="M102" s="8" t="inlineStr"/>
+      <c r="N102" s="8" t="inlineStr"/>
+      <c r="O102" s="8" t="inlineStr"/>
+      <c r="P102" s="8" t="inlineStr"/>
+      <c r="Q102" s="8" t="inlineStr"/>
+      <c r="R102" s="8" t="inlineStr"/>
+      <c r="S102" s="8" t="inlineStr"/>
+      <c r="T102" s="8" t="inlineStr"/>
+      <c r="U102" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="V102" s="8" t="inlineStr"/>
+      <c r="W102" s="9" t="inlineStr"/>
+      <c r="X102" s="10" t="inlineStr"/>
+      <c r="Y102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="1" t="n"/>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr"/>
+      <c r="D103" s="8" t="inlineStr"/>
+      <c r="E103" s="8" t="inlineStr"/>
+      <c r="F103" s="8" t="inlineStr"/>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="inlineStr"/>
+      <c r="J103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="inlineStr"/>
+      <c r="L103" s="8" t="inlineStr"/>
+      <c r="M103" s="8" t="inlineStr"/>
+      <c r="N103" s="8" t="inlineStr"/>
+      <c r="O103" s="8" t="inlineStr"/>
+      <c r="P103" s="8" t="inlineStr"/>
+      <c r="Q103" s="8" t="inlineStr"/>
+      <c r="R103" s="8" t="inlineStr"/>
+      <c r="S103" s="8" t="inlineStr"/>
+      <c r="T103" s="8" t="inlineStr"/>
+      <c r="U103" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="V103" s="8" t="inlineStr"/>
+      <c r="W103" s="9" t="inlineStr"/>
+      <c r="X103" s="10" t="inlineStr"/>
+      <c r="Y103" s="11" t="inlineStr"/>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>UpNDown
+Random: 533.4
+Human: 11693.2</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 7985</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr"/>
+      <c r="L104" s="4" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr"/>
+      <c r="P104" s="4" t="inlineStr"/>
+      <c r="Q104" s="4" t="inlineStr"/>
+      <c r="R104" s="4" t="inlineStr"/>
+      <c r="S104" s="4" t="inlineStr"/>
+      <c r="T104" s="4" t="inlineStr"/>
+      <c r="U104" s="4" t="inlineStr"/>
+      <c r="V104" s="4" t="inlineStr"/>
+      <c r="W104" s="5" t="inlineStr"/>
+      <c r="X104" s="6" t="n">
+        <v>-2963</v>
+      </c>
+      <c r="Y104" s="7" t="n">
+        <v>-0.2655065502966003</v>
+      </c>
+    </row>
+    <row r="105" ht="24" customHeight="1">
+      <c r="A105" s="1" t="n"/>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>9044.00</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr"/>
+      <c r="E105" s="8" t="inlineStr"/>
+      <c r="F105" s="8" t="inlineStr"/>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr"/>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>5849.00</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr"/>
+      <c r="L105" s="8" t="inlineStr"/>
+      <c r="M105" s="8" t="inlineStr"/>
+      <c r="N105" s="8" t="inlineStr"/>
+      <c r="O105" s="8" t="inlineStr">
+        <is>
+          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
+        </is>
+      </c>
+      <c r="P105" s="8" t="inlineStr">
+        <is>
+          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
+        </is>
+      </c>
+      <c r="Q105" s="8" t="inlineStr">
+        <is>
+          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
+        </is>
+      </c>
+      <c r="R105" s="8" t="inlineStr"/>
+      <c r="S105" s="8" t="inlineStr"/>
+      <c r="T105" s="8" t="inlineStr"/>
+      <c r="U105" s="8" t="inlineStr"/>
+      <c r="V105" s="8" t="inlineStr"/>
+      <c r="W105" s="9" t="n">
+        <v>5022</v>
+      </c>
+      <c r="X105" s="10" t="inlineStr"/>
+      <c r="Y105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="1" t="n"/>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr"/>
+      <c r="D106" s="8" t="inlineStr"/>
+      <c r="E106" s="8" t="inlineStr"/>
+      <c r="F106" s="8" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr"/>
+      <c r="H106" s="8" t="inlineStr"/>
+      <c r="I106" s="8" t="inlineStr"/>
+      <c r="J106" s="8" t="inlineStr"/>
+      <c r="K106" s="8" t="inlineStr"/>
+      <c r="L106" s="8" t="inlineStr"/>
+      <c r="M106" s="8" t="inlineStr"/>
+      <c r="N106" s="8" t="inlineStr"/>
+      <c r="O106" s="8" t="inlineStr">
+        <is>
+          <t>5670.00</t>
+        </is>
+      </c>
+      <c r="P106" s="8" t="inlineStr">
+        <is>
+          <t>7178.00</t>
+        </is>
+      </c>
+      <c r="Q106" s="8" t="inlineStr">
+        <is>
+          <t>3066.00</t>
+        </is>
+      </c>
+      <c r="R106" s="8" t="inlineStr"/>
+      <c r="S106" s="8" t="inlineStr"/>
+      <c r="T106" s="8" t="inlineStr"/>
+      <c r="U106" s="8" t="inlineStr"/>
+      <c r="V106" s="8" t="inlineStr"/>
+      <c r="W106" s="9" t="inlineStr"/>
+      <c r="X106" s="10" t="inlineStr"/>
+      <c r="Y106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="1" t="n"/>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr"/>
+      <c r="D107" s="8" t="inlineStr"/>
+      <c r="E107" s="8" t="inlineStr"/>
+      <c r="F107" s="8" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr"/>
+      <c r="J107" s="8" t="inlineStr"/>
+      <c r="K107" s="8" t="inlineStr"/>
+      <c r="L107" s="8" t="inlineStr"/>
+      <c r="M107" s="8" t="inlineStr"/>
+      <c r="N107" s="8" t="inlineStr"/>
+      <c r="O107" s="8" t="inlineStr">
         <is>
           <t>6043.00</t>
         </is>
       </c>
-      <c r="P98" s="8" t="inlineStr">
+      <c r="P107" s="8" t="inlineStr">
         <is>
           <t>6658.00</t>
         </is>
       </c>
-      <c r="Q98" s="8" t="inlineStr">
+      <c r="Q107" s="8" t="inlineStr">
         <is>
           <t>2974.50</t>
         </is>
       </c>
-      <c r="R98" s="8" t="inlineStr"/>
-      <c r="S98" s="8" t="inlineStr"/>
-      <c r="T98" s="8" t="inlineStr"/>
-      <c r="U98" s="8" t="inlineStr"/>
-      <c r="V98" s="8" t="inlineStr"/>
-      <c r="W98" s="9" t="n">
+      <c r="R107" s="8" t="inlineStr"/>
+      <c r="S107" s="8" t="inlineStr"/>
+      <c r="T107" s="8" t="inlineStr"/>
+      <c r="U107" s="8" t="inlineStr"/>
+      <c r="V107" s="8" t="inlineStr"/>
+      <c r="W107" s="9" t="n">
         <v>5225.166666666667</v>
       </c>
-      <c r="X98" s="9" t="n">
+      <c r="X107" s="9" t="n">
         <v>203.166666666667</v>
       </c>
-      <c r="Y98" s="11" t="n">
+      <c r="Y107" s="11" t="n">
         <v>0.01820522470534122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A98:A103"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A49:A51"/>
     <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="A104:A107"/>
+    <mergeCell ref="A87:A89"/>
     <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="A59:A62"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="A35:A38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -338,44 +338,16 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O60" authorId="0" shapeId="0">
+    <comment ref="E59" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P60" authorId="0" shapeId="0">
+    <comment ref="E60" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="U60" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O61" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P61" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="U61" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -401,30 +373,44 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K75" authorId="0" shapeId="0">
+    <comment ref="O63" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L75" authorId="0" shapeId="0">
+    <comment ref="P63" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K76" authorId="0" shapeId="0">
+    <comment ref="U63" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L76" authorId="0" shapeId="0">
+    <comment ref="O64" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P64" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="U64" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -443,35 +429,63 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O88" authorId="0" shapeId="0">
+    <comment ref="K78" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L78" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O90" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O89" authorId="0" shapeId="0">
+    <comment ref="O91" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I91" authorId="0" shapeId="0">
+    <comment ref="I93" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I92" authorId="0" shapeId="0">
+    <comment ref="I94" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I93" authorId="0" shapeId="0">
+    <comment ref="I95" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -771,7 +785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y107"/>
+  <dimension ref="A1:Y109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
@@ -3558,170 +3572,148 @@
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Gopher
-Random: 257.6
-Human: 2412.5</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 8240</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr"/>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr"/>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr"/>
-      <c r="K59" s="4" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr"/>
-      <c r="M59" s="4" t="inlineStr"/>
-      <c r="N59" s="4" t="inlineStr"/>
-      <c r="O59" s="4" t="inlineStr"/>
-      <c r="P59" s="4" t="inlineStr"/>
-      <c r="Q59" s="4" t="inlineStr"/>
-      <c r="R59" s="4" t="inlineStr"/>
-      <c r="S59" s="4" t="inlineStr"/>
-      <c r="T59" s="4" t="inlineStr"/>
-      <c r="U59" s="4" t="inlineStr"/>
-      <c r="V59" s="4" t="inlineStr"/>
-      <c r="W59" s="5" t="inlineStr"/>
-      <c r="X59" s="6" t="n">
-        <v>-4547</v>
-      </c>
-      <c r="Y59" s="7" t="n">
-        <v>-2.110074713443779</v>
-      </c>
+      <c r="A59" s="1" t="n"/>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr"/>
+      <c r="D59" s="8" t="inlineStr"/>
+      <c r="E59" s="13" t="inlineStr"/>
+      <c r="F59" s="8" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr"/>
+      <c r="J59" s="8" t="inlineStr"/>
+      <c r="K59" s="8" t="inlineStr"/>
+      <c r="L59" s="8" t="inlineStr"/>
+      <c r="M59" s="8" t="inlineStr"/>
+      <c r="N59" s="8" t="inlineStr"/>
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="P59" s="8" t="inlineStr"/>
+      <c r="Q59" s="8" t="inlineStr"/>
+      <c r="R59" s="8" t="inlineStr"/>
+      <c r="S59" s="8" t="inlineStr"/>
+      <c r="T59" s="8" t="inlineStr"/>
+      <c r="U59" s="8" t="inlineStr"/>
+      <c r="V59" s="8" t="inlineStr"/>
+      <c r="W59" s="9" t="inlineStr"/>
+      <c r="X59" s="10" t="inlineStr"/>
+      <c r="Y59" s="11" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>5968.00</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>3752.00</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>3275.00</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>3914.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr"/>
+      <c r="D60" s="8" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr"/>
+      <c r="F60" s="8" t="inlineStr"/>
       <c r="G60" s="8" t="inlineStr"/>
       <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>4219.00</t>
-        </is>
-      </c>
+      <c r="I60" s="8" t="inlineStr"/>
       <c r="J60" s="8" t="inlineStr"/>
       <c r="K60" s="8" t="inlineStr"/>
       <c r="L60" s="8" t="inlineStr"/>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
-      <c r="O60" s="13" t="inlineStr">
-        <is>
-          <t>2486.00</t>
-        </is>
-      </c>
-      <c r="P60" s="13" t="inlineStr">
-        <is>
-          <t>1250.00</t>
-        </is>
-      </c>
+      <c r="O60" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="P60" s="8" t="inlineStr"/>
       <c r="Q60" s="8" t="inlineStr"/>
       <c r="R60" s="8" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr"/>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>3585.00</t>
-        </is>
-      </c>
-      <c r="U60" s="13" t="inlineStr">
-        <is>
-          <t>2594.00</t>
-        </is>
-      </c>
+      <c r="T60" s="8" t="inlineStr"/>
+      <c r="U60" s="8" t="inlineStr"/>
       <c r="V60" s="8" t="inlineStr"/>
-      <c r="W60" s="9" t="n">
-        <v>3693</v>
-      </c>
+      <c r="W60" s="9" t="inlineStr"/>
       <c r="X60" s="10" t="inlineStr"/>
       <c r="Y60" s="11" t="inlineStr"/>
     </row>
     <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="1" t="n"/>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr"/>
-      <c r="D61" s="8" t="inlineStr"/>
-      <c r="E61" s="8" t="inlineStr"/>
-      <c r="F61" s="8" t="inlineStr"/>
-      <c r="G61" s="8" t="inlineStr"/>
-      <c r="H61" s="8" t="inlineStr"/>
-      <c r="I61" s="8" t="inlineStr"/>
-      <c r="J61" s="8" t="inlineStr"/>
-      <c r="K61" s="8" t="inlineStr"/>
-      <c r="L61" s="8" t="inlineStr"/>
-      <c r="M61" s="8" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="13" t="inlineStr"/>
-      <c r="P61" s="13" t="inlineStr"/>
-      <c r="Q61" s="8" t="inlineStr"/>
-      <c r="R61" s="8" t="inlineStr">
-        <is>
-          <t>2533.00</t>
-        </is>
-      </c>
-      <c r="S61" s="8" t="inlineStr"/>
-      <c r="T61" s="8" t="inlineStr"/>
-      <c r="U61" s="13" t="inlineStr"/>
-      <c r="V61" s="8" t="inlineStr"/>
-      <c r="W61" s="9" t="inlineStr"/>
-      <c r="X61" s="10" t="inlineStr"/>
-      <c r="Y61" s="11" t="inlineStr"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Gopher
+Random: 257.6
+Human: 2412.5</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 8240</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="4" t="inlineStr"/>
+      <c r="P61" s="4" t="inlineStr"/>
+      <c r="Q61" s="4" t="inlineStr"/>
+      <c r="R61" s="4" t="inlineStr"/>
+      <c r="S61" s="4" t="inlineStr"/>
+      <c r="T61" s="4" t="inlineStr"/>
+      <c r="U61" s="4" t="inlineStr"/>
+      <c r="V61" s="4" t="inlineStr"/>
+      <c r="W61" s="5" t="inlineStr"/>
+      <c r="X61" s="6" t="n">
+        <v>-4547</v>
+      </c>
+      <c r="Y61" s="7" t="n">
+        <v>-2.110074713443779</v>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr"/>
-      <c r="D62" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>5968.00</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>3752.00</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>3327.00</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr"/>
+          <t>3275.00</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>3914.00</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="inlineStr"/>
       <c r="H62" s="8" t="inlineStr"/>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>3829.00</t>
+          <t>4219.00</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr"/>
@@ -3731,12 +3723,12 @@
       <c r="N62" s="8" t="inlineStr"/>
       <c r="O62" s="13" t="inlineStr">
         <is>
-          <t>1024.00</t>
+          <t>2486.00</t>
         </is>
       </c>
       <c r="P62" s="13" t="inlineStr">
         <is>
-          <t>927.00</t>
+          <t>1250.00</t>
         </is>
       </c>
       <c r="Q62" s="8" t="inlineStr"/>
@@ -3744,94 +3736,76 @@
       <c r="S62" s="8" t="inlineStr"/>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>7531.00</t>
+          <t>3585.00</t>
         </is>
       </c>
       <c r="U62" s="13" t="inlineStr">
         <is>
-          <t>1005.00</t>
+          <t>2594.00</t>
         </is>
       </c>
       <c r="V62" s="8" t="inlineStr"/>
       <c r="W62" s="9" t="n">
-        <v>4895.666666666667</v>
-      </c>
-      <c r="X62" s="9" t="n">
-        <v>1202.666666666667</v>
-      </c>
-      <c r="Y62" s="11" t="n">
-        <v>0.558107878169134</v>
-      </c>
+        <v>3693</v>
+      </c>
+      <c r="X62" s="10" t="inlineStr"/>
+      <c r="Y62" s="11" t="inlineStr"/>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Hero
-Random: 1027.0
-Human: 30826.4</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11044</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr"/>
-      <c r="D63" s="4" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="4" t="inlineStr"/>
-      <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr"/>
-      <c r="M63" s="4" t="inlineStr"/>
-      <c r="N63" s="4" t="inlineStr"/>
-      <c r="O63" s="4" t="inlineStr"/>
-      <c r="P63" s="4" t="inlineStr"/>
-      <c r="Q63" s="4" t="inlineStr"/>
-      <c r="R63" s="4" t="inlineStr"/>
-      <c r="S63" s="4" t="inlineStr"/>
-      <c r="T63" s="4" t="inlineStr"/>
-      <c r="U63" s="4" t="inlineStr"/>
-      <c r="V63" s="4" t="inlineStr"/>
-      <c r="W63" s="5" t="inlineStr"/>
-      <c r="X63" s="6" t="n">
-        <v>2134</v>
-      </c>
-      <c r="Y63" s="7" t="n">
-        <v>0.07161218011100895</v>
-      </c>
+      <c r="A63" s="1" t="n"/>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr"/>
+      <c r="D63" s="8" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr"/>
+      <c r="F63" s="8" t="inlineStr"/>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr"/>
+      <c r="K63" s="8" t="inlineStr"/>
+      <c r="L63" s="8" t="inlineStr"/>
+      <c r="M63" s="8" t="inlineStr"/>
+      <c r="N63" s="8" t="inlineStr"/>
+      <c r="O63" s="13" t="inlineStr"/>
+      <c r="P63" s="13" t="inlineStr"/>
+      <c r="Q63" s="8" t="inlineStr"/>
+      <c r="R63" s="8" t="inlineStr">
+        <is>
+          <t>2533.00</t>
+        </is>
+      </c>
+      <c r="S63" s="8" t="inlineStr"/>
+      <c r="T63" s="8" t="inlineStr"/>
+      <c r="U63" s="13" t="inlineStr"/>
+      <c r="V63" s="8" t="inlineStr"/>
+      <c r="W63" s="9" t="inlineStr"/>
+      <c r="X63" s="10" t="inlineStr"/>
+      <c r="Y63" s="11" t="inlineStr"/>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>7608.50</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr"/>
       <c r="D64" s="8" t="inlineStr"/>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>12996.75</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>13456.25</t>
-        </is>
-      </c>
+          <t>3327.00</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr"/>
       <c r="H64" s="8" t="inlineStr"/>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>13081.00</t>
+          <t>3829.00</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr"/>
@@ -3839,202 +3813,232 @@
       <c r="L64" s="8" t="inlineStr"/>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
-      <c r="O64" s="8" t="inlineStr"/>
-      <c r="P64" s="8" t="inlineStr"/>
+      <c r="O64" s="13" t="inlineStr">
+        <is>
+          <t>1024.00</t>
+        </is>
+      </c>
+      <c r="P64" s="13" t="inlineStr">
+        <is>
+          <t>927.00</t>
+        </is>
+      </c>
       <c r="Q64" s="8" t="inlineStr"/>
       <c r="R64" s="8" t="inlineStr"/>
       <c r="S64" s="8" t="inlineStr"/>
-      <c r="T64" s="8" t="inlineStr"/>
-      <c r="U64" s="8" t="inlineStr"/>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>7531.00</t>
+        </is>
+      </c>
+      <c r="U64" s="13" t="inlineStr">
+        <is>
+          <t>1005.00</t>
+        </is>
+      </c>
       <c r="V64" s="8" t="inlineStr"/>
       <c r="W64" s="9" t="n">
+        <v>4895.666666666667</v>
+      </c>
+      <c r="X64" s="9" t="n">
+        <v>1202.666666666667</v>
+      </c>
+      <c r="Y64" s="11" t="n">
+        <v>0.558107878169134</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Hero
+Random: 1027.0
+Human: 30826.4</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11044</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="4" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr"/>
+      <c r="Q65" s="4" t="inlineStr"/>
+      <c r="R65" s="4" t="inlineStr"/>
+      <c r="S65" s="4" t="inlineStr"/>
+      <c r="T65" s="4" t="inlineStr"/>
+      <c r="U65" s="4" t="inlineStr"/>
+      <c r="V65" s="4" t="inlineStr"/>
+      <c r="W65" s="5" t="inlineStr"/>
+      <c r="X65" s="6" t="n">
+        <v>2134</v>
+      </c>
+      <c r="Y65" s="7" t="n">
+        <v>0.07161218011100895</v>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="1" t="n"/>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>7608.50</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr"/>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>12996.75</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>13456.25</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>13081.00</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr"/>
+      <c r="K66" s="8" t="inlineStr"/>
+      <c r="L66" s="8" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr"/>
+      <c r="N66" s="8" t="inlineStr"/>
+      <c r="O66" s="8" t="inlineStr"/>
+      <c r="P66" s="8" t="inlineStr"/>
+      <c r="Q66" s="8" t="inlineStr"/>
+      <c r="R66" s="8" t="inlineStr"/>
+      <c r="S66" s="8" t="inlineStr"/>
+      <c r="T66" s="8" t="inlineStr"/>
+      <c r="U66" s="8" t="inlineStr"/>
+      <c r="V66" s="8" t="inlineStr"/>
+      <c r="W66" s="9" t="n">
         <v>13178</v>
       </c>
-      <c r="X64" s="10" t="inlineStr"/>
-      <c r="Y64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="1" t="n"/>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr"/>
-      <c r="D65" s="8" t="inlineStr"/>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>13251.25</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>13231.50</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>13325.50</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr"/>
-      <c r="L65" s="8" t="inlineStr"/>
-      <c r="M65" s="8" t="inlineStr"/>
-      <c r="N65" s="8" t="inlineStr"/>
-      <c r="O65" s="8" t="inlineStr"/>
-      <c r="P65" s="8" t="inlineStr"/>
-      <c r="Q65" s="8" t="inlineStr"/>
-      <c r="R65" s="8" t="inlineStr"/>
-      <c r="S65" s="8" t="inlineStr"/>
-      <c r="T65" s="8" t="inlineStr"/>
-      <c r="U65" s="8" t="inlineStr"/>
-      <c r="V65" s="8" t="inlineStr"/>
-      <c r="W65" s="9" t="n">
-        <v>13269.41666666667</v>
-      </c>
-      <c r="X65" s="9" t="n">
-        <v>91.41666666666606</v>
-      </c>
-      <c r="Y65" s="11" t="n">
-        <v>0.003067735144555463</v>
-      </c>
-    </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Jamesbond
-Random: 29.0
-Human: 302.8</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 509</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr"/>
-      <c r="D66" s="4" t="inlineStr"/>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr"/>
-      <c r="K66" s="4" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr"/>
-      <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr"/>
-      <c r="O66" s="4" t="inlineStr"/>
-      <c r="P66" s="4" t="inlineStr"/>
-      <c r="Q66" s="4" t="inlineStr"/>
-      <c r="R66" s="4" t="inlineStr"/>
-      <c r="S66" s="4" t="inlineStr"/>
-      <c r="T66" s="4" t="inlineStr"/>
-      <c r="U66" s="4" t="inlineStr"/>
-      <c r="V66" s="4" t="inlineStr"/>
-      <c r="W66" s="5" t="inlineStr"/>
-      <c r="X66" s="6" t="n">
-        <v>-35.66666666666669</v>
-      </c>
-      <c r="Y66" s="7" t="n">
-        <v>-0.1302654005356709</v>
-      </c>
+      <c r="X66" s="10" t="inlineStr"/>
+      <c r="Y66" s="11" t="inlineStr"/>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>490.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr"/>
       <c r="D67" s="8" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>13251.25</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>13231.50</t>
+        </is>
+      </c>
       <c r="G67" s="8" t="inlineStr"/>
       <c r="H67" s="8" t="inlineStr"/>
-      <c r="I67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>13325.50</t>
+        </is>
+      </c>
       <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr">
-        <is>
-          <t>532.50, 537.50</t>
-        </is>
-      </c>
+      <c r="K67" s="8" t="inlineStr"/>
       <c r="L67" s="8" t="inlineStr"/>
       <c r="M67" s="8" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
-      <c r="O67" s="8" t="inlineStr">
-        <is>
-          <t>522.50</t>
-        </is>
-      </c>
+      <c r="O67" s="8" t="inlineStr"/>
       <c r="P67" s="8" t="inlineStr"/>
       <c r="Q67" s="8" t="inlineStr"/>
       <c r="R67" s="8" t="inlineStr"/>
       <c r="S67" s="8" t="inlineStr"/>
       <c r="T67" s="8" t="inlineStr"/>
-      <c r="U67" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
-        </is>
-      </c>
+      <c r="U67" s="8" t="inlineStr"/>
       <c r="V67" s="8" t="inlineStr"/>
       <c r="W67" s="9" t="n">
-        <v>473.3333333333333</v>
-      </c>
-      <c r="X67" s="10" t="inlineStr"/>
-      <c r="Y67" s="11" t="inlineStr"/>
+        <v>13269.41666666667</v>
+      </c>
+      <c r="X67" s="9" t="n">
+        <v>91.41666666666606</v>
+      </c>
+      <c r="Y67" s="11" t="n">
+        <v>0.003067735144555463</v>
+      </c>
     </row>
     <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="1" t="n"/>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr"/>
-      <c r="D68" s="8" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr"/>
-      <c r="G68" s="8" t="inlineStr"/>
-      <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr"/>
-      <c r="K68" s="8" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr"/>
-      <c r="M68" s="8" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
-      <c r="O68" s="8" t="inlineStr">
-        <is>
-          <t>575.00</t>
-        </is>
-      </c>
-      <c r="P68" s="8" t="inlineStr"/>
-      <c r="Q68" s="8" t="inlineStr"/>
-      <c r="R68" s="8" t="inlineStr"/>
-      <c r="S68" s="8" t="inlineStr"/>
-      <c r="T68" s="8" t="inlineStr"/>
-      <c r="U68" s="8" t="inlineStr"/>
-      <c r="V68" s="8" t="inlineStr"/>
-      <c r="W68" s="9" t="inlineStr"/>
-      <c r="X68" s="10" t="inlineStr"/>
-      <c r="Y68" s="11" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Jamesbond
+Random: 29.0
+Human: 302.8</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 509</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr"/>
+      <c r="Q68" s="4" t="inlineStr"/>
+      <c r="R68" s="4" t="inlineStr"/>
+      <c r="S68" s="4" t="inlineStr"/>
+      <c r="T68" s="4" t="inlineStr"/>
+      <c r="U68" s="4" t="inlineStr"/>
+      <c r="V68" s="4" t="inlineStr"/>
+      <c r="W68" s="5" t="inlineStr"/>
+      <c r="X68" s="6" t="n">
+        <v>-35.66666666666669</v>
+      </c>
+      <c r="Y68" s="7" t="n">
+        <v>-0.1302654005356709</v>
+      </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>490.00</t>
+        </is>
+      </c>
       <c r="D69" s="8" t="inlineStr"/>
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr"/>
@@ -4044,7 +4048,7 @@
       <c r="J69" s="8" t="inlineStr"/>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>567.50, 660.00</t>
+          <t>532.50, 537.50</t>
         </is>
       </c>
       <c r="L69" s="8" t="inlineStr"/>
@@ -4052,7 +4056,7 @@
       <c r="N69" s="8" t="inlineStr"/>
       <c r="O69" s="8" t="inlineStr">
         <is>
-          <t>665.00</t>
+          <t>522.50</t>
         </is>
       </c>
       <c r="P69" s="8" t="inlineStr"/>
@@ -4062,75 +4066,61 @@
       <c r="T69" s="8" t="inlineStr"/>
       <c r="U69" s="8" t="inlineStr">
         <is>
-          <t>375.00</t>
+          <t>365.00</t>
         </is>
       </c>
       <c r="V69" s="8" t="inlineStr"/>
       <c r="W69" s="9" t="n">
-        <v>535.8333333333334</v>
-      </c>
-      <c r="X69" s="9" t="n">
-        <v>62.50000000000006</v>
-      </c>
-      <c r="Y69" s="11" t="n">
-        <v>0.2282688093498906</v>
-      </c>
+        <v>473.3333333333333</v>
+      </c>
+      <c r="X69" s="10" t="inlineStr"/>
+      <c r="Y69" s="11" t="inlineStr"/>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Kangaroo
-Random: 52.0
-Human: 3035.0</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4208</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr"/>
-      <c r="D70" s="4" t="inlineStr"/>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr"/>
-      <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="4" t="inlineStr"/>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr"/>
-      <c r="O70" s="4" t="inlineStr"/>
-      <c r="P70" s="4" t="inlineStr"/>
-      <c r="Q70" s="4" t="inlineStr"/>
-      <c r="R70" s="4" t="inlineStr"/>
-      <c r="S70" s="4" t="inlineStr"/>
-      <c r="T70" s="4" t="inlineStr"/>
-      <c r="U70" s="4" t="inlineStr"/>
-      <c r="V70" s="4" t="inlineStr"/>
-      <c r="W70" s="5" t="inlineStr"/>
-      <c r="X70" s="6" t="n">
-        <v>-2778</v>
-      </c>
-      <c r="Y70" s="7" t="n">
-        <v>-0.9312772376801878</v>
-      </c>
+      <c r="A70" s="1" t="n"/>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr"/>
+      <c r="D70" s="8" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr"/>
+      <c r="F70" s="8" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr"/>
+      <c r="K70" s="8" t="inlineStr"/>
+      <c r="L70" s="8" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
+      <c r="N70" s="8" t="inlineStr"/>
+      <c r="O70" s="8" t="inlineStr">
+        <is>
+          <t>575.00</t>
+        </is>
+      </c>
+      <c r="P70" s="8" t="inlineStr"/>
+      <c r="Q70" s="8" t="inlineStr"/>
+      <c r="R70" s="8" t="inlineStr"/>
+      <c r="S70" s="8" t="inlineStr"/>
+      <c r="T70" s="8" t="inlineStr"/>
+      <c r="U70" s="8" t="inlineStr"/>
+      <c r="V70" s="8" t="inlineStr"/>
+      <c r="W70" s="9" t="inlineStr"/>
+      <c r="X70" s="10" t="inlineStr"/>
+      <c r="Y70" s="11" t="inlineStr"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr"/>
       <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>1770.00</t>
-        </is>
-      </c>
+      <c r="E71" s="8" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr"/>
       <c r="G71" s="8" t="inlineStr"/>
       <c r="H71" s="8" t="inlineStr"/>
@@ -4138,93 +4128,91 @@
       <c r="J71" s="8" t="inlineStr"/>
       <c r="K71" s="8" t="inlineStr">
         <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="L71" s="8" t="inlineStr">
-        <is>
-          <t>1730.00</t>
-        </is>
-      </c>
+          <t>567.50, 660.00</t>
+        </is>
+      </c>
+      <c r="L71" s="8" t="inlineStr"/>
       <c r="M71" s="8" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
       <c r="O71" s="8" t="inlineStr">
         <is>
-          <t>1550.00</t>
-        </is>
-      </c>
-      <c r="P71" s="8" t="inlineStr">
-        <is>
-          <t>930.00</t>
-        </is>
-      </c>
+          <t>665.00</t>
+        </is>
+      </c>
+      <c r="P71" s="8" t="inlineStr"/>
       <c r="Q71" s="8" t="inlineStr"/>
       <c r="R71" s="8" t="inlineStr"/>
       <c r="S71" s="8" t="inlineStr"/>
       <c r="T71" s="8" t="inlineStr"/>
-      <c r="U71" s="8" t="inlineStr"/>
+      <c r="U71" s="8" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
       <c r="V71" s="8" t="inlineStr"/>
       <c r="W71" s="9" t="n">
-        <v>1430</v>
-      </c>
-      <c r="X71" s="10" t="inlineStr"/>
-      <c r="Y71" s="11" t="inlineStr"/>
+        <v>535.8333333333334</v>
+      </c>
+      <c r="X71" s="9" t="n">
+        <v>62.50000000000006</v>
+      </c>
+      <c r="Y71" s="11" t="n">
+        <v>0.2282688093498906</v>
+      </c>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="1" t="n"/>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr"/>
-      <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr"/>
-      <c r="F72" s="8" t="inlineStr"/>
-      <c r="G72" s="8" t="inlineStr"/>
-      <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr"/>
-      <c r="J72" s="8" t="inlineStr"/>
-      <c r="K72" s="8" t="inlineStr">
-        <is>
-          <t>1310.00</t>
-        </is>
-      </c>
-      <c r="L72" s="8" t="inlineStr"/>
-      <c r="M72" s="8" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
-      <c r="O72" s="8" t="inlineStr">
-        <is>
-          <t>1500.00</t>
-        </is>
-      </c>
-      <c r="P72" s="8" t="inlineStr">
-        <is>
-          <t>1030.00</t>
-        </is>
-      </c>
-      <c r="Q72" s="8" t="inlineStr"/>
-      <c r="R72" s="8" t="inlineStr"/>
-      <c r="S72" s="8" t="inlineStr"/>
-      <c r="T72" s="8" t="inlineStr"/>
-      <c r="U72" s="8" t="inlineStr"/>
-      <c r="V72" s="8" t="inlineStr"/>
-      <c r="W72" s="9" t="inlineStr"/>
-      <c r="X72" s="10" t="inlineStr"/>
-      <c r="Y72" s="11" t="inlineStr"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Kangaroo
+Random: 52.0
+Human: 3035.0</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4208</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr"/>
+      <c r="P72" s="4" t="inlineStr"/>
+      <c r="Q72" s="4" t="inlineStr"/>
+      <c r="R72" s="4" t="inlineStr"/>
+      <c r="S72" s="4" t="inlineStr"/>
+      <c r="T72" s="4" t="inlineStr"/>
+      <c r="U72" s="4" t="inlineStr"/>
+      <c r="V72" s="4" t="inlineStr"/>
+      <c r="W72" s="5" t="inlineStr"/>
+      <c r="X72" s="6" t="n">
+        <v>-2778</v>
+      </c>
+      <c r="Y72" s="7" t="n">
+        <v>-0.9312772376801878</v>
+      </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr"/>
       <c r="D73" s="8" t="inlineStr"/>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>1760.00</t>
+          <t>1770.00</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr"/>
@@ -4234,20 +4222,24 @@
       <c r="J73" s="8" t="inlineStr"/>
       <c r="K73" s="8" t="inlineStr">
         <is>
-          <t>1590.00</t>
-        </is>
-      </c>
-      <c r="L73" s="8" t="inlineStr"/>
+          <t>1470.00</t>
+        </is>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>1730.00</t>
+        </is>
+      </c>
       <c r="M73" s="8" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
       <c r="O73" s="8" t="inlineStr">
         <is>
-          <t>1670.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="P73" s="8" t="inlineStr">
         <is>
-          <t>760.00</t>
+          <t>930.00</t>
         </is>
       </c>
       <c r="Q73" s="8" t="inlineStr"/>
@@ -4257,204 +4249,196 @@
       <c r="U73" s="8" t="inlineStr"/>
       <c r="V73" s="8" t="inlineStr"/>
       <c r="W73" s="9" t="n">
+        <v>1430</v>
+      </c>
+      <c r="X73" s="10" t="inlineStr"/>
+      <c r="Y73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="1" t="n"/>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr"/>
+      <c r="D74" s="8" t="inlineStr"/>
+      <c r="E74" s="8" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr"/>
+      <c r="J74" s="8" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>1310.00</t>
+        </is>
+      </c>
+      <c r="L74" s="8" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
+      <c r="N74" s="8" t="inlineStr"/>
+      <c r="O74" s="8" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>1030.00</t>
+        </is>
+      </c>
+      <c r="Q74" s="8" t="inlineStr"/>
+      <c r="R74" s="8" t="inlineStr"/>
+      <c r="S74" s="8" t="inlineStr"/>
+      <c r="T74" s="8" t="inlineStr"/>
+      <c r="U74" s="8" t="inlineStr"/>
+      <c r="V74" s="8" t="inlineStr"/>
+      <c r="W74" s="9" t="inlineStr"/>
+      <c r="X74" s="10" t="inlineStr"/>
+      <c r="Y74" s="11" t="inlineStr"/>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="1" t="n"/>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr"/>
+      <c r="D75" s="8" t="inlineStr"/>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr"/>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr"/>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="8" t="inlineStr">
+        <is>
+          <t>1590.00</t>
+        </is>
+      </c>
+      <c r="L75" s="8" t="inlineStr"/>
+      <c r="M75" s="8" t="inlineStr"/>
+      <c r="N75" s="8" t="inlineStr"/>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>1670.00</t>
+        </is>
+      </c>
+      <c r="P75" s="8" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
+      <c r="Q75" s="8" t="inlineStr"/>
+      <c r="R75" s="8" t="inlineStr"/>
+      <c r="S75" s="8" t="inlineStr"/>
+      <c r="T75" s="8" t="inlineStr"/>
+      <c r="U75" s="8" t="inlineStr"/>
+      <c r="V75" s="8" t="inlineStr"/>
+      <c r="W75" s="9" t="n">
         <v>1445</v>
       </c>
-      <c r="X73" s="9" t="n">
+      <c r="X75" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="Y73" s="11" t="n">
+      <c r="Y75" s="11" t="n">
         <v>0.005028494803888703</v>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Krull
 Random: 1598.0
 Human: 2665.5</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 8413</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr"/>
-      <c r="D74" s="4" t="inlineStr"/>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr"/>
-      <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="4" t="inlineStr"/>
-      <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr"/>
-      <c r="O74" s="4" t="inlineStr"/>
-      <c r="P74" s="4" t="inlineStr"/>
-      <c r="Q74" s="4" t="inlineStr"/>
-      <c r="R74" s="4" t="inlineStr"/>
-      <c r="S74" s="4" t="inlineStr"/>
-      <c r="T74" s="4" t="inlineStr"/>
-      <c r="U74" s="4" t="inlineStr"/>
-      <c r="V74" s="4" t="inlineStr"/>
-      <c r="W74" s="5" t="inlineStr"/>
-      <c r="X74" s="6" t="n">
+      <c r="C76" s="4" t="inlineStr"/>
+      <c r="D76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr"/>
+      <c r="L76" s="4" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr"/>
+      <c r="N76" s="4" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr"/>
+      <c r="Q76" s="4" t="inlineStr"/>
+      <c r="R76" s="4" t="inlineStr"/>
+      <c r="S76" s="4" t="inlineStr"/>
+      <c r="T76" s="4" t="inlineStr"/>
+      <c r="U76" s="4" t="inlineStr"/>
+      <c r="V76" s="4" t="inlineStr"/>
+      <c r="W76" s="5" t="inlineStr"/>
+      <c r="X76" s="6" t="n">
         <v>-2583.375</v>
       </c>
-      <c r="Y74" s="7" t="n">
+      <c r="Y76" s="7" t="n">
         <v>-2.420023419203747</v>
       </c>
-    </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="1" t="n"/>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr"/>
-      <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>6202.00</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>5689.00</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>6107.50</t>
-        </is>
-      </c>
-      <c r="J75" s="8" t="inlineStr"/>
-      <c r="K75" s="13" t="inlineStr">
-        <is>
-          <t>4708.50</t>
-        </is>
-      </c>
-      <c r="L75" s="13" t="inlineStr">
-        <is>
-          <t>5913.50</t>
-        </is>
-      </c>
-      <c r="M75" s="8" t="inlineStr"/>
-      <c r="N75" s="8" t="inlineStr"/>
-      <c r="O75" s="8" t="inlineStr">
-        <is>
-          <t>5228.50</t>
-        </is>
-      </c>
-      <c r="P75" s="8" t="inlineStr"/>
-      <c r="Q75" s="8" t="inlineStr">
-        <is>
-          <t>5599.00</t>
-        </is>
-      </c>
-      <c r="R75" s="8" t="inlineStr"/>
-      <c r="S75" s="8" t="inlineStr"/>
-      <c r="T75" s="8" t="inlineStr"/>
-      <c r="U75" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
-      <c r="V75" s="8" t="inlineStr"/>
-      <c r="W75" s="9" t="n">
-        <v>5829.625</v>
-      </c>
-      <c r="X75" s="10" t="inlineStr"/>
-      <c r="Y75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="1" t="n"/>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr"/>
-      <c r="D76" s="8" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="8" t="inlineStr"/>
-      <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr"/>
-      <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>4851.00</t>
-        </is>
-      </c>
-      <c r="L76" s="13" t="inlineStr">
-        <is>
-          <t>6044.00</t>
-        </is>
-      </c>
-      <c r="M76" s="8" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr"/>
-      <c r="O76" s="8" t="inlineStr"/>
-      <c r="P76" s="8" t="inlineStr"/>
-      <c r="Q76" s="8" t="inlineStr"/>
-      <c r="R76" s="8" t="inlineStr"/>
-      <c r="S76" s="8" t="inlineStr"/>
-      <c r="T76" s="8" t="inlineStr"/>
-      <c r="U76" s="8" t="inlineStr">
-        <is>
-          <t>6587.00</t>
-        </is>
-      </c>
-      <c r="V76" s="8" t="inlineStr"/>
-      <c r="W76" s="9" t="inlineStr"/>
-      <c r="X76" s="10" t="inlineStr"/>
-      <c r="Y76" s="11" t="inlineStr"/>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr"/>
       <c r="D77" s="8" t="inlineStr"/>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>6576.50</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr"/>
+          <t>6202.00</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>5689.00</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="inlineStr"/>
       <c r="H77" s="8" t="inlineStr"/>
-      <c r="I77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>6107.50</t>
+        </is>
+      </c>
       <c r="J77" s="8" t="inlineStr"/>
       <c r="K77" s="13" t="inlineStr">
         <is>
-          <t>5279.50</t>
+          <t>4708.50</t>
         </is>
       </c>
       <c r="L77" s="13" t="inlineStr">
         <is>
-          <t>5889.50</t>
+          <t>5913.50</t>
         </is>
       </c>
       <c r="M77" s="8" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr"/>
       <c r="O77" s="8" t="inlineStr">
         <is>
-          <t>6447.50</t>
+          <t>5228.50</t>
         </is>
       </c>
       <c r="P77" s="8" t="inlineStr"/>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>6828.50</t>
+          <t>5599.00</t>
         </is>
       </c>
       <c r="R77" s="8" t="inlineStr"/>
@@ -4462,73 +4446,71 @@
       <c r="T77" s="8" t="inlineStr"/>
       <c r="U77" s="8" t="inlineStr">
         <is>
-          <t>6796.50</t>
+          <t>6289.00</t>
         </is>
       </c>
       <c r="V77" s="8" t="inlineStr"/>
       <c r="W77" s="9" t="n">
-        <v>6662.25</v>
-      </c>
-      <c r="X77" s="9" t="n">
-        <v>832.625</v>
-      </c>
-      <c r="Y77" s="11" t="n">
-        <v>0.779976580796253</v>
-      </c>
+        <v>5829.625</v>
+      </c>
+      <c r="X77" s="10" t="inlineStr"/>
+      <c r="Y77" s="11" t="inlineStr"/>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>KungFuMaster
-Random: 258.5
-Human: 22736.3</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 26182</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr"/>
-      <c r="D78" s="4" t="inlineStr"/>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr"/>
-      <c r="H78" s="4" t="inlineStr"/>
-      <c r="I78" s="4" t="inlineStr"/>
-      <c r="J78" s="4" t="inlineStr"/>
-      <c r="K78" s="4" t="inlineStr"/>
-      <c r="L78" s="4" t="inlineStr"/>
-      <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr"/>
-      <c r="O78" s="4" t="inlineStr"/>
-      <c r="P78" s="4" t="inlineStr"/>
-      <c r="Q78" s="4" t="inlineStr"/>
-      <c r="R78" s="4" t="inlineStr"/>
-      <c r="S78" s="4" t="inlineStr"/>
-      <c r="T78" s="4" t="inlineStr"/>
-      <c r="U78" s="4" t="inlineStr"/>
-      <c r="V78" s="4" t="inlineStr"/>
-      <c r="W78" s="5" t="inlineStr"/>
-      <c r="X78" s="6" t="n">
-        <v>-1044.5</v>
-      </c>
-      <c r="Y78" s="7" t="n">
-        <v>-0.04646807071866464</v>
-      </c>
+      <c r="A78" s="1" t="n"/>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr"/>
+      <c r="D78" s="8" t="inlineStr"/>
+      <c r="E78" s="8" t="inlineStr"/>
+      <c r="F78" s="8" t="inlineStr"/>
+      <c r="G78" s="8" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr"/>
+      <c r="I78" s="8" t="inlineStr"/>
+      <c r="J78" s="8" t="inlineStr"/>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>4851.00</t>
+        </is>
+      </c>
+      <c r="L78" s="13" t="inlineStr">
+        <is>
+          <t>6044.00</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="inlineStr"/>
+      <c r="N78" s="8" t="inlineStr"/>
+      <c r="O78" s="8" t="inlineStr"/>
+      <c r="P78" s="8" t="inlineStr"/>
+      <c r="Q78" s="8" t="inlineStr"/>
+      <c r="R78" s="8" t="inlineStr"/>
+      <c r="S78" s="8" t="inlineStr"/>
+      <c r="T78" s="8" t="inlineStr"/>
+      <c r="U78" s="8" t="inlineStr">
+        <is>
+          <t>6587.00</t>
+        </is>
+      </c>
+      <c r="V78" s="8" t="inlineStr"/>
+      <c r="W78" s="9" t="inlineStr"/>
+      <c r="X78" s="10" t="inlineStr"/>
+      <c r="Y78" s="11" t="inlineStr"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr"/>
       <c r="D79" s="8" t="inlineStr"/>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>26460.00</t>
+          <t>6576.50</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr"/>
@@ -4536,134 +4518,146 @@
       <c r="H79" s="8" t="inlineStr"/>
       <c r="I79" s="8" t="inlineStr"/>
       <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" s="8" t="inlineStr">
-        <is>
-          <t>23815.00</t>
-        </is>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
-        <is>
-          <t>20895.00</t>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>5279.50</t>
+        </is>
+      </c>
+      <c r="L79" s="13" t="inlineStr">
+        <is>
+          <t>5889.50</t>
         </is>
       </c>
       <c r="M79" s="8" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr"/>
-      <c r="O79" s="8" t="inlineStr"/>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>6447.50</t>
+        </is>
+      </c>
       <c r="P79" s="8" t="inlineStr"/>
-      <c r="Q79" s="8" t="inlineStr"/>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>6828.50</t>
+        </is>
+      </c>
       <c r="R79" s="8" t="inlineStr"/>
       <c r="S79" s="8" t="inlineStr"/>
       <c r="T79" s="8" t="inlineStr"/>
-      <c r="U79" s="8" t="inlineStr"/>
+      <c r="U79" s="8" t="inlineStr">
+        <is>
+          <t>6796.50</t>
+        </is>
+      </c>
       <c r="V79" s="8" t="inlineStr"/>
       <c r="W79" s="9" t="n">
+        <v>6662.25</v>
+      </c>
+      <c r="X79" s="9" t="n">
+        <v>832.625</v>
+      </c>
+      <c r="Y79" s="11" t="n">
+        <v>0.779976580796253</v>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>KungFuMaster
+Random: 258.5
+Human: 22736.3</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 26182</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr"/>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr"/>
+      <c r="P80" s="4" t="inlineStr"/>
+      <c r="Q80" s="4" t="inlineStr"/>
+      <c r="R80" s="4" t="inlineStr"/>
+      <c r="S80" s="4" t="inlineStr"/>
+      <c r="T80" s="4" t="inlineStr"/>
+      <c r="U80" s="4" t="inlineStr"/>
+      <c r="V80" s="4" t="inlineStr"/>
+      <c r="W80" s="5" t="inlineStr"/>
+      <c r="X80" s="6" t="n">
+        <v>-1044.5</v>
+      </c>
+      <c r="Y80" s="7" t="n">
+        <v>-0.04646807071866464</v>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="1" t="n"/>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr"/>
+      <c r="D81" s="8" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>26460.00</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr">
+        <is>
+          <t>23815.00</t>
+        </is>
+      </c>
+      <c r="L81" s="8" t="inlineStr">
+        <is>
+          <t>20895.00</t>
+        </is>
+      </c>
+      <c r="M81" s="8" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr"/>
+      <c r="O81" s="8" t="inlineStr"/>
+      <c r="P81" s="8" t="inlineStr"/>
+      <c r="Q81" s="8" t="inlineStr"/>
+      <c r="R81" s="8" t="inlineStr"/>
+      <c r="S81" s="8" t="inlineStr"/>
+      <c r="T81" s="8" t="inlineStr"/>
+      <c r="U81" s="8" t="inlineStr"/>
+      <c r="V81" s="8" t="inlineStr"/>
+      <c r="W81" s="9" t="n">
         <v>25137.5</v>
       </c>
-      <c r="X79" s="10" t="inlineStr"/>
-      <c r="Y79" s="11" t="inlineStr"/>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="1" t="n"/>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr"/>
-      <c r="D80" s="8" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>30110.00</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr"/>
-      <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" s="8" t="inlineStr"/>
-      <c r="J80" s="8" t="inlineStr"/>
-      <c r="K80" s="8" t="inlineStr">
-        <is>
-          <t>20245.00</t>
-        </is>
-      </c>
-      <c r="L80" s="8" t="inlineStr"/>
-      <c r="M80" s="8" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
-      <c r="O80" s="8" t="inlineStr"/>
-      <c r="P80" s="8" t="inlineStr"/>
-      <c r="Q80" s="8" t="inlineStr"/>
-      <c r="R80" s="8" t="inlineStr"/>
-      <c r="S80" s="8" t="inlineStr"/>
-      <c r="T80" s="8" t="inlineStr"/>
-      <c r="U80" s="8" t="inlineStr"/>
-      <c r="V80" s="8" t="inlineStr"/>
-      <c r="W80" s="9" t="n">
-        <v>25177.5</v>
-      </c>
-      <c r="X80" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y80" s="11" t="n">
-        <v>0.001779533584247569</v>
-      </c>
-    </row>
-    <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>MsPacman
-Random: 307.3
-Human: 6951.6</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 2673</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr"/>
-      <c r="D81" s="4" t="inlineStr"/>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr"/>
-      <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr"/>
-      <c r="K81" s="4" t="inlineStr"/>
-      <c r="L81" s="4" t="inlineStr"/>
-      <c r="M81" s="4" t="inlineStr"/>
-      <c r="N81" s="4" t="inlineStr"/>
-      <c r="O81" s="4" t="inlineStr"/>
-      <c r="P81" s="4" t="inlineStr"/>
-      <c r="Q81" s="4" t="inlineStr"/>
-      <c r="R81" s="4" t="inlineStr"/>
-      <c r="S81" s="4" t="inlineStr"/>
-      <c r="T81" s="4" t="inlineStr"/>
-      <c r="U81" s="4" t="inlineStr"/>
-      <c r="V81" s="4" t="inlineStr"/>
-      <c r="W81" s="5" t="inlineStr"/>
-      <c r="X81" s="6" t="n">
-        <v>-602</v>
-      </c>
-      <c r="Y81" s="7" t="n">
-        <v>-0.09060397634062278</v>
-      </c>
+      <c r="X81" s="10" t="inlineStr"/>
+      <c r="Y81" s="11" t="inlineStr"/>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>1807.50</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr"/>
       <c r="D82" s="8" t="inlineStr"/>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>2007.00</t>
+          <t>30110.00</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr"/>
@@ -4673,17 +4667,13 @@
       <c r="J82" s="8" t="inlineStr"/>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>2388.00</t>
+          <t>20245.00</t>
         </is>
       </c>
       <c r="L82" s="8" t="inlineStr"/>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
-      <c r="O82" s="8" t="inlineStr">
-        <is>
-          <t>1754.00</t>
-        </is>
-      </c>
+      <c r="O82" s="8" t="inlineStr"/>
       <c r="P82" s="8" t="inlineStr"/>
       <c r="Q82" s="8" t="inlineStr"/>
       <c r="R82" s="8" t="inlineStr"/>
@@ -4692,133 +4682,133 @@
       <c r="U82" s="8" t="inlineStr"/>
       <c r="V82" s="8" t="inlineStr"/>
       <c r="W82" s="9" t="n">
+        <v>25177.5</v>
+      </c>
+      <c r="X82" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y82" s="11" t="n">
+        <v>0.001779533584247569</v>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>MsPacman
+Random: 307.3
+Human: 6951.6</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 2673</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr"/>
+      <c r="O83" s="4" t="inlineStr"/>
+      <c r="P83" s="4" t="inlineStr"/>
+      <c r="Q83" s="4" t="inlineStr"/>
+      <c r="R83" s="4" t="inlineStr"/>
+      <c r="S83" s="4" t="inlineStr"/>
+      <c r="T83" s="4" t="inlineStr"/>
+      <c r="U83" s="4" t="inlineStr"/>
+      <c r="V83" s="4" t="inlineStr"/>
+      <c r="W83" s="5" t="inlineStr"/>
+      <c r="X83" s="6" t="n">
+        <v>-602</v>
+      </c>
+      <c r="Y83" s="7" t="n">
+        <v>-0.09060397634062278</v>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="1" t="n"/>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>1807.50</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr"/>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>2007.00</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr"/>
+      <c r="G84" s="8" t="inlineStr"/>
+      <c r="H84" s="8" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>2388.00</t>
+        </is>
+      </c>
+      <c r="L84" s="8" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
+      <c r="N84" s="8" t="inlineStr"/>
+      <c r="O84" s="8" t="inlineStr">
+        <is>
+          <t>1754.00</t>
+        </is>
+      </c>
+      <c r="P84" s="8" t="inlineStr"/>
+      <c r="Q84" s="8" t="inlineStr"/>
+      <c r="R84" s="8" t="inlineStr"/>
+      <c r="S84" s="8" t="inlineStr"/>
+      <c r="T84" s="8" t="inlineStr"/>
+      <c r="U84" s="8" t="inlineStr"/>
+      <c r="V84" s="8" t="inlineStr"/>
+      <c r="W84" s="9" t="n">
         <v>2071</v>
       </c>
-      <c r="X82" s="10" t="inlineStr"/>
-      <c r="Y82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="1" t="n"/>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr"/>
-      <c r="D83" s="8" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr"/>
-      <c r="F83" s="8" t="inlineStr"/>
-      <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="8" t="inlineStr"/>
-      <c r="I83" s="8" t="inlineStr"/>
-      <c r="J83" s="8" t="inlineStr"/>
-      <c r="K83" s="8" t="inlineStr">
-        <is>
-          <t>2250.00</t>
-        </is>
-      </c>
-      <c r="L83" s="8" t="inlineStr"/>
-      <c r="M83" s="8" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
-      <c r="O83" s="8" t="inlineStr">
-        <is>
-          <t>1886.50</t>
-        </is>
-      </c>
-      <c r="P83" s="8" t="inlineStr"/>
-      <c r="Q83" s="8" t="inlineStr"/>
-      <c r="R83" s="8" t="inlineStr"/>
-      <c r="S83" s="8" t="inlineStr"/>
-      <c r="T83" s="8" t="inlineStr"/>
-      <c r="U83" s="8" t="inlineStr"/>
-      <c r="V83" s="8" t="inlineStr"/>
-      <c r="W83" s="9" t="n">
-        <v>2068.25</v>
-      </c>
-      <c r="X83" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y83" s="11" t="n">
-        <v>-0.0004138885962403865</v>
-      </c>
-    </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Pong
-Random: -20.7
-Human: 14.6</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr"/>
-      <c r="D84" s="4" t="inlineStr"/>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
-      <c r="K84" s="4" t="inlineStr"/>
-      <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr"/>
-      <c r="O84" s="4" t="inlineStr"/>
-      <c r="P84" s="4" t="inlineStr"/>
-      <c r="Q84" s="4" t="inlineStr"/>
-      <c r="R84" s="4" t="inlineStr"/>
-      <c r="S84" s="4" t="inlineStr"/>
-      <c r="T84" s="4" t="inlineStr"/>
-      <c r="U84" s="4" t="inlineStr"/>
-      <c r="V84" s="4" t="inlineStr"/>
-      <c r="W84" s="5" t="inlineStr"/>
-      <c r="X84" s="6" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="Y84" s="7" t="n">
-        <v>-0.1529745042492918</v>
-      </c>
+      <c r="X84" s="10" t="inlineStr"/>
+      <c r="Y84" s="11" t="inlineStr"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr"/>
       <c r="D85" s="8" t="inlineStr"/>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
+      <c r="E85" s="8" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr"/>
       <c r="G85" s="8" t="inlineStr"/>
       <c r="H85" s="8" t="inlineStr"/>
       <c r="I85" s="8" t="inlineStr"/>
       <c r="J85" s="8" t="inlineStr"/>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>5.70</t>
-        </is>
-      </c>
-      <c r="L85" s="8" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
+          <t>2250.00</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr"/>
       <c r="M85" s="8" t="inlineStr"/>
       <c r="N85" s="8" t="inlineStr"/>
-      <c r="O85" s="8" t="inlineStr"/>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>1886.50</t>
+        </is>
+      </c>
       <c r="P85" s="8" t="inlineStr"/>
       <c r="Q85" s="8" t="inlineStr"/>
       <c r="R85" s="8" t="inlineStr"/>
@@ -4827,372 +4817,366 @@
       <c r="U85" s="8" t="inlineStr"/>
       <c r="V85" s="8" t="inlineStr"/>
       <c r="W85" s="9" t="n">
+        <v>2068.25</v>
+      </c>
+      <c r="X85" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y85" s="11" t="n">
+        <v>-0.0004138885962403865</v>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Pong
+Random: -20.7
+Human: 14.6</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr"/>
+      <c r="D86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="4" t="inlineStr"/>
+      <c r="N86" s="4" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr"/>
+      <c r="P86" s="4" t="inlineStr"/>
+      <c r="Q86" s="4" t="inlineStr"/>
+      <c r="R86" s="4" t="inlineStr"/>
+      <c r="S86" s="4" t="inlineStr"/>
+      <c r="T86" s="4" t="inlineStr"/>
+      <c r="U86" s="4" t="inlineStr"/>
+      <c r="V86" s="4" t="inlineStr"/>
+      <c r="W86" s="5" t="inlineStr"/>
+      <c r="X86" s="6" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="Y86" s="7" t="n">
+        <v>-0.1529745042492918</v>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="1" t="n"/>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr"/>
+      <c r="D87" s="8" t="inlineStr"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr"/>
+      <c r="J87" s="8" t="inlineStr"/>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>13.70</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr"/>
+      <c r="N87" s="8" t="inlineStr"/>
+      <c r="O87" s="8" t="inlineStr"/>
+      <c r="P87" s="8" t="inlineStr"/>
+      <c r="Q87" s="8" t="inlineStr"/>
+      <c r="R87" s="8" t="inlineStr"/>
+      <c r="S87" s="8" t="inlineStr"/>
+      <c r="T87" s="8" t="inlineStr"/>
+      <c r="U87" s="8" t="inlineStr"/>
+      <c r="V87" s="8" t="inlineStr"/>
+      <c r="W87" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="X85" s="10" t="inlineStr"/>
-      <c r="Y85" s="11" t="inlineStr"/>
-    </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="1" t="n"/>
-      <c r="B86" s="1" t="inlineStr">
+      <c r="X87" s="10" t="inlineStr"/>
+      <c r="Y87" s="11" t="inlineStr"/>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="1" t="n"/>
+      <c r="B88" s="1" t="inlineStr">
         <is>
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr"/>
-      <c r="D86" s="8" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr"/>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr"/>
+      <c r="D88" s="8" t="inlineStr"/>
+      <c r="E88" s="8" t="inlineStr"/>
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>8.20</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr"/>
+      <c r="H88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>14.45</t>
         </is>
       </c>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr">
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr">
         <is>
           <t>9.80</t>
         </is>
       </c>
-      <c r="L86" s="8" t="inlineStr"/>
-      <c r="M86" s="8" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
-      <c r="O86" s="8" t="inlineStr"/>
-      <c r="P86" s="8" t="inlineStr"/>
-      <c r="Q86" s="8" t="inlineStr"/>
-      <c r="R86" s="8" t="inlineStr"/>
-      <c r="S86" s="8" t="inlineStr"/>
-      <c r="T86" s="8" t="inlineStr"/>
-      <c r="U86" s="8" t="inlineStr"/>
-      <c r="V86" s="8" t="inlineStr"/>
-      <c r="W86" s="9" t="n">
+      <c r="L88" s="8" t="inlineStr"/>
+      <c r="M88" s="8" t="inlineStr"/>
+      <c r="N88" s="8" t="inlineStr"/>
+      <c r="O88" s="8" t="inlineStr"/>
+      <c r="P88" s="8" t="inlineStr"/>
+      <c r="Q88" s="8" t="inlineStr"/>
+      <c r="R88" s="8" t="inlineStr"/>
+      <c r="S88" s="8" t="inlineStr"/>
+      <c r="T88" s="8" t="inlineStr"/>
+      <c r="U88" s="8" t="inlineStr"/>
+      <c r="V88" s="8" t="inlineStr"/>
+      <c r="W88" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="X86" s="9" t="n">
+      <c r="X88" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="Y86" s="11" t="n">
+      <c r="Y88" s="11" t="n">
         <v>0.09631728045325781</v>
       </c>
     </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>PrivateEye
 Random: 24.9
 Human: 69571.3</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 7781</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr"/>
-      <c r="D87" s="4" t="inlineStr"/>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr"/>
-      <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
-      <c r="K87" s="4" t="inlineStr"/>
-      <c r="L87" s="4" t="inlineStr"/>
-      <c r="M87" s="4" t="inlineStr"/>
-      <c r="N87" s="4" t="inlineStr"/>
-      <c r="O87" s="4" t="inlineStr"/>
-      <c r="P87" s="4" t="inlineStr"/>
-      <c r="Q87" s="4" t="inlineStr"/>
-      <c r="R87" s="4" t="inlineStr"/>
-      <c r="S87" s="4" t="inlineStr"/>
-      <c r="T87" s="4" t="inlineStr"/>
-      <c r="U87" s="4" t="inlineStr"/>
-      <c r="V87" s="4" t="inlineStr"/>
-      <c r="W87" s="5" t="inlineStr"/>
-      <c r="X87" s="6" t="n">
+      <c r="C89" s="4" t="inlineStr"/>
+      <c r="D89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr"/>
+      <c r="L89" s="4" t="inlineStr"/>
+      <c r="M89" s="4" t="inlineStr"/>
+      <c r="N89" s="4" t="inlineStr"/>
+      <c r="O89" s="4" t="inlineStr"/>
+      <c r="P89" s="4" t="inlineStr"/>
+      <c r="Q89" s="4" t="inlineStr"/>
+      <c r="R89" s="4" t="inlineStr"/>
+      <c r="S89" s="4" t="inlineStr"/>
+      <c r="T89" s="4" t="inlineStr"/>
+      <c r="U89" s="4" t="inlineStr"/>
+      <c r="V89" s="4" t="inlineStr"/>
+      <c r="W89" s="5" t="inlineStr"/>
+      <c r="X89" s="6" t="n">
         <v>-6778.35</v>
       </c>
-      <c r="Y87" s="7" t="n">
+      <c r="Y89" s="7" t="n">
         <v>-0.09746514557187719</v>
       </c>
     </row>
-    <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="1" t="n"/>
-      <c r="B88" s="1" t="inlineStr">
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="1" t="n"/>
+      <c r="B90" s="1" t="inlineStr">
         <is>
           <t>Retrieval 미사용</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>75.30</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr"/>
-      <c r="E88" s="8" t="inlineStr"/>
-      <c r="F88" s="8" t="inlineStr"/>
-      <c r="G88" s="8" t="inlineStr"/>
-      <c r="H88" s="8" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr"/>
-      <c r="J88" s="8" t="inlineStr"/>
-      <c r="K88" s="8" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr"/>
+      <c r="E90" s="8" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr"/>
+      <c r="J90" s="8" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr">
         <is>
           <t>199.35</t>
         </is>
       </c>
-      <c r="L88" s="8" t="inlineStr"/>
-      <c r="M88" s="8" t="inlineStr"/>
-      <c r="N88" s="8" t="inlineStr"/>
-      <c r="O88" s="13" t="inlineStr">
+      <c r="L90" s="8" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr"/>
+      <c r="N90" s="8" t="inlineStr"/>
+      <c r="O90" s="13" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P88" s="8" t="inlineStr">
+      <c r="P90" s="8" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="Q88" s="8" t="inlineStr">
+      <c r="Q90" s="8" t="inlineStr">
         <is>
           <t>3551.75</t>
         </is>
       </c>
-      <c r="R88" s="8" t="inlineStr"/>
-      <c r="S88" s="8" t="inlineStr"/>
-      <c r="T88" s="8" t="inlineStr"/>
-      <c r="U88" s="8" t="inlineStr">
+      <c r="R90" s="8" t="inlineStr"/>
+      <c r="S90" s="8" t="inlineStr"/>
+      <c r="T90" s="8" t="inlineStr"/>
+      <c r="U90" s="8" t="inlineStr">
         <is>
           <t>159.50</t>
         </is>
       </c>
-      <c r="V88" s="8" t="inlineStr"/>
-      <c r="W88" s="9" t="n">
+      <c r="V90" s="8" t="inlineStr"/>
+      <c r="W90" s="9" t="n">
         <v>1002.65</v>
       </c>
-      <c r="X88" s="10" t="inlineStr"/>
-      <c r="Y88" s="11" t="inlineStr"/>
-    </row>
-    <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="1" t="n"/>
-      <c r="B89" s="1" t="inlineStr">
+      <c r="X90" s="10" t="inlineStr"/>
+      <c r="Y90" s="11" t="inlineStr"/>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="1" t="n"/>
+      <c r="B91" s="1" t="inlineStr">
         <is>
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr"/>
-      <c r="D89" s="8" t="inlineStr"/>
-      <c r="E89" s="8" t="inlineStr"/>
-      <c r="F89" s="8" t="inlineStr"/>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="8" t="inlineStr"/>
-      <c r="I89" s="8" t="inlineStr"/>
-      <c r="J89" s="8" t="inlineStr"/>
-      <c r="K89" s="8" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr"/>
+      <c r="D91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr"/>
+      <c r="J91" s="8" t="inlineStr"/>
+      <c r="K91" s="8" t="inlineStr">
         <is>
           <t>191.95</t>
         </is>
       </c>
-      <c r="L89" s="8" t="inlineStr"/>
-      <c r="M89" s="8" t="inlineStr"/>
-      <c r="N89" s="8" t="inlineStr"/>
-      <c r="O89" s="13" t="inlineStr">
+      <c r="L91" s="8" t="inlineStr"/>
+      <c r="M91" s="8" t="inlineStr"/>
+      <c r="N91" s="8" t="inlineStr"/>
+      <c r="O91" s="13" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="P89" s="8" t="inlineStr">
+      <c r="P91" s="8" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="Q89" s="8" t="inlineStr">
+      <c r="Q91" s="8" t="inlineStr">
         <is>
           <t>166.80</t>
         </is>
       </c>
-      <c r="R89" s="8" t="inlineStr"/>
-      <c r="S89" s="8" t="inlineStr"/>
-      <c r="T89" s="8" t="inlineStr"/>
-      <c r="U89" s="8" t="inlineStr">
+      <c r="R91" s="8" t="inlineStr"/>
+      <c r="S91" s="8" t="inlineStr"/>
+      <c r="T91" s="8" t="inlineStr"/>
+      <c r="U91" s="8" t="inlineStr">
         <is>
           <t>153.20</t>
         </is>
       </c>
-      <c r="V89" s="8" t="inlineStr"/>
-      <c r="W89" s="9" t="n">
+      <c r="V91" s="8" t="inlineStr"/>
+      <c r="W91" s="9" t="n">
         <v>152.9875</v>
       </c>
-      <c r="X89" s="9" t="n">
+      <c r="X91" s="9" t="n">
         <v>849.6624999999999</v>
       </c>
-      <c r="Y89" s="11" t="n">
+      <c r="Y91" s="11" t="n">
         <v>-0.01221720319096315</v>
       </c>
     </row>
-    <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Qbert
 Random: 163.9
 Human: 13455.0</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 4522</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr"/>
-      <c r="D90" s="4" t="inlineStr"/>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="4" t="inlineStr"/>
-      <c r="H90" s="4" t="inlineStr"/>
-      <c r="I90" s="4" t="inlineStr"/>
-      <c r="J90" s="4" t="inlineStr"/>
-      <c r="K90" s="4" t="inlineStr"/>
-      <c r="L90" s="4" t="inlineStr"/>
-      <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr"/>
-      <c r="O90" s="4" t="inlineStr"/>
-      <c r="P90" s="4" t="inlineStr"/>
-      <c r="Q90" s="4" t="inlineStr"/>
-      <c r="R90" s="4" t="inlineStr"/>
-      <c r="S90" s="4" t="inlineStr"/>
-      <c r="T90" s="4" t="inlineStr"/>
-      <c r="U90" s="4" t="inlineStr"/>
-      <c r="V90" s="4" t="inlineStr"/>
-      <c r="W90" s="5" t="inlineStr"/>
-      <c r="X90" s="6" t="n">
+      <c r="C92" s="4" t="inlineStr"/>
+      <c r="D92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr"/>
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="inlineStr"/>
+      <c r="N92" s="4" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr"/>
+      <c r="P92" s="4" t="inlineStr"/>
+      <c r="Q92" s="4" t="inlineStr"/>
+      <c r="R92" s="4" t="inlineStr"/>
+      <c r="S92" s="4" t="inlineStr"/>
+      <c r="T92" s="4" t="inlineStr"/>
+      <c r="U92" s="4" t="inlineStr"/>
+      <c r="V92" s="4" t="inlineStr"/>
+      <c r="W92" s="5" t="inlineStr"/>
+      <c r="X92" s="6" t="n">
         <v>-1662.9375</v>
       </c>
-      <c r="Y90" s="7" t="n">
+      <c r="Y92" s="7" t="n">
         <v>-0.1251166193919239</v>
       </c>
-    </row>
-    <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="1" t="n"/>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr"/>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
-      <c r="F91" s="8" t="inlineStr"/>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr"/>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
-      <c r="J91" s="8" t="inlineStr"/>
-      <c r="K91" s="8" t="inlineStr">
-        <is>
-          <t>3193.75</t>
-        </is>
-      </c>
-      <c r="L91" s="8" t="inlineStr"/>
-      <c r="M91" s="8" t="inlineStr"/>
-      <c r="N91" s="8" t="inlineStr"/>
-      <c r="O91" s="8" t="inlineStr">
-        <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="P91" s="8" t="inlineStr"/>
-      <c r="Q91" s="8" t="inlineStr"/>
-      <c r="R91" s="8" t="inlineStr"/>
-      <c r="S91" s="8" t="inlineStr"/>
-      <c r="T91" s="8" t="inlineStr"/>
-      <c r="U91" s="8" t="inlineStr"/>
-      <c r="V91" s="8" t="inlineStr"/>
-      <c r="W91" s="9" t="n">
-        <v>2859.0625</v>
-      </c>
-      <c r="X91" s="10" t="inlineStr"/>
-      <c r="Y91" s="11" t="inlineStr"/>
-    </row>
-    <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="1" t="n"/>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>2818.75</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr"/>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>1918.75</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="inlineStr"/>
-      <c r="G92" s="8" t="inlineStr"/>
-      <c r="H92" s="8" t="inlineStr"/>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>2553.75</t>
-        </is>
-      </c>
-      <c r="J92" s="8" t="inlineStr"/>
-      <c r="K92" s="8" t="inlineStr"/>
-      <c r="L92" s="8" t="inlineStr"/>
-      <c r="M92" s="8" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr"/>
-      <c r="O92" s="8" t="inlineStr">
-        <is>
-          <t>3782.50</t>
-        </is>
-      </c>
-      <c r="P92" s="8" t="inlineStr"/>
-      <c r="Q92" s="8" t="inlineStr"/>
-      <c r="R92" s="8" t="inlineStr"/>
-      <c r="S92" s="8" t="inlineStr"/>
-      <c r="T92" s="8" t="inlineStr"/>
-      <c r="U92" s="8" t="inlineStr"/>
-      <c r="V92" s="8" t="inlineStr"/>
-      <c r="W92" s="9" t="inlineStr"/>
-      <c r="X92" s="10" t="inlineStr"/>
-      <c r="Y92" s="11" t="inlineStr"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>2702.50</t>
+          <t>1771.25</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>4056.25</t>
+          <t>3786.25</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr"/>
@@ -5200,13 +5184,13 @@
       <c r="H93" s="8" t="inlineStr"/>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>2338.75</t>
+          <t>2940.00</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr"/>
       <c r="K93" s="8" t="inlineStr">
         <is>
-          <t>2608.75</t>
+          <t>3193.75</t>
         </is>
       </c>
       <c r="L93" s="8" t="inlineStr"/>
@@ -5214,7 +5198,7 @@
       <c r="N93" s="8" t="inlineStr"/>
       <c r="O93" s="8" t="inlineStr">
         <is>
-          <t>2895.00</t>
+          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
         </is>
       </c>
       <c r="P93" s="8" t="inlineStr"/>
@@ -5225,74 +5209,88 @@
       <c r="U93" s="8" t="inlineStr"/>
       <c r="V93" s="8" t="inlineStr"/>
       <c r="W93" s="9" t="n">
-        <v>3065.625</v>
-      </c>
-      <c r="X93" s="9" t="n">
-        <v>206.5625</v>
-      </c>
-      <c r="Y93" s="11" t="n">
-        <v>0.01554141493179646</v>
-      </c>
+        <v>2859.0625</v>
+      </c>
+      <c r="X93" s="10" t="inlineStr"/>
+      <c r="Y93" s="11" t="inlineStr"/>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>RoadRunner
-Random: 11.5
-Human: 7845.0</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 17564</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr"/>
-      <c r="D94" s="4" t="inlineStr"/>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr"/>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
-      <c r="K94" s="4" t="inlineStr"/>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr"/>
-      <c r="O94" s="4" t="inlineStr"/>
-      <c r="P94" s="4" t="inlineStr"/>
-      <c r="Q94" s="4" t="inlineStr"/>
-      <c r="R94" s="4" t="inlineStr"/>
-      <c r="S94" s="4" t="inlineStr"/>
-      <c r="T94" s="4" t="inlineStr"/>
-      <c r="U94" s="4" t="inlineStr"/>
-      <c r="V94" s="4" t="inlineStr"/>
-      <c r="W94" s="5" t="inlineStr"/>
-      <c r="X94" s="6" t="n">
-        <v>-8627.75</v>
-      </c>
-      <c r="Y94" s="7" t="n">
-        <v>-1.101391459756175</v>
-      </c>
+      <c r="A94" s="1" t="n"/>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>2818.75</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr"/>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>1918.75</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr"/>
+      <c r="G94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>2553.75</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr"/>
+      <c r="L94" s="8" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr"/>
+      <c r="N94" s="8" t="inlineStr"/>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>3782.50</t>
+        </is>
+      </c>
+      <c r="P94" s="8" t="inlineStr"/>
+      <c r="Q94" s="8" t="inlineStr"/>
+      <c r="R94" s="8" t="inlineStr"/>
+      <c r="S94" s="8" t="inlineStr"/>
+      <c r="T94" s="8" t="inlineStr"/>
+      <c r="U94" s="8" t="inlineStr"/>
+      <c r="V94" s="8" t="inlineStr"/>
+      <c r="W94" s="9" t="inlineStr"/>
+      <c r="X94" s="10" t="inlineStr"/>
+      <c r="Y94" s="11" t="inlineStr"/>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>2702.50</t>
+        </is>
+      </c>
       <c r="D95" s="8" t="inlineStr"/>
-      <c r="E95" s="8" t="inlineStr"/>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>4056.25</t>
+        </is>
+      </c>
       <c r="F95" s="8" t="inlineStr"/>
       <c r="G95" s="8" t="inlineStr"/>
       <c r="H95" s="8" t="inlineStr"/>
-      <c r="I95" s="8" t="inlineStr"/>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>2338.75</t>
+        </is>
+      </c>
       <c r="J95" s="8" t="inlineStr"/>
       <c r="K95" s="8" t="inlineStr">
         <is>
-          <t>8610.00</t>
+          <t>2608.75</t>
         </is>
       </c>
       <c r="L95" s="8" t="inlineStr"/>
@@ -5300,78 +5298,72 @@
       <c r="N95" s="8" t="inlineStr"/>
       <c r="O95" s="8" t="inlineStr">
         <is>
-          <t>7290.00</t>
-        </is>
-      </c>
-      <c r="P95" s="8" t="inlineStr">
-        <is>
-          <t>9690.00</t>
-        </is>
-      </c>
-      <c r="Q95" s="8" t="inlineStr">
-        <is>
-          <t>10155.00</t>
-        </is>
-      </c>
+          <t>2895.00</t>
+        </is>
+      </c>
+      <c r="P95" s="8" t="inlineStr"/>
+      <c r="Q95" s="8" t="inlineStr"/>
       <c r="R95" s="8" t="inlineStr"/>
       <c r="S95" s="8" t="inlineStr"/>
       <c r="T95" s="8" t="inlineStr"/>
       <c r="U95" s="8" t="inlineStr"/>
       <c r="V95" s="8" t="inlineStr"/>
       <c r="W95" s="9" t="n">
-        <v>8936.25</v>
-      </c>
-      <c r="X95" s="10" t="inlineStr"/>
-      <c r="Y95" s="11" t="inlineStr"/>
+        <v>3065.625</v>
+      </c>
+      <c r="X95" s="9" t="n">
+        <v>206.5625</v>
+      </c>
+      <c r="Y95" s="11" t="n">
+        <v>0.01554141493179646</v>
+      </c>
     </row>
     <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="1" t="n"/>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr"/>
-      <c r="D96" s="8" t="inlineStr"/>
-      <c r="E96" s="8" t="inlineStr"/>
-      <c r="F96" s="8" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr"/>
-      <c r="K96" s="8" t="inlineStr"/>
-      <c r="L96" s="8" t="inlineStr"/>
-      <c r="M96" s="8" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
-      <c r="O96" s="8" t="inlineStr">
-        <is>
-          <t>8520.00</t>
-        </is>
-      </c>
-      <c r="P96" s="8" t="inlineStr">
-        <is>
-          <t>11830.00</t>
-        </is>
-      </c>
-      <c r="Q96" s="8" t="inlineStr">
-        <is>
-          <t>16805.00</t>
-        </is>
-      </c>
-      <c r="R96" s="8" t="inlineStr"/>
-      <c r="S96" s="8" t="inlineStr"/>
-      <c r="T96" s="8" t="inlineStr"/>
-      <c r="U96" s="8" t="inlineStr"/>
-      <c r="V96" s="8" t="inlineStr"/>
-      <c r="W96" s="9" t="inlineStr"/>
-      <c r="X96" s="10" t="inlineStr"/>
-      <c r="Y96" s="11" t="inlineStr"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>RoadRunner
+Random: 11.5
+Human: 7845.0</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 17564</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr"/>
+      <c r="L96" s="4" t="inlineStr"/>
+      <c r="M96" s="4" t="inlineStr"/>
+      <c r="N96" s="4" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr"/>
+      <c r="P96" s="4" t="inlineStr"/>
+      <c r="Q96" s="4" t="inlineStr"/>
+      <c r="R96" s="4" t="inlineStr"/>
+      <c r="S96" s="4" t="inlineStr"/>
+      <c r="T96" s="4" t="inlineStr"/>
+      <c r="U96" s="4" t="inlineStr"/>
+      <c r="V96" s="4" t="inlineStr"/>
+      <c r="W96" s="5" t="inlineStr"/>
+      <c r="X96" s="6" t="n">
+        <v>-8627.75</v>
+      </c>
+      <c r="Y96" s="7" t="n">
+        <v>-1.101391459756175</v>
+      </c>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
@@ -5384,7 +5376,7 @@
       <c r="J97" s="8" t="inlineStr"/>
       <c r="K97" s="8" t="inlineStr">
         <is>
-          <t>8195.00</t>
+          <t>8610.00</t>
         </is>
       </c>
       <c r="L97" s="8" t="inlineStr"/>
@@ -5392,17 +5384,17 @@
       <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="8" t="inlineStr">
         <is>
-          <t>8325.00</t>
+          <t>7290.00</t>
         </is>
       </c>
       <c r="P97" s="8" t="inlineStr">
         <is>
-          <t>12890.00</t>
+          <t>9690.00</t>
         </is>
       </c>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>16980.00</t>
+          <t>10155.00</t>
         </is>
       </c>
       <c r="R97" s="8" t="inlineStr"/>
@@ -5411,68 +5403,62 @@
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
       <c r="W97" s="9" t="n">
-        <v>11597.5</v>
-      </c>
-      <c r="X97" s="9" t="n">
-        <v>2661.25</v>
-      </c>
-      <c r="Y97" s="11" t="n">
-        <v>0.3397268143230995</v>
-      </c>
+        <v>8936.25</v>
+      </c>
+      <c r="X97" s="10" t="inlineStr"/>
+      <c r="Y97" s="11" t="inlineStr"/>
     </row>
     <row r="98" ht="24" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Seaquest
-Random: 68.4
-Human: 42054.7</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 525</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr"/>
-      <c r="D98" s="4" t="inlineStr"/>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr"/>
-      <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="4" t="inlineStr"/>
-      <c r="J98" s="4" t="inlineStr"/>
-      <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="4" t="inlineStr"/>
-      <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr"/>
-      <c r="O98" s="4" t="inlineStr"/>
-      <c r="P98" s="4" t="inlineStr"/>
-      <c r="Q98" s="4" t="inlineStr"/>
-      <c r="R98" s="4" t="inlineStr"/>
-      <c r="S98" s="4" t="inlineStr"/>
-      <c r="T98" s="4" t="inlineStr"/>
-      <c r="U98" s="4" t="inlineStr"/>
-      <c r="V98" s="4" t="inlineStr"/>
-      <c r="W98" s="5" t="inlineStr"/>
-      <c r="X98" s="6" t="n">
-        <v>-64.33333333333331</v>
-      </c>
-      <c r="Y98" s="7" t="n">
-        <v>-0.001532245835744834</v>
-      </c>
+      <c r="A98" s="1" t="n"/>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr"/>
+      <c r="D98" s="8" t="inlineStr"/>
+      <c r="E98" s="8" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr"/>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
+      <c r="J98" s="8" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr"/>
+      <c r="L98" s="8" t="inlineStr"/>
+      <c r="M98" s="8" t="inlineStr"/>
+      <c r="N98" s="8" t="inlineStr"/>
+      <c r="O98" s="8" t="inlineStr">
+        <is>
+          <t>8520.00</t>
+        </is>
+      </c>
+      <c r="P98" s="8" t="inlineStr">
+        <is>
+          <t>11830.00</t>
+        </is>
+      </c>
+      <c r="Q98" s="8" t="inlineStr">
+        <is>
+          <t>16805.00</t>
+        </is>
+      </c>
+      <c r="R98" s="8" t="inlineStr"/>
+      <c r="S98" s="8" t="inlineStr"/>
+      <c r="T98" s="8" t="inlineStr"/>
+      <c r="U98" s="8" t="inlineStr"/>
+      <c r="V98" s="8" t="inlineStr"/>
+      <c r="W98" s="9" t="inlineStr"/>
+      <c r="X98" s="10" t="inlineStr"/>
+      <c r="Y98" s="11" t="inlineStr"/>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>454.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr"/>
       <c r="D99" s="8" t="inlineStr"/>
       <c r="E99" s="8" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr"/>
@@ -5482,7 +5468,7 @@
       <c r="J99" s="8" t="inlineStr"/>
       <c r="K99" s="8" t="inlineStr">
         <is>
-          <t>494.00</t>
+          <t>8195.00</t>
         </is>
       </c>
       <c r="L99" s="8" t="inlineStr"/>
@@ -5490,73 +5476,87 @@
       <c r="N99" s="8" t="inlineStr"/>
       <c r="O99" s="8" t="inlineStr">
         <is>
-          <t>418.00</t>
-        </is>
-      </c>
-      <c r="P99" s="8" t="inlineStr"/>
-      <c r="Q99" s="8" t="inlineStr"/>
+          <t>8325.00</t>
+        </is>
+      </c>
+      <c r="P99" s="8" t="inlineStr">
+        <is>
+          <t>12890.00</t>
+        </is>
+      </c>
+      <c r="Q99" s="8" t="inlineStr">
+        <is>
+          <t>16980.00</t>
+        </is>
+      </c>
       <c r="R99" s="8" t="inlineStr"/>
       <c r="S99" s="8" t="inlineStr"/>
       <c r="T99" s="8" t="inlineStr"/>
-      <c r="U99" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
+      <c r="U99" s="8" t="inlineStr"/>
       <c r="V99" s="8" t="inlineStr"/>
       <c r="W99" s="9" t="n">
-        <v>460.6666666666667</v>
-      </c>
-      <c r="X99" s="10" t="inlineStr"/>
-      <c r="Y99" s="11" t="inlineStr"/>
+        <v>11597.5</v>
+      </c>
+      <c r="X99" s="9" t="n">
+        <v>2661.25</v>
+      </c>
+      <c r="Y99" s="11" t="n">
+        <v>0.3397268143230995</v>
+      </c>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="1" t="n"/>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr"/>
-      <c r="D100" s="8" t="inlineStr"/>
-      <c r="E100" s="8" t="inlineStr"/>
-      <c r="F100" s="8" t="inlineStr"/>
-      <c r="G100" s="8" t="inlineStr"/>
-      <c r="H100" s="8" t="inlineStr"/>
-      <c r="I100" s="8" t="inlineStr"/>
-      <c r="J100" s="8" t="inlineStr"/>
-      <c r="K100" s="8" t="inlineStr"/>
-      <c r="L100" s="8" t="inlineStr"/>
-      <c r="M100" s="8" t="inlineStr"/>
-      <c r="N100" s="8" t="inlineStr"/>
-      <c r="O100" s="8" t="inlineStr">
-        <is>
-          <t>476.00</t>
-        </is>
-      </c>
-      <c r="P100" s="8" t="inlineStr"/>
-      <c r="Q100" s="8" t="inlineStr"/>
-      <c r="R100" s="8" t="inlineStr"/>
-      <c r="S100" s="8" t="inlineStr"/>
-      <c r="T100" s="8" t="inlineStr"/>
-      <c r="U100" s="8" t="inlineStr">
-        <is>
-          <t>557.00</t>
-        </is>
-      </c>
-      <c r="V100" s="8" t="inlineStr"/>
-      <c r="W100" s="9" t="inlineStr"/>
-      <c r="X100" s="10" t="inlineStr"/>
-      <c r="Y100" s="11" t="inlineStr"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Seaquest
+Random: 68.4
+Human: 42054.7</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 525</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr"/>
+      <c r="L100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr"/>
+      <c r="P100" s="4" t="inlineStr"/>
+      <c r="Q100" s="4" t="inlineStr"/>
+      <c r="R100" s="4" t="inlineStr"/>
+      <c r="S100" s="4" t="inlineStr"/>
+      <c r="T100" s="4" t="inlineStr"/>
+      <c r="U100" s="4" t="inlineStr"/>
+      <c r="V100" s="4" t="inlineStr"/>
+      <c r="W100" s="5" t="inlineStr"/>
+      <c r="X100" s="6" t="n">
+        <v>-64.33333333333331</v>
+      </c>
+      <c r="Y100" s="7" t="n">
+        <v>-0.001532245835744834</v>
+      </c>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>454.00</t>
+        </is>
+      </c>
       <c r="D101" s="8" t="inlineStr"/>
       <c r="E101" s="8" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr"/>
@@ -5566,7 +5566,7 @@
       <c r="J101" s="8" t="inlineStr"/>
       <c r="K101" s="8" t="inlineStr">
         <is>
-          <t>521.00</t>
+          <t>494.00</t>
         </is>
       </c>
       <c r="L101" s="8" t="inlineStr"/>
@@ -5574,7 +5574,7 @@
       <c r="N101" s="8" t="inlineStr"/>
       <c r="O101" s="8" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>418.00</t>
         </is>
       </c>
       <c r="P101" s="8" t="inlineStr"/>
@@ -5584,25 +5584,21 @@
       <c r="T101" s="8" t="inlineStr"/>
       <c r="U101" s="8" t="inlineStr">
         <is>
-          <t>545.00</t>
+          <t>470.00</t>
         </is>
       </c>
       <c r="V101" s="8" t="inlineStr"/>
       <c r="W101" s="9" t="n">
-        <v>505.3333333333333</v>
-      </c>
-      <c r="X101" s="9" t="n">
-        <v>44.66666666666663</v>
-      </c>
-      <c r="Y101" s="11" t="n">
-        <v>0.001063839077667397</v>
-      </c>
+        <v>460.6666666666667</v>
+      </c>
+      <c r="X101" s="10" t="inlineStr"/>
+      <c r="Y101" s="11" t="inlineStr"/>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr"/>
@@ -5617,15 +5613,19 @@
       <c r="L102" s="8" t="inlineStr"/>
       <c r="M102" s="8" t="inlineStr"/>
       <c r="N102" s="8" t="inlineStr"/>
-      <c r="O102" s="8" t="inlineStr"/>
+      <c r="O102" s="8" t="inlineStr">
+        <is>
+          <t>476.00</t>
+        </is>
+      </c>
       <c r="P102" s="8" t="inlineStr"/>
       <c r="Q102" s="8" t="inlineStr"/>
       <c r="R102" s="8" t="inlineStr"/>
       <c r="S102" s="8" t="inlineStr"/>
       <c r="T102" s="8" t="inlineStr"/>
-      <c r="U102" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="U102" s="8" t="inlineStr">
+        <is>
+          <t>557.00</t>
         </is>
       </c>
       <c r="V102" s="8" t="inlineStr"/>
@@ -5637,7 +5637,7 @@
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr"/>
@@ -5648,177 +5648,173 @@
       <c r="H103" s="8" t="inlineStr"/>
       <c r="I103" s="8" t="inlineStr"/>
       <c r="J103" s="8" t="inlineStr"/>
-      <c r="K103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="inlineStr">
+        <is>
+          <t>521.00</t>
+        </is>
+      </c>
       <c r="L103" s="8" t="inlineStr"/>
       <c r="M103" s="8" t="inlineStr"/>
       <c r="N103" s="8" t="inlineStr"/>
-      <c r="O103" s="8" t="inlineStr"/>
+      <c r="O103" s="8" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
       <c r="P103" s="8" t="inlineStr"/>
       <c r="Q103" s="8" t="inlineStr"/>
       <c r="R103" s="8" t="inlineStr"/>
       <c r="S103" s="8" t="inlineStr"/>
       <c r="T103" s="8" t="inlineStr"/>
-      <c r="U103" s="12" t="inlineStr">
+      <c r="U103" s="8" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
+      <c r="V103" s="8" t="inlineStr"/>
+      <c r="W103" s="9" t="n">
+        <v>505.3333333333333</v>
+      </c>
+      <c r="X103" s="9" t="n">
+        <v>44.66666666666663</v>
+      </c>
+      <c r="Y103" s="11" t="n">
+        <v>0.001063839077667397</v>
+      </c>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="1" t="n"/>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr"/>
+      <c r="D104" s="8" t="inlineStr"/>
+      <c r="E104" s="8" t="inlineStr"/>
+      <c r="F104" s="8" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr"/>
+      <c r="H104" s="8" t="inlineStr"/>
+      <c r="I104" s="8" t="inlineStr"/>
+      <c r="J104" s="8" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr"/>
+      <c r="L104" s="8" t="inlineStr"/>
+      <c r="M104" s="8" t="inlineStr"/>
+      <c r="N104" s="8" t="inlineStr"/>
+      <c r="O104" s="8" t="inlineStr"/>
+      <c r="P104" s="8" t="inlineStr"/>
+      <c r="Q104" s="8" t="inlineStr"/>
+      <c r="R104" s="8" t="inlineStr"/>
+      <c r="S104" s="8" t="inlineStr"/>
+      <c r="T104" s="8" t="inlineStr"/>
+      <c r="U104" s="12" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="V103" s="8" t="inlineStr"/>
-      <c r="W103" s="9" t="inlineStr"/>
-      <c r="X103" s="10" t="inlineStr"/>
-      <c r="Y103" s="11" t="inlineStr"/>
-    </row>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>UpNDown
-Random: 533.4
-Human: 11693.2</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7985</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr"/>
-      <c r="D104" s="4" t="inlineStr"/>
-      <c r="E104" s="4" t="inlineStr"/>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr"/>
-      <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="4" t="inlineStr"/>
-      <c r="K104" s="4" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr"/>
-      <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr"/>
-      <c r="O104" s="4" t="inlineStr"/>
-      <c r="P104" s="4" t="inlineStr"/>
-      <c r="Q104" s="4" t="inlineStr"/>
-      <c r="R104" s="4" t="inlineStr"/>
-      <c r="S104" s="4" t="inlineStr"/>
-      <c r="T104" s="4" t="inlineStr"/>
-      <c r="U104" s="4" t="inlineStr"/>
-      <c r="V104" s="4" t="inlineStr"/>
-      <c r="W104" s="5" t="inlineStr"/>
-      <c r="X104" s="6" t="n">
-        <v>-2963</v>
-      </c>
-      <c r="Y104" s="7" t="n">
-        <v>-0.2655065502966003</v>
-      </c>
+      <c r="V104" s="8" t="inlineStr"/>
+      <c r="W104" s="9" t="inlineStr"/>
+      <c r="X104" s="10" t="inlineStr"/>
+      <c r="Y104" s="11" t="inlineStr"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>9044.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr"/>
       <c r="D105" s="8" t="inlineStr"/>
       <c r="E105" s="8" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr"/>
       <c r="G105" s="8" t="inlineStr"/>
       <c r="H105" s="8" t="inlineStr"/>
-      <c r="I105" s="8" t="inlineStr">
-        <is>
-          <t>5849.00</t>
-        </is>
-      </c>
+      <c r="I105" s="8" t="inlineStr"/>
       <c r="J105" s="8" t="inlineStr"/>
       <c r="K105" s="8" t="inlineStr"/>
       <c r="L105" s="8" t="inlineStr"/>
       <c r="M105" s="8" t="inlineStr"/>
       <c r="N105" s="8" t="inlineStr"/>
-      <c r="O105" s="8" t="inlineStr">
-        <is>
-          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
-        </is>
-      </c>
-      <c r="P105" s="8" t="inlineStr">
-        <is>
-          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
-        </is>
-      </c>
-      <c r="Q105" s="8" t="inlineStr">
-        <is>
-          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
-        </is>
-      </c>
+      <c r="O105" s="8" t="inlineStr"/>
+      <c r="P105" s="8" t="inlineStr"/>
+      <c r="Q105" s="8" t="inlineStr"/>
       <c r="R105" s="8" t="inlineStr"/>
       <c r="S105" s="8" t="inlineStr"/>
       <c r="T105" s="8" t="inlineStr"/>
-      <c r="U105" s="8" t="inlineStr"/>
+      <c r="U105" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="V105" s="8" t="inlineStr"/>
-      <c r="W105" s="9" t="n">
-        <v>5022</v>
-      </c>
+      <c r="W105" s="9" t="inlineStr"/>
       <c r="X105" s="10" t="inlineStr"/>
       <c r="Y105" s="11" t="inlineStr"/>
     </row>
     <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="1" t="n"/>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr"/>
-      <c r="D106" s="8" t="inlineStr"/>
-      <c r="E106" s="8" t="inlineStr"/>
-      <c r="F106" s="8" t="inlineStr"/>
-      <c r="G106" s="8" t="inlineStr"/>
-      <c r="H106" s="8" t="inlineStr"/>
-      <c r="I106" s="8" t="inlineStr"/>
-      <c r="J106" s="8" t="inlineStr"/>
-      <c r="K106" s="8" t="inlineStr"/>
-      <c r="L106" s="8" t="inlineStr"/>
-      <c r="M106" s="8" t="inlineStr"/>
-      <c r="N106" s="8" t="inlineStr"/>
-      <c r="O106" s="8" t="inlineStr">
-        <is>
-          <t>5670.00</t>
-        </is>
-      </c>
-      <c r="P106" s="8" t="inlineStr">
-        <is>
-          <t>7178.00</t>
-        </is>
-      </c>
-      <c r="Q106" s="8" t="inlineStr">
-        <is>
-          <t>3066.00</t>
-        </is>
-      </c>
-      <c r="R106" s="8" t="inlineStr"/>
-      <c r="S106" s="8" t="inlineStr"/>
-      <c r="T106" s="8" t="inlineStr"/>
-      <c r="U106" s="8" t="inlineStr"/>
-      <c r="V106" s="8" t="inlineStr"/>
-      <c r="W106" s="9" t="inlineStr"/>
-      <c r="X106" s="10" t="inlineStr"/>
-      <c r="Y106" s="11" t="inlineStr"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>UpNDown
+Random: 533.4
+Human: 11693.2</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 7985</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr"/>
+      <c r="J106" s="4" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr"/>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="inlineStr"/>
+      <c r="N106" s="4" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr"/>
+      <c r="P106" s="4" t="inlineStr"/>
+      <c r="Q106" s="4" t="inlineStr"/>
+      <c r="R106" s="4" t="inlineStr"/>
+      <c r="S106" s="4" t="inlineStr"/>
+      <c r="T106" s="4" t="inlineStr"/>
+      <c r="U106" s="4" t="inlineStr"/>
+      <c r="V106" s="4" t="inlineStr"/>
+      <c r="W106" s="5" t="inlineStr"/>
+      <c r="X106" s="6" t="n">
+        <v>-2963</v>
+      </c>
+      <c r="Y106" s="7" t="n">
+        <v>-0.2655065502966003</v>
+      </c>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>9044.00</t>
+        </is>
+      </c>
       <c r="D107" s="8" t="inlineStr"/>
       <c r="E107" s="8" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr"/>
       <c r="G107" s="8" t="inlineStr"/>
       <c r="H107" s="8" t="inlineStr"/>
-      <c r="I107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>5849.00</t>
+        </is>
+      </c>
       <c r="J107" s="8" t="inlineStr"/>
       <c r="K107" s="8" t="inlineStr"/>
       <c r="L107" s="8" t="inlineStr"/>
@@ -5826,17 +5822,17 @@
       <c r="N107" s="8" t="inlineStr"/>
       <c r="O107" s="8" t="inlineStr">
         <is>
-          <t>6043.00</t>
+          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
         </is>
       </c>
       <c r="P107" s="8" t="inlineStr">
         <is>
-          <t>6658.00</t>
+          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
         </is>
       </c>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2974.50</t>
+          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr"/>
@@ -5845,42 +5841,130 @@
       <c r="U107" s="8" t="inlineStr"/>
       <c r="V107" s="8" t="inlineStr"/>
       <c r="W107" s="9" t="n">
+        <v>5022</v>
+      </c>
+      <c r="X107" s="10" t="inlineStr"/>
+      <c r="Y107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="24" customHeight="1">
+      <c r="A108" s="1" t="n"/>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr"/>
+      <c r="D108" s="8" t="inlineStr"/>
+      <c r="E108" s="8" t="inlineStr"/>
+      <c r="F108" s="8" t="inlineStr"/>
+      <c r="G108" s="8" t="inlineStr"/>
+      <c r="H108" s="8" t="inlineStr"/>
+      <c r="I108" s="8" t="inlineStr"/>
+      <c r="J108" s="8" t="inlineStr"/>
+      <c r="K108" s="8" t="inlineStr"/>
+      <c r="L108" s="8" t="inlineStr"/>
+      <c r="M108" s="8" t="inlineStr"/>
+      <c r="N108" s="8" t="inlineStr"/>
+      <c r="O108" s="8" t="inlineStr">
+        <is>
+          <t>5670.00</t>
+        </is>
+      </c>
+      <c r="P108" s="8" t="inlineStr">
+        <is>
+          <t>7178.00</t>
+        </is>
+      </c>
+      <c r="Q108" s="8" t="inlineStr">
+        <is>
+          <t>3066.00</t>
+        </is>
+      </c>
+      <c r="R108" s="8" t="inlineStr"/>
+      <c r="S108" s="8" t="inlineStr"/>
+      <c r="T108" s="8" t="inlineStr"/>
+      <c r="U108" s="8" t="inlineStr"/>
+      <c r="V108" s="8" t="inlineStr"/>
+      <c r="W108" s="9" t="inlineStr"/>
+      <c r="X108" s="10" t="inlineStr"/>
+      <c r="Y108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="1" t="n"/>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr"/>
+      <c r="D109" s="8" t="inlineStr"/>
+      <c r="E109" s="8" t="inlineStr"/>
+      <c r="F109" s="8" t="inlineStr"/>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="8" t="inlineStr"/>
+      <c r="I109" s="8" t="inlineStr"/>
+      <c r="J109" s="8" t="inlineStr"/>
+      <c r="K109" s="8" t="inlineStr"/>
+      <c r="L109" s="8" t="inlineStr"/>
+      <c r="M109" s="8" t="inlineStr"/>
+      <c r="N109" s="8" t="inlineStr"/>
+      <c r="O109" s="8" t="inlineStr">
+        <is>
+          <t>6043.00</t>
+        </is>
+      </c>
+      <c r="P109" s="8" t="inlineStr">
+        <is>
+          <t>6658.00</t>
+        </is>
+      </c>
+      <c r="Q109" s="8" t="inlineStr">
+        <is>
+          <t>2974.50</t>
+        </is>
+      </c>
+      <c r="R109" s="8" t="inlineStr"/>
+      <c r="S109" s="8" t="inlineStr"/>
+      <c r="T109" s="8" t="inlineStr"/>
+      <c r="U109" s="8" t="inlineStr"/>
+      <c r="V109" s="8" t="inlineStr"/>
+      <c r="W109" s="9" t="n">
         <v>5225.166666666667</v>
       </c>
-      <c r="X107" s="9" t="n">
+      <c r="X109" s="9" t="n">
         <v>203.166666666667</v>
       </c>
-      <c r="Y107" s="11" t="n">
+      <c r="Y109" s="11" t="n">
         <v>0.01820522470534122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A98:A103"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="A70:A73"/>
     <mergeCell ref="A39:A44"/>
-    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="A61:A64"/>
     <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A63:A65"/>
     <mergeCell ref="A26:A30"/>
-    <mergeCell ref="A90:A93"/>
     <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A74:A77"/>
     <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A89:A91"/>
     <mergeCell ref="A49:A51"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A55:A60"/>
     <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A84:A86"/>
-    <mergeCell ref="A104:A107"/>
-    <mergeCell ref="A87:A89"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A100:A105"/>
     <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="A106:A109"/>
     <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A80:A82"/>
     <mergeCell ref="A35:A38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="+0.00;-0.00;0.00"/>
     <numFmt numFmtId="165" formatCode="+0.0000;-0.0000;0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +52,14 @@
       <color rgb="00808080"/>
       <sz val="16"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,8 +76,13 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -122,11 +133,26 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0000B050"/>
+      </left>
+      <right style="medium">
+        <color rgb="0000B050"/>
+      </right>
+      <top style="medium">
+        <color rgb="0000B050"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0000B050"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -147,6 +173,7 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,6 +440,16 @@
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q72" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="R72" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
     <comment ref="U72" authorId="0" shapeId="0">
@@ -4143,12 +4180,12 @@
           <t>927.00</t>
         </is>
       </c>
-      <c r="Q72" s="8" t="inlineStr">
+      <c r="Q72" s="14" t="inlineStr">
         <is>
           <t>847.00</t>
         </is>
       </c>
-      <c r="R72" s="8" t="inlineStr">
+      <c r="R72" s="14" t="inlineStr">
         <is>
           <t>2933.00</t>
         </is>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -152,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -174,6 +174,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -256,18 +257,18 @@
     <author>STORM</author>
   </authors>
   <commentList>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>Retrieval 미사용과 target: 16 양쪽에 유효한 점수가 있는 공통 시드만 사용합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드는 제외합니다. 각 시드에 여러 결과가 있으면 첫 번째 점수를 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: Retrieval 미사용의 공통 시드 평균 − STORM 논문 점수.
 target: 16 행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: (Retrieval 미사용 평균 − STORM 논문 점수) / (Human − Random).
 target: 16 행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
@@ -379,9 +380,23 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E68" authorId="0" shapeId="0">
+    <comment ref="O69" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Frostbite, seed 10
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P69" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="V69" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -400,7 +415,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="U70" authorId="0" shapeId="0">
+    <comment ref="V70" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -421,7 +436,22 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="U71" authorId="0" shapeId="0">
+    <comment ref="Q71" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="R71" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="S71" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="V71" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -442,17 +472,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q72" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="R72" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="U72" authorId="0" shapeId="0">
+    <comment ref="V72" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -473,37 +493,9 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="U73" authorId="0" shapeId="0">
+    <comment ref="V73" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K86" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="L86" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K87" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="L87" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -522,35 +514,73 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O102" authorId="0" shapeId="0">
+    <comment ref="K89" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L89" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K90" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L90" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P90" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="L102" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="O104" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O103" authorId="0" shapeId="0">
+    <comment ref="O105" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I105" authorId="0" shapeId="0">
+    <comment ref="I107" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I106" authorId="0" shapeId="0">
+    <comment ref="I108" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I107" authorId="0" shapeId="0">
+    <comment ref="I109" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -850,18 +880,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y121"/>
+  <dimension ref="A1:Z123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
     <col width="54.7" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="19" max="19"/>
-    <col width="3" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="46" customWidth="1" min="24" max="24"/>
-    <col width="32" customWidth="1" min="25" max="25"/>
+    <col width="3" customWidth="1" min="20" max="20"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="46" customWidth="1" min="25" max="25"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -927,33 +957,36 @@
       <c r="R1" s="1" t="n">
         <v>6030</v>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="n">
+        <v>6040</v>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>    </t>
         </is>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>9998</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>9999</v>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>   </t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -992,11 +1025,12 @@
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
       <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="6" t="n">
+      <c r="W2" s="4" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="6" t="n">
         <v>57.79999999999995</v>
       </c>
-      <c r="Y2" s="7" t="n">
+      <c r="Z2" s="7" t="n">
         <v>0.008376932999028966</v>
       </c>
     </row>
@@ -1051,11 +1085,12 @@
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="8" t="inlineStr"/>
       <c r="V3" s="8" t="inlineStr"/>
-      <c r="W3" s="9" t="n">
+      <c r="W3" s="8" t="inlineStr"/>
+      <c r="X3" s="9" t="n">
         <v>1041.8</v>
       </c>
-      <c r="X3" s="10" t="inlineStr"/>
-      <c r="Y3" s="11" t="inlineStr"/>
+      <c r="Y3" s="10" t="inlineStr"/>
+      <c r="Z3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -1100,9 +1135,10 @@
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="8" t="inlineStr"/>
       <c r="V4" s="8" t="inlineStr"/>
-      <c r="W4" s="9" t="inlineStr"/>
-      <c r="X4" s="10" t="inlineStr"/>
-      <c r="Y4" s="11" t="inlineStr"/>
+      <c r="W4" s="8" t="inlineStr"/>
+      <c r="X4" s="9" t="inlineStr"/>
+      <c r="Y4" s="10" t="inlineStr"/>
+      <c r="Z4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -1151,13 +1187,14 @@
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="8" t="inlineStr"/>
       <c r="V5" s="8" t="inlineStr"/>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="inlineStr"/>
+      <c r="X5" s="9" t="n">
         <v>1091.1</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="Y5" s="9" t="n">
         <v>49.29999999999995</v>
       </c>
-      <c r="Y5" s="11" t="n">
+      <c r="Z5" s="11" t="n">
         <v>0.007145031087407058</v>
       </c>
     </row>
@@ -1192,9 +1229,10 @@
       <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="8" t="inlineStr"/>
       <c r="V6" s="8" t="inlineStr"/>
-      <c r="W6" s="9" t="inlineStr"/>
-      <c r="X6" s="10" t="inlineStr"/>
-      <c r="Y6" s="11" t="inlineStr"/>
+      <c r="W6" s="8" t="inlineStr"/>
+      <c r="X6" s="9" t="inlineStr"/>
+      <c r="Y6" s="10" t="inlineStr"/>
+      <c r="Z6" s="11" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="1" t="n"/>
@@ -1211,9 +1249,9 @@
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>1066.50</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr"/>
@@ -1227,9 +1265,10 @@
       <c r="T7" s="8" t="inlineStr"/>
       <c r="U7" s="8" t="inlineStr"/>
       <c r="V7" s="8" t="inlineStr"/>
-      <c r="W7" s="9" t="inlineStr"/>
-      <c r="X7" s="10" t="inlineStr"/>
-      <c r="Y7" s="11" t="inlineStr"/>
+      <c r="W7" s="8" t="inlineStr"/>
+      <c r="X7" s="9" t="inlineStr"/>
+      <c r="Y7" s="10" t="inlineStr"/>
+      <c r="Z7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1264,11 +1303,12 @@
       <c r="T8" s="4" t="inlineStr"/>
       <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="6" t="n">
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="6" t="n">
         <v>2.849999999999994</v>
       </c>
-      <c r="Y8" s="7" t="n">
+      <c r="Z8" s="7" t="n">
         <v>0.001663068214973446</v>
       </c>
     </row>
@@ -1323,11 +1363,12 @@
       <c r="T9" s="8" t="inlineStr"/>
       <c r="U9" s="8" t="inlineStr"/>
       <c r="V9" s="8" t="inlineStr"/>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="8" t="inlineStr"/>
+      <c r="X9" s="9" t="n">
         <v>207.85</v>
       </c>
-      <c r="X9" s="10" t="inlineStr"/>
-      <c r="Y9" s="11" t="inlineStr"/>
+      <c r="Y9" s="10" t="inlineStr"/>
+      <c r="Z9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -1372,9 +1413,10 @@
       <c r="T10" s="8" t="inlineStr"/>
       <c r="U10" s="8" t="inlineStr"/>
       <c r="V10" s="8" t="inlineStr"/>
-      <c r="W10" s="9" t="inlineStr"/>
-      <c r="X10" s="10" t="inlineStr"/>
-      <c r="Y10" s="11" t="inlineStr"/>
+      <c r="W10" s="8" t="inlineStr"/>
+      <c r="X10" s="9" t="inlineStr"/>
+      <c r="Y10" s="10" t="inlineStr"/>
+      <c r="Z10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="1" t="n"/>
@@ -1423,13 +1465,14 @@
       <c r="T11" s="8" t="inlineStr"/>
       <c r="U11" s="8" t="inlineStr"/>
       <c r="V11" s="8" t="inlineStr"/>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="inlineStr"/>
+      <c r="X11" s="9" t="n">
         <v>164.88</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="Y11" s="9" t="n">
         <v>42.96999999999997</v>
       </c>
-      <c r="Y11" s="11" t="n">
+      <c r="Z11" s="11" t="n">
         <v>-0.02507440042014353</v>
       </c>
     </row>
@@ -1464,9 +1507,10 @@
       <c r="T12" s="8" t="inlineStr"/>
       <c r="U12" s="8" t="inlineStr"/>
       <c r="V12" s="8" t="inlineStr"/>
-      <c r="W12" s="9" t="inlineStr"/>
-      <c r="X12" s="10" t="inlineStr"/>
-      <c r="Y12" s="11" t="inlineStr"/>
+      <c r="W12" s="8" t="inlineStr"/>
+      <c r="X12" s="9" t="inlineStr"/>
+      <c r="Y12" s="10" t="inlineStr"/>
+      <c r="Z12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -1499,9 +1543,10 @@
       <c r="T13" s="8" t="inlineStr"/>
       <c r="U13" s="8" t="inlineStr"/>
       <c r="V13" s="8" t="inlineStr"/>
-      <c r="W13" s="9" t="inlineStr"/>
-      <c r="X13" s="10" t="inlineStr"/>
-      <c r="Y13" s="11" t="inlineStr"/>
+      <c r="W13" s="8" t="inlineStr"/>
+      <c r="X13" s="9" t="inlineStr"/>
+      <c r="Y13" s="10" t="inlineStr"/>
+      <c r="Z13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1536,11 +1581,12 @@
       <c r="T14" s="4" t="inlineStr"/>
       <c r="U14" s="4" t="inlineStr"/>
       <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="5" t="inlineStr"/>
-      <c r="X14" s="6" t="n">
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="6" t="n">
         <v>-22.95000000000005</v>
       </c>
-      <c r="Y14" s="7" t="n">
+      <c r="Z14" s="7" t="n">
         <v>-0.04416859122401856</v>
       </c>
     </row>
@@ -1595,11 +1641,12 @@
       <c r="T15" s="8" t="inlineStr"/>
       <c r="U15" s="8" t="inlineStr"/>
       <c r="V15" s="8" t="inlineStr"/>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="inlineStr"/>
+      <c r="X15" s="9" t="n">
         <v>778.05</v>
       </c>
-      <c r="X15" s="10" t="inlineStr"/>
-      <c r="Y15" s="11" t="inlineStr"/>
+      <c r="Y15" s="10" t="inlineStr"/>
+      <c r="Z15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -1644,9 +1691,10 @@
       <c r="T16" s="8" t="inlineStr"/>
       <c r="U16" s="8" t="inlineStr"/>
       <c r="V16" s="8" t="inlineStr"/>
-      <c r="W16" s="9" t="inlineStr"/>
-      <c r="X16" s="10" t="inlineStr"/>
-      <c r="Y16" s="11" t="inlineStr"/>
+      <c r="W16" s="8" t="inlineStr"/>
+      <c r="X16" s="9" t="inlineStr"/>
+      <c r="Y16" s="10" t="inlineStr"/>
+      <c r="Z16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -1707,13 +1755,14 @@
       <c r="T17" s="8" t="inlineStr"/>
       <c r="U17" s="8" t="inlineStr"/>
       <c r="V17" s="8" t="inlineStr"/>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="8" t="inlineStr"/>
+      <c r="X17" s="9" t="n">
         <v>705.5400000000001</v>
       </c>
-      <c r="X17" s="9" t="n">
+      <c r="Y17" s="9" t="n">
         <v>72.50999999999988</v>
       </c>
-      <c r="Y17" s="11" t="n">
+      <c r="Z17" s="11" t="n">
         <v>-0.1395496535796764</v>
       </c>
     </row>
@@ -1748,9 +1797,10 @@
       <c r="T18" s="8" t="inlineStr"/>
       <c r="U18" s="8" t="inlineStr"/>
       <c r="V18" s="8" t="inlineStr"/>
-      <c r="W18" s="9" t="inlineStr"/>
-      <c r="X18" s="10" t="inlineStr"/>
-      <c r="Y18" s="11" t="inlineStr"/>
+      <c r="W18" s="8" t="inlineStr"/>
+      <c r="X18" s="9" t="inlineStr"/>
+      <c r="Y18" s="10" t="inlineStr"/>
+      <c r="Z18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
@@ -1783,9 +1833,10 @@
       <c r="T19" s="8" t="inlineStr"/>
       <c r="U19" s="8" t="inlineStr"/>
       <c r="V19" s="8" t="inlineStr"/>
-      <c r="W19" s="9" t="inlineStr"/>
-      <c r="X19" s="10" t="inlineStr"/>
-      <c r="Y19" s="11" t="inlineStr"/>
+      <c r="W19" s="8" t="inlineStr"/>
+      <c r="X19" s="9" t="inlineStr"/>
+      <c r="Y19" s="10" t="inlineStr"/>
+      <c r="Z19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1820,11 +1871,12 @@
       <c r="T20" s="4" t="inlineStr"/>
       <c r="U20" s="4" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr"/>
-      <c r="W20" s="5" t="inlineStr"/>
-      <c r="X20" s="6" t="n">
+      <c r="W20" s="4" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="6" t="n">
         <v>-350.5</v>
       </c>
-      <c r="Y20" s="7" t="n">
+      <c r="Z20" s="7" t="n">
         <v>-0.04226303160382478</v>
       </c>
     </row>
@@ -1875,11 +1927,12 @@
       <c r="T21" s="8" t="inlineStr"/>
       <c r="U21" s="8" t="inlineStr"/>
       <c r="V21" s="8" t="inlineStr"/>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="inlineStr"/>
+      <c r="X21" s="9" t="n">
         <v>677.5</v>
       </c>
-      <c r="X21" s="10" t="inlineStr"/>
-      <c r="Y21" s="11" t="inlineStr"/>
+      <c r="Y21" s="10" t="inlineStr"/>
+      <c r="Z21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="1" t="n"/>
@@ -1920,9 +1973,10 @@
       <c r="T22" s="8" t="inlineStr"/>
       <c r="U22" s="8" t="inlineStr"/>
       <c r="V22" s="8" t="inlineStr"/>
-      <c r="W22" s="9" t="inlineStr"/>
-      <c r="X22" s="10" t="inlineStr"/>
-      <c r="Y22" s="11" t="inlineStr"/>
+      <c r="W22" s="8" t="inlineStr"/>
+      <c r="X22" s="9" t="inlineStr"/>
+      <c r="Y22" s="10" t="inlineStr"/>
+      <c r="Z22" s="11" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="1" t="n"/>
@@ -1967,13 +2021,14 @@
       <c r="T23" s="8" t="inlineStr"/>
       <c r="U23" s="8" t="inlineStr"/>
       <c r="V23" s="8" t="inlineStr"/>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="inlineStr"/>
+      <c r="X23" s="9" t="n">
         <v>759.375</v>
       </c>
-      <c r="X23" s="9" t="n">
+      <c r="Y23" s="9" t="n">
         <v>81.875</v>
       </c>
-      <c r="Y23" s="11" t="n">
+      <c r="Z23" s="11" t="n">
         <v>0.009872427139980468</v>
       </c>
     </row>
@@ -2008,9 +2063,10 @@
       <c r="T24" s="8" t="inlineStr"/>
       <c r="U24" s="8" t="inlineStr"/>
       <c r="V24" s="8" t="inlineStr"/>
-      <c r="W24" s="9" t="inlineStr"/>
-      <c r="X24" s="10" t="inlineStr"/>
-      <c r="Y24" s="11" t="inlineStr"/>
+      <c r="W24" s="8" t="inlineStr"/>
+      <c r="X24" s="9" t="inlineStr"/>
+      <c r="Y24" s="10" t="inlineStr"/>
+      <c r="Z24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -2043,9 +2099,10 @@
       <c r="T25" s="8" t="inlineStr"/>
       <c r="U25" s="8" t="inlineStr"/>
       <c r="V25" s="8" t="inlineStr"/>
-      <c r="W25" s="9" t="inlineStr"/>
-      <c r="X25" s="10" t="inlineStr"/>
-      <c r="Y25" s="11" t="inlineStr"/>
+      <c r="W25" s="8" t="inlineStr"/>
+      <c r="X25" s="9" t="inlineStr"/>
+      <c r="Y25" s="10" t="inlineStr"/>
+      <c r="Z25" s="11" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2080,11 +2137,12 @@
       <c r="T26" s="4" t="inlineStr"/>
       <c r="U26" s="4" t="inlineStr"/>
       <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="5" t="inlineStr"/>
-      <c r="X26" s="6" t="n">
+      <c r="W26" s="4" t="inlineStr"/>
+      <c r="X26" s="5" t="inlineStr"/>
+      <c r="Y26" s="6" t="n">
         <v>-84.75</v>
       </c>
-      <c r="Y26" s="7" t="n">
+      <c r="Z26" s="7" t="n">
         <v>-0.1146975233455136</v>
       </c>
     </row>
@@ -2136,22 +2194,23 @@
       </c>
       <c r="R27" s="8" t="inlineStr"/>
       <c r="S27" s="8" t="inlineStr"/>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="T27" s="8" t="inlineStr"/>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>694.50</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
+      <c r="V27" s="8" t="inlineStr">
         <is>
           <t>668.50</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr"/>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="8" t="inlineStr"/>
+      <c r="X27" s="9" t="n">
         <v>556.25</v>
       </c>
-      <c r="X27" s="10" t="inlineStr"/>
-      <c r="Y27" s="11" t="inlineStr"/>
+      <c r="Y27" s="10" t="inlineStr"/>
+      <c r="Z27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -2178,15 +2237,16 @@
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr"/>
       <c r="T28" s="8" t="inlineStr"/>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr"/>
+      <c r="V28" s="8" t="inlineStr">
         <is>
           <t>507.50</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr"/>
-      <c r="W28" s="9" t="inlineStr"/>
-      <c r="X28" s="10" t="inlineStr"/>
-      <c r="Y28" s="11" t="inlineStr"/>
+      <c r="W28" s="8" t="inlineStr"/>
+      <c r="X28" s="9" t="inlineStr"/>
+      <c r="Y28" s="10" t="inlineStr"/>
+      <c r="Z28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -2224,24 +2284,25 @@
       </c>
       <c r="R29" s="8" t="inlineStr"/>
       <c r="S29" s="8" t="inlineStr"/>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="T29" s="8" t="inlineStr"/>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>566.00</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t>565.00</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr"/>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="8" t="inlineStr"/>
+      <c r="X29" s="9" t="n">
         <v>483.5</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="Y29" s="9" t="n">
         <v>72.75</v>
       </c>
-      <c r="Y29" s="11" t="n">
+      <c r="Z29" s="11" t="n">
         <v>-0.09845716605765327</v>
       </c>
     </row>
@@ -2278,11 +2339,12 @@
       <c r="T30" s="4" t="inlineStr"/>
       <c r="U30" s="4" t="inlineStr"/>
       <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="5" t="inlineStr"/>
-      <c r="X30" s="6" t="n">
+      <c r="W30" s="4" t="inlineStr"/>
+      <c r="X30" s="5" t="inlineStr"/>
+      <c r="Y30" s="6" t="n">
         <v>-2710</v>
       </c>
-      <c r="Y30" s="7" t="n">
+      <c r="Z30" s="7" t="n">
         <v>-0.07781207379226186</v>
       </c>
     </row>
@@ -2337,11 +2399,12 @@
       <c r="T31" s="8" t="inlineStr"/>
       <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr"/>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="8" t="inlineStr"/>
+      <c r="X31" s="9" t="n">
         <v>10830</v>
       </c>
-      <c r="X31" s="10" t="inlineStr"/>
-      <c r="Y31" s="11" t="inlineStr"/>
+      <c r="Y31" s="10" t="inlineStr"/>
+      <c r="Z31" s="11" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="1" t="n"/>
@@ -2390,9 +2453,10 @@
       <c r="T32" s="8" t="inlineStr"/>
       <c r="U32" s="8" t="inlineStr"/>
       <c r="V32" s="8" t="inlineStr"/>
-      <c r="W32" s="9" t="inlineStr"/>
-      <c r="X32" s="10" t="inlineStr"/>
-      <c r="Y32" s="11" t="inlineStr"/>
+      <c r="W32" s="8" t="inlineStr"/>
+      <c r="X32" s="9" t="inlineStr"/>
+      <c r="Y32" s="10" t="inlineStr"/>
+      <c r="Z32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="1" t="n"/>
@@ -2445,13 +2509,14 @@
       <c r="T33" s="8" t="inlineStr"/>
       <c r="U33" s="8" t="inlineStr"/>
       <c r="V33" s="8" t="inlineStr"/>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="inlineStr"/>
+      <c r="X33" s="9" t="n">
         <v>11600</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="Y33" s="9" t="n">
         <v>770</v>
       </c>
-      <c r="Y33" s="11" t="n">
+      <c r="Z33" s="11" t="n">
         <v>0.02210896561625153</v>
       </c>
     </row>
@@ -2486,9 +2551,10 @@
       <c r="T34" s="8" t="inlineStr"/>
       <c r="U34" s="8" t="inlineStr"/>
       <c r="V34" s="8" t="inlineStr"/>
-      <c r="W34" s="9" t="inlineStr"/>
-      <c r="X34" s="10" t="inlineStr"/>
-      <c r="Y34" s="11" t="inlineStr"/>
+      <c r="W34" s="8" t="inlineStr"/>
+      <c r="X34" s="9" t="inlineStr"/>
+      <c r="Y34" s="10" t="inlineStr"/>
+      <c r="Z34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="1" t="n"/>
@@ -2521,9 +2587,10 @@
       <c r="T35" s="8" t="inlineStr"/>
       <c r="U35" s="8" t="inlineStr"/>
       <c r="V35" s="8" t="inlineStr"/>
-      <c r="W35" s="9" t="inlineStr"/>
-      <c r="X35" s="10" t="inlineStr"/>
-      <c r="Y35" s="11" t="inlineStr"/>
+      <c r="W35" s="8" t="inlineStr"/>
+      <c r="X35" s="9" t="inlineStr"/>
+      <c r="Y35" s="10" t="inlineStr"/>
+      <c r="Z35" s="11" t="inlineStr"/>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -2558,11 +2625,12 @@
       <c r="T36" s="4" t="inlineStr"/>
       <c r="U36" s="4" t="inlineStr"/>
       <c r="V36" s="4" t="inlineStr"/>
-      <c r="W36" s="5" t="inlineStr"/>
-      <c r="X36" s="6" t="n">
+      <c r="W36" s="4" t="inlineStr"/>
+      <c r="X36" s="5" t="inlineStr"/>
+      <c r="Y36" s="6" t="n">
         <v>-1.350000000000009</v>
       </c>
-      <c r="Y36" s="7" t="n">
+      <c r="Z36" s="7" t="n">
         <v>-0.1125000000000007</v>
       </c>
     </row>
@@ -2621,11 +2689,12 @@
       <c r="T37" s="8" t="inlineStr"/>
       <c r="U37" s="8" t="inlineStr"/>
       <c r="V37" s="8" t="inlineStr"/>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="inlineStr"/>
+      <c r="X37" s="9" t="n">
         <v>78.64999999999999</v>
       </c>
-      <c r="X37" s="10" t="inlineStr"/>
-      <c r="Y37" s="11" t="inlineStr"/>
+      <c r="Y37" s="10" t="inlineStr"/>
+      <c r="Z37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="1" t="n"/>
@@ -2658,9 +2727,10 @@
       <c r="T38" s="8" t="inlineStr"/>
       <c r="U38" s="8" t="inlineStr"/>
       <c r="V38" s="8" t="inlineStr"/>
-      <c r="W38" s="9" t="inlineStr"/>
-      <c r="X38" s="10" t="inlineStr"/>
-      <c r="Y38" s="11" t="inlineStr"/>
+      <c r="W38" s="8" t="inlineStr"/>
+      <c r="X38" s="9" t="inlineStr"/>
+      <c r="Y38" s="10" t="inlineStr"/>
+      <c r="Z38" s="11" t="inlineStr"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="1" t="n"/>
@@ -2709,13 +2779,14 @@
       <c r="T39" s="8" t="inlineStr"/>
       <c r="U39" s="8" t="inlineStr"/>
       <c r="V39" s="8" t="inlineStr"/>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="inlineStr"/>
+      <c r="X39" s="9" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="Y39" s="9" t="n">
         <v>3.250000000000014</v>
       </c>
-      <c r="Y39" s="11" t="n">
+      <c r="Z39" s="11" t="n">
         <v>0.2708333333333345</v>
       </c>
     </row>
@@ -2752,11 +2823,12 @@
       <c r="T40" s="4" t="inlineStr"/>
       <c r="U40" s="4" t="inlineStr"/>
       <c r="V40" s="4" t="inlineStr"/>
-      <c r="W40" s="5" t="inlineStr"/>
-      <c r="X40" s="6" t="n">
+      <c r="W40" s="4" t="inlineStr"/>
+      <c r="X40" s="5" t="inlineStr"/>
+      <c r="Y40" s="6" t="n">
         <v>-4.266666666666666</v>
       </c>
-      <c r="Y40" s="7" t="n">
+      <c r="Z40" s="7" t="n">
         <v>-0.1481481481481481</v>
       </c>
     </row>
@@ -2807,11 +2879,12 @@
       <c r="T41" s="8" t="inlineStr"/>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="inlineStr"/>
+      <c r="X41" s="9" t="n">
         <v>11.73333333333333</v>
       </c>
-      <c r="X41" s="10" t="inlineStr"/>
-      <c r="Y41" s="11" t="inlineStr"/>
+      <c r="Y41" s="10" t="inlineStr"/>
+      <c r="Z41" s="11" t="inlineStr"/>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="1" t="n"/>
@@ -2852,9 +2925,10 @@
       <c r="T42" s="8" t="inlineStr"/>
       <c r="U42" s="8" t="inlineStr"/>
       <c r="V42" s="8" t="inlineStr"/>
-      <c r="W42" s="9" t="inlineStr"/>
-      <c r="X42" s="10" t="inlineStr"/>
-      <c r="Y42" s="11" t="inlineStr"/>
+      <c r="W42" s="8" t="inlineStr"/>
+      <c r="X42" s="9" t="inlineStr"/>
+      <c r="Y42" s="10" t="inlineStr"/>
+      <c r="Z42" s="11" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
@@ -2895,13 +2969,14 @@
       <c r="T43" s="8" t="inlineStr"/>
       <c r="U43" s="8" t="inlineStr"/>
       <c r="V43" s="8" t="inlineStr"/>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="8" t="inlineStr"/>
+      <c r="X43" s="9" t="n">
         <v>12.36666666666667</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="Y43" s="9" t="n">
         <v>0.6333333333333311</v>
       </c>
-      <c r="Y43" s="11" t="n">
+      <c r="Z43" s="11" t="n">
         <v>0.02199074074074066</v>
       </c>
     </row>
@@ -2938,11 +3013,12 @@
       <c r="T44" s="4" t="inlineStr"/>
       <c r="U44" s="4" t="inlineStr"/>
       <c r="V44" s="4" t="inlineStr"/>
-      <c r="W44" s="5" t="inlineStr"/>
-      <c r="X44" s="6" t="n">
+      <c r="W44" s="4" t="inlineStr"/>
+      <c r="X44" s="5" t="inlineStr"/>
+      <c r="Y44" s="6" t="n">
         <v>-289.6666666666667</v>
       </c>
-      <c r="Y44" s="7" t="n">
+      <c r="Z44" s="7" t="n">
         <v>-0.04404370920001623</v>
       </c>
     </row>
@@ -2993,11 +3069,12 @@
       <c r="T45" s="8" t="inlineStr"/>
       <c r="U45" s="8" t="inlineStr"/>
       <c r="V45" s="8" t="inlineStr"/>
-      <c r="W45" s="9" t="n">
+      <c r="W45" s="8" t="inlineStr"/>
+      <c r="X45" s="9" t="n">
         <v>1598.333333333333</v>
       </c>
-      <c r="X45" s="10" t="inlineStr"/>
-      <c r="Y45" s="11" t="inlineStr"/>
+      <c r="Y45" s="10" t="inlineStr"/>
+      <c r="Z45" s="11" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="1" t="n"/>
@@ -3030,9 +3107,10 @@
       <c r="T46" s="8" t="inlineStr"/>
       <c r="U46" s="8" t="inlineStr"/>
       <c r="V46" s="8" t="inlineStr"/>
-      <c r="W46" s="9" t="inlineStr"/>
-      <c r="X46" s="10" t="inlineStr"/>
-      <c r="Y46" s="11" t="inlineStr"/>
+      <c r="W46" s="8" t="inlineStr"/>
+      <c r="X46" s="9" t="inlineStr"/>
+      <c r="Y46" s="10" t="inlineStr"/>
+      <c r="Z46" s="11" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="1" t="n"/>
@@ -3073,13 +3151,14 @@
       <c r="T47" s="8" t="inlineStr"/>
       <c r="U47" s="8" t="inlineStr"/>
       <c r="V47" s="8" t="inlineStr"/>
-      <c r="W47" s="9" t="n">
+      <c r="W47" s="8" t="inlineStr"/>
+      <c r="X47" s="9" t="n">
         <v>1225</v>
       </c>
-      <c r="X47" s="9" t="n">
+      <c r="Y47" s="9" t="n">
         <v>373.3333333333333</v>
       </c>
-      <c r="Y47" s="11" t="n">
+      <c r="Z47" s="11" t="n">
         <v>-0.05676519482625794</v>
       </c>
     </row>
@@ -3114,9 +3193,10 @@
       <c r="T48" s="8" t="inlineStr"/>
       <c r="U48" s="8" t="inlineStr"/>
       <c r="V48" s="8" t="inlineStr"/>
-      <c r="W48" s="9" t="inlineStr"/>
-      <c r="X48" s="10" t="inlineStr"/>
-      <c r="Y48" s="11" t="inlineStr"/>
+      <c r="W48" s="8" t="inlineStr"/>
+      <c r="X48" s="9" t="inlineStr"/>
+      <c r="Y48" s="10" t="inlineStr"/>
+      <c r="Z48" s="11" t="inlineStr"/>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="1" t="n"/>
@@ -3149,9 +3229,10 @@
       <c r="T49" s="8" t="inlineStr"/>
       <c r="U49" s="8" t="inlineStr"/>
       <c r="V49" s="8" t="inlineStr"/>
-      <c r="W49" s="9" t="inlineStr"/>
-      <c r="X49" s="10" t="inlineStr"/>
-      <c r="Y49" s="11" t="inlineStr"/>
+      <c r="W49" s="8" t="inlineStr"/>
+      <c r="X49" s="9" t="inlineStr"/>
+      <c r="Y49" s="10" t="inlineStr"/>
+      <c r="Z49" s="11" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -3186,11 +3267,12 @@
       <c r="T50" s="4" t="inlineStr"/>
       <c r="U50" s="4" t="inlineStr"/>
       <c r="V50" s="4" t="inlineStr"/>
-      <c r="W50" s="5" t="inlineStr"/>
-      <c r="X50" s="6" t="n">
+      <c r="W50" s="4" t="inlineStr"/>
+      <c r="X50" s="5" t="inlineStr"/>
+      <c r="Y50" s="6" t="n">
         <v>-9204.333333333336</v>
       </c>
-      <c r="Y50" s="7" t="n">
+      <c r="Z50" s="7" t="n">
         <v>-0.3674545921510859</v>
       </c>
     </row>
@@ -3241,11 +3323,12 @@
       <c r="T51" s="8" t="inlineStr"/>
       <c r="U51" s="8" t="inlineStr"/>
       <c r="V51" s="8" t="inlineStr"/>
-      <c r="W51" s="9" t="n">
+      <c r="W51" s="8" t="inlineStr"/>
+      <c r="X51" s="9" t="n">
         <v>57571.66666666666</v>
       </c>
-      <c r="X51" s="10" t="inlineStr"/>
-      <c r="Y51" s="11" t="inlineStr"/>
+      <c r="Y51" s="10" t="inlineStr"/>
+      <c r="Z51" s="11" t="inlineStr"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="1" t="n"/>
@@ -3278,9 +3361,10 @@
       <c r="T52" s="8" t="inlineStr"/>
       <c r="U52" s="8" t="inlineStr"/>
       <c r="V52" s="8" t="inlineStr"/>
-      <c r="W52" s="9" t="inlineStr"/>
-      <c r="X52" s="10" t="inlineStr"/>
-      <c r="Y52" s="11" t="inlineStr"/>
+      <c r="W52" s="8" t="inlineStr"/>
+      <c r="X52" s="9" t="inlineStr"/>
+      <c r="Y52" s="10" t="inlineStr"/>
+      <c r="Z52" s="11" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="1" t="n"/>
@@ -3321,13 +3405,14 @@
       <c r="T53" s="8" t="inlineStr"/>
       <c r="U53" s="8" t="inlineStr"/>
       <c r="V53" s="8" t="inlineStr"/>
-      <c r="W53" s="9" t="n">
+      <c r="W53" s="8" t="inlineStr"/>
+      <c r="X53" s="9" t="n">
         <v>57908.33333333334</v>
       </c>
-      <c r="X53" s="9" t="n">
+      <c r="Y53" s="9" t="n">
         <v>336.6666666666715</v>
       </c>
-      <c r="Y53" s="11" t="n">
+      <c r="Z53" s="11" t="n">
         <v>0.01344037728869018</v>
       </c>
     </row>
@@ -3364,11 +3449,12 @@
       <c r="T54" s="4" t="inlineStr"/>
       <c r="U54" s="4" t="inlineStr"/>
       <c r="V54" s="4" t="inlineStr"/>
-      <c r="W54" s="5" t="inlineStr"/>
-      <c r="X54" s="6" t="n">
+      <c r="W54" s="4" t="inlineStr"/>
+      <c r="X54" s="5" t="inlineStr"/>
+      <c r="Y54" s="6" t="n">
         <v>30.58333333333334</v>
       </c>
-      <c r="Y54" s="7" t="n">
+      <c r="Z54" s="7" t="n">
         <v>0.01681419172760094</v>
       </c>
     </row>
@@ -3419,11 +3505,12 @@
       <c r="T55" s="8" t="inlineStr"/>
       <c r="U55" s="8" t="inlineStr"/>
       <c r="V55" s="8" t="inlineStr"/>
-      <c r="W55" s="9" t="n">
+      <c r="W55" s="8" t="inlineStr"/>
+      <c r="X55" s="9" t="n">
         <v>195.5833333333333</v>
       </c>
-      <c r="X55" s="10" t="inlineStr"/>
-      <c r="Y55" s="11" t="inlineStr"/>
+      <c r="Y55" s="10" t="inlineStr"/>
+      <c r="Z55" s="11" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="1" t="n"/>
@@ -3456,9 +3543,10 @@
       <c r="T56" s="8" t="inlineStr"/>
       <c r="U56" s="8" t="inlineStr"/>
       <c r="V56" s="8" t="inlineStr"/>
-      <c r="W56" s="9" t="inlineStr"/>
-      <c r="X56" s="10" t="inlineStr"/>
-      <c r="Y56" s="11" t="inlineStr"/>
+      <c r="W56" s="8" t="inlineStr"/>
+      <c r="X56" s="9" t="inlineStr"/>
+      <c r="Y56" s="10" t="inlineStr"/>
+      <c r="Z56" s="11" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="1" t="n"/>
@@ -3499,13 +3587,14 @@
       <c r="T57" s="8" t="inlineStr"/>
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr"/>
-      <c r="W57" s="9" t="n">
+      <c r="W57" s="8" t="inlineStr"/>
+      <c r="X57" s="9" t="n">
         <v>157.0833333333333</v>
       </c>
-      <c r="X57" s="9" t="n">
+      <c r="Y57" s="9" t="n">
         <v>38.5</v>
       </c>
-      <c r="Y57" s="11" t="n">
+      <c r="Z57" s="11" t="n">
         <v>-0.02116663917752488</v>
       </c>
     </row>
@@ -3540,9 +3629,10 @@
       <c r="T58" s="8" t="inlineStr"/>
       <c r="U58" s="8" t="inlineStr"/>
       <c r="V58" s="8" t="inlineStr"/>
-      <c r="W58" s="9" t="inlineStr"/>
-      <c r="X58" s="10" t="inlineStr"/>
-      <c r="Y58" s="11" t="inlineStr"/>
+      <c r="W58" s="8" t="inlineStr"/>
+      <c r="X58" s="9" t="inlineStr"/>
+      <c r="Y58" s="10" t="inlineStr"/>
+      <c r="Z58" s="11" t="inlineStr"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="1" t="n"/>
@@ -3575,9 +3665,10 @@
       <c r="T59" s="8" t="inlineStr"/>
       <c r="U59" s="8" t="inlineStr"/>
       <c r="V59" s="8" t="inlineStr"/>
-      <c r="W59" s="9" t="inlineStr"/>
-      <c r="X59" s="10" t="inlineStr"/>
-      <c r="Y59" s="11" t="inlineStr"/>
+      <c r="W59" s="8" t="inlineStr"/>
+      <c r="X59" s="9" t="inlineStr"/>
+      <c r="Y59" s="10" t="inlineStr"/>
+      <c r="Z59" s="11" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -3612,11 +3703,12 @@
       <c r="T60" s="4" t="inlineStr"/>
       <c r="U60" s="4" t="inlineStr"/>
       <c r="V60" s="4" t="inlineStr"/>
-      <c r="W60" s="5" t="inlineStr"/>
-      <c r="X60" s="6" t="n">
+      <c r="W60" s="4" t="inlineStr"/>
+      <c r="X60" s="5" t="inlineStr"/>
+      <c r="Y60" s="6" t="n">
         <v>-0.7000000000000028</v>
       </c>
-      <c r="Y60" s="7" t="n">
+      <c r="Z60" s="7" t="n">
         <v>-0.02364864864864874</v>
       </c>
     </row>
@@ -3653,21 +3745,18 @@
           <t>32.75</t>
         </is>
       </c>
-      <c r="Q61" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="Q61" s="8" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr"/>
       <c r="T61" s="8" t="inlineStr"/>
       <c r="U61" s="8" t="inlineStr"/>
       <c r="V61" s="8" t="inlineStr"/>
-      <c r="W61" s="9" t="n">
+      <c r="W61" s="8" t="inlineStr"/>
+      <c r="X61" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="X61" s="10" t="inlineStr"/>
-      <c r="Y61" s="11" t="inlineStr"/>
+      <c r="Y61" s="10" t="inlineStr"/>
+      <c r="Z61" s="11" t="inlineStr"/>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="1" t="n"/>
@@ -3708,13 +3797,14 @@
       <c r="T62" s="8" t="inlineStr"/>
       <c r="U62" s="8" t="inlineStr"/>
       <c r="V62" s="8" t="inlineStr"/>
-      <c r="W62" s="9" t="n">
+      <c r="W62" s="8" t="inlineStr"/>
+      <c r="X62" s="9" t="n">
         <v>33.15</v>
       </c>
-      <c r="X62" s="9" t="n">
+      <c r="Y62" s="9" t="n">
         <v>0.1499999999999986</v>
       </c>
-      <c r="Y62" s="11" t="n">
+      <c r="Z62" s="11" t="n">
         <v>-0.005067567567567519</v>
       </c>
     </row>
@@ -3751,11 +3841,12 @@
       <c r="T63" s="4" t="inlineStr"/>
       <c r="U63" s="4" t="inlineStr"/>
       <c r="V63" s="4" t="inlineStr"/>
-      <c r="W63" s="5" t="inlineStr"/>
-      <c r="X63" s="6" t="n">
+      <c r="W63" s="4" t="inlineStr"/>
+      <c r="X63" s="5" t="inlineStr"/>
+      <c r="Y63" s="6" t="n">
         <v>426.375</v>
       </c>
-      <c r="Y63" s="7" t="n">
+      <c r="Z63" s="7" t="n">
         <v>0.09986532380840848</v>
       </c>
     </row>
@@ -3806,11 +3897,12 @@
       <c r="T64" s="8" t="inlineStr"/>
       <c r="U64" s="8" t="inlineStr"/>
       <c r="V64" s="8" t="inlineStr"/>
-      <c r="W64" s="9" t="n">
+      <c r="W64" s="8" t="inlineStr"/>
+      <c r="X64" s="9" t="n">
         <v>1742.375</v>
       </c>
-      <c r="X64" s="10" t="inlineStr"/>
-      <c r="Y64" s="11" t="inlineStr"/>
+      <c r="Y64" s="10" t="inlineStr"/>
+      <c r="Z64" s="11" t="inlineStr"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="1" t="n"/>
@@ -3859,9 +3951,10 @@
       <c r="T65" s="8" t="inlineStr"/>
       <c r="U65" s="8" t="inlineStr"/>
       <c r="V65" s="8" t="inlineStr"/>
-      <c r="W65" s="9" t="inlineStr"/>
-      <c r="X65" s="10" t="inlineStr"/>
-      <c r="Y65" s="11" t="inlineStr"/>
+      <c r="W65" s="8" t="inlineStr"/>
+      <c r="X65" s="9" t="inlineStr"/>
+      <c r="Y65" s="10" t="inlineStr"/>
+      <c r="Z65" s="11" t="inlineStr"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="1" t="n"/>
@@ -3918,13 +4011,14 @@
       <c r="T66" s="8" t="inlineStr"/>
       <c r="U66" s="8" t="inlineStr"/>
       <c r="V66" s="8" t="inlineStr"/>
-      <c r="W66" s="9" t="n">
+      <c r="W66" s="8" t="inlineStr"/>
+      <c r="X66" s="9" t="n">
         <v>1986.75</v>
       </c>
-      <c r="X66" s="9" t="n">
+      <c r="Y66" s="9" t="n">
         <v>244.375</v>
       </c>
-      <c r="Y66" s="11" t="n">
+      <c r="Z66" s="11" t="n">
         <v>0.05723738142639653</v>
       </c>
     </row>
@@ -3959,264 +4053,278 @@
       <c r="T67" s="8" t="inlineStr"/>
       <c r="U67" s="8" t="inlineStr"/>
       <c r="V67" s="8" t="inlineStr"/>
-      <c r="W67" s="9" t="inlineStr"/>
-      <c r="X67" s="10" t="inlineStr"/>
-      <c r="Y67" s="11" t="inlineStr"/>
+      <c r="W67" s="8" t="inlineStr"/>
+      <c r="X67" s="9" t="inlineStr"/>
+      <c r="Y67" s="10" t="inlineStr"/>
+      <c r="Z67" s="11" t="inlineStr"/>
     </row>
     <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="1" t="n"/>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr"/>
-      <c r="D68" s="8" t="inlineStr"/>
-      <c r="E68" s="13" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr"/>
-      <c r="G68" s="8" t="inlineStr"/>
-      <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr"/>
-      <c r="K68" s="8" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr"/>
-      <c r="M68" s="8" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
-      <c r="O68" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="P68" s="8" t="inlineStr"/>
-      <c r="Q68" s="8" t="inlineStr"/>
-      <c r="R68" s="8" t="inlineStr"/>
-      <c r="S68" s="8" t="inlineStr"/>
-      <c r="T68" s="8" t="inlineStr"/>
-      <c r="U68" s="8" t="inlineStr"/>
-      <c r="V68" s="8" t="inlineStr"/>
-      <c r="W68" s="9" t="inlineStr"/>
-      <c r="X68" s="10" t="inlineStr"/>
-      <c r="Y68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Gopher
 Random: 257.6
 Human: 2412.5</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 8240</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr"/>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="4" t="inlineStr"/>
-      <c r="K69" s="4" t="inlineStr"/>
-      <c r="L69" s="4" t="inlineStr"/>
-      <c r="M69" s="4" t="inlineStr"/>
-      <c r="N69" s="4" t="inlineStr"/>
-      <c r="O69" s="4" t="inlineStr"/>
-      <c r="P69" s="4" t="inlineStr"/>
-      <c r="Q69" s="4" t="inlineStr"/>
-      <c r="R69" s="4" t="inlineStr"/>
-      <c r="S69" s="4" t="inlineStr"/>
-      <c r="T69" s="4" t="inlineStr"/>
-      <c r="U69" s="4" t="inlineStr"/>
-      <c r="V69" s="4" t="inlineStr"/>
-      <c r="W69" s="5" t="inlineStr"/>
-      <c r="X69" s="6" t="n">
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr"/>
+      <c r="Q68" s="4" t="inlineStr"/>
+      <c r="R68" s="4" t="inlineStr"/>
+      <c r="S68" s="4" t="inlineStr"/>
+      <c r="T68" s="4" t="inlineStr"/>
+      <c r="U68" s="4" t="inlineStr"/>
+      <c r="V68" s="4" t="inlineStr"/>
+      <c r="W68" s="4" t="inlineStr"/>
+      <c r="X68" s="5" t="inlineStr"/>
+      <c r="Y68" s="6" t="n">
         <v>-4547</v>
       </c>
-      <c r="Y69" s="7" t="n">
+      <c r="Z68" s="7" t="n">
         <v>-2.110074713443779</v>
       </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="1" t="n"/>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>5968.00</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>3752.00</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>3275.00</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>3914.00</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>4219.00</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="inlineStr"/>
+      <c r="K69" s="8" t="inlineStr"/>
+      <c r="L69" s="8" t="inlineStr"/>
+      <c r="M69" s="8" t="inlineStr"/>
+      <c r="N69" s="8" t="inlineStr"/>
+      <c r="O69" s="13" t="inlineStr">
+        <is>
+          <t>2486.00</t>
+        </is>
+      </c>
+      <c r="P69" s="13" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
+      <c r="Q69" s="8" t="inlineStr"/>
+      <c r="R69" s="8" t="inlineStr"/>
+      <c r="S69" s="8" t="inlineStr"/>
+      <c r="T69" s="8" t="inlineStr"/>
+      <c r="U69" s="8" t="inlineStr">
+        <is>
+          <t>3585.00</t>
+        </is>
+      </c>
+      <c r="V69" s="13" t="inlineStr">
+        <is>
+          <t>2594.00</t>
+        </is>
+      </c>
+      <c r="W69" s="8" t="inlineStr"/>
+      <c r="X69" s="9" t="n">
+        <v>3693</v>
+      </c>
+      <c r="Y69" s="10" t="inlineStr"/>
+      <c r="Z69" s="11" t="inlineStr"/>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>5968.00</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>3752.00</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>3275.00</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>3914.00</t>
-        </is>
-      </c>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr"/>
+      <c r="D70" s="8" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr"/>
+      <c r="F70" s="8" t="inlineStr"/>
       <c r="G70" s="8" t="inlineStr"/>
       <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>4219.00</t>
-        </is>
-      </c>
+      <c r="I70" s="8" t="inlineStr"/>
       <c r="J70" s="8" t="inlineStr"/>
       <c r="K70" s="8" t="inlineStr"/>
       <c r="L70" s="8" t="inlineStr"/>
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
-      <c r="O70" s="13" t="inlineStr">
-        <is>
-          <t>2486.00</t>
-        </is>
-      </c>
-      <c r="P70" s="13" t="inlineStr">
-        <is>
-          <t>1250.00</t>
-        </is>
-      </c>
+      <c r="O70" s="13" t="inlineStr"/>
+      <c r="P70" s="13" t="inlineStr"/>
       <c r="Q70" s="8" t="inlineStr"/>
-      <c r="R70" s="8" t="inlineStr"/>
+      <c r="R70" s="8" t="inlineStr">
+        <is>
+          <t>2533.00</t>
+        </is>
+      </c>
       <c r="S70" s="8" t="inlineStr"/>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>3585.00</t>
-        </is>
-      </c>
-      <c r="U70" s="13" t="inlineStr">
-        <is>
-          <t>2594.00</t>
-        </is>
-      </c>
-      <c r="V70" s="8" t="inlineStr"/>
-      <c r="W70" s="9" t="n">
-        <v>3693</v>
-      </c>
-      <c r="X70" s="10" t="inlineStr"/>
-      <c r="Y70" s="11" t="inlineStr"/>
+      <c r="T70" s="8" t="inlineStr"/>
+      <c r="U70" s="8" t="inlineStr">
+        <is>
+          <t>4472.00</t>
+        </is>
+      </c>
+      <c r="V70" s="13" t="inlineStr"/>
+      <c r="W70" s="8" t="inlineStr"/>
+      <c r="X70" s="9" t="inlineStr"/>
+      <c r="Y70" s="10" t="inlineStr"/>
+      <c r="Z70" s="11" t="inlineStr"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr"/>
       <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>3327.00</t>
+        </is>
+      </c>
       <c r="F71" s="8" t="inlineStr"/>
       <c r="G71" s="8" t="inlineStr"/>
       <c r="H71" s="8" t="inlineStr"/>
-      <c r="I71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>3829.00</t>
+        </is>
+      </c>
       <c r="J71" s="8" t="inlineStr"/>
       <c r="K71" s="8" t="inlineStr"/>
       <c r="L71" s="8" t="inlineStr"/>
       <c r="M71" s="8" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
-      <c r="O71" s="13" t="inlineStr"/>
-      <c r="P71" s="13" t="inlineStr"/>
-      <c r="Q71" s="8" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr">
-        <is>
-          <t>2533.00</t>
-        </is>
-      </c>
-      <c r="S71" s="8" t="inlineStr"/>
+      <c r="O71" s="13" t="inlineStr">
+        <is>
+          <t>1024.00</t>
+        </is>
+      </c>
+      <c r="P71" s="13" t="inlineStr">
+        <is>
+          <t>927.00</t>
+        </is>
+      </c>
+      <c r="Q71" s="14" t="inlineStr">
+        <is>
+          <t>847.00</t>
+        </is>
+      </c>
+      <c r="R71" s="14" t="inlineStr">
+        <is>
+          <t>2933.00</t>
+        </is>
+      </c>
+      <c r="S71" s="15" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="T71" s="8" t="inlineStr"/>
-      <c r="U71" s="13" t="inlineStr"/>
-      <c r="V71" s="8" t="inlineStr"/>
-      <c r="W71" s="9" t="inlineStr"/>
-      <c r="X71" s="10" t="inlineStr"/>
-      <c r="Y71" s="11" t="inlineStr"/>
+      <c r="U71" s="8" t="inlineStr">
+        <is>
+          <t>7531.00</t>
+        </is>
+      </c>
+      <c r="V71" s="13" t="inlineStr">
+        <is>
+          <t>1005.00</t>
+        </is>
+      </c>
+      <c r="W71" s="8" t="inlineStr"/>
+      <c r="X71" s="9" t="n">
+        <v>4895.666666666667</v>
+      </c>
+      <c r="Y71" s="9" t="n">
+        <v>1202.666666666667</v>
+      </c>
+      <c r="Z71" s="11" t="n">
+        <v>0.558107878169134</v>
+      </c>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr"/>
       <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>3327.00</t>
-        </is>
-      </c>
+      <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr"/>
       <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>3829.00</t>
-        </is>
-      </c>
+      <c r="I72" s="8" t="inlineStr"/>
       <c r="J72" s="8" t="inlineStr"/>
       <c r="K72" s="8" t="inlineStr"/>
       <c r="L72" s="8" t="inlineStr"/>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
-      <c r="O72" s="13" t="inlineStr">
-        <is>
-          <t>1024.00</t>
-        </is>
-      </c>
-      <c r="P72" s="13" t="inlineStr">
-        <is>
-          <t>927.00</t>
-        </is>
-      </c>
-      <c r="Q72" s="14" t="inlineStr">
-        <is>
-          <t>847.00</t>
-        </is>
-      </c>
-      <c r="R72" s="14" t="inlineStr">
-        <is>
-          <t>2933.00</t>
-        </is>
-      </c>
+      <c r="O72" s="13" t="inlineStr"/>
+      <c r="P72" s="13" t="inlineStr"/>
+      <c r="Q72" s="8" t="inlineStr"/>
+      <c r="R72" s="8" t="inlineStr"/>
       <c r="S72" s="8" t="inlineStr"/>
-      <c r="T72" s="8" t="inlineStr">
-        <is>
-          <t>7531.00</t>
-        </is>
-      </c>
-      <c r="U72" s="13" t="inlineStr">
-        <is>
-          <t>1005.00</t>
-        </is>
-      </c>
-      <c r="V72" s="8" t="inlineStr"/>
-      <c r="W72" s="9" t="n">
-        <v>4895.666666666667</v>
-      </c>
-      <c r="X72" s="9" t="n">
-        <v>1202.666666666667</v>
-      </c>
-      <c r="Y72" s="11" t="n">
-        <v>0.558107878169134</v>
-      </c>
+      <c r="T72" s="8" t="inlineStr"/>
+      <c r="U72" s="8" t="inlineStr">
+        <is>
+          <t>5320.00</t>
+        </is>
+      </c>
+      <c r="V72" s="13" t="inlineStr"/>
+      <c r="W72" s="8" t="inlineStr"/>
+      <c r="X72" s="9" t="inlineStr"/>
+      <c r="Y72" s="10" t="inlineStr"/>
+      <c r="Z72" s="11" t="inlineStr"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr"/>
@@ -4236,16 +4344,17 @@
       <c r="Q73" s="8" t="inlineStr"/>
       <c r="R73" s="8" t="inlineStr"/>
       <c r="S73" s="8" t="inlineStr"/>
-      <c r="T73" s="12" t="inlineStr">
+      <c r="T73" s="8" t="inlineStr"/>
+      <c r="U73" s="12" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="U73" s="13" t="inlineStr"/>
-      <c r="V73" s="8" t="inlineStr"/>
-      <c r="W73" s="9" t="inlineStr"/>
-      <c r="X73" s="10" t="inlineStr"/>
-      <c r="Y73" s="11" t="inlineStr"/>
+      <c r="V73" s="13" t="inlineStr"/>
+      <c r="W73" s="8" t="inlineStr"/>
+      <c r="X73" s="9" t="inlineStr"/>
+      <c r="Y73" s="10" t="inlineStr"/>
+      <c r="Z73" s="11" t="inlineStr"/>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -4280,12 +4389,13 @@
       <c r="T74" s="4" t="inlineStr"/>
       <c r="U74" s="4" t="inlineStr"/>
       <c r="V74" s="4" t="inlineStr"/>
-      <c r="W74" s="5" t="inlineStr"/>
-      <c r="X74" s="6" t="n">
-        <v>2134</v>
-      </c>
-      <c r="Y74" s="7" t="n">
-        <v>0.07161218011100895</v>
+      <c r="W74" s="4" t="inlineStr"/>
+      <c r="X74" s="5" t="inlineStr"/>
+      <c r="Y74" s="6" t="n">
+        <v>741.625</v>
+      </c>
+      <c r="Z74" s="7" t="n">
+        <v>0.02488724605193393</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
@@ -4331,42 +4441,31 @@
       <c r="T75" s="8" t="inlineStr"/>
       <c r="U75" s="8" t="inlineStr"/>
       <c r="V75" s="8" t="inlineStr"/>
-      <c r="W75" s="9" t="n">
-        <v>13178</v>
-      </c>
-      <c r="X75" s="10" t="inlineStr"/>
-      <c r="Y75" s="11" t="inlineStr"/>
+      <c r="W75" s="8" t="inlineStr"/>
+      <c r="X75" s="9" t="n">
+        <v>11785.625</v>
+      </c>
+      <c r="Y75" s="10" t="inlineStr"/>
+      <c r="Z75" s="11" t="inlineStr"/>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>13473.00</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>13251.25</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>13231.50</t>
-        </is>
-      </c>
+      <c r="E76" s="8" t="inlineStr"/>
+      <c r="F76" s="8" t="inlineStr"/>
       <c r="G76" s="8" t="inlineStr"/>
       <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>13325.50</t>
-        </is>
-      </c>
+      <c r="I76" s="8" t="inlineStr"/>
       <c r="J76" s="8" t="inlineStr"/>
       <c r="K76" s="8" t="inlineStr"/>
       <c r="L76" s="8" t="inlineStr"/>
@@ -4380,67 +4479,75 @@
       <c r="T76" s="8" t="inlineStr"/>
       <c r="U76" s="8" t="inlineStr"/>
       <c r="V76" s="8" t="inlineStr"/>
-      <c r="W76" s="9" t="n">
-        <v>13269.41666666667</v>
-      </c>
-      <c r="X76" s="9" t="n">
-        <v>91.41666666666606</v>
-      </c>
-      <c r="Y76" s="11" t="n">
-        <v>0.003067735144555463</v>
-      </c>
+      <c r="W76" s="8" t="inlineStr"/>
+      <c r="X76" s="9" t="inlineStr"/>
+      <c r="Y76" s="10" t="inlineStr"/>
+      <c r="Z76" s="11" t="inlineStr"/>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Jamesbond
-Random: 29.0
-Human: 302.8</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 509</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr"/>
-      <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="4" t="inlineStr"/>
-      <c r="J77" s="4" t="inlineStr"/>
-      <c r="K77" s="4" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr"/>
-      <c r="M77" s="4" t="inlineStr"/>
-      <c r="N77" s="4" t="inlineStr"/>
-      <c r="O77" s="4" t="inlineStr"/>
-      <c r="P77" s="4" t="inlineStr"/>
-      <c r="Q77" s="4" t="inlineStr"/>
-      <c r="R77" s="4" t="inlineStr"/>
-      <c r="S77" s="4" t="inlineStr"/>
-      <c r="T77" s="4" t="inlineStr"/>
-      <c r="U77" s="4" t="inlineStr"/>
-      <c r="V77" s="4" t="inlineStr"/>
-      <c r="W77" s="5" t="inlineStr"/>
-      <c r="X77" s="6" t="n">
-        <v>-35.66666666666669</v>
-      </c>
-      <c r="Y77" s="7" t="n">
-        <v>-0.1302654005356709</v>
+      <c r="A77" s="1" t="n"/>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>13108.75</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>13251.25</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>13231.50</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>13325.50</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr"/>
+      <c r="K77" s="8" t="inlineStr"/>
+      <c r="L77" s="8" t="inlineStr"/>
+      <c r="M77" s="8" t="inlineStr"/>
+      <c r="N77" s="8" t="inlineStr"/>
+      <c r="O77" s="8" t="inlineStr"/>
+      <c r="P77" s="8" t="inlineStr"/>
+      <c r="Q77" s="8" t="inlineStr"/>
+      <c r="R77" s="8" t="inlineStr"/>
+      <c r="S77" s="8" t="inlineStr"/>
+      <c r="T77" s="8" t="inlineStr"/>
+      <c r="U77" s="8" t="inlineStr"/>
+      <c r="V77" s="8" t="inlineStr"/>
+      <c r="W77" s="8" t="inlineStr"/>
+      <c r="X77" s="9" t="n">
+        <v>13229.25</v>
+      </c>
+      <c r="Y77" s="9" t="n">
+        <v>1443.625</v>
+      </c>
+      <c r="Z77" s="11" t="n">
+        <v>0.04844476734430894</v>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>490.00</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr"/>
@@ -4450,79 +4557,77 @@
       <c r="H78" s="8" t="inlineStr"/>
       <c r="I78" s="8" t="inlineStr"/>
       <c r="J78" s="8" t="inlineStr"/>
-      <c r="K78" s="8" t="inlineStr">
-        <is>
-          <t>532.50, 537.50</t>
-        </is>
-      </c>
+      <c r="K78" s="8" t="inlineStr"/>
       <c r="L78" s="8" t="inlineStr"/>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr"/>
-      <c r="O78" s="8" t="inlineStr">
-        <is>
-          <t>522.50</t>
-        </is>
-      </c>
+      <c r="O78" s="8" t="inlineStr"/>
       <c r="P78" s="8" t="inlineStr"/>
       <c r="Q78" s="8" t="inlineStr"/>
       <c r="R78" s="8" t="inlineStr"/>
       <c r="S78" s="8" t="inlineStr"/>
       <c r="T78" s="8" t="inlineStr"/>
-      <c r="U78" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
-        </is>
-      </c>
+      <c r="U78" s="8" t="inlineStr"/>
       <c r="V78" s="8" t="inlineStr"/>
-      <c r="W78" s="9" t="n">
-        <v>473.3333333333333</v>
-      </c>
-      <c r="X78" s="10" t="inlineStr"/>
-      <c r="Y78" s="11" t="inlineStr"/>
+      <c r="W78" s="8" t="inlineStr"/>
+      <c r="X78" s="9" t="inlineStr"/>
+      <c r="Y78" s="10" t="inlineStr"/>
+      <c r="Z78" s="11" t="inlineStr"/>
     </row>
     <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="1" t="n"/>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr"/>
-      <c r="D79" s="8" t="inlineStr"/>
-      <c r="E79" s="8" t="inlineStr"/>
-      <c r="F79" s="8" t="inlineStr"/>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr"/>
-      <c r="I79" s="8" t="inlineStr"/>
-      <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" s="8" t="inlineStr"/>
-      <c r="L79" s="8" t="inlineStr"/>
-      <c r="M79" s="8" t="inlineStr"/>
-      <c r="N79" s="8" t="inlineStr"/>
-      <c r="O79" s="8" t="inlineStr">
-        <is>
-          <t>575.00</t>
-        </is>
-      </c>
-      <c r="P79" s="8" t="inlineStr"/>
-      <c r="Q79" s="8" t="inlineStr"/>
-      <c r="R79" s="8" t="inlineStr"/>
-      <c r="S79" s="8" t="inlineStr"/>
-      <c r="T79" s="8" t="inlineStr"/>
-      <c r="U79" s="8" t="inlineStr"/>
-      <c r="V79" s="8" t="inlineStr"/>
-      <c r="W79" s="9" t="inlineStr"/>
-      <c r="X79" s="10" t="inlineStr"/>
-      <c r="Y79" s="11" t="inlineStr"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Jamesbond
+Random: 29.0
+Human: 302.8</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 509</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr"/>
+      <c r="J79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr"/>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr"/>
+      <c r="O79" s="4" t="inlineStr"/>
+      <c r="P79" s="4" t="inlineStr"/>
+      <c r="Q79" s="4" t="inlineStr"/>
+      <c r="R79" s="4" t="inlineStr"/>
+      <c r="S79" s="4" t="inlineStr"/>
+      <c r="T79" s="4" t="inlineStr"/>
+      <c r="U79" s="4" t="inlineStr"/>
+      <c r="V79" s="4" t="inlineStr"/>
+      <c r="W79" s="4" t="inlineStr"/>
+      <c r="X79" s="5" t="inlineStr"/>
+      <c r="Y79" s="6" t="n">
+        <v>-35.66666666666669</v>
+      </c>
+      <c r="Z79" s="7" t="n">
+        <v>-0.1302654005356709</v>
+      </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>490.00</t>
+        </is>
+      </c>
       <c r="D80" s="8" t="inlineStr"/>
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="8" t="inlineStr"/>
@@ -4532,7 +4637,7 @@
       <c r="J80" s="8" t="inlineStr"/>
       <c r="K80" s="8" t="inlineStr">
         <is>
-          <t>567.50, 660.00</t>
+          <t>532.50, 537.50</t>
         </is>
       </c>
       <c r="L80" s="8" t="inlineStr"/>
@@ -4540,7 +4645,7 @@
       <c r="N80" s="8" t="inlineStr"/>
       <c r="O80" s="8" t="inlineStr">
         <is>
-          <t>665.00</t>
+          <t>522.50</t>
         </is>
       </c>
       <c r="P80" s="8" t="inlineStr"/>
@@ -4548,77 +4653,65 @@
       <c r="R80" s="8" t="inlineStr"/>
       <c r="S80" s="8" t="inlineStr"/>
       <c r="T80" s="8" t="inlineStr"/>
-      <c r="U80" s="8" t="inlineStr">
-        <is>
-          <t>375.00</t>
-        </is>
-      </c>
-      <c r="V80" s="8" t="inlineStr"/>
-      <c r="W80" s="9" t="n">
-        <v>535.8333333333334</v>
-      </c>
+      <c r="U80" s="8" t="inlineStr"/>
+      <c r="V80" s="8" t="inlineStr">
+        <is>
+          <t>365.00</t>
+        </is>
+      </c>
+      <c r="W80" s="8" t="inlineStr"/>
       <c r="X80" s="9" t="n">
-        <v>62.50000000000006</v>
-      </c>
-      <c r="Y80" s="11" t="n">
-        <v>0.2282688093498906</v>
-      </c>
+        <v>473.3333333333333</v>
+      </c>
+      <c r="Y80" s="10" t="inlineStr"/>
+      <c r="Z80" s="11" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Kangaroo
-Random: 52.0
-Human: 3035.0</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4208</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr"/>
-      <c r="D81" s="4" t="inlineStr"/>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr"/>
-      <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr"/>
-      <c r="K81" s="4" t="inlineStr"/>
-      <c r="L81" s="4" t="inlineStr"/>
-      <c r="M81" s="4" t="inlineStr"/>
-      <c r="N81" s="4" t="inlineStr"/>
-      <c r="O81" s="4" t="inlineStr"/>
-      <c r="P81" s="4" t="inlineStr"/>
-      <c r="Q81" s="4" t="inlineStr"/>
-      <c r="R81" s="4" t="inlineStr"/>
-      <c r="S81" s="4" t="inlineStr"/>
-      <c r="T81" s="4" t="inlineStr"/>
-      <c r="U81" s="4" t="inlineStr"/>
-      <c r="V81" s="4" t="inlineStr"/>
-      <c r="W81" s="5" t="inlineStr"/>
-      <c r="X81" s="6" t="n">
-        <v>-2778</v>
-      </c>
-      <c r="Y81" s="7" t="n">
-        <v>-0.9312772376801878</v>
-      </c>
+      <c r="A81" s="1" t="n"/>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr"/>
+      <c r="D81" s="8" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr"/>
+      <c r="F81" s="8" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr"/>
+      <c r="L81" s="8" t="inlineStr"/>
+      <c r="M81" s="8" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr"/>
+      <c r="O81" s="8" t="inlineStr">
+        <is>
+          <t>575.00</t>
+        </is>
+      </c>
+      <c r="P81" s="8" t="inlineStr"/>
+      <c r="Q81" s="8" t="inlineStr"/>
+      <c r="R81" s="8" t="inlineStr"/>
+      <c r="S81" s="8" t="inlineStr"/>
+      <c r="T81" s="8" t="inlineStr"/>
+      <c r="U81" s="8" t="inlineStr"/>
+      <c r="V81" s="8" t="inlineStr"/>
+      <c r="W81" s="8" t="inlineStr"/>
+      <c r="X81" s="9" t="inlineStr"/>
+      <c r="Y81" s="10" t="inlineStr"/>
+      <c r="Z81" s="11" t="inlineStr"/>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr"/>
       <c r="D82" s="8" t="inlineStr"/>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>1770.00</t>
-        </is>
-      </c>
+      <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="8" t="inlineStr"/>
       <c r="G82" s="8" t="inlineStr"/>
       <c r="H82" s="8" t="inlineStr"/>
@@ -4626,93 +4719,93 @@
       <c r="J82" s="8" t="inlineStr"/>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
-        <is>
-          <t>1730.00</t>
-        </is>
-      </c>
+          <t>567.50, 660.00</t>
+        </is>
+      </c>
+      <c r="L82" s="8" t="inlineStr"/>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
       <c r="O82" s="8" t="inlineStr">
         <is>
-          <t>1550.00</t>
-        </is>
-      </c>
-      <c r="P82" s="8" t="inlineStr">
-        <is>
-          <t>930.00</t>
-        </is>
-      </c>
+          <t>665.00</t>
+        </is>
+      </c>
+      <c r="P82" s="8" t="inlineStr"/>
       <c r="Q82" s="8" t="inlineStr"/>
       <c r="R82" s="8" t="inlineStr"/>
       <c r="S82" s="8" t="inlineStr"/>
       <c r="T82" s="8" t="inlineStr"/>
       <c r="U82" s="8" t="inlineStr"/>
-      <c r="V82" s="8" t="inlineStr"/>
-      <c r="W82" s="9" t="n">
-        <v>1430</v>
-      </c>
-      <c r="X82" s="10" t="inlineStr"/>
-      <c r="Y82" s="11" t="inlineStr"/>
+      <c r="V82" s="8" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
+      <c r="W82" s="8" t="inlineStr"/>
+      <c r="X82" s="9" t="n">
+        <v>535.8333333333334</v>
+      </c>
+      <c r="Y82" s="9" t="n">
+        <v>62.50000000000006</v>
+      </c>
+      <c r="Z82" s="11" t="n">
+        <v>0.2282688093498906</v>
+      </c>
     </row>
     <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="1" t="n"/>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr"/>
-      <c r="D83" s="8" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr"/>
-      <c r="F83" s="8" t="inlineStr"/>
-      <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="8" t="inlineStr"/>
-      <c r="I83" s="8" t="inlineStr"/>
-      <c r="J83" s="8" t="inlineStr"/>
-      <c r="K83" s="8" t="inlineStr">
-        <is>
-          <t>1310.00</t>
-        </is>
-      </c>
-      <c r="L83" s="8" t="inlineStr"/>
-      <c r="M83" s="8" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
-      <c r="O83" s="8" t="inlineStr">
-        <is>
-          <t>1500.00</t>
-        </is>
-      </c>
-      <c r="P83" s="8" t="inlineStr">
-        <is>
-          <t>1030.00</t>
-        </is>
-      </c>
-      <c r="Q83" s="8" t="inlineStr"/>
-      <c r="R83" s="8" t="inlineStr"/>
-      <c r="S83" s="8" t="inlineStr"/>
-      <c r="T83" s="8" t="inlineStr"/>
-      <c r="U83" s="8" t="inlineStr"/>
-      <c r="V83" s="8" t="inlineStr"/>
-      <c r="W83" s="9" t="inlineStr"/>
-      <c r="X83" s="10" t="inlineStr"/>
-      <c r="Y83" s="11" t="inlineStr"/>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Kangaroo
+Random: 52.0
+Human: 3035.0</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4208</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr"/>
+      <c r="O83" s="4" t="inlineStr"/>
+      <c r="P83" s="4" t="inlineStr"/>
+      <c r="Q83" s="4" t="inlineStr"/>
+      <c r="R83" s="4" t="inlineStr"/>
+      <c r="S83" s="4" t="inlineStr"/>
+      <c r="T83" s="4" t="inlineStr"/>
+      <c r="U83" s="4" t="inlineStr"/>
+      <c r="V83" s="4" t="inlineStr"/>
+      <c r="W83" s="4" t="inlineStr"/>
+      <c r="X83" s="5" t="inlineStr"/>
+      <c r="Y83" s="6" t="n">
+        <v>-2778</v>
+      </c>
+      <c r="Z83" s="7" t="n">
+        <v>-0.9312772376801878</v>
+      </c>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr"/>
       <c r="D84" s="8" t="inlineStr"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>1760.00</t>
+          <t>1770.00</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr"/>
@@ -4722,20 +4815,24 @@
       <c r="J84" s="8" t="inlineStr"/>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>1590.00</t>
-        </is>
-      </c>
-      <c r="L84" s="8" t="inlineStr"/>
+          <t>1470.00</t>
+        </is>
+      </c>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>1730.00</t>
+        </is>
+      </c>
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="8" t="inlineStr"/>
       <c r="O84" s="8" t="inlineStr">
         <is>
-          <t>1670.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="P84" s="8" t="inlineStr">
         <is>
-          <t>760.00</t>
+          <t>930.00</t>
         </is>
       </c>
       <c r="Q84" s="8" t="inlineStr"/>
@@ -4744,279 +4841,275 @@
       <c r="T84" s="8" t="inlineStr"/>
       <c r="U84" s="8" t="inlineStr"/>
       <c r="V84" s="8" t="inlineStr"/>
-      <c r="W84" s="9" t="n">
+      <c r="W84" s="8" t="inlineStr"/>
+      <c r="X84" s="9" t="n">
+        <v>1430</v>
+      </c>
+      <c r="Y84" s="10" t="inlineStr"/>
+      <c r="Z84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="1" t="n"/>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr"/>
+      <c r="D85" s="8" t="inlineStr"/>
+      <c r="E85" s="8" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr"/>
+      <c r="J85" s="8" t="inlineStr"/>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>1310.00</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr"/>
+      <c r="M85" s="8" t="inlineStr"/>
+      <c r="N85" s="8" t="inlineStr"/>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="P85" s="8" t="inlineStr">
+        <is>
+          <t>1030.00</t>
+        </is>
+      </c>
+      <c r="Q85" s="8" t="inlineStr"/>
+      <c r="R85" s="8" t="inlineStr"/>
+      <c r="S85" s="8" t="inlineStr"/>
+      <c r="T85" s="8" t="inlineStr"/>
+      <c r="U85" s="8" t="inlineStr"/>
+      <c r="V85" s="8" t="inlineStr"/>
+      <c r="W85" s="8" t="inlineStr"/>
+      <c r="X85" s="9" t="inlineStr"/>
+      <c r="Y85" s="10" t="inlineStr"/>
+      <c r="Z85" s="11" t="inlineStr"/>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="1" t="n"/>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr"/>
+      <c r="D86" s="8" t="inlineStr"/>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr"/>
+      <c r="G86" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr"/>
+      <c r="I86" s="8" t="inlineStr"/>
+      <c r="J86" s="8" t="inlineStr"/>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>1590.00</t>
+        </is>
+      </c>
+      <c r="L86" s="8" t="inlineStr"/>
+      <c r="M86" s="8" t="inlineStr"/>
+      <c r="N86" s="8" t="inlineStr"/>
+      <c r="O86" s="8" t="inlineStr">
+        <is>
+          <t>1670.00</t>
+        </is>
+      </c>
+      <c r="P86" s="8" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
+      <c r="Q86" s="8" t="inlineStr"/>
+      <c r="R86" s="8" t="inlineStr"/>
+      <c r="S86" s="8" t="inlineStr"/>
+      <c r="T86" s="8" t="inlineStr"/>
+      <c r="U86" s="8" t="inlineStr"/>
+      <c r="V86" s="8" t="inlineStr"/>
+      <c r="W86" s="8" t="inlineStr"/>
+      <c r="X86" s="9" t="n">
         <v>1445</v>
       </c>
-      <c r="X84" s="9" t="n">
+      <c r="Y86" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="Y84" s="11" t="n">
+      <c r="Z86" s="11" t="n">
         <v>0.005028494803888703</v>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Krull
 Random: 1598.0
 Human: 2665.5</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 8413</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr"/>
-      <c r="D85" s="4" t="inlineStr"/>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr"/>
-      <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr"/>
-      <c r="J85" s="4" t="inlineStr"/>
-      <c r="K85" s="4" t="inlineStr"/>
-      <c r="L85" s="4" t="inlineStr"/>
-      <c r="M85" s="4" t="inlineStr"/>
-      <c r="N85" s="4" t="inlineStr"/>
-      <c r="O85" s="4" t="inlineStr"/>
-      <c r="P85" s="4" t="inlineStr"/>
-      <c r="Q85" s="4" t="inlineStr"/>
-      <c r="R85" s="4" t="inlineStr"/>
-      <c r="S85" s="4" t="inlineStr"/>
-      <c r="T85" s="4" t="inlineStr"/>
-      <c r="U85" s="4" t="inlineStr"/>
-      <c r="V85" s="4" t="inlineStr"/>
-      <c r="W85" s="5" t="inlineStr"/>
-      <c r="X85" s="6" t="n">
+      <c r="C87" s="4" t="inlineStr"/>
+      <c r="D87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
+      <c r="M87" s="4" t="inlineStr"/>
+      <c r="N87" s="4" t="inlineStr"/>
+      <c r="O87" s="4" t="inlineStr"/>
+      <c r="P87" s="4" t="inlineStr"/>
+      <c r="Q87" s="4" t="inlineStr"/>
+      <c r="R87" s="4" t="inlineStr"/>
+      <c r="S87" s="4" t="inlineStr"/>
+      <c r="T87" s="4" t="inlineStr"/>
+      <c r="U87" s="4" t="inlineStr"/>
+      <c r="V87" s="4" t="inlineStr"/>
+      <c r="W87" s="4" t="inlineStr"/>
+      <c r="X87" s="5" t="inlineStr"/>
+      <c r="Y87" s="6" t="n">
         <v>-2583.375</v>
       </c>
-      <c r="Y85" s="7" t="n">
+      <c r="Z87" s="7" t="n">
         <v>-2.420023419203747</v>
       </c>
-    </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="1" t="n"/>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr"/>
-      <c r="D86" s="8" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>6202.00</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>5689.00</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>6107.50</t>
-        </is>
-      </c>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="13" t="inlineStr">
-        <is>
-          <t>4708.50</t>
-        </is>
-      </c>
-      <c r="L86" s="13" t="inlineStr">
-        <is>
-          <t>5913.50</t>
-        </is>
-      </c>
-      <c r="M86" s="8" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
-      <c r="O86" s="8" t="inlineStr">
-        <is>
-          <t>5228.50</t>
-        </is>
-      </c>
-      <c r="P86" s="8" t="inlineStr"/>
-      <c r="Q86" s="8" t="inlineStr">
-        <is>
-          <t>5599.00</t>
-        </is>
-      </c>
-      <c r="R86" s="8" t="inlineStr"/>
-      <c r="S86" s="8" t="inlineStr"/>
-      <c r="T86" s="8" t="inlineStr"/>
-      <c r="U86" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
-      <c r="V86" s="8" t="inlineStr"/>
-      <c r="W86" s="9" t="n">
-        <v>5829.625</v>
-      </c>
-      <c r="X86" s="10" t="inlineStr"/>
-      <c r="Y86" s="11" t="inlineStr"/>
-    </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="1" t="n"/>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr"/>
-      <c r="D87" s="8" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr"/>
-      <c r="F87" s="8" t="inlineStr"/>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr"/>
-      <c r="I87" s="8" t="inlineStr"/>
-      <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="13" t="inlineStr">
-        <is>
-          <t>4851.00</t>
-        </is>
-      </c>
-      <c r="L87" s="13" t="inlineStr">
-        <is>
-          <t>6044.00</t>
-        </is>
-      </c>
-      <c r="M87" s="8" t="inlineStr"/>
-      <c r="N87" s="8" t="inlineStr"/>
-      <c r="O87" s="8" t="inlineStr"/>
-      <c r="P87" s="8" t="inlineStr"/>
-      <c r="Q87" s="8" t="inlineStr"/>
-      <c r="R87" s="8" t="inlineStr"/>
-      <c r="S87" s="8" t="inlineStr"/>
-      <c r="T87" s="8" t="inlineStr"/>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>6587.00</t>
-        </is>
-      </c>
-      <c r="V87" s="8" t="inlineStr"/>
-      <c r="W87" s="9" t="inlineStr"/>
-      <c r="X87" s="10" t="inlineStr"/>
-      <c r="Y87" s="11" t="inlineStr"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr"/>
       <c r="D88" s="8" t="inlineStr"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>6576.50</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr"/>
+          <t>6202.00</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>5689.00</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="inlineStr"/>
       <c r="H88" s="8" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>6107.50</t>
+        </is>
+      </c>
       <c r="J88" s="8" t="inlineStr"/>
       <c r="K88" s="13" t="inlineStr">
         <is>
-          <t>5279.50</t>
+          <t>4708.50</t>
         </is>
       </c>
       <c r="L88" s="13" t="inlineStr">
         <is>
-          <t>5889.50</t>
+          <t>5913.50</t>
         </is>
       </c>
       <c r="M88" s="8" t="inlineStr"/>
       <c r="N88" s="8" t="inlineStr"/>
       <c r="O88" s="8" t="inlineStr">
         <is>
-          <t>6447.50</t>
+          <t>5228.50</t>
         </is>
       </c>
       <c r="P88" s="8" t="inlineStr"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>6828.50</t>
+          <t>5599.00</t>
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr"/>
       <c r="S88" s="8" t="inlineStr"/>
       <c r="T88" s="8" t="inlineStr"/>
-      <c r="U88" s="8" t="inlineStr">
-        <is>
-          <t>6796.50</t>
-        </is>
-      </c>
-      <c r="V88" s="8" t="inlineStr"/>
-      <c r="W88" s="9" t="n">
-        <v>6662.25</v>
-      </c>
+      <c r="U88" s="8" t="inlineStr"/>
+      <c r="V88" s="8" t="inlineStr">
+        <is>
+          <t>6289.00</t>
+        </is>
+      </c>
+      <c r="W88" s="8" t="inlineStr"/>
       <c r="X88" s="9" t="n">
-        <v>832.625</v>
-      </c>
-      <c r="Y88" s="11" t="n">
-        <v>0.779976580796253</v>
-      </c>
+        <v>5829.625</v>
+      </c>
+      <c r="Y88" s="10" t="inlineStr"/>
+      <c r="Z88" s="11" t="inlineStr"/>
     </row>
     <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>KungFuMaster
-Random: 258.5
-Human: 22736.3</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 26182</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr"/>
-      <c r="D89" s="4" t="inlineStr"/>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr"/>
-      <c r="H89" s="4" t="inlineStr"/>
-      <c r="I89" s="4" t="inlineStr"/>
-      <c r="J89" s="4" t="inlineStr"/>
-      <c r="K89" s="4" t="inlineStr"/>
-      <c r="L89" s="4" t="inlineStr"/>
-      <c r="M89" s="4" t="inlineStr"/>
-      <c r="N89" s="4" t="inlineStr"/>
-      <c r="O89" s="4" t="inlineStr"/>
-      <c r="P89" s="4" t="inlineStr"/>
-      <c r="Q89" s="4" t="inlineStr"/>
-      <c r="R89" s="4" t="inlineStr"/>
-      <c r="S89" s="4" t="inlineStr"/>
-      <c r="T89" s="4" t="inlineStr"/>
-      <c r="U89" s="4" t="inlineStr"/>
-      <c r="V89" s="4" t="inlineStr"/>
-      <c r="W89" s="5" t="inlineStr"/>
-      <c r="X89" s="6" t="n">
-        <v>-1044.5</v>
-      </c>
-      <c r="Y89" s="7" t="n">
-        <v>-0.04646807071866464</v>
-      </c>
+      <c r="A89" s="1" t="n"/>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr"/>
+      <c r="D89" s="8" t="inlineStr"/>
+      <c r="E89" s="8" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="8" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr"/>
+      <c r="J89" s="8" t="inlineStr"/>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>4851.00</t>
+        </is>
+      </c>
+      <c r="L89" s="13" t="inlineStr">
+        <is>
+          <t>6044.00</t>
+        </is>
+      </c>
+      <c r="M89" s="8" t="inlineStr"/>
+      <c r="N89" s="8" t="inlineStr"/>
+      <c r="O89" s="8" t="inlineStr"/>
+      <c r="P89" s="8" t="inlineStr"/>
+      <c r="Q89" s="8" t="inlineStr"/>
+      <c r="R89" s="8" t="inlineStr"/>
+      <c r="S89" s="8" t="inlineStr"/>
+      <c r="T89" s="8" t="inlineStr"/>
+      <c r="U89" s="8" t="inlineStr"/>
+      <c r="V89" s="8" t="inlineStr">
+        <is>
+          <t>6587.00</t>
+        </is>
+      </c>
+      <c r="W89" s="8" t="inlineStr"/>
+      <c r="X89" s="9" t="inlineStr"/>
+      <c r="Y89" s="10" t="inlineStr"/>
+      <c r="Z89" s="11" t="inlineStr"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr"/>
       <c r="D90" s="8" t="inlineStr"/>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>26460.00</t>
+          <t>6576.50</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr"/>
@@ -5024,134 +5117,153 @@
       <c r="H90" s="8" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr"/>
       <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr">
-        <is>
-          <t>23815.00</t>
-        </is>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
-        <is>
-          <t>20895.00</t>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>5279.50</t>
+        </is>
+      </c>
+      <c r="L90" s="13" t="inlineStr">
+        <is>
+          <t>5889.50</t>
         </is>
       </c>
       <c r="M90" s="8" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr"/>
-      <c r="O90" s="8" t="inlineStr"/>
-      <c r="P90" s="8" t="inlineStr"/>
-      <c r="Q90" s="8" t="inlineStr"/>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>6447.50</t>
+        </is>
+      </c>
+      <c r="P90" s="15" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>6828.50</t>
+        </is>
+      </c>
       <c r="R90" s="8" t="inlineStr"/>
       <c r="S90" s="8" t="inlineStr"/>
       <c r="T90" s="8" t="inlineStr"/>
       <c r="U90" s="8" t="inlineStr"/>
-      <c r="V90" s="8" t="inlineStr"/>
-      <c r="W90" s="9" t="n">
+      <c r="V90" s="8" t="inlineStr">
+        <is>
+          <t>6796.50</t>
+        </is>
+      </c>
+      <c r="W90" s="8" t="inlineStr"/>
+      <c r="X90" s="9" t="n">
+        <v>6662.25</v>
+      </c>
+      <c r="Y90" s="9" t="n">
+        <v>832.625</v>
+      </c>
+      <c r="Z90" s="11" t="n">
+        <v>0.779976580796253</v>
+      </c>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>KungFuMaster
+Random: 258.5
+Human: 22736.3</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 26182</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="inlineStr"/>
+      <c r="N91" s="4" t="inlineStr"/>
+      <c r="O91" s="4" t="inlineStr"/>
+      <c r="P91" s="4" t="inlineStr"/>
+      <c r="Q91" s="4" t="inlineStr"/>
+      <c r="R91" s="4" t="inlineStr"/>
+      <c r="S91" s="4" t="inlineStr"/>
+      <c r="T91" s="4" t="inlineStr"/>
+      <c r="U91" s="4" t="inlineStr"/>
+      <c r="V91" s="4" t="inlineStr"/>
+      <c r="W91" s="4" t="inlineStr"/>
+      <c r="X91" s="5" t="inlineStr"/>
+      <c r="Y91" s="6" t="n">
+        <v>-1044.5</v>
+      </c>
+      <c r="Z91" s="7" t="n">
+        <v>-0.04646807071866464</v>
+      </c>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="1" t="n"/>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr"/>
+      <c r="D92" s="8" t="inlineStr"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>26460.00</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr"/>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>23815.00</t>
+        </is>
+      </c>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>20895.00</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="inlineStr"/>
+      <c r="N92" s="8" t="inlineStr"/>
+      <c r="O92" s="8" t="inlineStr"/>
+      <c r="P92" s="8" t="inlineStr"/>
+      <c r="Q92" s="8" t="inlineStr"/>
+      <c r="R92" s="8" t="inlineStr"/>
+      <c r="S92" s="8" t="inlineStr"/>
+      <c r="T92" s="8" t="inlineStr"/>
+      <c r="U92" s="8" t="inlineStr"/>
+      <c r="V92" s="8" t="inlineStr"/>
+      <c r="W92" s="8" t="inlineStr"/>
+      <c r="X92" s="9" t="n">
         <v>25137.5</v>
       </c>
-      <c r="X90" s="10" t="inlineStr"/>
-      <c r="Y90" s="11" t="inlineStr"/>
-    </row>
-    <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="1" t="n"/>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr"/>
-      <c r="D91" s="8" t="inlineStr"/>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>30110.00</t>
-        </is>
-      </c>
-      <c r="F91" s="8" t="inlineStr"/>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr"/>
-      <c r="I91" s="8" t="inlineStr"/>
-      <c r="J91" s="8" t="inlineStr"/>
-      <c r="K91" s="8" t="inlineStr">
-        <is>
-          <t>20245.00</t>
-        </is>
-      </c>
-      <c r="L91" s="8" t="inlineStr"/>
-      <c r="M91" s="8" t="inlineStr"/>
-      <c r="N91" s="8" t="inlineStr"/>
-      <c r="O91" s="8" t="inlineStr"/>
-      <c r="P91" s="8" t="inlineStr"/>
-      <c r="Q91" s="8" t="inlineStr"/>
-      <c r="R91" s="8" t="inlineStr"/>
-      <c r="S91" s="8" t="inlineStr"/>
-      <c r="T91" s="8" t="inlineStr"/>
-      <c r="U91" s="8" t="inlineStr"/>
-      <c r="V91" s="8" t="inlineStr"/>
-      <c r="W91" s="9" t="n">
-        <v>25177.5</v>
-      </c>
-      <c r="X91" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y91" s="11" t="n">
-        <v>0.001779533584247569</v>
-      </c>
-    </row>
-    <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>MsPacman
-Random: 307.3
-Human: 6951.6</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 2673</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr"/>
-      <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr"/>
-      <c r="K92" s="4" t="inlineStr"/>
-      <c r="L92" s="4" t="inlineStr"/>
-      <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr"/>
-      <c r="O92" s="4" t="inlineStr"/>
-      <c r="P92" s="4" t="inlineStr"/>
-      <c r="Q92" s="4" t="inlineStr"/>
-      <c r="R92" s="4" t="inlineStr"/>
-      <c r="S92" s="4" t="inlineStr"/>
-      <c r="T92" s="4" t="inlineStr"/>
-      <c r="U92" s="4" t="inlineStr"/>
-      <c r="V92" s="4" t="inlineStr"/>
-      <c r="W92" s="5" t="inlineStr"/>
-      <c r="X92" s="6" t="n">
-        <v>-602</v>
-      </c>
-      <c r="Y92" s="7" t="n">
-        <v>-0.09060397634062278</v>
-      </c>
+      <c r="Y92" s="10" t="inlineStr"/>
+      <c r="Z92" s="11" t="inlineStr"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>1807.50</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr"/>
       <c r="D93" s="8" t="inlineStr"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>2007.00</t>
+          <t>30110.00</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr"/>
@@ -5161,17 +5273,13 @@
       <c r="J93" s="8" t="inlineStr"/>
       <c r="K93" s="8" t="inlineStr">
         <is>
-          <t>2388.00</t>
+          <t>20245.00</t>
         </is>
       </c>
       <c r="L93" s="8" t="inlineStr"/>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
-      <c r="O93" s="8" t="inlineStr">
-        <is>
-          <t>1754.00</t>
-        </is>
-      </c>
+      <c r="O93" s="8" t="inlineStr"/>
       <c r="P93" s="8" t="inlineStr"/>
       <c r="Q93" s="8" t="inlineStr"/>
       <c r="R93" s="8" t="inlineStr"/>
@@ -5179,57 +5287,77 @@
       <c r="T93" s="8" t="inlineStr"/>
       <c r="U93" s="8" t="inlineStr"/>
       <c r="V93" s="8" t="inlineStr"/>
-      <c r="W93" s="9" t="n">
-        <v>2071</v>
-      </c>
-      <c r="X93" s="10" t="inlineStr"/>
-      <c r="Y93" s="11" t="inlineStr"/>
+      <c r="W93" s="8" t="inlineStr"/>
+      <c r="X93" s="9" t="n">
+        <v>25177.5</v>
+      </c>
+      <c r="Y93" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z93" s="11" t="n">
+        <v>0.001779533584247569</v>
+      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="1" t="n"/>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr"/>
-      <c r="D94" s="8" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr"/>
-      <c r="F94" s="8" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr"/>
-      <c r="L94" s="8" t="inlineStr"/>
-      <c r="M94" s="8" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
-      <c r="O94" s="8" t="inlineStr">
-        <is>
-          <t>2110.50</t>
-        </is>
-      </c>
-      <c r="P94" s="8" t="inlineStr"/>
-      <c r="Q94" s="8" t="inlineStr"/>
-      <c r="R94" s="8" t="inlineStr"/>
-      <c r="S94" s="8" t="inlineStr"/>
-      <c r="T94" s="8" t="inlineStr"/>
-      <c r="U94" s="8" t="inlineStr"/>
-      <c r="V94" s="8" t="inlineStr"/>
-      <c r="W94" s="9" t="inlineStr"/>
-      <c r="X94" s="10" t="inlineStr"/>
-      <c r="Y94" s="11" t="inlineStr"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>MsPacman
+Random: 307.3
+Human: 6951.6</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 2673</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
+      <c r="D94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr"/>
+      <c r="P94" s="4" t="inlineStr"/>
+      <c r="Q94" s="4" t="inlineStr"/>
+      <c r="R94" s="4" t="inlineStr"/>
+      <c r="S94" s="4" t="inlineStr"/>
+      <c r="T94" s="4" t="inlineStr"/>
+      <c r="U94" s="4" t="inlineStr"/>
+      <c r="V94" s="4" t="inlineStr"/>
+      <c r="W94" s="4" t="inlineStr"/>
+      <c r="X94" s="5" t="inlineStr"/>
+      <c r="Y94" s="6" t="n">
+        <v>-602</v>
+      </c>
+      <c r="Z94" s="7" t="n">
+        <v>-0.09060397634062278</v>
+      </c>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>1807.50</t>
+        </is>
+      </c>
       <c r="D95" s="8" t="inlineStr"/>
-      <c r="E95" s="8" t="inlineStr"/>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>2007.00</t>
+        </is>
+      </c>
       <c r="F95" s="8" t="inlineStr"/>
       <c r="G95" s="8" t="inlineStr"/>
       <c r="H95" s="8" t="inlineStr"/>
@@ -5237,7 +5365,7 @@
       <c r="J95" s="8" t="inlineStr"/>
       <c r="K95" s="8" t="inlineStr">
         <is>
-          <t>2250.00</t>
+          <t>2388.00</t>
         </is>
       </c>
       <c r="L95" s="8" t="inlineStr"/>
@@ -5245,7 +5373,7 @@
       <c r="N95" s="8" t="inlineStr"/>
       <c r="O95" s="8" t="inlineStr">
         <is>
-          <t>1886.50</t>
+          <t>1754.00</t>
         </is>
       </c>
       <c r="P95" s="8" t="inlineStr"/>
@@ -5255,21 +5383,18 @@
       <c r="T95" s="8" t="inlineStr"/>
       <c r="U95" s="8" t="inlineStr"/>
       <c r="V95" s="8" t="inlineStr"/>
-      <c r="W95" s="9" t="n">
-        <v>2068.25</v>
-      </c>
+      <c r="W95" s="8" t="inlineStr"/>
       <c r="X95" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y95" s="11" t="n">
-        <v>-0.0004138885962403865</v>
-      </c>
+        <v>2071</v>
+      </c>
+      <c r="Y95" s="10" t="inlineStr"/>
+      <c r="Z95" s="11" t="inlineStr"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr"/>
@@ -5286,7 +5411,7 @@
       <c r="N96" s="8" t="inlineStr"/>
       <c r="O96" s="8" t="inlineStr">
         <is>
-          <t>2197.00</t>
+          <t>2110.50</t>
         </is>
       </c>
       <c r="P96" s="8" t="inlineStr"/>
@@ -5296,15 +5421,16 @@
       <c r="T96" s="8" t="inlineStr"/>
       <c r="U96" s="8" t="inlineStr"/>
       <c r="V96" s="8" t="inlineStr"/>
-      <c r="W96" s="9" t="inlineStr"/>
-      <c r="X96" s="10" t="inlineStr"/>
-      <c r="Y96" s="11" t="inlineStr"/>
+      <c r="W96" s="8" t="inlineStr"/>
+      <c r="X96" s="9" t="inlineStr"/>
+      <c r="Y96" s="10" t="inlineStr"/>
+      <c r="Z96" s="11" t="inlineStr"/>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
@@ -5315,13 +5441,17 @@
       <c r="H97" s="8" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr"/>
       <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>2250.00</t>
+        </is>
+      </c>
       <c r="L97" s="8" t="inlineStr"/>
       <c r="M97" s="8" t="inlineStr"/>
       <c r="N97" s="8" t="inlineStr"/>
-      <c r="O97" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="O97" s="8" t="inlineStr">
+        <is>
+          <t>1886.50</t>
         </is>
       </c>
       <c r="P97" s="8" t="inlineStr"/>
@@ -5331,87 +5461,77 @@
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
-      <c r="W97" s="9" t="inlineStr"/>
-      <c r="X97" s="10" t="inlineStr"/>
-      <c r="Y97" s="11" t="inlineStr"/>
+      <c r="W97" s="8" t="inlineStr"/>
+      <c r="X97" s="9" t="n">
+        <v>2068.25</v>
+      </c>
+      <c r="Y97" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z97" s="11" t="n">
+        <v>-0.0004138885962403865</v>
+      </c>
     </row>
     <row r="98" ht="24" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Pong
-Random: -20.7
-Human: 14.6</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr"/>
-      <c r="D98" s="4" t="inlineStr"/>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr"/>
-      <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="4" t="inlineStr"/>
-      <c r="J98" s="4" t="inlineStr"/>
-      <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="4" t="inlineStr"/>
-      <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr"/>
-      <c r="O98" s="4" t="inlineStr"/>
-      <c r="P98" s="4" t="inlineStr"/>
-      <c r="Q98" s="4" t="inlineStr"/>
-      <c r="R98" s="4" t="inlineStr"/>
-      <c r="S98" s="4" t="inlineStr"/>
-      <c r="T98" s="4" t="inlineStr"/>
-      <c r="U98" s="4" t="inlineStr"/>
-      <c r="V98" s="4" t="inlineStr"/>
-      <c r="W98" s="5" t="inlineStr"/>
-      <c r="X98" s="6" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="Y98" s="7" t="n">
-        <v>-0.1529745042492918</v>
-      </c>
+      <c r="A98" s="1" t="n"/>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr"/>
+      <c r="D98" s="8" t="inlineStr"/>
+      <c r="E98" s="8" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr"/>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
+      <c r="J98" s="8" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr"/>
+      <c r="L98" s="8" t="inlineStr"/>
+      <c r="M98" s="8" t="inlineStr"/>
+      <c r="N98" s="8" t="inlineStr"/>
+      <c r="O98" s="8" t="inlineStr">
+        <is>
+          <t>2197.00</t>
+        </is>
+      </c>
+      <c r="P98" s="8" t="inlineStr"/>
+      <c r="Q98" s="8" t="inlineStr"/>
+      <c r="R98" s="8" t="inlineStr"/>
+      <c r="S98" s="8" t="inlineStr"/>
+      <c r="T98" s="8" t="inlineStr"/>
+      <c r="U98" s="8" t="inlineStr"/>
+      <c r="V98" s="8" t="inlineStr"/>
+      <c r="W98" s="8" t="inlineStr"/>
+      <c r="X98" s="9" t="inlineStr"/>
+      <c r="Y98" s="10" t="inlineStr"/>
+      <c r="Z98" s="11" t="inlineStr"/>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr"/>
       <c r="D99" s="8" t="inlineStr"/>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
+      <c r="E99" s="8" t="inlineStr"/>
+      <c r="F99" s="8" t="inlineStr"/>
       <c r="G99" s="8" t="inlineStr"/>
       <c r="H99" s="8" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr"/>
       <c r="J99" s="8" t="inlineStr"/>
-      <c r="K99" s="8" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
+      <c r="K99" s="8" t="inlineStr"/>
+      <c r="L99" s="8" t="inlineStr"/>
       <c r="M99" s="8" t="inlineStr"/>
       <c r="N99" s="8" t="inlineStr"/>
-      <c r="O99" s="8" t="inlineStr"/>
+      <c r="O99" s="8" t="inlineStr">
+        <is>
+          <t>2170.00</t>
+        </is>
+      </c>
       <c r="P99" s="8" t="inlineStr"/>
       <c r="Q99" s="8" t="inlineStr"/>
       <c r="R99" s="8" t="inlineStr"/>
@@ -5419,373 +5539,373 @@
       <c r="T99" s="8" t="inlineStr"/>
       <c r="U99" s="8" t="inlineStr"/>
       <c r="V99" s="8" t="inlineStr"/>
-      <c r="W99" s="9" t="n">
+      <c r="W99" s="8" t="inlineStr"/>
+      <c r="X99" s="9" t="inlineStr"/>
+      <c r="Y99" s="10" t="inlineStr"/>
+      <c r="Z99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Pong
+Random: -20.7
+Human: 14.6</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr"/>
+      <c r="L100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr"/>
+      <c r="P100" s="4" t="inlineStr"/>
+      <c r="Q100" s="4" t="inlineStr"/>
+      <c r="R100" s="4" t="inlineStr"/>
+      <c r="S100" s="4" t="inlineStr"/>
+      <c r="T100" s="4" t="inlineStr"/>
+      <c r="U100" s="4" t="inlineStr"/>
+      <c r="V100" s="4" t="inlineStr"/>
+      <c r="W100" s="4" t="inlineStr"/>
+      <c r="X100" s="5" t="inlineStr"/>
+      <c r="Y100" s="6" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="Z100" s="7" t="n">
+        <v>-0.1529745042492918</v>
+      </c>
+    </row>
+    <row r="101" ht="24" customHeight="1">
+      <c r="A101" s="1" t="n"/>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr"/>
+      <c r="D101" s="8" t="inlineStr"/>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="inlineStr"/>
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>13.70</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="inlineStr"/>
+      <c r="N101" s="8" t="inlineStr"/>
+      <c r="O101" s="8" t="inlineStr"/>
+      <c r="P101" s="8" t="inlineStr"/>
+      <c r="Q101" s="8" t="inlineStr"/>
+      <c r="R101" s="8" t="inlineStr"/>
+      <c r="S101" s="8" t="inlineStr"/>
+      <c r="T101" s="8" t="inlineStr"/>
+      <c r="U101" s="8" t="inlineStr"/>
+      <c r="V101" s="8" t="inlineStr"/>
+      <c r="W101" s="8" t="inlineStr"/>
+      <c r="X101" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="X99" s="10" t="inlineStr"/>
-      <c r="Y99" s="11" t="inlineStr"/>
-    </row>
-    <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="1" t="n"/>
-      <c r="B100" s="1" t="inlineStr">
+      <c r="Y101" s="10" t="inlineStr"/>
+      <c r="Z101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102" ht="24" customHeight="1">
+      <c r="A102" s="1" t="n"/>
+      <c r="B102" s="1" t="inlineStr">
         <is>
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr"/>
-      <c r="D100" s="8" t="inlineStr"/>
-      <c r="E100" s="8" t="inlineStr"/>
-      <c r="F100" s="8" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr"/>
+      <c r="D102" s="8" t="inlineStr"/>
+      <c r="E102" s="8" t="inlineStr"/>
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>8.20</t>
         </is>
       </c>
-      <c r="G100" s="8" t="inlineStr"/>
-      <c r="H100" s="8" t="inlineStr"/>
-      <c r="I100" s="8" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr"/>
+      <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="8" t="inlineStr">
         <is>
           <t>14.45</t>
         </is>
       </c>
-      <c r="J100" s="8" t="inlineStr"/>
-      <c r="K100" s="8" t="inlineStr">
+      <c r="J102" s="8" t="inlineStr"/>
+      <c r="K102" s="8" t="inlineStr">
         <is>
           <t>9.80</t>
         </is>
       </c>
-      <c r="L100" s="8" t="inlineStr"/>
-      <c r="M100" s="8" t="inlineStr"/>
-      <c r="N100" s="8" t="inlineStr"/>
-      <c r="O100" s="8" t="inlineStr"/>
-      <c r="P100" s="8" t="inlineStr"/>
-      <c r="Q100" s="8" t="inlineStr"/>
-      <c r="R100" s="8" t="inlineStr"/>
-      <c r="S100" s="8" t="inlineStr"/>
-      <c r="T100" s="8" t="inlineStr"/>
-      <c r="U100" s="8" t="inlineStr"/>
-      <c r="V100" s="8" t="inlineStr"/>
-      <c r="W100" s="9" t="n">
+      <c r="L102" s="15" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="M102" s="8" t="inlineStr"/>
+      <c r="N102" s="8" t="inlineStr"/>
+      <c r="O102" s="8" t="inlineStr"/>
+      <c r="P102" s="8" t="inlineStr"/>
+      <c r="Q102" s="8" t="inlineStr"/>
+      <c r="R102" s="8" t="inlineStr"/>
+      <c r="S102" s="8" t="inlineStr"/>
+      <c r="T102" s="8" t="inlineStr"/>
+      <c r="U102" s="8" t="inlineStr"/>
+      <c r="V102" s="8" t="inlineStr"/>
+      <c r="W102" s="8" t="inlineStr"/>
+      <c r="X102" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="X100" s="9" t="n">
+      <c r="Y102" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="Y100" s="11" t="n">
+      <c r="Z102" s="11" t="n">
         <v>0.09631728045325781</v>
       </c>
     </row>
-    <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>PrivateEye
 Random: 24.9
 Human: 69571.3</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 7781</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr"/>
-      <c r="D101" s="4" t="inlineStr"/>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr"/>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="4" t="inlineStr"/>
-      <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="4" t="inlineStr"/>
-      <c r="M101" s="4" t="inlineStr"/>
-      <c r="N101" s="4" t="inlineStr"/>
-      <c r="O101" s="4" t="inlineStr"/>
-      <c r="P101" s="4" t="inlineStr"/>
-      <c r="Q101" s="4" t="inlineStr"/>
-      <c r="R101" s="4" t="inlineStr"/>
-      <c r="S101" s="4" t="inlineStr"/>
-      <c r="T101" s="4" t="inlineStr"/>
-      <c r="U101" s="4" t="inlineStr"/>
-      <c r="V101" s="4" t="inlineStr"/>
-      <c r="W101" s="5" t="inlineStr"/>
-      <c r="X101" s="6" t="n">
+      <c r="C103" s="4" t="inlineStr"/>
+      <c r="D103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr"/>
+      <c r="L103" s="4" t="inlineStr"/>
+      <c r="M103" s="4" t="inlineStr"/>
+      <c r="N103" s="4" t="inlineStr"/>
+      <c r="O103" s="4" t="inlineStr"/>
+      <c r="P103" s="4" t="inlineStr"/>
+      <c r="Q103" s="4" t="inlineStr"/>
+      <c r="R103" s="4" t="inlineStr"/>
+      <c r="S103" s="4" t="inlineStr"/>
+      <c r="T103" s="4" t="inlineStr"/>
+      <c r="U103" s="4" t="inlineStr"/>
+      <c r="V103" s="4" t="inlineStr"/>
+      <c r="W103" s="4" t="inlineStr"/>
+      <c r="X103" s="5" t="inlineStr"/>
+      <c r="Y103" s="6" t="n">
         <v>-6778.35</v>
       </c>
-      <c r="Y101" s="7" t="n">
+      <c r="Z103" s="7" t="n">
         <v>-0.09746514557187719</v>
       </c>
     </row>
-    <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="1" t="n"/>
-      <c r="B102" s="1" t="inlineStr">
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="1" t="n"/>
+      <c r="B104" s="1" t="inlineStr">
         <is>
           <t>Retrieval 미사용</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>75.30</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr"/>
-      <c r="E102" s="8" t="inlineStr"/>
-      <c r="F102" s="8" t="inlineStr"/>
-      <c r="G102" s="8" t="inlineStr"/>
-      <c r="H102" s="8" t="inlineStr"/>
-      <c r="I102" s="8" t="inlineStr"/>
-      <c r="J102" s="8" t="inlineStr"/>
-      <c r="K102" s="8" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr"/>
+      <c r="E104" s="8" t="inlineStr"/>
+      <c r="F104" s="8" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr"/>
+      <c r="H104" s="8" t="inlineStr"/>
+      <c r="I104" s="8" t="inlineStr"/>
+      <c r="J104" s="8" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr">
         <is>
           <t>199.35</t>
         </is>
       </c>
-      <c r="L102" s="8" t="inlineStr"/>
-      <c r="M102" s="8" t="inlineStr"/>
-      <c r="N102" s="8" t="inlineStr"/>
-      <c r="O102" s="13" t="inlineStr">
+      <c r="L104" s="8" t="inlineStr"/>
+      <c r="M104" s="8" t="inlineStr"/>
+      <c r="N104" s="8" t="inlineStr"/>
+      <c r="O104" s="13" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P102" s="8" t="inlineStr">
+      <c r="P104" s="8" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="Q102" s="8" t="inlineStr">
+      <c r="Q104" s="8" t="inlineStr">
         <is>
           <t>3551.75</t>
         </is>
       </c>
-      <c r="R102" s="8" t="inlineStr"/>
-      <c r="S102" s="8" t="inlineStr"/>
-      <c r="T102" s="8" t="inlineStr"/>
-      <c r="U102" s="8" t="inlineStr">
+      <c r="R104" s="8" t="inlineStr"/>
+      <c r="S104" s="8" t="inlineStr"/>
+      <c r="T104" s="8" t="inlineStr"/>
+      <c r="U104" s="8" t="inlineStr"/>
+      <c r="V104" s="8" t="inlineStr">
         <is>
           <t>159.50</t>
         </is>
       </c>
-      <c r="V102" s="8" t="inlineStr"/>
-      <c r="W102" s="9" t="n">
+      <c r="W104" s="8" t="inlineStr"/>
+      <c r="X104" s="9" t="n">
         <v>1002.65</v>
       </c>
-      <c r="X102" s="10" t="inlineStr"/>
-      <c r="Y102" s="11" t="inlineStr"/>
-    </row>
-    <row r="103" ht="24" customHeight="1">
-      <c r="A103" s="1" t="n"/>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr"/>
-      <c r="D103" s="8" t="inlineStr"/>
-      <c r="E103" s="8" t="inlineStr"/>
-      <c r="F103" s="8" t="inlineStr"/>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="8" t="inlineStr"/>
-      <c r="I103" s="8" t="inlineStr"/>
-      <c r="J103" s="8" t="inlineStr"/>
-      <c r="K103" s="8" t="inlineStr">
-        <is>
-          <t>191.95</t>
-        </is>
-      </c>
-      <c r="L103" s="8" t="inlineStr"/>
-      <c r="M103" s="8" t="inlineStr"/>
-      <c r="N103" s="8" t="inlineStr"/>
-      <c r="O103" s="13" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="P103" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q103" s="8" t="inlineStr">
-        <is>
-          <t>166.80</t>
-        </is>
-      </c>
-      <c r="R103" s="8" t="inlineStr"/>
-      <c r="S103" s="8" t="inlineStr"/>
-      <c r="T103" s="8" t="inlineStr"/>
-      <c r="U103" s="8" t="inlineStr">
-        <is>
-          <t>153.20</t>
-        </is>
-      </c>
-      <c r="V103" s="8" t="inlineStr"/>
-      <c r="W103" s="9" t="n">
-        <v>152.9875</v>
-      </c>
-      <c r="X103" s="9" t="n">
-        <v>849.6624999999999</v>
-      </c>
-      <c r="Y103" s="11" t="n">
-        <v>-0.01221720319096315</v>
-      </c>
-    </row>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Qbert
-Random: 163.9
-Human: 13455.0</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4522</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr"/>
-      <c r="D104" s="4" t="inlineStr"/>
-      <c r="E104" s="4" t="inlineStr"/>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr"/>
-      <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="4" t="inlineStr"/>
-      <c r="K104" s="4" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr"/>
-      <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr"/>
-      <c r="O104" s="4" t="inlineStr"/>
-      <c r="P104" s="4" t="inlineStr"/>
-      <c r="Q104" s="4" t="inlineStr"/>
-      <c r="R104" s="4" t="inlineStr"/>
-      <c r="S104" s="4" t="inlineStr"/>
-      <c r="T104" s="4" t="inlineStr"/>
-      <c r="U104" s="4" t="inlineStr"/>
-      <c r="V104" s="4" t="inlineStr"/>
-      <c r="W104" s="5" t="inlineStr"/>
-      <c r="X104" s="6" t="n">
-        <v>-1662.9375</v>
-      </c>
-      <c r="Y104" s="7" t="n">
-        <v>-0.1251166193919239</v>
-      </c>
+      <c r="Y104" s="10" t="inlineStr"/>
+      <c r="Z104" s="11" t="inlineStr"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr"/>
       <c r="D105" s="8" t="inlineStr"/>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
+      <c r="E105" s="8" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr"/>
       <c r="G105" s="8" t="inlineStr"/>
       <c r="H105" s="8" t="inlineStr"/>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
+      <c r="I105" s="8" t="inlineStr"/>
       <c r="J105" s="8" t="inlineStr"/>
       <c r="K105" s="8" t="inlineStr">
         <is>
-          <t>3193.75</t>
+          <t>191.95</t>
         </is>
       </c>
       <c r="L105" s="8" t="inlineStr"/>
       <c r="M105" s="8" t="inlineStr"/>
       <c r="N105" s="8" t="inlineStr"/>
-      <c r="O105" s="8" t="inlineStr">
-        <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="P105" s="8" t="inlineStr"/>
-      <c r="Q105" s="8" t="inlineStr"/>
+      <c r="O105" s="13" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="P105" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q105" s="8" t="inlineStr">
+        <is>
+          <t>166.80</t>
+        </is>
+      </c>
       <c r="R105" s="8" t="inlineStr"/>
       <c r="S105" s="8" t="inlineStr"/>
       <c r="T105" s="8" t="inlineStr"/>
       <c r="U105" s="8" t="inlineStr"/>
-      <c r="V105" s="8" t="inlineStr"/>
-      <c r="W105" s="9" t="n">
-        <v>2859.0625</v>
-      </c>
-      <c r="X105" s="10" t="inlineStr"/>
-      <c r="Y105" s="11" t="inlineStr"/>
+      <c r="V105" s="8" t="inlineStr">
+        <is>
+          <t>153.20</t>
+        </is>
+      </c>
+      <c r="W105" s="8" t="inlineStr"/>
+      <c r="X105" s="9" t="n">
+        <v>152.9875</v>
+      </c>
+      <c r="Y105" s="9" t="n">
+        <v>849.6624999999999</v>
+      </c>
+      <c r="Z105" s="11" t="n">
+        <v>-0.01221720319096315</v>
+      </c>
     </row>
     <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="1" t="n"/>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t>2818.75</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr"/>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t>1918.75</t>
-        </is>
-      </c>
-      <c r="F106" s="8" t="inlineStr"/>
-      <c r="G106" s="8" t="inlineStr"/>
-      <c r="H106" s="8" t="inlineStr"/>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>2553.75</t>
-        </is>
-      </c>
-      <c r="J106" s="8" t="inlineStr"/>
-      <c r="K106" s="8" t="inlineStr"/>
-      <c r="L106" s="8" t="inlineStr"/>
-      <c r="M106" s="8" t="inlineStr"/>
-      <c r="N106" s="8" t="inlineStr"/>
-      <c r="O106" s="8" t="inlineStr">
-        <is>
-          <t>3782.50</t>
-        </is>
-      </c>
-      <c r="P106" s="8" t="inlineStr"/>
-      <c r="Q106" s="8" t="inlineStr"/>
-      <c r="R106" s="8" t="inlineStr"/>
-      <c r="S106" s="8" t="inlineStr"/>
-      <c r="T106" s="8" t="inlineStr"/>
-      <c r="U106" s="8" t="inlineStr"/>
-      <c r="V106" s="8" t="inlineStr"/>
-      <c r="W106" s="9" t="inlineStr"/>
-      <c r="X106" s="10" t="inlineStr"/>
-      <c r="Y106" s="11" t="inlineStr"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Qbert
+Random: 163.9
+Human: 13455.0</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4522</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr"/>
+      <c r="J106" s="4" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr"/>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="inlineStr"/>
+      <c r="N106" s="4" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr"/>
+      <c r="P106" s="4" t="inlineStr"/>
+      <c r="Q106" s="4" t="inlineStr"/>
+      <c r="R106" s="4" t="inlineStr"/>
+      <c r="S106" s="4" t="inlineStr"/>
+      <c r="T106" s="4" t="inlineStr"/>
+      <c r="U106" s="4" t="inlineStr"/>
+      <c r="V106" s="4" t="inlineStr"/>
+      <c r="W106" s="4" t="inlineStr"/>
+      <c r="X106" s="5" t="inlineStr"/>
+      <c r="Y106" s="6" t="n">
+        <v>-1662.9375</v>
+      </c>
+      <c r="Z106" s="7" t="n">
+        <v>-0.1251166193919239</v>
+      </c>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>2702.50</t>
+          <t>1771.25</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr"/>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>4056.25</t>
+          <t>3786.25</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr"/>
@@ -5793,13 +5913,13 @@
       <c r="H107" s="8" t="inlineStr"/>
       <c r="I107" s="13" t="inlineStr">
         <is>
-          <t>2338.75</t>
+          <t>2940.00</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr"/>
       <c r="K107" s="8" t="inlineStr">
         <is>
-          <t>2608.75</t>
+          <t>3193.75</t>
         </is>
       </c>
       <c r="L107" s="8" t="inlineStr"/>
@@ -5807,7 +5927,7 @@
       <c r="N107" s="8" t="inlineStr"/>
       <c r="O107" s="8" t="inlineStr">
         <is>
-          <t>2895.00</t>
+          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
         </is>
       </c>
       <c r="P107" s="8" t="inlineStr"/>
@@ -5817,75 +5937,91 @@
       <c r="T107" s="8" t="inlineStr"/>
       <c r="U107" s="8" t="inlineStr"/>
       <c r="V107" s="8" t="inlineStr"/>
-      <c r="W107" s="9" t="n">
-        <v>3065.625</v>
-      </c>
+      <c r="W107" s="8" t="inlineStr"/>
       <c r="X107" s="9" t="n">
-        <v>206.5625</v>
-      </c>
-      <c r="Y107" s="11" t="n">
-        <v>0.01554141493179646</v>
-      </c>
+        <v>2859.0625</v>
+      </c>
+      <c r="Y107" s="10" t="inlineStr"/>
+      <c r="Z107" s="11" t="inlineStr"/>
     </row>
     <row r="108" ht="24" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>RoadRunner
-Random: 11.5
-Human: 7845.0</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 17564</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr"/>
-      <c r="D108" s="4" t="inlineStr"/>
-      <c r="E108" s="4" t="inlineStr"/>
-      <c r="F108" s="4" t="inlineStr"/>
-      <c r="G108" s="4" t="inlineStr"/>
-      <c r="H108" s="4" t="inlineStr"/>
-      <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="4" t="inlineStr"/>
-      <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="4" t="inlineStr"/>
-      <c r="M108" s="4" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr"/>
-      <c r="O108" s="4" t="inlineStr"/>
-      <c r="P108" s="4" t="inlineStr"/>
-      <c r="Q108" s="4" t="inlineStr"/>
-      <c r="R108" s="4" t="inlineStr"/>
-      <c r="S108" s="4" t="inlineStr"/>
-      <c r="T108" s="4" t="inlineStr"/>
-      <c r="U108" s="4" t="inlineStr"/>
-      <c r="V108" s="4" t="inlineStr"/>
-      <c r="W108" s="5" t="inlineStr"/>
-      <c r="X108" s="6" t="n">
-        <v>-8627.75</v>
-      </c>
-      <c r="Y108" s="7" t="n">
-        <v>-1.101391459756175</v>
-      </c>
+      <c r="A108" s="1" t="n"/>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>2818.75</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr"/>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>1918.75</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr"/>
+      <c r="G108" s="8" t="inlineStr"/>
+      <c r="H108" s="8" t="inlineStr"/>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>2553.75</t>
+        </is>
+      </c>
+      <c r="J108" s="8" t="inlineStr"/>
+      <c r="K108" s="8" t="inlineStr"/>
+      <c r="L108" s="8" t="inlineStr"/>
+      <c r="M108" s="8" t="inlineStr"/>
+      <c r="N108" s="8" t="inlineStr"/>
+      <c r="O108" s="8" t="inlineStr">
+        <is>
+          <t>3782.50</t>
+        </is>
+      </c>
+      <c r="P108" s="8" t="inlineStr"/>
+      <c r="Q108" s="8" t="inlineStr"/>
+      <c r="R108" s="8" t="inlineStr"/>
+      <c r="S108" s="8" t="inlineStr"/>
+      <c r="T108" s="8" t="inlineStr"/>
+      <c r="U108" s="8" t="inlineStr"/>
+      <c r="V108" s="8" t="inlineStr"/>
+      <c r="W108" s="8" t="inlineStr"/>
+      <c r="X108" s="9" t="inlineStr"/>
+      <c r="Y108" s="10" t="inlineStr"/>
+      <c r="Z108" s="11" t="inlineStr"/>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>2702.50</t>
+        </is>
+      </c>
       <c r="D109" s="8" t="inlineStr"/>
-      <c r="E109" s="8" t="inlineStr"/>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>4056.25</t>
+        </is>
+      </c>
       <c r="F109" s="8" t="inlineStr"/>
       <c r="G109" s="8" t="inlineStr"/>
       <c r="H109" s="8" t="inlineStr"/>
-      <c r="I109" s="8" t="inlineStr"/>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>2338.75</t>
+        </is>
+      </c>
       <c r="J109" s="8" t="inlineStr"/>
       <c r="K109" s="8" t="inlineStr">
         <is>
-          <t>8610.00</t>
+          <t>2608.75</t>
         </is>
       </c>
       <c r="L109" s="8" t="inlineStr"/>
@@ -5893,78 +6029,74 @@
       <c r="N109" s="8" t="inlineStr"/>
       <c r="O109" s="8" t="inlineStr">
         <is>
-          <t>7290.00</t>
-        </is>
-      </c>
-      <c r="P109" s="8" t="inlineStr">
-        <is>
-          <t>9690.00</t>
-        </is>
-      </c>
-      <c r="Q109" s="8" t="inlineStr">
-        <is>
-          <t>10155.00</t>
-        </is>
-      </c>
+          <t>2895.00</t>
+        </is>
+      </c>
+      <c r="P109" s="8" t="inlineStr"/>
+      <c r="Q109" s="8" t="inlineStr"/>
       <c r="R109" s="8" t="inlineStr"/>
       <c r="S109" s="8" t="inlineStr"/>
       <c r="T109" s="8" t="inlineStr"/>
       <c r="U109" s="8" t="inlineStr"/>
       <c r="V109" s="8" t="inlineStr"/>
-      <c r="W109" s="9" t="n">
-        <v>8936.25</v>
-      </c>
-      <c r="X109" s="10" t="inlineStr"/>
-      <c r="Y109" s="11" t="inlineStr"/>
+      <c r="W109" s="8" t="inlineStr"/>
+      <c r="X109" s="9" t="n">
+        <v>3065.625</v>
+      </c>
+      <c r="Y109" s="9" t="n">
+        <v>206.5625</v>
+      </c>
+      <c r="Z109" s="11" t="n">
+        <v>0.01554141493179646</v>
+      </c>
     </row>
     <row r="110" ht="24" customHeight="1">
-      <c r="A110" s="1" t="n"/>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr"/>
-      <c r="D110" s="8" t="inlineStr"/>
-      <c r="E110" s="8" t="inlineStr"/>
-      <c r="F110" s="8" t="inlineStr"/>
-      <c r="G110" s="8" t="inlineStr"/>
-      <c r="H110" s="8" t="inlineStr"/>
-      <c r="I110" s="8" t="inlineStr"/>
-      <c r="J110" s="8" t="inlineStr"/>
-      <c r="K110" s="8" t="inlineStr"/>
-      <c r="L110" s="8" t="inlineStr"/>
-      <c r="M110" s="8" t="inlineStr"/>
-      <c r="N110" s="8" t="inlineStr"/>
-      <c r="O110" s="8" t="inlineStr">
-        <is>
-          <t>8520.00</t>
-        </is>
-      </c>
-      <c r="P110" s="8" t="inlineStr">
-        <is>
-          <t>11830.00</t>
-        </is>
-      </c>
-      <c r="Q110" s="8" t="inlineStr">
-        <is>
-          <t>16805.00</t>
-        </is>
-      </c>
-      <c r="R110" s="8" t="inlineStr"/>
-      <c r="S110" s="8" t="inlineStr"/>
-      <c r="T110" s="8" t="inlineStr"/>
-      <c r="U110" s="8" t="inlineStr"/>
-      <c r="V110" s="8" t="inlineStr"/>
-      <c r="W110" s="9" t="inlineStr"/>
-      <c r="X110" s="10" t="inlineStr"/>
-      <c r="Y110" s="11" t="inlineStr"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>RoadRunner
+Random: 11.5
+Human: 7845.0</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 17564</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr"/>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr"/>
+      <c r="L110" s="4" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr"/>
+      <c r="N110" s="4" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr"/>
+      <c r="P110" s="4" t="inlineStr"/>
+      <c r="Q110" s="4" t="inlineStr"/>
+      <c r="R110" s="4" t="inlineStr"/>
+      <c r="S110" s="4" t="inlineStr"/>
+      <c r="T110" s="4" t="inlineStr"/>
+      <c r="U110" s="4" t="inlineStr"/>
+      <c r="V110" s="4" t="inlineStr"/>
+      <c r="W110" s="4" t="inlineStr"/>
+      <c r="X110" s="5" t="inlineStr"/>
+      <c r="Y110" s="6" t="n">
+        <v>-8627.75</v>
+      </c>
+      <c r="Z110" s="7" t="n">
+        <v>-1.101391459756175</v>
+      </c>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr"/>
@@ -5977,7 +6109,7 @@
       <c r="J111" s="8" t="inlineStr"/>
       <c r="K111" s="8" t="inlineStr">
         <is>
-          <t>8195.00</t>
+          <t>8610.00</t>
         </is>
       </c>
       <c r="L111" s="8" t="inlineStr"/>
@@ -5985,17 +6117,17 @@
       <c r="N111" s="8" t="inlineStr"/>
       <c r="O111" s="8" t="inlineStr">
         <is>
-          <t>8325.00</t>
+          <t>7290.00</t>
         </is>
       </c>
       <c r="P111" s="8" t="inlineStr">
         <is>
-          <t>12890.00</t>
+          <t>9690.00</t>
         </is>
       </c>
       <c r="Q111" s="8" t="inlineStr">
         <is>
-          <t>16980.00</t>
+          <t>10155.00</t>
         </is>
       </c>
       <c r="R111" s="8" t="inlineStr"/>
@@ -6003,69 +6135,65 @@
       <c r="T111" s="8" t="inlineStr"/>
       <c r="U111" s="8" t="inlineStr"/>
       <c r="V111" s="8" t="inlineStr"/>
-      <c r="W111" s="9" t="n">
-        <v>11597.5</v>
-      </c>
+      <c r="W111" s="8" t="inlineStr"/>
       <c r="X111" s="9" t="n">
-        <v>2661.25</v>
-      </c>
-      <c r="Y111" s="11" t="n">
-        <v>0.3397268143230995</v>
-      </c>
+        <v>8936.25</v>
+      </c>
+      <c r="Y111" s="10" t="inlineStr"/>
+      <c r="Z111" s="11" t="inlineStr"/>
     </row>
     <row r="112" ht="24" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Seaquest
-Random: 68.4
-Human: 42054.7</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 525</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr"/>
-      <c r="D112" s="4" t="inlineStr"/>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="4" t="inlineStr"/>
-      <c r="H112" s="4" t="inlineStr"/>
-      <c r="I112" s="4" t="inlineStr"/>
-      <c r="J112" s="4" t="inlineStr"/>
-      <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="4" t="inlineStr"/>
-      <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr"/>
-      <c r="O112" s="4" t="inlineStr"/>
-      <c r="P112" s="4" t="inlineStr"/>
-      <c r="Q112" s="4" t="inlineStr"/>
-      <c r="R112" s="4" t="inlineStr"/>
-      <c r="S112" s="4" t="inlineStr"/>
-      <c r="T112" s="4" t="inlineStr"/>
-      <c r="U112" s="4" t="inlineStr"/>
-      <c r="V112" s="4" t="inlineStr"/>
-      <c r="W112" s="5" t="inlineStr"/>
-      <c r="X112" s="6" t="n">
-        <v>-64.33333333333331</v>
-      </c>
-      <c r="Y112" s="7" t="n">
-        <v>-0.001532245835744834</v>
-      </c>
+      <c r="A112" s="1" t="n"/>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr"/>
+      <c r="D112" s="8" t="inlineStr"/>
+      <c r="E112" s="8" t="inlineStr"/>
+      <c r="F112" s="8" t="inlineStr"/>
+      <c r="G112" s="8" t="inlineStr"/>
+      <c r="H112" s="8" t="inlineStr"/>
+      <c r="I112" s="8" t="inlineStr"/>
+      <c r="J112" s="8" t="inlineStr"/>
+      <c r="K112" s="8" t="inlineStr"/>
+      <c r="L112" s="8" t="inlineStr"/>
+      <c r="M112" s="8" t="inlineStr"/>
+      <c r="N112" s="8" t="inlineStr"/>
+      <c r="O112" s="8" t="inlineStr">
+        <is>
+          <t>8520.00</t>
+        </is>
+      </c>
+      <c r="P112" s="8" t="inlineStr">
+        <is>
+          <t>11830.00</t>
+        </is>
+      </c>
+      <c r="Q112" s="8" t="inlineStr">
+        <is>
+          <t>16805.00</t>
+        </is>
+      </c>
+      <c r="R112" s="8" t="inlineStr"/>
+      <c r="S112" s="8" t="inlineStr"/>
+      <c r="T112" s="8" t="inlineStr"/>
+      <c r="U112" s="8" t="inlineStr"/>
+      <c r="V112" s="8" t="inlineStr"/>
+      <c r="W112" s="8" t="inlineStr"/>
+      <c r="X112" s="9" t="inlineStr"/>
+      <c r="Y112" s="10" t="inlineStr"/>
+      <c r="Z112" s="11" t="inlineStr"/>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>454.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="8" t="inlineStr"/>
       <c r="E113" s="8" t="inlineStr"/>
       <c r="F113" s="8" t="inlineStr"/>
@@ -6075,7 +6203,7 @@
       <c r="J113" s="8" t="inlineStr"/>
       <c r="K113" s="8" t="inlineStr">
         <is>
-          <t>494.00</t>
+          <t>8195.00</t>
         </is>
       </c>
       <c r="L113" s="8" t="inlineStr"/>
@@ -6083,73 +6211,89 @@
       <c r="N113" s="8" t="inlineStr"/>
       <c r="O113" s="8" t="inlineStr">
         <is>
-          <t>418.00</t>
-        </is>
-      </c>
-      <c r="P113" s="8" t="inlineStr"/>
-      <c r="Q113" s="8" t="inlineStr"/>
+          <t>8325.00</t>
+        </is>
+      </c>
+      <c r="P113" s="8" t="inlineStr">
+        <is>
+          <t>12890.00</t>
+        </is>
+      </c>
+      <c r="Q113" s="8" t="inlineStr">
+        <is>
+          <t>16980.00</t>
+        </is>
+      </c>
       <c r="R113" s="8" t="inlineStr"/>
       <c r="S113" s="8" t="inlineStr"/>
       <c r="T113" s="8" t="inlineStr"/>
-      <c r="U113" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
+      <c r="U113" s="8" t="inlineStr"/>
       <c r="V113" s="8" t="inlineStr"/>
-      <c r="W113" s="9" t="n">
-        <v>460.6666666666667</v>
-      </c>
-      <c r="X113" s="10" t="inlineStr"/>
-      <c r="Y113" s="11" t="inlineStr"/>
+      <c r="W113" s="8" t="inlineStr"/>
+      <c r="X113" s="9" t="n">
+        <v>11597.5</v>
+      </c>
+      <c r="Y113" s="9" t="n">
+        <v>2661.25</v>
+      </c>
+      <c r="Z113" s="11" t="n">
+        <v>0.3397268143230995</v>
+      </c>
     </row>
     <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="1" t="n"/>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr"/>
-      <c r="D114" s="8" t="inlineStr"/>
-      <c r="E114" s="8" t="inlineStr"/>
-      <c r="F114" s="8" t="inlineStr"/>
-      <c r="G114" s="8" t="inlineStr"/>
-      <c r="H114" s="8" t="inlineStr"/>
-      <c r="I114" s="8" t="inlineStr"/>
-      <c r="J114" s="8" t="inlineStr"/>
-      <c r="K114" s="8" t="inlineStr"/>
-      <c r="L114" s="8" t="inlineStr"/>
-      <c r="M114" s="8" t="inlineStr"/>
-      <c r="N114" s="8" t="inlineStr"/>
-      <c r="O114" s="8" t="inlineStr">
-        <is>
-          <t>476.00</t>
-        </is>
-      </c>
-      <c r="P114" s="8" t="inlineStr"/>
-      <c r="Q114" s="8" t="inlineStr"/>
-      <c r="R114" s="8" t="inlineStr"/>
-      <c r="S114" s="8" t="inlineStr"/>
-      <c r="T114" s="8" t="inlineStr"/>
-      <c r="U114" s="8" t="inlineStr">
-        <is>
-          <t>557.00</t>
-        </is>
-      </c>
-      <c r="V114" s="8" t="inlineStr"/>
-      <c r="W114" s="9" t="inlineStr"/>
-      <c r="X114" s="10" t="inlineStr"/>
-      <c r="Y114" s="11" t="inlineStr"/>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Seaquest
+Random: 68.4
+Human: 42054.7</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 525</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr"/>
+      <c r="D114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr"/>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr"/>
+      <c r="K114" s="4" t="inlineStr"/>
+      <c r="L114" s="4" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr"/>
+      <c r="N114" s="4" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr"/>
+      <c r="P114" s="4" t="inlineStr"/>
+      <c r="Q114" s="4" t="inlineStr"/>
+      <c r="R114" s="4" t="inlineStr"/>
+      <c r="S114" s="4" t="inlineStr"/>
+      <c r="T114" s="4" t="inlineStr"/>
+      <c r="U114" s="4" t="inlineStr"/>
+      <c r="V114" s="4" t="inlineStr"/>
+      <c r="W114" s="4" t="inlineStr"/>
+      <c r="X114" s="5" t="inlineStr"/>
+      <c r="Y114" s="6" t="n">
+        <v>-64.33333333333331</v>
+      </c>
+      <c r="Z114" s="7" t="n">
+        <v>-0.001532245835744834</v>
+      </c>
     </row>
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>454.00</t>
+        </is>
+      </c>
       <c r="D115" s="8" t="inlineStr"/>
       <c r="E115" s="8" t="inlineStr"/>
       <c r="F115" s="8" t="inlineStr"/>
@@ -6159,7 +6303,7 @@
       <c r="J115" s="8" t="inlineStr"/>
       <c r="K115" s="8" t="inlineStr">
         <is>
-          <t>521.00</t>
+          <t>494.00</t>
         </is>
       </c>
       <c r="L115" s="8" t="inlineStr"/>
@@ -6167,7 +6311,7 @@
       <c r="N115" s="8" t="inlineStr"/>
       <c r="O115" s="8" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>418.00</t>
         </is>
       </c>
       <c r="P115" s="8" t="inlineStr"/>
@@ -6175,27 +6319,24 @@
       <c r="R115" s="8" t="inlineStr"/>
       <c r="S115" s="8" t="inlineStr"/>
       <c r="T115" s="8" t="inlineStr"/>
-      <c r="U115" s="8" t="inlineStr">
-        <is>
-          <t>545.00</t>
-        </is>
-      </c>
-      <c r="V115" s="8" t="inlineStr"/>
-      <c r="W115" s="9" t="n">
-        <v>505.3333333333333</v>
-      </c>
+      <c r="U115" s="8" t="inlineStr"/>
+      <c r="V115" s="8" t="inlineStr">
+        <is>
+          <t>470.00</t>
+        </is>
+      </c>
+      <c r="W115" s="8" t="inlineStr"/>
       <c r="X115" s="9" t="n">
-        <v>44.66666666666663</v>
-      </c>
-      <c r="Y115" s="11" t="n">
-        <v>0.001063839077667397</v>
-      </c>
+        <v>460.6666666666667</v>
+      </c>
+      <c r="Y115" s="10" t="inlineStr"/>
+      <c r="Z115" s="11" t="inlineStr"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr"/>
@@ -6210,27 +6351,32 @@
       <c r="L116" s="8" t="inlineStr"/>
       <c r="M116" s="8" t="inlineStr"/>
       <c r="N116" s="8" t="inlineStr"/>
-      <c r="O116" s="8" t="inlineStr"/>
+      <c r="O116" s="8" t="inlineStr">
+        <is>
+          <t>476.00</t>
+        </is>
+      </c>
       <c r="P116" s="8" t="inlineStr"/>
       <c r="Q116" s="8" t="inlineStr"/>
       <c r="R116" s="8" t="inlineStr"/>
       <c r="S116" s="8" t="inlineStr"/>
       <c r="T116" s="8" t="inlineStr"/>
-      <c r="U116" s="8" t="inlineStr">
-        <is>
-          <t>411.00</t>
-        </is>
-      </c>
-      <c r="V116" s="8" t="inlineStr"/>
-      <c r="W116" s="9" t="inlineStr"/>
-      <c r="X116" s="10" t="inlineStr"/>
-      <c r="Y116" s="11" t="inlineStr"/>
+      <c r="U116" s="8" t="inlineStr"/>
+      <c r="V116" s="8" t="inlineStr">
+        <is>
+          <t>557.00</t>
+        </is>
+      </c>
+      <c r="W116" s="8" t="inlineStr"/>
+      <c r="X116" s="9" t="inlineStr"/>
+      <c r="Y116" s="10" t="inlineStr"/>
+      <c r="Z116" s="11" t="inlineStr"/>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr"/>
@@ -6241,177 +6387,177 @@
       <c r="H117" s="8" t="inlineStr"/>
       <c r="I117" s="8" t="inlineStr"/>
       <c r="J117" s="8" t="inlineStr"/>
-      <c r="K117" s="8" t="inlineStr"/>
+      <c r="K117" s="8" t="inlineStr">
+        <is>
+          <t>521.00</t>
+        </is>
+      </c>
       <c r="L117" s="8" t="inlineStr"/>
       <c r="M117" s="8" t="inlineStr"/>
       <c r="N117" s="8" t="inlineStr"/>
-      <c r="O117" s="8" t="inlineStr"/>
+      <c r="O117" s="8" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
       <c r="P117" s="8" t="inlineStr"/>
       <c r="Q117" s="8" t="inlineStr"/>
       <c r="R117" s="8" t="inlineStr"/>
       <c r="S117" s="8" t="inlineStr"/>
       <c r="T117" s="8" t="inlineStr"/>
-      <c r="U117" s="8" t="inlineStr">
-        <is>
-          <t>415.00</t>
-        </is>
-      </c>
-      <c r="V117" s="8" t="inlineStr"/>
-      <c r="W117" s="9" t="inlineStr"/>
-      <c r="X117" s="10" t="inlineStr"/>
-      <c r="Y117" s="11" t="inlineStr"/>
+      <c r="U117" s="8" t="inlineStr"/>
+      <c r="V117" s="8" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
+      <c r="W117" s="8" t="inlineStr"/>
+      <c r="X117" s="9" t="n">
+        <v>505.3333333333333</v>
+      </c>
+      <c r="Y117" s="9" t="n">
+        <v>44.66666666666663</v>
+      </c>
+      <c r="Z117" s="11" t="n">
+        <v>0.001063839077667397</v>
+      </c>
     </row>
     <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>UpNDown
-Random: 533.4
-Human: 11693.2</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7985</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr"/>
-      <c r="D118" s="4" t="inlineStr"/>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
-      <c r="G118" s="4" t="inlineStr"/>
-      <c r="H118" s="4" t="inlineStr"/>
-      <c r="I118" s="4" t="inlineStr"/>
-      <c r="J118" s="4" t="inlineStr"/>
-      <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="4" t="inlineStr"/>
-      <c r="M118" s="4" t="inlineStr"/>
-      <c r="N118" s="4" t="inlineStr"/>
-      <c r="O118" s="4" t="inlineStr"/>
-      <c r="P118" s="4" t="inlineStr"/>
-      <c r="Q118" s="4" t="inlineStr"/>
-      <c r="R118" s="4" t="inlineStr"/>
-      <c r="S118" s="4" t="inlineStr"/>
-      <c r="T118" s="4" t="inlineStr"/>
-      <c r="U118" s="4" t="inlineStr"/>
-      <c r="V118" s="4" t="inlineStr"/>
-      <c r="W118" s="5" t="inlineStr"/>
-      <c r="X118" s="6" t="n">
-        <v>-2963</v>
-      </c>
-      <c r="Y118" s="7" t="n">
-        <v>-0.2655065502966003</v>
-      </c>
+      <c r="A118" s="1" t="n"/>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr"/>
+      <c r="D118" s="8" t="inlineStr"/>
+      <c r="E118" s="8" t="inlineStr"/>
+      <c r="F118" s="8" t="inlineStr"/>
+      <c r="G118" s="8" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr"/>
+      <c r="I118" s="8" t="inlineStr"/>
+      <c r="J118" s="8" t="inlineStr"/>
+      <c r="K118" s="8" t="inlineStr"/>
+      <c r="L118" s="8" t="inlineStr"/>
+      <c r="M118" s="8" t="inlineStr"/>
+      <c r="N118" s="8" t="inlineStr"/>
+      <c r="O118" s="8" t="inlineStr"/>
+      <c r="P118" s="8" t="inlineStr"/>
+      <c r="Q118" s="8" t="inlineStr"/>
+      <c r="R118" s="8" t="inlineStr"/>
+      <c r="S118" s="8" t="inlineStr"/>
+      <c r="T118" s="8" t="inlineStr"/>
+      <c r="U118" s="8" t="inlineStr"/>
+      <c r="V118" s="8" t="inlineStr">
+        <is>
+          <t>411.00</t>
+        </is>
+      </c>
+      <c r="W118" s="8" t="inlineStr"/>
+      <c r="X118" s="9" t="inlineStr"/>
+      <c r="Y118" s="10" t="inlineStr"/>
+      <c r="Z118" s="11" t="inlineStr"/>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>9044.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr"/>
       <c r="D119" s="8" t="inlineStr"/>
       <c r="E119" s="8" t="inlineStr"/>
       <c r="F119" s="8" t="inlineStr"/>
       <c r="G119" s="8" t="inlineStr"/>
       <c r="H119" s="8" t="inlineStr"/>
-      <c r="I119" s="8" t="inlineStr">
-        <is>
-          <t>5849.00</t>
-        </is>
-      </c>
+      <c r="I119" s="8" t="inlineStr"/>
       <c r="J119" s="8" t="inlineStr"/>
       <c r="K119" s="8" t="inlineStr"/>
       <c r="L119" s="8" t="inlineStr"/>
       <c r="M119" s="8" t="inlineStr"/>
       <c r="N119" s="8" t="inlineStr"/>
-      <c r="O119" s="8" t="inlineStr">
-        <is>
-          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
-        </is>
-      </c>
-      <c r="P119" s="8" t="inlineStr">
-        <is>
-          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
-        </is>
-      </c>
-      <c r="Q119" s="8" t="inlineStr">
-        <is>
-          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
-        </is>
-      </c>
+      <c r="O119" s="8" t="inlineStr"/>
+      <c r="P119" s="8" t="inlineStr"/>
+      <c r="Q119" s="8" t="inlineStr"/>
       <c r="R119" s="8" t="inlineStr"/>
       <c r="S119" s="8" t="inlineStr"/>
       <c r="T119" s="8" t="inlineStr"/>
       <c r="U119" s="8" t="inlineStr"/>
-      <c r="V119" s="8" t="inlineStr"/>
-      <c r="W119" s="9" t="n">
-        <v>5022</v>
-      </c>
-      <c r="X119" s="10" t="inlineStr"/>
-      <c r="Y119" s="11" t="inlineStr"/>
+      <c r="V119" s="8" t="inlineStr">
+        <is>
+          <t>415.00</t>
+        </is>
+      </c>
+      <c r="W119" s="8" t="inlineStr"/>
+      <c r="X119" s="9" t="inlineStr"/>
+      <c r="Y119" s="10" t="inlineStr"/>
+      <c r="Z119" s="11" t="inlineStr"/>
     </row>
     <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="1" t="n"/>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr"/>
-      <c r="D120" s="8" t="inlineStr"/>
-      <c r="E120" s="8" t="inlineStr"/>
-      <c r="F120" s="8" t="inlineStr"/>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="8" t="inlineStr"/>
-      <c r="I120" s="8" t="inlineStr"/>
-      <c r="J120" s="8" t="inlineStr"/>
-      <c r="K120" s="8" t="inlineStr"/>
-      <c r="L120" s="8" t="inlineStr"/>
-      <c r="M120" s="8" t="inlineStr"/>
-      <c r="N120" s="8" t="inlineStr"/>
-      <c r="O120" s="8" t="inlineStr">
-        <is>
-          <t>5670.00</t>
-        </is>
-      </c>
-      <c r="P120" s="8" t="inlineStr">
-        <is>
-          <t>7178.00</t>
-        </is>
-      </c>
-      <c r="Q120" s="8" t="inlineStr">
-        <is>
-          <t>3066.00</t>
-        </is>
-      </c>
-      <c r="R120" s="8" t="inlineStr"/>
-      <c r="S120" s="8" t="inlineStr"/>
-      <c r="T120" s="8" t="inlineStr"/>
-      <c r="U120" s="8" t="inlineStr"/>
-      <c r="V120" s="8" t="inlineStr"/>
-      <c r="W120" s="9" t="inlineStr"/>
-      <c r="X120" s="10" t="inlineStr"/>
-      <c r="Y120" s="11" t="inlineStr"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>UpNDown
+Random: 533.4
+Human: 11693.2</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 7985</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr"/>
+      <c r="D120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
+      <c r="G120" s="4" t="inlineStr"/>
+      <c r="H120" s="4" t="inlineStr"/>
+      <c r="I120" s="4" t="inlineStr"/>
+      <c r="J120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr"/>
+      <c r="L120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr"/>
+      <c r="N120" s="4" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr"/>
+      <c r="P120" s="4" t="inlineStr"/>
+      <c r="Q120" s="4" t="inlineStr"/>
+      <c r="R120" s="4" t="inlineStr"/>
+      <c r="S120" s="4" t="inlineStr"/>
+      <c r="T120" s="4" t="inlineStr"/>
+      <c r="U120" s="4" t="inlineStr"/>
+      <c r="V120" s="4" t="inlineStr"/>
+      <c r="W120" s="4" t="inlineStr"/>
+      <c r="X120" s="5" t="inlineStr"/>
+      <c r="Y120" s="6" t="n">
+        <v>-2963</v>
+      </c>
+      <c r="Z120" s="7" t="n">
+        <v>-0.2655065502966003</v>
+      </c>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="1" t="n"/>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>9044.00</t>
+        </is>
+      </c>
       <c r="D121" s="8" t="inlineStr"/>
       <c r="E121" s="8" t="inlineStr"/>
       <c r="F121" s="8" t="inlineStr"/>
       <c r="G121" s="8" t="inlineStr"/>
       <c r="H121" s="8" t="inlineStr"/>
-      <c r="I121" s="8" t="inlineStr"/>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>5849.00</t>
+        </is>
+      </c>
       <c r="J121" s="8" t="inlineStr"/>
       <c r="K121" s="8" t="inlineStr"/>
       <c r="L121" s="8" t="inlineStr"/>
@@ -6419,17 +6565,17 @@
       <c r="N121" s="8" t="inlineStr"/>
       <c r="O121" s="8" t="inlineStr">
         <is>
-          <t>6043.00</t>
+          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
         </is>
       </c>
       <c r="P121" s="8" t="inlineStr">
         <is>
-          <t>6658.00</t>
+          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
         </is>
       </c>
       <c r="Q121" s="8" t="inlineStr">
         <is>
-          <t>2974.50</t>
+          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
         </is>
       </c>
       <c r="R121" s="8" t="inlineStr"/>
@@ -6437,42 +6583,133 @@
       <c r="T121" s="8" t="inlineStr"/>
       <c r="U121" s="8" t="inlineStr"/>
       <c r="V121" s="8" t="inlineStr"/>
-      <c r="W121" s="9" t="n">
+      <c r="W121" s="8" t="inlineStr"/>
+      <c r="X121" s="9" t="n">
+        <v>5022</v>
+      </c>
+      <c r="Y121" s="10" t="inlineStr"/>
+      <c r="Z121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="1" t="n"/>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr"/>
+      <c r="D122" s="8" t="inlineStr"/>
+      <c r="E122" s="8" t="inlineStr"/>
+      <c r="F122" s="8" t="inlineStr"/>
+      <c r="G122" s="8" t="inlineStr"/>
+      <c r="H122" s="8" t="inlineStr"/>
+      <c r="I122" s="8" t="inlineStr"/>
+      <c r="J122" s="8" t="inlineStr"/>
+      <c r="K122" s="8" t="inlineStr"/>
+      <c r="L122" s="8" t="inlineStr"/>
+      <c r="M122" s="8" t="inlineStr"/>
+      <c r="N122" s="8" t="inlineStr"/>
+      <c r="O122" s="8" t="inlineStr">
+        <is>
+          <t>5670.00</t>
+        </is>
+      </c>
+      <c r="P122" s="8" t="inlineStr">
+        <is>
+          <t>7178.00</t>
+        </is>
+      </c>
+      <c r="Q122" s="8" t="inlineStr">
+        <is>
+          <t>3066.00</t>
+        </is>
+      </c>
+      <c r="R122" s="8" t="inlineStr"/>
+      <c r="S122" s="8" t="inlineStr"/>
+      <c r="T122" s="8" t="inlineStr"/>
+      <c r="U122" s="8" t="inlineStr"/>
+      <c r="V122" s="8" t="inlineStr"/>
+      <c r="W122" s="8" t="inlineStr"/>
+      <c r="X122" s="9" t="inlineStr"/>
+      <c r="Y122" s="10" t="inlineStr"/>
+      <c r="Z122" s="11" t="inlineStr"/>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="1" t="n"/>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr"/>
+      <c r="D123" s="8" t="inlineStr"/>
+      <c r="E123" s="8" t="inlineStr"/>
+      <c r="F123" s="8" t="inlineStr"/>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="8" t="inlineStr"/>
+      <c r="I123" s="8" t="inlineStr"/>
+      <c r="J123" s="8" t="inlineStr"/>
+      <c r="K123" s="8" t="inlineStr"/>
+      <c r="L123" s="8" t="inlineStr"/>
+      <c r="M123" s="8" t="inlineStr"/>
+      <c r="N123" s="8" t="inlineStr"/>
+      <c r="O123" s="8" t="inlineStr">
+        <is>
+          <t>6043.00</t>
+        </is>
+      </c>
+      <c r="P123" s="8" t="inlineStr">
+        <is>
+          <t>6658.00</t>
+        </is>
+      </c>
+      <c r="Q123" s="8" t="inlineStr">
+        <is>
+          <t>2974.50</t>
+        </is>
+      </c>
+      <c r="R123" s="8" t="inlineStr"/>
+      <c r="S123" s="8" t="inlineStr"/>
+      <c r="T123" s="8" t="inlineStr"/>
+      <c r="U123" s="8" t="inlineStr"/>
+      <c r="V123" s="8" t="inlineStr"/>
+      <c r="W123" s="8" t="inlineStr"/>
+      <c r="X123" s="9" t="n">
         <v>5225.166666666667</v>
       </c>
-      <c r="X121" s="9" t="n">
+      <c r="Y123" s="9" t="n">
         <v>203.166666666667</v>
       </c>
-      <c r="Y121" s="11" t="n">
+      <c r="Z123" s="11" t="n">
         <v>0.01820522470534122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A101:A103"/>
     <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A92:A97"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="A114:A119"/>
+    <mergeCell ref="A100:A102"/>
+    <mergeCell ref="A91:A93"/>
+    <mergeCell ref="A87:A90"/>
     <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="A94:A99"/>
+    <mergeCell ref="A63:A67"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A108:A111"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A85:A88"/>
+    <mergeCell ref="A120:A123"/>
     <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A104:A107"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A69:A73"/>
-    <mergeCell ref="A81:A84"/>
+    <mergeCell ref="A103:A105"/>
     <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A112:A117"/>
     <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="A83:A86"/>
     <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A63:A68"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A74:A78"/>
+    <mergeCell ref="A68:A73"/>
     <mergeCell ref="A44:A49"/>
     <mergeCell ref="A40:A43"/>
   </mergeCells>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -500,20 +500,6 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K88" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="L88" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
     <comment ref="K89" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
@@ -542,21 +528,23 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P90" authorId="0" shapeId="0">
+    <comment ref="K91" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L91" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P91" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="L102" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="O104" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="O105" authorId="0" shapeId="0">
@@ -566,9 +554,9 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I107" authorId="0" shapeId="0">
+    <comment ref="O106" authorId="0" shapeId="0">
       <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -581,6 +569,13 @@
       </text>
     </comment>
     <comment ref="I109" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I110" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -880,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z123"/>
+  <dimension ref="A1:Z124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
@@ -3745,7 +3740,11 @@
           <t>32.75</t>
         </is>
       </c>
-      <c r="Q61" s="8" t="inlineStr"/>
+      <c r="Q61" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr"/>
       <c r="T61" s="8" t="inlineStr"/>
@@ -4575,105 +4574,95 @@
       <c r="Z78" s="11" t="inlineStr"/>
     </row>
     <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="1" t="n"/>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr"/>
+      <c r="E79" s="8" t="inlineStr"/>
+      <c r="F79" s="8" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr"/>
+      <c r="J79" s="8" t="inlineStr"/>
+      <c r="K79" s="8" t="inlineStr"/>
+      <c r="L79" s="8" t="inlineStr"/>
+      <c r="M79" s="8" t="inlineStr"/>
+      <c r="N79" s="8" t="inlineStr"/>
+      <c r="O79" s="8" t="inlineStr"/>
+      <c r="P79" s="8" t="inlineStr"/>
+      <c r="Q79" s="8" t="inlineStr"/>
+      <c r="R79" s="8" t="inlineStr"/>
+      <c r="S79" s="8" t="inlineStr"/>
+      <c r="T79" s="8" t="inlineStr"/>
+      <c r="U79" s="8" t="inlineStr"/>
+      <c r="V79" s="8" t="inlineStr"/>
+      <c r="W79" s="8" t="inlineStr"/>
+      <c r="X79" s="9" t="inlineStr"/>
+      <c r="Y79" s="10" t="inlineStr"/>
+      <c r="Z79" s="11" t="inlineStr"/>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Jamesbond
 Random: 29.0
 Human: 302.8</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 509</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr"/>
-      <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="4" t="inlineStr"/>
-      <c r="K79" s="4" t="inlineStr"/>
-      <c r="L79" s="4" t="inlineStr"/>
-      <c r="M79" s="4" t="inlineStr"/>
-      <c r="N79" s="4" t="inlineStr"/>
-      <c r="O79" s="4" t="inlineStr"/>
-      <c r="P79" s="4" t="inlineStr"/>
-      <c r="Q79" s="4" t="inlineStr"/>
-      <c r="R79" s="4" t="inlineStr"/>
-      <c r="S79" s="4" t="inlineStr"/>
-      <c r="T79" s="4" t="inlineStr"/>
-      <c r="U79" s="4" t="inlineStr"/>
-      <c r="V79" s="4" t="inlineStr"/>
-      <c r="W79" s="4" t="inlineStr"/>
-      <c r="X79" s="5" t="inlineStr"/>
-      <c r="Y79" s="6" t="n">
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr"/>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr"/>
+      <c r="P80" s="4" t="inlineStr"/>
+      <c r="Q80" s="4" t="inlineStr"/>
+      <c r="R80" s="4" t="inlineStr"/>
+      <c r="S80" s="4" t="inlineStr"/>
+      <c r="T80" s="4" t="inlineStr"/>
+      <c r="U80" s="4" t="inlineStr"/>
+      <c r="V80" s="4" t="inlineStr"/>
+      <c r="W80" s="4" t="inlineStr"/>
+      <c r="X80" s="5" t="inlineStr"/>
+      <c r="Y80" s="6" t="n">
         <v>-35.66666666666669</v>
       </c>
-      <c r="Z79" s="7" t="n">
+      <c r="Z80" s="7" t="n">
         <v>-0.1302654005356709</v>
       </c>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="1" t="n"/>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>490.00</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr"/>
-      <c r="F80" s="8" t="inlineStr"/>
-      <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" s="8" t="inlineStr"/>
-      <c r="J80" s="8" t="inlineStr"/>
-      <c r="K80" s="8" t="inlineStr">
-        <is>
-          <t>532.50, 537.50</t>
-        </is>
-      </c>
-      <c r="L80" s="8" t="inlineStr"/>
-      <c r="M80" s="8" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
-      <c r="O80" s="8" t="inlineStr">
-        <is>
-          <t>522.50</t>
-        </is>
-      </c>
-      <c r="P80" s="8" t="inlineStr"/>
-      <c r="Q80" s="8" t="inlineStr"/>
-      <c r="R80" s="8" t="inlineStr"/>
-      <c r="S80" s="8" t="inlineStr"/>
-      <c r="T80" s="8" t="inlineStr"/>
-      <c r="U80" s="8" t="inlineStr"/>
-      <c r="V80" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
-        </is>
-      </c>
-      <c r="W80" s="8" t="inlineStr"/>
-      <c r="X80" s="9" t="n">
-        <v>473.3333333333333</v>
-      </c>
-      <c r="Y80" s="10" t="inlineStr"/>
-      <c r="Z80" s="11" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>490.00</t>
+        </is>
+      </c>
       <c r="D81" s="8" t="inlineStr"/>
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr"/>
@@ -4681,13 +4670,17 @@
       <c r="H81" s="8" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr"/>
       <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr">
+        <is>
+          <t>532.50, 537.50</t>
+        </is>
+      </c>
       <c r="L81" s="8" t="inlineStr"/>
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="8" t="inlineStr"/>
       <c r="O81" s="8" t="inlineStr">
         <is>
-          <t>575.00</t>
+          <t>522.50</t>
         </is>
       </c>
       <c r="P81" s="8" t="inlineStr"/>
@@ -4696,9 +4689,15 @@
       <c r="S81" s="8" t="inlineStr"/>
       <c r="T81" s="8" t="inlineStr"/>
       <c r="U81" s="8" t="inlineStr"/>
-      <c r="V81" s="8" t="inlineStr"/>
+      <c r="V81" s="8" t="inlineStr">
+        <is>
+          <t>365.00</t>
+        </is>
+      </c>
       <c r="W81" s="8" t="inlineStr"/>
-      <c r="X81" s="9" t="inlineStr"/>
+      <c r="X81" s="9" t="n">
+        <v>473.3333333333333</v>
+      </c>
       <c r="Y81" s="10" t="inlineStr"/>
       <c r="Z81" s="11" t="inlineStr"/>
     </row>
@@ -4706,7 +4705,7 @@
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr"/>
@@ -4717,17 +4716,13 @@
       <c r="H82" s="8" t="inlineStr"/>
       <c r="I82" s="8" t="inlineStr"/>
       <c r="J82" s="8" t="inlineStr"/>
-      <c r="K82" s="8" t="inlineStr">
-        <is>
-          <t>567.50, 660.00</t>
-        </is>
-      </c>
+      <c r="K82" s="8" t="inlineStr"/>
       <c r="L82" s="8" t="inlineStr"/>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
       <c r="O82" s="8" t="inlineStr">
         <is>
-          <t>665.00</t>
+          <t>575.00</t>
         </is>
       </c>
       <c r="P82" s="8" t="inlineStr"/>
@@ -4736,128 +4731,118 @@
       <c r="S82" s="8" t="inlineStr"/>
       <c r="T82" s="8" t="inlineStr"/>
       <c r="U82" s="8" t="inlineStr"/>
-      <c r="V82" s="8" t="inlineStr">
+      <c r="V82" s="8" t="inlineStr"/>
+      <c r="W82" s="8" t="inlineStr"/>
+      <c r="X82" s="9" t="inlineStr"/>
+      <c r="Y82" s="10" t="inlineStr"/>
+      <c r="Z82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="1" t="n"/>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr"/>
+      <c r="D83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr"/>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr"/>
+      <c r="J83" s="8" t="inlineStr"/>
+      <c r="K83" s="8" t="inlineStr">
+        <is>
+          <t>567.50, 660.00</t>
+        </is>
+      </c>
+      <c r="L83" s="8" t="inlineStr"/>
+      <c r="M83" s="8" t="inlineStr"/>
+      <c r="N83" s="8" t="inlineStr"/>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>665.00</t>
+        </is>
+      </c>
+      <c r="P83" s="8" t="inlineStr"/>
+      <c r="Q83" s="8" t="inlineStr"/>
+      <c r="R83" s="8" t="inlineStr"/>
+      <c r="S83" s="8" t="inlineStr"/>
+      <c r="T83" s="8" t="inlineStr"/>
+      <c r="U83" s="8" t="inlineStr"/>
+      <c r="V83" s="8" t="inlineStr">
         <is>
           <t>375.00</t>
         </is>
       </c>
-      <c r="W82" s="8" t="inlineStr"/>
-      <c r="X82" s="9" t="n">
+      <c r="W83" s="8" t="inlineStr"/>
+      <c r="X83" s="9" t="n">
         <v>535.8333333333334</v>
       </c>
-      <c r="Y82" s="9" t="n">
+      <c r="Y83" s="9" t="n">
         <v>62.50000000000006</v>
       </c>
-      <c r="Z82" s="11" t="n">
+      <c r="Z83" s="11" t="n">
         <v>0.2282688093498906</v>
       </c>
     </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Kangaroo
 Random: 52.0
 Human: 3035.0</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 4208</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr"/>
-      <c r="D83" s="4" t="inlineStr"/>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr"/>
-      <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
-      <c r="K83" s="4" t="inlineStr"/>
-      <c r="L83" s="4" t="inlineStr"/>
-      <c r="M83" s="4" t="inlineStr"/>
-      <c r="N83" s="4" t="inlineStr"/>
-      <c r="O83" s="4" t="inlineStr"/>
-      <c r="P83" s="4" t="inlineStr"/>
-      <c r="Q83" s="4" t="inlineStr"/>
-      <c r="R83" s="4" t="inlineStr"/>
-      <c r="S83" s="4" t="inlineStr"/>
-      <c r="T83" s="4" t="inlineStr"/>
-      <c r="U83" s="4" t="inlineStr"/>
-      <c r="V83" s="4" t="inlineStr"/>
-      <c r="W83" s="4" t="inlineStr"/>
-      <c r="X83" s="5" t="inlineStr"/>
-      <c r="Y83" s="6" t="n">
+      <c r="C84" s="4" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr"/>
+      <c r="N84" s="4" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr"/>
+      <c r="P84" s="4" t="inlineStr"/>
+      <c r="Q84" s="4" t="inlineStr"/>
+      <c r="R84" s="4" t="inlineStr"/>
+      <c r="S84" s="4" t="inlineStr"/>
+      <c r="T84" s="4" t="inlineStr"/>
+      <c r="U84" s="4" t="inlineStr"/>
+      <c r="V84" s="4" t="inlineStr"/>
+      <c r="W84" s="4" t="inlineStr"/>
+      <c r="X84" s="5" t="inlineStr"/>
+      <c r="Y84" s="6" t="n">
         <v>-2778</v>
       </c>
-      <c r="Z83" s="7" t="n">
+      <c r="Z84" s="7" t="n">
         <v>-0.9312772376801878</v>
       </c>
-    </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="1" t="n"/>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr"/>
-      <c r="D84" s="8" t="inlineStr"/>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>1770.00</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" s="8" t="inlineStr"/>
-      <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr">
-        <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="L84" s="8" t="inlineStr">
-        <is>
-          <t>1730.00</t>
-        </is>
-      </c>
-      <c r="M84" s="8" t="inlineStr"/>
-      <c r="N84" s="8" t="inlineStr"/>
-      <c r="O84" s="8" t="inlineStr">
-        <is>
-          <t>1550.00</t>
-        </is>
-      </c>
-      <c r="P84" s="8" t="inlineStr">
-        <is>
-          <t>930.00</t>
-        </is>
-      </c>
-      <c r="Q84" s="8" t="inlineStr"/>
-      <c r="R84" s="8" t="inlineStr"/>
-      <c r="S84" s="8" t="inlineStr"/>
-      <c r="T84" s="8" t="inlineStr"/>
-      <c r="U84" s="8" t="inlineStr"/>
-      <c r="V84" s="8" t="inlineStr"/>
-      <c r="W84" s="8" t="inlineStr"/>
-      <c r="X84" s="9" t="n">
-        <v>1430</v>
-      </c>
-      <c r="Y84" s="10" t="inlineStr"/>
-      <c r="Z84" s="11" t="inlineStr"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr"/>
       <c r="D85" s="8" t="inlineStr"/>
-      <c r="E85" s="8" t="inlineStr"/>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>1770.00</t>
+        </is>
+      </c>
       <c r="F85" s="8" t="inlineStr"/>
       <c r="G85" s="8" t="inlineStr"/>
       <c r="H85" s="8" t="inlineStr"/>
@@ -4865,20 +4850,24 @@
       <c r="J85" s="8" t="inlineStr"/>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>1310.00</t>
-        </is>
-      </c>
-      <c r="L85" s="8" t="inlineStr"/>
+          <t>1470.00</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>1730.00</t>
+        </is>
+      </c>
       <c r="M85" s="8" t="inlineStr"/>
       <c r="N85" s="8" t="inlineStr"/>
       <c r="O85" s="8" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="P85" s="8" t="inlineStr">
         <is>
-          <t>1030.00</t>
+          <t>930.00</t>
         </is>
       </c>
       <c r="Q85" s="8" t="inlineStr"/>
@@ -4888,7 +4877,9 @@
       <c r="U85" s="8" t="inlineStr"/>
       <c r="V85" s="8" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr"/>
-      <c r="X85" s="9" t="inlineStr"/>
+      <c r="X85" s="9" t="n">
+        <v>1430</v>
+      </c>
       <c r="Y85" s="10" t="inlineStr"/>
       <c r="Z85" s="11" t="inlineStr"/>
     </row>
@@ -4896,16 +4887,12 @@
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr"/>
       <c r="D86" s="8" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>1760.00</t>
-        </is>
-      </c>
+      <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="8" t="inlineStr"/>
       <c r="G86" s="8" t="inlineStr"/>
       <c r="H86" s="8" t="inlineStr"/>
@@ -4913,7 +4900,7 @@
       <c r="J86" s="8" t="inlineStr"/>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="L86" s="8" t="inlineStr"/>
@@ -4921,12 +4908,12 @@
       <c r="N86" s="8" t="inlineStr"/>
       <c r="O86" s="8" t="inlineStr">
         <is>
-          <t>1670.00</t>
+          <t>1500.00</t>
         </is>
       </c>
       <c r="P86" s="8" t="inlineStr">
         <is>
-          <t>760.00</t>
+          <t>1030.00</t>
         </is>
       </c>
       <c r="Q86" s="8" t="inlineStr"/>
@@ -4936,165 +4923,169 @@
       <c r="U86" s="8" t="inlineStr"/>
       <c r="V86" s="8" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr"/>
-      <c r="X86" s="9" t="n">
+      <c r="X86" s="9" t="inlineStr"/>
+      <c r="Y86" s="10" t="inlineStr"/>
+      <c r="Z86" s="11" t="inlineStr"/>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="1" t="n"/>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr"/>
+      <c r="D87" s="8" t="inlineStr"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr"/>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr"/>
+      <c r="J87" s="8" t="inlineStr"/>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>1590.00</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr"/>
+      <c r="M87" s="8" t="inlineStr"/>
+      <c r="N87" s="8" t="inlineStr"/>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>1670.00</t>
+        </is>
+      </c>
+      <c r="P87" s="8" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
+      <c r="Q87" s="8" t="inlineStr"/>
+      <c r="R87" s="8" t="inlineStr"/>
+      <c r="S87" s="8" t="inlineStr"/>
+      <c r="T87" s="8" t="inlineStr"/>
+      <c r="U87" s="8" t="inlineStr"/>
+      <c r="V87" s="8" t="inlineStr"/>
+      <c r="W87" s="8" t="inlineStr"/>
+      <c r="X87" s="9" t="n">
         <v>1445</v>
       </c>
-      <c r="Y86" s="9" t="n">
+      <c r="Y87" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="Z86" s="11" t="n">
+      <c r="Z87" s="11" t="n">
         <v>0.005028494803888703</v>
       </c>
     </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Krull
 Random: 1598.0
 Human: 2665.5</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 8413</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr"/>
-      <c r="D87" s="4" t="inlineStr"/>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr"/>
-      <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
-      <c r="K87" s="4" t="inlineStr"/>
-      <c r="L87" s="4" t="inlineStr"/>
-      <c r="M87" s="4" t="inlineStr"/>
-      <c r="N87" s="4" t="inlineStr"/>
-      <c r="O87" s="4" t="inlineStr"/>
-      <c r="P87" s="4" t="inlineStr"/>
-      <c r="Q87" s="4" t="inlineStr"/>
-      <c r="R87" s="4" t="inlineStr"/>
-      <c r="S87" s="4" t="inlineStr"/>
-      <c r="T87" s="4" t="inlineStr"/>
-      <c r="U87" s="4" t="inlineStr"/>
-      <c r="V87" s="4" t="inlineStr"/>
-      <c r="W87" s="4" t="inlineStr"/>
-      <c r="X87" s="5" t="inlineStr"/>
-      <c r="Y87" s="6" t="n">
+      <c r="C88" s="4" t="inlineStr"/>
+      <c r="D88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr"/>
+      <c r="L88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr"/>
+      <c r="N88" s="4" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr"/>
+      <c r="P88" s="4" t="inlineStr"/>
+      <c r="Q88" s="4" t="inlineStr"/>
+      <c r="R88" s="4" t="inlineStr"/>
+      <c r="S88" s="4" t="inlineStr"/>
+      <c r="T88" s="4" t="inlineStr"/>
+      <c r="U88" s="4" t="inlineStr"/>
+      <c r="V88" s="4" t="inlineStr"/>
+      <c r="W88" s="4" t="inlineStr"/>
+      <c r="X88" s="5" t="inlineStr"/>
+      <c r="Y88" s="6" t="n">
         <v>-2583.375</v>
       </c>
-      <c r="Z87" s="7" t="n">
+      <c r="Z88" s="7" t="n">
         <v>-2.420023419203747</v>
       </c>
-    </row>
-    <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="1" t="n"/>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr"/>
-      <c r="D88" s="8" t="inlineStr"/>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>6202.00</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>5689.00</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr"/>
-      <c r="H88" s="8" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>6107.50</t>
-        </is>
-      </c>
-      <c r="J88" s="8" t="inlineStr"/>
-      <c r="K88" s="13" t="inlineStr">
-        <is>
-          <t>4708.50</t>
-        </is>
-      </c>
-      <c r="L88" s="13" t="inlineStr">
-        <is>
-          <t>5913.50</t>
-        </is>
-      </c>
-      <c r="M88" s="8" t="inlineStr"/>
-      <c r="N88" s="8" t="inlineStr"/>
-      <c r="O88" s="8" t="inlineStr">
-        <is>
-          <t>5228.50</t>
-        </is>
-      </c>
-      <c r="P88" s="8" t="inlineStr"/>
-      <c r="Q88" s="8" t="inlineStr">
-        <is>
-          <t>5599.00</t>
-        </is>
-      </c>
-      <c r="R88" s="8" t="inlineStr"/>
-      <c r="S88" s="8" t="inlineStr"/>
-      <c r="T88" s="8" t="inlineStr"/>
-      <c r="U88" s="8" t="inlineStr"/>
-      <c r="V88" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
-      <c r="W88" s="8" t="inlineStr"/>
-      <c r="X88" s="9" t="n">
-        <v>5829.625</v>
-      </c>
-      <c r="Y88" s="10" t="inlineStr"/>
-      <c r="Z88" s="11" t="inlineStr"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr"/>
       <c r="D89" s="8" t="inlineStr"/>
-      <c r="E89" s="8" t="inlineStr"/>
-      <c r="F89" s="8" t="inlineStr"/>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>6202.00</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>5689.00</t>
+        </is>
+      </c>
       <c r="G89" s="8" t="inlineStr"/>
       <c r="H89" s="8" t="inlineStr"/>
-      <c r="I89" s="8" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>6107.50</t>
+        </is>
+      </c>
       <c r="J89" s="8" t="inlineStr"/>
       <c r="K89" s="13" t="inlineStr">
         <is>
-          <t>4851.00</t>
+          <t>4708.50</t>
         </is>
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
-          <t>6044.00</t>
+          <t>5913.50</t>
         </is>
       </c>
       <c r="M89" s="8" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr"/>
-      <c r="O89" s="8" t="inlineStr"/>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>5228.50</t>
+        </is>
+      </c>
       <c r="P89" s="8" t="inlineStr"/>
-      <c r="Q89" s="8" t="inlineStr"/>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>5599.00</t>
+        </is>
+      </c>
       <c r="R89" s="8" t="inlineStr"/>
       <c r="S89" s="8" t="inlineStr"/>
       <c r="T89" s="8" t="inlineStr"/>
       <c r="U89" s="8" t="inlineStr"/>
       <c r="V89" s="8" t="inlineStr">
         <is>
-          <t>6587.00</t>
+          <t>6289.00</t>
         </is>
       </c>
       <c r="W89" s="8" t="inlineStr"/>
-      <c r="X89" s="9" t="inlineStr"/>
+      <c r="X89" s="9" t="n">
+        <v>5829.625</v>
+      </c>
       <c r="Y89" s="10" t="inlineStr"/>
       <c r="Z89" s="11" t="inlineStr"/>
     </row>
@@ -5102,16 +5093,12 @@
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr"/>
       <c r="D90" s="8" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>6576.50</t>
-        </is>
-      </c>
+      <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" s="8" t="inlineStr"/>
       <c r="G90" s="8" t="inlineStr"/>
       <c r="H90" s="8" t="inlineStr"/>
@@ -5119,151 +5106,153 @@
       <c r="J90" s="8" t="inlineStr"/>
       <c r="K90" s="13" t="inlineStr">
         <is>
-          <t>5279.50</t>
+          <t>4851.00</t>
         </is>
       </c>
       <c r="L90" s="13" t="inlineStr">
         <is>
-          <t>5889.50</t>
+          <t>6044.00</t>
         </is>
       </c>
       <c r="M90" s="8" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr"/>
-      <c r="O90" s="8" t="inlineStr">
-        <is>
-          <t>6447.50</t>
-        </is>
-      </c>
-      <c r="P90" s="15" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="Q90" s="8" t="inlineStr">
-        <is>
-          <t>6828.50</t>
-        </is>
-      </c>
+      <c r="O90" s="8" t="inlineStr"/>
+      <c r="P90" s="8" t="inlineStr"/>
+      <c r="Q90" s="8" t="inlineStr"/>
       <c r="R90" s="8" t="inlineStr"/>
       <c r="S90" s="8" t="inlineStr"/>
       <c r="T90" s="8" t="inlineStr"/>
       <c r="U90" s="8" t="inlineStr"/>
       <c r="V90" s="8" t="inlineStr">
         <is>
+          <t>6587.00</t>
+        </is>
+      </c>
+      <c r="W90" s="8" t="inlineStr"/>
+      <c r="X90" s="9" t="inlineStr"/>
+      <c r="Y90" s="10" t="inlineStr"/>
+      <c r="Z90" s="11" t="inlineStr"/>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="1" t="n"/>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr"/>
+      <c r="D91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>6576.50</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr"/>
+      <c r="J91" s="8" t="inlineStr"/>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>5279.50</t>
+        </is>
+      </c>
+      <c r="L91" s="13" t="inlineStr">
+        <is>
+          <t>5889.50</t>
+        </is>
+      </c>
+      <c r="M91" s="8" t="inlineStr"/>
+      <c r="N91" s="8" t="inlineStr"/>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>6447.50</t>
+        </is>
+      </c>
+      <c r="P91" s="15" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>6828.50</t>
+        </is>
+      </c>
+      <c r="R91" s="8" t="inlineStr"/>
+      <c r="S91" s="8" t="inlineStr"/>
+      <c r="T91" s="8" t="inlineStr"/>
+      <c r="U91" s="8" t="inlineStr"/>
+      <c r="V91" s="8" t="inlineStr">
+        <is>
           <t>6796.50</t>
         </is>
       </c>
-      <c r="W90" s="8" t="inlineStr"/>
-      <c r="X90" s="9" t="n">
+      <c r="W91" s="8" t="inlineStr"/>
+      <c r="X91" s="9" t="n">
         <v>6662.25</v>
       </c>
-      <c r="Y90" s="9" t="n">
+      <c r="Y91" s="9" t="n">
         <v>832.625</v>
       </c>
-      <c r="Z90" s="11" t="n">
+      <c r="Z91" s="11" t="n">
         <v>0.779976580796253</v>
       </c>
     </row>
-    <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>KungFuMaster
 Random: 258.5
 Human: 22736.3</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 26182</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="4" t="inlineStr"/>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr"/>
-      <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="4" t="inlineStr"/>
-      <c r="J91" s="4" t="inlineStr"/>
-      <c r="K91" s="4" t="inlineStr"/>
-      <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="4" t="inlineStr"/>
-      <c r="N91" s="4" t="inlineStr"/>
-      <c r="O91" s="4" t="inlineStr"/>
-      <c r="P91" s="4" t="inlineStr"/>
-      <c r="Q91" s="4" t="inlineStr"/>
-      <c r="R91" s="4" t="inlineStr"/>
-      <c r="S91" s="4" t="inlineStr"/>
-      <c r="T91" s="4" t="inlineStr"/>
-      <c r="U91" s="4" t="inlineStr"/>
-      <c r="V91" s="4" t="inlineStr"/>
-      <c r="W91" s="4" t="inlineStr"/>
-      <c r="X91" s="5" t="inlineStr"/>
-      <c r="Y91" s="6" t="n">
+      <c r="C92" s="4" t="inlineStr"/>
+      <c r="D92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr"/>
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="inlineStr"/>
+      <c r="N92" s="4" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr"/>
+      <c r="P92" s="4" t="inlineStr"/>
+      <c r="Q92" s="4" t="inlineStr"/>
+      <c r="R92" s="4" t="inlineStr"/>
+      <c r="S92" s="4" t="inlineStr"/>
+      <c r="T92" s="4" t="inlineStr"/>
+      <c r="U92" s="4" t="inlineStr"/>
+      <c r="V92" s="4" t="inlineStr"/>
+      <c r="W92" s="4" t="inlineStr"/>
+      <c r="X92" s="5" t="inlineStr"/>
+      <c r="Y92" s="6" t="n">
         <v>-1044.5</v>
       </c>
-      <c r="Z91" s="7" t="n">
+      <c r="Z92" s="7" t="n">
         <v>-0.04646807071866464</v>
       </c>
-    </row>
-    <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="1" t="n"/>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr"/>
-      <c r="D92" s="8" t="inlineStr"/>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>26460.00</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="inlineStr"/>
-      <c r="G92" s="8" t="inlineStr"/>
-      <c r="H92" s="8" t="inlineStr"/>
-      <c r="I92" s="8" t="inlineStr"/>
-      <c r="J92" s="8" t="inlineStr"/>
-      <c r="K92" s="8" t="inlineStr">
-        <is>
-          <t>23815.00</t>
-        </is>
-      </c>
-      <c r="L92" s="8" t="inlineStr">
-        <is>
-          <t>20895.00</t>
-        </is>
-      </c>
-      <c r="M92" s="8" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr"/>
-      <c r="O92" s="8" t="inlineStr"/>
-      <c r="P92" s="8" t="inlineStr"/>
-      <c r="Q92" s="8" t="inlineStr"/>
-      <c r="R92" s="8" t="inlineStr"/>
-      <c r="S92" s="8" t="inlineStr"/>
-      <c r="T92" s="8" t="inlineStr"/>
-      <c r="U92" s="8" t="inlineStr"/>
-      <c r="V92" s="8" t="inlineStr"/>
-      <c r="W92" s="8" t="inlineStr"/>
-      <c r="X92" s="9" t="n">
-        <v>25137.5</v>
-      </c>
-      <c r="Y92" s="10" t="inlineStr"/>
-      <c r="Z92" s="11" t="inlineStr"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr"/>
       <c r="D93" s="8" t="inlineStr"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>30110.00</t>
+          <t>26460.00</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr"/>
@@ -5273,10 +5262,14 @@
       <c r="J93" s="8" t="inlineStr"/>
       <c r="K93" s="8" t="inlineStr">
         <is>
-          <t>20245.00</t>
-        </is>
-      </c>
-      <c r="L93" s="8" t="inlineStr"/>
+          <t>23815.00</t>
+        </is>
+      </c>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>20895.00</t>
+        </is>
+      </c>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
       <c r="O93" s="8" t="inlineStr"/>
@@ -5289,129 +5282,133 @@
       <c r="V93" s="8" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr"/>
       <c r="X93" s="9" t="n">
+        <v>25137.5</v>
+      </c>
+      <c r="Y93" s="10" t="inlineStr"/>
+      <c r="Z93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="1" t="n"/>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr"/>
+      <c r="D94" s="8" t="inlineStr"/>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>30110.00</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr"/>
+      <c r="G94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr"/>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>20245.00</t>
+        </is>
+      </c>
+      <c r="L94" s="8" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr"/>
+      <c r="N94" s="8" t="inlineStr"/>
+      <c r="O94" s="8" t="inlineStr"/>
+      <c r="P94" s="8" t="inlineStr"/>
+      <c r="Q94" s="8" t="inlineStr"/>
+      <c r="R94" s="8" t="inlineStr"/>
+      <c r="S94" s="8" t="inlineStr"/>
+      <c r="T94" s="8" t="inlineStr"/>
+      <c r="U94" s="8" t="inlineStr"/>
+      <c r="V94" s="8" t="inlineStr"/>
+      <c r="W94" s="8" t="inlineStr"/>
+      <c r="X94" s="9" t="n">
         <v>25177.5</v>
       </c>
-      <c r="Y93" s="9" t="n">
+      <c r="Y94" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="Z93" s="11" t="n">
+      <c r="Z94" s="11" t="n">
         <v>0.001779533584247569</v>
       </c>
     </row>
-    <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95" ht="24" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>MsPacman
 Random: 307.3
 Human: 6951.6</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 2673</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr"/>
-      <c r="D94" s="4" t="inlineStr"/>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr"/>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
-      <c r="K94" s="4" t="inlineStr"/>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr"/>
-      <c r="O94" s="4" t="inlineStr"/>
-      <c r="P94" s="4" t="inlineStr"/>
-      <c r="Q94" s="4" t="inlineStr"/>
-      <c r="R94" s="4" t="inlineStr"/>
-      <c r="S94" s="4" t="inlineStr"/>
-      <c r="T94" s="4" t="inlineStr"/>
-      <c r="U94" s="4" t="inlineStr"/>
-      <c r="V94" s="4" t="inlineStr"/>
-      <c r="W94" s="4" t="inlineStr"/>
-      <c r="X94" s="5" t="inlineStr"/>
-      <c r="Y94" s="6" t="n">
+      <c r="C95" s="4" t="inlineStr"/>
+      <c r="D95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="inlineStr"/>
+      <c r="N95" s="4" t="inlineStr"/>
+      <c r="O95" s="4" t="inlineStr"/>
+      <c r="P95" s="4" t="inlineStr"/>
+      <c r="Q95" s="4" t="inlineStr"/>
+      <c r="R95" s="4" t="inlineStr"/>
+      <c r="S95" s="4" t="inlineStr"/>
+      <c r="T95" s="4" t="inlineStr"/>
+      <c r="U95" s="4" t="inlineStr"/>
+      <c r="V95" s="4" t="inlineStr"/>
+      <c r="W95" s="4" t="inlineStr"/>
+      <c r="X95" s="5" t="inlineStr"/>
+      <c r="Y95" s="6" t="n">
         <v>-602</v>
       </c>
-      <c r="Z94" s="7" t="n">
+      <c r="Z95" s="7" t="n">
         <v>-0.09060397634062278</v>
       </c>
-    </row>
-    <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="1" t="n"/>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>1807.50</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="inlineStr"/>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>2007.00</t>
-        </is>
-      </c>
-      <c r="F95" s="8" t="inlineStr"/>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="inlineStr"/>
-      <c r="I95" s="8" t="inlineStr"/>
-      <c r="J95" s="8" t="inlineStr"/>
-      <c r="K95" s="8" t="inlineStr">
-        <is>
-          <t>2388.00</t>
-        </is>
-      </c>
-      <c r="L95" s="8" t="inlineStr"/>
-      <c r="M95" s="8" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr"/>
-      <c r="O95" s="8" t="inlineStr">
-        <is>
-          <t>1754.00</t>
-        </is>
-      </c>
-      <c r="P95" s="8" t="inlineStr"/>
-      <c r="Q95" s="8" t="inlineStr"/>
-      <c r="R95" s="8" t="inlineStr"/>
-      <c r="S95" s="8" t="inlineStr"/>
-      <c r="T95" s="8" t="inlineStr"/>
-      <c r="U95" s="8" t="inlineStr"/>
-      <c r="V95" s="8" t="inlineStr"/>
-      <c r="W95" s="8" t="inlineStr"/>
-      <c r="X95" s="9" t="n">
-        <v>2071</v>
-      </c>
-      <c r="Y95" s="10" t="inlineStr"/>
-      <c r="Z95" s="11" t="inlineStr"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>1807.50</t>
+        </is>
+      </c>
       <c r="D96" s="8" t="inlineStr"/>
-      <c r="E96" s="8" t="inlineStr"/>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>2007.00</t>
+        </is>
+      </c>
       <c r="F96" s="8" t="inlineStr"/>
       <c r="G96" s="8" t="inlineStr"/>
       <c r="H96" s="8" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr"/>
       <c r="J96" s="8" t="inlineStr"/>
-      <c r="K96" s="8" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>2388.00</t>
+        </is>
+      </c>
       <c r="L96" s="8" t="inlineStr"/>
       <c r="M96" s="8" t="inlineStr"/>
       <c r="N96" s="8" t="inlineStr"/>
       <c r="O96" s="8" t="inlineStr">
         <is>
-          <t>2110.50</t>
+          <t>1754.00</t>
         </is>
       </c>
       <c r="P96" s="8" t="inlineStr"/>
@@ -5422,7 +5419,9 @@
       <c r="U96" s="8" t="inlineStr"/>
       <c r="V96" s="8" t="inlineStr"/>
       <c r="W96" s="8" t="inlineStr"/>
-      <c r="X96" s="9" t="inlineStr"/>
+      <c r="X96" s="9" t="n">
+        <v>2071</v>
+      </c>
       <c r="Y96" s="10" t="inlineStr"/>
       <c r="Z96" s="11" t="inlineStr"/>
     </row>
@@ -5430,7 +5429,7 @@
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
@@ -5441,17 +5440,13 @@
       <c r="H97" s="8" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr"/>
       <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr">
-        <is>
-          <t>2250.00</t>
-        </is>
-      </c>
+      <c r="K97" s="8" t="inlineStr"/>
       <c r="L97" s="8" t="inlineStr"/>
       <c r="M97" s="8" t="inlineStr"/>
       <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="8" t="inlineStr">
         <is>
-          <t>1886.50</t>
+          <t>2110.50</t>
         </is>
       </c>
       <c r="P97" s="8" t="inlineStr"/>
@@ -5462,21 +5457,15 @@
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr"/>
-      <c r="X97" s="9" t="n">
-        <v>2068.25</v>
-      </c>
-      <c r="Y97" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z97" s="11" t="n">
-        <v>-0.0004138885962403865</v>
-      </c>
+      <c r="X97" s="9" t="inlineStr"/>
+      <c r="Y97" s="10" t="inlineStr"/>
+      <c r="Z97" s="11" t="inlineStr"/>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr"/>
@@ -5487,13 +5476,17 @@
       <c r="H98" s="8" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr"/>
       <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="8" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr">
+        <is>
+          <t>2250.00</t>
+        </is>
+      </c>
       <c r="L98" s="8" t="inlineStr"/>
       <c r="M98" s="8" t="inlineStr"/>
       <c r="N98" s="8" t="inlineStr"/>
       <c r="O98" s="8" t="inlineStr">
         <is>
-          <t>2197.00</t>
+          <t>1886.50</t>
         </is>
       </c>
       <c r="P98" s="8" t="inlineStr"/>
@@ -5504,15 +5497,21 @@
       <c r="U98" s="8" t="inlineStr"/>
       <c r="V98" s="8" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr"/>
-      <c r="X98" s="9" t="inlineStr"/>
-      <c r="Y98" s="10" t="inlineStr"/>
-      <c r="Z98" s="11" t="inlineStr"/>
+      <c r="X98" s="9" t="n">
+        <v>2068.25</v>
+      </c>
+      <c r="Y98" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z98" s="11" t="n">
+        <v>-0.0004138885962403865</v>
+      </c>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr"/>
@@ -5529,7 +5528,7 @@
       <c r="N99" s="8" t="inlineStr"/>
       <c r="O99" s="8" t="inlineStr">
         <is>
-          <t>2170.00</t>
+          <t>2197.00</t>
         </is>
       </c>
       <c r="P99" s="8" t="inlineStr"/>
@@ -5545,128 +5544,114 @@
       <c r="Z99" s="11" t="inlineStr"/>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="1" t="n"/>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr"/>
+      <c r="D100" s="8" t="inlineStr"/>
+      <c r="E100" s="8" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr"/>
+      <c r="G100" s="8" t="inlineStr"/>
+      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr"/>
+      <c r="J100" s="8" t="inlineStr"/>
+      <c r="K100" s="8" t="inlineStr"/>
+      <c r="L100" s="8" t="inlineStr"/>
+      <c r="M100" s="8" t="inlineStr"/>
+      <c r="N100" s="8" t="inlineStr"/>
+      <c r="O100" s="8" t="inlineStr">
+        <is>
+          <t>2170.00</t>
+        </is>
+      </c>
+      <c r="P100" s="8" t="inlineStr"/>
+      <c r="Q100" s="8" t="inlineStr"/>
+      <c r="R100" s="8" t="inlineStr"/>
+      <c r="S100" s="8" t="inlineStr"/>
+      <c r="T100" s="8" t="inlineStr"/>
+      <c r="U100" s="8" t="inlineStr"/>
+      <c r="V100" s="8" t="inlineStr"/>
+      <c r="W100" s="8" t="inlineStr"/>
+      <c r="X100" s="9" t="inlineStr"/>
+      <c r="Y100" s="10" t="inlineStr"/>
+      <c r="Z100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101" ht="24" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Pong
 Random: -20.7
 Human: 14.6</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 11</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr"/>
-      <c r="D100" s="4" t="inlineStr"/>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
-      <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="4" t="inlineStr"/>
-      <c r="J100" s="4" t="inlineStr"/>
-      <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="4" t="inlineStr"/>
-      <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr"/>
-      <c r="O100" s="4" t="inlineStr"/>
-      <c r="P100" s="4" t="inlineStr"/>
-      <c r="Q100" s="4" t="inlineStr"/>
-      <c r="R100" s="4" t="inlineStr"/>
-      <c r="S100" s="4" t="inlineStr"/>
-      <c r="T100" s="4" t="inlineStr"/>
-      <c r="U100" s="4" t="inlineStr"/>
-      <c r="V100" s="4" t="inlineStr"/>
-      <c r="W100" s="4" t="inlineStr"/>
-      <c r="X100" s="5" t="inlineStr"/>
-      <c r="Y100" s="6" t="n">
+      <c r="C101" s="4" t="inlineStr"/>
+      <c r="D101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr"/>
+      <c r="J101" s="4" t="inlineStr"/>
+      <c r="K101" s="4" t="inlineStr"/>
+      <c r="L101" s="4" t="inlineStr"/>
+      <c r="M101" s="4" t="inlineStr"/>
+      <c r="N101" s="4" t="inlineStr"/>
+      <c r="O101" s="4" t="inlineStr"/>
+      <c r="P101" s="4" t="inlineStr"/>
+      <c r="Q101" s="4" t="inlineStr"/>
+      <c r="R101" s="4" t="inlineStr"/>
+      <c r="S101" s="4" t="inlineStr"/>
+      <c r="T101" s="4" t="inlineStr"/>
+      <c r="U101" s="4" t="inlineStr"/>
+      <c r="V101" s="4" t="inlineStr"/>
+      <c r="W101" s="4" t="inlineStr"/>
+      <c r="X101" s="5" t="inlineStr"/>
+      <c r="Y101" s="6" t="n">
         <v>-5.4</v>
       </c>
-      <c r="Z100" s="7" t="n">
+      <c r="Z101" s="7" t="n">
         <v>-0.1529745042492918</v>
       </c>
-    </row>
-    <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="1" t="n"/>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr"/>
-      <c r="D101" s="8" t="inlineStr"/>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="8" t="inlineStr"/>
-      <c r="I101" s="8" t="inlineStr"/>
-      <c r="J101" s="8" t="inlineStr"/>
-      <c r="K101" s="8" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
-      <c r="M101" s="8" t="inlineStr"/>
-      <c r="N101" s="8" t="inlineStr"/>
-      <c r="O101" s="8" t="inlineStr"/>
-      <c r="P101" s="8" t="inlineStr"/>
-      <c r="Q101" s="8" t="inlineStr"/>
-      <c r="R101" s="8" t="inlineStr"/>
-      <c r="S101" s="8" t="inlineStr"/>
-      <c r="T101" s="8" t="inlineStr"/>
-      <c r="U101" s="8" t="inlineStr"/>
-      <c r="V101" s="8" t="inlineStr"/>
-      <c r="W101" s="8" t="inlineStr"/>
-      <c r="X101" s="9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y101" s="10" t="inlineStr"/>
-      <c r="Z101" s="11" t="inlineStr"/>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr"/>
       <c r="D102" s="8" t="inlineStr"/>
-      <c r="E102" s="8" t="inlineStr"/>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr"/>
       <c r="H102" s="8" t="inlineStr"/>
-      <c r="I102" s="8" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
+      <c r="I102" s="8" t="inlineStr"/>
       <c r="J102" s="8" t="inlineStr"/>
       <c r="K102" s="8" t="inlineStr">
         <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="L102" s="15" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>13.70</t>
         </is>
       </c>
       <c r="M102" s="8" t="inlineStr"/>
@@ -5681,123 +5666,119 @@
       <c r="V102" s="8" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr"/>
       <c r="X102" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y102" s="10" t="inlineStr"/>
+      <c r="Z102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="1" t="n"/>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr"/>
+      <c r="D103" s="8" t="inlineStr"/>
+      <c r="E103" s="8" t="inlineStr"/>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>8.20</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="inlineStr">
+        <is>
+          <t>9.80</t>
+        </is>
+      </c>
+      <c r="L103" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="M103" s="8" t="inlineStr"/>
+      <c r="N103" s="8" t="inlineStr"/>
+      <c r="O103" s="8" t="inlineStr"/>
+      <c r="P103" s="8" t="inlineStr"/>
+      <c r="Q103" s="8" t="inlineStr"/>
+      <c r="R103" s="8" t="inlineStr"/>
+      <c r="S103" s="8" t="inlineStr"/>
+      <c r="T103" s="8" t="inlineStr"/>
+      <c r="U103" s="8" t="inlineStr"/>
+      <c r="V103" s="8" t="inlineStr"/>
+      <c r="W103" s="8" t="inlineStr"/>
+      <c r="X103" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="Y102" s="9" t="n">
+      <c r="Y103" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="Z102" s="11" t="n">
+      <c r="Z103" s="11" t="n">
         <v>0.09631728045325781</v>
       </c>
     </row>
-    <row r="103" ht="24" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>PrivateEye
 Random: 24.9
 Human: 69571.3</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 7781</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr"/>
-      <c r="D103" s="4" t="inlineStr"/>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr"/>
-      <c r="H103" s="4" t="inlineStr"/>
-      <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="4" t="inlineStr"/>
-      <c r="K103" s="4" t="inlineStr"/>
-      <c r="L103" s="4" t="inlineStr"/>
-      <c r="M103" s="4" t="inlineStr"/>
-      <c r="N103" s="4" t="inlineStr"/>
-      <c r="O103" s="4" t="inlineStr"/>
-      <c r="P103" s="4" t="inlineStr"/>
-      <c r="Q103" s="4" t="inlineStr"/>
-      <c r="R103" s="4" t="inlineStr"/>
-      <c r="S103" s="4" t="inlineStr"/>
-      <c r="T103" s="4" t="inlineStr"/>
-      <c r="U103" s="4" t="inlineStr"/>
-      <c r="V103" s="4" t="inlineStr"/>
-      <c r="W103" s="4" t="inlineStr"/>
-      <c r="X103" s="5" t="inlineStr"/>
-      <c r="Y103" s="6" t="n">
+      <c r="C104" s="4" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr"/>
+      <c r="L104" s="4" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr"/>
+      <c r="P104" s="4" t="inlineStr"/>
+      <c r="Q104" s="4" t="inlineStr"/>
+      <c r="R104" s="4" t="inlineStr"/>
+      <c r="S104" s="4" t="inlineStr"/>
+      <c r="T104" s="4" t="inlineStr"/>
+      <c r="U104" s="4" t="inlineStr"/>
+      <c r="V104" s="4" t="inlineStr"/>
+      <c r="W104" s="4" t="inlineStr"/>
+      <c r="X104" s="5" t="inlineStr"/>
+      <c r="Y104" s="6" t="n">
         <v>-6778.35</v>
       </c>
-      <c r="Z103" s="7" t="n">
+      <c r="Z104" s="7" t="n">
         <v>-0.09746514557187719</v>
       </c>
-    </row>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="1" t="n"/>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C104" s="8" t="inlineStr">
-        <is>
-          <t>75.30</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr"/>
-      <c r="E104" s="8" t="inlineStr"/>
-      <c r="F104" s="8" t="inlineStr"/>
-      <c r="G104" s="8" t="inlineStr"/>
-      <c r="H104" s="8" t="inlineStr"/>
-      <c r="I104" s="8" t="inlineStr"/>
-      <c r="J104" s="8" t="inlineStr"/>
-      <c r="K104" s="8" t="inlineStr">
-        <is>
-          <t>199.35</t>
-        </is>
-      </c>
-      <c r="L104" s="8" t="inlineStr"/>
-      <c r="M104" s="8" t="inlineStr"/>
-      <c r="N104" s="8" t="inlineStr"/>
-      <c r="O104" s="13" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="P104" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q104" s="8" t="inlineStr">
-        <is>
-          <t>3551.75</t>
-        </is>
-      </c>
-      <c r="R104" s="8" t="inlineStr"/>
-      <c r="S104" s="8" t="inlineStr"/>
-      <c r="T104" s="8" t="inlineStr"/>
-      <c r="U104" s="8" t="inlineStr"/>
-      <c r="V104" s="8" t="inlineStr">
-        <is>
-          <t>159.50</t>
-        </is>
-      </c>
-      <c r="W104" s="8" t="inlineStr"/>
-      <c r="X104" s="9" t="n">
-        <v>1002.65</v>
-      </c>
-      <c r="Y104" s="10" t="inlineStr"/>
-      <c r="Z104" s="11" t="inlineStr"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>75.30</t>
+        </is>
+      </c>
       <c r="D105" s="8" t="inlineStr"/>
       <c r="E105" s="8" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr"/>
@@ -5807,7 +5788,7 @@
       <c r="J105" s="8" t="inlineStr"/>
       <c r="K105" s="8" t="inlineStr">
         <is>
-          <t>191.95</t>
+          <t>199.35</t>
         </is>
       </c>
       <c r="L105" s="8" t="inlineStr"/>
@@ -5815,7 +5796,7 @@
       <c r="N105" s="8" t="inlineStr"/>
       <c r="O105" s="13" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P105" s="8" t="inlineStr">
@@ -5825,7 +5806,7 @@
       </c>
       <c r="Q105" s="8" t="inlineStr">
         <is>
-          <t>166.80</t>
+          <t>3551.75</t>
         </is>
       </c>
       <c r="R105" s="8" t="inlineStr"/>
@@ -5834,132 +5815,132 @@
       <c r="U105" s="8" t="inlineStr"/>
       <c r="V105" s="8" t="inlineStr">
         <is>
-          <t>153.20</t>
+          <t>159.50</t>
         </is>
       </c>
       <c r="W105" s="8" t="inlineStr"/>
       <c r="X105" s="9" t="n">
+        <v>1002.65</v>
+      </c>
+      <c r="Y105" s="10" t="inlineStr"/>
+      <c r="Z105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="1" t="n"/>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr"/>
+      <c r="D106" s="8" t="inlineStr"/>
+      <c r="E106" s="8" t="inlineStr"/>
+      <c r="F106" s="8" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr"/>
+      <c r="H106" s="8" t="inlineStr"/>
+      <c r="I106" s="8" t="inlineStr"/>
+      <c r="J106" s="8" t="inlineStr"/>
+      <c r="K106" s="8" t="inlineStr">
+        <is>
+          <t>191.95</t>
+        </is>
+      </c>
+      <c r="L106" s="8" t="inlineStr"/>
+      <c r="M106" s="8" t="inlineStr"/>
+      <c r="N106" s="8" t="inlineStr"/>
+      <c r="O106" s="13" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="P106" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q106" s="8" t="inlineStr">
+        <is>
+          <t>166.80</t>
+        </is>
+      </c>
+      <c r="R106" s="8" t="inlineStr"/>
+      <c r="S106" s="8" t="inlineStr"/>
+      <c r="T106" s="8" t="inlineStr"/>
+      <c r="U106" s="8" t="inlineStr"/>
+      <c r="V106" s="8" t="inlineStr">
+        <is>
+          <t>153.20</t>
+        </is>
+      </c>
+      <c r="W106" s="8" t="inlineStr"/>
+      <c r="X106" s="9" t="n">
         <v>152.9875</v>
       </c>
-      <c r="Y105" s="9" t="n">
+      <c r="Y106" s="9" t="n">
         <v>849.6624999999999</v>
       </c>
-      <c r="Z105" s="11" t="n">
+      <c r="Z106" s="11" t="n">
         <v>-0.01221720319096315</v>
       </c>
     </row>
-    <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Qbert
 Random: 163.9
 Human: 13455.0</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 4522</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr"/>
-      <c r="D106" s="4" t="inlineStr"/>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="4" t="inlineStr"/>
-      <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="4" t="inlineStr"/>
-      <c r="J106" s="4" t="inlineStr"/>
-      <c r="K106" s="4" t="inlineStr"/>
-      <c r="L106" s="4" t="inlineStr"/>
-      <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr"/>
-      <c r="O106" s="4" t="inlineStr"/>
-      <c r="P106" s="4" t="inlineStr"/>
-      <c r="Q106" s="4" t="inlineStr"/>
-      <c r="R106" s="4" t="inlineStr"/>
-      <c r="S106" s="4" t="inlineStr"/>
-      <c r="T106" s="4" t="inlineStr"/>
-      <c r="U106" s="4" t="inlineStr"/>
-      <c r="V106" s="4" t="inlineStr"/>
-      <c r="W106" s="4" t="inlineStr"/>
-      <c r="X106" s="5" t="inlineStr"/>
-      <c r="Y106" s="6" t="n">
+      <c r="C107" s="4" t="inlineStr"/>
+      <c r="D107" s="4" t="inlineStr"/>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr"/>
+      <c r="K107" s="4" t="inlineStr"/>
+      <c r="L107" s="4" t="inlineStr"/>
+      <c r="M107" s="4" t="inlineStr"/>
+      <c r="N107" s="4" t="inlineStr"/>
+      <c r="O107" s="4" t="inlineStr"/>
+      <c r="P107" s="4" t="inlineStr"/>
+      <c r="Q107" s="4" t="inlineStr"/>
+      <c r="R107" s="4" t="inlineStr"/>
+      <c r="S107" s="4" t="inlineStr"/>
+      <c r="T107" s="4" t="inlineStr"/>
+      <c r="U107" s="4" t="inlineStr"/>
+      <c r="V107" s="4" t="inlineStr"/>
+      <c r="W107" s="4" t="inlineStr"/>
+      <c r="X107" s="5" t="inlineStr"/>
+      <c r="Y107" s="6" t="n">
         <v>-1662.9375</v>
       </c>
-      <c r="Z106" s="7" t="n">
+      <c r="Z107" s="7" t="n">
         <v>-0.1251166193919239</v>
       </c>
-    </row>
-    <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="1" t="n"/>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr"/>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr"/>
-      <c r="G107" s="8" t="inlineStr"/>
-      <c r="H107" s="8" t="inlineStr"/>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
-      <c r="J107" s="8" t="inlineStr"/>
-      <c r="K107" s="8" t="inlineStr">
-        <is>
-          <t>3193.75</t>
-        </is>
-      </c>
-      <c r="L107" s="8" t="inlineStr"/>
-      <c r="M107" s="8" t="inlineStr"/>
-      <c r="N107" s="8" t="inlineStr"/>
-      <c r="O107" s="8" t="inlineStr">
-        <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="P107" s="8" t="inlineStr"/>
-      <c r="Q107" s="8" t="inlineStr"/>
-      <c r="R107" s="8" t="inlineStr"/>
-      <c r="S107" s="8" t="inlineStr"/>
-      <c r="T107" s="8" t="inlineStr"/>
-      <c r="U107" s="8" t="inlineStr"/>
-      <c r="V107" s="8" t="inlineStr"/>
-      <c r="W107" s="8" t="inlineStr"/>
-      <c r="X107" s="9" t="n">
-        <v>2859.0625</v>
-      </c>
-      <c r="Y107" s="10" t="inlineStr"/>
-      <c r="Z107" s="11" t="inlineStr"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>2818.75</t>
+          <t>1771.25</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr"/>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>1918.75</t>
+          <t>3786.25</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr"/>
@@ -5967,17 +5948,21 @@
       <c r="H108" s="8" t="inlineStr"/>
       <c r="I108" s="13" t="inlineStr">
         <is>
-          <t>2553.75</t>
+          <t>2940.00</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr"/>
-      <c r="K108" s="8" t="inlineStr"/>
+      <c r="K108" s="8" t="inlineStr">
+        <is>
+          <t>3193.75</t>
+        </is>
+      </c>
       <c r="L108" s="8" t="inlineStr"/>
       <c r="M108" s="8" t="inlineStr"/>
       <c r="N108" s="8" t="inlineStr"/>
       <c r="O108" s="8" t="inlineStr">
         <is>
-          <t>3782.50</t>
+          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
         </is>
       </c>
       <c r="P108" s="8" t="inlineStr"/>
@@ -5988,7 +5973,9 @@
       <c r="U108" s="8" t="inlineStr"/>
       <c r="V108" s="8" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr"/>
-      <c r="X108" s="9" t="inlineStr"/>
+      <c r="X108" s="9" t="n">
+        <v>2859.0625</v>
+      </c>
       <c r="Y108" s="10" t="inlineStr"/>
       <c r="Z108" s="11" t="inlineStr"/>
     </row>
@@ -5996,18 +5983,18 @@
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>2702.50</t>
+          <t>2818.75</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr"/>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>4056.25</t>
+          <t>1918.75</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr"/>
@@ -6015,21 +6002,17 @@
       <c r="H109" s="8" t="inlineStr"/>
       <c r="I109" s="13" t="inlineStr">
         <is>
-          <t>2338.75</t>
+          <t>2553.75</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr"/>
-      <c r="K109" s="8" t="inlineStr">
-        <is>
-          <t>2608.75</t>
-        </is>
-      </c>
+      <c r="K109" s="8" t="inlineStr"/>
       <c r="L109" s="8" t="inlineStr"/>
       <c r="M109" s="8" t="inlineStr"/>
       <c r="N109" s="8" t="inlineStr"/>
       <c r="O109" s="8" t="inlineStr">
         <is>
-          <t>2895.00</t>
+          <t>3782.50</t>
         </is>
       </c>
       <c r="P109" s="8" t="inlineStr"/>
@@ -6040,113 +6023,115 @@
       <c r="U109" s="8" t="inlineStr"/>
       <c r="V109" s="8" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr"/>
-      <c r="X109" s="9" t="n">
+      <c r="X109" s="9" t="inlineStr"/>
+      <c r="Y109" s="10" t="inlineStr"/>
+      <c r="Z109" s="11" t="inlineStr"/>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="1" t="n"/>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>2702.50</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr"/>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>4056.25</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="inlineStr"/>
+      <c r="G110" s="8" t="inlineStr"/>
+      <c r="H110" s="8" t="inlineStr"/>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>2338.75</t>
+        </is>
+      </c>
+      <c r="J110" s="8" t="inlineStr"/>
+      <c r="K110" s="8" t="inlineStr">
+        <is>
+          <t>2608.75</t>
+        </is>
+      </c>
+      <c r="L110" s="8" t="inlineStr"/>
+      <c r="M110" s="8" t="inlineStr"/>
+      <c r="N110" s="8" t="inlineStr"/>
+      <c r="O110" s="8" t="inlineStr">
+        <is>
+          <t>2895.00</t>
+        </is>
+      </c>
+      <c r="P110" s="8" t="inlineStr"/>
+      <c r="Q110" s="8" t="inlineStr"/>
+      <c r="R110" s="8" t="inlineStr"/>
+      <c r="S110" s="8" t="inlineStr"/>
+      <c r="T110" s="8" t="inlineStr"/>
+      <c r="U110" s="8" t="inlineStr"/>
+      <c r="V110" s="8" t="inlineStr"/>
+      <c r="W110" s="8" t="inlineStr"/>
+      <c r="X110" s="9" t="n">
         <v>3065.625</v>
       </c>
-      <c r="Y109" s="9" t="n">
+      <c r="Y110" s="9" t="n">
         <v>206.5625</v>
       </c>
-      <c r="Z109" s="11" t="n">
+      <c r="Z110" s="11" t="n">
         <v>0.01554141493179646</v>
       </c>
     </row>
-    <row r="110" ht="24" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111" ht="24" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>RoadRunner
 Random: 11.5
 Human: 7845.0</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 17564</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr"/>
-      <c r="D110" s="4" t="inlineStr"/>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="4" t="inlineStr"/>
-      <c r="H110" s="4" t="inlineStr"/>
-      <c r="I110" s="4" t="inlineStr"/>
-      <c r="J110" s="4" t="inlineStr"/>
-      <c r="K110" s="4" t="inlineStr"/>
-      <c r="L110" s="4" t="inlineStr"/>
-      <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr"/>
-      <c r="O110" s="4" t="inlineStr"/>
-      <c r="P110" s="4" t="inlineStr"/>
-      <c r="Q110" s="4" t="inlineStr"/>
-      <c r="R110" s="4" t="inlineStr"/>
-      <c r="S110" s="4" t="inlineStr"/>
-      <c r="T110" s="4" t="inlineStr"/>
-      <c r="U110" s="4" t="inlineStr"/>
-      <c r="V110" s="4" t="inlineStr"/>
-      <c r="W110" s="4" t="inlineStr"/>
-      <c r="X110" s="5" t="inlineStr"/>
-      <c r="Y110" s="6" t="n">
+      <c r="C111" s="4" t="inlineStr"/>
+      <c r="D111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr"/>
+      <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr"/>
+      <c r="K111" s="4" t="inlineStr"/>
+      <c r="L111" s="4" t="inlineStr"/>
+      <c r="M111" s="4" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr"/>
+      <c r="O111" s="4" t="inlineStr"/>
+      <c r="P111" s="4" t="inlineStr"/>
+      <c r="Q111" s="4" t="inlineStr"/>
+      <c r="R111" s="4" t="inlineStr"/>
+      <c r="S111" s="4" t="inlineStr"/>
+      <c r="T111" s="4" t="inlineStr"/>
+      <c r="U111" s="4" t="inlineStr"/>
+      <c r="V111" s="4" t="inlineStr"/>
+      <c r="W111" s="4" t="inlineStr"/>
+      <c r="X111" s="5" t="inlineStr"/>
+      <c r="Y111" s="6" t="n">
         <v>-8627.75</v>
       </c>
-      <c r="Z110" s="7" t="n">
+      <c r="Z111" s="7" t="n">
         <v>-1.101391459756175</v>
       </c>
-    </row>
-    <row r="111" ht="24" customHeight="1">
-      <c r="A111" s="1" t="n"/>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr"/>
-      <c r="D111" s="8" t="inlineStr"/>
-      <c r="E111" s="8" t="inlineStr"/>
-      <c r="F111" s="8" t="inlineStr"/>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="8" t="inlineStr"/>
-      <c r="I111" s="8" t="inlineStr"/>
-      <c r="J111" s="8" t="inlineStr"/>
-      <c r="K111" s="8" t="inlineStr">
-        <is>
-          <t>8610.00</t>
-        </is>
-      </c>
-      <c r="L111" s="8" t="inlineStr"/>
-      <c r="M111" s="8" t="inlineStr"/>
-      <c r="N111" s="8" t="inlineStr"/>
-      <c r="O111" s="8" t="inlineStr">
-        <is>
-          <t>7290.00</t>
-        </is>
-      </c>
-      <c r="P111" s="8" t="inlineStr">
-        <is>
-          <t>9690.00</t>
-        </is>
-      </c>
-      <c r="Q111" s="8" t="inlineStr">
-        <is>
-          <t>10155.00</t>
-        </is>
-      </c>
-      <c r="R111" s="8" t="inlineStr"/>
-      <c r="S111" s="8" t="inlineStr"/>
-      <c r="T111" s="8" t="inlineStr"/>
-      <c r="U111" s="8" t="inlineStr"/>
-      <c r="V111" s="8" t="inlineStr"/>
-      <c r="W111" s="8" t="inlineStr"/>
-      <c r="X111" s="9" t="n">
-        <v>8936.25</v>
-      </c>
-      <c r="Y111" s="10" t="inlineStr"/>
-      <c r="Z111" s="11" t="inlineStr"/>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr"/>
@@ -6157,23 +6142,27 @@
       <c r="H112" s="8" t="inlineStr"/>
       <c r="I112" s="8" t="inlineStr"/>
       <c r="J112" s="8" t="inlineStr"/>
-      <c r="K112" s="8" t="inlineStr"/>
+      <c r="K112" s="8" t="inlineStr">
+        <is>
+          <t>8610.00</t>
+        </is>
+      </c>
       <c r="L112" s="8" t="inlineStr"/>
       <c r="M112" s="8" t="inlineStr"/>
       <c r="N112" s="8" t="inlineStr"/>
       <c r="O112" s="8" t="inlineStr">
         <is>
-          <t>8520.00</t>
+          <t>7290.00</t>
         </is>
       </c>
       <c r="P112" s="8" t="inlineStr">
         <is>
-          <t>11830.00</t>
+          <t>9690.00</t>
         </is>
       </c>
       <c r="Q112" s="8" t="inlineStr">
         <is>
-          <t>16805.00</t>
+          <t>10155.00</t>
         </is>
       </c>
       <c r="R112" s="8" t="inlineStr"/>
@@ -6182,7 +6171,9 @@
       <c r="U112" s="8" t="inlineStr"/>
       <c r="V112" s="8" t="inlineStr"/>
       <c r="W112" s="8" t="inlineStr"/>
-      <c r="X112" s="9" t="inlineStr"/>
+      <c r="X112" s="9" t="n">
+        <v>8936.25</v>
+      </c>
       <c r="Y112" s="10" t="inlineStr"/>
       <c r="Z112" s="11" t="inlineStr"/>
     </row>
@@ -6190,7 +6181,7 @@
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr"/>
@@ -6201,27 +6192,23 @@
       <c r="H113" s="8" t="inlineStr"/>
       <c r="I113" s="8" t="inlineStr"/>
       <c r="J113" s="8" t="inlineStr"/>
-      <c r="K113" s="8" t="inlineStr">
-        <is>
-          <t>8195.00</t>
-        </is>
-      </c>
+      <c r="K113" s="8" t="inlineStr"/>
       <c r="L113" s="8" t="inlineStr"/>
       <c r="M113" s="8" t="inlineStr"/>
       <c r="N113" s="8" t="inlineStr"/>
       <c r="O113" s="8" t="inlineStr">
         <is>
-          <t>8325.00</t>
+          <t>8520.00</t>
         </is>
       </c>
       <c r="P113" s="8" t="inlineStr">
         <is>
-          <t>12890.00</t>
+          <t>11830.00</t>
         </is>
       </c>
       <c r="Q113" s="8" t="inlineStr">
         <is>
-          <t>16980.00</t>
+          <t>16805.00</t>
         </is>
       </c>
       <c r="R113" s="8" t="inlineStr"/>
@@ -6230,116 +6217,118 @@
       <c r="U113" s="8" t="inlineStr"/>
       <c r="V113" s="8" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr"/>
-      <c r="X113" s="9" t="n">
+      <c r="X113" s="9" t="inlineStr"/>
+      <c r="Y113" s="10" t="inlineStr"/>
+      <c r="Z113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="1" t="n"/>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr"/>
+      <c r="D114" s="8" t="inlineStr"/>
+      <c r="E114" s="8" t="inlineStr"/>
+      <c r="F114" s="8" t="inlineStr"/>
+      <c r="G114" s="8" t="inlineStr"/>
+      <c r="H114" s="8" t="inlineStr"/>
+      <c r="I114" s="8" t="inlineStr"/>
+      <c r="J114" s="8" t="inlineStr"/>
+      <c r="K114" s="8" t="inlineStr">
+        <is>
+          <t>8195.00</t>
+        </is>
+      </c>
+      <c r="L114" s="8" t="inlineStr"/>
+      <c r="M114" s="8" t="inlineStr"/>
+      <c r="N114" s="8" t="inlineStr"/>
+      <c r="O114" s="8" t="inlineStr">
+        <is>
+          <t>8325.00</t>
+        </is>
+      </c>
+      <c r="P114" s="8" t="inlineStr">
+        <is>
+          <t>12890.00</t>
+        </is>
+      </c>
+      <c r="Q114" s="8" t="inlineStr">
+        <is>
+          <t>16980.00</t>
+        </is>
+      </c>
+      <c r="R114" s="8" t="inlineStr"/>
+      <c r="S114" s="8" t="inlineStr"/>
+      <c r="T114" s="8" t="inlineStr"/>
+      <c r="U114" s="8" t="inlineStr"/>
+      <c r="V114" s="8" t="inlineStr"/>
+      <c r="W114" s="8" t="inlineStr"/>
+      <c r="X114" s="9" t="n">
         <v>11597.5</v>
       </c>
-      <c r="Y113" s="9" t="n">
+      <c r="Y114" s="9" t="n">
         <v>2661.25</v>
       </c>
-      <c r="Z113" s="11" t="n">
+      <c r="Z114" s="11" t="n">
         <v>0.3397268143230995</v>
       </c>
     </row>
-    <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115" ht="24" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Seaquest
 Random: 68.4
 Human: 42054.7</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 525</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr"/>
-      <c r="D114" s="4" t="inlineStr"/>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="4" t="inlineStr"/>
-      <c r="H114" s="4" t="inlineStr"/>
-      <c r="I114" s="4" t="inlineStr"/>
-      <c r="J114" s="4" t="inlineStr"/>
-      <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="4" t="inlineStr"/>
-      <c r="M114" s="4" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr"/>
-      <c r="O114" s="4" t="inlineStr"/>
-      <c r="P114" s="4" t="inlineStr"/>
-      <c r="Q114" s="4" t="inlineStr"/>
-      <c r="R114" s="4" t="inlineStr"/>
-      <c r="S114" s="4" t="inlineStr"/>
-      <c r="T114" s="4" t="inlineStr"/>
-      <c r="U114" s="4" t="inlineStr"/>
-      <c r="V114" s="4" t="inlineStr"/>
-      <c r="W114" s="4" t="inlineStr"/>
-      <c r="X114" s="5" t="inlineStr"/>
-      <c r="Y114" s="6" t="n">
+      <c r="C115" s="4" t="inlineStr"/>
+      <c r="D115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr"/>
+      <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr"/>
+      <c r="K115" s="4" t="inlineStr"/>
+      <c r="L115" s="4" t="inlineStr"/>
+      <c r="M115" s="4" t="inlineStr"/>
+      <c r="N115" s="4" t="inlineStr"/>
+      <c r="O115" s="4" t="inlineStr"/>
+      <c r="P115" s="4" t="inlineStr"/>
+      <c r="Q115" s="4" t="inlineStr"/>
+      <c r="R115" s="4" t="inlineStr"/>
+      <c r="S115" s="4" t="inlineStr"/>
+      <c r="T115" s="4" t="inlineStr"/>
+      <c r="U115" s="4" t="inlineStr"/>
+      <c r="V115" s="4" t="inlineStr"/>
+      <c r="W115" s="4" t="inlineStr"/>
+      <c r="X115" s="5" t="inlineStr"/>
+      <c r="Y115" s="6" t="n">
         <v>-64.33333333333331</v>
       </c>
-      <c r="Z114" s="7" t="n">
+      <c r="Z115" s="7" t="n">
         <v>-0.001532245835744834</v>
       </c>
-    </row>
-    <row r="115" ht="24" customHeight="1">
-      <c r="A115" s="1" t="n"/>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>454.00</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr"/>
-      <c r="E115" s="8" t="inlineStr"/>
-      <c r="F115" s="8" t="inlineStr"/>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="8" t="inlineStr"/>
-      <c r="I115" s="8" t="inlineStr"/>
-      <c r="J115" s="8" t="inlineStr"/>
-      <c r="K115" s="8" t="inlineStr">
-        <is>
-          <t>494.00</t>
-        </is>
-      </c>
-      <c r="L115" s="8" t="inlineStr"/>
-      <c r="M115" s="8" t="inlineStr"/>
-      <c r="N115" s="8" t="inlineStr"/>
-      <c r="O115" s="8" t="inlineStr">
-        <is>
-          <t>418.00</t>
-        </is>
-      </c>
-      <c r="P115" s="8" t="inlineStr"/>
-      <c r="Q115" s="8" t="inlineStr"/>
-      <c r="R115" s="8" t="inlineStr"/>
-      <c r="S115" s="8" t="inlineStr"/>
-      <c r="T115" s="8" t="inlineStr"/>
-      <c r="U115" s="8" t="inlineStr"/>
-      <c r="V115" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
-      <c r="W115" s="8" t="inlineStr"/>
-      <c r="X115" s="9" t="n">
-        <v>460.6666666666667</v>
-      </c>
-      <c r="Y115" s="10" t="inlineStr"/>
-      <c r="Z115" s="11" t="inlineStr"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>454.00</t>
+        </is>
+      </c>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr"/>
       <c r="F116" s="8" t="inlineStr"/>
@@ -6347,13 +6336,17 @@
       <c r="H116" s="8" t="inlineStr"/>
       <c r="I116" s="8" t="inlineStr"/>
       <c r="J116" s="8" t="inlineStr"/>
-      <c r="K116" s="8" t="inlineStr"/>
+      <c r="K116" s="8" t="inlineStr">
+        <is>
+          <t>494.00</t>
+        </is>
+      </c>
       <c r="L116" s="8" t="inlineStr"/>
       <c r="M116" s="8" t="inlineStr"/>
       <c r="N116" s="8" t="inlineStr"/>
       <c r="O116" s="8" t="inlineStr">
         <is>
-          <t>476.00</t>
+          <t>418.00</t>
         </is>
       </c>
       <c r="P116" s="8" t="inlineStr"/>
@@ -6364,11 +6357,13 @@
       <c r="U116" s="8" t="inlineStr"/>
       <c r="V116" s="8" t="inlineStr">
         <is>
-          <t>557.00</t>
+          <t>470.00</t>
         </is>
       </c>
       <c r="W116" s="8" t="inlineStr"/>
-      <c r="X116" s="9" t="inlineStr"/>
+      <c r="X116" s="9" t="n">
+        <v>460.6666666666667</v>
+      </c>
       <c r="Y116" s="10" t="inlineStr"/>
       <c r="Z116" s="11" t="inlineStr"/>
     </row>
@@ -6376,7 +6371,7 @@
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr"/>
@@ -6387,17 +6382,13 @@
       <c r="H117" s="8" t="inlineStr"/>
       <c r="I117" s="8" t="inlineStr"/>
       <c r="J117" s="8" t="inlineStr"/>
-      <c r="K117" s="8" t="inlineStr">
-        <is>
-          <t>521.00</t>
-        </is>
-      </c>
+      <c r="K117" s="8" t="inlineStr"/>
       <c r="L117" s="8" t="inlineStr"/>
       <c r="M117" s="8" t="inlineStr"/>
       <c r="N117" s="8" t="inlineStr"/>
       <c r="O117" s="8" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>476.00</t>
         </is>
       </c>
       <c r="P117" s="8" t="inlineStr"/>
@@ -6408,25 +6399,19 @@
       <c r="U117" s="8" t="inlineStr"/>
       <c r="V117" s="8" t="inlineStr">
         <is>
-          <t>545.00</t>
+          <t>557.00</t>
         </is>
       </c>
       <c r="W117" s="8" t="inlineStr"/>
-      <c r="X117" s="9" t="n">
-        <v>505.3333333333333</v>
-      </c>
-      <c r="Y117" s="9" t="n">
-        <v>44.66666666666663</v>
-      </c>
-      <c r="Z117" s="11" t="n">
-        <v>0.001063839077667397</v>
-      </c>
+      <c r="X117" s="9" t="inlineStr"/>
+      <c r="Y117" s="10" t="inlineStr"/>
+      <c r="Z117" s="11" t="inlineStr"/>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr"/>
@@ -6437,11 +6422,19 @@
       <c r="H118" s="8" t="inlineStr"/>
       <c r="I118" s="8" t="inlineStr"/>
       <c r="J118" s="8" t="inlineStr"/>
-      <c r="K118" s="8" t="inlineStr"/>
+      <c r="K118" s="8" t="inlineStr">
+        <is>
+          <t>521.00</t>
+        </is>
+      </c>
       <c r="L118" s="8" t="inlineStr"/>
       <c r="M118" s="8" t="inlineStr"/>
       <c r="N118" s="8" t="inlineStr"/>
-      <c r="O118" s="8" t="inlineStr"/>
+      <c r="O118" s="8" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
       <c r="P118" s="8" t="inlineStr"/>
       <c r="Q118" s="8" t="inlineStr"/>
       <c r="R118" s="8" t="inlineStr"/>
@@ -6450,19 +6443,25 @@
       <c r="U118" s="8" t="inlineStr"/>
       <c r="V118" s="8" t="inlineStr">
         <is>
-          <t>411.00</t>
+          <t>545.00</t>
         </is>
       </c>
       <c r="W118" s="8" t="inlineStr"/>
-      <c r="X118" s="9" t="inlineStr"/>
-      <c r="Y118" s="10" t="inlineStr"/>
-      <c r="Z118" s="11" t="inlineStr"/>
+      <c r="X118" s="9" t="n">
+        <v>505.3333333333333</v>
+      </c>
+      <c r="Y118" s="9" t="n">
+        <v>44.66666666666663</v>
+      </c>
+      <c r="Z118" s="11" t="n">
+        <v>0.001063839077667397</v>
+      </c>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr"/>
@@ -6486,7 +6485,7 @@
       <c r="U119" s="8" t="inlineStr"/>
       <c r="V119" s="8" t="inlineStr">
         <is>
-          <t>415.00</t>
+          <t>411.00</t>
         </is>
       </c>
       <c r="W119" s="8" t="inlineStr"/>
@@ -6495,115 +6494,105 @@
       <c r="Z119" s="11" t="inlineStr"/>
     </row>
     <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="1" t="n"/>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr"/>
+      <c r="D120" s="8" t="inlineStr"/>
+      <c r="E120" s="8" t="inlineStr"/>
+      <c r="F120" s="8" t="inlineStr"/>
+      <c r="G120" s="8" t="inlineStr"/>
+      <c r="H120" s="8" t="inlineStr"/>
+      <c r="I120" s="8" t="inlineStr"/>
+      <c r="J120" s="8" t="inlineStr"/>
+      <c r="K120" s="8" t="inlineStr"/>
+      <c r="L120" s="8" t="inlineStr"/>
+      <c r="M120" s="8" t="inlineStr"/>
+      <c r="N120" s="8" t="inlineStr"/>
+      <c r="O120" s="8" t="inlineStr"/>
+      <c r="P120" s="8" t="inlineStr"/>
+      <c r="Q120" s="8" t="inlineStr"/>
+      <c r="R120" s="8" t="inlineStr"/>
+      <c r="S120" s="8" t="inlineStr"/>
+      <c r="T120" s="8" t="inlineStr"/>
+      <c r="U120" s="8" t="inlineStr"/>
+      <c r="V120" s="8" t="inlineStr">
+        <is>
+          <t>415.00</t>
+        </is>
+      </c>
+      <c r="W120" s="8" t="inlineStr"/>
+      <c r="X120" s="9" t="inlineStr"/>
+      <c r="Y120" s="10" t="inlineStr"/>
+      <c r="Z120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121" ht="24" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>UpNDown
 Random: 533.4
 Human: 11693.2</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 7985</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr"/>
-      <c r="D120" s="4" t="inlineStr"/>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="4" t="inlineStr"/>
-      <c r="H120" s="4" t="inlineStr"/>
-      <c r="I120" s="4" t="inlineStr"/>
-      <c r="J120" s="4" t="inlineStr"/>
-      <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="4" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr"/>
-      <c r="O120" s="4" t="inlineStr"/>
-      <c r="P120" s="4" t="inlineStr"/>
-      <c r="Q120" s="4" t="inlineStr"/>
-      <c r="R120" s="4" t="inlineStr"/>
-      <c r="S120" s="4" t="inlineStr"/>
-      <c r="T120" s="4" t="inlineStr"/>
-      <c r="U120" s="4" t="inlineStr"/>
-      <c r="V120" s="4" t="inlineStr"/>
-      <c r="W120" s="4" t="inlineStr"/>
-      <c r="X120" s="5" t="inlineStr"/>
-      <c r="Y120" s="6" t="n">
+      <c r="C121" s="4" t="inlineStr"/>
+      <c r="D121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
+      <c r="G121" s="4" t="inlineStr"/>
+      <c r="H121" s="4" t="inlineStr"/>
+      <c r="I121" s="4" t="inlineStr"/>
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr"/>
+      <c r="L121" s="4" t="inlineStr"/>
+      <c r="M121" s="4" t="inlineStr"/>
+      <c r="N121" s="4" t="inlineStr"/>
+      <c r="O121" s="4" t="inlineStr"/>
+      <c r="P121" s="4" t="inlineStr"/>
+      <c r="Q121" s="4" t="inlineStr"/>
+      <c r="R121" s="4" t="inlineStr"/>
+      <c r="S121" s="4" t="inlineStr"/>
+      <c r="T121" s="4" t="inlineStr"/>
+      <c r="U121" s="4" t="inlineStr"/>
+      <c r="V121" s="4" t="inlineStr"/>
+      <c r="W121" s="4" t="inlineStr"/>
+      <c r="X121" s="5" t="inlineStr"/>
+      <c r="Y121" s="6" t="n">
         <v>-2963</v>
       </c>
-      <c r="Z120" s="7" t="n">
+      <c r="Z121" s="7" t="n">
         <v>-0.2655065502966003</v>
       </c>
-    </row>
-    <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="1" t="n"/>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t>9044.00</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="inlineStr"/>
-      <c r="E121" s="8" t="inlineStr"/>
-      <c r="F121" s="8" t="inlineStr"/>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="8" t="inlineStr"/>
-      <c r="I121" s="8" t="inlineStr">
-        <is>
-          <t>5849.00</t>
-        </is>
-      </c>
-      <c r="J121" s="8" t="inlineStr"/>
-      <c r="K121" s="8" t="inlineStr"/>
-      <c r="L121" s="8" t="inlineStr"/>
-      <c r="M121" s="8" t="inlineStr"/>
-      <c r="N121" s="8" t="inlineStr"/>
-      <c r="O121" s="8" t="inlineStr">
-        <is>
-          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
-        </is>
-      </c>
-      <c r="P121" s="8" t="inlineStr">
-        <is>
-          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
-        </is>
-      </c>
-      <c r="Q121" s="8" t="inlineStr">
-        <is>
-          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="R121" s="8" t="inlineStr"/>
-      <c r="S121" s="8" t="inlineStr"/>
-      <c r="T121" s="8" t="inlineStr"/>
-      <c r="U121" s="8" t="inlineStr"/>
-      <c r="V121" s="8" t="inlineStr"/>
-      <c r="W121" s="8" t="inlineStr"/>
-      <c r="X121" s="9" t="n">
-        <v>5022</v>
-      </c>
-      <c r="Y121" s="10" t="inlineStr"/>
-      <c r="Z121" s="11" t="inlineStr"/>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>9044.00</t>
+        </is>
+      </c>
       <c r="D122" s="8" t="inlineStr"/>
       <c r="E122" s="8" t="inlineStr"/>
       <c r="F122" s="8" t="inlineStr"/>
       <c r="G122" s="8" t="inlineStr"/>
       <c r="H122" s="8" t="inlineStr"/>
-      <c r="I122" s="8" t="inlineStr"/>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>5849.00</t>
+        </is>
+      </c>
       <c r="J122" s="8" t="inlineStr"/>
       <c r="K122" s="8" t="inlineStr"/>
       <c r="L122" s="8" t="inlineStr"/>
@@ -6611,17 +6600,17 @@
       <c r="N122" s="8" t="inlineStr"/>
       <c r="O122" s="8" t="inlineStr">
         <is>
-          <t>5670.00</t>
+          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
         </is>
       </c>
       <c r="P122" s="8" t="inlineStr">
         <is>
-          <t>7178.00</t>
+          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
         </is>
       </c>
       <c r="Q122" s="8" t="inlineStr">
         <is>
-          <t>3066.00</t>
+          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
         </is>
       </c>
       <c r="R122" s="8" t="inlineStr"/>
@@ -6630,7 +6619,9 @@
       <c r="U122" s="8" t="inlineStr"/>
       <c r="V122" s="8" t="inlineStr"/>
       <c r="W122" s="8" t="inlineStr"/>
-      <c r="X122" s="9" t="inlineStr"/>
+      <c r="X122" s="9" t="n">
+        <v>5022</v>
+      </c>
       <c r="Y122" s="10" t="inlineStr"/>
       <c r="Z122" s="11" t="inlineStr"/>
     </row>
@@ -6638,7 +6629,7 @@
       <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr"/>
@@ -6655,17 +6646,17 @@
       <c r="N123" s="8" t="inlineStr"/>
       <c r="O123" s="8" t="inlineStr">
         <is>
-          <t>6043.00</t>
+          <t>5670.00</t>
         </is>
       </c>
       <c r="P123" s="8" t="inlineStr">
         <is>
-          <t>6658.00</t>
+          <t>7178.00</t>
         </is>
       </c>
       <c r="Q123" s="8" t="inlineStr">
         <is>
-          <t>2974.50</t>
+          <t>3066.00</t>
         </is>
       </c>
       <c r="R123" s="8" t="inlineStr"/>
@@ -6674,42 +6665,86 @@
       <c r="U123" s="8" t="inlineStr"/>
       <c r="V123" s="8" t="inlineStr"/>
       <c r="W123" s="8" t="inlineStr"/>
-      <c r="X123" s="9" t="n">
+      <c r="X123" s="9" t="inlineStr"/>
+      <c r="Y123" s="10" t="inlineStr"/>
+      <c r="Z123" s="11" t="inlineStr"/>
+    </row>
+    <row r="124" ht="24" customHeight="1">
+      <c r="A124" s="1" t="n"/>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr"/>
+      <c r="D124" s="8" t="inlineStr"/>
+      <c r="E124" s="8" t="inlineStr"/>
+      <c r="F124" s="8" t="inlineStr"/>
+      <c r="G124" s="8" t="inlineStr"/>
+      <c r="H124" s="8" t="inlineStr"/>
+      <c r="I124" s="8" t="inlineStr"/>
+      <c r="J124" s="8" t="inlineStr"/>
+      <c r="K124" s="8" t="inlineStr"/>
+      <c r="L124" s="8" t="inlineStr"/>
+      <c r="M124" s="8" t="inlineStr"/>
+      <c r="N124" s="8" t="inlineStr"/>
+      <c r="O124" s="8" t="inlineStr">
+        <is>
+          <t>6043.00</t>
+        </is>
+      </c>
+      <c r="P124" s="8" t="inlineStr">
+        <is>
+          <t>6658.00</t>
+        </is>
+      </c>
+      <c r="Q124" s="8" t="inlineStr">
+        <is>
+          <t>2974.50</t>
+        </is>
+      </c>
+      <c r="R124" s="8" t="inlineStr"/>
+      <c r="S124" s="8" t="inlineStr"/>
+      <c r="T124" s="8" t="inlineStr"/>
+      <c r="U124" s="8" t="inlineStr"/>
+      <c r="V124" s="8" t="inlineStr"/>
+      <c r="W124" s="8" t="inlineStr"/>
+      <c r="X124" s="9" t="n">
         <v>5225.166666666667</v>
       </c>
-      <c r="Y123" s="9" t="n">
+      <c r="Y124" s="9" t="n">
         <v>203.166666666667</v>
       </c>
-      <c r="Z123" s="11" t="n">
+      <c r="Z124" s="11" t="n">
         <v>0.01820522470534122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A101:A103"/>
     <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A114:A119"/>
-    <mergeCell ref="A100:A102"/>
-    <mergeCell ref="A91:A93"/>
-    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="A107:A110"/>
     <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A94:A99"/>
     <mergeCell ref="A63:A67"/>
+    <mergeCell ref="A84:A87"/>
     <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A92:A94"/>
     <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A74:A79"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A95:A100"/>
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A103:A105"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A121:A124"/>
     <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A74:A78"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A115:A120"/>
     <mergeCell ref="A68:A73"/>
+    <mergeCell ref="A111:A114"/>
     <mergeCell ref="A44:A49"/>
     <mergeCell ref="A40:A43"/>
   </mergeCells>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="+0.00;-0.00;0.00"/>
     <numFmt numFmtId="165" formatCode="+0.0000;-0.0000;0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,13 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <strike val="1"/>
+      <color rgb="00808080"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <strike val="1"/>
       <color rgb="00808080"/>
       <sz val="16"/>
@@ -152,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -171,9 +178,10 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -257,18 +265,18 @@
     <author>STORM</author>
   </authors>
   <commentList>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>Retrieval 미사용과 target: 16 양쪽에 유효한 점수가 있는 공통 시드만 사용합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드는 제외합니다. 각 시드에 여러 결과가 있으면 첫 번째 점수를 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: Retrieval 미사용의 공통 시드 평균 − STORM 논문 점수.
 target: 16 행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AB1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: (Retrieval 미사용 평균 − STORM 논문 점수) / (Human − Random).
 target: 16 행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
@@ -282,6 +290,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="R27" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="Q28" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
@@ -289,6 +304,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="R28" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="Q29" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
@@ -296,290 +318,588 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P31" authorId="0" shapeId="0">
+    <comment ref="R29" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P33" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P32" authorId="0" shapeId="0">
+    <comment ref="P34" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
+    <comment ref="P35" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P34" authorId="0" shapeId="0">
+    <comment ref="P36" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P35" authorId="0" shapeId="0">
+    <comment ref="P37" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O37" authorId="0" shapeId="0">
+    <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O38" authorId="0" shapeId="0">
+    <comment ref="O40" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O39" authorId="0" shapeId="0">
+    <comment ref="O41" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E64" authorId="0" shapeId="0">
+    <comment ref="O42" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O43" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="E71" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E65" authorId="0" shapeId="0">
+    <comment ref="E72" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E66" authorId="0" shapeId="0">
+    <comment ref="E73" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E67" authorId="0" shapeId="0">
+    <comment ref="E74" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 10
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O69" authorId="0" shapeId="0">
+    <comment ref="E75" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O77" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P69" authorId="0" shapeId="0">
+    <comment ref="P77" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="V69" authorId="0" shapeId="0">
+    <comment ref="Q77" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R77" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S77" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="X77" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O70" authorId="0" shapeId="0">
+    <comment ref="O78" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P70" authorId="0" shapeId="0">
+    <comment ref="P78" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="V70" authorId="0" shapeId="0">
+    <comment ref="Q78" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R78" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S78" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="X78" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O71" authorId="0" shapeId="0">
+    <comment ref="O79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P71" authorId="0" shapeId="0">
+    <comment ref="P79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q71" authorId="0" shapeId="0">
+    <comment ref="Q79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="R79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="S79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="U79" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="R71" authorId="0" shapeId="0">
+    <comment ref="V79" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="S71" authorId="0" shapeId="0">
+    <comment ref="X79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="X80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="X81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R95" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="V71" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+    <comment ref="K97" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O72" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+    <comment ref="L97" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P72" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+    <comment ref="P97" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="V72" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+    <comment ref="R97" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O73" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+    <comment ref="K98" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P73" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+    <comment ref="L98" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="V73" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+    <comment ref="P98" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K89" authorId="0" shapeId="0">
+    <comment ref="R98" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K99" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L89" authorId="0" shapeId="0">
+    <comment ref="L99" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K90" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
+    <comment ref="P99" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="R99" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="X114" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="O118" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L90" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
+    <comment ref="R118" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K91" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
+    <comment ref="O119" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L91" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
+    <comment ref="R119" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="I121" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="P91" authorId="0" shapeId="0">
+    <comment ref="R121" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I122" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R122" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I123" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R123" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="K125" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K126" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K127" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R127" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="O105" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
+    <comment ref="Q135" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O106" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
+    <comment ref="Q136" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I108" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+    <comment ref="Q137" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I109" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 3710
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="I110" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 3710
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+    <comment ref="R137" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
   </commentList>
@@ -875,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z124"/>
+  <dimension ref="A1:AB137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
@@ -883,10 +1203,10 @@
     <col width="3" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="13" max="13"/>
     <col width="3" customWidth="1" min="20" max="20"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="46" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="3" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="46" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -961,27 +1281,33 @@
         </is>
       </c>
       <c r="U1" s="1" t="n">
+        <v>9996</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>9997</v>
+      </c>
+      <c r="W1" s="1" t="n">
         <v>9998</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="X1" s="1" t="n">
         <v>9999</v>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>   </t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -1021,11 +1347,13 @@
       <c r="U2" s="4" t="inlineStr"/>
       <c r="V2" s="4" t="inlineStr"/>
       <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="6" t="n">
+      <c r="X2" s="4" t="inlineStr"/>
+      <c r="Y2" s="4" t="inlineStr"/>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="6" t="n">
         <v>57.79999999999995</v>
       </c>
-      <c r="Z2" s="7" t="n">
+      <c r="AB2" s="7" t="n">
         <v>0.008376932999028966</v>
       </c>
     </row>
@@ -1081,11 +1409,13 @@
       <c r="U3" s="8" t="inlineStr"/>
       <c r="V3" s="8" t="inlineStr"/>
       <c r="W3" s="8" t="inlineStr"/>
-      <c r="X3" s="9" t="n">
+      <c r="X3" s="8" t="inlineStr"/>
+      <c r="Y3" s="8" t="inlineStr"/>
+      <c r="Z3" s="9" t="n">
         <v>1041.8</v>
       </c>
-      <c r="Y3" s="10" t="inlineStr"/>
-      <c r="Z3" s="11" t="inlineStr"/>
+      <c r="AA3" s="10" t="inlineStr"/>
+      <c r="AB3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -1131,9 +1461,11 @@
       <c r="U4" s="8" t="inlineStr"/>
       <c r="V4" s="8" t="inlineStr"/>
       <c r="W4" s="8" t="inlineStr"/>
-      <c r="X4" s="9" t="inlineStr"/>
-      <c r="Y4" s="10" t="inlineStr"/>
-      <c r="Z4" s="11" t="inlineStr"/>
+      <c r="X4" s="8" t="inlineStr"/>
+      <c r="Y4" s="8" t="inlineStr"/>
+      <c r="Z4" s="9" t="inlineStr"/>
+      <c r="AA4" s="10" t="inlineStr"/>
+      <c r="AB4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -1183,13 +1515,15 @@
       <c r="U5" s="8" t="inlineStr"/>
       <c r="V5" s="8" t="inlineStr"/>
       <c r="W5" s="8" t="inlineStr"/>
-      <c r="X5" s="9" t="n">
+      <c r="X5" s="8" t="inlineStr"/>
+      <c r="Y5" s="8" t="inlineStr"/>
+      <c r="Z5" s="9" t="n">
         <v>1091.1</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="AA5" s="9" t="n">
         <v>49.29999999999995</v>
       </c>
-      <c r="Z5" s="11" t="n">
+      <c r="AB5" s="11" t="n">
         <v>0.007145031087407058</v>
       </c>
     </row>
@@ -1225,9 +1559,11 @@
       <c r="U6" s="8" t="inlineStr"/>
       <c r="V6" s="8" t="inlineStr"/>
       <c r="W6" s="8" t="inlineStr"/>
-      <c r="X6" s="9" t="inlineStr"/>
-      <c r="Y6" s="10" t="inlineStr"/>
-      <c r="Z6" s="11" t="inlineStr"/>
+      <c r="X6" s="8" t="inlineStr"/>
+      <c r="Y6" s="8" t="inlineStr"/>
+      <c r="Z6" s="9" t="inlineStr"/>
+      <c r="AA6" s="10" t="inlineStr"/>
+      <c r="AB6" s="11" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="1" t="n"/>
@@ -1261,9 +1597,11 @@
       <c r="U7" s="8" t="inlineStr"/>
       <c r="V7" s="8" t="inlineStr"/>
       <c r="W7" s="8" t="inlineStr"/>
-      <c r="X7" s="9" t="inlineStr"/>
-      <c r="Y7" s="10" t="inlineStr"/>
-      <c r="Z7" s="11" t="inlineStr"/>
+      <c r="X7" s="8" t="inlineStr"/>
+      <c r="Y7" s="8" t="inlineStr"/>
+      <c r="Z7" s="9" t="inlineStr"/>
+      <c r="AA7" s="10" t="inlineStr"/>
+      <c r="AB7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1299,11 +1637,13 @@
       <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr"/>
       <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr"/>
-      <c r="Y8" s="6" t="n">
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="AA8" s="6" t="n">
         <v>2.849999999999994</v>
       </c>
-      <c r="Z8" s="7" t="n">
+      <c r="AB8" s="7" t="n">
         <v>0.001663068214973446</v>
       </c>
     </row>
@@ -1359,11 +1699,13 @@
       <c r="U9" s="8" t="inlineStr"/>
       <c r="V9" s="8" t="inlineStr"/>
       <c r="W9" s="8" t="inlineStr"/>
-      <c r="X9" s="9" t="n">
+      <c r="X9" s="8" t="inlineStr"/>
+      <c r="Y9" s="8" t="inlineStr"/>
+      <c r="Z9" s="9" t="n">
         <v>207.85</v>
       </c>
-      <c r="Y9" s="10" t="inlineStr"/>
-      <c r="Z9" s="11" t="inlineStr"/>
+      <c r="AA9" s="10" t="inlineStr"/>
+      <c r="AB9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -1409,9 +1751,11 @@
       <c r="U10" s="8" t="inlineStr"/>
       <c r="V10" s="8" t="inlineStr"/>
       <c r="W10" s="8" t="inlineStr"/>
-      <c r="X10" s="9" t="inlineStr"/>
-      <c r="Y10" s="10" t="inlineStr"/>
-      <c r="Z10" s="11" t="inlineStr"/>
+      <c r="X10" s="8" t="inlineStr"/>
+      <c r="Y10" s="8" t="inlineStr"/>
+      <c r="Z10" s="9" t="inlineStr"/>
+      <c r="AA10" s="10" t="inlineStr"/>
+      <c r="AB10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="1" t="n"/>
@@ -1461,13 +1805,15 @@
       <c r="U11" s="8" t="inlineStr"/>
       <c r="V11" s="8" t="inlineStr"/>
       <c r="W11" s="8" t="inlineStr"/>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="8" t="inlineStr"/>
+      <c r="Y11" s="8" t="inlineStr"/>
+      <c r="Z11" s="9" t="n">
         <v>164.88</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="AA11" s="9" t="n">
         <v>42.96999999999997</v>
       </c>
-      <c r="Z11" s="11" t="n">
+      <c r="AB11" s="11" t="n">
         <v>-0.02507440042014353</v>
       </c>
     </row>
@@ -1503,9 +1849,11 @@
       <c r="U12" s="8" t="inlineStr"/>
       <c r="V12" s="8" t="inlineStr"/>
       <c r="W12" s="8" t="inlineStr"/>
-      <c r="X12" s="9" t="inlineStr"/>
-      <c r="Y12" s="10" t="inlineStr"/>
-      <c r="Z12" s="11" t="inlineStr"/>
+      <c r="X12" s="8" t="inlineStr"/>
+      <c r="Y12" s="8" t="inlineStr"/>
+      <c r="Z12" s="9" t="inlineStr"/>
+      <c r="AA12" s="10" t="inlineStr"/>
+      <c r="AB12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -1539,9 +1887,11 @@
       <c r="U13" s="8" t="inlineStr"/>
       <c r="V13" s="8" t="inlineStr"/>
       <c r="W13" s="8" t="inlineStr"/>
-      <c r="X13" s="9" t="inlineStr"/>
-      <c r="Y13" s="10" t="inlineStr"/>
-      <c r="Z13" s="11" t="inlineStr"/>
+      <c r="X13" s="8" t="inlineStr"/>
+      <c r="Y13" s="8" t="inlineStr"/>
+      <c r="Z13" s="9" t="inlineStr"/>
+      <c r="AA13" s="10" t="inlineStr"/>
+      <c r="AB13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1577,11 +1927,13 @@
       <c r="U14" s="4" t="inlineStr"/>
       <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="5" t="inlineStr"/>
-      <c r="Y14" s="6" t="n">
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="AA14" s="6" t="n">
         <v>-22.95000000000005</v>
       </c>
-      <c r="Z14" s="7" t="n">
+      <c r="AB14" s="7" t="n">
         <v>-0.04416859122401856</v>
       </c>
     </row>
@@ -1637,11 +1989,13 @@
       <c r="U15" s="8" t="inlineStr"/>
       <c r="V15" s="8" t="inlineStr"/>
       <c r="W15" s="8" t="inlineStr"/>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="8" t="inlineStr"/>
+      <c r="Y15" s="8" t="inlineStr"/>
+      <c r="Z15" s="9" t="n">
         <v>778.05</v>
       </c>
-      <c r="Y15" s="10" t="inlineStr"/>
-      <c r="Z15" s="11" t="inlineStr"/>
+      <c r="AA15" s="10" t="inlineStr"/>
+      <c r="AB15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -1687,9 +2041,11 @@
       <c r="U16" s="8" t="inlineStr"/>
       <c r="V16" s="8" t="inlineStr"/>
       <c r="W16" s="8" t="inlineStr"/>
-      <c r="X16" s="9" t="inlineStr"/>
-      <c r="Y16" s="10" t="inlineStr"/>
-      <c r="Z16" s="11" t="inlineStr"/>
+      <c r="X16" s="8" t="inlineStr"/>
+      <c r="Y16" s="8" t="inlineStr"/>
+      <c r="Z16" s="9" t="inlineStr"/>
+      <c r="AA16" s="10" t="inlineStr"/>
+      <c r="AB16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -1751,13 +2107,15 @@
       <c r="U17" s="8" t="inlineStr"/>
       <c r="V17" s="8" t="inlineStr"/>
       <c r="W17" s="8" t="inlineStr"/>
-      <c r="X17" s="9" t="n">
+      <c r="X17" s="8" t="inlineStr"/>
+      <c r="Y17" s="8" t="inlineStr"/>
+      <c r="Z17" s="9" t="n">
         <v>705.5400000000001</v>
       </c>
-      <c r="Y17" s="9" t="n">
+      <c r="AA17" s="9" t="n">
         <v>72.50999999999988</v>
       </c>
-      <c r="Z17" s="11" t="n">
+      <c r="AB17" s="11" t="n">
         <v>-0.1395496535796764</v>
       </c>
     </row>
@@ -1793,9 +2151,11 @@
       <c r="U18" s="8" t="inlineStr"/>
       <c r="V18" s="8" t="inlineStr"/>
       <c r="W18" s="8" t="inlineStr"/>
-      <c r="X18" s="9" t="inlineStr"/>
-      <c r="Y18" s="10" t="inlineStr"/>
-      <c r="Z18" s="11" t="inlineStr"/>
+      <c r="X18" s="8" t="inlineStr"/>
+      <c r="Y18" s="8" t="inlineStr"/>
+      <c r="Z18" s="9" t="inlineStr"/>
+      <c r="AA18" s="10" t="inlineStr"/>
+      <c r="AB18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
@@ -1817,9 +2177,9 @@
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="8" t="inlineStr"/>
-      <c r="P19" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>671.95</t>
         </is>
       </c>
       <c r="Q19" s="8" t="inlineStr"/>
@@ -1829,9 +2189,11 @@
       <c r="U19" s="8" t="inlineStr"/>
       <c r="V19" s="8" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr"/>
-      <c r="X19" s="9" t="inlineStr"/>
-      <c r="Y19" s="10" t="inlineStr"/>
-      <c r="Z19" s="11" t="inlineStr"/>
+      <c r="X19" s="8" t="inlineStr"/>
+      <c r="Y19" s="8" t="inlineStr"/>
+      <c r="Z19" s="9" t="inlineStr"/>
+      <c r="AA19" s="10" t="inlineStr"/>
+      <c r="AB19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1867,11 +2229,13 @@
       <c r="U20" s="4" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="5" t="inlineStr"/>
-      <c r="Y20" s="6" t="n">
+      <c r="X20" s="4" t="inlineStr"/>
+      <c r="Y20" s="4" t="inlineStr"/>
+      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="AA20" s="6" t="n">
         <v>-350.5</v>
       </c>
-      <c r="Z20" s="7" t="n">
+      <c r="AB20" s="7" t="n">
         <v>-0.04226303160382478</v>
       </c>
     </row>
@@ -1923,11 +2287,13 @@
       <c r="U21" s="8" t="inlineStr"/>
       <c r="V21" s="8" t="inlineStr"/>
       <c r="W21" s="8" t="inlineStr"/>
-      <c r="X21" s="9" t="n">
+      <c r="X21" s="8" t="inlineStr"/>
+      <c r="Y21" s="8" t="inlineStr"/>
+      <c r="Z21" s="9" t="n">
         <v>677.5</v>
       </c>
-      <c r="Y21" s="10" t="inlineStr"/>
-      <c r="Z21" s="11" t="inlineStr"/>
+      <c r="AA21" s="10" t="inlineStr"/>
+      <c r="AB21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="1" t="n"/>
@@ -1969,9 +2335,11 @@
       <c r="U22" s="8" t="inlineStr"/>
       <c r="V22" s="8" t="inlineStr"/>
       <c r="W22" s="8" t="inlineStr"/>
-      <c r="X22" s="9" t="inlineStr"/>
-      <c r="Y22" s="10" t="inlineStr"/>
-      <c r="Z22" s="11" t="inlineStr"/>
+      <c r="X22" s="8" t="inlineStr"/>
+      <c r="Y22" s="8" t="inlineStr"/>
+      <c r="Z22" s="9" t="inlineStr"/>
+      <c r="AA22" s="10" t="inlineStr"/>
+      <c r="AB22" s="11" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="1" t="n"/>
@@ -2017,13 +2385,15 @@
       <c r="U23" s="8" t="inlineStr"/>
       <c r="V23" s="8" t="inlineStr"/>
       <c r="W23" s="8" t="inlineStr"/>
-      <c r="X23" s="9" t="n">
+      <c r="X23" s="8" t="inlineStr"/>
+      <c r="Y23" s="8" t="inlineStr"/>
+      <c r="Z23" s="9" t="n">
         <v>759.375</v>
       </c>
-      <c r="Y23" s="9" t="n">
+      <c r="AA23" s="9" t="n">
         <v>81.875</v>
       </c>
-      <c r="Z23" s="11" t="n">
+      <c r="AB23" s="11" t="n">
         <v>0.009872427139980468</v>
       </c>
     </row>
@@ -2059,9 +2429,11 @@
       <c r="U24" s="8" t="inlineStr"/>
       <c r="V24" s="8" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr"/>
-      <c r="X24" s="9" t="inlineStr"/>
-      <c r="Y24" s="10" t="inlineStr"/>
-      <c r="Z24" s="11" t="inlineStr"/>
+      <c r="X24" s="8" t="inlineStr"/>
+      <c r="Y24" s="8" t="inlineStr"/>
+      <c r="Z24" s="9" t="inlineStr"/>
+      <c r="AA24" s="10" t="inlineStr"/>
+      <c r="AB24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -2095,9 +2467,11 @@
       <c r="U25" s="8" t="inlineStr"/>
       <c r="V25" s="8" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr"/>
-      <c r="X25" s="9" t="inlineStr"/>
-      <c r="Y25" s="10" t="inlineStr"/>
-      <c r="Z25" s="11" t="inlineStr"/>
+      <c r="X25" s="8" t="inlineStr"/>
+      <c r="Y25" s="8" t="inlineStr"/>
+      <c r="Z25" s="9" t="inlineStr"/>
+      <c r="AA25" s="10" t="inlineStr"/>
+      <c r="AB25" s="11" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2133,11 +2507,13 @@
       <c r="U26" s="4" t="inlineStr"/>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr"/>
-      <c r="X26" s="5" t="inlineStr"/>
-      <c r="Y26" s="6" t="n">
+      <c r="X26" s="4" t="inlineStr"/>
+      <c r="Y26" s="4" t="inlineStr"/>
+      <c r="Z26" s="5" t="inlineStr"/>
+      <c r="AA26" s="6" t="n">
         <v>-84.75</v>
       </c>
-      <c r="Z26" s="7" t="n">
+      <c r="AB26" s="7" t="n">
         <v>-0.1146975233455136</v>
       </c>
     </row>
@@ -2182,30 +2558,32 @@
           <t>170.00</t>
         </is>
       </c>
-      <c r="Q27" s="13" t="inlineStr">
+      <c r="Q27" s="12" t="inlineStr">
         <is>
           <t>677.00</t>
         </is>
       </c>
-      <c r="R27" s="8" t="inlineStr"/>
+      <c r="R27" s="12" t="inlineStr"/>
       <c r="S27" s="8" t="inlineStr"/>
       <c r="T27" s="8" t="inlineStr"/>
-      <c r="U27" s="8" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr"/>
+      <c r="V27" s="8" t="inlineStr"/>
+      <c r="W27" s="8" t="inlineStr">
         <is>
           <t>694.50</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
+      <c r="X27" s="8" t="inlineStr">
         <is>
           <t>668.50</t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr"/>
-      <c r="X27" s="9" t="n">
+      <c r="Y27" s="8" t="inlineStr"/>
+      <c r="Z27" s="9" t="n">
         <v>556.25</v>
       </c>
-      <c r="Y27" s="10" t="inlineStr"/>
-      <c r="Z27" s="11" t="inlineStr"/>
+      <c r="AA27" s="10" t="inlineStr"/>
+      <c r="AB27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -2228,20 +2606,22 @@
       <c r="N28" s="8" t="inlineStr"/>
       <c r="O28" s="8" t="inlineStr"/>
       <c r="P28" s="8" t="inlineStr"/>
-      <c r="Q28" s="13" t="inlineStr"/>
-      <c r="R28" s="8" t="inlineStr"/>
+      <c r="Q28" s="12" t="inlineStr"/>
+      <c r="R28" s="12" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr"/>
       <c r="T28" s="8" t="inlineStr"/>
       <c r="U28" s="8" t="inlineStr"/>
-      <c r="V28" s="8" t="inlineStr">
+      <c r="V28" s="8" t="inlineStr"/>
+      <c r="W28" s="8" t="inlineStr"/>
+      <c r="X28" s="8" t="inlineStr">
         <is>
           <t>507.50</t>
         </is>
       </c>
-      <c r="W28" s="8" t="inlineStr"/>
-      <c r="X28" s="9" t="inlineStr"/>
-      <c r="Y28" s="10" t="inlineStr"/>
-      <c r="Z28" s="11" t="inlineStr"/>
+      <c r="Y28" s="8" t="inlineStr"/>
+      <c r="Z28" s="9" t="inlineStr"/>
+      <c r="AA28" s="10" t="inlineStr"/>
+      <c r="AB28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -2272,82 +2652,84 @@
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="8" t="inlineStr"/>
       <c r="P29" s="8" t="inlineStr"/>
-      <c r="Q29" s="13" t="inlineStr">
+      <c r="Q29" s="12" t="inlineStr">
         <is>
           <t>114.00</t>
         </is>
       </c>
-      <c r="R29" s="8" t="inlineStr"/>
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>144.00</t>
+        </is>
+      </c>
       <c r="S29" s="8" t="inlineStr"/>
       <c r="T29" s="8" t="inlineStr"/>
-      <c r="U29" s="8" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr"/>
+      <c r="V29" s="8" t="inlineStr"/>
+      <c r="W29" s="8" t="inlineStr">
         <is>
           <t>566.00</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
+      <c r="X29" s="8" t="inlineStr">
         <is>
           <t>565.00</t>
         </is>
       </c>
-      <c r="W29" s="8" t="inlineStr"/>
-      <c r="X29" s="9" t="n">
+      <c r="Y29" s="8" t="inlineStr"/>
+      <c r="Z29" s="9" t="n">
         <v>483.5</v>
       </c>
-      <c r="Y29" s="9" t="n">
+      <c r="AA29" s="9" t="n">
         <v>72.75</v>
       </c>
-      <c r="Z29" s="11" t="n">
+      <c r="AB29" s="11" t="n">
         <v>-0.09845716605765327</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>BattleZone
-Random: 2360.0
-Human: 37187.5</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 13540</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr"/>
-      <c r="O30" s="4" t="inlineStr"/>
-      <c r="P30" s="4" t="inlineStr"/>
-      <c r="Q30" s="4" t="inlineStr"/>
-      <c r="R30" s="4" t="inlineStr"/>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="4" t="inlineStr"/>
-      <c r="X30" s="5" t="inlineStr"/>
-      <c r="Y30" s="6" t="n">
-        <v>-2710</v>
-      </c>
-      <c r="Z30" s="7" t="n">
-        <v>-0.07781207379226186</v>
-      </c>
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
+      <c r="J30" s="8" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr"/>
+      <c r="L30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
+      <c r="N30" s="8" t="inlineStr"/>
+      <c r="O30" s="8" t="inlineStr"/>
+      <c r="P30" s="8" t="inlineStr"/>
+      <c r="Q30" s="12" t="inlineStr"/>
+      <c r="R30" s="12" t="inlineStr"/>
+      <c r="S30" s="8" t="inlineStr"/>
+      <c r="T30" s="8" t="inlineStr"/>
+      <c r="U30" s="8" t="inlineStr"/>
+      <c r="V30" s="8" t="inlineStr"/>
+      <c r="W30" s="8" t="inlineStr"/>
+      <c r="X30" s="8" t="inlineStr">
+        <is>
+          <t>652.50</t>
+        </is>
+      </c>
+      <c r="Y30" s="8" t="inlineStr"/>
+      <c r="Z30" s="9" t="inlineStr"/>
+      <c r="AA30" s="10" t="inlineStr"/>
+      <c r="AB30" s="11" t="inlineStr"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr"/>
@@ -2358,106 +2740,78 @@
       <c r="H31" s="8" t="inlineStr"/>
       <c r="I31" s="8" t="inlineStr"/>
       <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>5300.00</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>15900.00</t>
-        </is>
-      </c>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr"/>
       <c r="M31" s="8" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>9650.00</t>
-        </is>
-      </c>
-      <c r="O31" s="8" t="inlineStr">
-        <is>
-          <t>15100.00, 16150.00, 14200.00, 14800.00</t>
-        </is>
-      </c>
-      <c r="P31" s="13" t="inlineStr">
-        <is>
-          <t>9300.00, 8850.00, 8250.00, 9250.00</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t>8200.00, 8400.00, 8550.00, 7950.00</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
+      <c r="P31" s="8" t="inlineStr"/>
+      <c r="Q31" s="12" t="inlineStr"/>
+      <c r="R31" s="12" t="inlineStr"/>
       <c r="S31" s="8" t="inlineStr"/>
       <c r="T31" s="8" t="inlineStr"/>
       <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr"/>
-      <c r="X31" s="9" t="n">
-        <v>10830</v>
-      </c>
-      <c r="Y31" s="10" t="inlineStr"/>
-      <c r="Z31" s="11" t="inlineStr"/>
+      <c r="X31" s="8" t="inlineStr">
+        <is>
+          <t>381.50</t>
+        </is>
+      </c>
+      <c r="Y31" s="8" t="inlineStr"/>
+      <c r="Z31" s="9" t="inlineStr"/>
+      <c r="AA31" s="10" t="inlineStr"/>
+      <c r="AB31" s="11" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr"/>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="8" t="inlineStr"/>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>5550.00</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>13900.00</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>10950.00</t>
-        </is>
-      </c>
-      <c r="P32" s="13" t="inlineStr">
-        <is>
-          <t>5900.00</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t>7450.00</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr"/>
-      <c r="S32" s="8" t="inlineStr"/>
-      <c r="T32" s="8" t="inlineStr"/>
-      <c r="U32" s="8" t="inlineStr"/>
-      <c r="V32" s="8" t="inlineStr"/>
-      <c r="W32" s="8" t="inlineStr"/>
-      <c r="X32" s="9" t="inlineStr"/>
-      <c r="Y32" s="10" t="inlineStr"/>
-      <c r="Z32" s="11" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>BattleZone
+Random: 2360.0
+Human: 37187.5</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 13540</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr"/>
+      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="inlineStr"/>
+      <c r="S32" s="4" t="inlineStr"/>
+      <c r="T32" s="4" t="inlineStr"/>
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="inlineStr"/>
+      <c r="X32" s="4" t="inlineStr"/>
+      <c r="Y32" s="4" t="inlineStr"/>
+      <c r="Z32" s="5" t="inlineStr"/>
+      <c r="AA32" s="6" t="n">
+        <v>-2710</v>
+      </c>
+      <c r="AB32" s="7" t="n">
+        <v>-0.07781207379226186</v>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr"/>
@@ -2470,33 +2824,33 @@
       <c r="J33" s="8" t="inlineStr"/>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>5300.00</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>14250.00</t>
+          <t>15900.00</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr"/>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>13050.00</t>
+          <t>9650.00</t>
         </is>
       </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
-          <t>14350.00</t>
-        </is>
-      </c>
-      <c r="P33" s="13" t="inlineStr">
-        <is>
-          <t>5650.00</t>
+          <t>15100.00, 16150.00, 14200.00, 14800.00</t>
+        </is>
+      </c>
+      <c r="P33" s="12" t="inlineStr">
+        <is>
+          <t>9300.00, 8850.00, 8250.00, 9250.00</t>
         </is>
       </c>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>10850.00</t>
+          <t>8200.00, 8400.00, 8550.00, 7950.00</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr"/>
@@ -2505,21 +2859,19 @@
       <c r="U33" s="8" t="inlineStr"/>
       <c r="V33" s="8" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr"/>
-      <c r="X33" s="9" t="n">
-        <v>11600</v>
-      </c>
-      <c r="Y33" s="9" t="n">
-        <v>770</v>
-      </c>
-      <c r="Z33" s="11" t="n">
-        <v>0.02210896561625153</v>
-      </c>
+      <c r="X33" s="8" t="inlineStr"/>
+      <c r="Y33" s="8" t="inlineStr"/>
+      <c r="Z33" s="9" t="n">
+        <v>10830</v>
+      </c>
+      <c r="AA33" s="10" t="inlineStr"/>
+      <c r="AB33" s="11" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr"/>
@@ -2530,32 +2882,50 @@
       <c r="H34" s="8" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr"/>
       <c r="J34" s="8" t="inlineStr"/>
-      <c r="K34" s="8" t="inlineStr"/>
-      <c r="L34" s="8" t="inlineStr"/>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>5550.00</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>13900.00</t>
+        </is>
+      </c>
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
       <c r="O34" s="8" t="inlineStr">
         <is>
-          <t>18350.00</t>
-        </is>
-      </c>
-      <c r="P34" s="13" t="inlineStr"/>
-      <c r="Q34" s="8" t="inlineStr"/>
+          <t>10950.00</t>
+        </is>
+      </c>
+      <c r="P34" s="12" t="inlineStr">
+        <is>
+          <t>5900.00</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>7450.00</t>
+        </is>
+      </c>
       <c r="R34" s="8" t="inlineStr"/>
       <c r="S34" s="8" t="inlineStr"/>
       <c r="T34" s="8" t="inlineStr"/>
       <c r="U34" s="8" t="inlineStr"/>
       <c r="V34" s="8" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr"/>
-      <c r="X34" s="9" t="inlineStr"/>
-      <c r="Y34" s="10" t="inlineStr"/>
-      <c r="Z34" s="11" t="inlineStr"/>
+      <c r="X34" s="8" t="inlineStr"/>
+      <c r="Y34" s="8" t="inlineStr"/>
+      <c r="Z34" s="9" t="inlineStr"/>
+      <c r="AA34" s="10" t="inlineStr"/>
+      <c r="AB34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr"/>
@@ -2566,117 +2936,125 @@
       <c r="H35" s="8" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
-      <c r="L35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>5500.00</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>14250.00</t>
+        </is>
+      </c>
       <c r="M35" s="8" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>13050.00</t>
+        </is>
+      </c>
       <c r="O35" s="8" t="inlineStr">
         <is>
-          <t>19850.00</t>
-        </is>
-      </c>
-      <c r="P35" s="13" t="inlineStr"/>
-      <c r="Q35" s="8" t="inlineStr"/>
+          <t>14350.00</t>
+        </is>
+      </c>
+      <c r="P35" s="12" t="inlineStr">
+        <is>
+          <t>5650.00</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>10850.00</t>
+        </is>
+      </c>
       <c r="R35" s="8" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr"/>
       <c r="T35" s="8" t="inlineStr"/>
       <c r="U35" s="8" t="inlineStr"/>
       <c r="V35" s="8" t="inlineStr"/>
       <c r="W35" s="8" t="inlineStr"/>
-      <c r="X35" s="9" t="inlineStr"/>
-      <c r="Y35" s="10" t="inlineStr"/>
-      <c r="Z35" s="11" t="inlineStr"/>
+      <c r="X35" s="8" t="inlineStr"/>
+      <c r="Y35" s="8" t="inlineStr"/>
+      <c r="Z35" s="9" t="n">
+        <v>11600</v>
+      </c>
+      <c r="AA35" s="9" t="n">
+        <v>770</v>
+      </c>
+      <c r="AB35" s="11" t="n">
+        <v>0.02210896561625153</v>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Boxing
-Random: 0.1
-Human: 12.1</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 80</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr"/>
-      <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr"/>
-      <c r="O36" s="4" t="inlineStr"/>
-      <c r="P36" s="4" t="inlineStr"/>
-      <c r="Q36" s="4" t="inlineStr"/>
-      <c r="R36" s="4" t="inlineStr"/>
-      <c r="S36" s="4" t="inlineStr"/>
-      <c r="T36" s="4" t="inlineStr"/>
-      <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="inlineStr"/>
-      <c r="W36" s="4" t="inlineStr"/>
-      <c r="X36" s="5" t="inlineStr"/>
-      <c r="Y36" s="6" t="n">
-        <v>-1.350000000000009</v>
-      </c>
-      <c r="Z36" s="7" t="n">
-        <v>-0.1125000000000007</v>
-      </c>
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr"/>
+      <c r="E36" s="8" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr"/>
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr"/>
+      <c r="J36" s="8" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr"/>
+      <c r="L36" s="8" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
+      <c r="N36" s="8" t="inlineStr"/>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>18350.00</t>
+        </is>
+      </c>
+      <c r="P36" s="12" t="inlineStr"/>
+      <c r="Q36" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr"/>
+      <c r="S36" s="8" t="inlineStr"/>
+      <c r="T36" s="8" t="inlineStr"/>
+      <c r="U36" s="8" t="inlineStr"/>
+      <c r="V36" s="8" t="inlineStr"/>
+      <c r="W36" s="8" t="inlineStr"/>
+      <c r="X36" s="8" t="inlineStr"/>
+      <c r="Y36" s="8" t="inlineStr"/>
+      <c r="Z36" s="9" t="inlineStr"/>
+      <c r="AA36" s="10" t="inlineStr"/>
+      <c r="AB36" s="11" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr"/>
       <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>68.60</t>
-        </is>
-      </c>
+      <c r="E37" s="8" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="8" t="inlineStr"/>
       <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>73.80</t>
-        </is>
-      </c>
+      <c r="I37" s="8" t="inlineStr"/>
       <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>81.00</t>
-        </is>
-      </c>
+      <c r="K37" s="8" t="inlineStr"/>
       <c r="L37" s="8" t="inlineStr"/>
       <c r="M37" s="8" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr">
-        <is>
-          <t>88.60</t>
-        </is>
-      </c>
-      <c r="O37" s="13" t="inlineStr">
-        <is>
-          <t>70.40</t>
-        </is>
-      </c>
-      <c r="P37" s="8" t="inlineStr">
-        <is>
-          <t>77.80</t>
-        </is>
-      </c>
-      <c r="Q37" s="8" t="inlineStr">
-        <is>
-          <t>87.20</t>
+      <c r="N37" s="8" t="inlineStr"/>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>19850.00</t>
+        </is>
+      </c>
+      <c r="P37" s="12" t="inlineStr"/>
+      <c r="Q37" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr"/>
@@ -2685,88 +3063,104 @@
       <c r="U37" s="8" t="inlineStr"/>
       <c r="V37" s="8" t="inlineStr"/>
       <c r="W37" s="8" t="inlineStr"/>
-      <c r="X37" s="9" t="n">
-        <v>78.64999999999999</v>
-      </c>
-      <c r="Y37" s="10" t="inlineStr"/>
-      <c r="Z37" s="11" t="inlineStr"/>
+      <c r="X37" s="8" t="inlineStr"/>
+      <c r="Y37" s="8" t="inlineStr"/>
+      <c r="Z37" s="9" t="inlineStr"/>
+      <c r="AA37" s="10" t="inlineStr"/>
+      <c r="AB37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr"/>
-      <c r="D38" s="8" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>74.85</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr"/>
-      <c r="G38" s="8" t="inlineStr"/>
-      <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="8" t="inlineStr"/>
-      <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr"/>
-      <c r="M38" s="8" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
-      <c r="O38" s="13" t="inlineStr"/>
-      <c r="P38" s="8" t="inlineStr"/>
-      <c r="Q38" s="8" t="inlineStr"/>
-      <c r="R38" s="8" t="inlineStr"/>
-      <c r="S38" s="8" t="inlineStr"/>
-      <c r="T38" s="8" t="inlineStr"/>
-      <c r="U38" s="8" t="inlineStr"/>
-      <c r="V38" s="8" t="inlineStr"/>
-      <c r="W38" s="8" t="inlineStr"/>
-      <c r="X38" s="9" t="inlineStr"/>
-      <c r="Y38" s="10" t="inlineStr"/>
-      <c r="Z38" s="11" t="inlineStr"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Boxing
+Random: 0.1
+Human: 12.1</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 80</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr"/>
+      <c r="Q38" s="4" t="inlineStr"/>
+      <c r="R38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="inlineStr"/>
+      <c r="T38" s="4" t="inlineStr"/>
+      <c r="U38" s="4" t="inlineStr"/>
+      <c r="V38" s="4" t="inlineStr"/>
+      <c r="W38" s="4" t="inlineStr"/>
+      <c r="X38" s="4" t="inlineStr"/>
+      <c r="Y38" s="4" t="inlineStr"/>
+      <c r="Z38" s="5" t="inlineStr"/>
+      <c r="AA38" s="6" t="n">
+        <v>-1.350000000000009</v>
+      </c>
+      <c r="AB38" s="7" t="n">
+        <v>-0.1125000000000007</v>
+      </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr"/>
       <c r="D39" s="8" t="inlineStr"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>68.60</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr"/>
       <c r="G39" s="8" t="inlineStr"/>
       <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>73.80</t>
+        </is>
+      </c>
       <c r="J39" s="8" t="inlineStr"/>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>78.50</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr"/>
       <c r="M39" s="8" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
-      <c r="O39" s="13" t="inlineStr">
-        <is>
-          <t>51.15</t>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>88.60</t>
+        </is>
+      </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>70.40</t>
         </is>
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>77.80</t>
         </is>
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>87.90</t>
+          <t>87.20</t>
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr"/>
@@ -2775,145 +3169,141 @@
       <c r="U39" s="8" t="inlineStr"/>
       <c r="V39" s="8" t="inlineStr"/>
       <c r="W39" s="8" t="inlineStr"/>
-      <c r="X39" s="9" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="Y39" s="9" t="n">
-        <v>3.250000000000014</v>
-      </c>
-      <c r="Z39" s="11" t="n">
-        <v>0.2708333333333345</v>
-      </c>
+      <c r="X39" s="8" t="inlineStr"/>
+      <c r="Y39" s="8" t="inlineStr"/>
+      <c r="Z39" s="9" t="n">
+        <v>78.64999999999999</v>
+      </c>
+      <c r="AA39" s="10" t="inlineStr"/>
+      <c r="AB39" s="11" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Breakout
-Random: 1.7
-Human: 30.5</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 16</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr"/>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr"/>
-      <c r="O40" s="4" t="inlineStr"/>
-      <c r="P40" s="4" t="inlineStr"/>
-      <c r="Q40" s="4" t="inlineStr"/>
-      <c r="R40" s="4" t="inlineStr"/>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="4" t="inlineStr"/>
-      <c r="W40" s="4" t="inlineStr"/>
-      <c r="X40" s="5" t="inlineStr"/>
-      <c r="Y40" s="6" t="n">
-        <v>-4.266666666666666</v>
-      </c>
-      <c r="Z40" s="7" t="n">
-        <v>-0.1481481481481481</v>
-      </c>
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr"/>
+      <c r="D40" s="8" t="inlineStr"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>74.85</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr"/>
+      <c r="G40" s="8" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr"/>
+      <c r="J40" s="8" t="inlineStr"/>
+      <c r="K40" s="8" t="inlineStr"/>
+      <c r="L40" s="8" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
+      <c r="N40" s="8" t="inlineStr"/>
+      <c r="O40" s="12" t="inlineStr"/>
+      <c r="P40" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr"/>
+      <c r="R40" s="8" t="inlineStr"/>
+      <c r="S40" s="8" t="inlineStr"/>
+      <c r="T40" s="8" t="inlineStr"/>
+      <c r="U40" s="8" t="inlineStr"/>
+      <c r="V40" s="8" t="inlineStr"/>
+      <c r="W40" s="8" t="inlineStr"/>
+      <c r="X40" s="8" t="inlineStr"/>
+      <c r="Y40" s="8" t="inlineStr"/>
+      <c r="Z40" s="9" t="inlineStr"/>
+      <c r="AA40" s="10" t="inlineStr"/>
+      <c r="AB40" s="11" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="inlineStr"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>11.40</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>9.60</t>
-        </is>
-      </c>
+          <t>76.15</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr"/>
       <c r="G41" s="8" t="inlineStr"/>
       <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
-      </c>
+      <c r="I41" s="8" t="inlineStr"/>
       <c r="J41" s="8" t="inlineStr"/>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>78.50</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr"/>
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
-      <c r="O41" s="8" t="inlineStr"/>
-      <c r="P41" s="8" t="inlineStr"/>
-      <c r="Q41" s="8" t="inlineStr"/>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>51.15</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t>85.05</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t>87.90</t>
+        </is>
+      </c>
       <c r="R41" s="8" t="inlineStr"/>
       <c r="S41" s="8" t="inlineStr"/>
       <c r="T41" s="8" t="inlineStr"/>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
       <c r="W41" s="8" t="inlineStr"/>
-      <c r="X41" s="9" t="n">
-        <v>11.73333333333333</v>
-      </c>
-      <c r="Y41" s="10" t="inlineStr"/>
-      <c r="Z41" s="11" t="inlineStr"/>
+      <c r="X41" s="8" t="inlineStr"/>
+      <c r="Y41" s="8" t="inlineStr"/>
+      <c r="Z41" s="9" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AA41" s="9" t="n">
+        <v>3.250000000000014</v>
+      </c>
+      <c r="AB41" s="11" t="n">
+        <v>0.2708333333333345</v>
+      </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr"/>
       <c r="D42" s="8" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>12.10</t>
-        </is>
-      </c>
+      <c r="E42" s="8" t="inlineStr"/>
       <c r="F42" s="8" t="inlineStr"/>
       <c r="G42" s="8" t="inlineStr"/>
       <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
+      <c r="I42" s="8" t="inlineStr"/>
       <c r="J42" s="8" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
-      </c>
+      <c r="K42" s="8" t="inlineStr"/>
       <c r="L42" s="8" t="inlineStr"/>
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="8" t="inlineStr"/>
-      <c r="O42" s="8" t="inlineStr"/>
-      <c r="P42" s="8" t="inlineStr"/>
+      <c r="O42" s="12" t="inlineStr"/>
+      <c r="P42" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="Q42" s="8" t="inlineStr"/>
       <c r="R42" s="8" t="inlineStr"/>
       <c r="S42" s="8" t="inlineStr"/>
@@ -2921,43 +3311,37 @@
       <c r="U42" s="8" t="inlineStr"/>
       <c r="V42" s="8" t="inlineStr"/>
       <c r="W42" s="8" t="inlineStr"/>
-      <c r="X42" s="9" t="inlineStr"/>
-      <c r="Y42" s="10" t="inlineStr"/>
-      <c r="Z42" s="11" t="inlineStr"/>
+      <c r="X42" s="8" t="inlineStr"/>
+      <c r="Y42" s="8" t="inlineStr"/>
+      <c r="Z42" s="9" t="inlineStr"/>
+      <c r="AA42" s="10" t="inlineStr"/>
+      <c r="AB42" s="11" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr"/>
       <c r="D43" s="8" t="inlineStr"/>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>12.70</t>
-        </is>
-      </c>
+      <c r="E43" s="8" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="8" t="inlineStr"/>
       <c r="H43" s="8" t="inlineStr"/>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
+      <c r="I43" s="8" t="inlineStr"/>
       <c r="J43" s="8" t="inlineStr"/>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>9.30</t>
-        </is>
-      </c>
+      <c r="K43" s="8" t="inlineStr"/>
       <c r="L43" s="8" t="inlineStr"/>
       <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
-      <c r="O43" s="8" t="inlineStr"/>
-      <c r="P43" s="8" t="inlineStr"/>
+      <c r="O43" s="12" t="inlineStr"/>
+      <c r="P43" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="8" t="inlineStr"/>
@@ -2965,27 +3349,23 @@
       <c r="U43" s="8" t="inlineStr"/>
       <c r="V43" s="8" t="inlineStr"/>
       <c r="W43" s="8" t="inlineStr"/>
-      <c r="X43" s="9" t="n">
-        <v>12.36666666666667</v>
-      </c>
-      <c r="Y43" s="9" t="n">
-        <v>0.6333333333333311</v>
-      </c>
-      <c r="Z43" s="11" t="n">
-        <v>0.02199074074074066</v>
-      </c>
+      <c r="X43" s="8" t="inlineStr"/>
+      <c r="Y43" s="8" t="inlineStr"/>
+      <c r="Z43" s="9" t="inlineStr"/>
+      <c r="AA43" s="10" t="inlineStr"/>
+      <c r="AB43" s="11" t="inlineStr"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ChopperCommand
-Random: 811.0
-Human: 7387.8</t>
+          <t>Breakout
+Random: 1.7
+Human: 30.5</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 1888</t>
+          <t>STORM (논문): 16</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -3009,12 +3389,14 @@
       <c r="U44" s="4" t="inlineStr"/>
       <c r="V44" s="4" t="inlineStr"/>
       <c r="W44" s="4" t="inlineStr"/>
-      <c r="X44" s="5" t="inlineStr"/>
-      <c r="Y44" s="6" t="n">
-        <v>-289.6666666666667</v>
-      </c>
-      <c r="Z44" s="7" t="n">
-        <v>-0.04404370920001623</v>
+      <c r="X44" s="4" t="inlineStr"/>
+      <c r="Y44" s="4" t="inlineStr"/>
+      <c r="Z44" s="5" t="inlineStr"/>
+      <c r="AA44" s="6" t="n">
+        <v>-4.266666666666666</v>
+      </c>
+      <c r="AB44" s="7" t="n">
+        <v>-0.1481481481481481</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
@@ -3027,30 +3409,30 @@
       <c r="C45" s="8" t="inlineStr"/>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>1960.00</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>1980.00</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr"/>
       <c r="H45" s="8" t="inlineStr"/>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr"/>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr"/>
@@ -3065,11 +3447,13 @@
       <c r="U45" s="8" t="inlineStr"/>
       <c r="V45" s="8" t="inlineStr"/>
       <c r="W45" s="8" t="inlineStr"/>
-      <c r="X45" s="9" t="n">
-        <v>1598.333333333333</v>
-      </c>
-      <c r="Y45" s="10" t="inlineStr"/>
-      <c r="Z45" s="11" t="inlineStr"/>
+      <c r="X45" s="8" t="inlineStr"/>
+      <c r="Y45" s="8" t="inlineStr"/>
+      <c r="Z45" s="9" t="n">
+        <v>11.73333333333333</v>
+      </c>
+      <c r="AA45" s="10" t="inlineStr"/>
+      <c r="AB45" s="11" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="1" t="n"/>
@@ -3080,17 +3464,25 @@
       </c>
       <c r="C46" s="8" t="inlineStr"/>
       <c r="D46" s="8" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr"/>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>1360.00</t>
-        </is>
-      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>12.10</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr"/>
       <c r="G46" s="8" t="inlineStr"/>
       <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
       <c r="J46" s="8" t="inlineStr"/>
-      <c r="K46" s="8" t="inlineStr"/>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
       <c r="L46" s="8" t="inlineStr"/>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
@@ -3103,9 +3495,11 @@
       <c r="U46" s="8" t="inlineStr"/>
       <c r="V46" s="8" t="inlineStr"/>
       <c r="W46" s="8" t="inlineStr"/>
-      <c r="X46" s="9" t="inlineStr"/>
-      <c r="Y46" s="10" t="inlineStr"/>
-      <c r="Z46" s="11" t="inlineStr"/>
+      <c r="X46" s="8" t="inlineStr"/>
+      <c r="Y46" s="8" t="inlineStr"/>
+      <c r="Z46" s="9" t="inlineStr"/>
+      <c r="AA46" s="10" t="inlineStr"/>
+      <c r="AB46" s="11" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="1" t="n"/>
@@ -3116,23 +3510,23 @@
       </c>
       <c r="C47" s="8" t="inlineStr"/>
       <c r="D47" s="8" t="inlineStr"/>
-      <c r="E47" s="8" t="inlineStr"/>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>970.00</t>
-        </is>
-      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>12.70</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr"/>
       <c r="G47" s="8" t="inlineStr"/>
       <c r="H47" s="8" t="inlineStr"/>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr"/>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>1260.00</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr"/>
@@ -3147,72 +3541,98 @@
       <c r="U47" s="8" t="inlineStr"/>
       <c r="V47" s="8" t="inlineStr"/>
       <c r="W47" s="8" t="inlineStr"/>
-      <c r="X47" s="9" t="n">
-        <v>1225</v>
-      </c>
-      <c r="Y47" s="9" t="n">
-        <v>373.3333333333333</v>
-      </c>
-      <c r="Z47" s="11" t="n">
-        <v>-0.05676519482625794</v>
+      <c r="X47" s="8" t="inlineStr"/>
+      <c r="Y47" s="8" t="inlineStr"/>
+      <c r="Z47" s="9" t="n">
+        <v>12.36666666666667</v>
+      </c>
+      <c r="AA47" s="9" t="n">
+        <v>0.6333333333333311</v>
+      </c>
+      <c r="AB47" s="11" t="n">
+        <v>0.02199074074074066</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr"/>
-      <c r="D48" s="8" t="inlineStr"/>
-      <c r="E48" s="8" t="inlineStr"/>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>1125.00</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr"/>
-      <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="8" t="inlineStr"/>
-      <c r="J48" s="8" t="inlineStr"/>
-      <c r="K48" s="8" t="inlineStr"/>
-      <c r="L48" s="8" t="inlineStr"/>
-      <c r="M48" s="8" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
-      <c r="O48" s="8" t="inlineStr"/>
-      <c r="P48" s="8" t="inlineStr"/>
-      <c r="Q48" s="8" t="inlineStr"/>
-      <c r="R48" s="8" t="inlineStr"/>
-      <c r="S48" s="8" t="inlineStr"/>
-      <c r="T48" s="8" t="inlineStr"/>
-      <c r="U48" s="8" t="inlineStr"/>
-      <c r="V48" s="8" t="inlineStr"/>
-      <c r="W48" s="8" t="inlineStr"/>
-      <c r="X48" s="9" t="inlineStr"/>
-      <c r="Y48" s="10" t="inlineStr"/>
-      <c r="Z48" s="11" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ChopperCommand
+Random: 811.0
+Human: 7387.8</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 1888</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr"/>
+      <c r="Q48" s="4" t="inlineStr"/>
+      <c r="R48" s="4" t="inlineStr"/>
+      <c r="S48" s="4" t="inlineStr"/>
+      <c r="T48" s="4" t="inlineStr"/>
+      <c r="U48" s="4" t="inlineStr"/>
+      <c r="V48" s="4" t="inlineStr"/>
+      <c r="W48" s="4" t="inlineStr"/>
+      <c r="X48" s="4" t="inlineStr"/>
+      <c r="Y48" s="4" t="inlineStr"/>
+      <c r="Z48" s="5" t="inlineStr"/>
+      <c r="AA48" s="6" t="n">
+        <v>-199.25</v>
+      </c>
+      <c r="AB48" s="7" t="n">
+        <v>-0.03029588857803187</v>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr"/>
-      <c r="D49" s="8" t="inlineStr"/>
-      <c r="E49" s="8" t="inlineStr"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>1530.00</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>1960.00</t>
+        </is>
+      </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>1305.00</t>
+          <t>1980.00</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr"/>
       <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>1345.00</t>
+        </is>
+      </c>
       <c r="J49" s="8" t="inlineStr"/>
-      <c r="K49" s="8" t="inlineStr"/>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>1470.00</t>
+        </is>
+      </c>
       <c r="L49" s="8" t="inlineStr"/>
       <c r="M49" s="8" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
@@ -3225,86 +3645,86 @@
       <c r="U49" s="8" t="inlineStr"/>
       <c r="V49" s="8" t="inlineStr"/>
       <c r="W49" s="8" t="inlineStr"/>
-      <c r="X49" s="9" t="inlineStr"/>
-      <c r="Y49" s="10" t="inlineStr"/>
-      <c r="Z49" s="11" t="inlineStr"/>
+      <c r="X49" s="8" t="inlineStr"/>
+      <c r="Y49" s="8" t="inlineStr"/>
+      <c r="Z49" s="9" t="n">
+        <v>1688.75</v>
+      </c>
+      <c r="AA49" s="10" t="inlineStr"/>
+      <c r="AB49" s="11" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CrazyClimber
-Random: 10780.5
-Human: 35829.4</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 66776</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr"/>
-      <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr"/>
-      <c r="O50" s="4" t="inlineStr"/>
-      <c r="P50" s="4" t="inlineStr"/>
-      <c r="Q50" s="4" t="inlineStr"/>
-      <c r="R50" s="4" t="inlineStr"/>
-      <c r="S50" s="4" t="inlineStr"/>
-      <c r="T50" s="4" t="inlineStr"/>
-      <c r="U50" s="4" t="inlineStr"/>
-      <c r="V50" s="4" t="inlineStr"/>
-      <c r="W50" s="4" t="inlineStr"/>
-      <c r="X50" s="5" t="inlineStr"/>
-      <c r="Y50" s="6" t="n">
-        <v>-9204.333333333336</v>
-      </c>
-      <c r="Z50" s="7" t="n">
-        <v>-0.3674545921510859</v>
-      </c>
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr"/>
+      <c r="D50" s="8" t="inlineStr"/>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>2255.00</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>1360.00</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr"/>
+      <c r="J50" s="8" t="inlineStr"/>
+      <c r="K50" s="8" t="inlineStr"/>
+      <c r="L50" s="8" t="inlineStr"/>
+      <c r="M50" s="8" t="inlineStr"/>
+      <c r="N50" s="8" t="inlineStr"/>
+      <c r="O50" s="8" t="inlineStr"/>
+      <c r="P50" s="8" t="inlineStr"/>
+      <c r="Q50" s="8" t="inlineStr"/>
+      <c r="R50" s="8" t="inlineStr"/>
+      <c r="S50" s="8" t="inlineStr"/>
+      <c r="T50" s="8" t="inlineStr"/>
+      <c r="U50" s="8" t="inlineStr"/>
+      <c r="V50" s="8" t="inlineStr"/>
+      <c r="W50" s="8" t="inlineStr"/>
+      <c r="X50" s="8" t="inlineStr"/>
+      <c r="Y50" s="8" t="inlineStr"/>
+      <c r="Z50" s="9" t="inlineStr"/>
+      <c r="AA50" s="10" t="inlineStr"/>
+      <c r="AB50" s="11" t="inlineStr"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>63125.00</t>
-        </is>
-      </c>
+      <c r="D51" s="8" t="inlineStr"/>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>46620.00</t>
+          <t>2025.00</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>49810.00</t>
+          <t>970.00</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr"/>
       <c r="H51" s="8" t="inlineStr"/>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>66125.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr"/>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>59970.00</t>
+          <t>1260.00</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr"/>
@@ -3319,32 +3739,42 @@
       <c r="U51" s="8" t="inlineStr"/>
       <c r="V51" s="8" t="inlineStr"/>
       <c r="W51" s="8" t="inlineStr"/>
-      <c r="X51" s="9" t="n">
-        <v>57571.66666666666</v>
-      </c>
-      <c r="Y51" s="10" t="inlineStr"/>
-      <c r="Z51" s="11" t="inlineStr"/>
+      <c r="X51" s="8" t="inlineStr"/>
+      <c r="Y51" s="8" t="inlineStr"/>
+      <c r="Z51" s="9" t="n">
+        <v>1425</v>
+      </c>
+      <c r="AA51" s="9" t="n">
+        <v>263.75</v>
+      </c>
+      <c r="AB51" s="11" t="n">
+        <v>-0.04010308964846126</v>
+      </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr"/>
       <c r="D52" s="8" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr"/>
-      <c r="F52" s="8" t="inlineStr"/>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>2120.00</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>1125.00</t>
+        </is>
+      </c>
       <c r="G52" s="8" t="inlineStr"/>
       <c r="H52" s="8" t="inlineStr"/>
       <c r="I52" s="8" t="inlineStr"/>
       <c r="J52" s="8" t="inlineStr"/>
-      <c r="K52" s="8" t="inlineStr">
-        <is>
-          <t>69230.00</t>
-        </is>
-      </c>
+      <c r="K52" s="8" t="inlineStr"/>
       <c r="L52" s="8" t="inlineStr"/>
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="8" t="inlineStr"/>
@@ -3357,38 +3787,36 @@
       <c r="U52" s="8" t="inlineStr"/>
       <c r="V52" s="8" t="inlineStr"/>
       <c r="W52" s="8" t="inlineStr"/>
-      <c r="X52" s="9" t="inlineStr"/>
-      <c r="Y52" s="10" t="inlineStr"/>
-      <c r="Z52" s="11" t="inlineStr"/>
+      <c r="X52" s="8" t="inlineStr"/>
+      <c r="Y52" s="8" t="inlineStr"/>
+      <c r="Z52" s="9" t="inlineStr"/>
+      <c r="AA52" s="10" t="inlineStr"/>
+      <c r="AB52" s="11" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr"/>
       <c r="D53" s="8" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>56795.00</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr"/>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>1305.00</t>
+        </is>
+      </c>
       <c r="G53" s="8" t="inlineStr"/>
       <c r="H53" s="8" t="inlineStr"/>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>53655.00</t>
-        </is>
-      </c>
+      <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr"/>
-      <c r="K53" s="8" t="inlineStr">
-        <is>
-          <t>63275.00</t>
-        </is>
-      </c>
+      <c r="K53" s="8" t="inlineStr"/>
       <c r="L53" s="8" t="inlineStr"/>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
@@ -3401,27 +3829,23 @@
       <c r="U53" s="8" t="inlineStr"/>
       <c r="V53" s="8" t="inlineStr"/>
       <c r="W53" s="8" t="inlineStr"/>
-      <c r="X53" s="9" t="n">
-        <v>57908.33333333334</v>
-      </c>
-      <c r="Y53" s="9" t="n">
-        <v>336.6666666666715</v>
-      </c>
-      <c r="Z53" s="11" t="n">
-        <v>0.01344037728869018</v>
-      </c>
+      <c r="X53" s="8" t="inlineStr"/>
+      <c r="Y53" s="8" t="inlineStr"/>
+      <c r="Z53" s="9" t="inlineStr"/>
+      <c r="AA53" s="10" t="inlineStr"/>
+      <c r="AB53" s="11" t="inlineStr"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DemonAttack
-Random: 152.1
-Human: 1971.0</t>
+          <t>CrazyClimber
+Random: 10780.5
+Human: 35829.4</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 165</t>
+          <t>STORM (논문): 66776</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -3445,12 +3869,14 @@
       <c r="U54" s="4" t="inlineStr"/>
       <c r="V54" s="4" t="inlineStr"/>
       <c r="W54" s="4" t="inlineStr"/>
-      <c r="X54" s="5" t="inlineStr"/>
-      <c r="Y54" s="6" t="n">
-        <v>30.58333333333334</v>
-      </c>
-      <c r="Z54" s="7" t="n">
-        <v>0.01681419172760094</v>
+      <c r="X54" s="4" t="inlineStr"/>
+      <c r="Y54" s="4" t="inlineStr"/>
+      <c r="Z54" s="5" t="inlineStr"/>
+      <c r="AA54" s="6" t="n">
+        <v>-9204.333333333336</v>
+      </c>
+      <c r="AB54" s="7" t="n">
+        <v>-0.3674545921510859</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
@@ -3461,37 +3887,37 @@
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>63125.00</t>
+        </is>
+      </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>214.25</t>
+          <t>46620.00</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>139.75</t>
+          <t>49810.00</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr"/>
       <c r="H55" s="8" t="inlineStr"/>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>200.75</t>
+          <t>66125.00</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr"/>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>171.75</t>
+          <t>59970.00</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr"/>
       <c r="M55" s="8" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr">
-        <is>
-          <t>188.00</t>
-        </is>
-      </c>
+      <c r="N55" s="8" t="inlineStr"/>
       <c r="O55" s="8" t="inlineStr"/>
       <c r="P55" s="8" t="inlineStr"/>
       <c r="Q55" s="8" t="inlineStr"/>
@@ -3501,11 +3927,13 @@
       <c r="U55" s="8" t="inlineStr"/>
       <c r="V55" s="8" t="inlineStr"/>
       <c r="W55" s="8" t="inlineStr"/>
-      <c r="X55" s="9" t="n">
-        <v>195.5833333333333</v>
-      </c>
-      <c r="Y55" s="10" t="inlineStr"/>
-      <c r="Z55" s="11" t="inlineStr"/>
+      <c r="X55" s="8" t="inlineStr"/>
+      <c r="Y55" s="8" t="inlineStr"/>
+      <c r="Z55" s="9" t="n">
+        <v>57571.66666666666</v>
+      </c>
+      <c r="AA55" s="10" t="inlineStr"/>
+      <c r="AB55" s="11" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="1" t="n"/>
@@ -3520,13 +3948,13 @@
       <c r="F56" s="8" t="inlineStr"/>
       <c r="G56" s="8" t="inlineStr"/>
       <c r="H56" s="8" t="inlineStr"/>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>138.00</t>
-        </is>
-      </c>
+      <c r="I56" s="8" t="inlineStr"/>
       <c r="J56" s="8" t="inlineStr"/>
-      <c r="K56" s="8" t="inlineStr"/>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>69230.00</t>
+        </is>
+      </c>
       <c r="L56" s="8" t="inlineStr"/>
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="8" t="inlineStr"/>
@@ -3539,9 +3967,11 @@
       <c r="U56" s="8" t="inlineStr"/>
       <c r="V56" s="8" t="inlineStr"/>
       <c r="W56" s="8" t="inlineStr"/>
-      <c r="X56" s="9" t="inlineStr"/>
-      <c r="Y56" s="10" t="inlineStr"/>
-      <c r="Z56" s="11" t="inlineStr"/>
+      <c r="X56" s="8" t="inlineStr"/>
+      <c r="Y56" s="8" t="inlineStr"/>
+      <c r="Z56" s="9" t="inlineStr"/>
+      <c r="AA56" s="10" t="inlineStr"/>
+      <c r="AB56" s="11" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="1" t="n"/>
@@ -3554,7 +3984,7 @@
       <c r="D57" s="8" t="inlineStr"/>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>150.75</t>
+          <t>56795.00</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr"/>
@@ -3562,13 +3992,13 @@
       <c r="H57" s="8" t="inlineStr"/>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>128.25</t>
+          <t>53655.00</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr"/>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>192.25</t>
+          <t>63275.00</t>
         </is>
       </c>
       <c r="L57" s="8" t="inlineStr"/>
@@ -3583,75 +4013,101 @@
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr"/>
       <c r="W57" s="8" t="inlineStr"/>
-      <c r="X57" s="9" t="n">
-        <v>157.0833333333333</v>
-      </c>
-      <c r="Y57" s="9" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="Z57" s="11" t="n">
-        <v>-0.02116663917752488</v>
+      <c r="X57" s="8" t="inlineStr"/>
+      <c r="Y57" s="8" t="inlineStr"/>
+      <c r="Z57" s="9" t="n">
+        <v>57908.33333333334</v>
+      </c>
+      <c r="AA57" s="9" t="n">
+        <v>336.6666666666715</v>
+      </c>
+      <c r="AB57" s="11" t="n">
+        <v>0.01344037728869018</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr"/>
-      <c r="D58" s="8" t="inlineStr"/>
-      <c r="E58" s="8" t="inlineStr"/>
-      <c r="F58" s="8" t="inlineStr"/>
-      <c r="G58" s="8" t="inlineStr"/>
-      <c r="H58" s="8" t="inlineStr"/>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>137.50</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr"/>
-      <c r="K58" s="8" t="inlineStr"/>
-      <c r="L58" s="8" t="inlineStr"/>
-      <c r="M58" s="8" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr"/>
-      <c r="O58" s="8" t="inlineStr"/>
-      <c r="P58" s="8" t="inlineStr"/>
-      <c r="Q58" s="8" t="inlineStr"/>
-      <c r="R58" s="8" t="inlineStr"/>
-      <c r="S58" s="8" t="inlineStr"/>
-      <c r="T58" s="8" t="inlineStr"/>
-      <c r="U58" s="8" t="inlineStr"/>
-      <c r="V58" s="8" t="inlineStr"/>
-      <c r="W58" s="8" t="inlineStr"/>
-      <c r="X58" s="9" t="inlineStr"/>
-      <c r="Y58" s="10" t="inlineStr"/>
-      <c r="Z58" s="11" t="inlineStr"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>DemonAttack
+Random: 152.1
+Human: 1971.0</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 165</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr"/>
+      <c r="Q58" s="4" t="inlineStr"/>
+      <c r="R58" s="4" t="inlineStr"/>
+      <c r="S58" s="4" t="inlineStr"/>
+      <c r="T58" s="4" t="inlineStr"/>
+      <c r="U58" s="4" t="inlineStr"/>
+      <c r="V58" s="4" t="inlineStr"/>
+      <c r="W58" s="4" t="inlineStr"/>
+      <c r="X58" s="4" t="inlineStr"/>
+      <c r="Y58" s="4" t="inlineStr"/>
+      <c r="Z58" s="5" t="inlineStr"/>
+      <c r="AA58" s="6" t="n">
+        <v>30.58333333333334</v>
+      </c>
+      <c r="AB58" s="7" t="n">
+        <v>0.01681419172760094</v>
+      </c>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr"/>
       <c r="D59" s="8" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr"/>
-      <c r="F59" s="8" t="inlineStr"/>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>214.25</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>139.75</t>
+        </is>
+      </c>
       <c r="G59" s="8" t="inlineStr"/>
       <c r="H59" s="8" t="inlineStr"/>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>148.50</t>
+          <t>200.75</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr"/>
-      <c r="K59" s="8" t="inlineStr"/>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>171.75</t>
+        </is>
+      </c>
       <c r="L59" s="8" t="inlineStr"/>
       <c r="M59" s="8" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t>188.00</t>
+        </is>
+      </c>
       <c r="O59" s="8" t="inlineStr"/>
       <c r="P59" s="8" t="inlineStr"/>
       <c r="Q59" s="8" t="inlineStr"/>
@@ -3661,107 +4117,109 @@
       <c r="U59" s="8" t="inlineStr"/>
       <c r="V59" s="8" t="inlineStr"/>
       <c r="W59" s="8" t="inlineStr"/>
-      <c r="X59" s="9" t="inlineStr"/>
-      <c r="Y59" s="10" t="inlineStr"/>
-      <c r="Z59" s="11" t="inlineStr"/>
+      <c r="X59" s="8" t="inlineStr"/>
+      <c r="Y59" s="8" t="inlineStr"/>
+      <c r="Z59" s="9" t="n">
+        <v>195.5833333333333</v>
+      </c>
+      <c r="AA59" s="10" t="inlineStr"/>
+      <c r="AB59" s="11" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Freeway
-Random: 0.0
-Human: 29.6</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 34</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr"/>
-      <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr"/>
-      <c r="O60" s="4" t="inlineStr"/>
-      <c r="P60" s="4" t="inlineStr"/>
-      <c r="Q60" s="4" t="inlineStr"/>
-      <c r="R60" s="4" t="inlineStr"/>
-      <c r="S60" s="4" t="inlineStr"/>
-      <c r="T60" s="4" t="inlineStr"/>
-      <c r="U60" s="4" t="inlineStr"/>
-      <c r="V60" s="4" t="inlineStr"/>
-      <c r="W60" s="4" t="inlineStr"/>
-      <c r="X60" s="5" t="inlineStr"/>
-      <c r="Y60" s="6" t="n">
-        <v>-0.7000000000000028</v>
-      </c>
-      <c r="Z60" s="7" t="n">
-        <v>-0.02364864864864874</v>
-      </c>
+      <c r="A60" s="1" t="n"/>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr"/>
+      <c r="D60" s="8" t="inlineStr"/>
+      <c r="E60" s="8" t="inlineStr"/>
+      <c r="F60" s="8" t="inlineStr"/>
+      <c r="G60" s="8" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>138.00</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr"/>
+      <c r="K60" s="8" t="inlineStr"/>
+      <c r="L60" s="8" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr"/>
+      <c r="N60" s="8" t="inlineStr"/>
+      <c r="O60" s="8" t="inlineStr"/>
+      <c r="P60" s="8" t="inlineStr"/>
+      <c r="Q60" s="8" t="inlineStr"/>
+      <c r="R60" s="8" t="inlineStr"/>
+      <c r="S60" s="8" t="inlineStr"/>
+      <c r="T60" s="8" t="inlineStr"/>
+      <c r="U60" s="8" t="inlineStr"/>
+      <c r="V60" s="8" t="inlineStr"/>
+      <c r="W60" s="8" t="inlineStr"/>
+      <c r="X60" s="8" t="inlineStr"/>
+      <c r="Y60" s="8" t="inlineStr"/>
+      <c r="Z60" s="9" t="inlineStr"/>
+      <c r="AA60" s="10" t="inlineStr"/>
+      <c r="AB60" s="11" t="inlineStr"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr"/>
       <c r="D61" s="8" t="inlineStr"/>
-      <c r="E61" s="8" t="inlineStr"/>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>150.75</t>
+        </is>
+      </c>
       <c r="F61" s="8" t="inlineStr"/>
       <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="8" t="inlineStr"/>
-      <c r="I61" s="8" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>128.25</t>
+        </is>
+      </c>
       <c r="J61" s="8" t="inlineStr"/>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>192.25</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr"/>
       <c r="M61" s="8" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="8" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
-      </c>
-      <c r="P61" s="8" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="Q61" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="O61" s="8" t="inlineStr"/>
+      <c r="P61" s="8" t="inlineStr"/>
+      <c r="Q61" s="8" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr"/>
       <c r="T61" s="8" t="inlineStr"/>
       <c r="U61" s="8" t="inlineStr"/>
       <c r="V61" s="8" t="inlineStr"/>
       <c r="W61" s="8" t="inlineStr"/>
-      <c r="X61" s="9" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Y61" s="10" t="inlineStr"/>
-      <c r="Z61" s="11" t="inlineStr"/>
+      <c r="X61" s="8" t="inlineStr"/>
+      <c r="Y61" s="8" t="inlineStr"/>
+      <c r="Z61" s="9" t="n">
+        <v>157.0833333333333</v>
+      </c>
+      <c r="AA61" s="9" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AB61" s="11" t="n">
+        <v>-0.02116663917752488</v>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr"/>
@@ -3770,240 +4228,190 @@
       <c r="F62" s="8" t="inlineStr"/>
       <c r="G62" s="8" t="inlineStr"/>
       <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>137.50</t>
+        </is>
+      </c>
       <c r="J62" s="8" t="inlineStr"/>
       <c r="K62" s="8" t="inlineStr"/>
       <c r="L62" s="8" t="inlineStr"/>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
-      <c r="O62" s="8" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="P62" s="8" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="Q62" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="O62" s="8" t="inlineStr"/>
+      <c r="P62" s="8" t="inlineStr"/>
+      <c r="Q62" s="8" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr"/>
       <c r="T62" s="8" t="inlineStr"/>
       <c r="U62" s="8" t="inlineStr"/>
       <c r="V62" s="8" t="inlineStr"/>
       <c r="W62" s="8" t="inlineStr"/>
-      <c r="X62" s="9" t="n">
-        <v>33.15</v>
-      </c>
-      <c r="Y62" s="9" t="n">
-        <v>0.1499999999999986</v>
-      </c>
-      <c r="Z62" s="11" t="n">
-        <v>-0.005067567567567519</v>
-      </c>
+      <c r="X62" s="8" t="inlineStr"/>
+      <c r="Y62" s="8" t="inlineStr"/>
+      <c r="Z62" s="9" t="inlineStr"/>
+      <c r="AA62" s="10" t="inlineStr"/>
+      <c r="AB62" s="11" t="inlineStr"/>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Frostbite
-Random: 65.2
-Human: 4334.7</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 1316</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr"/>
-      <c r="D63" s="4" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="4" t="inlineStr"/>
-      <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr"/>
-      <c r="M63" s="4" t="inlineStr"/>
-      <c r="N63" s="4" t="inlineStr"/>
-      <c r="O63" s="4" t="inlineStr"/>
-      <c r="P63" s="4" t="inlineStr"/>
-      <c r="Q63" s="4" t="inlineStr"/>
-      <c r="R63" s="4" t="inlineStr"/>
-      <c r="S63" s="4" t="inlineStr"/>
-      <c r="T63" s="4" t="inlineStr"/>
-      <c r="U63" s="4" t="inlineStr"/>
-      <c r="V63" s="4" t="inlineStr"/>
-      <c r="W63" s="4" t="inlineStr"/>
-      <c r="X63" s="5" t="inlineStr"/>
-      <c r="Y63" s="6" t="n">
-        <v>426.375</v>
-      </c>
-      <c r="Z63" s="7" t="n">
-        <v>0.09986532380840848</v>
-      </c>
+      <c r="A63" s="1" t="n"/>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr"/>
+      <c r="D63" s="8" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr"/>
+      <c r="F63" s="8" t="inlineStr"/>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>148.50</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr"/>
+      <c r="K63" s="8" t="inlineStr"/>
+      <c r="L63" s="8" t="inlineStr"/>
+      <c r="M63" s="8" t="inlineStr"/>
+      <c r="N63" s="8" t="inlineStr"/>
+      <c r="O63" s="8" t="inlineStr"/>
+      <c r="P63" s="8" t="inlineStr"/>
+      <c r="Q63" s="8" t="inlineStr"/>
+      <c r="R63" s="8" t="inlineStr"/>
+      <c r="S63" s="8" t="inlineStr"/>
+      <c r="T63" s="8" t="inlineStr"/>
+      <c r="U63" s="8" t="inlineStr"/>
+      <c r="V63" s="8" t="inlineStr"/>
+      <c r="W63" s="8" t="inlineStr"/>
+      <c r="X63" s="8" t="inlineStr"/>
+      <c r="Y63" s="8" t="inlineStr"/>
+      <c r="Z63" s="9" t="inlineStr"/>
+      <c r="AA63" s="10" t="inlineStr"/>
+      <c r="AB63" s="11" t="inlineStr"/>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="1" t="n"/>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr"/>
-      <c r="D64" s="8" t="inlineStr"/>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>2068.00</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>2270.50</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr"/>
-      <c r="H64" s="8" t="inlineStr"/>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>1904.00</t>
-        </is>
-      </c>
-      <c r="J64" s="8" t="inlineStr"/>
-      <c r="K64" s="8" t="inlineStr"/>
-      <c r="L64" s="8" t="inlineStr"/>
-      <c r="M64" s="8" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
-      <c r="O64" s="8" t="inlineStr">
-        <is>
-          <t>2544.50, 2833.50, 2600.50, 2639.00</t>
-        </is>
-      </c>
-      <c r="P64" s="8" t="inlineStr">
-        <is>
-          <t>250.50, 252.50, 255.00, 255.00</t>
-        </is>
-      </c>
-      <c r="Q64" s="8" t="inlineStr"/>
-      <c r="R64" s="8" t="inlineStr"/>
-      <c r="S64" s="8" t="inlineStr"/>
-      <c r="T64" s="8" t="inlineStr"/>
-      <c r="U64" s="8" t="inlineStr"/>
-      <c r="V64" s="8" t="inlineStr"/>
-      <c r="W64" s="8" t="inlineStr"/>
-      <c r="X64" s="9" t="n">
-        <v>1742.375</v>
-      </c>
-      <c r="Y64" s="10" t="inlineStr"/>
-      <c r="Z64" s="11" t="inlineStr"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Freeway
+Random: 0.0
+Human: 29.6</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 34</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" s="4" t="inlineStr"/>
+      <c r="J64" s="4" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr"/>
+      <c r="M64" s="4" t="inlineStr"/>
+      <c r="N64" s="4" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr"/>
+      <c r="Q64" s="4" t="inlineStr"/>
+      <c r="R64" s="4" t="inlineStr"/>
+      <c r="S64" s="4" t="inlineStr"/>
+      <c r="T64" s="4" t="inlineStr"/>
+      <c r="U64" s="4" t="inlineStr"/>
+      <c r="V64" s="4" t="inlineStr"/>
+      <c r="W64" s="4" t="inlineStr"/>
+      <c r="X64" s="4" t="inlineStr"/>
+      <c r="Y64" s="4" t="inlineStr"/>
+      <c r="Z64" s="5" t="inlineStr"/>
+      <c r="AA64" s="6" t="n">
+        <v>-0.5500000000000043</v>
+      </c>
+      <c r="AB64" s="7" t="n">
+        <v>-0.01858108108108122</v>
+      </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr"/>
       <c r="D65" s="8" t="inlineStr"/>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>2301.00</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>2609.00</t>
-        </is>
-      </c>
+      <c r="E65" s="8" t="inlineStr"/>
+      <c r="F65" s="8" t="inlineStr"/>
       <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>3242.50</t>
-        </is>
-      </c>
+      <c r="I65" s="8" t="inlineStr"/>
       <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr"/>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="L65" s="8" t="inlineStr"/>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="8" t="inlineStr">
         <is>
-          <t>2119.50</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="P65" s="8" t="inlineStr">
         <is>
-          <t>261.50</t>
-        </is>
-      </c>
-      <c r="Q65" s="8" t="inlineStr"/>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="Q65" s="8" t="inlineStr">
+        <is>
+          <t>33.75</t>
+        </is>
+      </c>
       <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr"/>
       <c r="T65" s="8" t="inlineStr"/>
       <c r="U65" s="8" t="inlineStr"/>
       <c r="V65" s="8" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr"/>
-      <c r="X65" s="9" t="inlineStr"/>
-      <c r="Y65" s="10" t="inlineStr"/>
-      <c r="Z65" s="11" t="inlineStr"/>
+      <c r="X65" s="8" t="inlineStr"/>
+      <c r="Y65" s="8" t="inlineStr"/>
+      <c r="Z65" s="9" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AA65" s="10" t="inlineStr"/>
+      <c r="AB65" s="11" t="inlineStr"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr"/>
       <c r="D66" s="8" t="inlineStr"/>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>2113.50, 2350.50</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>2443.00</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>283.50</t>
-        </is>
-      </c>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>252.00</t>
-        </is>
-      </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>2779.00</t>
-        </is>
-      </c>
+      <c r="E66" s="8" t="inlineStr"/>
+      <c r="F66" s="8" t="inlineStr"/>
+      <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr"/>
       <c r="J66" s="8" t="inlineStr"/>
       <c r="K66" s="8" t="inlineStr"/>
       <c r="L66" s="8" t="inlineStr"/>
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="8" t="inlineStr"/>
-      <c r="O66" s="8" t="inlineStr">
-        <is>
-          <t>2474.00</t>
-        </is>
-      </c>
-      <c r="P66" s="8" t="inlineStr">
-        <is>
-          <t>251.00</t>
-        </is>
-      </c>
+      <c r="O66" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="P66" s="8" t="inlineStr"/>
       <c r="Q66" s="8" t="inlineStr"/>
       <c r="R66" s="8" t="inlineStr"/>
       <c r="S66" s="8" t="inlineStr"/>
@@ -4011,26 +4419,22 @@
       <c r="U66" s="8" t="inlineStr"/>
       <c r="V66" s="8" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr"/>
-      <c r="X66" s="9" t="n">
-        <v>1986.75</v>
-      </c>
-      <c r="Y66" s="9" t="n">
-        <v>244.375</v>
-      </c>
-      <c r="Z66" s="11" t="n">
-        <v>0.05723738142639653</v>
-      </c>
+      <c r="X66" s="8" t="inlineStr"/>
+      <c r="Y66" s="8" t="inlineStr"/>
+      <c r="Z66" s="9" t="inlineStr"/>
+      <c r="AA66" s="10" t="inlineStr"/>
+      <c r="AB66" s="11" t="inlineStr"/>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr"/>
       <c r="D67" s="8" t="inlineStr"/>
-      <c r="E67" s="13" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr"/>
       <c r="G67" s="8" t="inlineStr"/>
       <c r="H67" s="8" t="inlineStr"/>
@@ -4042,193 +4446,181 @@
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="8" t="inlineStr">
         <is>
-          <t>271.00</t>
-        </is>
-      </c>
-      <c r="P67" s="8" t="inlineStr"/>
-      <c r="Q67" s="8" t="inlineStr"/>
+          <t>33.55</t>
+        </is>
+      </c>
+      <c r="P67" s="8" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="Q67" s="8" t="inlineStr">
+        <is>
+          <t>33.75</t>
+        </is>
+      </c>
       <c r="R67" s="8" t="inlineStr"/>
       <c r="S67" s="8" t="inlineStr"/>
       <c r="T67" s="8" t="inlineStr"/>
       <c r="U67" s="8" t="inlineStr"/>
       <c r="V67" s="8" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr"/>
-      <c r="X67" s="9" t="inlineStr"/>
-      <c r="Y67" s="10" t="inlineStr"/>
-      <c r="Z67" s="11" t="inlineStr"/>
+      <c r="X67" s="8" t="inlineStr"/>
+      <c r="Y67" s="8" t="inlineStr"/>
+      <c r="Z67" s="9" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="AA67" s="9" t="n">
+        <v>0.09999999999999432</v>
+      </c>
+      <c r="AB67" s="11" t="n">
+        <v>-0.003378378378378186</v>
+      </c>
     </row>
     <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Gopher
-Random: 257.6
-Human: 2412.5</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 8240</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
-      <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr"/>
-      <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr"/>
-      <c r="O68" s="4" t="inlineStr"/>
-      <c r="P68" s="4" t="inlineStr"/>
-      <c r="Q68" s="4" t="inlineStr"/>
-      <c r="R68" s="4" t="inlineStr"/>
-      <c r="S68" s="4" t="inlineStr"/>
-      <c r="T68" s="4" t="inlineStr"/>
-      <c r="U68" s="4" t="inlineStr"/>
-      <c r="V68" s="4" t="inlineStr"/>
-      <c r="W68" s="4" t="inlineStr"/>
-      <c r="X68" s="5" t="inlineStr"/>
-      <c r="Y68" s="6" t="n">
-        <v>-4547</v>
-      </c>
-      <c r="Z68" s="7" t="n">
-        <v>-2.110074713443779</v>
-      </c>
+      <c r="A68" s="1" t="n"/>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr"/>
+      <c r="D68" s="8" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr"/>
+      <c r="F68" s="8" t="inlineStr"/>
+      <c r="G68" s="8" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr"/>
+      <c r="J68" s="8" t="inlineStr"/>
+      <c r="K68" s="8" t="inlineStr"/>
+      <c r="L68" s="8" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr"/>
+      <c r="N68" s="8" t="inlineStr"/>
+      <c r="O68" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="P68" s="8" t="inlineStr"/>
+      <c r="Q68" s="8" t="inlineStr"/>
+      <c r="R68" s="8" t="inlineStr"/>
+      <c r="S68" s="8" t="inlineStr"/>
+      <c r="T68" s="8" t="inlineStr"/>
+      <c r="U68" s="8" t="inlineStr"/>
+      <c r="V68" s="8" t="inlineStr"/>
+      <c r="W68" s="8" t="inlineStr"/>
+      <c r="X68" s="8" t="inlineStr"/>
+      <c r="Y68" s="8" t="inlineStr"/>
+      <c r="Z68" s="9" t="inlineStr"/>
+      <c r="AA68" s="10" t="inlineStr"/>
+      <c r="AB68" s="11" t="inlineStr"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>5968.00</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>3752.00</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>3275.00</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>3914.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr"/>
+      <c r="D69" s="8" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr"/>
+      <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr"/>
       <c r="H69" s="8" t="inlineStr"/>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>4219.00</t>
-        </is>
-      </c>
+      <c r="I69" s="8" t="inlineStr"/>
       <c r="J69" s="8" t="inlineStr"/>
       <c r="K69" s="8" t="inlineStr"/>
       <c r="L69" s="8" t="inlineStr"/>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
-      <c r="O69" s="13" t="inlineStr">
-        <is>
-          <t>2486.00</t>
-        </is>
-      </c>
-      <c r="P69" s="13" t="inlineStr">
-        <is>
-          <t>1250.00</t>
-        </is>
-      </c>
+      <c r="O69" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="P69" s="8" t="inlineStr"/>
       <c r="Q69" s="8" t="inlineStr"/>
       <c r="R69" s="8" t="inlineStr"/>
       <c r="S69" s="8" t="inlineStr"/>
       <c r="T69" s="8" t="inlineStr"/>
-      <c r="U69" s="8" t="inlineStr">
-        <is>
-          <t>3585.00</t>
-        </is>
-      </c>
-      <c r="V69" s="13" t="inlineStr">
-        <is>
-          <t>2594.00</t>
-        </is>
-      </c>
+      <c r="U69" s="8" t="inlineStr"/>
+      <c r="V69" s="8" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr"/>
-      <c r="X69" s="9" t="n">
-        <v>3693</v>
-      </c>
-      <c r="Y69" s="10" t="inlineStr"/>
-      <c r="Z69" s="11" t="inlineStr"/>
+      <c r="X69" s="8" t="inlineStr"/>
+      <c r="Y69" s="8" t="inlineStr"/>
+      <c r="Z69" s="9" t="inlineStr"/>
+      <c r="AA69" s="10" t="inlineStr"/>
+      <c r="AB69" s="11" t="inlineStr"/>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr"/>
-      <c r="D70" s="8" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr"/>
-      <c r="F70" s="8" t="inlineStr"/>
-      <c r="G70" s="8" t="inlineStr"/>
-      <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr"/>
-      <c r="J70" s="8" t="inlineStr"/>
-      <c r="K70" s="8" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
-      <c r="M70" s="8" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
-      <c r="O70" s="13" t="inlineStr"/>
-      <c r="P70" s="13" t="inlineStr"/>
-      <c r="Q70" s="8" t="inlineStr"/>
-      <c r="R70" s="8" t="inlineStr">
-        <is>
-          <t>2533.00</t>
-        </is>
-      </c>
-      <c r="S70" s="8" t="inlineStr"/>
-      <c r="T70" s="8" t="inlineStr"/>
-      <c r="U70" s="8" t="inlineStr">
-        <is>
-          <t>4472.00</t>
-        </is>
-      </c>
-      <c r="V70" s="13" t="inlineStr"/>
-      <c r="W70" s="8" t="inlineStr"/>
-      <c r="X70" s="9" t="inlineStr"/>
-      <c r="Y70" s="10" t="inlineStr"/>
-      <c r="Z70" s="11" t="inlineStr"/>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Frostbite
+Random: 65.2
+Human: 4334.7</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 1316</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr"/>
+      <c r="Q70" s="4" t="inlineStr"/>
+      <c r="R70" s="4" t="inlineStr"/>
+      <c r="S70" s="4" t="inlineStr"/>
+      <c r="T70" s="4" t="inlineStr"/>
+      <c r="U70" s="4" t="inlineStr"/>
+      <c r="V70" s="4" t="inlineStr"/>
+      <c r="W70" s="4" t="inlineStr"/>
+      <c r="X70" s="4" t="inlineStr"/>
+      <c r="Y70" s="4" t="inlineStr"/>
+      <c r="Z70" s="5" t="inlineStr"/>
+      <c r="AA70" s="6" t="n">
+        <v>426.375</v>
+      </c>
+      <c r="AB70" s="7" t="n">
+        <v>0.09986532380840848</v>
+      </c>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr"/>
       <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>3327.00</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr"/>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>2068.00</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>2270.50</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="inlineStr"/>
       <c r="H71" s="8" t="inlineStr"/>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>3829.00</t>
+          <t>1904.00</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr"/>
@@ -4236,204 +4628,220 @@
       <c r="L71" s="8" t="inlineStr"/>
       <c r="M71" s="8" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
-      <c r="O71" s="13" t="inlineStr">
-        <is>
-          <t>1024.00</t>
-        </is>
-      </c>
-      <c r="P71" s="13" t="inlineStr">
-        <is>
-          <t>927.00</t>
-        </is>
-      </c>
-      <c r="Q71" s="14" t="inlineStr">
-        <is>
-          <t>847.00</t>
-        </is>
-      </c>
-      <c r="R71" s="14" t="inlineStr">
-        <is>
-          <t>2933.00</t>
-        </is>
-      </c>
-      <c r="S71" s="15" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>2544.50, 2833.50, 2600.50, 2639.00</t>
+        </is>
+      </c>
+      <c r="P71" s="8" t="inlineStr">
+        <is>
+          <t>250.50, 252.50, 255.00, 255.00</t>
+        </is>
+      </c>
+      <c r="Q71" s="8" t="inlineStr"/>
+      <c r="R71" s="8" t="inlineStr"/>
+      <c r="S71" s="8" t="inlineStr"/>
       <c r="T71" s="8" t="inlineStr"/>
-      <c r="U71" s="8" t="inlineStr">
-        <is>
-          <t>7531.00</t>
-        </is>
-      </c>
-      <c r="V71" s="13" t="inlineStr">
-        <is>
-          <t>1005.00</t>
-        </is>
-      </c>
+      <c r="U71" s="8" t="inlineStr"/>
+      <c r="V71" s="8" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr"/>
-      <c r="X71" s="9" t="n">
-        <v>4895.666666666667</v>
-      </c>
-      <c r="Y71" s="9" t="n">
-        <v>1202.666666666667</v>
-      </c>
-      <c r="Z71" s="11" t="n">
-        <v>0.558107878169134</v>
-      </c>
+      <c r="X71" s="8" t="inlineStr"/>
+      <c r="Y71" s="8" t="inlineStr"/>
+      <c r="Z71" s="9" t="n">
+        <v>1742.375</v>
+      </c>
+      <c r="AA71" s="10" t="inlineStr"/>
+      <c r="AB71" s="11" t="inlineStr"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr"/>
       <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr"/>
-      <c r="F72" s="8" t="inlineStr"/>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>2301.00</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>2609.00</t>
+        </is>
+      </c>
       <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>3242.50</t>
+        </is>
+      </c>
       <c r="J72" s="8" t="inlineStr"/>
       <c r="K72" s="8" t="inlineStr"/>
       <c r="L72" s="8" t="inlineStr"/>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
-      <c r="O72" s="13" t="inlineStr"/>
-      <c r="P72" s="13" t="inlineStr"/>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>2119.50</t>
+        </is>
+      </c>
+      <c r="P72" s="8" t="inlineStr">
+        <is>
+          <t>261.50</t>
+        </is>
+      </c>
       <c r="Q72" s="8" t="inlineStr"/>
       <c r="R72" s="8" t="inlineStr"/>
       <c r="S72" s="8" t="inlineStr"/>
       <c r="T72" s="8" t="inlineStr"/>
-      <c r="U72" s="8" t="inlineStr">
-        <is>
-          <t>5320.00</t>
-        </is>
-      </c>
-      <c r="V72" s="13" t="inlineStr"/>
+      <c r="U72" s="8" t="inlineStr"/>
+      <c r="V72" s="8" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr"/>
-      <c r="X72" s="9" t="inlineStr"/>
-      <c r="Y72" s="10" t="inlineStr"/>
-      <c r="Z72" s="11" t="inlineStr"/>
+      <c r="X72" s="8" t="inlineStr"/>
+      <c r="Y72" s="8" t="inlineStr"/>
+      <c r="Z72" s="9" t="inlineStr"/>
+      <c r="AA72" s="10" t="inlineStr"/>
+      <c r="AB72" s="11" t="inlineStr"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr"/>
       <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="8" t="inlineStr"/>
-      <c r="F73" s="8" t="inlineStr"/>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr"/>
-      <c r="I73" s="8" t="inlineStr"/>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>2113.50, 2350.50</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>2443.00</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>283.50</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>252.00</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>2779.00</t>
+        </is>
+      </c>
       <c r="J73" s="8" t="inlineStr"/>
       <c r="K73" s="8" t="inlineStr"/>
       <c r="L73" s="8" t="inlineStr"/>
       <c r="M73" s="8" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
-      <c r="O73" s="13" t="inlineStr"/>
-      <c r="P73" s="13" t="inlineStr"/>
+      <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>2474.00</t>
+        </is>
+      </c>
+      <c r="P73" s="8" t="inlineStr">
+        <is>
+          <t>251.00</t>
+        </is>
+      </c>
       <c r="Q73" s="8" t="inlineStr"/>
       <c r="R73" s="8" t="inlineStr"/>
       <c r="S73" s="8" t="inlineStr"/>
       <c r="T73" s="8" t="inlineStr"/>
-      <c r="U73" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="V73" s="13" t="inlineStr"/>
+      <c r="U73" s="8" t="inlineStr"/>
+      <c r="V73" s="8" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr"/>
-      <c r="X73" s="9" t="inlineStr"/>
-      <c r="Y73" s="10" t="inlineStr"/>
-      <c r="Z73" s="11" t="inlineStr"/>
+      <c r="X73" s="8" t="inlineStr"/>
+      <c r="Y73" s="8" t="inlineStr"/>
+      <c r="Z73" s="9" t="n">
+        <v>1986.75</v>
+      </c>
+      <c r="AA73" s="9" t="n">
+        <v>244.375</v>
+      </c>
+      <c r="AB73" s="11" t="n">
+        <v>0.05723738142639653</v>
+      </c>
     </row>
     <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Hero
-Random: 1027.0
-Human: 30826.4</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11044</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr"/>
-      <c r="D74" s="4" t="inlineStr"/>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr"/>
-      <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="4" t="inlineStr"/>
-      <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr"/>
-      <c r="O74" s="4" t="inlineStr"/>
-      <c r="P74" s="4" t="inlineStr"/>
-      <c r="Q74" s="4" t="inlineStr"/>
-      <c r="R74" s="4" t="inlineStr"/>
-      <c r="S74" s="4" t="inlineStr"/>
-      <c r="T74" s="4" t="inlineStr"/>
-      <c r="U74" s="4" t="inlineStr"/>
-      <c r="V74" s="4" t="inlineStr"/>
-      <c r="W74" s="4" t="inlineStr"/>
-      <c r="X74" s="5" t="inlineStr"/>
-      <c r="Y74" s="6" t="n">
-        <v>741.625</v>
-      </c>
-      <c r="Z74" s="7" t="n">
-        <v>0.02488724605193393</v>
-      </c>
+      <c r="A74" s="1" t="n"/>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr"/>
+      <c r="D74" s="8" t="inlineStr"/>
+      <c r="E74" s="12" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr"/>
+      <c r="J74" s="8" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr"/>
+      <c r="L74" s="8" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
+      <c r="N74" s="8" t="inlineStr"/>
+      <c r="O74" s="8" t="inlineStr">
+        <is>
+          <t>271.00</t>
+        </is>
+      </c>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>238.50</t>
+        </is>
+      </c>
+      <c r="Q74" s="8" t="inlineStr"/>
+      <c r="R74" s="8" t="inlineStr"/>
+      <c r="S74" s="8" t="inlineStr"/>
+      <c r="T74" s="8" t="inlineStr"/>
+      <c r="U74" s="8" t="inlineStr"/>
+      <c r="V74" s="8" t="inlineStr"/>
+      <c r="W74" s="8" t="inlineStr"/>
+      <c r="X74" s="8" t="inlineStr"/>
+      <c r="Y74" s="8" t="inlineStr"/>
+      <c r="Z74" s="9" t="inlineStr"/>
+      <c r="AA74" s="10" t="inlineStr"/>
+      <c r="AB74" s="11" t="inlineStr"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>7608.50</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr"/>
       <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>12996.75</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>13456.25</t>
-        </is>
-      </c>
+      <c r="E75" s="12" t="inlineStr"/>
+      <c r="F75" s="8" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>13081.00</t>
-        </is>
-      </c>
+      <c r="I75" s="8" t="inlineStr"/>
       <c r="J75" s="8" t="inlineStr"/>
       <c r="K75" s="8" t="inlineStr"/>
       <c r="L75" s="8" t="inlineStr"/>
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr"/>
       <c r="O75" s="8" t="inlineStr"/>
-      <c r="P75" s="8" t="inlineStr"/>
+      <c r="P75" s="8" t="inlineStr">
+        <is>
+          <t>226.50</t>
+        </is>
+      </c>
       <c r="Q75" s="8" t="inlineStr"/>
       <c r="R75" s="8" t="inlineStr"/>
       <c r="S75" s="8" t="inlineStr"/>
@@ -4441,76 +4849,88 @@
       <c r="U75" s="8" t="inlineStr"/>
       <c r="V75" s="8" t="inlineStr"/>
       <c r="W75" s="8" t="inlineStr"/>
-      <c r="X75" s="9" t="n">
-        <v>11785.625</v>
-      </c>
-      <c r="Y75" s="10" t="inlineStr"/>
-      <c r="Z75" s="11" t="inlineStr"/>
+      <c r="X75" s="8" t="inlineStr"/>
+      <c r="Y75" s="8" t="inlineStr"/>
+      <c r="Z75" s="9" t="inlineStr"/>
+      <c r="AA75" s="10" t="inlineStr"/>
+      <c r="AB75" s="11" t="inlineStr"/>
     </row>
     <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="1" t="n"/>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>13473.00</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="8" t="inlineStr"/>
-      <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr"/>
-      <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr"/>
-      <c r="L76" s="8" t="inlineStr"/>
-      <c r="M76" s="8" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr"/>
-      <c r="O76" s="8" t="inlineStr"/>
-      <c r="P76" s="8" t="inlineStr"/>
-      <c r="Q76" s="8" t="inlineStr"/>
-      <c r="R76" s="8" t="inlineStr"/>
-      <c r="S76" s="8" t="inlineStr"/>
-      <c r="T76" s="8" t="inlineStr"/>
-      <c r="U76" s="8" t="inlineStr"/>
-      <c r="V76" s="8" t="inlineStr"/>
-      <c r="W76" s="8" t="inlineStr"/>
-      <c r="X76" s="9" t="inlineStr"/>
-      <c r="Y76" s="10" t="inlineStr"/>
-      <c r="Z76" s="11" t="inlineStr"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Gopher
+Random: 257.6
+Human: 2412.5</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 8240</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr"/>
+      <c r="D76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr"/>
+      <c r="L76" s="4" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr"/>
+      <c r="N76" s="4" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr"/>
+      <c r="Q76" s="4" t="inlineStr"/>
+      <c r="R76" s="4" t="inlineStr"/>
+      <c r="S76" s="4" t="inlineStr"/>
+      <c r="T76" s="4" t="inlineStr"/>
+      <c r="U76" s="4" t="inlineStr"/>
+      <c r="V76" s="4" t="inlineStr"/>
+      <c r="W76" s="4" t="inlineStr"/>
+      <c r="X76" s="4" t="inlineStr"/>
+      <c r="Y76" s="4" t="inlineStr"/>
+      <c r="Z76" s="5" t="inlineStr"/>
+      <c r="AA76" s="6" t="n">
+        <v>-4547</v>
+      </c>
+      <c r="AB76" s="7" t="n">
+        <v>-2.110074713443779</v>
+      </c>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>13108.75</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr"/>
+          <t>5968.00</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>3752.00</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>13251.25</t>
+          <t>3275.00</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>13231.50</t>
+          <t>3914.00</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
       <c r="H77" s="8" t="inlineStr"/>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>13325.50</t>
+          <t>4219.00</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr"/>
@@ -4518,37 +4938,47 @@
       <c r="L77" s="8" t="inlineStr"/>
       <c r="M77" s="8" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr"/>
-      <c r="O77" s="8" t="inlineStr"/>
-      <c r="P77" s="8" t="inlineStr"/>
-      <c r="Q77" s="8" t="inlineStr"/>
-      <c r="R77" s="8" t="inlineStr"/>
-      <c r="S77" s="8" t="inlineStr"/>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>2486.00</t>
+        </is>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
+      <c r="Q77" s="12" t="inlineStr"/>
+      <c r="R77" s="12" t="inlineStr"/>
+      <c r="S77" s="12" t="inlineStr"/>
       <c r="T77" s="8" t="inlineStr"/>
       <c r="U77" s="8" t="inlineStr"/>
       <c r="V77" s="8" t="inlineStr"/>
-      <c r="W77" s="8" t="inlineStr"/>
-      <c r="X77" s="9" t="n">
-        <v>13229.25</v>
-      </c>
-      <c r="Y77" s="9" t="n">
-        <v>1443.625</v>
-      </c>
-      <c r="Z77" s="11" t="n">
-        <v>0.04844476734430894</v>
-      </c>
+      <c r="W77" s="8" t="inlineStr">
+        <is>
+          <t>3585.00</t>
+        </is>
+      </c>
+      <c r="X77" s="12" t="inlineStr">
+        <is>
+          <t>2594.00</t>
+        </is>
+      </c>
+      <c r="Y77" s="8" t="inlineStr"/>
+      <c r="Z77" s="9" t="n">
+        <v>3693</v>
+      </c>
+      <c r="AA77" s="10" t="inlineStr"/>
+      <c r="AB77" s="11" t="inlineStr"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
-        </is>
-      </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr"/>
       <c r="D78" s="8" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="8" t="inlineStr"/>
@@ -4560,109 +4990,159 @@
       <c r="L78" s="8" t="inlineStr"/>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr"/>
-      <c r="O78" s="8" t="inlineStr"/>
-      <c r="P78" s="8" t="inlineStr"/>
-      <c r="Q78" s="8" t="inlineStr"/>
-      <c r="R78" s="8" t="inlineStr"/>
-      <c r="S78" s="8" t="inlineStr"/>
+      <c r="O78" s="12" t="inlineStr"/>
+      <c r="P78" s="12" t="inlineStr"/>
+      <c r="Q78" s="12" t="inlineStr"/>
+      <c r="R78" s="12" t="inlineStr">
+        <is>
+          <t>2533.00</t>
+        </is>
+      </c>
+      <c r="S78" s="12" t="inlineStr"/>
       <c r="T78" s="8" t="inlineStr"/>
       <c r="U78" s="8" t="inlineStr"/>
       <c r="V78" s="8" t="inlineStr"/>
-      <c r="W78" s="8" t="inlineStr"/>
-      <c r="X78" s="9" t="inlineStr"/>
-      <c r="Y78" s="10" t="inlineStr"/>
-      <c r="Z78" s="11" t="inlineStr"/>
+      <c r="W78" s="8" t="inlineStr">
+        <is>
+          <t>4472.00</t>
+        </is>
+      </c>
+      <c r="X78" s="12" t="inlineStr"/>
+      <c r="Y78" s="8" t="inlineStr"/>
+      <c r="Z78" s="9" t="inlineStr"/>
+      <c r="AA78" s="10" t="inlineStr"/>
+      <c r="AB78" s="11" t="inlineStr"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr"/>
       <c r="D79" s="8" t="inlineStr"/>
-      <c r="E79" s="8" t="inlineStr"/>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>3327.00</t>
+        </is>
+      </c>
       <c r="F79" s="8" t="inlineStr"/>
       <c r="G79" s="8" t="inlineStr"/>
       <c r="H79" s="8" t="inlineStr"/>
-      <c r="I79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>3829.00</t>
+        </is>
+      </c>
       <c r="J79" s="8" t="inlineStr"/>
       <c r="K79" s="8" t="inlineStr"/>
       <c r="L79" s="8" t="inlineStr"/>
       <c r="M79" s="8" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr"/>
-      <c r="O79" s="8" t="inlineStr"/>
-      <c r="P79" s="8" t="inlineStr"/>
-      <c r="Q79" s="8" t="inlineStr"/>
-      <c r="R79" s="8" t="inlineStr"/>
-      <c r="S79" s="8" t="inlineStr"/>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>1024.00</t>
+        </is>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>927.00</t>
+        </is>
+      </c>
+      <c r="Q79" s="13" t="inlineStr">
+        <is>
+          <t>847.00</t>
+        </is>
+      </c>
+      <c r="R79" s="13" t="inlineStr">
+        <is>
+          <t>2933.00</t>
+        </is>
+      </c>
+      <c r="S79" s="13" t="inlineStr">
+        <is>
+          <t>2775.00</t>
+        </is>
+      </c>
       <c r="T79" s="8" t="inlineStr"/>
-      <c r="U79" s="8" t="inlineStr"/>
-      <c r="V79" s="8" t="inlineStr"/>
-      <c r="W79" s="8" t="inlineStr"/>
-      <c r="X79" s="9" t="inlineStr"/>
-      <c r="Y79" s="10" t="inlineStr"/>
-      <c r="Z79" s="11" t="inlineStr"/>
+      <c r="U79" s="15" t="inlineStr">
+        <is>
+          <t>3061.00</t>
+        </is>
+      </c>
+      <c r="V79" s="15" t="inlineStr">
+        <is>
+          <t>8373.00</t>
+        </is>
+      </c>
+      <c r="W79" s="8" t="inlineStr">
+        <is>
+          <t>7531.00</t>
+        </is>
+      </c>
+      <c r="X79" s="12" t="inlineStr">
+        <is>
+          <t>1005.00</t>
+        </is>
+      </c>
+      <c r="Y79" s="8" t="inlineStr"/>
+      <c r="Z79" s="9" t="n">
+        <v>4895.666666666667</v>
+      </c>
+      <c r="AA79" s="9" t="n">
+        <v>1202.666666666667</v>
+      </c>
+      <c r="AB79" s="11" t="n">
+        <v>0.558107878169134</v>
+      </c>
     </row>
     <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Jamesbond
-Random: 29.0
-Human: 302.8</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 509</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
-      <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr"/>
-      <c r="K80" s="4" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr"/>
-      <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr"/>
-      <c r="O80" s="4" t="inlineStr"/>
-      <c r="P80" s="4" t="inlineStr"/>
-      <c r="Q80" s="4" t="inlineStr"/>
-      <c r="R80" s="4" t="inlineStr"/>
-      <c r="S80" s="4" t="inlineStr"/>
-      <c r="T80" s="4" t="inlineStr"/>
-      <c r="U80" s="4" t="inlineStr"/>
-      <c r="V80" s="4" t="inlineStr"/>
-      <c r="W80" s="4" t="inlineStr"/>
-      <c r="X80" s="5" t="inlineStr"/>
-      <c r="Y80" s="6" t="n">
-        <v>-35.66666666666669</v>
-      </c>
-      <c r="Z80" s="7" t="n">
-        <v>-0.1302654005356709</v>
-      </c>
+      <c r="A80" s="1" t="n"/>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr"/>
+      <c r="D80" s="8" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr"/>
+      <c r="F80" s="8" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr"/>
+      <c r="J80" s="8" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr"/>
+      <c r="L80" s="8" t="inlineStr"/>
+      <c r="M80" s="8" t="inlineStr"/>
+      <c r="N80" s="8" t="inlineStr"/>
+      <c r="O80" s="12" t="inlineStr"/>
+      <c r="P80" s="12" t="inlineStr"/>
+      <c r="Q80" s="12" t="inlineStr"/>
+      <c r="R80" s="12" t="inlineStr"/>
+      <c r="S80" s="12" t="inlineStr"/>
+      <c r="T80" s="8" t="inlineStr"/>
+      <c r="U80" s="8" t="inlineStr"/>
+      <c r="V80" s="8" t="inlineStr"/>
+      <c r="W80" s="8" t="inlineStr">
+        <is>
+          <t>5320.00</t>
+        </is>
+      </c>
+      <c r="X80" s="12" t="inlineStr"/>
+      <c r="Y80" s="8" t="inlineStr"/>
+      <c r="Z80" s="9" t="inlineStr"/>
+      <c r="AA80" s="10" t="inlineStr"/>
+      <c r="AB80" s="11" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>490.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr"/>
       <c r="D81" s="8" t="inlineStr"/>
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr"/>
@@ -4670,206 +5150,200 @@
       <c r="H81" s="8" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr"/>
       <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr">
-        <is>
-          <t>532.50, 537.50</t>
-        </is>
-      </c>
+      <c r="K81" s="8" t="inlineStr"/>
       <c r="L81" s="8" t="inlineStr"/>
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="8" t="inlineStr"/>
-      <c r="O81" s="8" t="inlineStr">
-        <is>
-          <t>522.50</t>
-        </is>
-      </c>
-      <c r="P81" s="8" t="inlineStr"/>
-      <c r="Q81" s="8" t="inlineStr"/>
-      <c r="R81" s="8" t="inlineStr"/>
-      <c r="S81" s="8" t="inlineStr"/>
+      <c r="O81" s="12" t="inlineStr"/>
+      <c r="P81" s="12" t="inlineStr"/>
+      <c r="Q81" s="12" t="inlineStr"/>
+      <c r="R81" s="12" t="inlineStr"/>
+      <c r="S81" s="12" t="inlineStr"/>
       <c r="T81" s="8" t="inlineStr"/>
       <c r="U81" s="8" t="inlineStr"/>
-      <c r="V81" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
-        </is>
-      </c>
-      <c r="W81" s="8" t="inlineStr"/>
-      <c r="X81" s="9" t="n">
-        <v>473.3333333333333</v>
-      </c>
-      <c r="Y81" s="10" t="inlineStr"/>
-      <c r="Z81" s="11" t="inlineStr"/>
+      <c r="V81" s="8" t="inlineStr"/>
+      <c r="W81" s="8" t="inlineStr">
+        <is>
+          <t>2516.00</t>
+        </is>
+      </c>
+      <c r="X81" s="12" t="inlineStr"/>
+      <c r="Y81" s="8" t="inlineStr"/>
+      <c r="Z81" s="9" t="inlineStr"/>
+      <c r="AA81" s="10" t="inlineStr"/>
+      <c r="AB81" s="11" t="inlineStr"/>
     </row>
     <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="1" t="n"/>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr"/>
-      <c r="D82" s="8" t="inlineStr"/>
-      <c r="E82" s="8" t="inlineStr"/>
-      <c r="F82" s="8" t="inlineStr"/>
-      <c r="G82" s="8" t="inlineStr"/>
-      <c r="H82" s="8" t="inlineStr"/>
-      <c r="I82" s="8" t="inlineStr"/>
-      <c r="J82" s="8" t="inlineStr"/>
-      <c r="K82" s="8" t="inlineStr"/>
-      <c r="L82" s="8" t="inlineStr"/>
-      <c r="M82" s="8" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr"/>
-      <c r="O82" s="8" t="inlineStr">
-        <is>
-          <t>575.00</t>
-        </is>
-      </c>
-      <c r="P82" s="8" t="inlineStr"/>
-      <c r="Q82" s="8" t="inlineStr"/>
-      <c r="R82" s="8" t="inlineStr"/>
-      <c r="S82" s="8" t="inlineStr"/>
-      <c r="T82" s="8" t="inlineStr"/>
-      <c r="U82" s="8" t="inlineStr"/>
-      <c r="V82" s="8" t="inlineStr"/>
-      <c r="W82" s="8" t="inlineStr"/>
-      <c r="X82" s="9" t="inlineStr"/>
-      <c r="Y82" s="10" t="inlineStr"/>
-      <c r="Z82" s="11" t="inlineStr"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Hero
+Random: 1027.0
+Human: 30826.4</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11044</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr"/>
+      <c r="D82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr"/>
+      <c r="P82" s="4" t="inlineStr"/>
+      <c r="Q82" s="4" t="inlineStr"/>
+      <c r="R82" s="4" t="inlineStr"/>
+      <c r="S82" s="4" t="inlineStr"/>
+      <c r="T82" s="4" t="inlineStr"/>
+      <c r="U82" s="4" t="inlineStr"/>
+      <c r="V82" s="4" t="inlineStr"/>
+      <c r="W82" s="4" t="inlineStr"/>
+      <c r="X82" s="4" t="inlineStr"/>
+      <c r="Y82" s="4" t="inlineStr"/>
+      <c r="Z82" s="5" t="inlineStr"/>
+      <c r="AA82" s="6" t="n">
+        <v>741.625</v>
+      </c>
+      <c r="AB82" s="7" t="n">
+        <v>0.02488724605193393</v>
+      </c>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>7608.50</t>
+        </is>
+      </c>
       <c r="D83" s="8" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr"/>
-      <c r="F83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>12996.75</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>13456.25</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="inlineStr"/>
       <c r="H83" s="8" t="inlineStr"/>
-      <c r="I83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>13081.00</t>
+        </is>
+      </c>
       <c r="J83" s="8" t="inlineStr"/>
-      <c r="K83" s="8" t="inlineStr">
-        <is>
-          <t>567.50, 660.00</t>
-        </is>
-      </c>
+      <c r="K83" s="8" t="inlineStr"/>
       <c r="L83" s="8" t="inlineStr"/>
       <c r="M83" s="8" t="inlineStr"/>
       <c r="N83" s="8" t="inlineStr"/>
-      <c r="O83" s="8" t="inlineStr">
-        <is>
-          <t>665.00</t>
-        </is>
-      </c>
+      <c r="O83" s="8" t="inlineStr"/>
       <c r="P83" s="8" t="inlineStr"/>
       <c r="Q83" s="8" t="inlineStr"/>
       <c r="R83" s="8" t="inlineStr"/>
       <c r="S83" s="8" t="inlineStr"/>
       <c r="T83" s="8" t="inlineStr"/>
       <c r="U83" s="8" t="inlineStr"/>
-      <c r="V83" s="8" t="inlineStr">
-        <is>
-          <t>375.00</t>
-        </is>
-      </c>
+      <c r="V83" s="8" t="inlineStr"/>
       <c r="W83" s="8" t="inlineStr"/>
-      <c r="X83" s="9" t="n">
-        <v>535.8333333333334</v>
-      </c>
-      <c r="Y83" s="9" t="n">
-        <v>62.50000000000006</v>
-      </c>
-      <c r="Z83" s="11" t="n">
-        <v>0.2282688093498906</v>
-      </c>
+      <c r="X83" s="8" t="inlineStr"/>
+      <c r="Y83" s="8" t="inlineStr"/>
+      <c r="Z83" s="9" t="n">
+        <v>11785.625</v>
+      </c>
+      <c r="AA83" s="10" t="inlineStr"/>
+      <c r="AB83" s="11" t="inlineStr"/>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Kangaroo
-Random: 52.0
-Human: 3035.0</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4208</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr"/>
-      <c r="D84" s="4" t="inlineStr"/>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
-      <c r="K84" s="4" t="inlineStr"/>
-      <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr"/>
-      <c r="O84" s="4" t="inlineStr"/>
-      <c r="P84" s="4" t="inlineStr"/>
-      <c r="Q84" s="4" t="inlineStr"/>
-      <c r="R84" s="4" t="inlineStr"/>
-      <c r="S84" s="4" t="inlineStr"/>
-      <c r="T84" s="4" t="inlineStr"/>
-      <c r="U84" s="4" t="inlineStr"/>
-      <c r="V84" s="4" t="inlineStr"/>
-      <c r="W84" s="4" t="inlineStr"/>
-      <c r="X84" s="5" t="inlineStr"/>
-      <c r="Y84" s="6" t="n">
-        <v>-2778</v>
-      </c>
-      <c r="Z84" s="7" t="n">
-        <v>-0.9312772376801878</v>
-      </c>
+      <c r="A84" s="1" t="n"/>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>13473.00</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr"/>
+      <c r="E84" s="8" t="inlineStr"/>
+      <c r="F84" s="8" t="inlineStr"/>
+      <c r="G84" s="8" t="inlineStr"/>
+      <c r="H84" s="8" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="8" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
+      <c r="N84" s="8" t="inlineStr"/>
+      <c r="O84" s="8" t="inlineStr"/>
+      <c r="P84" s="8" t="inlineStr"/>
+      <c r="Q84" s="8" t="inlineStr"/>
+      <c r="R84" s="8" t="inlineStr"/>
+      <c r="S84" s="8" t="inlineStr"/>
+      <c r="T84" s="8" t="inlineStr"/>
+      <c r="U84" s="8" t="inlineStr"/>
+      <c r="V84" s="8" t="inlineStr"/>
+      <c r="W84" s="8" t="inlineStr"/>
+      <c r="X84" s="8" t="inlineStr"/>
+      <c r="Y84" s="8" t="inlineStr"/>
+      <c r="Z84" s="9" t="inlineStr"/>
+      <c r="AA84" s="10" t="inlineStr"/>
+      <c r="AB84" s="11" t="inlineStr"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>13108.75</t>
+        </is>
+      </c>
       <c r="D85" s="8" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>1770.00</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr"/>
+          <t>13251.25</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>13231.50</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="inlineStr"/>
       <c r="H85" s="8" t="inlineStr"/>
-      <c r="I85" s="8" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>13325.50</t>
+        </is>
+      </c>
       <c r="J85" s="8" t="inlineStr"/>
-      <c r="K85" s="8" t="inlineStr">
-        <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="L85" s="8" t="inlineStr">
-        <is>
-          <t>1730.00</t>
-        </is>
-      </c>
+      <c r="K85" s="8" t="inlineStr"/>
+      <c r="L85" s="8" t="inlineStr"/>
       <c r="M85" s="8" t="inlineStr"/>
       <c r="N85" s="8" t="inlineStr"/>
-      <c r="O85" s="8" t="inlineStr">
-        <is>
-          <t>1550.00</t>
-        </is>
-      </c>
-      <c r="P85" s="8" t="inlineStr">
-        <is>
-          <t>930.00</t>
-        </is>
-      </c>
+      <c r="O85" s="8" t="inlineStr"/>
+      <c r="P85" s="8" t="inlineStr"/>
       <c r="Q85" s="8" t="inlineStr"/>
       <c r="R85" s="8" t="inlineStr"/>
       <c r="S85" s="8" t="inlineStr"/>
@@ -4877,20 +5351,30 @@
       <c r="U85" s="8" t="inlineStr"/>
       <c r="V85" s="8" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr"/>
-      <c r="X85" s="9" t="n">
-        <v>1430</v>
-      </c>
-      <c r="Y85" s="10" t="inlineStr"/>
-      <c r="Z85" s="11" t="inlineStr"/>
+      <c r="X85" s="8" t="inlineStr"/>
+      <c r="Y85" s="8" t="inlineStr"/>
+      <c r="Z85" s="9" t="n">
+        <v>13229.25</v>
+      </c>
+      <c r="AA85" s="9" t="n">
+        <v>1443.625</v>
+      </c>
+      <c r="AB85" s="11" t="n">
+        <v>0.04844476734430894</v>
+      </c>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>13335.00</t>
+        </is>
+      </c>
       <c r="D86" s="8" t="inlineStr"/>
       <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="8" t="inlineStr"/>
@@ -4898,24 +5382,12 @@
       <c r="H86" s="8" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr"/>
       <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr">
-        <is>
-          <t>1310.00</t>
-        </is>
-      </c>
+      <c r="K86" s="8" t="inlineStr"/>
       <c r="L86" s="8" t="inlineStr"/>
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr"/>
-      <c r="O86" s="8" t="inlineStr">
-        <is>
-          <t>1500.00</t>
-        </is>
-      </c>
-      <c r="P86" s="8" t="inlineStr">
-        <is>
-          <t>1030.00</t>
-        </is>
-      </c>
+      <c r="O86" s="8" t="inlineStr"/>
+      <c r="P86" s="8" t="inlineStr"/>
       <c r="Q86" s="8" t="inlineStr"/>
       <c r="R86" s="8" t="inlineStr"/>
       <c r="S86" s="8" t="inlineStr"/>
@@ -4923,47 +5395,37 @@
       <c r="U86" s="8" t="inlineStr"/>
       <c r="V86" s="8" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr"/>
-      <c r="X86" s="9" t="inlineStr"/>
-      <c r="Y86" s="10" t="inlineStr"/>
-      <c r="Z86" s="11" t="inlineStr"/>
+      <c r="X86" s="8" t="inlineStr"/>
+      <c r="Y86" s="8" t="inlineStr"/>
+      <c r="Z86" s="9" t="inlineStr"/>
+      <c r="AA86" s="10" t="inlineStr"/>
+      <c r="AB86" s="11" t="inlineStr"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>13410.50</t>
+        </is>
+      </c>
       <c r="D87" s="8" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>1760.00</t>
-        </is>
-      </c>
+      <c r="E87" s="8" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr"/>
       <c r="G87" s="8" t="inlineStr"/>
       <c r="H87" s="8" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr"/>
       <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="8" t="inlineStr">
-        <is>
-          <t>1590.00</t>
-        </is>
-      </c>
+      <c r="K87" s="8" t="inlineStr"/>
       <c r="L87" s="8" t="inlineStr"/>
       <c r="M87" s="8" t="inlineStr"/>
       <c r="N87" s="8" t="inlineStr"/>
-      <c r="O87" s="8" t="inlineStr">
-        <is>
-          <t>1670.00</t>
-        </is>
-      </c>
-      <c r="P87" s="8" t="inlineStr">
-        <is>
-          <t>760.00</t>
-        </is>
-      </c>
+      <c r="O87" s="8" t="inlineStr"/>
+      <c r="P87" s="8" t="inlineStr"/>
       <c r="Q87" s="8" t="inlineStr"/>
       <c r="R87" s="8" t="inlineStr"/>
       <c r="S87" s="8" t="inlineStr"/>
@@ -4971,27 +5433,23 @@
       <c r="U87" s="8" t="inlineStr"/>
       <c r="V87" s="8" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr"/>
-      <c r="X87" s="9" t="n">
-        <v>1445</v>
-      </c>
-      <c r="Y87" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z87" s="11" t="n">
-        <v>0.005028494803888703</v>
-      </c>
+      <c r="X87" s="8" t="inlineStr"/>
+      <c r="Y87" s="8" t="inlineStr"/>
+      <c r="Z87" s="9" t="inlineStr"/>
+      <c r="AA87" s="10" t="inlineStr"/>
+      <c r="AB87" s="11" t="inlineStr"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Krull
-Random: 1598.0
-Human: 2665.5</t>
+          <t>Jamesbond
+Random: 29.0
+Human: 302.8</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 8413</t>
+          <t>STORM (논문): 509</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -5015,12 +5473,14 @@
       <c r="U88" s="4" t="inlineStr"/>
       <c r="V88" s="4" t="inlineStr"/>
       <c r="W88" s="4" t="inlineStr"/>
-      <c r="X88" s="5" t="inlineStr"/>
-      <c r="Y88" s="6" t="n">
-        <v>-2583.375</v>
-      </c>
-      <c r="Z88" s="7" t="n">
-        <v>-2.420023419203747</v>
+      <c r="X88" s="4" t="inlineStr"/>
+      <c r="Y88" s="4" t="inlineStr"/>
+      <c r="Z88" s="5" t="inlineStr"/>
+      <c r="AA88" s="6" t="n">
+        <v>-35.66666666666669</v>
+      </c>
+      <c r="AB88" s="7" t="n">
+        <v>-0.1302654005356709</v>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1">
@@ -5030,64 +5490,50 @@
           <t>Retrieval 미사용</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr"/>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>490.00</t>
+        </is>
+      </c>
       <c r="D89" s="8" t="inlineStr"/>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>6202.00</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>5689.00</t>
-        </is>
-      </c>
+      <c r="E89" s="8" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr"/>
       <c r="G89" s="8" t="inlineStr"/>
       <c r="H89" s="8" t="inlineStr"/>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>6107.50</t>
-        </is>
-      </c>
+      <c r="I89" s="8" t="inlineStr"/>
       <c r="J89" s="8" t="inlineStr"/>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
-          <t>4708.50</t>
-        </is>
-      </c>
-      <c r="L89" s="13" t="inlineStr">
-        <is>
-          <t>5913.50</t>
-        </is>
-      </c>
+      <c r="K89" s="8" t="inlineStr">
+        <is>
+          <t>532.50, 537.50</t>
+        </is>
+      </c>
+      <c r="L89" s="8" t="inlineStr"/>
       <c r="M89" s="8" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr"/>
       <c r="O89" s="8" t="inlineStr">
         <is>
-          <t>5228.50</t>
+          <t>522.50</t>
         </is>
       </c>
       <c r="P89" s="8" t="inlineStr"/>
-      <c r="Q89" s="8" t="inlineStr">
-        <is>
-          <t>5599.00</t>
-        </is>
-      </c>
+      <c r="Q89" s="8" t="inlineStr"/>
       <c r="R89" s="8" t="inlineStr"/>
       <c r="S89" s="8" t="inlineStr"/>
       <c r="T89" s="8" t="inlineStr"/>
       <c r="U89" s="8" t="inlineStr"/>
-      <c r="V89" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
+      <c r="V89" s="8" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr"/>
-      <c r="X89" s="9" t="n">
-        <v>5829.625</v>
-      </c>
-      <c r="Y89" s="10" t="inlineStr"/>
-      <c r="Z89" s="11" t="inlineStr"/>
+      <c r="X89" s="8" t="inlineStr">
+        <is>
+          <t>365.00</t>
+        </is>
+      </c>
+      <c r="Y89" s="8" t="inlineStr"/>
+      <c r="Z89" s="9" t="n">
+        <v>473.3333333333333</v>
+      </c>
+      <c r="AA89" s="10" t="inlineStr"/>
+      <c r="AB89" s="11" t="inlineStr"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="1" t="n"/>
@@ -5104,34 +5550,28 @@
       <c r="H90" s="8" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr"/>
       <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="13" t="inlineStr">
-        <is>
-          <t>4851.00</t>
-        </is>
-      </c>
-      <c r="L90" s="13" t="inlineStr">
-        <is>
-          <t>6044.00</t>
-        </is>
-      </c>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="8" t="inlineStr"/>
       <c r="M90" s="8" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr"/>
-      <c r="O90" s="8" t="inlineStr"/>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>575.00</t>
+        </is>
+      </c>
       <c r="P90" s="8" t="inlineStr"/>
       <c r="Q90" s="8" t="inlineStr"/>
       <c r="R90" s="8" t="inlineStr"/>
       <c r="S90" s="8" t="inlineStr"/>
       <c r="T90" s="8" t="inlineStr"/>
       <c r="U90" s="8" t="inlineStr"/>
-      <c r="V90" s="8" t="inlineStr">
-        <is>
-          <t>6587.00</t>
-        </is>
-      </c>
+      <c r="V90" s="8" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr"/>
-      <c r="X90" s="9" t="inlineStr"/>
-      <c r="Y90" s="10" t="inlineStr"/>
-      <c r="Z90" s="11" t="inlineStr"/>
+      <c r="X90" s="8" t="inlineStr"/>
+      <c r="Y90" s="8" t="inlineStr"/>
+      <c r="Z90" s="9" t="inlineStr"/>
+      <c r="AA90" s="10" t="inlineStr"/>
+      <c r="AB90" s="11" t="inlineStr"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="1" t="n"/>
@@ -5142,74 +5582,60 @@
       </c>
       <c r="C91" s="8" t="inlineStr"/>
       <c r="D91" s="8" t="inlineStr"/>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>6576.50</t>
-        </is>
-      </c>
+      <c r="E91" s="8" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr"/>
       <c r="G91" s="8" t="inlineStr"/>
       <c r="H91" s="8" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr"/>
       <c r="J91" s="8" t="inlineStr"/>
-      <c r="K91" s="13" t="inlineStr">
-        <is>
-          <t>5279.50</t>
-        </is>
-      </c>
-      <c r="L91" s="13" t="inlineStr">
-        <is>
-          <t>5889.50</t>
-        </is>
-      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>567.50, 660.00</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="inlineStr"/>
       <c r="M91" s="8" t="inlineStr"/>
       <c r="N91" s="8" t="inlineStr"/>
       <c r="O91" s="8" t="inlineStr">
         <is>
-          <t>6447.50</t>
-        </is>
-      </c>
-      <c r="P91" s="15" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="Q91" s="8" t="inlineStr">
-        <is>
-          <t>6828.50</t>
-        </is>
-      </c>
+          <t>665.00</t>
+        </is>
+      </c>
+      <c r="P91" s="8" t="inlineStr"/>
+      <c r="Q91" s="8" t="inlineStr"/>
       <c r="R91" s="8" t="inlineStr"/>
       <c r="S91" s="8" t="inlineStr"/>
       <c r="T91" s="8" t="inlineStr"/>
       <c r="U91" s="8" t="inlineStr"/>
-      <c r="V91" s="8" t="inlineStr">
-        <is>
-          <t>6796.50</t>
-        </is>
-      </c>
+      <c r="V91" s="8" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr"/>
-      <c r="X91" s="9" t="n">
-        <v>6662.25</v>
-      </c>
-      <c r="Y91" s="9" t="n">
-        <v>832.625</v>
-      </c>
-      <c r="Z91" s="11" t="n">
-        <v>0.779976580796253</v>
+      <c r="X91" s="8" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
+      <c r="Y91" s="8" t="inlineStr"/>
+      <c r="Z91" s="9" t="n">
+        <v>535.8333333333334</v>
+      </c>
+      <c r="AA91" s="9" t="n">
+        <v>62.50000000000006</v>
+      </c>
+      <c r="AB91" s="11" t="n">
+        <v>0.2282688093498906</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KungFuMaster
-Random: 258.5
-Human: 22736.3</t>
+          <t>Kangaroo
+Random: 52.0
+Human: 3035.0</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>STORM (논문): 26182</t>
+          <t>STORM (논문): 4208</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -5233,12 +5659,14 @@
       <c r="U92" s="4" t="inlineStr"/>
       <c r="V92" s="4" t="inlineStr"/>
       <c r="W92" s="4" t="inlineStr"/>
-      <c r="X92" s="5" t="inlineStr"/>
-      <c r="Y92" s="6" t="n">
-        <v>-1044.5</v>
-      </c>
-      <c r="Z92" s="7" t="n">
-        <v>-0.04646807071866464</v>
+      <c r="X92" s="4" t="inlineStr"/>
+      <c r="Y92" s="4" t="inlineStr"/>
+      <c r="Z92" s="5" t="inlineStr"/>
+      <c r="AA92" s="6" t="n">
+        <v>-2778</v>
+      </c>
+      <c r="AB92" s="7" t="n">
+        <v>-0.9312772376801878</v>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1">
@@ -5252,7 +5680,7 @@
       <c r="D93" s="8" t="inlineStr"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>26460.00</t>
+          <t>1770.00</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr"/>
@@ -5262,18 +5690,26 @@
       <c r="J93" s="8" t="inlineStr"/>
       <c r="K93" s="8" t="inlineStr">
         <is>
-          <t>23815.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
-          <t>20895.00</t>
+          <t>1730.00</t>
         </is>
       </c>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
-      <c r="O93" s="8" t="inlineStr"/>
-      <c r="P93" s="8" t="inlineStr"/>
+      <c r="O93" s="8" t="inlineStr">
+        <is>
+          <t>1550.00</t>
+        </is>
+      </c>
+      <c r="P93" s="8" t="inlineStr">
+        <is>
+          <t>930.00</t>
+        </is>
+      </c>
       <c r="Q93" s="8" t="inlineStr"/>
       <c r="R93" s="8" t="inlineStr"/>
       <c r="S93" s="8" t="inlineStr"/>
@@ -5281,26 +5717,24 @@
       <c r="U93" s="8" t="inlineStr"/>
       <c r="V93" s="8" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr"/>
-      <c r="X93" s="9" t="n">
-        <v>25137.5</v>
-      </c>
-      <c r="Y93" s="10" t="inlineStr"/>
-      <c r="Z93" s="11" t="inlineStr"/>
+      <c r="X93" s="8" t="inlineStr"/>
+      <c r="Y93" s="8" t="inlineStr"/>
+      <c r="Z93" s="9" t="n">
+        <v>1430</v>
+      </c>
+      <c r="AA93" s="10" t="inlineStr"/>
+      <c r="AB93" s="11" t="inlineStr"/>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr"/>
       <c r="D94" s="8" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>30110.00</t>
-        </is>
-      </c>
+      <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" s="8" t="inlineStr"/>
       <c r="G94" s="8" t="inlineStr"/>
       <c r="H94" s="8" t="inlineStr"/>
@@ -5308,14 +5742,22 @@
       <c r="J94" s="8" t="inlineStr"/>
       <c r="K94" s="8" t="inlineStr">
         <is>
-          <t>20245.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="L94" s="8" t="inlineStr"/>
       <c r="M94" s="8" t="inlineStr"/>
       <c r="N94" s="8" t="inlineStr"/>
-      <c r="O94" s="8" t="inlineStr"/>
-      <c r="P94" s="8" t="inlineStr"/>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="P94" s="8" t="inlineStr">
+        <is>
+          <t>1030.00</t>
+        </is>
+      </c>
       <c r="Q94" s="8" t="inlineStr"/>
       <c r="R94" s="8" t="inlineStr"/>
       <c r="S94" s="8" t="inlineStr"/>
@@ -5323,149 +5765,189 @@
       <c r="U94" s="8" t="inlineStr"/>
       <c r="V94" s="8" t="inlineStr"/>
       <c r="W94" s="8" t="inlineStr"/>
-      <c r="X94" s="9" t="n">
-        <v>25177.5</v>
-      </c>
-      <c r="Y94" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z94" s="11" t="n">
-        <v>0.001779533584247569</v>
-      </c>
+      <c r="X94" s="8" t="inlineStr"/>
+      <c r="Y94" s="8" t="inlineStr"/>
+      <c r="Z94" s="9" t="inlineStr"/>
+      <c r="AA94" s="10" t="inlineStr"/>
+      <c r="AB94" s="11" t="inlineStr"/>
     </row>
     <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>MsPacman
-Random: 307.3
-Human: 6951.6</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 2673</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr"/>
-      <c r="D95" s="4" t="inlineStr"/>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr"/>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
-      <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="inlineStr"/>
-      <c r="N95" s="4" t="inlineStr"/>
-      <c r="O95" s="4" t="inlineStr"/>
-      <c r="P95" s="4" t="inlineStr"/>
-      <c r="Q95" s="4" t="inlineStr"/>
-      <c r="R95" s="4" t="inlineStr"/>
-      <c r="S95" s="4" t="inlineStr"/>
-      <c r="T95" s="4" t="inlineStr"/>
-      <c r="U95" s="4" t="inlineStr"/>
-      <c r="V95" s="4" t="inlineStr"/>
-      <c r="W95" s="4" t="inlineStr"/>
-      <c r="X95" s="5" t="inlineStr"/>
-      <c r="Y95" s="6" t="n">
-        <v>-602</v>
-      </c>
-      <c r="Z95" s="7" t="n">
-        <v>-0.09060397634062278</v>
+      <c r="A95" s="1" t="n"/>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr"/>
+      <c r="D95" s="8" t="inlineStr"/>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>1590.00</t>
+        </is>
+      </c>
+      <c r="L95" s="8" t="inlineStr"/>
+      <c r="M95" s="8" t="inlineStr"/>
+      <c r="N95" s="8" t="inlineStr"/>
+      <c r="O95" s="8" t="inlineStr">
+        <is>
+          <t>1670.00</t>
+        </is>
+      </c>
+      <c r="P95" s="8" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
+      <c r="Q95" s="8" t="inlineStr"/>
+      <c r="R95" s="15" t="inlineStr">
+        <is>
+          <t>2900.00</t>
+        </is>
+      </c>
+      <c r="S95" s="8" t="inlineStr"/>
+      <c r="T95" s="8" t="inlineStr"/>
+      <c r="U95" s="8" t="inlineStr"/>
+      <c r="V95" s="8" t="inlineStr"/>
+      <c r="W95" s="8" t="inlineStr"/>
+      <c r="X95" s="8" t="inlineStr"/>
+      <c r="Y95" s="8" t="inlineStr"/>
+      <c r="Z95" s="9" t="n">
+        <v>1445</v>
+      </c>
+      <c r="AA95" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB95" s="11" t="n">
+        <v>0.005028494803888703</v>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="1" t="n"/>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr">
-        <is>
-          <t>1807.50</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="inlineStr"/>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>2007.00</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr"/>
-      <c r="K96" s="8" t="inlineStr">
-        <is>
-          <t>2388.00</t>
-        </is>
-      </c>
-      <c r="L96" s="8" t="inlineStr"/>
-      <c r="M96" s="8" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
-      <c r="O96" s="8" t="inlineStr">
-        <is>
-          <t>1754.00</t>
-        </is>
-      </c>
-      <c r="P96" s="8" t="inlineStr"/>
-      <c r="Q96" s="8" t="inlineStr"/>
-      <c r="R96" s="8" t="inlineStr"/>
-      <c r="S96" s="8" t="inlineStr"/>
-      <c r="T96" s="8" t="inlineStr"/>
-      <c r="U96" s="8" t="inlineStr"/>
-      <c r="V96" s="8" t="inlineStr"/>
-      <c r="W96" s="8" t="inlineStr"/>
-      <c r="X96" s="9" t="n">
-        <v>2071</v>
-      </c>
-      <c r="Y96" s="10" t="inlineStr"/>
-      <c r="Z96" s="11" t="inlineStr"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Krull
+Random: 1598.0
+Human: 2665.5</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 8413</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr"/>
+      <c r="L96" s="4" t="inlineStr"/>
+      <c r="M96" s="4" t="inlineStr"/>
+      <c r="N96" s="4" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr"/>
+      <c r="P96" s="4" t="inlineStr"/>
+      <c r="Q96" s="4" t="inlineStr"/>
+      <c r="R96" s="4" t="inlineStr"/>
+      <c r="S96" s="4" t="inlineStr"/>
+      <c r="T96" s="4" t="inlineStr"/>
+      <c r="U96" s="4" t="inlineStr"/>
+      <c r="V96" s="4" t="inlineStr"/>
+      <c r="W96" s="4" t="inlineStr"/>
+      <c r="X96" s="4" t="inlineStr"/>
+      <c r="Y96" s="4" t="inlineStr"/>
+      <c r="Z96" s="5" t="inlineStr"/>
+      <c r="AA96" s="6" t="n">
+        <v>-2583.375</v>
+      </c>
+      <c r="AB96" s="7" t="n">
+        <v>-2.420023419203747</v>
+      </c>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
       <c r="D97" s="8" t="inlineStr"/>
-      <c r="E97" s="8" t="inlineStr"/>
-      <c r="F97" s="8" t="inlineStr"/>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>6202.00</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>5689.00</t>
+        </is>
+      </c>
       <c r="G97" s="8" t="inlineStr"/>
       <c r="H97" s="8" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>6107.50</t>
+        </is>
+      </c>
       <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr"/>
-      <c r="L97" s="8" t="inlineStr"/>
+      <c r="K97" s="12" t="inlineStr">
+        <is>
+          <t>4708.50</t>
+        </is>
+      </c>
+      <c r="L97" s="12" t="inlineStr">
+        <is>
+          <t>5913.50</t>
+        </is>
+      </c>
       <c r="M97" s="8" t="inlineStr"/>
       <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="8" t="inlineStr">
         <is>
-          <t>2110.50</t>
-        </is>
-      </c>
-      <c r="P97" s="8" t="inlineStr"/>
-      <c r="Q97" s="8" t="inlineStr"/>
-      <c r="R97" s="8" t="inlineStr"/>
+          <t>5228.50</t>
+        </is>
+      </c>
+      <c r="P97" s="12" t="inlineStr"/>
+      <c r="Q97" s="8" t="inlineStr">
+        <is>
+          <t>5599.00</t>
+        </is>
+      </c>
+      <c r="R97" s="12" t="inlineStr"/>
       <c r="S97" s="8" t="inlineStr"/>
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr"/>
-      <c r="X97" s="9" t="inlineStr"/>
-      <c r="Y97" s="10" t="inlineStr"/>
-      <c r="Z97" s="11" t="inlineStr"/>
+      <c r="X97" s="8" t="inlineStr">
+        <is>
+          <t>6289.00</t>
+        </is>
+      </c>
+      <c r="Y97" s="8" t="inlineStr"/>
+      <c r="Z97" s="9" t="n">
+        <v>5829.625</v>
+      </c>
+      <c r="AA97" s="10" t="inlineStr"/>
+      <c r="AB97" s="11" t="inlineStr"/>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr"/>
@@ -5476,184 +5958,222 @@
       <c r="H98" s="8" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr"/>
       <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="8" t="inlineStr">
-        <is>
-          <t>2250.00</t>
-        </is>
-      </c>
-      <c r="L98" s="8" t="inlineStr"/>
+      <c r="K98" s="12" t="inlineStr">
+        <is>
+          <t>4851.00</t>
+        </is>
+      </c>
+      <c r="L98" s="12" t="inlineStr">
+        <is>
+          <t>6044.00</t>
+        </is>
+      </c>
       <c r="M98" s="8" t="inlineStr"/>
       <c r="N98" s="8" t="inlineStr"/>
-      <c r="O98" s="8" t="inlineStr">
-        <is>
-          <t>1886.50</t>
-        </is>
-      </c>
-      <c r="P98" s="8" t="inlineStr"/>
+      <c r="O98" s="8" t="inlineStr"/>
+      <c r="P98" s="12" t="inlineStr"/>
       <c r="Q98" s="8" t="inlineStr"/>
-      <c r="R98" s="8" t="inlineStr"/>
+      <c r="R98" s="12" t="inlineStr"/>
       <c r="S98" s="8" t="inlineStr"/>
       <c r="T98" s="8" t="inlineStr"/>
       <c r="U98" s="8" t="inlineStr"/>
       <c r="V98" s="8" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr"/>
-      <c r="X98" s="9" t="n">
-        <v>2068.25</v>
-      </c>
-      <c r="Y98" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z98" s="11" t="n">
-        <v>-0.0004138885962403865</v>
-      </c>
+      <c r="X98" s="8" t="inlineStr">
+        <is>
+          <t>6587.00</t>
+        </is>
+      </c>
+      <c r="Y98" s="8" t="inlineStr"/>
+      <c r="Z98" s="9" t="inlineStr"/>
+      <c r="AA98" s="10" t="inlineStr"/>
+      <c r="AB98" s="11" t="inlineStr"/>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr"/>
       <c r="D99" s="8" t="inlineStr"/>
-      <c r="E99" s="8" t="inlineStr"/>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>6576.50</t>
+        </is>
+      </c>
       <c r="F99" s="8" t="inlineStr"/>
       <c r="G99" s="8" t="inlineStr"/>
       <c r="H99" s="8" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr"/>
       <c r="J99" s="8" t="inlineStr"/>
-      <c r="K99" s="8" t="inlineStr"/>
-      <c r="L99" s="8" t="inlineStr"/>
+      <c r="K99" s="12" t="inlineStr">
+        <is>
+          <t>5279.50</t>
+        </is>
+      </c>
+      <c r="L99" s="12" t="inlineStr">
+        <is>
+          <t>5889.50</t>
+        </is>
+      </c>
       <c r="M99" s="8" t="inlineStr"/>
       <c r="N99" s="8" t="inlineStr"/>
       <c r="O99" s="8" t="inlineStr">
         <is>
-          <t>2197.00</t>
-        </is>
-      </c>
-      <c r="P99" s="8" t="inlineStr"/>
-      <c r="Q99" s="8" t="inlineStr"/>
-      <c r="R99" s="8" t="inlineStr"/>
+          <t>6447.50</t>
+        </is>
+      </c>
+      <c r="P99" s="13" t="inlineStr">
+        <is>
+          <t>5900.50</t>
+        </is>
+      </c>
+      <c r="Q99" s="8" t="inlineStr">
+        <is>
+          <t>6828.50</t>
+        </is>
+      </c>
+      <c r="R99" s="13" t="inlineStr">
+        <is>
+          <t>5596.50</t>
+        </is>
+      </c>
       <c r="S99" s="8" t="inlineStr"/>
       <c r="T99" s="8" t="inlineStr"/>
       <c r="U99" s="8" t="inlineStr"/>
       <c r="V99" s="8" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr"/>
-      <c r="X99" s="9" t="inlineStr"/>
-      <c r="Y99" s="10" t="inlineStr"/>
-      <c r="Z99" s="11" t="inlineStr"/>
+      <c r="X99" s="8" t="inlineStr">
+        <is>
+          <t>6796.50</t>
+        </is>
+      </c>
+      <c r="Y99" s="8" t="inlineStr"/>
+      <c r="Z99" s="9" t="n">
+        <v>6662.25</v>
+      </c>
+      <c r="AA99" s="9" t="n">
+        <v>832.625</v>
+      </c>
+      <c r="AB99" s="11" t="n">
+        <v>0.779976580796253</v>
+      </c>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="1" t="n"/>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr"/>
-      <c r="D100" s="8" t="inlineStr"/>
-      <c r="E100" s="8" t="inlineStr"/>
-      <c r="F100" s="8" t="inlineStr"/>
-      <c r="G100" s="8" t="inlineStr"/>
-      <c r="H100" s="8" t="inlineStr"/>
-      <c r="I100" s="8" t="inlineStr"/>
-      <c r="J100" s="8" t="inlineStr"/>
-      <c r="K100" s="8" t="inlineStr"/>
-      <c r="L100" s="8" t="inlineStr"/>
-      <c r="M100" s="8" t="inlineStr"/>
-      <c r="N100" s="8" t="inlineStr"/>
-      <c r="O100" s="8" t="inlineStr">
-        <is>
-          <t>2170.00</t>
-        </is>
-      </c>
-      <c r="P100" s="8" t="inlineStr"/>
-      <c r="Q100" s="8" t="inlineStr"/>
-      <c r="R100" s="8" t="inlineStr"/>
-      <c r="S100" s="8" t="inlineStr"/>
-      <c r="T100" s="8" t="inlineStr"/>
-      <c r="U100" s="8" t="inlineStr"/>
-      <c r="V100" s="8" t="inlineStr"/>
-      <c r="W100" s="8" t="inlineStr"/>
-      <c r="X100" s="9" t="inlineStr"/>
-      <c r="Y100" s="10" t="inlineStr"/>
-      <c r="Z100" s="11" t="inlineStr"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>KungFuMaster
+Random: 258.5
+Human: 22736.3</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 26182</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr"/>
+      <c r="L100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr"/>
+      <c r="P100" s="4" t="inlineStr"/>
+      <c r="Q100" s="4" t="inlineStr"/>
+      <c r="R100" s="4" t="inlineStr"/>
+      <c r="S100" s="4" t="inlineStr"/>
+      <c r="T100" s="4" t="inlineStr"/>
+      <c r="U100" s="4" t="inlineStr"/>
+      <c r="V100" s="4" t="inlineStr"/>
+      <c r="W100" s="4" t="inlineStr"/>
+      <c r="X100" s="4" t="inlineStr"/>
+      <c r="Y100" s="4" t="inlineStr"/>
+      <c r="Z100" s="5" t="inlineStr"/>
+      <c r="AA100" s="6" t="n">
+        <v>-1044.5</v>
+      </c>
+      <c r="AB100" s="7" t="n">
+        <v>-0.04646807071866464</v>
+      </c>
     </row>
     <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Pong
-Random: -20.7
-Human: 14.6</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr"/>
-      <c r="D101" s="4" t="inlineStr"/>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr"/>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="4" t="inlineStr"/>
-      <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="4" t="inlineStr"/>
-      <c r="M101" s="4" t="inlineStr"/>
-      <c r="N101" s="4" t="inlineStr"/>
-      <c r="O101" s="4" t="inlineStr"/>
-      <c r="P101" s="4" t="inlineStr"/>
-      <c r="Q101" s="4" t="inlineStr"/>
-      <c r="R101" s="4" t="inlineStr"/>
-      <c r="S101" s="4" t="inlineStr"/>
-      <c r="T101" s="4" t="inlineStr"/>
-      <c r="U101" s="4" t="inlineStr"/>
-      <c r="V101" s="4" t="inlineStr"/>
-      <c r="W101" s="4" t="inlineStr"/>
-      <c r="X101" s="5" t="inlineStr"/>
-      <c r="Y101" s="6" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="Z101" s="7" t="n">
-        <v>-0.1529745042492918</v>
-      </c>
+      <c r="A101" s="1" t="n"/>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr"/>
+      <c r="D101" s="8" t="inlineStr"/>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>26460.00</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr"/>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="inlineStr"/>
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>23815.00</t>
+        </is>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>20895.00</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="inlineStr"/>
+      <c r="N101" s="8" t="inlineStr"/>
+      <c r="O101" s="8" t="inlineStr"/>
+      <c r="P101" s="8" t="inlineStr"/>
+      <c r="Q101" s="8" t="inlineStr"/>
+      <c r="R101" s="8" t="inlineStr"/>
+      <c r="S101" s="8" t="inlineStr"/>
+      <c r="T101" s="8" t="inlineStr"/>
+      <c r="U101" s="8" t="inlineStr"/>
+      <c r="V101" s="8" t="inlineStr"/>
+      <c r="W101" s="8" t="inlineStr"/>
+      <c r="X101" s="8" t="inlineStr"/>
+      <c r="Y101" s="8" t="inlineStr"/>
+      <c r="Z101" s="9" t="n">
+        <v>25137.5</v>
+      </c>
+      <c r="AA101" s="10" t="inlineStr"/>
+      <c r="AB101" s="11" t="inlineStr"/>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr"/>
       <c r="D102" s="8" t="inlineStr"/>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
+          <t>16365.00</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr"/>
       <c r="G102" s="8" t="inlineStr"/>
       <c r="H102" s="8" t="inlineStr"/>
       <c r="I102" s="8" t="inlineStr"/>
       <c r="J102" s="8" t="inlineStr"/>
-      <c r="K102" s="8" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
+      <c r="K102" s="8" t="inlineStr"/>
+      <c r="L102" s="8" t="inlineStr"/>
       <c r="M102" s="8" t="inlineStr"/>
       <c r="N102" s="8" t="inlineStr"/>
       <c r="O102" s="8" t="inlineStr"/>
@@ -5665,11 +6185,11 @@
       <c r="U102" s="8" t="inlineStr"/>
       <c r="V102" s="8" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr"/>
-      <c r="X102" s="9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y102" s="10" t="inlineStr"/>
-      <c r="Z102" s="11" t="inlineStr"/>
+      <c r="X102" s="8" t="inlineStr"/>
+      <c r="Y102" s="8" t="inlineStr"/>
+      <c r="Z102" s="9" t="inlineStr"/>
+      <c r="AA102" s="10" t="inlineStr"/>
+      <c r="AB102" s="11" t="inlineStr"/>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="1" t="n"/>
@@ -5680,30 +6200,22 @@
       </c>
       <c r="C103" s="8" t="inlineStr"/>
       <c r="D103" s="8" t="inlineStr"/>
-      <c r="E103" s="8" t="inlineStr"/>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>8.20</t>
-        </is>
-      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>30110.00</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr"/>
       <c r="G103" s="8" t="inlineStr"/>
       <c r="H103" s="8" t="inlineStr"/>
-      <c r="I103" s="8" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
+      <c r="I103" s="8" t="inlineStr"/>
       <c r="J103" s="8" t="inlineStr"/>
       <c r="K103" s="8" t="inlineStr">
         <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="L103" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+          <t>20245.00</t>
+        </is>
+      </c>
+      <c r="L103" s="8" t="inlineStr"/>
       <c r="M103" s="8" t="inlineStr"/>
       <c r="N103" s="8" t="inlineStr"/>
       <c r="O103" s="8" t="inlineStr"/>
@@ -5715,254 +6227,212 @@
       <c r="U103" s="8" t="inlineStr"/>
       <c r="V103" s="8" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr"/>
-      <c r="X103" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y103" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z103" s="11" t="n">
-        <v>0.09631728045325781</v>
+      <c r="X103" s="8" t="inlineStr"/>
+      <c r="Y103" s="8" t="inlineStr"/>
+      <c r="Z103" s="9" t="n">
+        <v>25177.5</v>
+      </c>
+      <c r="AA103" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB103" s="11" t="n">
+        <v>0.001779533584247569</v>
       </c>
     </row>
     <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>PrivateEye
-Random: 24.9
-Human: 69571.3</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7781</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr"/>
-      <c r="D104" s="4" t="inlineStr"/>
-      <c r="E104" s="4" t="inlineStr"/>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr"/>
-      <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="4" t="inlineStr"/>
-      <c r="K104" s="4" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr"/>
-      <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr"/>
-      <c r="O104" s="4" t="inlineStr"/>
-      <c r="P104" s="4" t="inlineStr"/>
-      <c r="Q104" s="4" t="inlineStr"/>
-      <c r="R104" s="4" t="inlineStr"/>
-      <c r="S104" s="4" t="inlineStr"/>
-      <c r="T104" s="4" t="inlineStr"/>
-      <c r="U104" s="4" t="inlineStr"/>
-      <c r="V104" s="4" t="inlineStr"/>
-      <c r="W104" s="4" t="inlineStr"/>
-      <c r="X104" s="5" t="inlineStr"/>
-      <c r="Y104" s="6" t="n">
-        <v>-6778.35</v>
-      </c>
-      <c r="Z104" s="7" t="n">
-        <v>-0.09746514557187719</v>
-      </c>
+      <c r="A104" s="1" t="n"/>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr"/>
+      <c r="D104" s="8" t="inlineStr"/>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>17935.00</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr"/>
+      <c r="H104" s="8" t="inlineStr"/>
+      <c r="I104" s="8" t="inlineStr"/>
+      <c r="J104" s="8" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr"/>
+      <c r="L104" s="8" t="inlineStr"/>
+      <c r="M104" s="8" t="inlineStr"/>
+      <c r="N104" s="8" t="inlineStr"/>
+      <c r="O104" s="8" t="inlineStr"/>
+      <c r="P104" s="8" t="inlineStr"/>
+      <c r="Q104" s="8" t="inlineStr"/>
+      <c r="R104" s="8" t="inlineStr"/>
+      <c r="S104" s="8" t="inlineStr"/>
+      <c r="T104" s="8" t="inlineStr"/>
+      <c r="U104" s="8" t="inlineStr"/>
+      <c r="V104" s="8" t="inlineStr"/>
+      <c r="W104" s="8" t="inlineStr"/>
+      <c r="X104" s="8" t="inlineStr"/>
+      <c r="Y104" s="8" t="inlineStr"/>
+      <c r="Z104" s="9" t="inlineStr"/>
+      <c r="AA104" s="10" t="inlineStr"/>
+      <c r="AB104" s="11" t="inlineStr"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>75.30</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr"/>
       <c r="D105" s="8" t="inlineStr"/>
-      <c r="E105" s="8" t="inlineStr"/>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>21915.00</t>
+        </is>
+      </c>
       <c r="F105" s="8" t="inlineStr"/>
       <c r="G105" s="8" t="inlineStr"/>
       <c r="H105" s="8" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr"/>
       <c r="J105" s="8" t="inlineStr"/>
-      <c r="K105" s="8" t="inlineStr">
-        <is>
-          <t>199.35</t>
-        </is>
-      </c>
+      <c r="K105" s="8" t="inlineStr"/>
       <c r="L105" s="8" t="inlineStr"/>
       <c r="M105" s="8" t="inlineStr"/>
       <c r="N105" s="8" t="inlineStr"/>
-      <c r="O105" s="13" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="P105" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q105" s="8" t="inlineStr">
-        <is>
-          <t>3551.75</t>
-        </is>
-      </c>
+      <c r="O105" s="8" t="inlineStr"/>
+      <c r="P105" s="8" t="inlineStr"/>
+      <c r="Q105" s="8" t="inlineStr"/>
       <c r="R105" s="8" t="inlineStr"/>
       <c r="S105" s="8" t="inlineStr"/>
       <c r="T105" s="8" t="inlineStr"/>
       <c r="U105" s="8" t="inlineStr"/>
-      <c r="V105" s="8" t="inlineStr">
-        <is>
-          <t>159.50</t>
-        </is>
-      </c>
+      <c r="V105" s="8" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr"/>
-      <c r="X105" s="9" t="n">
-        <v>1002.65</v>
-      </c>
-      <c r="Y105" s="10" t="inlineStr"/>
-      <c r="Z105" s="11" t="inlineStr"/>
+      <c r="X105" s="8" t="inlineStr"/>
+      <c r="Y105" s="8" t="inlineStr"/>
+      <c r="Z105" s="9" t="inlineStr"/>
+      <c r="AA105" s="10" t="inlineStr"/>
+      <c r="AB105" s="11" t="inlineStr"/>
     </row>
     <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="1" t="n"/>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr"/>
-      <c r="D106" s="8" t="inlineStr"/>
-      <c r="E106" s="8" t="inlineStr"/>
-      <c r="F106" s="8" t="inlineStr"/>
-      <c r="G106" s="8" t="inlineStr"/>
-      <c r="H106" s="8" t="inlineStr"/>
-      <c r="I106" s="8" t="inlineStr"/>
-      <c r="J106" s="8" t="inlineStr"/>
-      <c r="K106" s="8" t="inlineStr">
-        <is>
-          <t>191.95</t>
-        </is>
-      </c>
-      <c r="L106" s="8" t="inlineStr"/>
-      <c r="M106" s="8" t="inlineStr"/>
-      <c r="N106" s="8" t="inlineStr"/>
-      <c r="O106" s="13" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="P106" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q106" s="8" t="inlineStr">
-        <is>
-          <t>166.80</t>
-        </is>
-      </c>
-      <c r="R106" s="8" t="inlineStr"/>
-      <c r="S106" s="8" t="inlineStr"/>
-      <c r="T106" s="8" t="inlineStr"/>
-      <c r="U106" s="8" t="inlineStr"/>
-      <c r="V106" s="8" t="inlineStr">
-        <is>
-          <t>153.20</t>
-        </is>
-      </c>
-      <c r="W106" s="8" t="inlineStr"/>
-      <c r="X106" s="9" t="n">
-        <v>152.9875</v>
-      </c>
-      <c r="Y106" s="9" t="n">
-        <v>849.6624999999999</v>
-      </c>
-      <c r="Z106" s="11" t="n">
-        <v>-0.01221720319096315</v>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>MsPacman
+Random: 307.3
+Human: 6951.6</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 2673</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr"/>
+      <c r="J106" s="4" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr"/>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="inlineStr"/>
+      <c r="N106" s="4" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr"/>
+      <c r="P106" s="4" t="inlineStr"/>
+      <c r="Q106" s="4" t="inlineStr"/>
+      <c r="R106" s="4" t="inlineStr"/>
+      <c r="S106" s="4" t="inlineStr"/>
+      <c r="T106" s="4" t="inlineStr"/>
+      <c r="U106" s="4" t="inlineStr"/>
+      <c r="V106" s="4" t="inlineStr"/>
+      <c r="W106" s="4" t="inlineStr"/>
+      <c r="X106" s="4" t="inlineStr"/>
+      <c r="Y106" s="4" t="inlineStr"/>
+      <c r="Z106" s="5" t="inlineStr"/>
+      <c r="AA106" s="6" t="n">
+        <v>-602</v>
+      </c>
+      <c r="AB106" s="7" t="n">
+        <v>-0.09060397634062278</v>
       </c>
     </row>
     <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Qbert
-Random: 163.9
-Human: 13455.0</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4522</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr"/>
-      <c r="D107" s="4" t="inlineStr"/>
-      <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr"/>
-      <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr"/>
-      <c r="K107" s="4" t="inlineStr"/>
-      <c r="L107" s="4" t="inlineStr"/>
-      <c r="M107" s="4" t="inlineStr"/>
-      <c r="N107" s="4" t="inlineStr"/>
-      <c r="O107" s="4" t="inlineStr"/>
-      <c r="P107" s="4" t="inlineStr"/>
-      <c r="Q107" s="4" t="inlineStr"/>
-      <c r="R107" s="4" t="inlineStr"/>
-      <c r="S107" s="4" t="inlineStr"/>
-      <c r="T107" s="4" t="inlineStr"/>
-      <c r="U107" s="4" t="inlineStr"/>
-      <c r="V107" s="4" t="inlineStr"/>
-      <c r="W107" s="4" t="inlineStr"/>
-      <c r="X107" s="5" t="inlineStr"/>
-      <c r="Y107" s="6" t="n">
-        <v>-1662.9375</v>
-      </c>
-      <c r="Z107" s="7" t="n">
-        <v>-0.1251166193919239</v>
-      </c>
+      <c r="A107" s="1" t="n"/>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>1807.50</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr"/>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>2007.00</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr"/>
+      <c r="J107" s="8" t="inlineStr"/>
+      <c r="K107" s="8" t="inlineStr">
+        <is>
+          <t>2388.00</t>
+        </is>
+      </c>
+      <c r="L107" s="8" t="inlineStr"/>
+      <c r="M107" s="8" t="inlineStr"/>
+      <c r="N107" s="8" t="inlineStr"/>
+      <c r="O107" s="8" t="inlineStr">
+        <is>
+          <t>1754.00</t>
+        </is>
+      </c>
+      <c r="P107" s="8" t="inlineStr"/>
+      <c r="Q107" s="8" t="inlineStr"/>
+      <c r="R107" s="8" t="inlineStr"/>
+      <c r="S107" s="8" t="inlineStr"/>
+      <c r="T107" s="8" t="inlineStr"/>
+      <c r="U107" s="8" t="inlineStr"/>
+      <c r="V107" s="8" t="inlineStr"/>
+      <c r="W107" s="8" t="inlineStr"/>
+      <c r="X107" s="8" t="inlineStr"/>
+      <c r="Y107" s="8" t="inlineStr"/>
+      <c r="Z107" s="9" t="n">
+        <v>2071</v>
+      </c>
+      <c r="AA107" s="10" t="inlineStr"/>
+      <c r="AB107" s="11" t="inlineStr"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr"/>
       <c r="D108" s="8" t="inlineStr"/>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
+      <c r="E108" s="8" t="inlineStr"/>
       <c r="F108" s="8" t="inlineStr"/>
       <c r="G108" s="8" t="inlineStr"/>
       <c r="H108" s="8" t="inlineStr"/>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
+      <c r="I108" s="8" t="inlineStr"/>
       <c r="J108" s="8" t="inlineStr"/>
-      <c r="K108" s="8" t="inlineStr">
-        <is>
-          <t>3193.75</t>
-        </is>
-      </c>
+      <c r="K108" s="8" t="inlineStr"/>
       <c r="L108" s="8" t="inlineStr"/>
       <c r="M108" s="8" t="inlineStr"/>
       <c r="N108" s="8" t="inlineStr"/>
       <c r="O108" s="8" t="inlineStr">
         <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
+          <t>2110.50</t>
         </is>
       </c>
       <c r="P108" s="8" t="inlineStr"/>
@@ -5973,46 +6443,38 @@
       <c r="U108" s="8" t="inlineStr"/>
       <c r="V108" s="8" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr"/>
-      <c r="X108" s="9" t="n">
-        <v>2859.0625</v>
-      </c>
-      <c r="Y108" s="10" t="inlineStr"/>
-      <c r="Z108" s="11" t="inlineStr"/>
+      <c r="X108" s="8" t="inlineStr"/>
+      <c r="Y108" s="8" t="inlineStr"/>
+      <c r="Z108" s="9" t="inlineStr"/>
+      <c r="AA108" s="10" t="inlineStr"/>
+      <c r="AB108" s="11" t="inlineStr"/>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>2818.75</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr"/>
       <c r="D109" s="8" t="inlineStr"/>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t>1918.75</t>
-        </is>
-      </c>
+      <c r="E109" s="8" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr"/>
       <c r="G109" s="8" t="inlineStr"/>
       <c r="H109" s="8" t="inlineStr"/>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>2553.75</t>
-        </is>
-      </c>
+      <c r="I109" s="8" t="inlineStr"/>
       <c r="J109" s="8" t="inlineStr"/>
-      <c r="K109" s="8" t="inlineStr"/>
+      <c r="K109" s="8" t="inlineStr">
+        <is>
+          <t>2250.00</t>
+        </is>
+      </c>
       <c r="L109" s="8" t="inlineStr"/>
       <c r="M109" s="8" t="inlineStr"/>
       <c r="N109" s="8" t="inlineStr"/>
       <c r="O109" s="8" t="inlineStr">
         <is>
-          <t>3782.50</t>
+          <t>1886.50</t>
         </is>
       </c>
       <c r="P109" s="8" t="inlineStr"/>
@@ -6023,51 +6485,47 @@
       <c r="U109" s="8" t="inlineStr"/>
       <c r="V109" s="8" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr"/>
-      <c r="X109" s="9" t="inlineStr"/>
-      <c r="Y109" s="10" t="inlineStr"/>
-      <c r="Z109" s="11" t="inlineStr"/>
+      <c r="X109" s="8" t="inlineStr"/>
+      <c r="Y109" s="8" t="inlineStr"/>
+      <c r="Z109" s="9" t="n">
+        <v>2068.25</v>
+      </c>
+      <c r="AA109" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB109" s="11" t="n">
+        <v>-0.0004138885962403865</v>
+      </c>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>2702.50</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr"/>
       <c r="D110" s="8" t="inlineStr"/>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>4056.25</t>
-        </is>
-      </c>
+      <c r="E110" s="8" t="inlineStr"/>
       <c r="F110" s="8" t="inlineStr"/>
       <c r="G110" s="8" t="inlineStr"/>
       <c r="H110" s="8" t="inlineStr"/>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>2338.75</t>
-        </is>
-      </c>
+      <c r="I110" s="8" t="inlineStr"/>
       <c r="J110" s="8" t="inlineStr"/>
-      <c r="K110" s="8" t="inlineStr">
-        <is>
-          <t>2608.75</t>
-        </is>
-      </c>
+      <c r="K110" s="8" t="inlineStr"/>
       <c r="L110" s="8" t="inlineStr"/>
       <c r="M110" s="8" t="inlineStr"/>
       <c r="N110" s="8" t="inlineStr"/>
       <c r="O110" s="8" t="inlineStr">
         <is>
-          <t>2895.00</t>
-        </is>
-      </c>
-      <c r="P110" s="8" t="inlineStr"/>
+          <t>2197.00</t>
+        </is>
+      </c>
+      <c r="P110" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="Q110" s="8" t="inlineStr"/>
       <c r="R110" s="8" t="inlineStr"/>
       <c r="S110" s="8" t="inlineStr"/>
@@ -6075,151 +6533,149 @@
       <c r="U110" s="8" t="inlineStr"/>
       <c r="V110" s="8" t="inlineStr"/>
       <c r="W110" s="8" t="inlineStr"/>
-      <c r="X110" s="9" t="n">
-        <v>3065.625</v>
-      </c>
-      <c r="Y110" s="9" t="n">
-        <v>206.5625</v>
-      </c>
-      <c r="Z110" s="11" t="n">
-        <v>0.01554141493179646</v>
-      </c>
+      <c r="X110" s="8" t="inlineStr"/>
+      <c r="Y110" s="8" t="inlineStr"/>
+      <c r="Z110" s="9" t="inlineStr"/>
+      <c r="AA110" s="10" t="inlineStr"/>
+      <c r="AB110" s="11" t="inlineStr"/>
     </row>
     <row r="111" ht="24" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>RoadRunner
-Random: 11.5
-Human: 7845.0</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 17564</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr"/>
-      <c r="D111" s="4" t="inlineStr"/>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr"/>
-      <c r="H111" s="4" t="inlineStr"/>
-      <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="4" t="inlineStr"/>
-      <c r="K111" s="4" t="inlineStr"/>
-      <c r="L111" s="4" t="inlineStr"/>
-      <c r="M111" s="4" t="inlineStr"/>
-      <c r="N111" s="4" t="inlineStr"/>
-      <c r="O111" s="4" t="inlineStr"/>
-      <c r="P111" s="4" t="inlineStr"/>
-      <c r="Q111" s="4" t="inlineStr"/>
-      <c r="R111" s="4" t="inlineStr"/>
-      <c r="S111" s="4" t="inlineStr"/>
-      <c r="T111" s="4" t="inlineStr"/>
-      <c r="U111" s="4" t="inlineStr"/>
-      <c r="V111" s="4" t="inlineStr"/>
-      <c r="W111" s="4" t="inlineStr"/>
-      <c r="X111" s="5" t="inlineStr"/>
-      <c r="Y111" s="6" t="n">
-        <v>-8627.75</v>
-      </c>
-      <c r="Z111" s="7" t="n">
-        <v>-1.101391459756175</v>
-      </c>
+      <c r="A111" s="1" t="n"/>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr"/>
+      <c r="D111" s="8" t="inlineStr"/>
+      <c r="E111" s="8" t="inlineStr"/>
+      <c r="F111" s="8" t="inlineStr"/>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr"/>
+      <c r="I111" s="8" t="inlineStr"/>
+      <c r="J111" s="8" t="inlineStr"/>
+      <c r="K111" s="8" t="inlineStr"/>
+      <c r="L111" s="8" t="inlineStr"/>
+      <c r="M111" s="8" t="inlineStr"/>
+      <c r="N111" s="8" t="inlineStr"/>
+      <c r="O111" s="8" t="inlineStr">
+        <is>
+          <t>2170.00</t>
+        </is>
+      </c>
+      <c r="P111" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="Q111" s="8" t="inlineStr"/>
+      <c r="R111" s="8" t="inlineStr"/>
+      <c r="S111" s="8" t="inlineStr"/>
+      <c r="T111" s="8" t="inlineStr"/>
+      <c r="U111" s="8" t="inlineStr"/>
+      <c r="V111" s="8" t="inlineStr"/>
+      <c r="W111" s="8" t="inlineStr"/>
+      <c r="X111" s="8" t="inlineStr"/>
+      <c r="Y111" s="8" t="inlineStr"/>
+      <c r="Z111" s="9" t="inlineStr"/>
+      <c r="AA111" s="10" t="inlineStr"/>
+      <c r="AB111" s="11" t="inlineStr"/>
     </row>
     <row r="112" ht="24" customHeight="1">
-      <c r="A112" s="1" t="n"/>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr"/>
-      <c r="D112" s="8" t="inlineStr"/>
-      <c r="E112" s="8" t="inlineStr"/>
-      <c r="F112" s="8" t="inlineStr"/>
-      <c r="G112" s="8" t="inlineStr"/>
-      <c r="H112" s="8" t="inlineStr"/>
-      <c r="I112" s="8" t="inlineStr"/>
-      <c r="J112" s="8" t="inlineStr"/>
-      <c r="K112" s="8" t="inlineStr">
-        <is>
-          <t>8610.00</t>
-        </is>
-      </c>
-      <c r="L112" s="8" t="inlineStr"/>
-      <c r="M112" s="8" t="inlineStr"/>
-      <c r="N112" s="8" t="inlineStr"/>
-      <c r="O112" s="8" t="inlineStr">
-        <is>
-          <t>7290.00</t>
-        </is>
-      </c>
-      <c r="P112" s="8" t="inlineStr">
-        <is>
-          <t>9690.00</t>
-        </is>
-      </c>
-      <c r="Q112" s="8" t="inlineStr">
-        <is>
-          <t>10155.00</t>
-        </is>
-      </c>
-      <c r="R112" s="8" t="inlineStr"/>
-      <c r="S112" s="8" t="inlineStr"/>
-      <c r="T112" s="8" t="inlineStr"/>
-      <c r="U112" s="8" t="inlineStr"/>
-      <c r="V112" s="8" t="inlineStr"/>
-      <c r="W112" s="8" t="inlineStr"/>
-      <c r="X112" s="9" t="n">
-        <v>8936.25</v>
-      </c>
-      <c r="Y112" s="10" t="inlineStr"/>
-      <c r="Z112" s="11" t="inlineStr"/>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Pong
+Random: -20.7
+Human: 14.6</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr"/>
+      <c r="D112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr"/>
+      <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" s="4" t="inlineStr"/>
+      <c r="J112" s="4" t="inlineStr"/>
+      <c r="K112" s="4" t="inlineStr"/>
+      <c r="L112" s="4" t="inlineStr"/>
+      <c r="M112" s="4" t="inlineStr"/>
+      <c r="N112" s="4" t="inlineStr"/>
+      <c r="O112" s="4" t="inlineStr"/>
+      <c r="P112" s="4" t="inlineStr"/>
+      <c r="Q112" s="4" t="inlineStr"/>
+      <c r="R112" s="4" t="inlineStr"/>
+      <c r="S112" s="4" t="inlineStr"/>
+      <c r="T112" s="4" t="inlineStr"/>
+      <c r="U112" s="4" t="inlineStr"/>
+      <c r="V112" s="4" t="inlineStr"/>
+      <c r="W112" s="4" t="inlineStr"/>
+      <c r="X112" s="4" t="inlineStr"/>
+      <c r="Y112" s="4" t="inlineStr"/>
+      <c r="Z112" s="5" t="inlineStr"/>
+      <c r="AA112" s="6" t="n">
+        <v>-2.700000000000001</v>
+      </c>
+      <c r="AB112" s="7" t="n">
+        <v>-0.07648725212464592</v>
+      </c>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="8" t="inlineStr"/>
-      <c r="E113" s="8" t="inlineStr"/>
-      <c r="F113" s="8" t="inlineStr"/>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
       <c r="G113" s="8" t="inlineStr"/>
       <c r="H113" s="8" t="inlineStr"/>
       <c r="I113" s="8" t="inlineStr"/>
       <c r="J113" s="8" t="inlineStr"/>
-      <c r="K113" s="8" t="inlineStr"/>
-      <c r="L113" s="8" t="inlineStr"/>
+      <c r="K113" s="8" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="L113" s="8" t="inlineStr">
+        <is>
+          <t>13.70</t>
+        </is>
+      </c>
       <c r="M113" s="8" t="inlineStr"/>
       <c r="N113" s="8" t="inlineStr"/>
-      <c r="O113" s="8" t="inlineStr">
-        <is>
-          <t>8520.00</t>
-        </is>
-      </c>
-      <c r="P113" s="8" t="inlineStr">
-        <is>
-          <t>11830.00</t>
-        </is>
-      </c>
-      <c r="Q113" s="8" t="inlineStr">
-        <is>
-          <t>16805.00</t>
-        </is>
-      </c>
+      <c r="O113" s="8" t="inlineStr"/>
+      <c r="P113" s="8" t="inlineStr"/>
+      <c r="Q113" s="8" t="inlineStr"/>
       <c r="R113" s="8" t="inlineStr"/>
       <c r="S113" s="8" t="inlineStr"/>
       <c r="T113" s="8" t="inlineStr"/>
       <c r="U113" s="8" t="inlineStr"/>
       <c r="V113" s="8" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr"/>
-      <c r="X113" s="9" t="inlineStr"/>
-      <c r="Y113" s="10" t="inlineStr"/>
-      <c r="Z113" s="11" t="inlineStr"/>
+      <c r="X113" s="8" t="inlineStr"/>
+      <c r="Y113" s="8" t="inlineStr"/>
+      <c r="Z113" s="9" t="n">
+        <v>8.299999999999999</v>
+      </c>
+      <c r="AA113" s="10" t="inlineStr"/>
+      <c r="AB113" s="11" t="inlineStr"/>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="1" t="n"/>
@@ -6231,104 +6687,102 @@
       <c r="C114" s="8" t="inlineStr"/>
       <c r="D114" s="8" t="inlineStr"/>
       <c r="E114" s="8" t="inlineStr"/>
-      <c r="F114" s="8" t="inlineStr"/>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>8.20</t>
+        </is>
+      </c>
       <c r="G114" s="8" t="inlineStr"/>
       <c r="H114" s="8" t="inlineStr"/>
-      <c r="I114" s="8" t="inlineStr"/>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
       <c r="J114" s="8" t="inlineStr"/>
       <c r="K114" s="8" t="inlineStr">
         <is>
-          <t>8195.00</t>
-        </is>
-      </c>
-      <c r="L114" s="8" t="inlineStr"/>
+          <t>9.80</t>
+        </is>
+      </c>
+      <c r="L114" s="8" t="inlineStr">
+        <is>
+          <t>-19.90</t>
+        </is>
+      </c>
       <c r="M114" s="8" t="inlineStr"/>
       <c r="N114" s="8" t="inlineStr"/>
-      <c r="O114" s="8" t="inlineStr">
-        <is>
-          <t>8325.00</t>
-        </is>
-      </c>
-      <c r="P114" s="8" t="inlineStr">
-        <is>
-          <t>12890.00</t>
-        </is>
-      </c>
-      <c r="Q114" s="8" t="inlineStr">
-        <is>
-          <t>16980.00</t>
-        </is>
-      </c>
+      <c r="O114" s="8" t="inlineStr"/>
+      <c r="P114" s="8" t="inlineStr"/>
+      <c r="Q114" s="8" t="inlineStr"/>
       <c r="R114" s="8" t="inlineStr"/>
       <c r="S114" s="8" t="inlineStr"/>
       <c r="T114" s="8" t="inlineStr"/>
       <c r="U114" s="8" t="inlineStr"/>
       <c r="V114" s="8" t="inlineStr"/>
       <c r="W114" s="8" t="inlineStr"/>
-      <c r="X114" s="9" t="n">
-        <v>11597.5</v>
-      </c>
-      <c r="Y114" s="9" t="n">
-        <v>2661.25</v>
-      </c>
-      <c r="Z114" s="11" t="n">
-        <v>0.3397268143230995</v>
+      <c r="X114" s="16" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="Y114" s="8" t="inlineStr"/>
+      <c r="Z114" s="9" t="n">
+        <v>-0.6333333333333329</v>
+      </c>
+      <c r="AA114" s="9" t="n">
+        <v>8.933333333333332</v>
+      </c>
+      <c r="AB114" s="11" t="n">
+        <v>-0.2530689329556185</v>
       </c>
     </row>
     <row r="115" ht="24" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Seaquest
-Random: 68.4
-Human: 42054.7</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 525</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr"/>
-      <c r="D115" s="4" t="inlineStr"/>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="4" t="inlineStr"/>
-      <c r="H115" s="4" t="inlineStr"/>
-      <c r="I115" s="4" t="inlineStr"/>
-      <c r="J115" s="4" t="inlineStr"/>
-      <c r="K115" s="4" t="inlineStr"/>
-      <c r="L115" s="4" t="inlineStr"/>
-      <c r="M115" s="4" t="inlineStr"/>
-      <c r="N115" s="4" t="inlineStr"/>
-      <c r="O115" s="4" t="inlineStr"/>
-      <c r="P115" s="4" t="inlineStr"/>
-      <c r="Q115" s="4" t="inlineStr"/>
-      <c r="R115" s="4" t="inlineStr"/>
-      <c r="S115" s="4" t="inlineStr"/>
-      <c r="T115" s="4" t="inlineStr"/>
-      <c r="U115" s="4" t="inlineStr"/>
-      <c r="V115" s="4" t="inlineStr"/>
-      <c r="W115" s="4" t="inlineStr"/>
-      <c r="X115" s="5" t="inlineStr"/>
-      <c r="Y115" s="6" t="n">
-        <v>-64.33333333333331</v>
-      </c>
-      <c r="Z115" s="7" t="n">
-        <v>-0.001532245835744834</v>
-      </c>
+      <c r="A115" s="1" t="n"/>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr"/>
+      <c r="D115" s="8" t="inlineStr"/>
+      <c r="E115" s="8" t="inlineStr"/>
+      <c r="F115" s="8" t="inlineStr"/>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="8" t="inlineStr"/>
+      <c r="I115" s="8" t="inlineStr"/>
+      <c r="J115" s="8" t="inlineStr"/>
+      <c r="K115" s="8" t="inlineStr"/>
+      <c r="L115" s="8" t="inlineStr">
+        <is>
+          <t>-20.40</t>
+        </is>
+      </c>
+      <c r="M115" s="8" t="inlineStr"/>
+      <c r="N115" s="8" t="inlineStr"/>
+      <c r="O115" s="8" t="inlineStr"/>
+      <c r="P115" s="8" t="inlineStr"/>
+      <c r="Q115" s="8" t="inlineStr"/>
+      <c r="R115" s="8" t="inlineStr"/>
+      <c r="S115" s="8" t="inlineStr"/>
+      <c r="T115" s="8" t="inlineStr"/>
+      <c r="U115" s="8" t="inlineStr"/>
+      <c r="V115" s="8" t="inlineStr"/>
+      <c r="W115" s="8" t="inlineStr"/>
+      <c r="X115" s="8" t="inlineStr"/>
+      <c r="Y115" s="8" t="inlineStr"/>
+      <c r="Z115" s="9" t="inlineStr"/>
+      <c r="AA115" s="10" t="inlineStr"/>
+      <c r="AB115" s="11" t="inlineStr"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>454.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr"/>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr"/>
       <c r="F116" s="8" t="inlineStr"/>
@@ -6336,85 +6790,85 @@
       <c r="H116" s="8" t="inlineStr"/>
       <c r="I116" s="8" t="inlineStr"/>
       <c r="J116" s="8" t="inlineStr"/>
-      <c r="K116" s="8" t="inlineStr">
-        <is>
-          <t>494.00</t>
-        </is>
-      </c>
-      <c r="L116" s="8" t="inlineStr"/>
+      <c r="K116" s="8" t="inlineStr"/>
+      <c r="L116" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="M116" s="8" t="inlineStr"/>
       <c r="N116" s="8" t="inlineStr"/>
-      <c r="O116" s="8" t="inlineStr">
-        <is>
-          <t>418.00</t>
-        </is>
-      </c>
+      <c r="O116" s="8" t="inlineStr"/>
       <c r="P116" s="8" t="inlineStr"/>
       <c r="Q116" s="8" t="inlineStr"/>
       <c r="R116" s="8" t="inlineStr"/>
       <c r="S116" s="8" t="inlineStr"/>
       <c r="T116" s="8" t="inlineStr"/>
       <c r="U116" s="8" t="inlineStr"/>
-      <c r="V116" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
+      <c r="V116" s="8" t="inlineStr"/>
       <c r="W116" s="8" t="inlineStr"/>
-      <c r="X116" s="9" t="n">
-        <v>460.6666666666667</v>
-      </c>
-      <c r="Y116" s="10" t="inlineStr"/>
-      <c r="Z116" s="11" t="inlineStr"/>
+      <c r="X116" s="8" t="inlineStr"/>
+      <c r="Y116" s="8" t="inlineStr"/>
+      <c r="Z116" s="9" t="inlineStr"/>
+      <c r="AA116" s="10" t="inlineStr"/>
+      <c r="AB116" s="11" t="inlineStr"/>
     </row>
     <row r="117" ht="24" customHeight="1">
-      <c r="A117" s="1" t="n"/>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr"/>
-      <c r="D117" s="8" t="inlineStr"/>
-      <c r="E117" s="8" t="inlineStr"/>
-      <c r="F117" s="8" t="inlineStr"/>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="8" t="inlineStr"/>
-      <c r="I117" s="8" t="inlineStr"/>
-      <c r="J117" s="8" t="inlineStr"/>
-      <c r="K117" s="8" t="inlineStr"/>
-      <c r="L117" s="8" t="inlineStr"/>
-      <c r="M117" s="8" t="inlineStr"/>
-      <c r="N117" s="8" t="inlineStr"/>
-      <c r="O117" s="8" t="inlineStr">
-        <is>
-          <t>476.00</t>
-        </is>
-      </c>
-      <c r="P117" s="8" t="inlineStr"/>
-      <c r="Q117" s="8" t="inlineStr"/>
-      <c r="R117" s="8" t="inlineStr"/>
-      <c r="S117" s="8" t="inlineStr"/>
-      <c r="T117" s="8" t="inlineStr"/>
-      <c r="U117" s="8" t="inlineStr"/>
-      <c r="V117" s="8" t="inlineStr">
-        <is>
-          <t>557.00</t>
-        </is>
-      </c>
-      <c r="W117" s="8" t="inlineStr"/>
-      <c r="X117" s="9" t="inlineStr"/>
-      <c r="Y117" s="10" t="inlineStr"/>
-      <c r="Z117" s="11" t="inlineStr"/>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>PrivateEye
+Random: 24.9
+Human: 69571.3</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 7781</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr"/>
+      <c r="D117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr"/>
+      <c r="L117" s="4" t="inlineStr"/>
+      <c r="M117" s="4" t="inlineStr"/>
+      <c r="N117" s="4" t="inlineStr"/>
+      <c r="O117" s="4" t="inlineStr"/>
+      <c r="P117" s="4" t="inlineStr"/>
+      <c r="Q117" s="4" t="inlineStr"/>
+      <c r="R117" s="4" t="inlineStr"/>
+      <c r="S117" s="4" t="inlineStr"/>
+      <c r="T117" s="4" t="inlineStr"/>
+      <c r="U117" s="4" t="inlineStr"/>
+      <c r="V117" s="4" t="inlineStr"/>
+      <c r="W117" s="4" t="inlineStr"/>
+      <c r="X117" s="4" t="inlineStr"/>
+      <c r="Y117" s="4" t="inlineStr"/>
+      <c r="Z117" s="5" t="inlineStr"/>
+      <c r="AA117" s="6" t="n">
+        <v>-6778.35</v>
+      </c>
+      <c r="AB117" s="7" t="n">
+        <v>-0.09746514557187719</v>
+      </c>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>75.30</t>
+        </is>
+      </c>
       <c r="D118" s="8" t="inlineStr"/>
       <c r="E118" s="8" t="inlineStr"/>
       <c r="F118" s="8" t="inlineStr"/>
@@ -6424,44 +6878,50 @@
       <c r="J118" s="8" t="inlineStr"/>
       <c r="K118" s="8" t="inlineStr">
         <is>
-          <t>521.00</t>
+          <t>199.35</t>
         </is>
       </c>
       <c r="L118" s="8" t="inlineStr"/>
       <c r="M118" s="8" t="inlineStr"/>
       <c r="N118" s="8" t="inlineStr"/>
-      <c r="O118" s="8" t="inlineStr">
-        <is>
-          <t>450.00</t>
-        </is>
-      </c>
-      <c r="P118" s="8" t="inlineStr"/>
-      <c r="Q118" s="8" t="inlineStr"/>
-      <c r="R118" s="8" t="inlineStr"/>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P118" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q118" s="8" t="inlineStr">
+        <is>
+          <t>3551.75</t>
+        </is>
+      </c>
+      <c r="R118" s="12" t="inlineStr"/>
       <c r="S118" s="8" t="inlineStr"/>
       <c r="T118" s="8" t="inlineStr"/>
       <c r="U118" s="8" t="inlineStr"/>
-      <c r="V118" s="8" t="inlineStr">
-        <is>
-          <t>545.00</t>
-        </is>
-      </c>
+      <c r="V118" s="8" t="inlineStr"/>
       <c r="W118" s="8" t="inlineStr"/>
-      <c r="X118" s="9" t="n">
-        <v>505.3333333333333</v>
-      </c>
-      <c r="Y118" s="9" t="n">
-        <v>44.66666666666663</v>
-      </c>
-      <c r="Z118" s="11" t="n">
-        <v>0.001063839077667397</v>
-      </c>
+      <c r="X118" s="8" t="inlineStr">
+        <is>
+          <t>159.50</t>
+        </is>
+      </c>
+      <c r="Y118" s="8" t="inlineStr"/>
+      <c r="Z118" s="9" t="n">
+        <v>1002.65</v>
+      </c>
+      <c r="AA118" s="10" t="inlineStr"/>
+      <c r="AB118" s="11" t="inlineStr"/>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr"/>
@@ -6472,125 +6932,179 @@
       <c r="H119" s="8" t="inlineStr"/>
       <c r="I119" s="8" t="inlineStr"/>
       <c r="J119" s="8" t="inlineStr"/>
-      <c r="K119" s="8" t="inlineStr"/>
+      <c r="K119" s="8" t="inlineStr">
+        <is>
+          <t>191.95</t>
+        </is>
+      </c>
       <c r="L119" s="8" t="inlineStr"/>
       <c r="M119" s="8" t="inlineStr"/>
       <c r="N119" s="8" t="inlineStr"/>
-      <c r="O119" s="8" t="inlineStr"/>
-      <c r="P119" s="8" t="inlineStr"/>
-      <c r="Q119" s="8" t="inlineStr"/>
-      <c r="R119" s="8" t="inlineStr"/>
+      <c r="O119" s="12" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="P119" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q119" s="8" t="inlineStr">
+        <is>
+          <t>166.80</t>
+        </is>
+      </c>
+      <c r="R119" s="13" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
       <c r="S119" s="8" t="inlineStr"/>
       <c r="T119" s="8" t="inlineStr"/>
       <c r="U119" s="8" t="inlineStr"/>
-      <c r="V119" s="8" t="inlineStr">
-        <is>
-          <t>411.00</t>
-        </is>
-      </c>
+      <c r="V119" s="8" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr"/>
-      <c r="X119" s="9" t="inlineStr"/>
-      <c r="Y119" s="10" t="inlineStr"/>
-      <c r="Z119" s="11" t="inlineStr"/>
+      <c r="X119" s="8" t="inlineStr">
+        <is>
+          <t>153.20</t>
+        </is>
+      </c>
+      <c r="Y119" s="8" t="inlineStr"/>
+      <c r="Z119" s="9" t="n">
+        <v>152.9875</v>
+      </c>
+      <c r="AA119" s="9" t="n">
+        <v>849.6624999999999</v>
+      </c>
+      <c r="AB119" s="11" t="n">
+        <v>-0.01221720319096315</v>
+      </c>
     </row>
     <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="1" t="n"/>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr"/>
-      <c r="D120" s="8" t="inlineStr"/>
-      <c r="E120" s="8" t="inlineStr"/>
-      <c r="F120" s="8" t="inlineStr"/>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="8" t="inlineStr"/>
-      <c r="I120" s="8" t="inlineStr"/>
-      <c r="J120" s="8" t="inlineStr"/>
-      <c r="K120" s="8" t="inlineStr"/>
-      <c r="L120" s="8" t="inlineStr"/>
-      <c r="M120" s="8" t="inlineStr"/>
-      <c r="N120" s="8" t="inlineStr"/>
-      <c r="O120" s="8" t="inlineStr"/>
-      <c r="P120" s="8" t="inlineStr"/>
-      <c r="Q120" s="8" t="inlineStr"/>
-      <c r="R120" s="8" t="inlineStr"/>
-      <c r="S120" s="8" t="inlineStr"/>
-      <c r="T120" s="8" t="inlineStr"/>
-      <c r="U120" s="8" t="inlineStr"/>
-      <c r="V120" s="8" t="inlineStr">
-        <is>
-          <t>415.00</t>
-        </is>
-      </c>
-      <c r="W120" s="8" t="inlineStr"/>
-      <c r="X120" s="9" t="inlineStr"/>
-      <c r="Y120" s="10" t="inlineStr"/>
-      <c r="Z120" s="11" t="inlineStr"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Qbert
+Random: 163.9
+Human: 13455.0</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4522</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr"/>
+      <c r="D120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
+      <c r="G120" s="4" t="inlineStr"/>
+      <c r="H120" s="4" t="inlineStr"/>
+      <c r="I120" s="4" t="inlineStr"/>
+      <c r="J120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr"/>
+      <c r="L120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr"/>
+      <c r="N120" s="4" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr"/>
+      <c r="P120" s="4" t="inlineStr"/>
+      <c r="Q120" s="4" t="inlineStr"/>
+      <c r="R120" s="4" t="inlineStr"/>
+      <c r="S120" s="4" t="inlineStr"/>
+      <c r="T120" s="4" t="inlineStr"/>
+      <c r="U120" s="4" t="inlineStr"/>
+      <c r="V120" s="4" t="inlineStr"/>
+      <c r="W120" s="4" t="inlineStr"/>
+      <c r="X120" s="4" t="inlineStr"/>
+      <c r="Y120" s="4" t="inlineStr"/>
+      <c r="Z120" s="5" t="inlineStr"/>
+      <c r="AA120" s="6" t="n">
+        <v>-1662.9375</v>
+      </c>
+      <c r="AB120" s="7" t="n">
+        <v>-0.1251166193919239</v>
+      </c>
     </row>
     <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>UpNDown
-Random: 533.4
-Human: 11693.2</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7985</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr"/>
-      <c r="D121" s="4" t="inlineStr"/>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="4" t="inlineStr"/>
-      <c r="H121" s="4" t="inlineStr"/>
-      <c r="I121" s="4" t="inlineStr"/>
-      <c r="J121" s="4" t="inlineStr"/>
-      <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="4" t="inlineStr"/>
-      <c r="M121" s="4" t="inlineStr"/>
-      <c r="N121" s="4" t="inlineStr"/>
-      <c r="O121" s="4" t="inlineStr"/>
-      <c r="P121" s="4" t="inlineStr"/>
-      <c r="Q121" s="4" t="inlineStr"/>
-      <c r="R121" s="4" t="inlineStr"/>
-      <c r="S121" s="4" t="inlineStr"/>
-      <c r="T121" s="4" t="inlineStr"/>
-      <c r="U121" s="4" t="inlineStr"/>
-      <c r="V121" s="4" t="inlineStr"/>
-      <c r="W121" s="4" t="inlineStr"/>
-      <c r="X121" s="5" t="inlineStr"/>
-      <c r="Y121" s="6" t="n">
-        <v>-2963</v>
-      </c>
-      <c r="Z121" s="7" t="n">
-        <v>-0.2655065502966003</v>
-      </c>
+      <c r="A121" s="1" t="n"/>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>1771.25</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr"/>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>3786.25</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr"/>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr"/>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>2940.00</t>
+        </is>
+      </c>
+      <c r="J121" s="8" t="inlineStr"/>
+      <c r="K121" s="8" t="inlineStr">
+        <is>
+          <t>3193.75</t>
+        </is>
+      </c>
+      <c r="L121" s="8" t="inlineStr"/>
+      <c r="M121" s="8" t="inlineStr"/>
+      <c r="N121" s="8" t="inlineStr"/>
+      <c r="O121" s="8" t="inlineStr">
+        <is>
+          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
+        </is>
+      </c>
+      <c r="P121" s="8" t="inlineStr"/>
+      <c r="Q121" s="8" t="inlineStr"/>
+      <c r="R121" s="12" t="inlineStr"/>
+      <c r="S121" s="8" t="inlineStr"/>
+      <c r="T121" s="8" t="inlineStr"/>
+      <c r="U121" s="8" t="inlineStr"/>
+      <c r="V121" s="8" t="inlineStr"/>
+      <c r="W121" s="8" t="inlineStr"/>
+      <c r="X121" s="8" t="inlineStr"/>
+      <c r="Y121" s="8" t="inlineStr"/>
+      <c r="Z121" s="9" t="n">
+        <v>2859.0625</v>
+      </c>
+      <c r="AA121" s="10" t="inlineStr"/>
+      <c r="AB121" s="11" t="inlineStr"/>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>9044.00</t>
+          <t>2818.75</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr"/>
-      <c r="E122" s="8" t="inlineStr"/>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>1918.75</t>
+        </is>
+      </c>
       <c r="F122" s="8" t="inlineStr"/>
       <c r="G122" s="8" t="inlineStr"/>
       <c r="H122" s="8" t="inlineStr"/>
-      <c r="I122" s="8" t="inlineStr">
-        <is>
-          <t>5849.00</t>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>2553.75</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr"/>
@@ -6600,153 +7114,785 @@
       <c r="N122" s="8" t="inlineStr"/>
       <c r="O122" s="8" t="inlineStr">
         <is>
-          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
-        </is>
-      </c>
-      <c r="P122" s="8" t="inlineStr">
-        <is>
-          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
-        </is>
-      </c>
-      <c r="Q122" s="8" t="inlineStr">
-        <is>
-          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="R122" s="8" t="inlineStr"/>
+          <t>3782.50</t>
+        </is>
+      </c>
+      <c r="P122" s="8" t="inlineStr"/>
+      <c r="Q122" s="8" t="inlineStr"/>
+      <c r="R122" s="12" t="inlineStr"/>
       <c r="S122" s="8" t="inlineStr"/>
       <c r="T122" s="8" t="inlineStr"/>
       <c r="U122" s="8" t="inlineStr"/>
       <c r="V122" s="8" t="inlineStr"/>
       <c r="W122" s="8" t="inlineStr"/>
-      <c r="X122" s="9" t="n">
-        <v>5022</v>
-      </c>
-      <c r="Y122" s="10" t="inlineStr"/>
-      <c r="Z122" s="11" t="inlineStr"/>
+      <c r="X122" s="8" t="inlineStr"/>
+      <c r="Y122" s="8" t="inlineStr"/>
+      <c r="Z122" s="9" t="inlineStr"/>
+      <c r="AA122" s="10" t="inlineStr"/>
+      <c r="AB122" s="11" t="inlineStr"/>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>2702.50</t>
+        </is>
+      </c>
       <c r="D123" s="8" t="inlineStr"/>
-      <c r="E123" s="8" t="inlineStr"/>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>4056.25</t>
+        </is>
+      </c>
       <c r="F123" s="8" t="inlineStr"/>
       <c r="G123" s="8" t="inlineStr"/>
       <c r="H123" s="8" t="inlineStr"/>
-      <c r="I123" s="8" t="inlineStr"/>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>2338.75</t>
+        </is>
+      </c>
       <c r="J123" s="8" t="inlineStr"/>
-      <c r="K123" s="8" t="inlineStr"/>
+      <c r="K123" s="8" t="inlineStr">
+        <is>
+          <t>2608.75</t>
+        </is>
+      </c>
       <c r="L123" s="8" t="inlineStr"/>
       <c r="M123" s="8" t="inlineStr"/>
       <c r="N123" s="8" t="inlineStr"/>
       <c r="O123" s="8" t="inlineStr">
         <is>
-          <t>5670.00</t>
-        </is>
-      </c>
-      <c r="P123" s="8" t="inlineStr">
-        <is>
-          <t>7178.00</t>
-        </is>
-      </c>
-      <c r="Q123" s="8" t="inlineStr">
-        <is>
-          <t>3066.00</t>
-        </is>
-      </c>
-      <c r="R123" s="8" t="inlineStr"/>
+          <t>2895.00</t>
+        </is>
+      </c>
+      <c r="P123" s="8" t="inlineStr"/>
+      <c r="Q123" s="8" t="inlineStr"/>
+      <c r="R123" s="13" t="inlineStr">
+        <is>
+          <t>833.75, 683.75</t>
+        </is>
+      </c>
       <c r="S123" s="8" t="inlineStr"/>
       <c r="T123" s="8" t="inlineStr"/>
       <c r="U123" s="8" t="inlineStr"/>
       <c r="V123" s="8" t="inlineStr"/>
       <c r="W123" s="8" t="inlineStr"/>
-      <c r="X123" s="9" t="inlineStr"/>
-      <c r="Y123" s="10" t="inlineStr"/>
-      <c r="Z123" s="11" t="inlineStr"/>
+      <c r="X123" s="8" t="inlineStr"/>
+      <c r="Y123" s="8" t="inlineStr"/>
+      <c r="Z123" s="9" t="n">
+        <v>3065.625</v>
+      </c>
+      <c r="AA123" s="9" t="n">
+        <v>206.5625</v>
+      </c>
+      <c r="AB123" s="11" t="n">
+        <v>0.01554141493179646</v>
+      </c>
     </row>
     <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="1" t="n"/>
-      <c r="B124" s="1" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>RoadRunner
+Random: 11.5
+Human: 7845.0</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 17564</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr"/>
+      <c r="D124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr"/>
+      <c r="L124" s="4" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr"/>
+      <c r="N124" s="4" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr"/>
+      <c r="P124" s="4" t="inlineStr"/>
+      <c r="Q124" s="4" t="inlineStr"/>
+      <c r="R124" s="4" t="inlineStr"/>
+      <c r="S124" s="4" t="inlineStr"/>
+      <c r="T124" s="4" t="inlineStr"/>
+      <c r="U124" s="4" t="inlineStr"/>
+      <c r="V124" s="4" t="inlineStr"/>
+      <c r="W124" s="4" t="inlineStr"/>
+      <c r="X124" s="4" t="inlineStr"/>
+      <c r="Y124" s="4" t="inlineStr"/>
+      <c r="Z124" s="5" t="inlineStr"/>
+      <c r="AA124" s="6" t="n">
+        <v>-8519</v>
+      </c>
+      <c r="AB124" s="7" t="n">
+        <v>-1.087508776409013</v>
+      </c>
+    </row>
+    <row r="125" ht="24" customHeight="1">
+      <c r="A125" s="1" t="n"/>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr"/>
+      <c r="D125" s="8" t="inlineStr"/>
+      <c r="E125" s="8" t="inlineStr"/>
+      <c r="F125" s="8" t="inlineStr"/>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="8" t="inlineStr"/>
+      <c r="I125" s="8" t="inlineStr"/>
+      <c r="J125" s="8" t="inlineStr"/>
+      <c r="K125" s="12" t="inlineStr">
+        <is>
+          <t>8610.00</t>
+        </is>
+      </c>
+      <c r="L125" s="8" t="inlineStr"/>
+      <c r="M125" s="8" t="inlineStr"/>
+      <c r="N125" s="8" t="inlineStr"/>
+      <c r="O125" s="8" t="inlineStr">
+        <is>
+          <t>7290.00</t>
+        </is>
+      </c>
+      <c r="P125" s="8" t="inlineStr">
+        <is>
+          <t>9690.00</t>
+        </is>
+      </c>
+      <c r="Q125" s="8" t="inlineStr">
+        <is>
+          <t>10155.00</t>
+        </is>
+      </c>
+      <c r="R125" s="8" t="inlineStr"/>
+      <c r="S125" s="8" t="inlineStr"/>
+      <c r="T125" s="8" t="inlineStr"/>
+      <c r="U125" s="8" t="inlineStr"/>
+      <c r="V125" s="8" t="inlineStr"/>
+      <c r="W125" s="8" t="inlineStr"/>
+      <c r="X125" s="8" t="inlineStr"/>
+      <c r="Y125" s="8" t="inlineStr"/>
+      <c r="Z125" s="9" t="n">
+        <v>9045</v>
+      </c>
+      <c r="AA125" s="10" t="inlineStr"/>
+      <c r="AB125" s="11" t="inlineStr"/>
+    </row>
+    <row r="126" ht="24" customHeight="1">
+      <c r="A126" s="1" t="n"/>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr"/>
+      <c r="D126" s="8" t="inlineStr"/>
+      <c r="E126" s="8" t="inlineStr"/>
+      <c r="F126" s="8" t="inlineStr"/>
+      <c r="G126" s="8" t="inlineStr"/>
+      <c r="H126" s="8" t="inlineStr"/>
+      <c r="I126" s="8" t="inlineStr"/>
+      <c r="J126" s="8" t="inlineStr"/>
+      <c r="K126" s="12" t="inlineStr"/>
+      <c r="L126" s="8" t="inlineStr"/>
+      <c r="M126" s="8" t="inlineStr"/>
+      <c r="N126" s="8" t="inlineStr"/>
+      <c r="O126" s="8" t="inlineStr">
+        <is>
+          <t>8520.00</t>
+        </is>
+      </c>
+      <c r="P126" s="8" t="inlineStr">
+        <is>
+          <t>11830.00</t>
+        </is>
+      </c>
+      <c r="Q126" s="8" t="inlineStr">
+        <is>
+          <t>16805.00</t>
+        </is>
+      </c>
+      <c r="R126" s="8" t="inlineStr"/>
+      <c r="S126" s="8" t="inlineStr"/>
+      <c r="T126" s="8" t="inlineStr"/>
+      <c r="U126" s="8" t="inlineStr"/>
+      <c r="V126" s="8" t="inlineStr"/>
+      <c r="W126" s="8" t="inlineStr"/>
+      <c r="X126" s="8" t="inlineStr"/>
+      <c r="Y126" s="8" t="inlineStr"/>
+      <c r="Z126" s="9" t="inlineStr"/>
+      <c r="AA126" s="10" t="inlineStr"/>
+      <c r="AB126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127" ht="24" customHeight="1">
+      <c r="A127" s="1" t="n"/>
+      <c r="B127" s="1" t="inlineStr">
         <is>
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C124" s="8" t="inlineStr"/>
-      <c r="D124" s="8" t="inlineStr"/>
-      <c r="E124" s="8" t="inlineStr"/>
-      <c r="F124" s="8" t="inlineStr"/>
-      <c r="G124" s="8" t="inlineStr"/>
-      <c r="H124" s="8" t="inlineStr"/>
-      <c r="I124" s="8" t="inlineStr"/>
-      <c r="J124" s="8" t="inlineStr"/>
-      <c r="K124" s="8" t="inlineStr"/>
-      <c r="L124" s="8" t="inlineStr"/>
-      <c r="M124" s="8" t="inlineStr"/>
-      <c r="N124" s="8" t="inlineStr"/>
-      <c r="O124" s="8" t="inlineStr">
+      <c r="C127" s="8" t="inlineStr"/>
+      <c r="D127" s="8" t="inlineStr"/>
+      <c r="E127" s="8" t="inlineStr"/>
+      <c r="F127" s="8" t="inlineStr"/>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="8" t="inlineStr"/>
+      <c r="I127" s="8" t="inlineStr"/>
+      <c r="J127" s="8" t="inlineStr"/>
+      <c r="K127" s="12" t="inlineStr">
+        <is>
+          <t>8195.00</t>
+        </is>
+      </c>
+      <c r="L127" s="8" t="inlineStr"/>
+      <c r="M127" s="8" t="inlineStr"/>
+      <c r="N127" s="8" t="inlineStr"/>
+      <c r="O127" s="8" t="inlineStr">
+        <is>
+          <t>8325.00</t>
+        </is>
+      </c>
+      <c r="P127" s="8" t="inlineStr">
+        <is>
+          <t>12890.00</t>
+        </is>
+      </c>
+      <c r="Q127" s="8" t="inlineStr">
+        <is>
+          <t>16980.00</t>
+        </is>
+      </c>
+      <c r="R127" s="15" t="inlineStr">
+        <is>
+          <t>16410.00</t>
+        </is>
+      </c>
+      <c r="S127" s="8" t="inlineStr"/>
+      <c r="T127" s="8" t="inlineStr"/>
+      <c r="U127" s="8" t="inlineStr"/>
+      <c r="V127" s="8" t="inlineStr"/>
+      <c r="W127" s="8" t="inlineStr"/>
+      <c r="X127" s="8" t="inlineStr"/>
+      <c r="Y127" s="8" t="inlineStr"/>
+      <c r="Z127" s="9" t="n">
+        <v>12731.66666666667</v>
+      </c>
+      <c r="AA127" s="9" t="n">
+        <v>3686.666666666666</v>
+      </c>
+      <c r="AB127" s="11" t="n">
+        <v>0.4706282845045849</v>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Seaquest
+Random: 68.4
+Human: 42054.7</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 525</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr"/>
+      <c r="D128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
+      <c r="G128" s="4" t="inlineStr"/>
+      <c r="H128" s="4" t="inlineStr"/>
+      <c r="I128" s="4" t="inlineStr"/>
+      <c r="J128" s="4" t="inlineStr"/>
+      <c r="K128" s="4" t="inlineStr"/>
+      <c r="L128" s="4" t="inlineStr"/>
+      <c r="M128" s="4" t="inlineStr"/>
+      <c r="N128" s="4" t="inlineStr"/>
+      <c r="O128" s="4" t="inlineStr"/>
+      <c r="P128" s="4" t="inlineStr"/>
+      <c r="Q128" s="4" t="inlineStr"/>
+      <c r="R128" s="4" t="inlineStr"/>
+      <c r="S128" s="4" t="inlineStr"/>
+      <c r="T128" s="4" t="inlineStr"/>
+      <c r="U128" s="4" t="inlineStr"/>
+      <c r="V128" s="4" t="inlineStr"/>
+      <c r="W128" s="4" t="inlineStr"/>
+      <c r="X128" s="4" t="inlineStr"/>
+      <c r="Y128" s="4" t="inlineStr"/>
+      <c r="Z128" s="5" t="inlineStr"/>
+      <c r="AA128" s="6" t="n">
+        <v>-64.33333333333331</v>
+      </c>
+      <c r="AB128" s="7" t="n">
+        <v>-0.001532245835744834</v>
+      </c>
+    </row>
+    <row r="129" ht="24" customHeight="1">
+      <c r="A129" s="1" t="n"/>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>454.00</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr"/>
+      <c r="E129" s="8" t="inlineStr"/>
+      <c r="F129" s="8" t="inlineStr"/>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="8" t="inlineStr"/>
+      <c r="I129" s="8" t="inlineStr"/>
+      <c r="J129" s="8" t="inlineStr"/>
+      <c r="K129" s="8" t="inlineStr">
+        <is>
+          <t>494.00</t>
+        </is>
+      </c>
+      <c r="L129" s="8" t="inlineStr"/>
+      <c r="M129" s="8" t="inlineStr"/>
+      <c r="N129" s="8" t="inlineStr"/>
+      <c r="O129" s="8" t="inlineStr">
+        <is>
+          <t>418.00</t>
+        </is>
+      </c>
+      <c r="P129" s="8" t="inlineStr"/>
+      <c r="Q129" s="8" t="inlineStr"/>
+      <c r="R129" s="8" t="inlineStr"/>
+      <c r="S129" s="8" t="inlineStr"/>
+      <c r="T129" s="8" t="inlineStr"/>
+      <c r="U129" s="8" t="inlineStr"/>
+      <c r="V129" s="8" t="inlineStr"/>
+      <c r="W129" s="8" t="inlineStr"/>
+      <c r="X129" s="8" t="inlineStr">
+        <is>
+          <t>470.00</t>
+        </is>
+      </c>
+      <c r="Y129" s="8" t="inlineStr"/>
+      <c r="Z129" s="9" t="n">
+        <v>460.6666666666667</v>
+      </c>
+      <c r="AA129" s="10" t="inlineStr"/>
+      <c r="AB129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130" ht="24" customHeight="1">
+      <c r="A130" s="1" t="n"/>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr"/>
+      <c r="D130" s="8" t="inlineStr"/>
+      <c r="E130" s="8" t="inlineStr"/>
+      <c r="F130" s="8" t="inlineStr"/>
+      <c r="G130" s="8" t="inlineStr"/>
+      <c r="H130" s="8" t="inlineStr"/>
+      <c r="I130" s="8" t="inlineStr"/>
+      <c r="J130" s="8" t="inlineStr"/>
+      <c r="K130" s="8" t="inlineStr"/>
+      <c r="L130" s="8" t="inlineStr"/>
+      <c r="M130" s="8" t="inlineStr"/>
+      <c r="N130" s="8" t="inlineStr"/>
+      <c r="O130" s="8" t="inlineStr">
+        <is>
+          <t>476.00</t>
+        </is>
+      </c>
+      <c r="P130" s="8" t="inlineStr"/>
+      <c r="Q130" s="8" t="inlineStr"/>
+      <c r="R130" s="8" t="inlineStr"/>
+      <c r="S130" s="8" t="inlineStr"/>
+      <c r="T130" s="8" t="inlineStr"/>
+      <c r="U130" s="8" t="inlineStr"/>
+      <c r="V130" s="8" t="inlineStr"/>
+      <c r="W130" s="8" t="inlineStr"/>
+      <c r="X130" s="8" t="inlineStr">
+        <is>
+          <t>557.00</t>
+        </is>
+      </c>
+      <c r="Y130" s="8" t="inlineStr"/>
+      <c r="Z130" s="9" t="inlineStr"/>
+      <c r="AA130" s="10" t="inlineStr"/>
+      <c r="AB130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131" ht="24" customHeight="1">
+      <c r="A131" s="1" t="n"/>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr"/>
+      <c r="D131" s="8" t="inlineStr"/>
+      <c r="E131" s="8" t="inlineStr"/>
+      <c r="F131" s="8" t="inlineStr"/>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="8" t="inlineStr"/>
+      <c r="I131" s="8" t="inlineStr"/>
+      <c r="J131" s="8" t="inlineStr"/>
+      <c r="K131" s="8" t="inlineStr">
+        <is>
+          <t>521.00</t>
+        </is>
+      </c>
+      <c r="L131" s="8" t="inlineStr"/>
+      <c r="M131" s="8" t="inlineStr"/>
+      <c r="N131" s="8" t="inlineStr"/>
+      <c r="O131" s="8" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
+      <c r="P131" s="8" t="inlineStr"/>
+      <c r="Q131" s="8" t="inlineStr"/>
+      <c r="R131" s="8" t="inlineStr"/>
+      <c r="S131" s="8" t="inlineStr"/>
+      <c r="T131" s="8" t="inlineStr"/>
+      <c r="U131" s="8" t="inlineStr"/>
+      <c r="V131" s="8" t="inlineStr"/>
+      <c r="W131" s="8" t="inlineStr"/>
+      <c r="X131" s="8" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
+      <c r="Y131" s="8" t="inlineStr"/>
+      <c r="Z131" s="9" t="n">
+        <v>505.3333333333333</v>
+      </c>
+      <c r="AA131" s="9" t="n">
+        <v>44.66666666666663</v>
+      </c>
+      <c r="AB131" s="11" t="n">
+        <v>0.001063839077667397</v>
+      </c>
+    </row>
+    <row r="132" ht="24" customHeight="1">
+      <c r="A132" s="1" t="n"/>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr"/>
+      <c r="D132" s="8" t="inlineStr"/>
+      <c r="E132" s="8" t="inlineStr"/>
+      <c r="F132" s="8" t="inlineStr"/>
+      <c r="G132" s="8" t="inlineStr"/>
+      <c r="H132" s="8" t="inlineStr"/>
+      <c r="I132" s="8" t="inlineStr"/>
+      <c r="J132" s="8" t="inlineStr"/>
+      <c r="K132" s="8" t="inlineStr"/>
+      <c r="L132" s="8" t="inlineStr"/>
+      <c r="M132" s="8" t="inlineStr"/>
+      <c r="N132" s="8" t="inlineStr"/>
+      <c r="O132" s="8" t="inlineStr"/>
+      <c r="P132" s="8" t="inlineStr"/>
+      <c r="Q132" s="8" t="inlineStr"/>
+      <c r="R132" s="8" t="inlineStr"/>
+      <c r="S132" s="8" t="inlineStr"/>
+      <c r="T132" s="8" t="inlineStr"/>
+      <c r="U132" s="8" t="inlineStr"/>
+      <c r="V132" s="8" t="inlineStr"/>
+      <c r="W132" s="8" t="inlineStr"/>
+      <c r="X132" s="8" t="inlineStr">
+        <is>
+          <t>411.00</t>
+        </is>
+      </c>
+      <c r="Y132" s="8" t="inlineStr"/>
+      <c r="Z132" s="9" t="inlineStr"/>
+      <c r="AA132" s="10" t="inlineStr"/>
+      <c r="AB132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133" ht="24" customHeight="1">
+      <c r="A133" s="1" t="n"/>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr"/>
+      <c r="D133" s="8" t="inlineStr"/>
+      <c r="E133" s="8" t="inlineStr"/>
+      <c r="F133" s="8" t="inlineStr"/>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr"/>
+      <c r="I133" s="8" t="inlineStr"/>
+      <c r="J133" s="8" t="inlineStr"/>
+      <c r="K133" s="8" t="inlineStr"/>
+      <c r="L133" s="8" t="inlineStr"/>
+      <c r="M133" s="8" t="inlineStr"/>
+      <c r="N133" s="8" t="inlineStr"/>
+      <c r="O133" s="8" t="inlineStr"/>
+      <c r="P133" s="8" t="inlineStr"/>
+      <c r="Q133" s="8" t="inlineStr"/>
+      <c r="R133" s="8" t="inlineStr"/>
+      <c r="S133" s="8" t="inlineStr"/>
+      <c r="T133" s="8" t="inlineStr"/>
+      <c r="U133" s="8" t="inlineStr"/>
+      <c r="V133" s="8" t="inlineStr"/>
+      <c r="W133" s="8" t="inlineStr"/>
+      <c r="X133" s="8" t="inlineStr">
+        <is>
+          <t>415.00</t>
+        </is>
+      </c>
+      <c r="Y133" s="8" t="inlineStr"/>
+      <c r="Z133" s="9" t="inlineStr"/>
+      <c r="AA133" s="10" t="inlineStr"/>
+      <c r="AB133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>UpNDown
+Random: 533.4
+Human: 11693.2</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 7985</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr"/>
+      <c r="D134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
+      <c r="G134" s="4" t="inlineStr"/>
+      <c r="H134" s="4" t="inlineStr"/>
+      <c r="I134" s="4" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr"/>
+      <c r="K134" s="4" t="inlineStr"/>
+      <c r="L134" s="4" t="inlineStr"/>
+      <c r="M134" s="4" t="inlineStr"/>
+      <c r="N134" s="4" t="inlineStr"/>
+      <c r="O134" s="4" t="inlineStr"/>
+      <c r="P134" s="4" t="inlineStr"/>
+      <c r="Q134" s="4" t="inlineStr"/>
+      <c r="R134" s="4" t="inlineStr"/>
+      <c r="S134" s="4" t="inlineStr"/>
+      <c r="T134" s="4" t="inlineStr"/>
+      <c r="U134" s="4" t="inlineStr"/>
+      <c r="V134" s="4" t="inlineStr"/>
+      <c r="W134" s="4" t="inlineStr"/>
+      <c r="X134" s="4" t="inlineStr"/>
+      <c r="Y134" s="4" t="inlineStr"/>
+      <c r="Z134" s="5" t="inlineStr"/>
+      <c r="AA134" s="6" t="n">
+        <v>-2053.75</v>
+      </c>
+      <c r="AB134" s="7" t="n">
+        <v>-0.1840310758257316</v>
+      </c>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="1" t="n"/>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>9044.00</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr"/>
+      <c r="E135" s="8" t="inlineStr"/>
+      <c r="F135" s="8" t="inlineStr"/>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr"/>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>5849.00</t>
+        </is>
+      </c>
+      <c r="J135" s="8" t="inlineStr"/>
+      <c r="K135" s="8" t="inlineStr"/>
+      <c r="L135" s="8" t="inlineStr"/>
+      <c r="M135" s="8" t="inlineStr"/>
+      <c r="N135" s="8" t="inlineStr"/>
+      <c r="O135" s="8" t="inlineStr">
+        <is>
+          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
+        </is>
+      </c>
+      <c r="P135" s="8" t="inlineStr">
+        <is>
+          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
+        </is>
+      </c>
+      <c r="Q135" s="12" t="inlineStr">
+        <is>
+          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
+        </is>
+      </c>
+      <c r="R135" s="8" t="inlineStr"/>
+      <c r="S135" s="8" t="inlineStr"/>
+      <c r="T135" s="8" t="inlineStr"/>
+      <c r="U135" s="8" t="inlineStr"/>
+      <c r="V135" s="8" t="inlineStr"/>
+      <c r="W135" s="8" t="inlineStr"/>
+      <c r="X135" s="8" t="inlineStr"/>
+      <c r="Y135" s="8" t="inlineStr"/>
+      <c r="Z135" s="9" t="n">
+        <v>5931.25</v>
+      </c>
+      <c r="AA135" s="10" t="inlineStr"/>
+      <c r="AB135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="1" t="n"/>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr"/>
+      <c r="D136" s="8" t="inlineStr"/>
+      <c r="E136" s="8" t="inlineStr"/>
+      <c r="F136" s="8" t="inlineStr"/>
+      <c r="G136" s="8" t="inlineStr"/>
+      <c r="H136" s="8" t="inlineStr"/>
+      <c r="I136" s="8" t="inlineStr"/>
+      <c r="J136" s="8" t="inlineStr"/>
+      <c r="K136" s="8" t="inlineStr"/>
+      <c r="L136" s="8" t="inlineStr"/>
+      <c r="M136" s="8" t="inlineStr"/>
+      <c r="N136" s="8" t="inlineStr"/>
+      <c r="O136" s="8" t="inlineStr">
+        <is>
+          <t>5670.00</t>
+        </is>
+      </c>
+      <c r="P136" s="8" t="inlineStr">
+        <is>
+          <t>7178.00</t>
+        </is>
+      </c>
+      <c r="Q136" s="12" t="inlineStr">
+        <is>
+          <t>3066.00</t>
+        </is>
+      </c>
+      <c r="R136" s="8" t="inlineStr"/>
+      <c r="S136" s="8" t="inlineStr"/>
+      <c r="T136" s="8" t="inlineStr"/>
+      <c r="U136" s="8" t="inlineStr"/>
+      <c r="V136" s="8" t="inlineStr"/>
+      <c r="W136" s="8" t="inlineStr"/>
+      <c r="X136" s="8" t="inlineStr"/>
+      <c r="Y136" s="8" t="inlineStr"/>
+      <c r="Z136" s="9" t="inlineStr"/>
+      <c r="AA136" s="10" t="inlineStr"/>
+      <c r="AB136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="24" customHeight="1">
+      <c r="A137" s="1" t="n"/>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr"/>
+      <c r="D137" s="8" t="inlineStr"/>
+      <c r="E137" s="8" t="inlineStr"/>
+      <c r="F137" s="8" t="inlineStr"/>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr"/>
+      <c r="I137" s="8" t="inlineStr"/>
+      <c r="J137" s="8" t="inlineStr"/>
+      <c r="K137" s="8" t="inlineStr"/>
+      <c r="L137" s="8" t="inlineStr"/>
+      <c r="M137" s="8" t="inlineStr"/>
+      <c r="N137" s="8" t="inlineStr"/>
+      <c r="O137" s="8" t="inlineStr">
         <is>
           <t>6043.00</t>
         </is>
       </c>
-      <c r="P124" s="8" t="inlineStr">
+      <c r="P137" s="8" t="inlineStr">
         <is>
           <t>6658.00</t>
         </is>
       </c>
-      <c r="Q124" s="8" t="inlineStr">
+      <c r="Q137" s="12" t="inlineStr">
         <is>
           <t>2974.50</t>
         </is>
       </c>
-      <c r="R124" s="8" t="inlineStr"/>
-      <c r="S124" s="8" t="inlineStr"/>
-      <c r="T124" s="8" t="inlineStr"/>
-      <c r="U124" s="8" t="inlineStr"/>
-      <c r="V124" s="8" t="inlineStr"/>
-      <c r="W124" s="8" t="inlineStr"/>
-      <c r="X124" s="9" t="n">
-        <v>5225.166666666667</v>
-      </c>
-      <c r="Y124" s="9" t="n">
-        <v>203.166666666667</v>
-      </c>
-      <c r="Z124" s="11" t="n">
-        <v>0.01820522470534122</v>
+      <c r="R137" s="15" t="inlineStr">
+        <is>
+          <t>7972.50</t>
+        </is>
+      </c>
+      <c r="S137" s="8" t="inlineStr"/>
+      <c r="T137" s="8" t="inlineStr"/>
+      <c r="U137" s="8" t="inlineStr"/>
+      <c r="V137" s="8" t="inlineStr"/>
+      <c r="W137" s="8" t="inlineStr"/>
+      <c r="X137" s="8" t="inlineStr"/>
+      <c r="Y137" s="8" t="inlineStr"/>
+      <c r="Z137" s="9" t="n">
+        <v>6350.5</v>
+      </c>
+      <c r="AA137" s="9" t="n">
+        <v>419.25</v>
+      </c>
+      <c r="AB137" s="11" t="n">
+        <v>0.03756787756052975</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A64:A69"/>
     <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="A74:A79"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A95:A100"/>
+    <mergeCell ref="A82:A87"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A128:A133"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="A117:A119"/>
+    <mergeCell ref="A124:A127"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A26:A31"/>
     <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A100:A105"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="A76:A81"/>
     <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A32:A37"/>
     <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="A96:A99"/>
     <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A115:A120"/>
-    <mergeCell ref="A68:A73"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="A44:A49"/>
-    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A92:A95"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -494,6 +494,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="U77" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="X77" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
@@ -532,6 +539,13 @@
     <comment ref="S78" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="U78" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -583,14 +597,17 @@
     </comment>
     <comment ref="U79" authorId="0" shapeId="0">
       <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="V79" authorId="0" shapeId="0">
+      <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="V79" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
     <comment ref="X79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
@@ -633,6 +650,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="U80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="X80" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
@@ -671,6 +695,13 @@
     <comment ref="S81" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="U81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -4952,7 +4983,7 @@
       <c r="R77" s="12" t="inlineStr"/>
       <c r="S77" s="12" t="inlineStr"/>
       <c r="T77" s="8" t="inlineStr"/>
-      <c r="U77" s="8" t="inlineStr"/>
+      <c r="U77" s="12" t="inlineStr"/>
       <c r="V77" s="8" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
@@ -5000,7 +5031,7 @@
       </c>
       <c r="S78" s="12" t="inlineStr"/>
       <c r="T78" s="8" t="inlineStr"/>
-      <c r="U78" s="8" t="inlineStr"/>
+      <c r="U78" s="12" t="inlineStr"/>
       <c r="V78" s="8" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
@@ -5066,7 +5097,7 @@
         </is>
       </c>
       <c r="T79" s="8" t="inlineStr"/>
-      <c r="U79" s="15" t="inlineStr">
+      <c r="U79" s="13" t="inlineStr">
         <is>
           <t>3061.00</t>
         </is>
@@ -5122,7 +5153,7 @@
       <c r="R80" s="12" t="inlineStr"/>
       <c r="S80" s="12" t="inlineStr"/>
       <c r="T80" s="8" t="inlineStr"/>
-      <c r="U80" s="8" t="inlineStr"/>
+      <c r="U80" s="12" t="inlineStr"/>
       <c r="V80" s="8" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
@@ -5160,7 +5191,7 @@
       <c r="R81" s="12" t="inlineStr"/>
       <c r="S81" s="12" t="inlineStr"/>
       <c r="T81" s="8" t="inlineStr"/>
-      <c r="U81" s="8" t="inlineStr"/>
+      <c r="U81" s="12" t="inlineStr"/>
       <c r="V81" s="8" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -175,10 +175,10 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -283,6 +283,111 @@
 모든 평균은 EXCLUDED_SEEDS를 제외한 공통 시드 기준이며 HNS 차이는 부호를 유지합니다. 백분율이 아닙니다.</t>
       </text>
     </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Alien, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Alien, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Alien, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Alien, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N7" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Alien, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Amidar, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Amidar, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Amidar, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N12" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Amidar, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N13" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Amidar, seed 5090
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Assault, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Assault, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L17" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Assault, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L18" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Assault, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Assault, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="Q27" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
@@ -354,6 +459,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="K33" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="P33" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
@@ -361,6 +473,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="K34" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="P34" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
@@ -368,6 +487,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="P35" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
@@ -375,9 +501,23 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="K36" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="P36" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K37" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -1382,10 +1522,10 @@
       <c r="Y2" s="4" t="inlineStr"/>
       <c r="Z2" s="5" t="inlineStr"/>
       <c r="AA2" s="6" t="n">
-        <v>57.79999999999995</v>
+        <v>107.625</v>
       </c>
       <c r="AB2" s="7" t="n">
-        <v>0.008376932999028966</v>
+        <v>0.01559805214568327</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
@@ -1418,7 +1558,7 @@
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>842.50</t>
         </is>
@@ -1442,11 +1582,11 @@
       <c r="W3" s="8" t="inlineStr"/>
       <c r="X3" s="8" t="inlineStr"/>
       <c r="Y3" s="8" t="inlineStr"/>
-      <c r="Z3" s="9" t="n">
-        <v>1041.8</v>
-      </c>
-      <c r="AA3" s="10" t="inlineStr"/>
-      <c r="AB3" s="11" t="inlineStr"/>
+      <c r="Z3" s="10" t="n">
+        <v>1091.625</v>
+      </c>
+      <c r="AA3" s="11" t="inlineStr"/>
+      <c r="AB3" s="12" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -1474,7 +1614,7 @@
       </c>
       <c r="L4" s="8" t="inlineStr"/>
       <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="9" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr">
         <is>
           <t>1303.50</t>
@@ -1494,9 +1634,9 @@
       <c r="W4" s="8" t="inlineStr"/>
       <c r="X4" s="8" t="inlineStr"/>
       <c r="Y4" s="8" t="inlineStr"/>
-      <c r="Z4" s="9" t="inlineStr"/>
-      <c r="AA4" s="10" t="inlineStr"/>
-      <c r="AB4" s="11" t="inlineStr"/>
+      <c r="Z4" s="10" t="inlineStr"/>
+      <c r="AA4" s="11" t="inlineStr"/>
+      <c r="AB4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -1524,7 +1664,7 @@
       </c>
       <c r="L5" s="8" t="inlineStr"/>
       <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>864.00</t>
         </is>
@@ -1548,14 +1688,14 @@
       <c r="W5" s="8" t="inlineStr"/>
       <c r="X5" s="8" t="inlineStr"/>
       <c r="Y5" s="8" t="inlineStr"/>
-      <c r="Z5" s="9" t="n">
-        <v>1091.1</v>
-      </c>
-      <c r="AA5" s="9" t="n">
-        <v>49.29999999999995</v>
-      </c>
-      <c r="AB5" s="11" t="n">
-        <v>0.007145031087407058</v>
+      <c r="Z5" s="10" t="n">
+        <v>1147.875</v>
+      </c>
+      <c r="AA5" s="10" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="AB5" s="12" t="n">
+        <v>0.0081522920622038</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
@@ -1580,7 +1720,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="9" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
@@ -1592,9 +1732,9 @@
       <c r="W6" s="8" t="inlineStr"/>
       <c r="X6" s="8" t="inlineStr"/>
       <c r="Y6" s="8" t="inlineStr"/>
-      <c r="Z6" s="9" t="inlineStr"/>
-      <c r="AA6" s="10" t="inlineStr"/>
-      <c r="AB6" s="11" t="inlineStr"/>
+      <c r="Z6" s="10" t="inlineStr"/>
+      <c r="AA6" s="11" t="inlineStr"/>
+      <c r="AB6" s="12" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="1" t="n"/>
@@ -1618,7 +1758,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr"/>
       <c r="M7" s="8" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="9" t="inlineStr"/>
       <c r="O7" s="8" t="inlineStr"/>
       <c r="P7" s="8" t="inlineStr"/>
       <c r="Q7" s="8" t="inlineStr"/>
@@ -1630,9 +1770,9 @@
       <c r="W7" s="8" t="inlineStr"/>
       <c r="X7" s="8" t="inlineStr"/>
       <c r="Y7" s="8" t="inlineStr"/>
-      <c r="Z7" s="9" t="inlineStr"/>
-      <c r="AA7" s="10" t="inlineStr"/>
-      <c r="AB7" s="11" t="inlineStr"/>
+      <c r="Z7" s="10" t="inlineStr"/>
+      <c r="AA7" s="11" t="inlineStr"/>
+      <c r="AB7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1672,10 +1812,10 @@
       <c r="Y8" s="4" t="inlineStr"/>
       <c r="Z8" s="5" t="inlineStr"/>
       <c r="AA8" s="6" t="n">
-        <v>2.849999999999994</v>
+        <v>3.599999999999994</v>
       </c>
       <c r="AB8" s="7" t="n">
-        <v>0.001663068214973446</v>
+        <v>0.002100717745229617</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -1704,7 +1844,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr"/>
       <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>204.85</t>
         </is>
@@ -1732,11 +1872,11 @@
       <c r="W9" s="8" t="inlineStr"/>
       <c r="X9" s="8" t="inlineStr"/>
       <c r="Y9" s="8" t="inlineStr"/>
-      <c r="Z9" s="9" t="n">
-        <v>207.85</v>
-      </c>
-      <c r="AA9" s="10" t="inlineStr"/>
-      <c r="AB9" s="11" t="inlineStr"/>
+      <c r="Z9" s="10" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="AA9" s="11" t="inlineStr"/>
+      <c r="AB9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -1760,7 +1900,7 @@
       <c r="K10" s="8" t="inlineStr"/>
       <c r="L10" s="8" t="inlineStr"/>
       <c r="M10" s="8" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr"/>
       <c r="O10" s="8" t="inlineStr">
         <is>
           <t>211.70</t>
@@ -1784,9 +1924,9 @@
       <c r="W10" s="8" t="inlineStr"/>
       <c r="X10" s="8" t="inlineStr"/>
       <c r="Y10" s="8" t="inlineStr"/>
-      <c r="Z10" s="9" t="inlineStr"/>
-      <c r="AA10" s="10" t="inlineStr"/>
-      <c r="AB10" s="11" t="inlineStr"/>
+      <c r="Z10" s="10" t="inlineStr"/>
+      <c r="AA10" s="11" t="inlineStr"/>
+      <c r="AB10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="1" t="n"/>
@@ -1814,7 +1954,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr"/>
       <c r="M11" s="8" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>147.80</t>
         </is>
@@ -1838,14 +1978,14 @@
       <c r="W11" s="8" t="inlineStr"/>
       <c r="X11" s="8" t="inlineStr"/>
       <c r="Y11" s="8" t="inlineStr"/>
-      <c r="Z11" s="9" t="n">
-        <v>164.88</v>
-      </c>
-      <c r="AA11" s="9" t="n">
-        <v>42.96999999999997</v>
-      </c>
-      <c r="AB11" s="11" t="n">
-        <v>-0.02507440042014353</v>
+      <c r="Z11" s="10" t="n">
+        <v>169.15</v>
+      </c>
+      <c r="AA11" s="10" t="n">
+        <v>39.44999999999999</v>
+      </c>
+      <c r="AB11" s="12" t="n">
+        <v>-0.02302036529147458</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
@@ -1866,7 +2006,7 @@
       <c r="K12" s="8" t="inlineStr"/>
       <c r="L12" s="8" t="inlineStr"/>
       <c r="M12" s="8" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="9" t="inlineStr"/>
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr">
@@ -1882,9 +2022,9 @@
       <c r="W12" s="8" t="inlineStr"/>
       <c r="X12" s="8" t="inlineStr"/>
       <c r="Y12" s="8" t="inlineStr"/>
-      <c r="Z12" s="9" t="inlineStr"/>
-      <c r="AA12" s="10" t="inlineStr"/>
-      <c r="AB12" s="11" t="inlineStr"/>
+      <c r="Z12" s="10" t="inlineStr"/>
+      <c r="AA12" s="11" t="inlineStr"/>
+      <c r="AB12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -1904,7 +2044,7 @@
       <c r="K13" s="8" t="inlineStr"/>
       <c r="L13" s="8" t="inlineStr"/>
       <c r="M13" s="8" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="9" t="inlineStr"/>
       <c r="O13" s="8" t="inlineStr"/>
       <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="8" t="inlineStr">
@@ -1920,9 +2060,9 @@
       <c r="W13" s="8" t="inlineStr"/>
       <c r="X13" s="8" t="inlineStr"/>
       <c r="Y13" s="8" t="inlineStr"/>
-      <c r="Z13" s="9" t="inlineStr"/>
-      <c r="AA13" s="10" t="inlineStr"/>
-      <c r="AB13" s="11" t="inlineStr"/>
+      <c r="Z13" s="10" t="inlineStr"/>
+      <c r="AA13" s="11" t="inlineStr"/>
+      <c r="AB13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1962,10 +2102,10 @@
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="5" t="inlineStr"/>
       <c r="AA14" s="6" t="n">
-        <v>-22.95000000000005</v>
+        <v>20.11249999999995</v>
       </c>
       <c r="AB14" s="7" t="n">
-        <v>-0.04416859122401856</v>
+        <v>0.03870765973826011</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
@@ -1992,7 +2132,7 @@
           <t>620.40</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>605.80</t>
         </is>
@@ -2022,11 +2162,11 @@
       <c r="W15" s="8" t="inlineStr"/>
       <c r="X15" s="8" t="inlineStr"/>
       <c r="Y15" s="8" t="inlineStr"/>
-      <c r="Z15" s="9" t="n">
-        <v>778.05</v>
-      </c>
-      <c r="AA15" s="10" t="inlineStr"/>
-      <c r="AB15" s="11" t="inlineStr"/>
+      <c r="Z15" s="10" t="n">
+        <v>821.1125</v>
+      </c>
+      <c r="AA15" s="11" t="inlineStr"/>
+      <c r="AB15" s="12" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -2052,7 +2192,7 @@
           <t>693.30</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr"/>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="8" t="inlineStr">
@@ -2074,9 +2214,9 @@
       <c r="W16" s="8" t="inlineStr"/>
       <c r="X16" s="8" t="inlineStr"/>
       <c r="Y16" s="8" t="inlineStr"/>
-      <c r="Z16" s="9" t="inlineStr"/>
-      <c r="AA16" s="10" t="inlineStr"/>
-      <c r="AB16" s="11" t="inlineStr"/>
+      <c r="Z16" s="10" t="inlineStr"/>
+      <c r="AA16" s="11" t="inlineStr"/>
+      <c r="AB16" s="12" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -2114,7 +2254,7 @@
           <t>666.55</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>633.05</t>
         </is>
@@ -2140,14 +2280,14 @@
       <c r="W17" s="8" t="inlineStr"/>
       <c r="X17" s="8" t="inlineStr"/>
       <c r="Y17" s="8" t="inlineStr"/>
-      <c r="Z17" s="9" t="n">
-        <v>705.5400000000001</v>
-      </c>
-      <c r="AA17" s="9" t="n">
-        <v>72.50999999999988</v>
-      </c>
-      <c r="AB17" s="11" t="n">
-        <v>-0.1395496535796764</v>
+      <c r="Z17" s="10" t="n">
+        <v>723.6625</v>
+      </c>
+      <c r="AA17" s="10" t="n">
+        <v>97.44999999999993</v>
+      </c>
+      <c r="AB17" s="12" t="n">
+        <v>-0.1875481139337951</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
@@ -2166,7 +2306,7 @@
       <c r="I18" s="8" t="inlineStr"/>
       <c r="J18" s="8" t="inlineStr"/>
       <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr"/>
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="8" t="inlineStr"/>
@@ -2184,9 +2324,9 @@
       <c r="W18" s="8" t="inlineStr"/>
       <c r="X18" s="8" t="inlineStr"/>
       <c r="Y18" s="8" t="inlineStr"/>
-      <c r="Z18" s="9" t="inlineStr"/>
-      <c r="AA18" s="10" t="inlineStr"/>
-      <c r="AB18" s="11" t="inlineStr"/>
+      <c r="Z18" s="10" t="inlineStr"/>
+      <c r="AA18" s="11" t="inlineStr"/>
+      <c r="AB18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
@@ -2204,7 +2344,7 @@
       <c r="I19" s="8" t="inlineStr"/>
       <c r="J19" s="8" t="inlineStr"/>
       <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr"/>
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="8" t="inlineStr"/>
@@ -2222,9 +2362,9 @@
       <c r="W19" s="8" t="inlineStr"/>
       <c r="X19" s="8" t="inlineStr"/>
       <c r="Y19" s="8" t="inlineStr"/>
-      <c r="Z19" s="9" t="inlineStr"/>
-      <c r="AA19" s="10" t="inlineStr"/>
-      <c r="AB19" s="11" t="inlineStr"/>
+      <c r="Z19" s="10" t="inlineStr"/>
+      <c r="AA19" s="11" t="inlineStr"/>
+      <c r="AB19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2320,11 +2460,11 @@
       <c r="W21" s="8" t="inlineStr"/>
       <c r="X21" s="8" t="inlineStr"/>
       <c r="Y21" s="8" t="inlineStr"/>
-      <c r="Z21" s="9" t="n">
+      <c r="Z21" s="10" t="n">
         <v>677.5</v>
       </c>
-      <c r="AA21" s="10" t="inlineStr"/>
-      <c r="AB21" s="11" t="inlineStr"/>
+      <c r="AA21" s="11" t="inlineStr"/>
+      <c r="AB21" s="12" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="1" t="n"/>
@@ -2368,9 +2508,9 @@
       <c r="W22" s="8" t="inlineStr"/>
       <c r="X22" s="8" t="inlineStr"/>
       <c r="Y22" s="8" t="inlineStr"/>
-      <c r="Z22" s="9" t="inlineStr"/>
-      <c r="AA22" s="10" t="inlineStr"/>
-      <c r="AB22" s="11" t="inlineStr"/>
+      <c r="Z22" s="10" t="inlineStr"/>
+      <c r="AA22" s="11" t="inlineStr"/>
+      <c r="AB22" s="12" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="1" t="n"/>
@@ -2418,13 +2558,13 @@
       <c r="W23" s="8" t="inlineStr"/>
       <c r="X23" s="8" t="inlineStr"/>
       <c r="Y23" s="8" t="inlineStr"/>
-      <c r="Z23" s="9" t="n">
+      <c r="Z23" s="10" t="n">
         <v>759.375</v>
       </c>
-      <c r="AA23" s="9" t="n">
+      <c r="AA23" s="10" t="n">
         <v>81.875</v>
       </c>
-      <c r="AB23" s="11" t="n">
+      <c r="AB23" s="12" t="n">
         <v>0.009872427139980468</v>
       </c>
     </row>
@@ -2462,9 +2602,9 @@
       <c r="W24" s="8" t="inlineStr"/>
       <c r="X24" s="8" t="inlineStr"/>
       <c r="Y24" s="8" t="inlineStr"/>
-      <c r="Z24" s="9" t="inlineStr"/>
-      <c r="AA24" s="10" t="inlineStr"/>
-      <c r="AB24" s="11" t="inlineStr"/>
+      <c r="Z24" s="10" t="inlineStr"/>
+      <c r="AA24" s="11" t="inlineStr"/>
+      <c r="AB24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -2500,9 +2640,9 @@
       <c r="W25" s="8" t="inlineStr"/>
       <c r="X25" s="8" t="inlineStr"/>
       <c r="Y25" s="8" t="inlineStr"/>
-      <c r="Z25" s="9" t="inlineStr"/>
-      <c r="AA25" s="10" t="inlineStr"/>
-      <c r="AB25" s="11" t="inlineStr"/>
+      <c r="Z25" s="10" t="inlineStr"/>
+      <c r="AA25" s="11" t="inlineStr"/>
+      <c r="AB25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2589,12 +2729,12 @@
           <t>170.00</t>
         </is>
       </c>
-      <c r="Q27" s="12" t="inlineStr">
+      <c r="Q27" s="9" t="inlineStr">
         <is>
           <t>677.00</t>
         </is>
       </c>
-      <c r="R27" s="12" t="inlineStr"/>
+      <c r="R27" s="9" t="inlineStr"/>
       <c r="S27" s="8" t="inlineStr"/>
       <c r="T27" s="8" t="inlineStr"/>
       <c r="U27" s="8" t="inlineStr"/>
@@ -2610,11 +2750,11 @@
         </is>
       </c>
       <c r="Y27" s="8" t="inlineStr"/>
-      <c r="Z27" s="9" t="n">
+      <c r="Z27" s="10" t="n">
         <v>556.25</v>
       </c>
-      <c r="AA27" s="10" t="inlineStr"/>
-      <c r="AB27" s="11" t="inlineStr"/>
+      <c r="AA27" s="11" t="inlineStr"/>
+      <c r="AB27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -2637,8 +2777,8 @@
       <c r="N28" s="8" t="inlineStr"/>
       <c r="O28" s="8" t="inlineStr"/>
       <c r="P28" s="8" t="inlineStr"/>
-      <c r="Q28" s="12" t="inlineStr"/>
-      <c r="R28" s="12" t="inlineStr"/>
+      <c r="Q28" s="9" t="inlineStr"/>
+      <c r="R28" s="9" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr"/>
       <c r="T28" s="8" t="inlineStr"/>
       <c r="U28" s="8" t="inlineStr"/>
@@ -2650,9 +2790,9 @@
         </is>
       </c>
       <c r="Y28" s="8" t="inlineStr"/>
-      <c r="Z28" s="9" t="inlineStr"/>
-      <c r="AA28" s="10" t="inlineStr"/>
-      <c r="AB28" s="11" t="inlineStr"/>
+      <c r="Z28" s="10" t="inlineStr"/>
+      <c r="AA28" s="11" t="inlineStr"/>
+      <c r="AB28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -2683,7 +2823,7 @@
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="8" t="inlineStr"/>
       <c r="P29" s="8" t="inlineStr"/>
-      <c r="Q29" s="12" t="inlineStr">
+      <c r="Q29" s="9" t="inlineStr">
         <is>
           <t>114.00</t>
         </is>
@@ -2708,13 +2848,13 @@
         </is>
       </c>
       <c r="Y29" s="8" t="inlineStr"/>
-      <c r="Z29" s="9" t="n">
+      <c r="Z29" s="10" t="n">
         <v>483.5</v>
       </c>
-      <c r="AA29" s="9" t="n">
+      <c r="AA29" s="10" t="n">
         <v>72.75</v>
       </c>
-      <c r="AB29" s="11" t="n">
+      <c r="AB29" s="12" t="n">
         <v>-0.09845716605765327</v>
       </c>
     </row>
@@ -2739,8 +2879,8 @@
       <c r="N30" s="8" t="inlineStr"/>
       <c r="O30" s="8" t="inlineStr"/>
       <c r="P30" s="8" t="inlineStr"/>
-      <c r="Q30" s="12" t="inlineStr"/>
-      <c r="R30" s="12" t="inlineStr"/>
+      <c r="Q30" s="9" t="inlineStr"/>
+      <c r="R30" s="9" t="inlineStr"/>
       <c r="S30" s="8" t="inlineStr"/>
       <c r="T30" s="8" t="inlineStr"/>
       <c r="U30" s="8" t="inlineStr"/>
@@ -2752,9 +2892,9 @@
         </is>
       </c>
       <c r="Y30" s="8" t="inlineStr"/>
-      <c r="Z30" s="9" t="inlineStr"/>
-      <c r="AA30" s="10" t="inlineStr"/>
-      <c r="AB30" s="11" t="inlineStr"/>
+      <c r="Z30" s="10" t="inlineStr"/>
+      <c r="AA30" s="11" t="inlineStr"/>
+      <c r="AB30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="1" t="n"/>
@@ -2777,8 +2917,8 @@
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="8" t="inlineStr"/>
       <c r="P31" s="8" t="inlineStr"/>
-      <c r="Q31" s="12" t="inlineStr"/>
-      <c r="R31" s="12" t="inlineStr"/>
+      <c r="Q31" s="9" t="inlineStr"/>
+      <c r="R31" s="9" t="inlineStr"/>
       <c r="S31" s="8" t="inlineStr"/>
       <c r="T31" s="8" t="inlineStr"/>
       <c r="U31" s="8" t="inlineStr"/>
@@ -2790,9 +2930,9 @@
         </is>
       </c>
       <c r="Y31" s="8" t="inlineStr"/>
-      <c r="Z31" s="9" t="inlineStr"/>
-      <c r="AA31" s="10" t="inlineStr"/>
-      <c r="AB31" s="11" t="inlineStr"/>
+      <c r="Z31" s="10" t="inlineStr"/>
+      <c r="AA31" s="11" t="inlineStr"/>
+      <c r="AB31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2832,10 +2972,10 @@
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="5" t="inlineStr"/>
       <c r="AA32" s="6" t="n">
-        <v>-2710</v>
+        <v>-1327.5</v>
       </c>
       <c r="AB32" s="7" t="n">
-        <v>-0.07781207379226186</v>
+        <v>-0.03811643098126481</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
@@ -2853,7 +2993,7 @@
       <c r="H33" s="8" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="8" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>5300.00</t>
         </is>
@@ -2874,7 +3014,7 @@
           <t>15100.00, 16150.00, 14200.00, 14800.00</t>
         </is>
       </c>
-      <c r="P33" s="12" t="inlineStr">
+      <c r="P33" s="9" t="inlineStr">
         <is>
           <t>9300.00, 8850.00, 8250.00, 9250.00</t>
         </is>
@@ -2892,11 +3032,11 @@
       <c r="W33" s="8" t="inlineStr"/>
       <c r="X33" s="8" t="inlineStr"/>
       <c r="Y33" s="8" t="inlineStr"/>
-      <c r="Z33" s="9" t="n">
-        <v>10830</v>
-      </c>
-      <c r="AA33" s="10" t="inlineStr"/>
-      <c r="AB33" s="11" t="inlineStr"/>
+      <c r="Z33" s="10" t="n">
+        <v>12212.5</v>
+      </c>
+      <c r="AA33" s="11" t="inlineStr"/>
+      <c r="AB33" s="12" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="1" t="n"/>
@@ -2913,7 +3053,7 @@
       <c r="H34" s="8" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr"/>
       <c r="J34" s="8" t="inlineStr"/>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>5550.00</t>
         </is>
@@ -2930,7 +3070,7 @@
           <t>10950.00</t>
         </is>
       </c>
-      <c r="P34" s="12" t="inlineStr">
+      <c r="P34" s="9" t="inlineStr">
         <is>
           <t>5900.00</t>
         </is>
@@ -2948,9 +3088,9 @@
       <c r="W34" s="8" t="inlineStr"/>
       <c r="X34" s="8" t="inlineStr"/>
       <c r="Y34" s="8" t="inlineStr"/>
-      <c r="Z34" s="9" t="inlineStr"/>
-      <c r="AA34" s="10" t="inlineStr"/>
-      <c r="AB34" s="11" t="inlineStr"/>
+      <c r="Z34" s="10" t="inlineStr"/>
+      <c r="AA34" s="11" t="inlineStr"/>
+      <c r="AB34" s="12" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="1" t="n"/>
@@ -2967,7 +3107,7 @@
       <c r="H35" s="8" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>5500.00</t>
         </is>
@@ -2988,7 +3128,7 @@
           <t>14350.00</t>
         </is>
       </c>
-      <c r="P35" s="12" t="inlineStr">
+      <c r="P35" s="9" t="inlineStr">
         <is>
           <t>5650.00</t>
         </is>
@@ -3006,14 +3146,14 @@
       <c r="W35" s="8" t="inlineStr"/>
       <c r="X35" s="8" t="inlineStr"/>
       <c r="Y35" s="8" t="inlineStr"/>
-      <c r="Z35" s="9" t="n">
-        <v>11600</v>
-      </c>
-      <c r="AA35" s="9" t="n">
-        <v>770</v>
-      </c>
-      <c r="AB35" s="11" t="n">
-        <v>0.02210896561625153</v>
+      <c r="Z35" s="10" t="n">
+        <v>13125</v>
+      </c>
+      <c r="AA35" s="10" t="n">
+        <v>912.5</v>
+      </c>
+      <c r="AB35" s="12" t="n">
+        <v>0.026200559902376</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
@@ -3031,7 +3171,7 @@
       <c r="H36" s="8" t="inlineStr"/>
       <c r="I36" s="8" t="inlineStr"/>
       <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
+      <c r="K36" s="9" t="inlineStr"/>
       <c r="L36" s="8" t="inlineStr"/>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
@@ -3040,7 +3180,7 @@
           <t>18350.00</t>
         </is>
       </c>
-      <c r="P36" s="12" t="inlineStr"/>
+      <c r="P36" s="9" t="inlineStr"/>
       <c r="Q36" s="14" t="inlineStr">
         <is>
           <t>RUNNING</t>
@@ -3054,9 +3194,9 @@
       <c r="W36" s="8" t="inlineStr"/>
       <c r="X36" s="8" t="inlineStr"/>
       <c r="Y36" s="8" t="inlineStr"/>
-      <c r="Z36" s="9" t="inlineStr"/>
-      <c r="AA36" s="10" t="inlineStr"/>
-      <c r="AB36" s="11" t="inlineStr"/>
+      <c r="Z36" s="10" t="inlineStr"/>
+      <c r="AA36" s="11" t="inlineStr"/>
+      <c r="AB36" s="12" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="1" t="n"/>
@@ -3073,7 +3213,7 @@
       <c r="H37" s="8" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr"/>
       <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr"/>
+      <c r="K37" s="9" t="inlineStr"/>
       <c r="L37" s="8" t="inlineStr"/>
       <c r="M37" s="8" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
@@ -3082,7 +3222,7 @@
           <t>19850.00</t>
         </is>
       </c>
-      <c r="P37" s="12" t="inlineStr"/>
+      <c r="P37" s="9" t="inlineStr"/>
       <c r="Q37" s="14" t="inlineStr">
         <is>
           <t>RUNNING</t>
@@ -3096,9 +3236,9 @@
       <c r="W37" s="8" t="inlineStr"/>
       <c r="X37" s="8" t="inlineStr"/>
       <c r="Y37" s="8" t="inlineStr"/>
-      <c r="Z37" s="9" t="inlineStr"/>
-      <c r="AA37" s="10" t="inlineStr"/>
-      <c r="AB37" s="11" t="inlineStr"/>
+      <c r="Z37" s="10" t="inlineStr"/>
+      <c r="AA37" s="11" t="inlineStr"/>
+      <c r="AB37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3179,7 +3319,7 @@
           <t>88.60</t>
         </is>
       </c>
-      <c r="O39" s="12" t="inlineStr">
+      <c r="O39" s="9" t="inlineStr">
         <is>
           <t>70.40</t>
         </is>
@@ -3202,11 +3342,11 @@
       <c r="W39" s="8" t="inlineStr"/>
       <c r="X39" s="8" t="inlineStr"/>
       <c r="Y39" s="8" t="inlineStr"/>
-      <c r="Z39" s="9" t="n">
+      <c r="Z39" s="10" t="n">
         <v>78.64999999999999</v>
       </c>
-      <c r="AA39" s="10" t="inlineStr"/>
-      <c r="AB39" s="11" t="inlineStr"/>
+      <c r="AA39" s="11" t="inlineStr"/>
+      <c r="AB39" s="12" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="1" t="n"/>
@@ -3231,7 +3371,7 @@
       <c r="L40" s="8" t="inlineStr"/>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
-      <c r="O40" s="12" t="inlineStr"/>
+      <c r="O40" s="9" t="inlineStr"/>
       <c r="P40" s="14" t="inlineStr">
         <is>
           <t>RUNNING</t>
@@ -3246,9 +3386,9 @@
       <c r="W40" s="8" t="inlineStr"/>
       <c r="X40" s="8" t="inlineStr"/>
       <c r="Y40" s="8" t="inlineStr"/>
-      <c r="Z40" s="9" t="inlineStr"/>
-      <c r="AA40" s="10" t="inlineStr"/>
-      <c r="AB40" s="11" t="inlineStr"/>
+      <c r="Z40" s="10" t="inlineStr"/>
+      <c r="AA40" s="11" t="inlineStr"/>
+      <c r="AB40" s="12" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="1" t="n"/>
@@ -3277,7 +3417,7 @@
       <c r="L41" s="8" t="inlineStr"/>
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
-      <c r="O41" s="12" t="inlineStr">
+      <c r="O41" s="9" t="inlineStr">
         <is>
           <t>51.15</t>
         </is>
@@ -3300,13 +3440,13 @@
       <c r="W41" s="8" t="inlineStr"/>
       <c r="X41" s="8" t="inlineStr"/>
       <c r="Y41" s="8" t="inlineStr"/>
-      <c r="Z41" s="9" t="n">
+      <c r="Z41" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="AA41" s="9" t="n">
+      <c r="AA41" s="10" t="n">
         <v>3.250000000000014</v>
       </c>
-      <c r="AB41" s="11" t="n">
+      <c r="AB41" s="12" t="n">
         <v>0.2708333333333345</v>
       </c>
     </row>
@@ -3329,7 +3469,7 @@
       <c r="L42" s="8" t="inlineStr"/>
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="8" t="inlineStr"/>
-      <c r="O42" s="12" t="inlineStr"/>
+      <c r="O42" s="9" t="inlineStr"/>
       <c r="P42" s="14" t="inlineStr">
         <is>
           <t>RUNNING</t>
@@ -3344,9 +3484,9 @@
       <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="8" t="inlineStr"/>
       <c r="Y42" s="8" t="inlineStr"/>
-      <c r="Z42" s="9" t="inlineStr"/>
-      <c r="AA42" s="10" t="inlineStr"/>
-      <c r="AB42" s="11" t="inlineStr"/>
+      <c r="Z42" s="10" t="inlineStr"/>
+      <c r="AA42" s="11" t="inlineStr"/>
+      <c r="AB42" s="12" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
@@ -3367,7 +3507,7 @@
       <c r="L43" s="8" t="inlineStr"/>
       <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
-      <c r="O43" s="12" t="inlineStr"/>
+      <c r="O43" s="9" t="inlineStr"/>
       <c r="P43" s="14" t="inlineStr">
         <is>
           <t>RUNNING</t>
@@ -3382,9 +3522,9 @@
       <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="8" t="inlineStr"/>
       <c r="Y43" s="8" t="inlineStr"/>
-      <c r="Z43" s="9" t="inlineStr"/>
-      <c r="AA43" s="10" t="inlineStr"/>
-      <c r="AB43" s="11" t="inlineStr"/>
+      <c r="Z43" s="10" t="inlineStr"/>
+      <c r="AA43" s="11" t="inlineStr"/>
+      <c r="AB43" s="12" t="inlineStr"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3480,11 +3620,11 @@
       <c r="W45" s="8" t="inlineStr"/>
       <c r="X45" s="8" t="inlineStr"/>
       <c r="Y45" s="8" t="inlineStr"/>
-      <c r="Z45" s="9" t="n">
+      <c r="Z45" s="10" t="n">
         <v>11.73333333333333</v>
       </c>
-      <c r="AA45" s="10" t="inlineStr"/>
-      <c r="AB45" s="11" t="inlineStr"/>
+      <c r="AA45" s="11" t="inlineStr"/>
+      <c r="AB45" s="12" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="1" t="n"/>
@@ -3528,9 +3668,9 @@
       <c r="W46" s="8" t="inlineStr"/>
       <c r="X46" s="8" t="inlineStr"/>
       <c r="Y46" s="8" t="inlineStr"/>
-      <c r="Z46" s="9" t="inlineStr"/>
-      <c r="AA46" s="10" t="inlineStr"/>
-      <c r="AB46" s="11" t="inlineStr"/>
+      <c r="Z46" s="10" t="inlineStr"/>
+      <c r="AA46" s="11" t="inlineStr"/>
+      <c r="AB46" s="12" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="1" t="n"/>
@@ -3574,13 +3714,13 @@
       <c r="W47" s="8" t="inlineStr"/>
       <c r="X47" s="8" t="inlineStr"/>
       <c r="Y47" s="8" t="inlineStr"/>
-      <c r="Z47" s="9" t="n">
+      <c r="Z47" s="10" t="n">
         <v>12.36666666666667</v>
       </c>
-      <c r="AA47" s="9" t="n">
+      <c r="AA47" s="10" t="n">
         <v>0.6333333333333311</v>
       </c>
-      <c r="AB47" s="11" t="n">
+      <c r="AB47" s="12" t="n">
         <v>0.02199074074074066</v>
       </c>
     </row>
@@ -3678,11 +3818,11 @@
       <c r="W49" s="8" t="inlineStr"/>
       <c r="X49" s="8" t="inlineStr"/>
       <c r="Y49" s="8" t="inlineStr"/>
-      <c r="Z49" s="9" t="n">
+      <c r="Z49" s="10" t="n">
         <v>1688.75</v>
       </c>
-      <c r="AA49" s="10" t="inlineStr"/>
-      <c r="AB49" s="11" t="inlineStr"/>
+      <c r="AA49" s="11" t="inlineStr"/>
+      <c r="AB49" s="12" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="1" t="n"/>
@@ -3722,9 +3862,9 @@
       <c r="W50" s="8" t="inlineStr"/>
       <c r="X50" s="8" t="inlineStr"/>
       <c r="Y50" s="8" t="inlineStr"/>
-      <c r="Z50" s="9" t="inlineStr"/>
-      <c r="AA50" s="10" t="inlineStr"/>
-      <c r="AB50" s="11" t="inlineStr"/>
+      <c r="Z50" s="10" t="inlineStr"/>
+      <c r="AA50" s="11" t="inlineStr"/>
+      <c r="AB50" s="12" t="inlineStr"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="1" t="n"/>
@@ -3772,13 +3912,13 @@
       <c r="W51" s="8" t="inlineStr"/>
       <c r="X51" s="8" t="inlineStr"/>
       <c r="Y51" s="8" t="inlineStr"/>
-      <c r="Z51" s="9" t="n">
+      <c r="Z51" s="10" t="n">
         <v>1425</v>
       </c>
-      <c r="AA51" s="9" t="n">
+      <c r="AA51" s="10" t="n">
         <v>263.75</v>
       </c>
-      <c r="AB51" s="11" t="n">
+      <c r="AB51" s="12" t="n">
         <v>-0.04010308964846126</v>
       </c>
     </row>
@@ -3820,9 +3960,9 @@
       <c r="W52" s="8" t="inlineStr"/>
       <c r="X52" s="8" t="inlineStr"/>
       <c r="Y52" s="8" t="inlineStr"/>
-      <c r="Z52" s="9" t="inlineStr"/>
-      <c r="AA52" s="10" t="inlineStr"/>
-      <c r="AB52" s="11" t="inlineStr"/>
+      <c r="Z52" s="10" t="inlineStr"/>
+      <c r="AA52" s="11" t="inlineStr"/>
+      <c r="AB52" s="12" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="1" t="n"/>
@@ -3862,9 +4002,9 @@
       <c r="W53" s="8" t="inlineStr"/>
       <c r="X53" s="8" t="inlineStr"/>
       <c r="Y53" s="8" t="inlineStr"/>
-      <c r="Z53" s="9" t="inlineStr"/>
-      <c r="AA53" s="10" t="inlineStr"/>
-      <c r="AB53" s="11" t="inlineStr"/>
+      <c r="Z53" s="10" t="inlineStr"/>
+      <c r="AA53" s="11" t="inlineStr"/>
+      <c r="AB53" s="12" t="inlineStr"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -3960,11 +4100,11 @@
       <c r="W55" s="8" t="inlineStr"/>
       <c r="X55" s="8" t="inlineStr"/>
       <c r="Y55" s="8" t="inlineStr"/>
-      <c r="Z55" s="9" t="n">
+      <c r="Z55" s="10" t="n">
         <v>57571.66666666666</v>
       </c>
-      <c r="AA55" s="10" t="inlineStr"/>
-      <c r="AB55" s="11" t="inlineStr"/>
+      <c r="AA55" s="11" t="inlineStr"/>
+      <c r="AB55" s="12" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="1" t="n"/>
@@ -4000,9 +4140,9 @@
       <c r="W56" s="8" t="inlineStr"/>
       <c r="X56" s="8" t="inlineStr"/>
       <c r="Y56" s="8" t="inlineStr"/>
-      <c r="Z56" s="9" t="inlineStr"/>
-      <c r="AA56" s="10" t="inlineStr"/>
-      <c r="AB56" s="11" t="inlineStr"/>
+      <c r="Z56" s="10" t="inlineStr"/>
+      <c r="AA56" s="11" t="inlineStr"/>
+      <c r="AB56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="1" t="n"/>
@@ -4046,13 +4186,13 @@
       <c r="W57" s="8" t="inlineStr"/>
       <c r="X57" s="8" t="inlineStr"/>
       <c r="Y57" s="8" t="inlineStr"/>
-      <c r="Z57" s="9" t="n">
+      <c r="Z57" s="10" t="n">
         <v>57908.33333333334</v>
       </c>
-      <c r="AA57" s="9" t="n">
+      <c r="AA57" s="10" t="n">
         <v>336.6666666666715</v>
       </c>
-      <c r="AB57" s="11" t="n">
+      <c r="AB57" s="12" t="n">
         <v>0.01344037728869018</v>
       </c>
     </row>
@@ -4150,11 +4290,11 @@
       <c r="W59" s="8" t="inlineStr"/>
       <c r="X59" s="8" t="inlineStr"/>
       <c r="Y59" s="8" t="inlineStr"/>
-      <c r="Z59" s="9" t="n">
+      <c r="Z59" s="10" t="n">
         <v>195.5833333333333</v>
       </c>
-      <c r="AA59" s="10" t="inlineStr"/>
-      <c r="AB59" s="11" t="inlineStr"/>
+      <c r="AA59" s="11" t="inlineStr"/>
+      <c r="AB59" s="12" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="1" t="n"/>
@@ -4190,9 +4330,9 @@
       <c r="W60" s="8" t="inlineStr"/>
       <c r="X60" s="8" t="inlineStr"/>
       <c r="Y60" s="8" t="inlineStr"/>
-      <c r="Z60" s="9" t="inlineStr"/>
-      <c r="AA60" s="10" t="inlineStr"/>
-      <c r="AB60" s="11" t="inlineStr"/>
+      <c r="Z60" s="10" t="inlineStr"/>
+      <c r="AA60" s="11" t="inlineStr"/>
+      <c r="AB60" s="12" t="inlineStr"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="1" t="n"/>
@@ -4236,13 +4376,13 @@
       <c r="W61" s="8" t="inlineStr"/>
       <c r="X61" s="8" t="inlineStr"/>
       <c r="Y61" s="8" t="inlineStr"/>
-      <c r="Z61" s="9" t="n">
+      <c r="Z61" s="10" t="n">
         <v>157.0833333333333</v>
       </c>
-      <c r="AA61" s="9" t="n">
+      <c r="AA61" s="10" t="n">
         <v>38.5</v>
       </c>
-      <c r="AB61" s="11" t="n">
+      <c r="AB61" s="12" t="n">
         <v>-0.02116663917752488</v>
       </c>
     </row>
@@ -4280,9 +4420,9 @@
       <c r="W62" s="8" t="inlineStr"/>
       <c r="X62" s="8" t="inlineStr"/>
       <c r="Y62" s="8" t="inlineStr"/>
-      <c r="Z62" s="9" t="inlineStr"/>
-      <c r="AA62" s="10" t="inlineStr"/>
-      <c r="AB62" s="11" t="inlineStr"/>
+      <c r="Z62" s="10" t="inlineStr"/>
+      <c r="AA62" s="11" t="inlineStr"/>
+      <c r="AB62" s="12" t="inlineStr"/>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="1" t="n"/>
@@ -4318,9 +4458,9 @@
       <c r="W63" s="8" t="inlineStr"/>
       <c r="X63" s="8" t="inlineStr"/>
       <c r="Y63" s="8" t="inlineStr"/>
-      <c r="Z63" s="9" t="inlineStr"/>
-      <c r="AA63" s="10" t="inlineStr"/>
-      <c r="AB63" s="11" t="inlineStr"/>
+      <c r="Z63" s="10" t="inlineStr"/>
+      <c r="AA63" s="11" t="inlineStr"/>
+      <c r="AB63" s="12" t="inlineStr"/>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -4412,11 +4552,11 @@
       <c r="W65" s="8" t="inlineStr"/>
       <c r="X65" s="8" t="inlineStr"/>
       <c r="Y65" s="8" t="inlineStr"/>
-      <c r="Z65" s="9" t="n">
+      <c r="Z65" s="10" t="n">
         <v>33.45</v>
       </c>
-      <c r="AA65" s="10" t="inlineStr"/>
-      <c r="AB65" s="11" t="inlineStr"/>
+      <c r="AA65" s="11" t="inlineStr"/>
+      <c r="AB65" s="12" t="inlineStr"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="1" t="n"/>
@@ -4452,9 +4592,9 @@
       <c r="W66" s="8" t="inlineStr"/>
       <c r="X66" s="8" t="inlineStr"/>
       <c r="Y66" s="8" t="inlineStr"/>
-      <c r="Z66" s="9" t="inlineStr"/>
-      <c r="AA66" s="10" t="inlineStr"/>
-      <c r="AB66" s="11" t="inlineStr"/>
+      <c r="Z66" s="10" t="inlineStr"/>
+      <c r="AA66" s="11" t="inlineStr"/>
+      <c r="AB66" s="12" t="inlineStr"/>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="1" t="n"/>
@@ -4498,13 +4638,13 @@
       <c r="W67" s="8" t="inlineStr"/>
       <c r="X67" s="8" t="inlineStr"/>
       <c r="Y67" s="8" t="inlineStr"/>
-      <c r="Z67" s="9" t="n">
+      <c r="Z67" s="10" t="n">
         <v>33.35</v>
       </c>
-      <c r="AA67" s="9" t="n">
+      <c r="AA67" s="10" t="n">
         <v>0.09999999999999432</v>
       </c>
-      <c r="AB67" s="11" t="n">
+      <c r="AB67" s="12" t="n">
         <v>-0.003378378378378186</v>
       </c>
     </row>
@@ -4542,9 +4682,9 @@
       <c r="W68" s="8" t="inlineStr"/>
       <c r="X68" s="8" t="inlineStr"/>
       <c r="Y68" s="8" t="inlineStr"/>
-      <c r="Z68" s="9" t="inlineStr"/>
-      <c r="AA68" s="10" t="inlineStr"/>
-      <c r="AB68" s="11" t="inlineStr"/>
+      <c r="Z68" s="10" t="inlineStr"/>
+      <c r="AA68" s="11" t="inlineStr"/>
+      <c r="AB68" s="12" t="inlineStr"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
@@ -4580,9 +4720,9 @@
       <c r="W69" s="8" t="inlineStr"/>
       <c r="X69" s="8" t="inlineStr"/>
       <c r="Y69" s="8" t="inlineStr"/>
-      <c r="Z69" s="9" t="inlineStr"/>
-      <c r="AA69" s="10" t="inlineStr"/>
-      <c r="AB69" s="11" t="inlineStr"/>
+      <c r="Z69" s="10" t="inlineStr"/>
+      <c r="AA69" s="11" t="inlineStr"/>
+      <c r="AB69" s="12" t="inlineStr"/>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -4637,7 +4777,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr"/>
       <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>2068.00</t>
         </is>
@@ -4678,11 +4818,11 @@
       <c r="W71" s="8" t="inlineStr"/>
       <c r="X71" s="8" t="inlineStr"/>
       <c r="Y71" s="8" t="inlineStr"/>
-      <c r="Z71" s="9" t="n">
+      <c r="Z71" s="10" t="n">
         <v>1742.375</v>
       </c>
-      <c r="AA71" s="10" t="inlineStr"/>
-      <c r="AB71" s="11" t="inlineStr"/>
+      <c r="AA71" s="11" t="inlineStr"/>
+      <c r="AB71" s="12" t="inlineStr"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="1" t="n"/>
@@ -4693,7 +4833,7 @@
       </c>
       <c r="C72" s="8" t="inlineStr"/>
       <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t>2301.00</t>
         </is>
@@ -4734,9 +4874,9 @@
       <c r="W72" s="8" t="inlineStr"/>
       <c r="X72" s="8" t="inlineStr"/>
       <c r="Y72" s="8" t="inlineStr"/>
-      <c r="Z72" s="9" t="inlineStr"/>
-      <c r="AA72" s="10" t="inlineStr"/>
-      <c r="AB72" s="11" t="inlineStr"/>
+      <c r="Z72" s="10" t="inlineStr"/>
+      <c r="AA72" s="11" t="inlineStr"/>
+      <c r="AB72" s="12" t="inlineStr"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="1" t="n"/>
@@ -4747,7 +4887,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr"/>
       <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>2113.50, 2350.50</t>
         </is>
@@ -4796,13 +4936,13 @@
       <c r="W73" s="8" t="inlineStr"/>
       <c r="X73" s="8" t="inlineStr"/>
       <c r="Y73" s="8" t="inlineStr"/>
-      <c r="Z73" s="9" t="n">
+      <c r="Z73" s="10" t="n">
         <v>1986.75</v>
       </c>
-      <c r="AA73" s="9" t="n">
+      <c r="AA73" s="10" t="n">
         <v>244.375</v>
       </c>
-      <c r="AB73" s="11" t="n">
+      <c r="AB73" s="12" t="n">
         <v>0.05723738142639653</v>
       </c>
     </row>
@@ -4815,7 +4955,7 @@
       </c>
       <c r="C74" s="8" t="inlineStr"/>
       <c r="D74" s="8" t="inlineStr"/>
-      <c r="E74" s="12" t="inlineStr"/>
+      <c r="E74" s="9" t="inlineStr"/>
       <c r="F74" s="8" t="inlineStr"/>
       <c r="G74" s="8" t="inlineStr"/>
       <c r="H74" s="8" t="inlineStr"/>
@@ -4844,9 +4984,9 @@
       <c r="W74" s="8" t="inlineStr"/>
       <c r="X74" s="8" t="inlineStr"/>
       <c r="Y74" s="8" t="inlineStr"/>
-      <c r="Z74" s="9" t="inlineStr"/>
-      <c r="AA74" s="10" t="inlineStr"/>
-      <c r="AB74" s="11" t="inlineStr"/>
+      <c r="Z74" s="10" t="inlineStr"/>
+      <c r="AA74" s="11" t="inlineStr"/>
+      <c r="AB74" s="12" t="inlineStr"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="1" t="n"/>
@@ -4857,7 +4997,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr"/>
       <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="12" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr"/>
@@ -4882,9 +5022,9 @@
       <c r="W75" s="8" t="inlineStr"/>
       <c r="X75" s="8" t="inlineStr"/>
       <c r="Y75" s="8" t="inlineStr"/>
-      <c r="Z75" s="9" t="inlineStr"/>
-      <c r="AA75" s="10" t="inlineStr"/>
-      <c r="AB75" s="11" t="inlineStr"/>
+      <c r="Z75" s="10" t="inlineStr"/>
+      <c r="AA75" s="11" t="inlineStr"/>
+      <c r="AB75" s="12" t="inlineStr"/>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -4969,38 +5109,38 @@
       <c r="L77" s="8" t="inlineStr"/>
       <c r="M77" s="8" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr"/>
-      <c r="O77" s="12" t="inlineStr">
+      <c r="O77" s="9" t="inlineStr">
         <is>
           <t>2486.00</t>
         </is>
       </c>
-      <c r="P77" s="12" t="inlineStr">
+      <c r="P77" s="9" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="Q77" s="12" t="inlineStr"/>
-      <c r="R77" s="12" t="inlineStr"/>
-      <c r="S77" s="12" t="inlineStr"/>
+      <c r="Q77" s="9" t="inlineStr"/>
+      <c r="R77" s="9" t="inlineStr"/>
+      <c r="S77" s="9" t="inlineStr"/>
       <c r="T77" s="8" t="inlineStr"/>
-      <c r="U77" s="12" t="inlineStr"/>
+      <c r="U77" s="9" t="inlineStr"/>
       <c r="V77" s="8" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
           <t>3585.00</t>
         </is>
       </c>
-      <c r="X77" s="12" t="inlineStr">
+      <c r="X77" s="9" t="inlineStr">
         <is>
           <t>2594.00</t>
         </is>
       </c>
       <c r="Y77" s="8" t="inlineStr"/>
-      <c r="Z77" s="9" t="n">
+      <c r="Z77" s="10" t="n">
         <v>3693</v>
       </c>
-      <c r="AA77" s="10" t="inlineStr"/>
-      <c r="AB77" s="11" t="inlineStr"/>
+      <c r="AA77" s="11" t="inlineStr"/>
+      <c r="AB77" s="12" t="inlineStr"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="1" t="n"/>
@@ -5021,28 +5161,28 @@
       <c r="L78" s="8" t="inlineStr"/>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr"/>
-      <c r="O78" s="12" t="inlineStr"/>
-      <c r="P78" s="12" t="inlineStr"/>
-      <c r="Q78" s="12" t="inlineStr"/>
-      <c r="R78" s="12" t="inlineStr">
+      <c r="O78" s="9" t="inlineStr"/>
+      <c r="P78" s="9" t="inlineStr"/>
+      <c r="Q78" s="9" t="inlineStr"/>
+      <c r="R78" s="9" t="inlineStr">
         <is>
           <t>2533.00</t>
         </is>
       </c>
-      <c r="S78" s="12" t="inlineStr"/>
+      <c r="S78" s="9" t="inlineStr"/>
       <c r="T78" s="8" t="inlineStr"/>
-      <c r="U78" s="12" t="inlineStr"/>
+      <c r="U78" s="9" t="inlineStr"/>
       <c r="V78" s="8" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
           <t>4472.00</t>
         </is>
       </c>
-      <c r="X78" s="12" t="inlineStr"/>
+      <c r="X78" s="9" t="inlineStr"/>
       <c r="Y78" s="8" t="inlineStr"/>
-      <c r="Z78" s="9" t="inlineStr"/>
-      <c r="AA78" s="10" t="inlineStr"/>
-      <c r="AB78" s="11" t="inlineStr"/>
+      <c r="Z78" s="10" t="inlineStr"/>
+      <c r="AA78" s="11" t="inlineStr"/>
+      <c r="AB78" s="12" t="inlineStr"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="1" t="n"/>
@@ -5071,12 +5211,12 @@
       <c r="L79" s="8" t="inlineStr"/>
       <c r="M79" s="8" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr"/>
-      <c r="O79" s="12" t="inlineStr">
+      <c r="O79" s="9" t="inlineStr">
         <is>
           <t>1024.00</t>
         </is>
       </c>
-      <c r="P79" s="12" t="inlineStr">
+      <c r="P79" s="9" t="inlineStr">
         <is>
           <t>927.00</t>
         </is>
@@ -5112,19 +5252,19 @@
           <t>7531.00</t>
         </is>
       </c>
-      <c r="X79" s="12" t="inlineStr">
+      <c r="X79" s="9" t="inlineStr">
         <is>
           <t>1005.00</t>
         </is>
       </c>
       <c r="Y79" s="8" t="inlineStr"/>
-      <c r="Z79" s="9" t="n">
+      <c r="Z79" s="10" t="n">
         <v>4895.666666666667</v>
       </c>
-      <c r="AA79" s="9" t="n">
+      <c r="AA79" s="10" t="n">
         <v>1202.666666666667</v>
       </c>
-      <c r="AB79" s="11" t="n">
+      <c r="AB79" s="12" t="n">
         <v>0.558107878169134</v>
       </c>
     </row>
@@ -5147,24 +5287,24 @@
       <c r="L80" s="8" t="inlineStr"/>
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="8" t="inlineStr"/>
-      <c r="O80" s="12" t="inlineStr"/>
-      <c r="P80" s="12" t="inlineStr"/>
-      <c r="Q80" s="12" t="inlineStr"/>
-      <c r="R80" s="12" t="inlineStr"/>
-      <c r="S80" s="12" t="inlineStr"/>
+      <c r="O80" s="9" t="inlineStr"/>
+      <c r="P80" s="9" t="inlineStr"/>
+      <c r="Q80" s="9" t="inlineStr"/>
+      <c r="R80" s="9" t="inlineStr"/>
+      <c r="S80" s="9" t="inlineStr"/>
       <c r="T80" s="8" t="inlineStr"/>
-      <c r="U80" s="12" t="inlineStr"/>
+      <c r="U80" s="9" t="inlineStr"/>
       <c r="V80" s="8" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
           <t>5320.00</t>
         </is>
       </c>
-      <c r="X80" s="12" t="inlineStr"/>
+      <c r="X80" s="9" t="inlineStr"/>
       <c r="Y80" s="8" t="inlineStr"/>
-      <c r="Z80" s="9" t="inlineStr"/>
-      <c r="AA80" s="10" t="inlineStr"/>
-      <c r="AB80" s="11" t="inlineStr"/>
+      <c r="Z80" s="10" t="inlineStr"/>
+      <c r="AA80" s="11" t="inlineStr"/>
+      <c r="AB80" s="12" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
@@ -5185,24 +5325,24 @@
       <c r="L81" s="8" t="inlineStr"/>
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="8" t="inlineStr"/>
-      <c r="O81" s="12" t="inlineStr"/>
-      <c r="P81" s="12" t="inlineStr"/>
-      <c r="Q81" s="12" t="inlineStr"/>
-      <c r="R81" s="12" t="inlineStr"/>
-      <c r="S81" s="12" t="inlineStr"/>
+      <c r="O81" s="9" t="inlineStr"/>
+      <c r="P81" s="9" t="inlineStr"/>
+      <c r="Q81" s="9" t="inlineStr"/>
+      <c r="R81" s="9" t="inlineStr"/>
+      <c r="S81" s="9" t="inlineStr"/>
       <c r="T81" s="8" t="inlineStr"/>
-      <c r="U81" s="12" t="inlineStr"/>
+      <c r="U81" s="9" t="inlineStr"/>
       <c r="V81" s="8" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>
           <t>2516.00</t>
         </is>
       </c>
-      <c r="X81" s="12" t="inlineStr"/>
+      <c r="X81" s="9" t="inlineStr"/>
       <c r="Y81" s="8" t="inlineStr"/>
-      <c r="Z81" s="9" t="inlineStr"/>
-      <c r="AA81" s="10" t="inlineStr"/>
-      <c r="AB81" s="11" t="inlineStr"/>
+      <c r="Z81" s="10" t="inlineStr"/>
+      <c r="AA81" s="11" t="inlineStr"/>
+      <c r="AB81" s="12" t="inlineStr"/>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -5294,11 +5434,11 @@
       <c r="W83" s="8" t="inlineStr"/>
       <c r="X83" s="8" t="inlineStr"/>
       <c r="Y83" s="8" t="inlineStr"/>
-      <c r="Z83" s="9" t="n">
+      <c r="Z83" s="10" t="n">
         <v>11785.625</v>
       </c>
-      <c r="AA83" s="10" t="inlineStr"/>
-      <c r="AB83" s="11" t="inlineStr"/>
+      <c r="AA83" s="11" t="inlineStr"/>
+      <c r="AB83" s="12" t="inlineStr"/>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="1" t="n"/>
@@ -5334,9 +5474,9 @@
       <c r="W84" s="8" t="inlineStr"/>
       <c r="X84" s="8" t="inlineStr"/>
       <c r="Y84" s="8" t="inlineStr"/>
-      <c r="Z84" s="9" t="inlineStr"/>
-      <c r="AA84" s="10" t="inlineStr"/>
-      <c r="AB84" s="11" t="inlineStr"/>
+      <c r="Z84" s="10" t="inlineStr"/>
+      <c r="AA84" s="11" t="inlineStr"/>
+      <c r="AB84" s="12" t="inlineStr"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
@@ -5384,13 +5524,13 @@
       <c r="W85" s="8" t="inlineStr"/>
       <c r="X85" s="8" t="inlineStr"/>
       <c r="Y85" s="8" t="inlineStr"/>
-      <c r="Z85" s="9" t="n">
+      <c r="Z85" s="10" t="n">
         <v>13229.25</v>
       </c>
-      <c r="AA85" s="9" t="n">
+      <c r="AA85" s="10" t="n">
         <v>1443.625</v>
       </c>
-      <c r="AB85" s="11" t="n">
+      <c r="AB85" s="12" t="n">
         <v>0.04844476734430894</v>
       </c>
     </row>
@@ -5428,9 +5568,9 @@
       <c r="W86" s="8" t="inlineStr"/>
       <c r="X86" s="8" t="inlineStr"/>
       <c r="Y86" s="8" t="inlineStr"/>
-      <c r="Z86" s="9" t="inlineStr"/>
-      <c r="AA86" s="10" t="inlineStr"/>
-      <c r="AB86" s="11" t="inlineStr"/>
+      <c r="Z86" s="10" t="inlineStr"/>
+      <c r="AA86" s="11" t="inlineStr"/>
+      <c r="AB86" s="12" t="inlineStr"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="1" t="n"/>
@@ -5466,9 +5606,9 @@
       <c r="W87" s="8" t="inlineStr"/>
       <c r="X87" s="8" t="inlineStr"/>
       <c r="Y87" s="8" t="inlineStr"/>
-      <c r="Z87" s="9" t="inlineStr"/>
-      <c r="AA87" s="10" t="inlineStr"/>
-      <c r="AB87" s="11" t="inlineStr"/>
+      <c r="Z87" s="10" t="inlineStr"/>
+      <c r="AA87" s="11" t="inlineStr"/>
+      <c r="AB87" s="12" t="inlineStr"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -5560,11 +5700,11 @@
         </is>
       </c>
       <c r="Y89" s="8" t="inlineStr"/>
-      <c r="Z89" s="9" t="n">
+      <c r="Z89" s="10" t="n">
         <v>473.3333333333333</v>
       </c>
-      <c r="AA89" s="10" t="inlineStr"/>
-      <c r="AB89" s="11" t="inlineStr"/>
+      <c r="AA89" s="11" t="inlineStr"/>
+      <c r="AB89" s="12" t="inlineStr"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="1" t="n"/>
@@ -5600,9 +5740,9 @@
       <c r="W90" s="8" t="inlineStr"/>
       <c r="X90" s="8" t="inlineStr"/>
       <c r="Y90" s="8" t="inlineStr"/>
-      <c r="Z90" s="9" t="inlineStr"/>
-      <c r="AA90" s="10" t="inlineStr"/>
-      <c r="AB90" s="11" t="inlineStr"/>
+      <c r="Z90" s="10" t="inlineStr"/>
+      <c r="AA90" s="11" t="inlineStr"/>
+      <c r="AB90" s="12" t="inlineStr"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="1" t="n"/>
@@ -5646,13 +5786,13 @@
         </is>
       </c>
       <c r="Y91" s="8" t="inlineStr"/>
-      <c r="Z91" s="9" t="n">
+      <c r="Z91" s="10" t="n">
         <v>535.8333333333334</v>
       </c>
-      <c r="AA91" s="9" t="n">
+      <c r="AA91" s="10" t="n">
         <v>62.50000000000006</v>
       </c>
-      <c r="AB91" s="11" t="n">
+      <c r="AB91" s="12" t="n">
         <v>0.2282688093498906</v>
       </c>
     </row>
@@ -5750,11 +5890,11 @@
       <c r="W93" s="8" t="inlineStr"/>
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="8" t="inlineStr"/>
-      <c r="Z93" s="9" t="n">
+      <c r="Z93" s="10" t="n">
         <v>1430</v>
       </c>
-      <c r="AA93" s="10" t="inlineStr"/>
-      <c r="AB93" s="11" t="inlineStr"/>
+      <c r="AA93" s="11" t="inlineStr"/>
+      <c r="AB93" s="12" t="inlineStr"/>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="1" t="n"/>
@@ -5798,9 +5938,9 @@
       <c r="W94" s="8" t="inlineStr"/>
       <c r="X94" s="8" t="inlineStr"/>
       <c r="Y94" s="8" t="inlineStr"/>
-      <c r="Z94" s="9" t="inlineStr"/>
-      <c r="AA94" s="10" t="inlineStr"/>
-      <c r="AB94" s="11" t="inlineStr"/>
+      <c r="Z94" s="10" t="inlineStr"/>
+      <c r="AA94" s="11" t="inlineStr"/>
+      <c r="AB94" s="12" t="inlineStr"/>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="1" t="n"/>
@@ -5852,13 +5992,13 @@
       <c r="W95" s="8" t="inlineStr"/>
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="8" t="inlineStr"/>
-      <c r="Z95" s="9" t="n">
+      <c r="Z95" s="10" t="n">
         <v>1445</v>
       </c>
-      <c r="AA95" s="9" t="n">
+      <c r="AA95" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="AB95" s="11" t="n">
+      <c r="AB95" s="12" t="n">
         <v>0.005028494803888703</v>
       </c>
     </row>
@@ -5933,12 +6073,12 @@
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="12" t="inlineStr">
+      <c r="K97" s="9" t="inlineStr">
         <is>
           <t>4708.50</t>
         </is>
       </c>
-      <c r="L97" s="12" t="inlineStr">
+      <c r="L97" s="9" t="inlineStr">
         <is>
           <t>5913.50</t>
         </is>
@@ -5950,13 +6090,13 @@
           <t>5228.50</t>
         </is>
       </c>
-      <c r="P97" s="12" t="inlineStr"/>
+      <c r="P97" s="9" t="inlineStr"/>
       <c r="Q97" s="8" t="inlineStr">
         <is>
           <t>5599.00</t>
         </is>
       </c>
-      <c r="R97" s="12" t="inlineStr"/>
+      <c r="R97" s="9" t="inlineStr"/>
       <c r="S97" s="8" t="inlineStr"/>
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
@@ -5968,11 +6108,11 @@
         </is>
       </c>
       <c r="Y97" s="8" t="inlineStr"/>
-      <c r="Z97" s="9" t="n">
+      <c r="Z97" s="10" t="n">
         <v>5829.625</v>
       </c>
-      <c r="AA97" s="10" t="inlineStr"/>
-      <c r="AB97" s="11" t="inlineStr"/>
+      <c r="AA97" s="11" t="inlineStr"/>
+      <c r="AB97" s="12" t="inlineStr"/>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="1" t="n"/>
@@ -5989,12 +6129,12 @@
       <c r="H98" s="8" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr"/>
       <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="12" t="inlineStr">
+      <c r="K98" s="9" t="inlineStr">
         <is>
           <t>4851.00</t>
         </is>
       </c>
-      <c r="L98" s="12" t="inlineStr">
+      <c r="L98" s="9" t="inlineStr">
         <is>
           <t>6044.00</t>
         </is>
@@ -6002,9 +6142,9 @@
       <c r="M98" s="8" t="inlineStr"/>
       <c r="N98" s="8" t="inlineStr"/>
       <c r="O98" s="8" t="inlineStr"/>
-      <c r="P98" s="12" t="inlineStr"/>
+      <c r="P98" s="9" t="inlineStr"/>
       <c r="Q98" s="8" t="inlineStr"/>
-      <c r="R98" s="12" t="inlineStr"/>
+      <c r="R98" s="9" t="inlineStr"/>
       <c r="S98" s="8" t="inlineStr"/>
       <c r="T98" s="8" t="inlineStr"/>
       <c r="U98" s="8" t="inlineStr"/>
@@ -6016,9 +6156,9 @@
         </is>
       </c>
       <c r="Y98" s="8" t="inlineStr"/>
-      <c r="Z98" s="9" t="inlineStr"/>
-      <c r="AA98" s="10" t="inlineStr"/>
-      <c r="AB98" s="11" t="inlineStr"/>
+      <c r="Z98" s="10" t="inlineStr"/>
+      <c r="AA98" s="11" t="inlineStr"/>
+      <c r="AB98" s="12" t="inlineStr"/>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="1" t="n"/>
@@ -6039,12 +6179,12 @@
       <c r="H99" s="8" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr"/>
       <c r="J99" s="8" t="inlineStr"/>
-      <c r="K99" s="12" t="inlineStr">
+      <c r="K99" s="9" t="inlineStr">
         <is>
           <t>5279.50</t>
         </is>
       </c>
-      <c r="L99" s="12" t="inlineStr">
+      <c r="L99" s="9" t="inlineStr">
         <is>
           <t>5889.50</t>
         </is>
@@ -6082,13 +6222,13 @@
         </is>
       </c>
       <c r="Y99" s="8" t="inlineStr"/>
-      <c r="Z99" s="9" t="n">
+      <c r="Z99" s="10" t="n">
         <v>6662.25</v>
       </c>
-      <c r="AA99" s="9" t="n">
+      <c r="AA99" s="10" t="n">
         <v>832.625</v>
       </c>
-      <c r="AB99" s="11" t="n">
+      <c r="AB99" s="12" t="n">
         <v>0.779976580796253</v>
       </c>
     </row>
@@ -6178,11 +6318,11 @@
       <c r="W101" s="8" t="inlineStr"/>
       <c r="X101" s="8" t="inlineStr"/>
       <c r="Y101" s="8" t="inlineStr"/>
-      <c r="Z101" s="9" t="n">
+      <c r="Z101" s="10" t="n">
         <v>25137.5</v>
       </c>
-      <c r="AA101" s="10" t="inlineStr"/>
-      <c r="AB101" s="11" t="inlineStr"/>
+      <c r="AA101" s="11" t="inlineStr"/>
+      <c r="AB101" s="12" t="inlineStr"/>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="1" t="n"/>
@@ -6218,9 +6358,9 @@
       <c r="W102" s="8" t="inlineStr"/>
       <c r="X102" s="8" t="inlineStr"/>
       <c r="Y102" s="8" t="inlineStr"/>
-      <c r="Z102" s="9" t="inlineStr"/>
-      <c r="AA102" s="10" t="inlineStr"/>
-      <c r="AB102" s="11" t="inlineStr"/>
+      <c r="Z102" s="10" t="inlineStr"/>
+      <c r="AA102" s="11" t="inlineStr"/>
+      <c r="AB102" s="12" t="inlineStr"/>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="1" t="n"/>
@@ -6260,13 +6400,13 @@
       <c r="W103" s="8" t="inlineStr"/>
       <c r="X103" s="8" t="inlineStr"/>
       <c r="Y103" s="8" t="inlineStr"/>
-      <c r="Z103" s="9" t="n">
+      <c r="Z103" s="10" t="n">
         <v>25177.5</v>
       </c>
-      <c r="AA103" s="9" t="n">
+      <c r="AA103" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="AB103" s="11" t="n">
+      <c r="AB103" s="12" t="n">
         <v>0.001779533584247569</v>
       </c>
     </row>
@@ -6304,9 +6444,9 @@
       <c r="W104" s="8" t="inlineStr"/>
       <c r="X104" s="8" t="inlineStr"/>
       <c r="Y104" s="8" t="inlineStr"/>
-      <c r="Z104" s="9" t="inlineStr"/>
-      <c r="AA104" s="10" t="inlineStr"/>
-      <c r="AB104" s="11" t="inlineStr"/>
+      <c r="Z104" s="10" t="inlineStr"/>
+      <c r="AA104" s="11" t="inlineStr"/>
+      <c r="AB104" s="12" t="inlineStr"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
@@ -6342,9 +6482,9 @@
       <c r="W105" s="8" t="inlineStr"/>
       <c r="X105" s="8" t="inlineStr"/>
       <c r="Y105" s="8" t="inlineStr"/>
-      <c r="Z105" s="9" t="inlineStr"/>
-      <c r="AA105" s="10" t="inlineStr"/>
-      <c r="AB105" s="11" t="inlineStr"/>
+      <c r="Z105" s="10" t="inlineStr"/>
+      <c r="AA105" s="11" t="inlineStr"/>
+      <c r="AB105" s="12" t="inlineStr"/>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -6436,11 +6576,11 @@
       <c r="W107" s="8" t="inlineStr"/>
       <c r="X107" s="8" t="inlineStr"/>
       <c r="Y107" s="8" t="inlineStr"/>
-      <c r="Z107" s="9" t="n">
+      <c r="Z107" s="10" t="n">
         <v>2071</v>
       </c>
-      <c r="AA107" s="10" t="inlineStr"/>
-      <c r="AB107" s="11" t="inlineStr"/>
+      <c r="AA107" s="11" t="inlineStr"/>
+      <c r="AB107" s="12" t="inlineStr"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="1" t="n"/>
@@ -6476,9 +6616,9 @@
       <c r="W108" s="8" t="inlineStr"/>
       <c r="X108" s="8" t="inlineStr"/>
       <c r="Y108" s="8" t="inlineStr"/>
-      <c r="Z108" s="9" t="inlineStr"/>
-      <c r="AA108" s="10" t="inlineStr"/>
-      <c r="AB108" s="11" t="inlineStr"/>
+      <c r="Z108" s="10" t="inlineStr"/>
+      <c r="AA108" s="11" t="inlineStr"/>
+      <c r="AB108" s="12" t="inlineStr"/>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="1" t="n"/>
@@ -6518,13 +6658,13 @@
       <c r="W109" s="8" t="inlineStr"/>
       <c r="X109" s="8" t="inlineStr"/>
       <c r="Y109" s="8" t="inlineStr"/>
-      <c r="Z109" s="9" t="n">
+      <c r="Z109" s="10" t="n">
         <v>2068.25</v>
       </c>
-      <c r="AA109" s="9" t="n">
+      <c r="AA109" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="AB109" s="11" t="n">
+      <c r="AB109" s="12" t="n">
         <v>-0.0004138885962403865</v>
       </c>
     </row>
@@ -6566,9 +6706,9 @@
       <c r="W110" s="8" t="inlineStr"/>
       <c r="X110" s="8" t="inlineStr"/>
       <c r="Y110" s="8" t="inlineStr"/>
-      <c r="Z110" s="9" t="inlineStr"/>
-      <c r="AA110" s="10" t="inlineStr"/>
-      <c r="AB110" s="11" t="inlineStr"/>
+      <c r="Z110" s="10" t="inlineStr"/>
+      <c r="AA110" s="11" t="inlineStr"/>
+      <c r="AB110" s="12" t="inlineStr"/>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="1" t="n"/>
@@ -6608,9 +6748,9 @@
       <c r="W111" s="8" t="inlineStr"/>
       <c r="X111" s="8" t="inlineStr"/>
       <c r="Y111" s="8" t="inlineStr"/>
-      <c r="Z111" s="9" t="inlineStr"/>
-      <c r="AA111" s="10" t="inlineStr"/>
-      <c r="AB111" s="11" t="inlineStr"/>
+      <c r="Z111" s="10" t="inlineStr"/>
+      <c r="AA111" s="11" t="inlineStr"/>
+      <c r="AB111" s="12" t="inlineStr"/>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -6702,11 +6842,11 @@
       <c r="W113" s="8" t="inlineStr"/>
       <c r="X113" s="8" t="inlineStr"/>
       <c r="Y113" s="8" t="inlineStr"/>
-      <c r="Z113" s="9" t="n">
+      <c r="Z113" s="10" t="n">
         <v>8.299999999999999</v>
       </c>
-      <c r="AA113" s="10" t="inlineStr"/>
-      <c r="AB113" s="11" t="inlineStr"/>
+      <c r="AA113" s="11" t="inlineStr"/>
+      <c r="AB113" s="12" t="inlineStr"/>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="1" t="n"/>
@@ -6758,13 +6898,13 @@
         </is>
       </c>
       <c r="Y114" s="8" t="inlineStr"/>
-      <c r="Z114" s="9" t="n">
+      <c r="Z114" s="10" t="n">
         <v>-0.6333333333333329</v>
       </c>
-      <c r="AA114" s="9" t="n">
+      <c r="AA114" s="10" t="n">
         <v>8.933333333333332</v>
       </c>
-      <c r="AB114" s="11" t="n">
+      <c r="AB114" s="12" t="n">
         <v>-0.2530689329556185</v>
       </c>
     </row>
@@ -6802,9 +6942,9 @@
       <c r="W115" s="8" t="inlineStr"/>
       <c r="X115" s="8" t="inlineStr"/>
       <c r="Y115" s="8" t="inlineStr"/>
-      <c r="Z115" s="9" t="inlineStr"/>
-      <c r="AA115" s="10" t="inlineStr"/>
-      <c r="AB115" s="11" t="inlineStr"/>
+      <c r="Z115" s="10" t="inlineStr"/>
+      <c r="AA115" s="11" t="inlineStr"/>
+      <c r="AB115" s="12" t="inlineStr"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="1" t="n"/>
@@ -6840,9 +6980,9 @@
       <c r="W116" s="8" t="inlineStr"/>
       <c r="X116" s="8" t="inlineStr"/>
       <c r="Y116" s="8" t="inlineStr"/>
-      <c r="Z116" s="9" t="inlineStr"/>
-      <c r="AA116" s="10" t="inlineStr"/>
-      <c r="AB116" s="11" t="inlineStr"/>
+      <c r="Z116" s="10" t="inlineStr"/>
+      <c r="AA116" s="11" t="inlineStr"/>
+      <c r="AB116" s="12" t="inlineStr"/>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
@@ -6915,7 +7055,7 @@
       <c r="L118" s="8" t="inlineStr"/>
       <c r="M118" s="8" t="inlineStr"/>
       <c r="N118" s="8" t="inlineStr"/>
-      <c r="O118" s="12" t="inlineStr">
+      <c r="O118" s="9" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
@@ -6930,7 +7070,7 @@
           <t>3551.75</t>
         </is>
       </c>
-      <c r="R118" s="12" t="inlineStr"/>
+      <c r="R118" s="9" t="inlineStr"/>
       <c r="S118" s="8" t="inlineStr"/>
       <c r="T118" s="8" t="inlineStr"/>
       <c r="U118" s="8" t="inlineStr"/>
@@ -6942,11 +7082,11 @@
         </is>
       </c>
       <c r="Y118" s="8" t="inlineStr"/>
-      <c r="Z118" s="9" t="n">
+      <c r="Z118" s="10" t="n">
         <v>1002.65</v>
       </c>
-      <c r="AA118" s="10" t="inlineStr"/>
-      <c r="AB118" s="11" t="inlineStr"/>
+      <c r="AA118" s="11" t="inlineStr"/>
+      <c r="AB118" s="12" t="inlineStr"/>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="1" t="n"/>
@@ -6971,7 +7111,7 @@
       <c r="L119" s="8" t="inlineStr"/>
       <c r="M119" s="8" t="inlineStr"/>
       <c r="N119" s="8" t="inlineStr"/>
-      <c r="O119" s="12" t="inlineStr">
+      <c r="O119" s="9" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
@@ -7002,13 +7142,13 @@
         </is>
       </c>
       <c r="Y119" s="8" t="inlineStr"/>
-      <c r="Z119" s="9" t="n">
+      <c r="Z119" s="10" t="n">
         <v>152.9875</v>
       </c>
-      <c r="AA119" s="9" t="n">
+      <c r="AA119" s="10" t="n">
         <v>849.6624999999999</v>
       </c>
-      <c r="AB119" s="11" t="n">
+      <c r="AB119" s="12" t="n">
         <v>-0.01221720319096315</v>
       </c>
     </row>
@@ -7077,7 +7217,7 @@
       <c r="F121" s="8" t="inlineStr"/>
       <c r="G121" s="8" t="inlineStr"/>
       <c r="H121" s="8" t="inlineStr"/>
-      <c r="I121" s="12" t="inlineStr">
+      <c r="I121" s="9" t="inlineStr">
         <is>
           <t>2940.00</t>
         </is>
@@ -7098,7 +7238,7 @@
       </c>
       <c r="P121" s="8" t="inlineStr"/>
       <c r="Q121" s="8" t="inlineStr"/>
-      <c r="R121" s="12" t="inlineStr"/>
+      <c r="R121" s="9" t="inlineStr"/>
       <c r="S121" s="8" t="inlineStr"/>
       <c r="T121" s="8" t="inlineStr"/>
       <c r="U121" s="8" t="inlineStr"/>
@@ -7106,11 +7246,11 @@
       <c r="W121" s="8" t="inlineStr"/>
       <c r="X121" s="8" t="inlineStr"/>
       <c r="Y121" s="8" t="inlineStr"/>
-      <c r="Z121" s="9" t="n">
+      <c r="Z121" s="10" t="n">
         <v>2859.0625</v>
       </c>
-      <c r="AA121" s="10" t="inlineStr"/>
-      <c r="AB121" s="11" t="inlineStr"/>
+      <c r="AA121" s="11" t="inlineStr"/>
+      <c r="AB121" s="12" t="inlineStr"/>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="1" t="n"/>
@@ -7133,7 +7273,7 @@
       <c r="F122" s="8" t="inlineStr"/>
       <c r="G122" s="8" t="inlineStr"/>
       <c r="H122" s="8" t="inlineStr"/>
-      <c r="I122" s="12" t="inlineStr">
+      <c r="I122" s="9" t="inlineStr">
         <is>
           <t>2553.75</t>
         </is>
@@ -7150,7 +7290,7 @@
       </c>
       <c r="P122" s="8" t="inlineStr"/>
       <c r="Q122" s="8" t="inlineStr"/>
-      <c r="R122" s="12" t="inlineStr"/>
+      <c r="R122" s="9" t="inlineStr"/>
       <c r="S122" s="8" t="inlineStr"/>
       <c r="T122" s="8" t="inlineStr"/>
       <c r="U122" s="8" t="inlineStr"/>
@@ -7158,9 +7298,9 @@
       <c r="W122" s="8" t="inlineStr"/>
       <c r="X122" s="8" t="inlineStr"/>
       <c r="Y122" s="8" t="inlineStr"/>
-      <c r="Z122" s="9" t="inlineStr"/>
-      <c r="AA122" s="10" t="inlineStr"/>
-      <c r="AB122" s="11" t="inlineStr"/>
+      <c r="Z122" s="10" t="inlineStr"/>
+      <c r="AA122" s="11" t="inlineStr"/>
+      <c r="AB122" s="12" t="inlineStr"/>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="1" t="n"/>
@@ -7183,7 +7323,7 @@
       <c r="F123" s="8" t="inlineStr"/>
       <c r="G123" s="8" t="inlineStr"/>
       <c r="H123" s="8" t="inlineStr"/>
-      <c r="I123" s="12" t="inlineStr">
+      <c r="I123" s="9" t="inlineStr">
         <is>
           <t>2338.75</t>
         </is>
@@ -7216,13 +7356,13 @@
       <c r="W123" s="8" t="inlineStr"/>
       <c r="X123" s="8" t="inlineStr"/>
       <c r="Y123" s="8" t="inlineStr"/>
-      <c r="Z123" s="9" t="n">
+      <c r="Z123" s="10" t="n">
         <v>3065.625</v>
       </c>
-      <c r="AA123" s="9" t="n">
+      <c r="AA123" s="10" t="n">
         <v>206.5625</v>
       </c>
-      <c r="AB123" s="11" t="n">
+      <c r="AB123" s="12" t="n">
         <v>0.01554141493179646</v>
       </c>
     </row>
@@ -7285,7 +7425,7 @@
       <c r="H125" s="8" t="inlineStr"/>
       <c r="I125" s="8" t="inlineStr"/>
       <c r="J125" s="8" t="inlineStr"/>
-      <c r="K125" s="12" t="inlineStr">
+      <c r="K125" s="9" t="inlineStr">
         <is>
           <t>8610.00</t>
         </is>
@@ -7316,11 +7456,11 @@
       <c r="W125" s="8" t="inlineStr"/>
       <c r="X125" s="8" t="inlineStr"/>
       <c r="Y125" s="8" t="inlineStr"/>
-      <c r="Z125" s="9" t="n">
+      <c r="Z125" s="10" t="n">
         <v>9045</v>
       </c>
-      <c r="AA125" s="10" t="inlineStr"/>
-      <c r="AB125" s="11" t="inlineStr"/>
+      <c r="AA125" s="11" t="inlineStr"/>
+      <c r="AB125" s="12" t="inlineStr"/>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="1" t="n"/>
@@ -7337,7 +7477,7 @@
       <c r="H126" s="8" t="inlineStr"/>
       <c r="I126" s="8" t="inlineStr"/>
       <c r="J126" s="8" t="inlineStr"/>
-      <c r="K126" s="12" t="inlineStr"/>
+      <c r="K126" s="9" t="inlineStr"/>
       <c r="L126" s="8" t="inlineStr"/>
       <c r="M126" s="8" t="inlineStr"/>
       <c r="N126" s="8" t="inlineStr"/>
@@ -7364,9 +7504,9 @@
       <c r="W126" s="8" t="inlineStr"/>
       <c r="X126" s="8" t="inlineStr"/>
       <c r="Y126" s="8" t="inlineStr"/>
-      <c r="Z126" s="9" t="inlineStr"/>
-      <c r="AA126" s="10" t="inlineStr"/>
-      <c r="AB126" s="11" t="inlineStr"/>
+      <c r="Z126" s="10" t="inlineStr"/>
+      <c r="AA126" s="11" t="inlineStr"/>
+      <c r="AB126" s="12" t="inlineStr"/>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="1" t="n"/>
@@ -7383,7 +7523,7 @@
       <c r="H127" s="8" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr"/>
       <c r="J127" s="8" t="inlineStr"/>
-      <c r="K127" s="12" t="inlineStr">
+      <c r="K127" s="9" t="inlineStr">
         <is>
           <t>8195.00</t>
         </is>
@@ -7418,13 +7558,13 @@
       <c r="W127" s="8" t="inlineStr"/>
       <c r="X127" s="8" t="inlineStr"/>
       <c r="Y127" s="8" t="inlineStr"/>
-      <c r="Z127" s="9" t="n">
+      <c r="Z127" s="10" t="n">
         <v>12731.66666666667</v>
       </c>
-      <c r="AA127" s="9" t="n">
+      <c r="AA127" s="10" t="n">
         <v>3686.666666666666</v>
       </c>
-      <c r="AB127" s="11" t="n">
+      <c r="AB127" s="12" t="n">
         <v>0.4706282845045849</v>
       </c>
     </row>
@@ -7518,11 +7658,11 @@
         </is>
       </c>
       <c r="Y129" s="8" t="inlineStr"/>
-      <c r="Z129" s="9" t="n">
+      <c r="Z129" s="10" t="n">
         <v>460.6666666666667</v>
       </c>
-      <c r="AA129" s="10" t="inlineStr"/>
-      <c r="AB129" s="11" t="inlineStr"/>
+      <c r="AA129" s="11" t="inlineStr"/>
+      <c r="AB129" s="12" t="inlineStr"/>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="1" t="n"/>
@@ -7562,9 +7702,9 @@
         </is>
       </c>
       <c r="Y130" s="8" t="inlineStr"/>
-      <c r="Z130" s="9" t="inlineStr"/>
-      <c r="AA130" s="10" t="inlineStr"/>
-      <c r="AB130" s="11" t="inlineStr"/>
+      <c r="Z130" s="10" t="inlineStr"/>
+      <c r="AA130" s="11" t="inlineStr"/>
+      <c r="AB130" s="12" t="inlineStr"/>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="1" t="n"/>
@@ -7608,13 +7748,13 @@
         </is>
       </c>
       <c r="Y131" s="8" t="inlineStr"/>
-      <c r="Z131" s="9" t="n">
+      <c r="Z131" s="10" t="n">
         <v>505.3333333333333</v>
       </c>
-      <c r="AA131" s="9" t="n">
+      <c r="AA131" s="10" t="n">
         <v>44.66666666666663</v>
       </c>
-      <c r="AB131" s="11" t="n">
+      <c r="AB131" s="12" t="n">
         <v>0.001063839077667397</v>
       </c>
     </row>
@@ -7652,9 +7792,9 @@
         </is>
       </c>
       <c r="Y132" s="8" t="inlineStr"/>
-      <c r="Z132" s="9" t="inlineStr"/>
-      <c r="AA132" s="10" t="inlineStr"/>
-      <c r="AB132" s="11" t="inlineStr"/>
+      <c r="Z132" s="10" t="inlineStr"/>
+      <c r="AA132" s="11" t="inlineStr"/>
+      <c r="AB132" s="12" t="inlineStr"/>
     </row>
     <row r="133" ht="24" customHeight="1">
       <c r="A133" s="1" t="n"/>
@@ -7690,9 +7830,9 @@
         </is>
       </c>
       <c r="Y133" s="8" t="inlineStr"/>
-      <c r="Z133" s="9" t="inlineStr"/>
-      <c r="AA133" s="10" t="inlineStr"/>
-      <c r="AB133" s="11" t="inlineStr"/>
+      <c r="Z133" s="10" t="inlineStr"/>
+      <c r="AA133" s="11" t="inlineStr"/>
+      <c r="AB133" s="12" t="inlineStr"/>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -7775,7 +7915,7 @@
           <t>6541.00, 6151.00, 6281.50, 5752.50</t>
         </is>
       </c>
-      <c r="Q135" s="12" t="inlineStr">
+      <c r="Q135" s="9" t="inlineStr">
         <is>
           <t>3203.50, 3308.00, 3088.00, 3095.00</t>
         </is>
@@ -7788,11 +7928,11 @@
       <c r="W135" s="8" t="inlineStr"/>
       <c r="X135" s="8" t="inlineStr"/>
       <c r="Y135" s="8" t="inlineStr"/>
-      <c r="Z135" s="9" t="n">
+      <c r="Z135" s="10" t="n">
         <v>5931.25</v>
       </c>
-      <c r="AA135" s="10" t="inlineStr"/>
-      <c r="AB135" s="11" t="inlineStr"/>
+      <c r="AA135" s="11" t="inlineStr"/>
+      <c r="AB135" s="12" t="inlineStr"/>
     </row>
     <row r="136" ht="24" customHeight="1">
       <c r="A136" s="1" t="n"/>
@@ -7823,7 +7963,7 @@
           <t>7178.00</t>
         </is>
       </c>
-      <c r="Q136" s="12" t="inlineStr">
+      <c r="Q136" s="9" t="inlineStr">
         <is>
           <t>3066.00</t>
         </is>
@@ -7836,9 +7976,9 @@
       <c r="W136" s="8" t="inlineStr"/>
       <c r="X136" s="8" t="inlineStr"/>
       <c r="Y136" s="8" t="inlineStr"/>
-      <c r="Z136" s="9" t="inlineStr"/>
-      <c r="AA136" s="10" t="inlineStr"/>
-      <c r="AB136" s="11" t="inlineStr"/>
+      <c r="Z136" s="10" t="inlineStr"/>
+      <c r="AA136" s="11" t="inlineStr"/>
+      <c r="AB136" s="12" t="inlineStr"/>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="1" t="n"/>
@@ -7869,7 +8009,7 @@
           <t>6658.00</t>
         </is>
       </c>
-      <c r="Q137" s="12" t="inlineStr">
+      <c r="Q137" s="9" t="inlineStr">
         <is>
           <t>2974.50</t>
         </is>
@@ -7886,13 +8026,13 @@
       <c r="W137" s="8" t="inlineStr"/>
       <c r="X137" s="8" t="inlineStr"/>
       <c r="Y137" s="8" t="inlineStr"/>
-      <c r="Z137" s="9" t="n">
+      <c r="Z137" s="10" t="n">
         <v>6350.5</v>
       </c>
-      <c r="AA137" s="9" t="n">
+      <c r="AA137" s="10" t="n">
         <v>419.25</v>
       </c>
-      <c r="AB137" s="11" t="n">
+      <c r="AB137" s="12" t="n">
         <v>0.03756787756052975</v>
       </c>
     </row>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -55,14 +55,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <strike val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="00006100"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <strike val="1"/>
+      <color rgb="00808080"/>
       <sz val="16"/>
     </font>
   </fonts>
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -179,10 +179,9 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -265,18 +264,18 @@
     <author>STORM</author>
   </authors>
   <commentList>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AB1" authorId="0" shapeId="0">
       <text>
         <t>Retrieval 미사용과 target: 16 양쪽에 유효한 점수가 있는 공통 시드만 사용합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드는 제외합니다. 각 시드에 여러 결과가 있으면 첫 번째 점수를 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: Retrieval 미사용의 공통 시드 평균 − STORM 논문 점수.
 target: 16 행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: (Retrieval 미사용 평균 − STORM 논문 점수) / (Human − Random).
 target: 16 행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
@@ -402,6 +401,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="S27" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="Q28" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
@@ -412,6 +418,13 @@
     <comment ref="R28" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S28" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -431,644 +444,890 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R30" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q31" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R31" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K33" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K34" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P34" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K35" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P35" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K36" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P36" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K37" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P37" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O39" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O40" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O41" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O42" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O43" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="E71" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="E72" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="E73" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="E74" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="E75" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Frostbite, seed 10
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O77" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P77" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q77" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R77" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="S77" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6040
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="U77" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9996
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="X77" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O78" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P78" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q78" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R78" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="S78" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6040
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="U78" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9996
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="X78" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O79" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P79" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q79" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+    <comment ref="S29" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="R79" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+    <comment ref="Q30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K33" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P33" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K34" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P34" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P35" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K36" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P36" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K37" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P37" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O39" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O40" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O41" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R41" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="O42" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O43" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="D45" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Breakout, seed 2
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="D46" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Breakout, seed 2
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="D47" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Breakout, seed 2
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="S79" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+    <comment ref="O57" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="R67" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Freeway, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R68" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Freeway, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R69" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Freeway, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="U79" authorId="0" shapeId="0">
+    <comment ref="R70" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Freeway, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R71" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Freeway, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="E73" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="E74" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="E75" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="E76" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="E77" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Frostbite, seed 10
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="V79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9995
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="W79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z79" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="V80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9995
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="W80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z80" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="V79" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="X79" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O80" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P80" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q80" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R80" authorId="0" shapeId="0">
+    <comment ref="R81" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="S80" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6040
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="U80" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9996
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="X80" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O81" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P81" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q81" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R81" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="S81" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6040
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="U81" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9996
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="X81" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R95" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="K97" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="L97" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P97" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R97" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K98" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="L98" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P98" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R98" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K99" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="L99" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 2010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P99" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 6010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="R99" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Krull, seed 6030
+    <comment ref="S81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="X114" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="O118" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R118" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: PrivateEye, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O119" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R119" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: PrivateEye, seed 6030
+    <comment ref="V81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="I121" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 3710
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R121" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="I122" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 3710
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R122" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="I123" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 3710
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R123" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+    <comment ref="W81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="K125" authorId="0" shapeId="0">
+    <comment ref="X81" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z81" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="V82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9995
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="W82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="V83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9995
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="W83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="C93" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="P95" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z95" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P96" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z96" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P97" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q97" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="R97" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z97" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="K99" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L99" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P99" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R99" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K100" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L100" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P100" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R100" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K101" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L101" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P101" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="R101" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="S101" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="L105" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="L115" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Pong, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="L116" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Pong, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z116" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="L117" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Pong, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O119" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R119" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O120" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R120" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: PrivateEye, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="I122" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R122" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I123" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R123" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I124" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R124" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="K126" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K126" authorId="0" shapeId="0">
+    <comment ref="O126" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: RoadRunner, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K127" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K127" authorId="0" shapeId="0">
+    <comment ref="O127" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: RoadRunner, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K128" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R127" authorId="0" shapeId="0">
+    <comment ref="O128" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: RoadRunner, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R128" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="Q135" authorId="0" shapeId="0">
+    <comment ref="S128" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="T128" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q136" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q136" authorId="0" shapeId="0">
+    <comment ref="Q137" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q137" authorId="0" shapeId="0">
+    <comment ref="Q138" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R137" authorId="0" shapeId="0">
+    <comment ref="R138" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z138" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1366,18 +1625,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB137"/>
+  <dimension ref="A1:AD138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
     <col width="54.7" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="20" max="20"/>
-    <col width="3" customWidth="1" min="25" max="25"/>
-    <col width="30" customWidth="1" min="26" max="26"/>
-    <col width="46" customWidth="1" min="27" max="27"/>
-    <col width="32" customWidth="1" min="28" max="28"/>
+    <col width="3" customWidth="1" min="21" max="21"/>
+    <col width="3" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="46" customWidth="1" min="29" max="29"/>
+    <col width="32" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1446,39 +1705,45 @@
       <c r="S1" s="1" t="n">
         <v>6040</v>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="n">
+        <v>6050</v>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>    </t>
         </is>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
+        <v>9995</v>
+      </c>
+      <c r="W1" s="1" t="n">
         <v>9996</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="X1" s="1" t="n">
         <v>9997</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="Y1" s="1" t="n">
         <v>9998</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="Z1" s="1" t="n">
         <v>9999</v>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>   </t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -1520,11 +1785,13 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr"/>
       <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="5" t="inlineStr"/>
-      <c r="AA2" s="6" t="n">
+      <c r="Z2" s="4" t="inlineStr"/>
+      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="AB2" s="5" t="inlineStr"/>
+      <c r="AC2" s="6" t="n">
         <v>107.625</v>
       </c>
-      <c r="AB2" s="7" t="n">
+      <c r="AD2" s="7" t="n">
         <v>0.01559805214568327</v>
       </c>
     </row>
@@ -1582,11 +1849,13 @@
       <c r="W3" s="8" t="inlineStr"/>
       <c r="X3" s="8" t="inlineStr"/>
       <c r="Y3" s="8" t="inlineStr"/>
-      <c r="Z3" s="10" t="n">
+      <c r="Z3" s="8" t="inlineStr"/>
+      <c r="AA3" s="8" t="inlineStr"/>
+      <c r="AB3" s="10" t="n">
         <v>1091.625</v>
       </c>
-      <c r="AA3" s="11" t="inlineStr"/>
-      <c r="AB3" s="12" t="inlineStr"/>
+      <c r="AC3" s="11" t="inlineStr"/>
+      <c r="AD3" s="12" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -1634,9 +1903,11 @@
       <c r="W4" s="8" t="inlineStr"/>
       <c r="X4" s="8" t="inlineStr"/>
       <c r="Y4" s="8" t="inlineStr"/>
-      <c r="Z4" s="10" t="inlineStr"/>
-      <c r="AA4" s="11" t="inlineStr"/>
-      <c r="AB4" s="12" t="inlineStr"/>
+      <c r="Z4" s="8" t="inlineStr"/>
+      <c r="AA4" s="8" t="inlineStr"/>
+      <c r="AB4" s="10" t="inlineStr"/>
+      <c r="AC4" s="11" t="inlineStr"/>
+      <c r="AD4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -1688,13 +1959,15 @@
       <c r="W5" s="8" t="inlineStr"/>
       <c r="X5" s="8" t="inlineStr"/>
       <c r="Y5" s="8" t="inlineStr"/>
-      <c r="Z5" s="10" t="n">
+      <c r="Z5" s="8" t="inlineStr"/>
+      <c r="AA5" s="8" t="inlineStr"/>
+      <c r="AB5" s="10" t="n">
         <v>1147.875</v>
       </c>
-      <c r="AA5" s="10" t="n">
+      <c r="AC5" s="10" t="n">
         <v>56.25</v>
       </c>
-      <c r="AB5" s="12" t="n">
+      <c r="AD5" s="12" t="n">
         <v>0.0081522920622038</v>
       </c>
     </row>
@@ -1732,9 +2005,11 @@
       <c r="W6" s="8" t="inlineStr"/>
       <c r="X6" s="8" t="inlineStr"/>
       <c r="Y6" s="8" t="inlineStr"/>
-      <c r="Z6" s="10" t="inlineStr"/>
-      <c r="AA6" s="11" t="inlineStr"/>
-      <c r="AB6" s="12" t="inlineStr"/>
+      <c r="Z6" s="8" t="inlineStr"/>
+      <c r="AA6" s="8" t="inlineStr"/>
+      <c r="AB6" s="10" t="inlineStr"/>
+      <c r="AC6" s="11" t="inlineStr"/>
+      <c r="AD6" s="12" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="1" t="n"/>
@@ -1770,9 +2045,11 @@
       <c r="W7" s="8" t="inlineStr"/>
       <c r="X7" s="8" t="inlineStr"/>
       <c r="Y7" s="8" t="inlineStr"/>
-      <c r="Z7" s="10" t="inlineStr"/>
-      <c r="AA7" s="11" t="inlineStr"/>
-      <c r="AB7" s="12" t="inlineStr"/>
+      <c r="Z7" s="8" t="inlineStr"/>
+      <c r="AA7" s="8" t="inlineStr"/>
+      <c r="AB7" s="10" t="inlineStr"/>
+      <c r="AC7" s="11" t="inlineStr"/>
+      <c r="AD7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1810,11 +2087,13 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
       <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="5" t="inlineStr"/>
-      <c r="AA8" s="6" t="n">
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="5" t="inlineStr"/>
+      <c r="AC8" s="6" t="n">
         <v>3.599999999999994</v>
       </c>
-      <c r="AB8" s="7" t="n">
+      <c r="AD8" s="7" t="n">
         <v>0.002100717745229617</v>
       </c>
     </row>
@@ -1872,11 +2151,13 @@
       <c r="W9" s="8" t="inlineStr"/>
       <c r="X9" s="8" t="inlineStr"/>
       <c r="Y9" s="8" t="inlineStr"/>
-      <c r="Z9" s="10" t="n">
+      <c r="Z9" s="8" t="inlineStr"/>
+      <c r="AA9" s="8" t="inlineStr"/>
+      <c r="AB9" s="10" t="n">
         <v>208.6</v>
       </c>
-      <c r="AA9" s="11" t="inlineStr"/>
-      <c r="AB9" s="12" t="inlineStr"/>
+      <c r="AC9" s="11" t="inlineStr"/>
+      <c r="AD9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -1924,9 +2205,11 @@
       <c r="W10" s="8" t="inlineStr"/>
       <c r="X10" s="8" t="inlineStr"/>
       <c r="Y10" s="8" t="inlineStr"/>
-      <c r="Z10" s="10" t="inlineStr"/>
-      <c r="AA10" s="11" t="inlineStr"/>
-      <c r="AB10" s="12" t="inlineStr"/>
+      <c r="Z10" s="8" t="inlineStr"/>
+      <c r="AA10" s="8" t="inlineStr"/>
+      <c r="AB10" s="10" t="inlineStr"/>
+      <c r="AC10" s="11" t="inlineStr"/>
+      <c r="AD10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="1" t="n"/>
@@ -1978,13 +2261,15 @@
       <c r="W11" s="8" t="inlineStr"/>
       <c r="X11" s="8" t="inlineStr"/>
       <c r="Y11" s="8" t="inlineStr"/>
-      <c r="Z11" s="10" t="n">
+      <c r="Z11" s="8" t="inlineStr"/>
+      <c r="AA11" s="8" t="inlineStr"/>
+      <c r="AB11" s="10" t="n">
         <v>169.15</v>
       </c>
-      <c r="AA11" s="10" t="n">
+      <c r="AC11" s="10" t="n">
         <v>39.44999999999999</v>
       </c>
-      <c r="AB11" s="12" t="n">
+      <c r="AD11" s="12" t="n">
         <v>-0.02302036529147458</v>
       </c>
     </row>
@@ -2022,9 +2307,11 @@
       <c r="W12" s="8" t="inlineStr"/>
       <c r="X12" s="8" t="inlineStr"/>
       <c r="Y12" s="8" t="inlineStr"/>
-      <c r="Z12" s="10" t="inlineStr"/>
-      <c r="AA12" s="11" t="inlineStr"/>
-      <c r="AB12" s="12" t="inlineStr"/>
+      <c r="Z12" s="8" t="inlineStr"/>
+      <c r="AA12" s="8" t="inlineStr"/>
+      <c r="AB12" s="10" t="inlineStr"/>
+      <c r="AC12" s="11" t="inlineStr"/>
+      <c r="AD12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -2060,9 +2347,11 @@
       <c r="W13" s="8" t="inlineStr"/>
       <c r="X13" s="8" t="inlineStr"/>
       <c r="Y13" s="8" t="inlineStr"/>
-      <c r="Z13" s="10" t="inlineStr"/>
-      <c r="AA13" s="11" t="inlineStr"/>
-      <c r="AB13" s="12" t="inlineStr"/>
+      <c r="Z13" s="8" t="inlineStr"/>
+      <c r="AA13" s="8" t="inlineStr"/>
+      <c r="AB13" s="10" t="inlineStr"/>
+      <c r="AC13" s="11" t="inlineStr"/>
+      <c r="AD13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2100,11 +2389,13 @@
       <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="5" t="inlineStr"/>
-      <c r="AA14" s="6" t="n">
+      <c r="Z14" s="4" t="inlineStr"/>
+      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AB14" s="5" t="inlineStr"/>
+      <c r="AC14" s="6" t="n">
         <v>20.11249999999995</v>
       </c>
-      <c r="AB14" s="7" t="n">
+      <c r="AD14" s="7" t="n">
         <v>0.03870765973826011</v>
       </c>
     </row>
@@ -2162,11 +2453,13 @@
       <c r="W15" s="8" t="inlineStr"/>
       <c r="X15" s="8" t="inlineStr"/>
       <c r="Y15" s="8" t="inlineStr"/>
-      <c r="Z15" s="10" t="n">
+      <c r="Z15" s="8" t="inlineStr"/>
+      <c r="AA15" s="8" t="inlineStr"/>
+      <c r="AB15" s="10" t="n">
         <v>821.1125</v>
       </c>
-      <c r="AA15" s="11" t="inlineStr"/>
-      <c r="AB15" s="12" t="inlineStr"/>
+      <c r="AC15" s="11" t="inlineStr"/>
+      <c r="AD15" s="12" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -2214,9 +2507,11 @@
       <c r="W16" s="8" t="inlineStr"/>
       <c r="X16" s="8" t="inlineStr"/>
       <c r="Y16" s="8" t="inlineStr"/>
-      <c r="Z16" s="10" t="inlineStr"/>
-      <c r="AA16" s="11" t="inlineStr"/>
-      <c r="AB16" s="12" t="inlineStr"/>
+      <c r="Z16" s="8" t="inlineStr"/>
+      <c r="AA16" s="8" t="inlineStr"/>
+      <c r="AB16" s="10" t="inlineStr"/>
+      <c r="AC16" s="11" t="inlineStr"/>
+      <c r="AD16" s="12" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -2280,13 +2575,15 @@
       <c r="W17" s="8" t="inlineStr"/>
       <c r="X17" s="8" t="inlineStr"/>
       <c r="Y17" s="8" t="inlineStr"/>
-      <c r="Z17" s="10" t="n">
+      <c r="Z17" s="8" t="inlineStr"/>
+      <c r="AA17" s="8" t="inlineStr"/>
+      <c r="AB17" s="10" t="n">
         <v>723.6625</v>
       </c>
-      <c r="AA17" s="10" t="n">
+      <c r="AC17" s="10" t="n">
         <v>97.44999999999993</v>
       </c>
-      <c r="AB17" s="12" t="n">
+      <c r="AD17" s="12" t="n">
         <v>-0.1875481139337951</v>
       </c>
     </row>
@@ -2324,9 +2621,11 @@
       <c r="W18" s="8" t="inlineStr"/>
       <c r="X18" s="8" t="inlineStr"/>
       <c r="Y18" s="8" t="inlineStr"/>
-      <c r="Z18" s="10" t="inlineStr"/>
-      <c r="AA18" s="11" t="inlineStr"/>
-      <c r="AB18" s="12" t="inlineStr"/>
+      <c r="Z18" s="8" t="inlineStr"/>
+      <c r="AA18" s="8" t="inlineStr"/>
+      <c r="AB18" s="10" t="inlineStr"/>
+      <c r="AC18" s="11" t="inlineStr"/>
+      <c r="AD18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
@@ -2362,9 +2661,11 @@
       <c r="W19" s="8" t="inlineStr"/>
       <c r="X19" s="8" t="inlineStr"/>
       <c r="Y19" s="8" t="inlineStr"/>
-      <c r="Z19" s="10" t="inlineStr"/>
-      <c r="AA19" s="11" t="inlineStr"/>
-      <c r="AB19" s="12" t="inlineStr"/>
+      <c r="Z19" s="8" t="inlineStr"/>
+      <c r="AA19" s="8" t="inlineStr"/>
+      <c r="AB19" s="10" t="inlineStr"/>
+      <c r="AC19" s="11" t="inlineStr"/>
+      <c r="AD19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2402,11 +2703,13 @@
       <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="5" t="inlineStr"/>
-      <c r="AA20" s="6" t="n">
+      <c r="Z20" s="4" t="inlineStr"/>
+      <c r="AA20" s="4" t="inlineStr"/>
+      <c r="AB20" s="5" t="inlineStr"/>
+      <c r="AC20" s="6" t="n">
         <v>-350.5</v>
       </c>
-      <c r="AB20" s="7" t="n">
+      <c r="AD20" s="7" t="n">
         <v>-0.04226303160382478</v>
       </c>
     </row>
@@ -2460,11 +2763,13 @@
       <c r="W21" s="8" t="inlineStr"/>
       <c r="X21" s="8" t="inlineStr"/>
       <c r="Y21" s="8" t="inlineStr"/>
-      <c r="Z21" s="10" t="n">
+      <c r="Z21" s="8" t="inlineStr"/>
+      <c r="AA21" s="8" t="inlineStr"/>
+      <c r="AB21" s="10" t="n">
         <v>677.5</v>
       </c>
-      <c r="AA21" s="11" t="inlineStr"/>
-      <c r="AB21" s="12" t="inlineStr"/>
+      <c r="AC21" s="11" t="inlineStr"/>
+      <c r="AD21" s="12" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="1" t="n"/>
@@ -2508,9 +2813,11 @@
       <c r="W22" s="8" t="inlineStr"/>
       <c r="X22" s="8" t="inlineStr"/>
       <c r="Y22" s="8" t="inlineStr"/>
-      <c r="Z22" s="10" t="inlineStr"/>
-      <c r="AA22" s="11" t="inlineStr"/>
-      <c r="AB22" s="12" t="inlineStr"/>
+      <c r="Z22" s="8" t="inlineStr"/>
+      <c r="AA22" s="8" t="inlineStr"/>
+      <c r="AB22" s="10" t="inlineStr"/>
+      <c r="AC22" s="11" t="inlineStr"/>
+      <c r="AD22" s="12" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="1" t="n"/>
@@ -2558,13 +2865,15 @@
       <c r="W23" s="8" t="inlineStr"/>
       <c r="X23" s="8" t="inlineStr"/>
       <c r="Y23" s="8" t="inlineStr"/>
-      <c r="Z23" s="10" t="n">
+      <c r="Z23" s="8" t="inlineStr"/>
+      <c r="AA23" s="8" t="inlineStr"/>
+      <c r="AB23" s="10" t="n">
         <v>759.375</v>
       </c>
-      <c r="AA23" s="10" t="n">
+      <c r="AC23" s="10" t="n">
         <v>81.875</v>
       </c>
-      <c r="AB23" s="12" t="n">
+      <c r="AD23" s="12" t="n">
         <v>0.009872427139980468</v>
       </c>
     </row>
@@ -2602,9 +2911,11 @@
       <c r="W24" s="8" t="inlineStr"/>
       <c r="X24" s="8" t="inlineStr"/>
       <c r="Y24" s="8" t="inlineStr"/>
-      <c r="Z24" s="10" t="inlineStr"/>
-      <c r="AA24" s="11" t="inlineStr"/>
-      <c r="AB24" s="12" t="inlineStr"/>
+      <c r="Z24" s="8" t="inlineStr"/>
+      <c r="AA24" s="8" t="inlineStr"/>
+      <c r="AB24" s="10" t="inlineStr"/>
+      <c r="AC24" s="11" t="inlineStr"/>
+      <c r="AD24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -2640,9 +2951,11 @@
       <c r="W25" s="8" t="inlineStr"/>
       <c r="X25" s="8" t="inlineStr"/>
       <c r="Y25" s="8" t="inlineStr"/>
-      <c r="Z25" s="10" t="inlineStr"/>
-      <c r="AA25" s="11" t="inlineStr"/>
-      <c r="AB25" s="12" t="inlineStr"/>
+      <c r="Z25" s="8" t="inlineStr"/>
+      <c r="AA25" s="8" t="inlineStr"/>
+      <c r="AB25" s="10" t="inlineStr"/>
+      <c r="AC25" s="11" t="inlineStr"/>
+      <c r="AD25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2680,11 +2993,13 @@
       <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
-      <c r="Z26" s="5" t="inlineStr"/>
-      <c r="AA26" s="6" t="n">
+      <c r="Z26" s="4" t="inlineStr"/>
+      <c r="AA26" s="4" t="inlineStr"/>
+      <c r="AB26" s="5" t="inlineStr"/>
+      <c r="AC26" s="6" t="n">
         <v>-84.75</v>
       </c>
-      <c r="AB26" s="7" t="n">
+      <c r="AD26" s="7" t="n">
         <v>-0.1146975233455136</v>
       </c>
     </row>
@@ -2735,26 +3050,28 @@
         </is>
       </c>
       <c r="R27" s="9" t="inlineStr"/>
-      <c r="S27" s="8" t="inlineStr"/>
+      <c r="S27" s="9" t="inlineStr"/>
       <c r="T27" s="8" t="inlineStr"/>
       <c r="U27" s="8" t="inlineStr"/>
       <c r="V27" s="8" t="inlineStr"/>
-      <c r="W27" s="8" t="inlineStr">
+      <c r="W27" s="8" t="inlineStr"/>
+      <c r="X27" s="8" t="inlineStr"/>
+      <c r="Y27" s="8" t="inlineStr">
         <is>
           <t>694.50</t>
         </is>
       </c>
-      <c r="X27" s="8" t="inlineStr">
+      <c r="Z27" s="8" t="inlineStr">
         <is>
           <t>668.50</t>
         </is>
       </c>
-      <c r="Y27" s="8" t="inlineStr"/>
-      <c r="Z27" s="10" t="n">
+      <c r="AA27" s="8" t="inlineStr"/>
+      <c r="AB27" s="10" t="n">
         <v>556.25</v>
       </c>
-      <c r="AA27" s="11" t="inlineStr"/>
-      <c r="AB27" s="12" t="inlineStr"/>
+      <c r="AC27" s="11" t="inlineStr"/>
+      <c r="AD27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -2779,20 +3096,22 @@
       <c r="P28" s="8" t="inlineStr"/>
       <c r="Q28" s="9" t="inlineStr"/>
       <c r="R28" s="9" t="inlineStr"/>
-      <c r="S28" s="8" t="inlineStr"/>
+      <c r="S28" s="9" t="inlineStr"/>
       <c r="T28" s="8" t="inlineStr"/>
       <c r="U28" s="8" t="inlineStr"/>
       <c r="V28" s="8" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr"/>
-      <c r="X28" s="8" t="inlineStr">
+      <c r="X28" s="8" t="inlineStr"/>
+      <c r="Y28" s="8" t="inlineStr"/>
+      <c r="Z28" s="8" t="inlineStr">
         <is>
           <t>507.50</t>
         </is>
       </c>
-      <c r="Y28" s="8" t="inlineStr"/>
-      <c r="Z28" s="10" t="inlineStr"/>
-      <c r="AA28" s="11" t="inlineStr"/>
-      <c r="AB28" s="12" t="inlineStr"/>
+      <c r="AA28" s="8" t="inlineStr"/>
+      <c r="AB28" s="10" t="inlineStr"/>
+      <c r="AC28" s="11" t="inlineStr"/>
+      <c r="AD28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -2833,28 +3152,34 @@
           <t>144.00</t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr"/>
+      <c r="S29" s="13" t="inlineStr">
+        <is>
+          <t>179.00</t>
+        </is>
+      </c>
       <c r="T29" s="8" t="inlineStr"/>
       <c r="U29" s="8" t="inlineStr"/>
       <c r="V29" s="8" t="inlineStr"/>
-      <c r="W29" s="8" t="inlineStr">
+      <c r="W29" s="8" t="inlineStr"/>
+      <c r="X29" s="8" t="inlineStr"/>
+      <c r="Y29" s="8" t="inlineStr">
         <is>
           <t>566.00</t>
         </is>
       </c>
-      <c r="X29" s="8" t="inlineStr">
+      <c r="Z29" s="8" t="inlineStr">
         <is>
           <t>565.00</t>
         </is>
       </c>
-      <c r="Y29" s="8" t="inlineStr"/>
-      <c r="Z29" s="10" t="n">
+      <c r="AA29" s="8" t="inlineStr"/>
+      <c r="AB29" s="10" t="n">
         <v>483.5</v>
       </c>
-      <c r="AA29" s="10" t="n">
+      <c r="AC29" s="10" t="n">
         <v>72.75</v>
       </c>
-      <c r="AB29" s="12" t="n">
+      <c r="AD29" s="12" t="n">
         <v>-0.09845716605765327</v>
       </c>
     </row>
@@ -2881,20 +3206,22 @@
       <c r="P30" s="8" t="inlineStr"/>
       <c r="Q30" s="9" t="inlineStr"/>
       <c r="R30" s="9" t="inlineStr"/>
-      <c r="S30" s="8" t="inlineStr"/>
+      <c r="S30" s="9" t="inlineStr"/>
       <c r="T30" s="8" t="inlineStr"/>
       <c r="U30" s="8" t="inlineStr"/>
       <c r="V30" s="8" t="inlineStr"/>
       <c r="W30" s="8" t="inlineStr"/>
-      <c r="X30" s="8" t="inlineStr">
+      <c r="X30" s="8" t="inlineStr"/>
+      <c r="Y30" s="8" t="inlineStr"/>
+      <c r="Z30" s="8" t="inlineStr">
         <is>
           <t>652.50</t>
         </is>
       </c>
-      <c r="Y30" s="8" t="inlineStr"/>
-      <c r="Z30" s="10" t="inlineStr"/>
-      <c r="AA30" s="11" t="inlineStr"/>
-      <c r="AB30" s="12" t="inlineStr"/>
+      <c r="AA30" s="8" t="inlineStr"/>
+      <c r="AB30" s="10" t="inlineStr"/>
+      <c r="AC30" s="11" t="inlineStr"/>
+      <c r="AD30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="1" t="n"/>
@@ -2919,20 +3246,22 @@
       <c r="P31" s="8" t="inlineStr"/>
       <c r="Q31" s="9" t="inlineStr"/>
       <c r="R31" s="9" t="inlineStr"/>
-      <c r="S31" s="8" t="inlineStr"/>
+      <c r="S31" s="9" t="inlineStr"/>
       <c r="T31" s="8" t="inlineStr"/>
       <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr"/>
-      <c r="X31" s="8" t="inlineStr">
+      <c r="X31" s="8" t="inlineStr"/>
+      <c r="Y31" s="8" t="inlineStr"/>
+      <c r="Z31" s="8" t="inlineStr">
         <is>
           <t>381.50</t>
         </is>
       </c>
-      <c r="Y31" s="8" t="inlineStr"/>
-      <c r="Z31" s="10" t="inlineStr"/>
-      <c r="AA31" s="11" t="inlineStr"/>
-      <c r="AB31" s="12" t="inlineStr"/>
+      <c r="AA31" s="8" t="inlineStr"/>
+      <c r="AB31" s="10" t="inlineStr"/>
+      <c r="AC31" s="11" t="inlineStr"/>
+      <c r="AD31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2970,11 +3299,13 @@
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
-      <c r="Z32" s="5" t="inlineStr"/>
-      <c r="AA32" s="6" t="n">
+      <c r="Z32" s="4" t="inlineStr"/>
+      <c r="AA32" s="4" t="inlineStr"/>
+      <c r="AB32" s="5" t="inlineStr"/>
+      <c r="AC32" s="6" t="n">
         <v>-1327.5</v>
       </c>
-      <c r="AB32" s="7" t="n">
+      <c r="AD32" s="7" t="n">
         <v>-0.03811643098126481</v>
       </c>
     </row>
@@ -3032,11 +3363,13 @@
       <c r="W33" s="8" t="inlineStr"/>
       <c r="X33" s="8" t="inlineStr"/>
       <c r="Y33" s="8" t="inlineStr"/>
-      <c r="Z33" s="10" t="n">
+      <c r="Z33" s="8" t="inlineStr"/>
+      <c r="AA33" s="8" t="inlineStr"/>
+      <c r="AB33" s="10" t="n">
         <v>12212.5</v>
       </c>
-      <c r="AA33" s="11" t="inlineStr"/>
-      <c r="AB33" s="12" t="inlineStr"/>
+      <c r="AC33" s="11" t="inlineStr"/>
+      <c r="AD33" s="12" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="1" t="n"/>
@@ -3088,9 +3421,11 @@
       <c r="W34" s="8" t="inlineStr"/>
       <c r="X34" s="8" t="inlineStr"/>
       <c r="Y34" s="8" t="inlineStr"/>
-      <c r="Z34" s="10" t="inlineStr"/>
-      <c r="AA34" s="11" t="inlineStr"/>
-      <c r="AB34" s="12" t="inlineStr"/>
+      <c r="Z34" s="8" t="inlineStr"/>
+      <c r="AA34" s="8" t="inlineStr"/>
+      <c r="AB34" s="10" t="inlineStr"/>
+      <c r="AC34" s="11" t="inlineStr"/>
+      <c r="AD34" s="12" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="1" t="n"/>
@@ -3146,13 +3481,15 @@
       <c r="W35" s="8" t="inlineStr"/>
       <c r="X35" s="8" t="inlineStr"/>
       <c r="Y35" s="8" t="inlineStr"/>
-      <c r="Z35" s="10" t="n">
+      <c r="Z35" s="8" t="inlineStr"/>
+      <c r="AA35" s="8" t="inlineStr"/>
+      <c r="AB35" s="10" t="n">
         <v>13125</v>
       </c>
-      <c r="AA35" s="10" t="n">
+      <c r="AC35" s="10" t="n">
         <v>912.5</v>
       </c>
-      <c r="AB35" s="12" t="n">
+      <c r="AD35" s="12" t="n">
         <v>0.026200559902376</v>
       </c>
     </row>
@@ -3181,9 +3518,9 @@
         </is>
       </c>
       <c r="P36" s="9" t="inlineStr"/>
-      <c r="Q36" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>8550.00</t>
         </is>
       </c>
       <c r="R36" s="8" t="inlineStr"/>
@@ -3194,9 +3531,11 @@
       <c r="W36" s="8" t="inlineStr"/>
       <c r="X36" s="8" t="inlineStr"/>
       <c r="Y36" s="8" t="inlineStr"/>
-      <c r="Z36" s="10" t="inlineStr"/>
-      <c r="AA36" s="11" t="inlineStr"/>
-      <c r="AB36" s="12" t="inlineStr"/>
+      <c r="Z36" s="8" t="inlineStr"/>
+      <c r="AA36" s="8" t="inlineStr"/>
+      <c r="AB36" s="10" t="inlineStr"/>
+      <c r="AC36" s="11" t="inlineStr"/>
+      <c r="AD36" s="12" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="1" t="n"/>
@@ -3223,9 +3562,9 @@
         </is>
       </c>
       <c r="P37" s="9" t="inlineStr"/>
-      <c r="Q37" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>6700.00</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr"/>
@@ -3236,9 +3575,11 @@
       <c r="W37" s="8" t="inlineStr"/>
       <c r="X37" s="8" t="inlineStr"/>
       <c r="Y37" s="8" t="inlineStr"/>
-      <c r="Z37" s="10" t="inlineStr"/>
-      <c r="AA37" s="11" t="inlineStr"/>
-      <c r="AB37" s="12" t="inlineStr"/>
+      <c r="Z37" s="8" t="inlineStr"/>
+      <c r="AA37" s="8" t="inlineStr"/>
+      <c r="AB37" s="10" t="inlineStr"/>
+      <c r="AC37" s="11" t="inlineStr"/>
+      <c r="AD37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3276,11 +3617,13 @@
       <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
-      <c r="Z38" s="5" t="inlineStr"/>
-      <c r="AA38" s="6" t="n">
+      <c r="Z38" s="4" t="inlineStr"/>
+      <c r="AA38" s="4" t="inlineStr"/>
+      <c r="AB38" s="5" t="inlineStr"/>
+      <c r="AC38" s="6" t="n">
         <v>-1.350000000000009</v>
       </c>
-      <c r="AB38" s="7" t="n">
+      <c r="AD38" s="7" t="n">
         <v>-0.1125000000000007</v>
       </c>
     </row>
@@ -3342,11 +3685,13 @@
       <c r="W39" s="8" t="inlineStr"/>
       <c r="X39" s="8" t="inlineStr"/>
       <c r="Y39" s="8" t="inlineStr"/>
-      <c r="Z39" s="10" t="n">
+      <c r="Z39" s="8" t="inlineStr"/>
+      <c r="AA39" s="8" t="inlineStr"/>
+      <c r="AB39" s="10" t="n">
         <v>78.64999999999999</v>
       </c>
-      <c r="AA39" s="11" t="inlineStr"/>
-      <c r="AB39" s="12" t="inlineStr"/>
+      <c r="AC39" s="11" t="inlineStr"/>
+      <c r="AD39" s="12" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="1" t="n"/>
@@ -3372,9 +3717,9 @@
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
       <c r="O40" s="9" t="inlineStr"/>
-      <c r="P40" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="P40" s="8" t="inlineStr">
+        <is>
+          <t>82.05</t>
         </is>
       </c>
       <c r="Q40" s="8" t="inlineStr"/>
@@ -3386,9 +3731,11 @@
       <c r="W40" s="8" t="inlineStr"/>
       <c r="X40" s="8" t="inlineStr"/>
       <c r="Y40" s="8" t="inlineStr"/>
-      <c r="Z40" s="10" t="inlineStr"/>
-      <c r="AA40" s="11" t="inlineStr"/>
-      <c r="AB40" s="12" t="inlineStr"/>
+      <c r="Z40" s="8" t="inlineStr"/>
+      <c r="AA40" s="8" t="inlineStr"/>
+      <c r="AB40" s="10" t="inlineStr"/>
+      <c r="AC40" s="11" t="inlineStr"/>
+      <c r="AD40" s="12" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="1" t="n"/>
@@ -3432,7 +3779,11 @@
           <t>87.90</t>
         </is>
       </c>
-      <c r="R41" s="8" t="inlineStr"/>
+      <c r="R41" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="S41" s="8" t="inlineStr"/>
       <c r="T41" s="8" t="inlineStr"/>
       <c r="U41" s="8" t="inlineStr"/>
@@ -3440,13 +3791,15 @@
       <c r="W41" s="8" t="inlineStr"/>
       <c r="X41" s="8" t="inlineStr"/>
       <c r="Y41" s="8" t="inlineStr"/>
-      <c r="Z41" s="10" t="n">
+      <c r="Z41" s="8" t="inlineStr"/>
+      <c r="AA41" s="8" t="inlineStr"/>
+      <c r="AB41" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="AA41" s="10" t="n">
+      <c r="AC41" s="10" t="n">
         <v>3.250000000000014</v>
       </c>
-      <c r="AB41" s="12" t="n">
+      <c r="AD41" s="12" t="n">
         <v>0.2708333333333345</v>
       </c>
     </row>
@@ -3470,9 +3823,9 @@
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="8" t="inlineStr"/>
       <c r="O42" s="9" t="inlineStr"/>
-      <c r="P42" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="P42" s="8" t="inlineStr">
+        <is>
+          <t>80.40</t>
         </is>
       </c>
       <c r="Q42" s="8" t="inlineStr"/>
@@ -3484,9 +3837,11 @@
       <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="8" t="inlineStr"/>
       <c r="Y42" s="8" t="inlineStr"/>
-      <c r="Z42" s="10" t="inlineStr"/>
-      <c r="AA42" s="11" t="inlineStr"/>
-      <c r="AB42" s="12" t="inlineStr"/>
+      <c r="Z42" s="8" t="inlineStr"/>
+      <c r="AA42" s="8" t="inlineStr"/>
+      <c r="AB42" s="10" t="inlineStr"/>
+      <c r="AC42" s="11" t="inlineStr"/>
+      <c r="AD42" s="12" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
@@ -3508,9 +3863,9 @@
       <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="9" t="inlineStr"/>
-      <c r="P43" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="P43" s="8" t="inlineStr">
+        <is>
+          <t>81.60</t>
         </is>
       </c>
       <c r="Q43" s="8" t="inlineStr"/>
@@ -3522,9 +3877,11 @@
       <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="8" t="inlineStr"/>
       <c r="Y43" s="8" t="inlineStr"/>
-      <c r="Z43" s="10" t="inlineStr"/>
-      <c r="AA43" s="11" t="inlineStr"/>
-      <c r="AB43" s="12" t="inlineStr"/>
+      <c r="Z43" s="8" t="inlineStr"/>
+      <c r="AA43" s="8" t="inlineStr"/>
+      <c r="AB43" s="10" t="inlineStr"/>
+      <c r="AC43" s="11" t="inlineStr"/>
+      <c r="AD43" s="12" t="inlineStr"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3562,11 +3919,13 @@
       <c r="W44" s="4" t="inlineStr"/>
       <c r="X44" s="4" t="inlineStr"/>
       <c r="Y44" s="4" t="inlineStr"/>
-      <c r="Z44" s="5" t="inlineStr"/>
-      <c r="AA44" s="6" t="n">
+      <c r="Z44" s="4" t="inlineStr"/>
+      <c r="AA44" s="4" t="inlineStr"/>
+      <c r="AB44" s="5" t="inlineStr"/>
+      <c r="AC44" s="6" t="n">
         <v>-4.266666666666666</v>
       </c>
-      <c r="AB44" s="7" t="n">
+      <c r="AD44" s="7" t="n">
         <v>-0.1481481481481481</v>
       </c>
     </row>
@@ -3578,7 +3937,7 @@
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr"/>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>14.35</t>
         </is>
@@ -3620,11 +3979,13 @@
       <c r="W45" s="8" t="inlineStr"/>
       <c r="X45" s="8" t="inlineStr"/>
       <c r="Y45" s="8" t="inlineStr"/>
-      <c r="Z45" s="10" t="n">
+      <c r="Z45" s="8" t="inlineStr"/>
+      <c r="AA45" s="8" t="inlineStr"/>
+      <c r="AB45" s="10" t="n">
         <v>11.73333333333333</v>
       </c>
-      <c r="AA45" s="11" t="inlineStr"/>
-      <c r="AB45" s="12" t="inlineStr"/>
+      <c r="AC45" s="11" t="inlineStr"/>
+      <c r="AD45" s="12" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="1" t="n"/>
@@ -3634,7 +3995,7 @@
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr"/>
-      <c r="D46" s="8" t="inlineStr"/>
+      <c r="D46" s="9" t="inlineStr"/>
       <c r="E46" s="8" t="inlineStr">
         <is>
           <t>12.10</t>
@@ -3668,9 +4029,11 @@
       <c r="W46" s="8" t="inlineStr"/>
       <c r="X46" s="8" t="inlineStr"/>
       <c r="Y46" s="8" t="inlineStr"/>
-      <c r="Z46" s="10" t="inlineStr"/>
-      <c r="AA46" s="11" t="inlineStr"/>
-      <c r="AB46" s="12" t="inlineStr"/>
+      <c r="Z46" s="8" t="inlineStr"/>
+      <c r="AA46" s="8" t="inlineStr"/>
+      <c r="AB46" s="10" t="inlineStr"/>
+      <c r="AC46" s="11" t="inlineStr"/>
+      <c r="AD46" s="12" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="1" t="n"/>
@@ -3680,7 +4043,11 @@
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr"/>
-      <c r="D47" s="8" t="inlineStr"/>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>8.90</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>12.70</t>
@@ -3714,13 +4081,15 @@
       <c r="W47" s="8" t="inlineStr"/>
       <c r="X47" s="8" t="inlineStr"/>
       <c r="Y47" s="8" t="inlineStr"/>
-      <c r="Z47" s="10" t="n">
+      <c r="Z47" s="8" t="inlineStr"/>
+      <c r="AA47" s="8" t="inlineStr"/>
+      <c r="AB47" s="10" t="n">
         <v>12.36666666666667</v>
       </c>
-      <c r="AA47" s="10" t="n">
+      <c r="AC47" s="10" t="n">
         <v>0.6333333333333311</v>
       </c>
-      <c r="AB47" s="12" t="n">
+      <c r="AD47" s="12" t="n">
         <v>0.02199074074074066</v>
       </c>
     </row>
@@ -3760,11 +4129,13 @@
       <c r="W48" s="4" t="inlineStr"/>
       <c r="X48" s="4" t="inlineStr"/>
       <c r="Y48" s="4" t="inlineStr"/>
-      <c r="Z48" s="5" t="inlineStr"/>
-      <c r="AA48" s="6" t="n">
+      <c r="Z48" s="4" t="inlineStr"/>
+      <c r="AA48" s="4" t="inlineStr"/>
+      <c r="AB48" s="5" t="inlineStr"/>
+      <c r="AC48" s="6" t="n">
         <v>-199.25</v>
       </c>
-      <c r="AB48" s="7" t="n">
+      <c r="AD48" s="7" t="n">
         <v>-0.03029588857803187</v>
       </c>
     </row>
@@ -3818,11 +4189,13 @@
       <c r="W49" s="8" t="inlineStr"/>
       <c r="X49" s="8" t="inlineStr"/>
       <c r="Y49" s="8" t="inlineStr"/>
-      <c r="Z49" s="10" t="n">
+      <c r="Z49" s="8" t="inlineStr"/>
+      <c r="AA49" s="8" t="inlineStr"/>
+      <c r="AB49" s="10" t="n">
         <v>1688.75</v>
       </c>
-      <c r="AA49" s="11" t="inlineStr"/>
-      <c r="AB49" s="12" t="inlineStr"/>
+      <c r="AC49" s="11" t="inlineStr"/>
+      <c r="AD49" s="12" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="1" t="n"/>
@@ -3862,9 +4235,11 @@
       <c r="W50" s="8" t="inlineStr"/>
       <c r="X50" s="8" t="inlineStr"/>
       <c r="Y50" s="8" t="inlineStr"/>
-      <c r="Z50" s="10" t="inlineStr"/>
-      <c r="AA50" s="11" t="inlineStr"/>
-      <c r="AB50" s="12" t="inlineStr"/>
+      <c r="Z50" s="8" t="inlineStr"/>
+      <c r="AA50" s="8" t="inlineStr"/>
+      <c r="AB50" s="10" t="inlineStr"/>
+      <c r="AC50" s="11" t="inlineStr"/>
+      <c r="AD50" s="12" t="inlineStr"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="1" t="n"/>
@@ -3912,13 +4287,15 @@
       <c r="W51" s="8" t="inlineStr"/>
       <c r="X51" s="8" t="inlineStr"/>
       <c r="Y51" s="8" t="inlineStr"/>
-      <c r="Z51" s="10" t="n">
+      <c r="Z51" s="8" t="inlineStr"/>
+      <c r="AA51" s="8" t="inlineStr"/>
+      <c r="AB51" s="10" t="n">
         <v>1425</v>
       </c>
-      <c r="AA51" s="10" t="n">
+      <c r="AC51" s="10" t="n">
         <v>263.75</v>
       </c>
-      <c r="AB51" s="12" t="n">
+      <c r="AD51" s="12" t="n">
         <v>-0.04010308964846126</v>
       </c>
     </row>
@@ -3960,9 +4337,11 @@
       <c r="W52" s="8" t="inlineStr"/>
       <c r="X52" s="8" t="inlineStr"/>
       <c r="Y52" s="8" t="inlineStr"/>
-      <c r="Z52" s="10" t="inlineStr"/>
-      <c r="AA52" s="11" t="inlineStr"/>
-      <c r="AB52" s="12" t="inlineStr"/>
+      <c r="Z52" s="8" t="inlineStr"/>
+      <c r="AA52" s="8" t="inlineStr"/>
+      <c r="AB52" s="10" t="inlineStr"/>
+      <c r="AC52" s="11" t="inlineStr"/>
+      <c r="AD52" s="12" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="1" t="n"/>
@@ -3973,9 +4352,9 @@
       </c>
       <c r="C53" s="8" t="inlineStr"/>
       <c r="D53" s="8" t="inlineStr"/>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>2025.00</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -4002,9 +4381,11 @@
       <c r="W53" s="8" t="inlineStr"/>
       <c r="X53" s="8" t="inlineStr"/>
       <c r="Y53" s="8" t="inlineStr"/>
-      <c r="Z53" s="10" t="inlineStr"/>
-      <c r="AA53" s="11" t="inlineStr"/>
-      <c r="AB53" s="12" t="inlineStr"/>
+      <c r="Z53" s="8" t="inlineStr"/>
+      <c r="AA53" s="8" t="inlineStr"/>
+      <c r="AB53" s="10" t="inlineStr"/>
+      <c r="AC53" s="11" t="inlineStr"/>
+      <c r="AD53" s="12" t="inlineStr"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -4042,11 +4423,13 @@
       <c r="W54" s="4" t="inlineStr"/>
       <c r="X54" s="4" t="inlineStr"/>
       <c r="Y54" s="4" t="inlineStr"/>
-      <c r="Z54" s="5" t="inlineStr"/>
-      <c r="AA54" s="6" t="n">
+      <c r="Z54" s="4" t="inlineStr"/>
+      <c r="AA54" s="4" t="inlineStr"/>
+      <c r="AB54" s="5" t="inlineStr"/>
+      <c r="AC54" s="6" t="n">
         <v>-9204.333333333336</v>
       </c>
-      <c r="AB54" s="7" t="n">
+      <c r="AD54" s="7" t="n">
         <v>-0.3674545921510859</v>
       </c>
     </row>
@@ -4100,11 +4483,13 @@
       <c r="W55" s="8" t="inlineStr"/>
       <c r="X55" s="8" t="inlineStr"/>
       <c r="Y55" s="8" t="inlineStr"/>
-      <c r="Z55" s="10" t="n">
+      <c r="Z55" s="8" t="inlineStr"/>
+      <c r="AA55" s="8" t="inlineStr"/>
+      <c r="AB55" s="10" t="n">
         <v>57571.66666666666</v>
       </c>
-      <c r="AA55" s="11" t="inlineStr"/>
-      <c r="AB55" s="12" t="inlineStr"/>
+      <c r="AC55" s="11" t="inlineStr"/>
+      <c r="AD55" s="12" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="1" t="n"/>
@@ -4140,9 +4525,11 @@
       <c r="W56" s="8" t="inlineStr"/>
       <c r="X56" s="8" t="inlineStr"/>
       <c r="Y56" s="8" t="inlineStr"/>
-      <c r="Z56" s="10" t="inlineStr"/>
-      <c r="AA56" s="11" t="inlineStr"/>
-      <c r="AB56" s="12" t="inlineStr"/>
+      <c r="Z56" s="8" t="inlineStr"/>
+      <c r="AA56" s="8" t="inlineStr"/>
+      <c r="AB56" s="10" t="inlineStr"/>
+      <c r="AC56" s="11" t="inlineStr"/>
+      <c r="AD56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="1" t="n"/>
@@ -4175,7 +4562,11 @@
       <c r="L57" s="8" t="inlineStr"/>
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
-      <c r="O57" s="8" t="inlineStr"/>
+      <c r="O57" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="P57" s="8" t="inlineStr"/>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
@@ -4186,99 +4577,81 @@
       <c r="W57" s="8" t="inlineStr"/>
       <c r="X57" s="8" t="inlineStr"/>
       <c r="Y57" s="8" t="inlineStr"/>
-      <c r="Z57" s="10" t="n">
+      <c r="Z57" s="8" t="inlineStr"/>
+      <c r="AA57" s="8" t="inlineStr"/>
+      <c r="AB57" s="10" t="n">
         <v>57908.33333333334</v>
       </c>
-      <c r="AA57" s="10" t="n">
+      <c r="AC57" s="10" t="n">
         <v>336.6666666666715</v>
       </c>
-      <c r="AB57" s="12" t="n">
+      <c r="AD57" s="12" t="n">
         <v>0.01344037728869018</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>DemonAttack
-Random: 152.1
-Human: 1971.0</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 165</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr"/>
-      <c r="O58" s="4" t="inlineStr"/>
-      <c r="P58" s="4" t="inlineStr"/>
-      <c r="Q58" s="4" t="inlineStr"/>
-      <c r="R58" s="4" t="inlineStr"/>
-      <c r="S58" s="4" t="inlineStr"/>
-      <c r="T58" s="4" t="inlineStr"/>
-      <c r="U58" s="4" t="inlineStr"/>
-      <c r="V58" s="4" t="inlineStr"/>
-      <c r="W58" s="4" t="inlineStr"/>
-      <c r="X58" s="4" t="inlineStr"/>
-      <c r="Y58" s="4" t="inlineStr"/>
-      <c r="Z58" s="5" t="inlineStr"/>
-      <c r="AA58" s="6" t="n">
-        <v>30.58333333333334</v>
-      </c>
-      <c r="AB58" s="7" t="n">
-        <v>0.01681419172760094</v>
-      </c>
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr"/>
+      <c r="D58" s="8" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr"/>
+      <c r="G58" s="8" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr"/>
+      <c r="J58" s="8" t="inlineStr"/>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>55845.00</t>
+        </is>
+      </c>
+      <c r="L58" s="8" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
+      <c r="N58" s="8" t="inlineStr"/>
+      <c r="O58" s="8" t="inlineStr"/>
+      <c r="P58" s="8" t="inlineStr"/>
+      <c r="Q58" s="8" t="inlineStr"/>
+      <c r="R58" s="8" t="inlineStr"/>
+      <c r="S58" s="8" t="inlineStr"/>
+      <c r="T58" s="8" t="inlineStr"/>
+      <c r="U58" s="8" t="inlineStr"/>
+      <c r="V58" s="8" t="inlineStr"/>
+      <c r="W58" s="8" t="inlineStr"/>
+      <c r="X58" s="8" t="inlineStr"/>
+      <c r="Y58" s="8" t="inlineStr"/>
+      <c r="Z58" s="8" t="inlineStr"/>
+      <c r="AA58" s="8" t="inlineStr"/>
+      <c r="AB58" s="10" t="inlineStr"/>
+      <c r="AC58" s="11" t="inlineStr"/>
+      <c r="AD58" s="12" t="inlineStr"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr"/>
       <c r="D59" s="8" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>214.25</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>139.75</t>
-        </is>
-      </c>
+      <c r="E59" s="8" t="inlineStr"/>
+      <c r="F59" s="8" t="inlineStr"/>
       <c r="G59" s="8" t="inlineStr"/>
       <c r="H59" s="8" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>200.75</t>
-        </is>
-      </c>
+      <c r="I59" s="8" t="inlineStr"/>
       <c r="J59" s="8" t="inlineStr"/>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>171.75</t>
+          <t>57965.00</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr"/>
       <c r="M59" s="8" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr">
-        <is>
-          <t>188.00</t>
-        </is>
-      </c>
+      <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="8" t="inlineStr"/>
       <c r="P59" s="8" t="inlineStr"/>
       <c r="Q59" s="8" t="inlineStr"/>
@@ -4290,81 +4663,97 @@
       <c r="W59" s="8" t="inlineStr"/>
       <c r="X59" s="8" t="inlineStr"/>
       <c r="Y59" s="8" t="inlineStr"/>
-      <c r="Z59" s="10" t="n">
-        <v>195.5833333333333</v>
-      </c>
-      <c r="AA59" s="11" t="inlineStr"/>
-      <c r="AB59" s="12" t="inlineStr"/>
+      <c r="Z59" s="8" t="inlineStr"/>
+      <c r="AA59" s="8" t="inlineStr"/>
+      <c r="AB59" s="10" t="inlineStr"/>
+      <c r="AC59" s="11" t="inlineStr"/>
+      <c r="AD59" s="12" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="1" t="n"/>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr"/>
-      <c r="D60" s="8" t="inlineStr"/>
-      <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="8" t="inlineStr"/>
-      <c r="G60" s="8" t="inlineStr"/>
-      <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>138.00</t>
-        </is>
-      </c>
-      <c r="J60" s="8" t="inlineStr"/>
-      <c r="K60" s="8" t="inlineStr"/>
-      <c r="L60" s="8" t="inlineStr"/>
-      <c r="M60" s="8" t="inlineStr"/>
-      <c r="N60" s="8" t="inlineStr"/>
-      <c r="O60" s="8" t="inlineStr"/>
-      <c r="P60" s="8" t="inlineStr"/>
-      <c r="Q60" s="8" t="inlineStr"/>
-      <c r="R60" s="8" t="inlineStr"/>
-      <c r="S60" s="8" t="inlineStr"/>
-      <c r="T60" s="8" t="inlineStr"/>
-      <c r="U60" s="8" t="inlineStr"/>
-      <c r="V60" s="8" t="inlineStr"/>
-      <c r="W60" s="8" t="inlineStr"/>
-      <c r="X60" s="8" t="inlineStr"/>
-      <c r="Y60" s="8" t="inlineStr"/>
-      <c r="Z60" s="10" t="inlineStr"/>
-      <c r="AA60" s="11" t="inlineStr"/>
-      <c r="AB60" s="12" t="inlineStr"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>DemonAttack
+Random: 152.1
+Human: 1971.0</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 165</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr"/>
+      <c r="M60" s="4" t="inlineStr"/>
+      <c r="N60" s="4" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr"/>
+      <c r="P60" s="4" t="inlineStr"/>
+      <c r="Q60" s="4" t="inlineStr"/>
+      <c r="R60" s="4" t="inlineStr"/>
+      <c r="S60" s="4" t="inlineStr"/>
+      <c r="T60" s="4" t="inlineStr"/>
+      <c r="U60" s="4" t="inlineStr"/>
+      <c r="V60" s="4" t="inlineStr"/>
+      <c r="W60" s="4" t="inlineStr"/>
+      <c r="X60" s="4" t="inlineStr"/>
+      <c r="Y60" s="4" t="inlineStr"/>
+      <c r="Z60" s="4" t="inlineStr"/>
+      <c r="AA60" s="4" t="inlineStr"/>
+      <c r="AB60" s="5" t="inlineStr"/>
+      <c r="AC60" s="6" t="n">
+        <v>16.625</v>
+      </c>
+      <c r="AD60" s="7" t="n">
+        <v>0.009140139644840287</v>
+      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr"/>
       <c r="D61" s="8" t="inlineStr"/>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>150.75</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr"/>
+          <t>214.25</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>139.75</t>
+        </is>
+      </c>
       <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="8" t="inlineStr"/>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>128.25</t>
+          <t>200.75</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr"/>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>192.25</t>
+          <t>171.75</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr"/>
       <c r="M61" s="8" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="8" t="inlineStr">
+        <is>
+          <t>188.00</t>
+        </is>
+      </c>
       <c r="O61" s="8" t="inlineStr"/>
       <c r="P61" s="8" t="inlineStr"/>
       <c r="Q61" s="8" t="inlineStr"/>
@@ -4376,32 +4765,34 @@
       <c r="W61" s="8" t="inlineStr"/>
       <c r="X61" s="8" t="inlineStr"/>
       <c r="Y61" s="8" t="inlineStr"/>
-      <c r="Z61" s="10" t="n">
-        <v>157.0833333333333</v>
-      </c>
-      <c r="AA61" s="10" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="AB61" s="12" t="n">
-        <v>-0.02116663917752488</v>
-      </c>
+      <c r="Z61" s="8" t="inlineStr"/>
+      <c r="AA61" s="8" t="inlineStr"/>
+      <c r="AB61" s="10" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AC61" s="11" t="inlineStr"/>
+      <c r="AD61" s="12" t="inlineStr"/>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr"/>
       <c r="D62" s="8" t="inlineStr"/>
       <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="8" t="inlineStr"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>130.00</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="inlineStr"/>
       <c r="H62" s="8" t="inlineStr"/>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>137.50</t>
+          <t>138.00</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr"/>
@@ -4420,30 +4811,44 @@
       <c r="W62" s="8" t="inlineStr"/>
       <c r="X62" s="8" t="inlineStr"/>
       <c r="Y62" s="8" t="inlineStr"/>
-      <c r="Z62" s="10" t="inlineStr"/>
-      <c r="AA62" s="11" t="inlineStr"/>
-      <c r="AB62" s="12" t="inlineStr"/>
+      <c r="Z62" s="8" t="inlineStr"/>
+      <c r="AA62" s="8" t="inlineStr"/>
+      <c r="AB62" s="10" t="inlineStr"/>
+      <c r="AC62" s="11" t="inlineStr"/>
+      <c r="AD62" s="12" t="inlineStr"/>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr"/>
       <c r="D63" s="8" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr"/>
-      <c r="F63" s="8" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>150.75</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>149.25</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="inlineStr"/>
       <c r="H63" s="8" t="inlineStr"/>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>148.50</t>
+          <t>128.25</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr"/>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>192.25</t>
+        </is>
+      </c>
       <c r="L63" s="8" t="inlineStr"/>
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
@@ -4458,92 +4863,92 @@
       <c r="W63" s="8" t="inlineStr"/>
       <c r="X63" s="8" t="inlineStr"/>
       <c r="Y63" s="8" t="inlineStr"/>
-      <c r="Z63" s="10" t="inlineStr"/>
-      <c r="AA63" s="11" t="inlineStr"/>
-      <c r="AB63" s="12" t="inlineStr"/>
+      <c r="Z63" s="8" t="inlineStr"/>
+      <c r="AA63" s="8" t="inlineStr"/>
+      <c r="AB63" s="10" t="n">
+        <v>155.125</v>
+      </c>
+      <c r="AC63" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD63" s="12" t="n">
+        <v>-0.01456924514816647</v>
+      </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Freeway
-Random: 0.0
-Human: 29.6</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 34</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr"/>
-      <c r="D64" s="4" t="inlineStr"/>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="4" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr"/>
-      <c r="J64" s="4" t="inlineStr"/>
-      <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr"/>
-      <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr"/>
-      <c r="O64" s="4" t="inlineStr"/>
-      <c r="P64" s="4" t="inlineStr"/>
-      <c r="Q64" s="4" t="inlineStr"/>
-      <c r="R64" s="4" t="inlineStr"/>
-      <c r="S64" s="4" t="inlineStr"/>
-      <c r="T64" s="4" t="inlineStr"/>
-      <c r="U64" s="4" t="inlineStr"/>
-      <c r="V64" s="4" t="inlineStr"/>
-      <c r="W64" s="4" t="inlineStr"/>
-      <c r="X64" s="4" t="inlineStr"/>
-      <c r="Y64" s="4" t="inlineStr"/>
-      <c r="Z64" s="5" t="inlineStr"/>
-      <c r="AA64" s="6" t="n">
-        <v>-0.5500000000000043</v>
-      </c>
-      <c r="AB64" s="7" t="n">
-        <v>-0.01858108108108122</v>
-      </c>
+      <c r="A64" s="1" t="n"/>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr"/>
+      <c r="D64" s="8" t="inlineStr"/>
+      <c r="E64" s="8" t="inlineStr"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>148.75</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>137.50</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr"/>
+      <c r="K64" s="8" t="inlineStr"/>
+      <c r="L64" s="8" t="inlineStr"/>
+      <c r="M64" s="8" t="inlineStr"/>
+      <c r="N64" s="8" t="inlineStr"/>
+      <c r="O64" s="8" t="inlineStr"/>
+      <c r="P64" s="8" t="inlineStr"/>
+      <c r="Q64" s="8" t="inlineStr"/>
+      <c r="R64" s="8" t="inlineStr"/>
+      <c r="S64" s="8" t="inlineStr"/>
+      <c r="T64" s="8" t="inlineStr"/>
+      <c r="U64" s="8" t="inlineStr"/>
+      <c r="V64" s="8" t="inlineStr"/>
+      <c r="W64" s="8" t="inlineStr"/>
+      <c r="X64" s="8" t="inlineStr"/>
+      <c r="Y64" s="8" t="inlineStr"/>
+      <c r="Z64" s="8" t="inlineStr"/>
+      <c r="AA64" s="8" t="inlineStr"/>
+      <c r="AB64" s="10" t="inlineStr"/>
+      <c r="AC64" s="11" t="inlineStr"/>
+      <c r="AD64" s="12" t="inlineStr"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr"/>
       <c r="D65" s="8" t="inlineStr"/>
       <c r="E65" s="8" t="inlineStr"/>
-      <c r="F65" s="8" t="inlineStr"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>165.25</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>148.50</t>
+        </is>
+      </c>
       <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="K65" s="8" t="inlineStr"/>
       <c r="L65" s="8" t="inlineStr"/>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
-      <c r="O65" s="8" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
-      </c>
-      <c r="P65" s="8" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="Q65" s="8" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
+      <c r="O65" s="8" t="inlineStr"/>
+      <c r="P65" s="8" t="inlineStr"/>
+      <c r="Q65" s="8" t="inlineStr"/>
       <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr"/>
       <c r="T65" s="8" t="inlineStr"/>
@@ -4552,55 +4957,63 @@
       <c r="W65" s="8" t="inlineStr"/>
       <c r="X65" s="8" t="inlineStr"/>
       <c r="Y65" s="8" t="inlineStr"/>
-      <c r="Z65" s="10" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="AA65" s="11" t="inlineStr"/>
-      <c r="AB65" s="12" t="inlineStr"/>
+      <c r="Z65" s="8" t="inlineStr"/>
+      <c r="AA65" s="8" t="inlineStr"/>
+      <c r="AB65" s="10" t="inlineStr"/>
+      <c r="AC65" s="11" t="inlineStr"/>
+      <c r="AD65" s="12" t="inlineStr"/>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="1" t="n"/>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr"/>
-      <c r="D66" s="8" t="inlineStr"/>
-      <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr"/>
-      <c r="G66" s="8" t="inlineStr"/>
-      <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="8" t="inlineStr"/>
-      <c r="J66" s="8" t="inlineStr"/>
-      <c r="K66" s="8" t="inlineStr"/>
-      <c r="L66" s="8" t="inlineStr"/>
-      <c r="M66" s="8" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
-      <c r="O66" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="P66" s="8" t="inlineStr"/>
-      <c r="Q66" s="8" t="inlineStr"/>
-      <c r="R66" s="8" t="inlineStr"/>
-      <c r="S66" s="8" t="inlineStr"/>
-      <c r="T66" s="8" t="inlineStr"/>
-      <c r="U66" s="8" t="inlineStr"/>
-      <c r="V66" s="8" t="inlineStr"/>
-      <c r="W66" s="8" t="inlineStr"/>
-      <c r="X66" s="8" t="inlineStr"/>
-      <c r="Y66" s="8" t="inlineStr"/>
-      <c r="Z66" s="10" t="inlineStr"/>
-      <c r="AA66" s="11" t="inlineStr"/>
-      <c r="AB66" s="12" t="inlineStr"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Freeway
+Random: 0.0
+Human: 29.6</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 34</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr"/>
+      <c r="Q66" s="4" t="inlineStr"/>
+      <c r="R66" s="4" t="inlineStr"/>
+      <c r="S66" s="4" t="inlineStr"/>
+      <c r="T66" s="4" t="inlineStr"/>
+      <c r="U66" s="4" t="inlineStr"/>
+      <c r="V66" s="4" t="inlineStr"/>
+      <c r="W66" s="4" t="inlineStr"/>
+      <c r="X66" s="4" t="inlineStr"/>
+      <c r="Y66" s="4" t="inlineStr"/>
+      <c r="Z66" s="4" t="inlineStr"/>
+      <c r="AA66" s="4" t="inlineStr"/>
+      <c r="AB66" s="5" t="inlineStr"/>
+      <c r="AC66" s="6" t="n">
+        <v>-0.5500000000000043</v>
+      </c>
+      <c r="AD66" s="7" t="n">
+        <v>-0.01858108108108122</v>
+      </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr"/>
@@ -4611,13 +5024,17 @@
       <c r="H67" s="8" t="inlineStr"/>
       <c r="I67" s="8" t="inlineStr"/>
       <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="L67" s="8" t="inlineStr"/>
       <c r="M67" s="8" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="8" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="P67" s="8" t="inlineStr">
@@ -4630,7 +5047,7 @@
           <t>33.75</t>
         </is>
       </c>
-      <c r="R67" s="8" t="inlineStr"/>
+      <c r="R67" s="9" t="inlineStr"/>
       <c r="S67" s="8" t="inlineStr"/>
       <c r="T67" s="8" t="inlineStr"/>
       <c r="U67" s="8" t="inlineStr"/>
@@ -4638,21 +5055,19 @@
       <c r="W67" s="8" t="inlineStr"/>
       <c r="X67" s="8" t="inlineStr"/>
       <c r="Y67" s="8" t="inlineStr"/>
-      <c r="Z67" s="10" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="AA67" s="10" t="n">
-        <v>0.09999999999999432</v>
-      </c>
-      <c r="AB67" s="12" t="n">
-        <v>-0.003378378378378186</v>
-      </c>
+      <c r="Z67" s="8" t="inlineStr"/>
+      <c r="AA67" s="8" t="inlineStr"/>
+      <c r="AB67" s="10" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AC67" s="11" t="inlineStr"/>
+      <c r="AD67" s="12" t="inlineStr"/>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr"/>
@@ -4667,14 +5082,14 @@
       <c r="L68" s="8" t="inlineStr"/>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
-      <c r="O68" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="O68" s="8" t="inlineStr">
+        <is>
+          <t>0.00</t>
         </is>
       </c>
       <c r="P68" s="8" t="inlineStr"/>
       <c r="Q68" s="8" t="inlineStr"/>
-      <c r="R68" s="8" t="inlineStr"/>
+      <c r="R68" s="9" t="inlineStr"/>
       <c r="S68" s="8" t="inlineStr"/>
       <c r="T68" s="8" t="inlineStr"/>
       <c r="U68" s="8" t="inlineStr"/>
@@ -4682,15 +5097,17 @@
       <c r="W68" s="8" t="inlineStr"/>
       <c r="X68" s="8" t="inlineStr"/>
       <c r="Y68" s="8" t="inlineStr"/>
-      <c r="Z68" s="10" t="inlineStr"/>
-      <c r="AA68" s="11" t="inlineStr"/>
-      <c r="AB68" s="12" t="inlineStr"/>
+      <c r="Z68" s="8" t="inlineStr"/>
+      <c r="AA68" s="8" t="inlineStr"/>
+      <c r="AB68" s="10" t="inlineStr"/>
+      <c r="AC68" s="11" t="inlineStr"/>
+      <c r="AD68" s="12" t="inlineStr"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr"/>
@@ -4705,14 +5122,26 @@
       <c r="L69" s="8" t="inlineStr"/>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
-      <c r="O69" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="P69" s="8" t="inlineStr"/>
-      <c r="Q69" s="8" t="inlineStr"/>
-      <c r="R69" s="8" t="inlineStr"/>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>33.55</t>
+        </is>
+      </c>
+      <c r="P69" s="8" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="Q69" s="8" t="inlineStr">
+        <is>
+          <t>33.75</t>
+        </is>
+      </c>
+      <c r="R69" s="13" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="S69" s="8" t="inlineStr"/>
       <c r="T69" s="8" t="inlineStr"/>
       <c r="U69" s="8" t="inlineStr"/>
@@ -4720,80 +5149,72 @@
       <c r="W69" s="8" t="inlineStr"/>
       <c r="X69" s="8" t="inlineStr"/>
       <c r="Y69" s="8" t="inlineStr"/>
-      <c r="Z69" s="10" t="inlineStr"/>
-      <c r="AA69" s="11" t="inlineStr"/>
-      <c r="AB69" s="12" t="inlineStr"/>
+      <c r="Z69" s="8" t="inlineStr"/>
+      <c r="AA69" s="8" t="inlineStr"/>
+      <c r="AB69" s="10" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="AC69" s="10" t="n">
+        <v>0.09999999999999432</v>
+      </c>
+      <c r="AD69" s="12" t="n">
+        <v>-0.003378378378378186</v>
+      </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Frostbite
-Random: 65.2
-Human: 4334.7</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 1316</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr"/>
-      <c r="D70" s="4" t="inlineStr"/>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr"/>
-      <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="4" t="inlineStr"/>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr"/>
-      <c r="O70" s="4" t="inlineStr"/>
-      <c r="P70" s="4" t="inlineStr"/>
-      <c r="Q70" s="4" t="inlineStr"/>
-      <c r="R70" s="4" t="inlineStr"/>
-      <c r="S70" s="4" t="inlineStr"/>
-      <c r="T70" s="4" t="inlineStr"/>
-      <c r="U70" s="4" t="inlineStr"/>
-      <c r="V70" s="4" t="inlineStr"/>
-      <c r="W70" s="4" t="inlineStr"/>
-      <c r="X70" s="4" t="inlineStr"/>
-      <c r="Y70" s="4" t="inlineStr"/>
-      <c r="Z70" s="5" t="inlineStr"/>
-      <c r="AA70" s="6" t="n">
-        <v>426.375</v>
-      </c>
-      <c r="AB70" s="7" t="n">
-        <v>0.09986532380840848</v>
-      </c>
+      <c r="A70" s="1" t="n"/>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr"/>
+      <c r="D70" s="8" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr"/>
+      <c r="F70" s="8" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr"/>
+      <c r="K70" s="8" t="inlineStr"/>
+      <c r="L70" s="8" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
+      <c r="N70" s="8" t="inlineStr"/>
+      <c r="O70" s="8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="P70" s="8" t="inlineStr"/>
+      <c r="Q70" s="8" t="inlineStr"/>
+      <c r="R70" s="9" t="inlineStr"/>
+      <c r="S70" s="8" t="inlineStr"/>
+      <c r="T70" s="8" t="inlineStr"/>
+      <c r="U70" s="8" t="inlineStr"/>
+      <c r="V70" s="8" t="inlineStr"/>
+      <c r="W70" s="8" t="inlineStr"/>
+      <c r="X70" s="8" t="inlineStr"/>
+      <c r="Y70" s="8" t="inlineStr"/>
+      <c r="Z70" s="8" t="inlineStr"/>
+      <c r="AA70" s="8" t="inlineStr"/>
+      <c r="AB70" s="10" t="inlineStr"/>
+      <c r="AC70" s="11" t="inlineStr"/>
+      <c r="AD70" s="12" t="inlineStr"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr"/>
       <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>2068.00</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>2270.50</t>
-        </is>
-      </c>
+      <c r="E71" s="8" t="inlineStr"/>
+      <c r="F71" s="8" t="inlineStr"/>
       <c r="G71" s="8" t="inlineStr"/>
       <c r="H71" s="8" t="inlineStr"/>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>1904.00</t>
-        </is>
-      </c>
+      <c r="I71" s="8" t="inlineStr"/>
       <c r="J71" s="8" t="inlineStr"/>
       <c r="K71" s="8" t="inlineStr"/>
       <c r="L71" s="8" t="inlineStr"/>
@@ -4801,16 +5222,12 @@
       <c r="N71" s="8" t="inlineStr"/>
       <c r="O71" s="8" t="inlineStr">
         <is>
-          <t>2544.50, 2833.50, 2600.50, 2639.00</t>
-        </is>
-      </c>
-      <c r="P71" s="8" t="inlineStr">
-        <is>
-          <t>250.50, 252.50, 255.00, 255.00</t>
-        </is>
-      </c>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="P71" s="8" t="inlineStr"/>
       <c r="Q71" s="8" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
+      <c r="R71" s="9" t="inlineStr"/>
       <c r="S71" s="8" t="inlineStr"/>
       <c r="T71" s="8" t="inlineStr"/>
       <c r="U71" s="8" t="inlineStr"/>
@@ -4818,98 +5235,82 @@
       <c r="W71" s="8" t="inlineStr"/>
       <c r="X71" s="8" t="inlineStr"/>
       <c r="Y71" s="8" t="inlineStr"/>
-      <c r="Z71" s="10" t="n">
-        <v>1742.375</v>
-      </c>
-      <c r="AA71" s="11" t="inlineStr"/>
-      <c r="AB71" s="12" t="inlineStr"/>
+      <c r="Z71" s="8" t="inlineStr"/>
+      <c r="AA71" s="8" t="inlineStr"/>
+      <c r="AB71" s="10" t="inlineStr"/>
+      <c r="AC71" s="11" t="inlineStr"/>
+      <c r="AD71" s="12" t="inlineStr"/>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="1" t="n"/>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr"/>
-      <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>2301.00</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>2609.00</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr"/>
-      <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>3242.50</t>
-        </is>
-      </c>
-      <c r="J72" s="8" t="inlineStr"/>
-      <c r="K72" s="8" t="inlineStr"/>
-      <c r="L72" s="8" t="inlineStr"/>
-      <c r="M72" s="8" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
-      <c r="O72" s="8" t="inlineStr">
-        <is>
-          <t>2119.50</t>
-        </is>
-      </c>
-      <c r="P72" s="8" t="inlineStr">
-        <is>
-          <t>261.50</t>
-        </is>
-      </c>
-      <c r="Q72" s="8" t="inlineStr"/>
-      <c r="R72" s="8" t="inlineStr"/>
-      <c r="S72" s="8" t="inlineStr"/>
-      <c r="T72" s="8" t="inlineStr"/>
-      <c r="U72" s="8" t="inlineStr"/>
-      <c r="V72" s="8" t="inlineStr"/>
-      <c r="W72" s="8" t="inlineStr"/>
-      <c r="X72" s="8" t="inlineStr"/>
-      <c r="Y72" s="8" t="inlineStr"/>
-      <c r="Z72" s="10" t="inlineStr"/>
-      <c r="AA72" s="11" t="inlineStr"/>
-      <c r="AB72" s="12" t="inlineStr"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Frostbite
+Random: 65.2
+Human: 4334.7</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 1316</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr"/>
+      <c r="P72" s="4" t="inlineStr"/>
+      <c r="Q72" s="4" t="inlineStr"/>
+      <c r="R72" s="4" t="inlineStr"/>
+      <c r="S72" s="4" t="inlineStr"/>
+      <c r="T72" s="4" t="inlineStr"/>
+      <c r="U72" s="4" t="inlineStr"/>
+      <c r="V72" s="4" t="inlineStr"/>
+      <c r="W72" s="4" t="inlineStr"/>
+      <c r="X72" s="4" t="inlineStr"/>
+      <c r="Y72" s="4" t="inlineStr"/>
+      <c r="Z72" s="4" t="inlineStr"/>
+      <c r="AA72" s="4" t="inlineStr"/>
+      <c r="AB72" s="5" t="inlineStr"/>
+      <c r="AC72" s="6" t="n">
+        <v>426.375</v>
+      </c>
+      <c r="AD72" s="7" t="n">
+        <v>0.09986532380840848</v>
+      </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr"/>
       <c r="D73" s="8" t="inlineStr"/>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>2113.50, 2350.50</t>
+          <t>2068.00</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>2443.00</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>283.50</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>252.00</t>
-        </is>
-      </c>
+          <t>2270.50</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr"/>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>2779.00</t>
+          <t>1904.00</t>
         </is>
       </c>
       <c r="J73" s="8" t="inlineStr"/>
@@ -4919,12 +5320,12 @@
       <c r="N73" s="8" t="inlineStr"/>
       <c r="O73" s="8" t="inlineStr">
         <is>
-          <t>2474.00</t>
+          <t>2544.50, 2833.50, 2600.50, 2639.00</t>
         </is>
       </c>
       <c r="P73" s="8" t="inlineStr">
         <is>
-          <t>251.00</t>
+          <t>250.50, 252.50, 255.00, 255.00</t>
         </is>
       </c>
       <c r="Q73" s="8" t="inlineStr"/>
@@ -4936,30 +5337,40 @@
       <c r="W73" s="8" t="inlineStr"/>
       <c r="X73" s="8" t="inlineStr"/>
       <c r="Y73" s="8" t="inlineStr"/>
-      <c r="Z73" s="10" t="n">
-        <v>1986.75</v>
-      </c>
-      <c r="AA73" s="10" t="n">
-        <v>244.375</v>
-      </c>
-      <c r="AB73" s="12" t="n">
-        <v>0.05723738142639653</v>
-      </c>
+      <c r="Z73" s="8" t="inlineStr"/>
+      <c r="AA73" s="8" t="inlineStr"/>
+      <c r="AB73" s="10" t="n">
+        <v>1742.375</v>
+      </c>
+      <c r="AC73" s="11" t="inlineStr"/>
+      <c r="AD73" s="12" t="inlineStr"/>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr"/>
       <c r="D74" s="8" t="inlineStr"/>
-      <c r="E74" s="9" t="inlineStr"/>
-      <c r="F74" s="8" t="inlineStr"/>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>2301.00</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>2609.00</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="inlineStr"/>
       <c r="H74" s="8" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>3242.50</t>
+        </is>
+      </c>
       <c r="J74" s="8" t="inlineStr"/>
       <c r="K74" s="8" t="inlineStr"/>
       <c r="L74" s="8" t="inlineStr"/>
@@ -4967,12 +5378,12 @@
       <c r="N74" s="8" t="inlineStr"/>
       <c r="O74" s="8" t="inlineStr">
         <is>
-          <t>271.00</t>
+          <t>2119.50</t>
         </is>
       </c>
       <c r="P74" s="8" t="inlineStr">
         <is>
-          <t>238.50</t>
+          <t>261.50</t>
         </is>
       </c>
       <c r="Q74" s="8" t="inlineStr"/>
@@ -4984,33 +5395,59 @@
       <c r="W74" s="8" t="inlineStr"/>
       <c r="X74" s="8" t="inlineStr"/>
       <c r="Y74" s="8" t="inlineStr"/>
-      <c r="Z74" s="10" t="inlineStr"/>
-      <c r="AA74" s="11" t="inlineStr"/>
-      <c r="AB74" s="12" t="inlineStr"/>
+      <c r="Z74" s="8" t="inlineStr"/>
+      <c r="AA74" s="8" t="inlineStr"/>
+      <c r="AB74" s="10" t="inlineStr"/>
+      <c r="AC74" s="11" t="inlineStr"/>
+      <c r="AD74" s="12" t="inlineStr"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr"/>
       <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="9" t="inlineStr"/>
-      <c r="F75" s="8" t="inlineStr"/>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>2113.50, 2350.50</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>2443.00</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>283.50</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>252.00</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>2779.00</t>
+        </is>
+      </c>
       <c r="J75" s="8" t="inlineStr"/>
       <c r="K75" s="8" t="inlineStr"/>
       <c r="L75" s="8" t="inlineStr"/>
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr"/>
-      <c r="O75" s="8" t="inlineStr"/>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>2474.00</t>
+        </is>
+      </c>
       <c r="P75" s="8" t="inlineStr">
         <is>
-          <t>226.50</t>
+          <t>251.00</t>
         </is>
       </c>
       <c r="Q75" s="8" t="inlineStr"/>
@@ -5022,188 +5459,180 @@
       <c r="W75" s="8" t="inlineStr"/>
       <c r="X75" s="8" t="inlineStr"/>
       <c r="Y75" s="8" t="inlineStr"/>
-      <c r="Z75" s="10" t="inlineStr"/>
-      <c r="AA75" s="11" t="inlineStr"/>
-      <c r="AB75" s="12" t="inlineStr"/>
+      <c r="Z75" s="8" t="inlineStr"/>
+      <c r="AA75" s="8" t="inlineStr"/>
+      <c r="AB75" s="10" t="n">
+        <v>1986.75</v>
+      </c>
+      <c r="AC75" s="10" t="n">
+        <v>244.375</v>
+      </c>
+      <c r="AD75" s="12" t="n">
+        <v>0.05723738142639653</v>
+      </c>
     </row>
     <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Gopher
-Random: 257.6
-Human: 2412.5</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 8240</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr"/>
-      <c r="D76" s="4" t="inlineStr"/>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr"/>
-      <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="4" t="inlineStr"/>
-      <c r="J76" s="4" t="inlineStr"/>
-      <c r="K76" s="4" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr"/>
-      <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr"/>
-      <c r="O76" s="4" t="inlineStr"/>
-      <c r="P76" s="4" t="inlineStr"/>
-      <c r="Q76" s="4" t="inlineStr"/>
-      <c r="R76" s="4" t="inlineStr"/>
-      <c r="S76" s="4" t="inlineStr"/>
-      <c r="T76" s="4" t="inlineStr"/>
-      <c r="U76" s="4" t="inlineStr"/>
-      <c r="V76" s="4" t="inlineStr"/>
-      <c r="W76" s="4" t="inlineStr"/>
-      <c r="X76" s="4" t="inlineStr"/>
-      <c r="Y76" s="4" t="inlineStr"/>
-      <c r="Z76" s="5" t="inlineStr"/>
-      <c r="AA76" s="6" t="n">
-        <v>-4547</v>
-      </c>
-      <c r="AB76" s="7" t="n">
-        <v>-2.110074713443779</v>
-      </c>
+      <c r="A76" s="1" t="n"/>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr"/>
+      <c r="D76" s="8" t="inlineStr"/>
+      <c r="E76" s="9" t="inlineStr"/>
+      <c r="F76" s="8" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="8" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr"/>
+      <c r="L76" s="8" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr"/>
+      <c r="N76" s="8" t="inlineStr"/>
+      <c r="O76" s="8" t="inlineStr">
+        <is>
+          <t>271.00</t>
+        </is>
+      </c>
+      <c r="P76" s="8" t="inlineStr">
+        <is>
+          <t>238.50</t>
+        </is>
+      </c>
+      <c r="Q76" s="8" t="inlineStr"/>
+      <c r="R76" s="8" t="inlineStr"/>
+      <c r="S76" s="8" t="inlineStr"/>
+      <c r="T76" s="8" t="inlineStr"/>
+      <c r="U76" s="8" t="inlineStr"/>
+      <c r="V76" s="8" t="inlineStr"/>
+      <c r="W76" s="8" t="inlineStr"/>
+      <c r="X76" s="8" t="inlineStr"/>
+      <c r="Y76" s="8" t="inlineStr"/>
+      <c r="Z76" s="8" t="inlineStr"/>
+      <c r="AA76" s="8" t="inlineStr"/>
+      <c r="AB76" s="10" t="inlineStr"/>
+      <c r="AC76" s="11" t="inlineStr"/>
+      <c r="AD76" s="12" t="inlineStr"/>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>5968.00</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>3752.00</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>3275.00</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>3914.00</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr"/>
+      <c r="D77" s="8" t="inlineStr"/>
+      <c r="E77" s="9" t="inlineStr"/>
+      <c r="F77" s="8" t="inlineStr"/>
       <c r="G77" s="8" t="inlineStr"/>
       <c r="H77" s="8" t="inlineStr"/>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>4219.00</t>
-        </is>
-      </c>
+      <c r="I77" s="8" t="inlineStr"/>
       <c r="J77" s="8" t="inlineStr"/>
       <c r="K77" s="8" t="inlineStr"/>
       <c r="L77" s="8" t="inlineStr"/>
       <c r="M77" s="8" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr"/>
-      <c r="O77" s="9" t="inlineStr">
-        <is>
-          <t>2486.00</t>
-        </is>
-      </c>
-      <c r="P77" s="9" t="inlineStr">
-        <is>
-          <t>1250.00</t>
-        </is>
-      </c>
-      <c r="Q77" s="9" t="inlineStr"/>
-      <c r="R77" s="9" t="inlineStr"/>
-      <c r="S77" s="9" t="inlineStr"/>
+      <c r="O77" s="8" t="inlineStr"/>
+      <c r="P77" s="8" t="inlineStr">
+        <is>
+          <t>226.50</t>
+        </is>
+      </c>
+      <c r="Q77" s="8" t="inlineStr"/>
+      <c r="R77" s="8" t="inlineStr"/>
+      <c r="S77" s="8" t="inlineStr"/>
       <c r="T77" s="8" t="inlineStr"/>
-      <c r="U77" s="9" t="inlineStr"/>
+      <c r="U77" s="8" t="inlineStr"/>
       <c r="V77" s="8" t="inlineStr"/>
-      <c r="W77" s="8" t="inlineStr">
-        <is>
-          <t>3585.00</t>
-        </is>
-      </c>
-      <c r="X77" s="9" t="inlineStr">
-        <is>
-          <t>2594.00</t>
-        </is>
-      </c>
+      <c r="W77" s="8" t="inlineStr"/>
+      <c r="X77" s="8" t="inlineStr"/>
       <c r="Y77" s="8" t="inlineStr"/>
-      <c r="Z77" s="10" t="n">
-        <v>3693</v>
-      </c>
-      <c r="AA77" s="11" t="inlineStr"/>
-      <c r="AB77" s="12" t="inlineStr"/>
+      <c r="Z77" s="8" t="inlineStr"/>
+      <c r="AA77" s="8" t="inlineStr"/>
+      <c r="AB77" s="10" t="inlineStr"/>
+      <c r="AC77" s="11" t="inlineStr"/>
+      <c r="AD77" s="12" t="inlineStr"/>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="1" t="n"/>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr"/>
-      <c r="D78" s="8" t="inlineStr"/>
-      <c r="E78" s="8" t="inlineStr"/>
-      <c r="F78" s="8" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="8" t="inlineStr"/>
-      <c r="I78" s="8" t="inlineStr"/>
-      <c r="J78" s="8" t="inlineStr"/>
-      <c r="K78" s="8" t="inlineStr"/>
-      <c r="L78" s="8" t="inlineStr"/>
-      <c r="M78" s="8" t="inlineStr"/>
-      <c r="N78" s="8" t="inlineStr"/>
-      <c r="O78" s="9" t="inlineStr"/>
-      <c r="P78" s="9" t="inlineStr"/>
-      <c r="Q78" s="9" t="inlineStr"/>
-      <c r="R78" s="9" t="inlineStr">
-        <is>
-          <t>2533.00</t>
-        </is>
-      </c>
-      <c r="S78" s="9" t="inlineStr"/>
-      <c r="T78" s="8" t="inlineStr"/>
-      <c r="U78" s="9" t="inlineStr"/>
-      <c r="V78" s="8" t="inlineStr"/>
-      <c r="W78" s="8" t="inlineStr">
-        <is>
-          <t>4472.00</t>
-        </is>
-      </c>
-      <c r="X78" s="9" t="inlineStr"/>
-      <c r="Y78" s="8" t="inlineStr"/>
-      <c r="Z78" s="10" t="inlineStr"/>
-      <c r="AA78" s="11" t="inlineStr"/>
-      <c r="AB78" s="12" t="inlineStr"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Gopher
+Random: 257.6
+Human: 2412.5</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 8240</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr"/>
+      <c r="J78" s="4" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr"/>
+      <c r="M78" s="4" t="inlineStr"/>
+      <c r="N78" s="4" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr"/>
+      <c r="P78" s="4" t="inlineStr"/>
+      <c r="Q78" s="4" t="inlineStr"/>
+      <c r="R78" s="4" t="inlineStr"/>
+      <c r="S78" s="4" t="inlineStr"/>
+      <c r="T78" s="4" t="inlineStr"/>
+      <c r="U78" s="4" t="inlineStr"/>
+      <c r="V78" s="4" t="inlineStr"/>
+      <c r="W78" s="4" t="inlineStr"/>
+      <c r="X78" s="4" t="inlineStr"/>
+      <c r="Y78" s="4" t="inlineStr"/>
+      <c r="Z78" s="4" t="inlineStr"/>
+      <c r="AA78" s="4" t="inlineStr"/>
+      <c r="AB78" s="5" t="inlineStr"/>
+      <c r="AC78" s="6" t="n">
+        <v>-3430.5</v>
+      </c>
+      <c r="AD78" s="7" t="n">
+        <v>-1.591953222887373</v>
+      </c>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr"/>
-      <c r="D79" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>5968.00</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>3752.00</t>
+        </is>
+      </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>3327.00</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="inlineStr"/>
+          <t>3275.00</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>3914.00</t>
+        </is>
+      </c>
       <c r="G79" s="8" t="inlineStr"/>
       <c r="H79" s="8" t="inlineStr"/>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>3829.00</t>
+          <t>4219.00</t>
         </is>
       </c>
       <c r="J79" s="8" t="inlineStr"/>
@@ -5213,66 +5642,48 @@
       <c r="N79" s="8" t="inlineStr"/>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>1024.00</t>
+          <t>2486.00</t>
         </is>
       </c>
       <c r="P79" s="9" t="inlineStr">
         <is>
-          <t>927.00</t>
-        </is>
-      </c>
-      <c r="Q79" s="13" t="inlineStr">
-        <is>
-          <t>847.00</t>
-        </is>
-      </c>
-      <c r="R79" s="13" t="inlineStr">
-        <is>
-          <t>2933.00</t>
-        </is>
-      </c>
-      <c r="S79" s="13" t="inlineStr">
-        <is>
-          <t>2775.00</t>
-        </is>
-      </c>
+          <t>1250.00</t>
+        </is>
+      </c>
+      <c r="Q79" s="9" t="inlineStr"/>
+      <c r="R79" s="9" t="inlineStr"/>
+      <c r="S79" s="9" t="inlineStr"/>
       <c r="T79" s="8" t="inlineStr"/>
-      <c r="U79" s="13" t="inlineStr">
-        <is>
-          <t>3061.00</t>
-        </is>
-      </c>
-      <c r="V79" s="15" t="inlineStr">
-        <is>
-          <t>8373.00</t>
-        </is>
-      </c>
-      <c r="W79" s="8" t="inlineStr">
-        <is>
-          <t>7531.00</t>
-        </is>
-      </c>
-      <c r="X79" s="9" t="inlineStr">
-        <is>
-          <t>1005.00</t>
-        </is>
-      </c>
-      <c r="Y79" s="8" t="inlineStr"/>
-      <c r="Z79" s="10" t="n">
-        <v>4895.666666666667</v>
-      </c>
-      <c r="AA79" s="10" t="n">
-        <v>1202.666666666667</v>
-      </c>
-      <c r="AB79" s="12" t="n">
-        <v>0.558107878169134</v>
-      </c>
+      <c r="U79" s="8" t="inlineStr"/>
+      <c r="V79" s="9" t="inlineStr"/>
+      <c r="W79" s="9" t="inlineStr"/>
+      <c r="X79" s="8" t="inlineStr">
+        <is>
+          <t>8159.00</t>
+        </is>
+      </c>
+      <c r="Y79" s="8" t="inlineStr">
+        <is>
+          <t>3585.00</t>
+        </is>
+      </c>
+      <c r="Z79" s="9" t="inlineStr">
+        <is>
+          <t>2594.00</t>
+        </is>
+      </c>
+      <c r="AA79" s="8" t="inlineStr"/>
+      <c r="AB79" s="10" t="n">
+        <v>4809.5</v>
+      </c>
+      <c r="AC79" s="11" t="inlineStr"/>
+      <c r="AD79" s="12" t="inlineStr"/>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr"/>
@@ -5290,222 +5701,272 @@
       <c r="O80" s="9" t="inlineStr"/>
       <c r="P80" s="9" t="inlineStr"/>
       <c r="Q80" s="9" t="inlineStr"/>
-      <c r="R80" s="9" t="inlineStr"/>
+      <c r="R80" s="9" t="inlineStr">
+        <is>
+          <t>2533.00</t>
+        </is>
+      </c>
       <c r="S80" s="9" t="inlineStr"/>
       <c r="T80" s="8" t="inlineStr"/>
-      <c r="U80" s="9" t="inlineStr"/>
-      <c r="V80" s="8" t="inlineStr"/>
-      <c r="W80" s="8" t="inlineStr">
-        <is>
-          <t>5320.00</t>
-        </is>
-      </c>
-      <c r="X80" s="9" t="inlineStr"/>
-      <c r="Y80" s="8" t="inlineStr"/>
-      <c r="Z80" s="10" t="inlineStr"/>
-      <c r="AA80" s="11" t="inlineStr"/>
-      <c r="AB80" s="12" t="inlineStr"/>
+      <c r="U80" s="8" t="inlineStr"/>
+      <c r="V80" s="9" t="inlineStr"/>
+      <c r="W80" s="9" t="inlineStr"/>
+      <c r="X80" s="8" t="inlineStr"/>
+      <c r="Y80" s="8" t="inlineStr">
+        <is>
+          <t>4472.00</t>
+        </is>
+      </c>
+      <c r="Z80" s="9" t="inlineStr"/>
+      <c r="AA80" s="8" t="inlineStr"/>
+      <c r="AB80" s="10" t="inlineStr"/>
+      <c r="AC80" s="11" t="inlineStr"/>
+      <c r="AD80" s="12" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr"/>
       <c r="D81" s="8" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>3327.00</t>
+        </is>
+      </c>
       <c r="F81" s="8" t="inlineStr"/>
       <c r="G81" s="8" t="inlineStr"/>
       <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>3829.00</t>
+        </is>
+      </c>
       <c r="J81" s="8" t="inlineStr"/>
       <c r="K81" s="8" t="inlineStr"/>
       <c r="L81" s="8" t="inlineStr"/>
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="8" t="inlineStr"/>
-      <c r="O81" s="9" t="inlineStr"/>
-      <c r="P81" s="9" t="inlineStr"/>
-      <c r="Q81" s="9" t="inlineStr"/>
-      <c r="R81" s="9" t="inlineStr"/>
-      <c r="S81" s="9" t="inlineStr"/>
+      <c r="O81" s="9" t="inlineStr">
+        <is>
+          <t>1024.00</t>
+        </is>
+      </c>
+      <c r="P81" s="9" t="inlineStr">
+        <is>
+          <t>927.00</t>
+        </is>
+      </c>
+      <c r="Q81" s="13" t="inlineStr">
+        <is>
+          <t>847.00</t>
+        </is>
+      </c>
+      <c r="R81" s="13" t="inlineStr">
+        <is>
+          <t>2933.00</t>
+        </is>
+      </c>
+      <c r="S81" s="13" t="inlineStr">
+        <is>
+          <t>2775.00</t>
+        </is>
+      </c>
       <c r="T81" s="8" t="inlineStr"/>
-      <c r="U81" s="9" t="inlineStr"/>
-      <c r="V81" s="8" t="inlineStr"/>
-      <c r="W81" s="8" t="inlineStr">
-        <is>
-          <t>2516.00</t>
-        </is>
-      </c>
-      <c r="X81" s="9" t="inlineStr"/>
-      <c r="Y81" s="8" t="inlineStr"/>
-      <c r="Z81" s="10" t="inlineStr"/>
-      <c r="AA81" s="11" t="inlineStr"/>
-      <c r="AB81" s="12" t="inlineStr"/>
+      <c r="U81" s="8" t="inlineStr"/>
+      <c r="V81" s="13" t="inlineStr">
+        <is>
+          <t>1437.00</t>
+        </is>
+      </c>
+      <c r="W81" s="13" t="inlineStr">
+        <is>
+          <t>3061.00</t>
+        </is>
+      </c>
+      <c r="X81" s="15" t="inlineStr">
+        <is>
+          <t>8373.00</t>
+        </is>
+      </c>
+      <c r="Y81" s="8" t="inlineStr">
+        <is>
+          <t>7531.00</t>
+        </is>
+      </c>
+      <c r="Z81" s="9" t="inlineStr">
+        <is>
+          <t>1005.00</t>
+        </is>
+      </c>
+      <c r="AA81" s="8" t="inlineStr"/>
+      <c r="AB81" s="10" t="n">
+        <v>5765</v>
+      </c>
+      <c r="AC81" s="10" t="n">
+        <v>955.5</v>
+      </c>
+      <c r="AD81" s="12" t="n">
+        <v>0.4434080467771126</v>
+      </c>
     </row>
     <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Hero
-Random: 1027.0
-Human: 30826.4</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11044</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr"/>
-      <c r="D82" s="4" t="inlineStr"/>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr"/>
-      <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr"/>
-      <c r="O82" s="4" t="inlineStr"/>
-      <c r="P82" s="4" t="inlineStr"/>
-      <c r="Q82" s="4" t="inlineStr"/>
-      <c r="R82" s="4" t="inlineStr"/>
-      <c r="S82" s="4" t="inlineStr"/>
-      <c r="T82" s="4" t="inlineStr"/>
-      <c r="U82" s="4" t="inlineStr"/>
-      <c r="V82" s="4" t="inlineStr"/>
-      <c r="W82" s="4" t="inlineStr"/>
-      <c r="X82" s="4" t="inlineStr"/>
-      <c r="Y82" s="4" t="inlineStr"/>
-      <c r="Z82" s="5" t="inlineStr"/>
-      <c r="AA82" s="6" t="n">
-        <v>741.625</v>
-      </c>
-      <c r="AB82" s="7" t="n">
-        <v>0.02488724605193393</v>
-      </c>
+      <c r="A82" s="1" t="n"/>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr"/>
+      <c r="D82" s="8" t="inlineStr"/>
+      <c r="E82" s="8" t="inlineStr"/>
+      <c r="F82" s="8" t="inlineStr"/>
+      <c r="G82" s="8" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr"/>
+      <c r="J82" s="8" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr"/>
+      <c r="L82" s="8" t="inlineStr"/>
+      <c r="M82" s="8" t="inlineStr"/>
+      <c r="N82" s="8" t="inlineStr"/>
+      <c r="O82" s="9" t="inlineStr"/>
+      <c r="P82" s="9" t="inlineStr"/>
+      <c r="Q82" s="9" t="inlineStr"/>
+      <c r="R82" s="9" t="inlineStr"/>
+      <c r="S82" s="9" t="inlineStr"/>
+      <c r="T82" s="8" t="inlineStr"/>
+      <c r="U82" s="8" t="inlineStr"/>
+      <c r="V82" s="9" t="inlineStr"/>
+      <c r="W82" s="9" t="inlineStr"/>
+      <c r="X82" s="8" t="inlineStr"/>
+      <c r="Y82" s="8" t="inlineStr">
+        <is>
+          <t>5320.00</t>
+        </is>
+      </c>
+      <c r="Z82" s="9" t="inlineStr"/>
+      <c r="AA82" s="8" t="inlineStr"/>
+      <c r="AB82" s="10" t="inlineStr"/>
+      <c r="AC82" s="11" t="inlineStr"/>
+      <c r="AD82" s="12" t="inlineStr"/>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>7608.50</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr"/>
       <c r="D83" s="8" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>12996.75</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>13456.25</t>
-        </is>
-      </c>
+      <c r="E83" s="8" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr"/>
       <c r="G83" s="8" t="inlineStr"/>
       <c r="H83" s="8" t="inlineStr"/>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>13081.00</t>
-        </is>
-      </c>
+      <c r="I83" s="8" t="inlineStr"/>
       <c r="J83" s="8" t="inlineStr"/>
       <c r="K83" s="8" t="inlineStr"/>
       <c r="L83" s="8" t="inlineStr"/>
       <c r="M83" s="8" t="inlineStr"/>
       <c r="N83" s="8" t="inlineStr"/>
-      <c r="O83" s="8" t="inlineStr"/>
-      <c r="P83" s="8" t="inlineStr"/>
-      <c r="Q83" s="8" t="inlineStr"/>
-      <c r="R83" s="8" t="inlineStr"/>
-      <c r="S83" s="8" t="inlineStr"/>
+      <c r="O83" s="9" t="inlineStr"/>
+      <c r="P83" s="9" t="inlineStr"/>
+      <c r="Q83" s="9" t="inlineStr"/>
+      <c r="R83" s="9" t="inlineStr"/>
+      <c r="S83" s="9" t="inlineStr"/>
       <c r="T83" s="8" t="inlineStr"/>
       <c r="U83" s="8" t="inlineStr"/>
-      <c r="V83" s="8" t="inlineStr"/>
-      <c r="W83" s="8" t="inlineStr"/>
+      <c r="V83" s="9" t="inlineStr"/>
+      <c r="W83" s="9" t="inlineStr"/>
       <c r="X83" s="8" t="inlineStr"/>
-      <c r="Y83" s="8" t="inlineStr"/>
-      <c r="Z83" s="10" t="n">
-        <v>11785.625</v>
-      </c>
-      <c r="AA83" s="11" t="inlineStr"/>
-      <c r="AB83" s="12" t="inlineStr"/>
+      <c r="Y83" s="8" t="inlineStr">
+        <is>
+          <t>2516.00</t>
+        </is>
+      </c>
+      <c r="Z83" s="9" t="inlineStr"/>
+      <c r="AA83" s="8" t="inlineStr"/>
+      <c r="AB83" s="10" t="inlineStr"/>
+      <c r="AC83" s="11" t="inlineStr"/>
+      <c r="AD83" s="12" t="inlineStr"/>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="1" t="n"/>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>13473.00</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr"/>
-      <c r="E84" s="8" t="inlineStr"/>
-      <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" s="8" t="inlineStr"/>
-      <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr"/>
-      <c r="L84" s="8" t="inlineStr"/>
-      <c r="M84" s="8" t="inlineStr"/>
-      <c r="N84" s="8" t="inlineStr"/>
-      <c r="O84" s="8" t="inlineStr"/>
-      <c r="P84" s="8" t="inlineStr"/>
-      <c r="Q84" s="8" t="inlineStr"/>
-      <c r="R84" s="8" t="inlineStr"/>
-      <c r="S84" s="8" t="inlineStr"/>
-      <c r="T84" s="8" t="inlineStr"/>
-      <c r="U84" s="8" t="inlineStr"/>
-      <c r="V84" s="8" t="inlineStr"/>
-      <c r="W84" s="8" t="inlineStr"/>
-      <c r="X84" s="8" t="inlineStr"/>
-      <c r="Y84" s="8" t="inlineStr"/>
-      <c r="Z84" s="10" t="inlineStr"/>
-      <c r="AA84" s="11" t="inlineStr"/>
-      <c r="AB84" s="12" t="inlineStr"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Hero
+Random: 1027.0
+Human: 30826.4</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11044</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr"/>
+      <c r="N84" s="4" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr"/>
+      <c r="P84" s="4" t="inlineStr"/>
+      <c r="Q84" s="4" t="inlineStr"/>
+      <c r="R84" s="4" t="inlineStr"/>
+      <c r="S84" s="4" t="inlineStr"/>
+      <c r="T84" s="4" t="inlineStr"/>
+      <c r="U84" s="4" t="inlineStr"/>
+      <c r="V84" s="4" t="inlineStr"/>
+      <c r="W84" s="4" t="inlineStr"/>
+      <c r="X84" s="4" t="inlineStr"/>
+      <c r="Y84" s="4" t="inlineStr"/>
+      <c r="Z84" s="4" t="inlineStr"/>
+      <c r="AA84" s="4" t="inlineStr"/>
+      <c r="AB84" s="5" t="inlineStr"/>
+      <c r="AC84" s="6" t="n">
+        <v>741.625</v>
+      </c>
+      <c r="AD84" s="7" t="n">
+        <v>0.02488724605193393</v>
+      </c>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>13108.75</t>
+          <t>7608.50</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>13251.25</t>
+          <t>12996.75</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>13231.50</t>
+          <t>13456.25</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr"/>
       <c r="H85" s="8" t="inlineStr"/>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>13325.50</t>
+          <t>13081.00</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr"/>
@@ -5524,26 +5985,24 @@
       <c r="W85" s="8" t="inlineStr"/>
       <c r="X85" s="8" t="inlineStr"/>
       <c r="Y85" s="8" t="inlineStr"/>
-      <c r="Z85" s="10" t="n">
-        <v>13229.25</v>
-      </c>
-      <c r="AA85" s="10" t="n">
-        <v>1443.625</v>
-      </c>
-      <c r="AB85" s="12" t="n">
-        <v>0.04844476734430894</v>
-      </c>
+      <c r="Z85" s="8" t="inlineStr"/>
+      <c r="AA85" s="8" t="inlineStr"/>
+      <c r="AB85" s="10" t="n">
+        <v>11785.625</v>
+      </c>
+      <c r="AC85" s="11" t="inlineStr"/>
+      <c r="AD85" s="12" t="inlineStr"/>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>13335.00</t>
+          <t>13473.00</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr"/>
@@ -5568,28 +6027,42 @@
       <c r="W86" s="8" t="inlineStr"/>
       <c r="X86" s="8" t="inlineStr"/>
       <c r="Y86" s="8" t="inlineStr"/>
-      <c r="Z86" s="10" t="inlineStr"/>
-      <c r="AA86" s="11" t="inlineStr"/>
-      <c r="AB86" s="12" t="inlineStr"/>
+      <c r="Z86" s="8" t="inlineStr"/>
+      <c r="AA86" s="8" t="inlineStr"/>
+      <c r="AB86" s="10" t="inlineStr"/>
+      <c r="AC86" s="11" t="inlineStr"/>
+      <c r="AD86" s="12" t="inlineStr"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>13410.50</t>
+          <t>13108.75</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr"/>
-      <c r="F87" s="8" t="inlineStr"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>13251.25</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>13231.50</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="inlineStr"/>
       <c r="H87" s="8" t="inlineStr"/>
-      <c r="I87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>13325.50</t>
+        </is>
+      </c>
       <c r="J87" s="8" t="inlineStr"/>
       <c r="K87" s="8" t="inlineStr"/>
       <c r="L87" s="8" t="inlineStr"/>
@@ -5606,64 +6079,68 @@
       <c r="W87" s="8" t="inlineStr"/>
       <c r="X87" s="8" t="inlineStr"/>
       <c r="Y87" s="8" t="inlineStr"/>
-      <c r="Z87" s="10" t="inlineStr"/>
-      <c r="AA87" s="11" t="inlineStr"/>
-      <c r="AB87" s="12" t="inlineStr"/>
+      <c r="Z87" s="8" t="inlineStr"/>
+      <c r="AA87" s="8" t="inlineStr"/>
+      <c r="AB87" s="10" t="n">
+        <v>13229.25</v>
+      </c>
+      <c r="AC87" s="10" t="n">
+        <v>1443.625</v>
+      </c>
+      <c r="AD87" s="12" t="n">
+        <v>0.04844476734430894</v>
+      </c>
     </row>
     <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Jamesbond
-Random: 29.0
-Human: 302.8</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 509</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr"/>
-      <c r="D88" s="4" t="inlineStr"/>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr"/>
-      <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="4" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr"/>
-      <c r="K88" s="4" t="inlineStr"/>
-      <c r="L88" s="4" t="inlineStr"/>
-      <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr"/>
-      <c r="O88" s="4" t="inlineStr"/>
-      <c r="P88" s="4" t="inlineStr"/>
-      <c r="Q88" s="4" t="inlineStr"/>
-      <c r="R88" s="4" t="inlineStr"/>
-      <c r="S88" s="4" t="inlineStr"/>
-      <c r="T88" s="4" t="inlineStr"/>
-      <c r="U88" s="4" t="inlineStr"/>
-      <c r="V88" s="4" t="inlineStr"/>
-      <c r="W88" s="4" t="inlineStr"/>
-      <c r="X88" s="4" t="inlineStr"/>
-      <c r="Y88" s="4" t="inlineStr"/>
-      <c r="Z88" s="5" t="inlineStr"/>
-      <c r="AA88" s="6" t="n">
-        <v>-35.66666666666669</v>
-      </c>
-      <c r="AB88" s="7" t="n">
-        <v>-0.1302654005356709</v>
-      </c>
+      <c r="A88" s="1" t="n"/>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>13335.00</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr"/>
+      <c r="E88" s="8" t="inlineStr"/>
+      <c r="F88" s="8" t="inlineStr"/>
+      <c r="G88" s="8" t="inlineStr"/>
+      <c r="H88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr"/>
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="8" t="inlineStr"/>
+      <c r="M88" s="8" t="inlineStr"/>
+      <c r="N88" s="8" t="inlineStr"/>
+      <c r="O88" s="8" t="inlineStr"/>
+      <c r="P88" s="8" t="inlineStr"/>
+      <c r="Q88" s="8" t="inlineStr"/>
+      <c r="R88" s="8" t="inlineStr"/>
+      <c r="S88" s="8" t="inlineStr"/>
+      <c r="T88" s="8" t="inlineStr"/>
+      <c r="U88" s="8" t="inlineStr"/>
+      <c r="V88" s="8" t="inlineStr"/>
+      <c r="W88" s="8" t="inlineStr"/>
+      <c r="X88" s="8" t="inlineStr"/>
+      <c r="Y88" s="8" t="inlineStr"/>
+      <c r="Z88" s="8" t="inlineStr"/>
+      <c r="AA88" s="8" t="inlineStr"/>
+      <c r="AB88" s="10" t="inlineStr"/>
+      <c r="AC88" s="11" t="inlineStr"/>
+      <c r="AD88" s="12" t="inlineStr"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>490.00</t>
+          <t>13410.50</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr"/>
@@ -5673,19 +6150,11 @@
       <c r="H89" s="8" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr"/>
       <c r="J89" s="8" t="inlineStr"/>
-      <c r="K89" s="8" t="inlineStr">
-        <is>
-          <t>532.50, 537.50</t>
-        </is>
-      </c>
+      <c r="K89" s="8" t="inlineStr"/>
       <c r="L89" s="8" t="inlineStr"/>
       <c r="M89" s="8" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr"/>
-      <c r="O89" s="8" t="inlineStr">
-        <is>
-          <t>522.50</t>
-        </is>
-      </c>
+      <c r="O89" s="8" t="inlineStr"/>
       <c r="P89" s="8" t="inlineStr"/>
       <c r="Q89" s="8" t="inlineStr"/>
       <c r="R89" s="8" t="inlineStr"/>
@@ -5694,64 +6163,72 @@
       <c r="U89" s="8" t="inlineStr"/>
       <c r="V89" s="8" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr"/>
-      <c r="X89" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
-        </is>
-      </c>
+      <c r="X89" s="8" t="inlineStr"/>
       <c r="Y89" s="8" t="inlineStr"/>
-      <c r="Z89" s="10" t="n">
-        <v>473.3333333333333</v>
-      </c>
-      <c r="AA89" s="11" t="inlineStr"/>
-      <c r="AB89" s="12" t="inlineStr"/>
+      <c r="Z89" s="8" t="inlineStr"/>
+      <c r="AA89" s="8" t="inlineStr"/>
+      <c r="AB89" s="10" t="inlineStr"/>
+      <c r="AC89" s="11" t="inlineStr"/>
+      <c r="AD89" s="12" t="inlineStr"/>
     </row>
     <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="1" t="n"/>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr"/>
-      <c r="D90" s="8" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr"/>
-      <c r="F90" s="8" t="inlineStr"/>
-      <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr"/>
-      <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr"/>
-      <c r="L90" s="8" t="inlineStr"/>
-      <c r="M90" s="8" t="inlineStr"/>
-      <c r="N90" s="8" t="inlineStr"/>
-      <c r="O90" s="8" t="inlineStr">
-        <is>
-          <t>575.00</t>
-        </is>
-      </c>
-      <c r="P90" s="8" t="inlineStr"/>
-      <c r="Q90" s="8" t="inlineStr"/>
-      <c r="R90" s="8" t="inlineStr"/>
-      <c r="S90" s="8" t="inlineStr"/>
-      <c r="T90" s="8" t="inlineStr"/>
-      <c r="U90" s="8" t="inlineStr"/>
-      <c r="V90" s="8" t="inlineStr"/>
-      <c r="W90" s="8" t="inlineStr"/>
-      <c r="X90" s="8" t="inlineStr"/>
-      <c r="Y90" s="8" t="inlineStr"/>
-      <c r="Z90" s="10" t="inlineStr"/>
-      <c r="AA90" s="11" t="inlineStr"/>
-      <c r="AB90" s="12" t="inlineStr"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Jamesbond
+Random: 29.0
+Human: 302.8</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 509</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr"/>
+      <c r="N90" s="4" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr"/>
+      <c r="P90" s="4" t="inlineStr"/>
+      <c r="Q90" s="4" t="inlineStr"/>
+      <c r="R90" s="4" t="inlineStr"/>
+      <c r="S90" s="4" t="inlineStr"/>
+      <c r="T90" s="4" t="inlineStr"/>
+      <c r="U90" s="4" t="inlineStr"/>
+      <c r="V90" s="4" t="inlineStr"/>
+      <c r="W90" s="4" t="inlineStr"/>
+      <c r="X90" s="4" t="inlineStr"/>
+      <c r="Y90" s="4" t="inlineStr"/>
+      <c r="Z90" s="4" t="inlineStr"/>
+      <c r="AA90" s="4" t="inlineStr"/>
+      <c r="AB90" s="5" t="inlineStr"/>
+      <c r="AC90" s="6" t="n">
+        <v>-35.66666666666669</v>
+      </c>
+      <c r="AD90" s="7" t="n">
+        <v>-0.1302654005356709</v>
+      </c>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>490.00</t>
+        </is>
+      </c>
       <c r="D91" s="8" t="inlineStr"/>
       <c r="E91" s="8" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr"/>
@@ -5761,7 +6238,7 @@
       <c r="J91" s="8" t="inlineStr"/>
       <c r="K91" s="8" t="inlineStr">
         <is>
-          <t>567.50, 660.00</t>
+          <t>532.50, 537.50</t>
         </is>
       </c>
       <c r="L91" s="8" t="inlineStr"/>
@@ -5769,7 +6246,7 @@
       <c r="N91" s="8" t="inlineStr"/>
       <c r="O91" s="8" t="inlineStr">
         <is>
-          <t>665.00</t>
+          <t>522.50</t>
         </is>
       </c>
       <c r="P91" s="8" t="inlineStr"/>
@@ -5780,80 +6257,74 @@
       <c r="U91" s="8" t="inlineStr"/>
       <c r="V91" s="8" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr"/>
-      <c r="X91" s="8" t="inlineStr">
-        <is>
-          <t>375.00</t>
-        </is>
-      </c>
+      <c r="X91" s="8" t="inlineStr"/>
       <c r="Y91" s="8" t="inlineStr"/>
-      <c r="Z91" s="10" t="n">
-        <v>535.8333333333334</v>
-      </c>
-      <c r="AA91" s="10" t="n">
-        <v>62.50000000000006</v>
-      </c>
-      <c r="AB91" s="12" t="n">
-        <v>0.2282688093498906</v>
-      </c>
+      <c r="Z91" s="8" t="inlineStr">
+        <is>
+          <t>365.00</t>
+        </is>
+      </c>
+      <c r="AA91" s="8" t="inlineStr"/>
+      <c r="AB91" s="10" t="n">
+        <v>473.3333333333333</v>
+      </c>
+      <c r="AC91" s="11" t="inlineStr"/>
+      <c r="AD91" s="12" t="inlineStr"/>
     </row>
     <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Kangaroo
-Random: 52.0
-Human: 3035.0</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4208</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr"/>
-      <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr"/>
-      <c r="K92" s="4" t="inlineStr"/>
-      <c r="L92" s="4" t="inlineStr"/>
-      <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr"/>
-      <c r="O92" s="4" t="inlineStr"/>
-      <c r="P92" s="4" t="inlineStr"/>
-      <c r="Q92" s="4" t="inlineStr"/>
-      <c r="R92" s="4" t="inlineStr"/>
-      <c r="S92" s="4" t="inlineStr"/>
-      <c r="T92" s="4" t="inlineStr"/>
-      <c r="U92" s="4" t="inlineStr"/>
-      <c r="V92" s="4" t="inlineStr"/>
-      <c r="W92" s="4" t="inlineStr"/>
-      <c r="X92" s="4" t="inlineStr"/>
-      <c r="Y92" s="4" t="inlineStr"/>
-      <c r="Z92" s="5" t="inlineStr"/>
-      <c r="AA92" s="6" t="n">
-        <v>-2778</v>
-      </c>
-      <c r="AB92" s="7" t="n">
-        <v>-0.9312772376801878</v>
-      </c>
+      <c r="A92" s="1" t="n"/>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr"/>
+      <c r="D92" s="8" t="inlineStr"/>
+      <c r="E92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr"/>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr"/>
+      <c r="L92" s="8" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr"/>
+      <c r="N92" s="8" t="inlineStr"/>
+      <c r="O92" s="8" t="inlineStr">
+        <is>
+          <t>575.00</t>
+        </is>
+      </c>
+      <c r="P92" s="8" t="inlineStr"/>
+      <c r="Q92" s="8" t="inlineStr"/>
+      <c r="R92" s="8" t="inlineStr"/>
+      <c r="S92" s="8" t="inlineStr"/>
+      <c r="T92" s="8" t="inlineStr"/>
+      <c r="U92" s="8" t="inlineStr"/>
+      <c r="V92" s="8" t="inlineStr"/>
+      <c r="W92" s="8" t="inlineStr"/>
+      <c r="X92" s="8" t="inlineStr"/>
+      <c r="Y92" s="8" t="inlineStr"/>
+      <c r="Z92" s="8" t="inlineStr"/>
+      <c r="AA92" s="8" t="inlineStr"/>
+      <c r="AB92" s="10" t="inlineStr"/>
+      <c r="AC92" s="11" t="inlineStr"/>
+      <c r="AD92" s="12" t="inlineStr"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr"/>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="D93" s="8" t="inlineStr"/>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>1770.00</t>
-        </is>
-      </c>
+      <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr"/>
       <c r="G93" s="8" t="inlineStr"/>
       <c r="H93" s="8" t="inlineStr"/>
@@ -5861,26 +6332,18 @@
       <c r="J93" s="8" t="inlineStr"/>
       <c r="K93" s="8" t="inlineStr">
         <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
-        <is>
-          <t>1730.00</t>
-        </is>
-      </c>
+          <t>567.50, 660.00</t>
+        </is>
+      </c>
+      <c r="L93" s="8" t="inlineStr"/>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
       <c r="O93" s="8" t="inlineStr">
         <is>
-          <t>1550.00</t>
-        </is>
-      </c>
-      <c r="P93" s="8" t="inlineStr">
-        <is>
-          <t>930.00</t>
-        </is>
-      </c>
+          <t>665.00</t>
+        </is>
+      </c>
+      <c r="P93" s="8" t="inlineStr"/>
       <c r="Q93" s="8" t="inlineStr"/>
       <c r="R93" s="8" t="inlineStr"/>
       <c r="S93" s="8" t="inlineStr"/>
@@ -5890,70 +6353,80 @@
       <c r="W93" s="8" t="inlineStr"/>
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="8" t="inlineStr"/>
-      <c r="Z93" s="10" t="n">
-        <v>1430</v>
-      </c>
-      <c r="AA93" s="11" t="inlineStr"/>
-      <c r="AB93" s="12" t="inlineStr"/>
+      <c r="Z93" s="8" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
+      <c r="AA93" s="8" t="inlineStr"/>
+      <c r="AB93" s="10" t="n">
+        <v>535.8333333333334</v>
+      </c>
+      <c r="AC93" s="10" t="n">
+        <v>62.50000000000006</v>
+      </c>
+      <c r="AD93" s="12" t="n">
+        <v>0.2282688093498906</v>
+      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="1" t="n"/>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr"/>
-      <c r="D94" s="8" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr"/>
-      <c r="F94" s="8" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr">
-        <is>
-          <t>1310.00</t>
-        </is>
-      </c>
-      <c r="L94" s="8" t="inlineStr"/>
-      <c r="M94" s="8" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
-      <c r="O94" s="8" t="inlineStr">
-        <is>
-          <t>1500.00</t>
-        </is>
-      </c>
-      <c r="P94" s="8" t="inlineStr">
-        <is>
-          <t>1030.00</t>
-        </is>
-      </c>
-      <c r="Q94" s="8" t="inlineStr"/>
-      <c r="R94" s="8" t="inlineStr"/>
-      <c r="S94" s="8" t="inlineStr"/>
-      <c r="T94" s="8" t="inlineStr"/>
-      <c r="U94" s="8" t="inlineStr"/>
-      <c r="V94" s="8" t="inlineStr"/>
-      <c r="W94" s="8" t="inlineStr"/>
-      <c r="X94" s="8" t="inlineStr"/>
-      <c r="Y94" s="8" t="inlineStr"/>
-      <c r="Z94" s="10" t="inlineStr"/>
-      <c r="AA94" s="11" t="inlineStr"/>
-      <c r="AB94" s="12" t="inlineStr"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Kangaroo
+Random: 52.0
+Human: 3035.0</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4208</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
+      <c r="D94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr"/>
+      <c r="P94" s="4" t="inlineStr"/>
+      <c r="Q94" s="4" t="inlineStr"/>
+      <c r="R94" s="4" t="inlineStr"/>
+      <c r="S94" s="4" t="inlineStr"/>
+      <c r="T94" s="4" t="inlineStr"/>
+      <c r="U94" s="4" t="inlineStr"/>
+      <c r="V94" s="4" t="inlineStr"/>
+      <c r="W94" s="4" t="inlineStr"/>
+      <c r="X94" s="4" t="inlineStr"/>
+      <c r="Y94" s="4" t="inlineStr"/>
+      <c r="Z94" s="4" t="inlineStr"/>
+      <c r="AA94" s="4" t="inlineStr"/>
+      <c r="AB94" s="5" t="inlineStr"/>
+      <c r="AC94" s="6" t="n">
+        <v>-2611.333333333333</v>
+      </c>
+      <c r="AD94" s="7" t="n">
+        <v>-0.8754050731925354</v>
+      </c>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr"/>
       <c r="D95" s="8" t="inlineStr"/>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>1760.00</t>
+          <t>1770.00</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr"/>
@@ -5963,28 +6436,28 @@
       <c r="J95" s="8" t="inlineStr"/>
       <c r="K95" s="8" t="inlineStr">
         <is>
-          <t>1590.00</t>
-        </is>
-      </c>
-      <c r="L95" s="8" t="inlineStr"/>
+          <t>1470.00</t>
+        </is>
+      </c>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>1730.00</t>
+        </is>
+      </c>
       <c r="M95" s="8" t="inlineStr"/>
       <c r="N95" s="8" t="inlineStr"/>
       <c r="O95" s="8" t="inlineStr">
         <is>
-          <t>1670.00</t>
-        </is>
-      </c>
-      <c r="P95" s="8" t="inlineStr">
-        <is>
-          <t>760.00</t>
+          <t>1550.00</t>
+        </is>
+      </c>
+      <c r="P95" s="9" t="inlineStr">
+        <is>
+          <t>930.00</t>
         </is>
       </c>
       <c r="Q95" s="8" t="inlineStr"/>
-      <c r="R95" s="15" t="inlineStr">
-        <is>
-          <t>2900.00</t>
-        </is>
-      </c>
+      <c r="R95" s="8" t="inlineStr"/>
       <c r="S95" s="8" t="inlineStr"/>
       <c r="T95" s="8" t="inlineStr"/>
       <c r="U95" s="8" t="inlineStr"/>
@@ -5992,302 +6465,308 @@
       <c r="W95" s="8" t="inlineStr"/>
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="8" t="inlineStr"/>
-      <c r="Z95" s="10" t="n">
-        <v>1445</v>
-      </c>
-      <c r="AA95" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB95" s="12" t="n">
-        <v>0.005028494803888703</v>
-      </c>
+      <c r="Z95" s="9" t="inlineStr"/>
+      <c r="AA95" s="8" t="inlineStr"/>
+      <c r="AB95" s="10" t="n">
+        <v>1596.666666666667</v>
+      </c>
+      <c r="AC95" s="11" t="inlineStr"/>
+      <c r="AD95" s="12" t="inlineStr"/>
     </row>
     <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Krull
-Random: 1598.0
-Human: 2665.5</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 8413</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr"/>
-      <c r="D96" s="4" t="inlineStr"/>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr"/>
-      <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="4" t="inlineStr"/>
-      <c r="J96" s="4" t="inlineStr"/>
-      <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="4" t="inlineStr"/>
-      <c r="M96" s="4" t="inlineStr"/>
-      <c r="N96" s="4" t="inlineStr"/>
-      <c r="O96" s="4" t="inlineStr"/>
-      <c r="P96" s="4" t="inlineStr"/>
-      <c r="Q96" s="4" t="inlineStr"/>
-      <c r="R96" s="4" t="inlineStr"/>
-      <c r="S96" s="4" t="inlineStr"/>
-      <c r="T96" s="4" t="inlineStr"/>
-      <c r="U96" s="4" t="inlineStr"/>
-      <c r="V96" s="4" t="inlineStr"/>
-      <c r="W96" s="4" t="inlineStr"/>
-      <c r="X96" s="4" t="inlineStr"/>
-      <c r="Y96" s="4" t="inlineStr"/>
-      <c r="Z96" s="5" t="inlineStr"/>
-      <c r="AA96" s="6" t="n">
-        <v>-2583.375</v>
-      </c>
-      <c r="AB96" s="7" t="n">
-        <v>-2.420023419203747</v>
-      </c>
+      <c r="A96" s="1" t="n"/>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr"/>
+      <c r="D96" s="8" t="inlineStr"/>
+      <c r="E96" s="8" t="inlineStr"/>
+      <c r="F96" s="8" t="inlineStr"/>
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr"/>
+      <c r="J96" s="8" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>1310.00</t>
+        </is>
+      </c>
+      <c r="L96" s="8" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr"/>
+      <c r="N96" s="8" t="inlineStr"/>
+      <c r="O96" s="8" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="P96" s="9" t="inlineStr">
+        <is>
+          <t>1030.00</t>
+        </is>
+      </c>
+      <c r="Q96" s="8" t="inlineStr"/>
+      <c r="R96" s="8" t="inlineStr"/>
+      <c r="S96" s="8" t="inlineStr"/>
+      <c r="T96" s="8" t="inlineStr"/>
+      <c r="U96" s="8" t="inlineStr"/>
+      <c r="V96" s="8" t="inlineStr"/>
+      <c r="W96" s="8" t="inlineStr"/>
+      <c r="X96" s="8" t="inlineStr"/>
+      <c r="Y96" s="8" t="inlineStr"/>
+      <c r="Z96" s="9" t="inlineStr"/>
+      <c r="AA96" s="8" t="inlineStr"/>
+      <c r="AB96" s="10" t="inlineStr"/>
+      <c r="AC96" s="11" t="inlineStr"/>
+      <c r="AD96" s="12" t="inlineStr"/>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr"/>
       <c r="D97" s="8" t="inlineStr"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>6202.00</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>5689.00</t>
-        </is>
-      </c>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr"/>
       <c r="G97" s="8" t="inlineStr"/>
       <c r="H97" s="8" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr">
-        <is>
-          <t>6107.50</t>
-        </is>
-      </c>
+      <c r="I97" s="8" t="inlineStr"/>
       <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>4708.50</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>5913.50</t>
-        </is>
-      </c>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>1590.00</t>
+        </is>
+      </c>
+      <c r="L97" s="8" t="inlineStr"/>
       <c r="M97" s="8" t="inlineStr"/>
       <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="8" t="inlineStr">
         <is>
-          <t>5228.50</t>
-        </is>
-      </c>
-      <c r="P97" s="9" t="inlineStr"/>
-      <c r="Q97" s="8" t="inlineStr">
-        <is>
-          <t>5599.00</t>
-        </is>
-      </c>
-      <c r="R97" s="9" t="inlineStr"/>
+          <t>1670.00</t>
+        </is>
+      </c>
+      <c r="P97" s="9" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
+      <c r="Q97" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="R97" s="15" t="inlineStr">
+        <is>
+          <t>2900.00</t>
+        </is>
+      </c>
       <c r="S97" s="8" t="inlineStr"/>
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr"/>
-      <c r="X97" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
+      <c r="X97" s="8" t="inlineStr"/>
       <c r="Y97" s="8" t="inlineStr"/>
-      <c r="Z97" s="10" t="n">
-        <v>5829.625</v>
-      </c>
-      <c r="AA97" s="11" t="inlineStr"/>
-      <c r="AB97" s="12" t="inlineStr"/>
+      <c r="Z97" s="13" t="inlineStr">
+        <is>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="AA97" s="8" t="inlineStr"/>
+      <c r="AB97" s="10" t="n">
+        <v>1673.333333333333</v>
+      </c>
+      <c r="AC97" s="10" t="n">
+        <v>76.66666666666652</v>
+      </c>
+      <c r="AD97" s="12" t="n">
+        <v>0.02570119566431998</v>
+      </c>
     </row>
     <row r="98" ht="24" customHeight="1">
-      <c r="A98" s="1" t="n"/>
-      <c r="B98" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr"/>
-      <c r="D98" s="8" t="inlineStr"/>
-      <c r="E98" s="8" t="inlineStr"/>
-      <c r="F98" s="8" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr"/>
-      <c r="H98" s="8" t="inlineStr"/>
-      <c r="I98" s="8" t="inlineStr"/>
-      <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="9" t="inlineStr">
-        <is>
-          <t>4851.00</t>
-        </is>
-      </c>
-      <c r="L98" s="9" t="inlineStr">
-        <is>
-          <t>6044.00</t>
-        </is>
-      </c>
-      <c r="M98" s="8" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr"/>
-      <c r="O98" s="8" t="inlineStr"/>
-      <c r="P98" s="9" t="inlineStr"/>
-      <c r="Q98" s="8" t="inlineStr"/>
-      <c r="R98" s="9" t="inlineStr"/>
-      <c r="S98" s="8" t="inlineStr"/>
-      <c r="T98" s="8" t="inlineStr"/>
-      <c r="U98" s="8" t="inlineStr"/>
-      <c r="V98" s="8" t="inlineStr"/>
-      <c r="W98" s="8" t="inlineStr"/>
-      <c r="X98" s="8" t="inlineStr">
-        <is>
-          <t>6587.00</t>
-        </is>
-      </c>
-      <c r="Y98" s="8" t="inlineStr"/>
-      <c r="Z98" s="10" t="inlineStr"/>
-      <c r="AA98" s="11" t="inlineStr"/>
-      <c r="AB98" s="12" t="inlineStr"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Krull
+Random: 1598.0
+Human: 2665.5</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 8413</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr"/>
+      <c r="D98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr"/>
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="inlineStr"/>
+      <c r="N98" s="4" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr"/>
+      <c r="P98" s="4" t="inlineStr"/>
+      <c r="Q98" s="4" t="inlineStr"/>
+      <c r="R98" s="4" t="inlineStr"/>
+      <c r="S98" s="4" t="inlineStr"/>
+      <c r="T98" s="4" t="inlineStr"/>
+      <c r="U98" s="4" t="inlineStr"/>
+      <c r="V98" s="4" t="inlineStr"/>
+      <c r="W98" s="4" t="inlineStr"/>
+      <c r="X98" s="4" t="inlineStr"/>
+      <c r="Y98" s="4" t="inlineStr"/>
+      <c r="Z98" s="4" t="inlineStr"/>
+      <c r="AA98" s="4" t="inlineStr"/>
+      <c r="AB98" s="5" t="inlineStr"/>
+      <c r="AC98" s="6" t="n">
+        <v>-2583.375</v>
+      </c>
+      <c r="AD98" s="7" t="n">
+        <v>-2.420023419203747</v>
+      </c>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr"/>
       <c r="D99" s="8" t="inlineStr"/>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>6576.50</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr"/>
+          <t>6202.00</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>5689.00</t>
+        </is>
+      </c>
       <c r="G99" s="8" t="inlineStr"/>
       <c r="H99" s="8" t="inlineStr"/>
-      <c r="I99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>6107.50</t>
+        </is>
+      </c>
       <c r="J99" s="8" t="inlineStr"/>
       <c r="K99" s="9" t="inlineStr">
         <is>
-          <t>5279.50</t>
+          <t>4708.50</t>
         </is>
       </c>
       <c r="L99" s="9" t="inlineStr">
         <is>
-          <t>5889.50</t>
+          <t>5913.50</t>
         </is>
       </c>
       <c r="M99" s="8" t="inlineStr"/>
       <c r="N99" s="8" t="inlineStr"/>
       <c r="O99" s="8" t="inlineStr">
         <is>
-          <t>6447.50</t>
-        </is>
-      </c>
-      <c r="P99" s="13" t="inlineStr">
-        <is>
-          <t>5900.50</t>
-        </is>
-      </c>
+          <t>5228.50</t>
+        </is>
+      </c>
+      <c r="P99" s="9" t="inlineStr"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>6828.50</t>
-        </is>
-      </c>
-      <c r="R99" s="13" t="inlineStr">
-        <is>
-          <t>5596.50</t>
-        </is>
-      </c>
+          <t>5599.00</t>
+        </is>
+      </c>
+      <c r="R99" s="9" t="inlineStr"/>
       <c r="S99" s="8" t="inlineStr"/>
       <c r="T99" s="8" t="inlineStr"/>
       <c r="U99" s="8" t="inlineStr"/>
       <c r="V99" s="8" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr"/>
-      <c r="X99" s="8" t="inlineStr">
-        <is>
-          <t>6796.50</t>
-        </is>
-      </c>
+      <c r="X99" s="8" t="inlineStr"/>
       <c r="Y99" s="8" t="inlineStr"/>
-      <c r="Z99" s="10" t="n">
-        <v>6662.25</v>
-      </c>
-      <c r="AA99" s="10" t="n">
-        <v>832.625</v>
-      </c>
-      <c r="AB99" s="12" t="n">
-        <v>0.779976580796253</v>
-      </c>
+      <c r="Z99" s="8" t="inlineStr">
+        <is>
+          <t>6289.00</t>
+        </is>
+      </c>
+      <c r="AA99" s="8" t="inlineStr"/>
+      <c r="AB99" s="10" t="n">
+        <v>5829.625</v>
+      </c>
+      <c r="AC99" s="11" t="inlineStr"/>
+      <c r="AD99" s="12" t="inlineStr"/>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>KungFuMaster
-Random: 258.5
-Human: 22736.3</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 26182</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr"/>
-      <c r="D100" s="4" t="inlineStr"/>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
-      <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="4" t="inlineStr"/>
-      <c r="J100" s="4" t="inlineStr"/>
-      <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="4" t="inlineStr"/>
-      <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr"/>
-      <c r="O100" s="4" t="inlineStr"/>
-      <c r="P100" s="4" t="inlineStr"/>
-      <c r="Q100" s="4" t="inlineStr"/>
-      <c r="R100" s="4" t="inlineStr"/>
-      <c r="S100" s="4" t="inlineStr"/>
-      <c r="T100" s="4" t="inlineStr"/>
-      <c r="U100" s="4" t="inlineStr"/>
-      <c r="V100" s="4" t="inlineStr"/>
-      <c r="W100" s="4" t="inlineStr"/>
-      <c r="X100" s="4" t="inlineStr"/>
-      <c r="Y100" s="4" t="inlineStr"/>
-      <c r="Z100" s="5" t="inlineStr"/>
-      <c r="AA100" s="6" t="n">
-        <v>-1044.5</v>
-      </c>
-      <c r="AB100" s="7" t="n">
-        <v>-0.04646807071866464</v>
-      </c>
+      <c r="A100" s="1" t="n"/>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>target: 1 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr"/>
+      <c r="D100" s="8" t="inlineStr"/>
+      <c r="E100" s="8" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr"/>
+      <c r="G100" s="8" t="inlineStr"/>
+      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr"/>
+      <c r="J100" s="8" t="inlineStr"/>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>4851.00</t>
+        </is>
+      </c>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>6044.00</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="inlineStr"/>
+      <c r="N100" s="8" t="inlineStr"/>
+      <c r="O100" s="8" t="inlineStr"/>
+      <c r="P100" s="9" t="inlineStr"/>
+      <c r="Q100" s="8" t="inlineStr"/>
+      <c r="R100" s="9" t="inlineStr"/>
+      <c r="S100" s="8" t="inlineStr"/>
+      <c r="T100" s="8" t="inlineStr"/>
+      <c r="U100" s="8" t="inlineStr"/>
+      <c r="V100" s="8" t="inlineStr"/>
+      <c r="W100" s="8" t="inlineStr"/>
+      <c r="X100" s="8" t="inlineStr"/>
+      <c r="Y100" s="8" t="inlineStr"/>
+      <c r="Z100" s="8" t="inlineStr">
+        <is>
+          <t>6587.00</t>
+        </is>
+      </c>
+      <c r="AA100" s="8" t="inlineStr"/>
+      <c r="AB100" s="10" t="inlineStr"/>
+      <c r="AC100" s="11" t="inlineStr"/>
+      <c r="AD100" s="12" t="inlineStr"/>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr"/>
       <c r="D101" s="8" t="inlineStr"/>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>26460.00</t>
+          <t>6576.50</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr"/>
@@ -6295,85 +6774,123 @@
       <c r="H101" s="8" t="inlineStr"/>
       <c r="I101" s="8" t="inlineStr"/>
       <c r="J101" s="8" t="inlineStr"/>
-      <c r="K101" s="8" t="inlineStr">
-        <is>
-          <t>23815.00</t>
-        </is>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
-        <is>
-          <t>20895.00</t>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>5279.50</t>
+        </is>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>5889.50</t>
         </is>
       </c>
       <c r="M101" s="8" t="inlineStr"/>
       <c r="N101" s="8" t="inlineStr"/>
-      <c r="O101" s="8" t="inlineStr"/>
-      <c r="P101" s="8" t="inlineStr"/>
-      <c r="Q101" s="8" t="inlineStr"/>
-      <c r="R101" s="8" t="inlineStr"/>
-      <c r="S101" s="8" t="inlineStr"/>
+      <c r="O101" s="8" t="inlineStr">
+        <is>
+          <t>6447.50</t>
+        </is>
+      </c>
+      <c r="P101" s="13" t="inlineStr">
+        <is>
+          <t>5900.50</t>
+        </is>
+      </c>
+      <c r="Q101" s="8" t="inlineStr">
+        <is>
+          <t>6828.50</t>
+        </is>
+      </c>
+      <c r="R101" s="13" t="inlineStr">
+        <is>
+          <t>5596.50</t>
+        </is>
+      </c>
+      <c r="S101" s="15" t="inlineStr">
+        <is>
+          <t>6424.00</t>
+        </is>
+      </c>
       <c r="T101" s="8" t="inlineStr"/>
       <c r="U101" s="8" t="inlineStr"/>
       <c r="V101" s="8" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr"/>
       <c r="X101" s="8" t="inlineStr"/>
       <c r="Y101" s="8" t="inlineStr"/>
-      <c r="Z101" s="10" t="n">
-        <v>25137.5</v>
-      </c>
-      <c r="AA101" s="11" t="inlineStr"/>
-      <c r="AB101" s="12" t="inlineStr"/>
+      <c r="Z101" s="8" t="inlineStr">
+        <is>
+          <t>6796.50</t>
+        </is>
+      </c>
+      <c r="AA101" s="8" t="inlineStr"/>
+      <c r="AB101" s="10" t="n">
+        <v>6662.25</v>
+      </c>
+      <c r="AC101" s="10" t="n">
+        <v>832.625</v>
+      </c>
+      <c r="AD101" s="12" t="n">
+        <v>0.779976580796253</v>
+      </c>
     </row>
     <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="1" t="n"/>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr"/>
-      <c r="D102" s="8" t="inlineStr"/>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>16365.00</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr"/>
-      <c r="G102" s="8" t="inlineStr"/>
-      <c r="H102" s="8" t="inlineStr"/>
-      <c r="I102" s="8" t="inlineStr"/>
-      <c r="J102" s="8" t="inlineStr"/>
-      <c r="K102" s="8" t="inlineStr"/>
-      <c r="L102" s="8" t="inlineStr"/>
-      <c r="M102" s="8" t="inlineStr"/>
-      <c r="N102" s="8" t="inlineStr"/>
-      <c r="O102" s="8" t="inlineStr"/>
-      <c r="P102" s="8" t="inlineStr"/>
-      <c r="Q102" s="8" t="inlineStr"/>
-      <c r="R102" s="8" t="inlineStr"/>
-      <c r="S102" s="8" t="inlineStr"/>
-      <c r="T102" s="8" t="inlineStr"/>
-      <c r="U102" s="8" t="inlineStr"/>
-      <c r="V102" s="8" t="inlineStr"/>
-      <c r="W102" s="8" t="inlineStr"/>
-      <c r="X102" s="8" t="inlineStr"/>
-      <c r="Y102" s="8" t="inlineStr"/>
-      <c r="Z102" s="10" t="inlineStr"/>
-      <c r="AA102" s="11" t="inlineStr"/>
-      <c r="AB102" s="12" t="inlineStr"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>KungFuMaster
+Random: 258.5
+Human: 22736.3</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 26182</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr"/>
+      <c r="D102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr"/>
+      <c r="J102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr"/>
+      <c r="L102" s="4" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr"/>
+      <c r="P102" s="4" t="inlineStr"/>
+      <c r="Q102" s="4" t="inlineStr"/>
+      <c r="R102" s="4" t="inlineStr"/>
+      <c r="S102" s="4" t="inlineStr"/>
+      <c r="T102" s="4" t="inlineStr"/>
+      <c r="U102" s="4" t="inlineStr"/>
+      <c r="V102" s="4" t="inlineStr"/>
+      <c r="W102" s="4" t="inlineStr"/>
+      <c r="X102" s="4" t="inlineStr"/>
+      <c r="Y102" s="4" t="inlineStr"/>
+      <c r="Z102" s="4" t="inlineStr"/>
+      <c r="AA102" s="4" t="inlineStr"/>
+      <c r="AB102" s="5" t="inlineStr"/>
+      <c r="AC102" s="6" t="n">
+        <v>-1044.5</v>
+      </c>
+      <c r="AD102" s="7" t="n">
+        <v>-0.04646807071866464</v>
+      </c>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr"/>
       <c r="D103" s="8" t="inlineStr"/>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>30110.00</t>
+          <t>26460.00</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr"/>
@@ -6383,10 +6900,14 @@
       <c r="J103" s="8" t="inlineStr"/>
       <c r="K103" s="8" t="inlineStr">
         <is>
-          <t>20245.00</t>
-        </is>
-      </c>
-      <c r="L103" s="8" t="inlineStr"/>
+          <t>23815.00</t>
+        </is>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>20895.00</t>
+        </is>
+      </c>
       <c r="M103" s="8" t="inlineStr"/>
       <c r="N103" s="8" t="inlineStr"/>
       <c r="O103" s="8" t="inlineStr"/>
@@ -6400,28 +6921,26 @@
       <c r="W103" s="8" t="inlineStr"/>
       <c r="X103" s="8" t="inlineStr"/>
       <c r="Y103" s="8" t="inlineStr"/>
-      <c r="Z103" s="10" t="n">
-        <v>25177.5</v>
-      </c>
-      <c r="AA103" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB103" s="12" t="n">
-        <v>0.001779533584247569</v>
-      </c>
+      <c r="Z103" s="8" t="inlineStr"/>
+      <c r="AA103" s="8" t="inlineStr"/>
+      <c r="AB103" s="10" t="n">
+        <v>25137.5</v>
+      </c>
+      <c r="AC103" s="11" t="inlineStr"/>
+      <c r="AD103" s="12" t="inlineStr"/>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr"/>
       <c r="D104" s="8" t="inlineStr"/>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>17935.00</t>
+          <t>16365.00</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr"/>
@@ -6444,22 +6963,24 @@
       <c r="W104" s="8" t="inlineStr"/>
       <c r="X104" s="8" t="inlineStr"/>
       <c r="Y104" s="8" t="inlineStr"/>
-      <c r="Z104" s="10" t="inlineStr"/>
-      <c r="AA104" s="11" t="inlineStr"/>
-      <c r="AB104" s="12" t="inlineStr"/>
+      <c r="Z104" s="8" t="inlineStr"/>
+      <c r="AA104" s="8" t="inlineStr"/>
+      <c r="AB104" s="10" t="inlineStr"/>
+      <c r="AC104" s="11" t="inlineStr"/>
+      <c r="AD104" s="12" t="inlineStr"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr"/>
       <c r="D105" s="8" t="inlineStr"/>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>21915.00</t>
+          <t>30110.00</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr"/>
@@ -6467,8 +6988,16 @@
       <c r="H105" s="8" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr"/>
       <c r="J105" s="8" t="inlineStr"/>
-      <c r="K105" s="8" t="inlineStr"/>
-      <c r="L105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr">
+        <is>
+          <t>20245.00</t>
+        </is>
+      </c>
+      <c r="L105" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="M105" s="8" t="inlineStr"/>
       <c r="N105" s="8" t="inlineStr"/>
       <c r="O105" s="8" t="inlineStr"/>
@@ -6482,70 +7011,70 @@
       <c r="W105" s="8" t="inlineStr"/>
       <c r="X105" s="8" t="inlineStr"/>
       <c r="Y105" s="8" t="inlineStr"/>
-      <c r="Z105" s="10" t="inlineStr"/>
-      <c r="AA105" s="11" t="inlineStr"/>
-      <c r="AB105" s="12" t="inlineStr"/>
+      <c r="Z105" s="8" t="inlineStr"/>
+      <c r="AA105" s="8" t="inlineStr"/>
+      <c r="AB105" s="10" t="n">
+        <v>25177.5</v>
+      </c>
+      <c r="AC105" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD105" s="12" t="n">
+        <v>0.001779533584247569</v>
+      </c>
     </row>
     <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>MsPacman
-Random: 307.3
-Human: 6951.6</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 2673</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr"/>
-      <c r="D106" s="4" t="inlineStr"/>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="4" t="inlineStr"/>
-      <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="4" t="inlineStr"/>
-      <c r="J106" s="4" t="inlineStr"/>
-      <c r="K106" s="4" t="inlineStr"/>
-      <c r="L106" s="4" t="inlineStr"/>
-      <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr"/>
-      <c r="O106" s="4" t="inlineStr"/>
-      <c r="P106" s="4" t="inlineStr"/>
-      <c r="Q106" s="4" t="inlineStr"/>
-      <c r="R106" s="4" t="inlineStr"/>
-      <c r="S106" s="4" t="inlineStr"/>
-      <c r="T106" s="4" t="inlineStr"/>
-      <c r="U106" s="4" t="inlineStr"/>
-      <c r="V106" s="4" t="inlineStr"/>
-      <c r="W106" s="4" t="inlineStr"/>
-      <c r="X106" s="4" t="inlineStr"/>
-      <c r="Y106" s="4" t="inlineStr"/>
-      <c r="Z106" s="5" t="inlineStr"/>
-      <c r="AA106" s="6" t="n">
-        <v>-602</v>
-      </c>
-      <c r="AB106" s="7" t="n">
-        <v>-0.09060397634062278</v>
-      </c>
+      <c r="A106" s="1" t="n"/>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr"/>
+      <c r="D106" s="8" t="inlineStr"/>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>17935.00</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr"/>
+      <c r="H106" s="8" t="inlineStr"/>
+      <c r="I106" s="8" t="inlineStr"/>
+      <c r="J106" s="8" t="inlineStr"/>
+      <c r="K106" s="8" t="inlineStr"/>
+      <c r="L106" s="8" t="inlineStr"/>
+      <c r="M106" s="8" t="inlineStr"/>
+      <c r="N106" s="8" t="inlineStr"/>
+      <c r="O106" s="8" t="inlineStr"/>
+      <c r="P106" s="8" t="inlineStr"/>
+      <c r="Q106" s="8" t="inlineStr"/>
+      <c r="R106" s="8" t="inlineStr"/>
+      <c r="S106" s="8" t="inlineStr"/>
+      <c r="T106" s="8" t="inlineStr"/>
+      <c r="U106" s="8" t="inlineStr"/>
+      <c r="V106" s="8" t="inlineStr"/>
+      <c r="W106" s="8" t="inlineStr"/>
+      <c r="X106" s="8" t="inlineStr"/>
+      <c r="Y106" s="8" t="inlineStr"/>
+      <c r="Z106" s="8" t="inlineStr"/>
+      <c r="AA106" s="8" t="inlineStr"/>
+      <c r="AB106" s="10" t="inlineStr"/>
+      <c r="AC106" s="11" t="inlineStr"/>
+      <c r="AD106" s="12" t="inlineStr"/>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>1807.50</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr"/>
       <c r="D107" s="8" t="inlineStr"/>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>2007.00</t>
+          <t>21915.00</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr"/>
@@ -6553,19 +7082,11 @@
       <c r="H107" s="8" t="inlineStr"/>
       <c r="I107" s="8" t="inlineStr"/>
       <c r="J107" s="8" t="inlineStr"/>
-      <c r="K107" s="8" t="inlineStr">
-        <is>
-          <t>2388.00</t>
-        </is>
-      </c>
+      <c r="K107" s="8" t="inlineStr"/>
       <c r="L107" s="8" t="inlineStr"/>
       <c r="M107" s="8" t="inlineStr"/>
       <c r="N107" s="8" t="inlineStr"/>
-      <c r="O107" s="8" t="inlineStr">
-        <is>
-          <t>1754.00</t>
-        </is>
-      </c>
+      <c r="O107" s="8" t="inlineStr"/>
       <c r="P107" s="8" t="inlineStr"/>
       <c r="Q107" s="8" t="inlineStr"/>
       <c r="R107" s="8" t="inlineStr"/>
@@ -6576,60 +7097,76 @@
       <c r="W107" s="8" t="inlineStr"/>
       <c r="X107" s="8" t="inlineStr"/>
       <c r="Y107" s="8" t="inlineStr"/>
-      <c r="Z107" s="10" t="n">
-        <v>2071</v>
-      </c>
-      <c r="AA107" s="11" t="inlineStr"/>
-      <c r="AB107" s="12" t="inlineStr"/>
+      <c r="Z107" s="8" t="inlineStr"/>
+      <c r="AA107" s="8" t="inlineStr"/>
+      <c r="AB107" s="10" t="inlineStr"/>
+      <c r="AC107" s="11" t="inlineStr"/>
+      <c r="AD107" s="12" t="inlineStr"/>
     </row>
     <row r="108" ht="24" customHeight="1">
-      <c r="A108" s="1" t="n"/>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr"/>
-      <c r="D108" s="8" t="inlineStr"/>
-      <c r="E108" s="8" t="inlineStr"/>
-      <c r="F108" s="8" t="inlineStr"/>
-      <c r="G108" s="8" t="inlineStr"/>
-      <c r="H108" s="8" t="inlineStr"/>
-      <c r="I108" s="8" t="inlineStr"/>
-      <c r="J108" s="8" t="inlineStr"/>
-      <c r="K108" s="8" t="inlineStr"/>
-      <c r="L108" s="8" t="inlineStr"/>
-      <c r="M108" s="8" t="inlineStr"/>
-      <c r="N108" s="8" t="inlineStr"/>
-      <c r="O108" s="8" t="inlineStr">
-        <is>
-          <t>2110.50</t>
-        </is>
-      </c>
-      <c r="P108" s="8" t="inlineStr"/>
-      <c r="Q108" s="8" t="inlineStr"/>
-      <c r="R108" s="8" t="inlineStr"/>
-      <c r="S108" s="8" t="inlineStr"/>
-      <c r="T108" s="8" t="inlineStr"/>
-      <c r="U108" s="8" t="inlineStr"/>
-      <c r="V108" s="8" t="inlineStr"/>
-      <c r="W108" s="8" t="inlineStr"/>
-      <c r="X108" s="8" t="inlineStr"/>
-      <c r="Y108" s="8" t="inlineStr"/>
-      <c r="Z108" s="10" t="inlineStr"/>
-      <c r="AA108" s="11" t="inlineStr"/>
-      <c r="AB108" s="12" t="inlineStr"/>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>MsPacman
+Random: 307.3
+Human: 6951.6</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 2673</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr"/>
+      <c r="D108" s="4" t="inlineStr"/>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr"/>
+      <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="inlineStr"/>
+      <c r="N108" s="4" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr"/>
+      <c r="P108" s="4" t="inlineStr"/>
+      <c r="Q108" s="4" t="inlineStr"/>
+      <c r="R108" s="4" t="inlineStr"/>
+      <c r="S108" s="4" t="inlineStr"/>
+      <c r="T108" s="4" t="inlineStr"/>
+      <c r="U108" s="4" t="inlineStr"/>
+      <c r="V108" s="4" t="inlineStr"/>
+      <c r="W108" s="4" t="inlineStr"/>
+      <c r="X108" s="4" t="inlineStr"/>
+      <c r="Y108" s="4" t="inlineStr"/>
+      <c r="Z108" s="4" t="inlineStr"/>
+      <c r="AA108" s="4" t="inlineStr"/>
+      <c r="AB108" s="5" t="inlineStr"/>
+      <c r="AC108" s="6" t="n">
+        <v>-699.3333333333333</v>
+      </c>
+      <c r="AD108" s="7" t="n">
+        <v>-0.1052531242317977</v>
+      </c>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>1807.50</t>
+        </is>
+      </c>
       <c r="D109" s="8" t="inlineStr"/>
-      <c r="E109" s="8" t="inlineStr"/>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>2007.00</t>
+        </is>
+      </c>
       <c r="F109" s="8" t="inlineStr"/>
       <c r="G109" s="8" t="inlineStr"/>
       <c r="H109" s="8" t="inlineStr"/>
@@ -6637,7 +7174,7 @@
       <c r="J109" s="8" t="inlineStr"/>
       <c r="K109" s="8" t="inlineStr">
         <is>
-          <t>2250.00</t>
+          <t>2388.00</t>
         </is>
       </c>
       <c r="L109" s="8" t="inlineStr"/>
@@ -6645,10 +7182,14 @@
       <c r="N109" s="8" t="inlineStr"/>
       <c r="O109" s="8" t="inlineStr">
         <is>
-          <t>1886.50</t>
-        </is>
-      </c>
-      <c r="P109" s="8" t="inlineStr"/>
+          <t>1754.00</t>
+        </is>
+      </c>
+      <c r="P109" s="8" t="inlineStr">
+        <is>
+          <t>1779.00</t>
+        </is>
+      </c>
       <c r="Q109" s="8" t="inlineStr"/>
       <c r="R109" s="8" t="inlineStr"/>
       <c r="S109" s="8" t="inlineStr"/>
@@ -6658,21 +7199,19 @@
       <c r="W109" s="8" t="inlineStr"/>
       <c r="X109" s="8" t="inlineStr"/>
       <c r="Y109" s="8" t="inlineStr"/>
-      <c r="Z109" s="10" t="n">
-        <v>2068.25</v>
-      </c>
-      <c r="AA109" s="10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB109" s="12" t="n">
-        <v>-0.0004138885962403865</v>
-      </c>
+      <c r="Z109" s="8" t="inlineStr"/>
+      <c r="AA109" s="8" t="inlineStr"/>
+      <c r="AB109" s="10" t="n">
+        <v>1973.666666666667</v>
+      </c>
+      <c r="AC109" s="11" t="inlineStr"/>
+      <c r="AD109" s="12" t="inlineStr"/>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr"/>
@@ -6689,14 +7228,10 @@
       <c r="N110" s="8" t="inlineStr"/>
       <c r="O110" s="8" t="inlineStr">
         <is>
-          <t>2197.00</t>
-        </is>
-      </c>
-      <c r="P110" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+          <t>2110.50</t>
+        </is>
+      </c>
+      <c r="P110" s="8" t="inlineStr"/>
       <c r="Q110" s="8" t="inlineStr"/>
       <c r="R110" s="8" t="inlineStr"/>
       <c r="S110" s="8" t="inlineStr"/>
@@ -6706,15 +7241,17 @@
       <c r="W110" s="8" t="inlineStr"/>
       <c r="X110" s="8" t="inlineStr"/>
       <c r="Y110" s="8" t="inlineStr"/>
-      <c r="Z110" s="10" t="inlineStr"/>
-      <c r="AA110" s="11" t="inlineStr"/>
-      <c r="AB110" s="12" t="inlineStr"/>
+      <c r="Z110" s="8" t="inlineStr"/>
+      <c r="AA110" s="8" t="inlineStr"/>
+      <c r="AB110" s="10" t="inlineStr"/>
+      <c r="AC110" s="11" t="inlineStr"/>
+      <c r="AD110" s="12" t="inlineStr"/>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr"/>
@@ -6725,18 +7262,22 @@
       <c r="H111" s="8" t="inlineStr"/>
       <c r="I111" s="8" t="inlineStr"/>
       <c r="J111" s="8" t="inlineStr"/>
-      <c r="K111" s="8" t="inlineStr"/>
+      <c r="K111" s="8" t="inlineStr">
+        <is>
+          <t>2250.00</t>
+        </is>
+      </c>
       <c r="L111" s="8" t="inlineStr"/>
       <c r="M111" s="8" t="inlineStr"/>
       <c r="N111" s="8" t="inlineStr"/>
       <c r="O111" s="8" t="inlineStr">
         <is>
-          <t>2170.00</t>
-        </is>
-      </c>
-      <c r="P111" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+          <t>1886.50</t>
+        </is>
+      </c>
+      <c r="P111" s="8" t="inlineStr">
+        <is>
+          <t>1885.00</t>
         </is>
       </c>
       <c r="Q111" s="8" t="inlineStr"/>
@@ -6748,91 +7289,91 @@
       <c r="W111" s="8" t="inlineStr"/>
       <c r="X111" s="8" t="inlineStr"/>
       <c r="Y111" s="8" t="inlineStr"/>
-      <c r="Z111" s="10" t="inlineStr"/>
-      <c r="AA111" s="11" t="inlineStr"/>
-      <c r="AB111" s="12" t="inlineStr"/>
+      <c r="Z111" s="8" t="inlineStr"/>
+      <c r="AA111" s="8" t="inlineStr"/>
+      <c r="AB111" s="10" t="n">
+        <v>2007.166666666667</v>
+      </c>
+      <c r="AC111" s="10" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="AD111" s="12" t="n">
+        <v>0.005041915626928344</v>
+      </c>
     </row>
     <row r="112" ht="24" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Pong
-Random: -20.7
-Human: 14.6</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 11</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr"/>
-      <c r="D112" s="4" t="inlineStr"/>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="4" t="inlineStr"/>
-      <c r="H112" s="4" t="inlineStr"/>
-      <c r="I112" s="4" t="inlineStr"/>
-      <c r="J112" s="4" t="inlineStr"/>
-      <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="4" t="inlineStr"/>
-      <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr"/>
-      <c r="O112" s="4" t="inlineStr"/>
-      <c r="P112" s="4" t="inlineStr"/>
-      <c r="Q112" s="4" t="inlineStr"/>
-      <c r="R112" s="4" t="inlineStr"/>
-      <c r="S112" s="4" t="inlineStr"/>
-      <c r="T112" s="4" t="inlineStr"/>
-      <c r="U112" s="4" t="inlineStr"/>
-      <c r="V112" s="4" t="inlineStr"/>
-      <c r="W112" s="4" t="inlineStr"/>
-      <c r="X112" s="4" t="inlineStr"/>
-      <c r="Y112" s="4" t="inlineStr"/>
-      <c r="Z112" s="5" t="inlineStr"/>
-      <c r="AA112" s="6" t="n">
-        <v>-2.700000000000001</v>
-      </c>
-      <c r="AB112" s="7" t="n">
-        <v>-0.07648725212464592</v>
-      </c>
+      <c r="A112" s="1" t="n"/>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr"/>
+      <c r="D112" s="8" t="inlineStr"/>
+      <c r="E112" s="8" t="inlineStr"/>
+      <c r="F112" s="8" t="inlineStr"/>
+      <c r="G112" s="8" t="inlineStr"/>
+      <c r="H112" s="8" t="inlineStr"/>
+      <c r="I112" s="8" t="inlineStr"/>
+      <c r="J112" s="8" t="inlineStr"/>
+      <c r="K112" s="8" t="inlineStr"/>
+      <c r="L112" s="8" t="inlineStr"/>
+      <c r="M112" s="8" t="inlineStr"/>
+      <c r="N112" s="8" t="inlineStr"/>
+      <c r="O112" s="8" t="inlineStr">
+        <is>
+          <t>2197.00</t>
+        </is>
+      </c>
+      <c r="P112" s="8" t="inlineStr">
+        <is>
+          <t>2647.50</t>
+        </is>
+      </c>
+      <c r="Q112" s="8" t="inlineStr"/>
+      <c r="R112" s="8" t="inlineStr"/>
+      <c r="S112" s="8" t="inlineStr"/>
+      <c r="T112" s="8" t="inlineStr"/>
+      <c r="U112" s="8" t="inlineStr"/>
+      <c r="V112" s="8" t="inlineStr"/>
+      <c r="W112" s="8" t="inlineStr"/>
+      <c r="X112" s="8" t="inlineStr"/>
+      <c r="Y112" s="8" t="inlineStr"/>
+      <c r="Z112" s="8" t="inlineStr"/>
+      <c r="AA112" s="8" t="inlineStr"/>
+      <c r="AB112" s="10" t="inlineStr"/>
+      <c r="AC112" s="11" t="inlineStr"/>
+      <c r="AD112" s="12" t="inlineStr"/>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
+          <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="8" t="inlineStr"/>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
+      <c r="E113" s="8" t="inlineStr"/>
+      <c r="F113" s="8" t="inlineStr"/>
       <c r="G113" s="8" t="inlineStr"/>
       <c r="H113" s="8" t="inlineStr"/>
       <c r="I113" s="8" t="inlineStr"/>
       <c r="J113" s="8" t="inlineStr"/>
-      <c r="K113" s="8" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
-      <c r="L113" s="8" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
+      <c r="K113" s="8" t="inlineStr"/>
+      <c r="L113" s="8" t="inlineStr"/>
       <c r="M113" s="8" t="inlineStr"/>
       <c r="N113" s="8" t="inlineStr"/>
-      <c r="O113" s="8" t="inlineStr"/>
-      <c r="P113" s="8" t="inlineStr"/>
+      <c r="O113" s="8" t="inlineStr">
+        <is>
+          <t>2170.00</t>
+        </is>
+      </c>
+      <c r="P113" s="8" t="inlineStr">
+        <is>
+          <t>2577.50</t>
+        </is>
+      </c>
       <c r="Q113" s="8" t="inlineStr"/>
       <c r="R113" s="8" t="inlineStr"/>
       <c r="S113" s="8" t="inlineStr"/>
@@ -6842,91 +7383,89 @@
       <c r="W113" s="8" t="inlineStr"/>
       <c r="X113" s="8" t="inlineStr"/>
       <c r="Y113" s="8" t="inlineStr"/>
-      <c r="Z113" s="10" t="n">
-        <v>8.299999999999999</v>
-      </c>
-      <c r="AA113" s="11" t="inlineStr"/>
-      <c r="AB113" s="12" t="inlineStr"/>
+      <c r="Z113" s="8" t="inlineStr"/>
+      <c r="AA113" s="8" t="inlineStr"/>
+      <c r="AB113" s="10" t="inlineStr"/>
+      <c r="AC113" s="11" t="inlineStr"/>
+      <c r="AD113" s="12" t="inlineStr"/>
     </row>
     <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="1" t="n"/>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr"/>
-      <c r="D114" s="8" t="inlineStr"/>
-      <c r="E114" s="8" t="inlineStr"/>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>8.20</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr"/>
-      <c r="H114" s="8" t="inlineStr"/>
-      <c r="I114" s="8" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="J114" s="8" t="inlineStr"/>
-      <c r="K114" s="8" t="inlineStr">
-        <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="L114" s="8" t="inlineStr">
-        <is>
-          <t>-19.90</t>
-        </is>
-      </c>
-      <c r="M114" s="8" t="inlineStr"/>
-      <c r="N114" s="8" t="inlineStr"/>
-      <c r="O114" s="8" t="inlineStr"/>
-      <c r="P114" s="8" t="inlineStr"/>
-      <c r="Q114" s="8" t="inlineStr"/>
-      <c r="R114" s="8" t="inlineStr"/>
-      <c r="S114" s="8" t="inlineStr"/>
-      <c r="T114" s="8" t="inlineStr"/>
-      <c r="U114" s="8" t="inlineStr"/>
-      <c r="V114" s="8" t="inlineStr"/>
-      <c r="W114" s="8" t="inlineStr"/>
-      <c r="X114" s="16" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="Y114" s="8" t="inlineStr"/>
-      <c r="Z114" s="10" t="n">
-        <v>-0.6333333333333329</v>
-      </c>
-      <c r="AA114" s="10" t="n">
-        <v>8.933333333333332</v>
-      </c>
-      <c r="AB114" s="12" t="n">
-        <v>-0.2530689329556185</v>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Pong
+Random: -20.7
+Human: 14.6</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 11</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr"/>
+      <c r="D114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr"/>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr"/>
+      <c r="K114" s="4" t="inlineStr"/>
+      <c r="L114" s="4" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr"/>
+      <c r="N114" s="4" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr"/>
+      <c r="P114" s="4" t="inlineStr"/>
+      <c r="Q114" s="4" t="inlineStr"/>
+      <c r="R114" s="4" t="inlineStr"/>
+      <c r="S114" s="4" t="inlineStr"/>
+      <c r="T114" s="4" t="inlineStr"/>
+      <c r="U114" s="4" t="inlineStr"/>
+      <c r="V114" s="4" t="inlineStr"/>
+      <c r="W114" s="4" t="inlineStr"/>
+      <c r="X114" s="4" t="inlineStr"/>
+      <c r="Y114" s="4" t="inlineStr"/>
+      <c r="Z114" s="4" t="inlineStr"/>
+      <c r="AA114" s="4" t="inlineStr"/>
+      <c r="AB114" s="5" t="inlineStr"/>
+      <c r="AC114" s="6" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AD114" s="7" t="n">
+        <v>-0.1529745042492918</v>
       </c>
     </row>
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr"/>
       <c r="D115" s="8" t="inlineStr"/>
-      <c r="E115" s="8" t="inlineStr"/>
-      <c r="F115" s="8" t="inlineStr"/>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
       <c r="G115" s="8" t="inlineStr"/>
       <c r="H115" s="8" t="inlineStr"/>
       <c r="I115" s="8" t="inlineStr"/>
       <c r="J115" s="8" t="inlineStr"/>
-      <c r="K115" s="8" t="inlineStr"/>
-      <c r="L115" s="8" t="inlineStr">
-        <is>
-          <t>-20.40</t>
+      <c r="K115" s="8" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>13.70</t>
         </is>
       </c>
       <c r="M115" s="8" t="inlineStr"/>
@@ -6942,29 +7481,45 @@
       <c r="W115" s="8" t="inlineStr"/>
       <c r="X115" s="8" t="inlineStr"/>
       <c r="Y115" s="8" t="inlineStr"/>
-      <c r="Z115" s="10" t="inlineStr"/>
-      <c r="AA115" s="11" t="inlineStr"/>
-      <c r="AB115" s="12" t="inlineStr"/>
+      <c r="Z115" s="8" t="inlineStr"/>
+      <c r="AA115" s="8" t="inlineStr"/>
+      <c r="AB115" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC115" s="11" t="inlineStr"/>
+      <c r="AD115" s="12" t="inlineStr"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr"/>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr"/>
-      <c r="F116" s="8" t="inlineStr"/>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>8.20</t>
+        </is>
+      </c>
       <c r="G116" s="8" t="inlineStr"/>
       <c r="H116" s="8" t="inlineStr"/>
-      <c r="I116" s="8" t="inlineStr"/>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
       <c r="J116" s="8" t="inlineStr"/>
-      <c r="K116" s="8" t="inlineStr"/>
-      <c r="L116" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="K116" s="8" t="inlineStr">
+        <is>
+          <t>9.80</t>
+        </is>
+      </c>
+      <c r="L116" s="9" t="inlineStr">
+        <is>
+          <t>-19.90</t>
         </is>
       </c>
       <c r="M116" s="8" t="inlineStr"/>
@@ -6980,122 +7535,120 @@
       <c r="W116" s="8" t="inlineStr"/>
       <c r="X116" s="8" t="inlineStr"/>
       <c r="Y116" s="8" t="inlineStr"/>
-      <c r="Z116" s="10" t="inlineStr"/>
-      <c r="AA116" s="11" t="inlineStr"/>
-      <c r="AB116" s="12" t="inlineStr"/>
+      <c r="Z116" s="15" t="inlineStr">
+        <is>
+          <t>16.30</t>
+        </is>
+      </c>
+      <c r="AA116" s="8" t="inlineStr"/>
+      <c r="AB116" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC116" s="10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD116" s="12" t="n">
+        <v>0.09631728045325781</v>
+      </c>
     </row>
     <row r="117" ht="24" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" s="1" t="n"/>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr"/>
+      <c r="D117" s="8" t="inlineStr"/>
+      <c r="E117" s="8" t="inlineStr"/>
+      <c r="F117" s="8" t="inlineStr"/>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr"/>
+      <c r="J117" s="8" t="inlineStr"/>
+      <c r="K117" s="8" t="inlineStr"/>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>-20.40</t>
+        </is>
+      </c>
+      <c r="M117" s="8" t="inlineStr"/>
+      <c r="N117" s="8" t="inlineStr"/>
+      <c r="O117" s="8" t="inlineStr"/>
+      <c r="P117" s="8" t="inlineStr"/>
+      <c r="Q117" s="8" t="inlineStr"/>
+      <c r="R117" s="8" t="inlineStr"/>
+      <c r="S117" s="8" t="inlineStr"/>
+      <c r="T117" s="8" t="inlineStr"/>
+      <c r="U117" s="8" t="inlineStr"/>
+      <c r="V117" s="8" t="inlineStr"/>
+      <c r="W117" s="8" t="inlineStr"/>
+      <c r="X117" s="8" t="inlineStr"/>
+      <c r="Y117" s="8" t="inlineStr"/>
+      <c r="Z117" s="8" t="inlineStr"/>
+      <c r="AA117" s="8" t="inlineStr"/>
+      <c r="AB117" s="10" t="inlineStr"/>
+      <c r="AC117" s="11" t="inlineStr"/>
+      <c r="AD117" s="12" t="inlineStr"/>
+    </row>
+    <row r="118" ht="24" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>PrivateEye
 Random: 24.9
 Human: 69571.3</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 7781</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr"/>
-      <c r="D117" s="4" t="inlineStr"/>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr"/>
-      <c r="H117" s="4" t="inlineStr"/>
-      <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr"/>
-      <c r="K117" s="4" t="inlineStr"/>
-      <c r="L117" s="4" t="inlineStr"/>
-      <c r="M117" s="4" t="inlineStr"/>
-      <c r="N117" s="4" t="inlineStr"/>
-      <c r="O117" s="4" t="inlineStr"/>
-      <c r="P117" s="4" t="inlineStr"/>
-      <c r="Q117" s="4" t="inlineStr"/>
-      <c r="R117" s="4" t="inlineStr"/>
-      <c r="S117" s="4" t="inlineStr"/>
-      <c r="T117" s="4" t="inlineStr"/>
-      <c r="U117" s="4" t="inlineStr"/>
-      <c r="V117" s="4" t="inlineStr"/>
-      <c r="W117" s="4" t="inlineStr"/>
-      <c r="X117" s="4" t="inlineStr"/>
-      <c r="Y117" s="4" t="inlineStr"/>
-      <c r="Z117" s="5" t="inlineStr"/>
-      <c r="AA117" s="6" t="n">
+      <c r="C118" s="4" t="inlineStr"/>
+      <c r="D118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr"/>
+      <c r="L118" s="4" t="inlineStr"/>
+      <c r="M118" s="4" t="inlineStr"/>
+      <c r="N118" s="4" t="inlineStr"/>
+      <c r="O118" s="4" t="inlineStr"/>
+      <c r="P118" s="4" t="inlineStr"/>
+      <c r="Q118" s="4" t="inlineStr"/>
+      <c r="R118" s="4" t="inlineStr"/>
+      <c r="S118" s="4" t="inlineStr"/>
+      <c r="T118" s="4" t="inlineStr"/>
+      <c r="U118" s="4" t="inlineStr"/>
+      <c r="V118" s="4" t="inlineStr"/>
+      <c r="W118" s="4" t="inlineStr"/>
+      <c r="X118" s="4" t="inlineStr"/>
+      <c r="Y118" s="4" t="inlineStr"/>
+      <c r="Z118" s="4" t="inlineStr"/>
+      <c r="AA118" s="4" t="inlineStr"/>
+      <c r="AB118" s="5" t="inlineStr"/>
+      <c r="AC118" s="6" t="n">
         <v>-6778.35</v>
       </c>
-      <c r="AB117" s="7" t="n">
+      <c r="AD118" s="7" t="n">
         <v>-0.09746514557187719</v>
       </c>
-    </row>
-    <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="1" t="n"/>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>75.30</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr"/>
-      <c r="E118" s="8" t="inlineStr"/>
-      <c r="F118" s="8" t="inlineStr"/>
-      <c r="G118" s="8" t="inlineStr"/>
-      <c r="H118" s="8" t="inlineStr"/>
-      <c r="I118" s="8" t="inlineStr"/>
-      <c r="J118" s="8" t="inlineStr"/>
-      <c r="K118" s="8" t="inlineStr">
-        <is>
-          <t>199.35</t>
-        </is>
-      </c>
-      <c r="L118" s="8" t="inlineStr"/>
-      <c r="M118" s="8" t="inlineStr"/>
-      <c r="N118" s="8" t="inlineStr"/>
-      <c r="O118" s="9" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="P118" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q118" s="8" t="inlineStr">
-        <is>
-          <t>3551.75</t>
-        </is>
-      </c>
-      <c r="R118" s="9" t="inlineStr"/>
-      <c r="S118" s="8" t="inlineStr"/>
-      <c r="T118" s="8" t="inlineStr"/>
-      <c r="U118" s="8" t="inlineStr"/>
-      <c r="V118" s="8" t="inlineStr"/>
-      <c r="W118" s="8" t="inlineStr"/>
-      <c r="X118" s="8" t="inlineStr">
-        <is>
-          <t>159.50</t>
-        </is>
-      </c>
-      <c r="Y118" s="8" t="inlineStr"/>
-      <c r="Z118" s="10" t="n">
-        <v>1002.65</v>
-      </c>
-      <c r="AA118" s="11" t="inlineStr"/>
-      <c r="AB118" s="12" t="inlineStr"/>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>75.30</t>
+        </is>
+      </c>
       <c r="D119" s="8" t="inlineStr"/>
       <c r="E119" s="8" t="inlineStr"/>
       <c r="F119" s="8" t="inlineStr"/>
@@ -7105,7 +7658,7 @@
       <c r="J119" s="8" t="inlineStr"/>
       <c r="K119" s="8" t="inlineStr">
         <is>
-          <t>191.95</t>
+          <t>199.35</t>
         </is>
       </c>
       <c r="L119" s="8" t="inlineStr"/>
@@ -7113,7 +7666,7 @@
       <c r="N119" s="8" t="inlineStr"/>
       <c r="O119" s="9" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P119" s="8" t="inlineStr">
@@ -7123,151 +7676,157 @@
       </c>
       <c r="Q119" s="8" t="inlineStr">
         <is>
-          <t>166.80</t>
-        </is>
-      </c>
-      <c r="R119" s="13" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
+          <t>3551.75</t>
+        </is>
+      </c>
+      <c r="R119" s="9" t="inlineStr"/>
       <c r="S119" s="8" t="inlineStr"/>
       <c r="T119" s="8" t="inlineStr"/>
       <c r="U119" s="8" t="inlineStr"/>
       <c r="V119" s="8" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr"/>
-      <c r="X119" s="8" t="inlineStr">
+      <c r="X119" s="8" t="inlineStr"/>
+      <c r="Y119" s="8" t="inlineStr"/>
+      <c r="Z119" s="8" t="inlineStr">
+        <is>
+          <t>159.50</t>
+        </is>
+      </c>
+      <c r="AA119" s="8" t="inlineStr"/>
+      <c r="AB119" s="10" t="n">
+        <v>1002.65</v>
+      </c>
+      <c r="AC119" s="11" t="inlineStr"/>
+      <c r="AD119" s="12" t="inlineStr"/>
+    </row>
+    <row r="120" ht="24" customHeight="1">
+      <c r="A120" s="1" t="n"/>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr"/>
+      <c r="D120" s="8" t="inlineStr"/>
+      <c r="E120" s="8" t="inlineStr"/>
+      <c r="F120" s="8" t="inlineStr"/>
+      <c r="G120" s="8" t="inlineStr"/>
+      <c r="H120" s="8" t="inlineStr"/>
+      <c r="I120" s="8" t="inlineStr"/>
+      <c r="J120" s="8" t="inlineStr"/>
+      <c r="K120" s="8" t="inlineStr">
+        <is>
+          <t>191.95</t>
+        </is>
+      </c>
+      <c r="L120" s="8" t="inlineStr"/>
+      <c r="M120" s="8" t="inlineStr"/>
+      <c r="N120" s="8" t="inlineStr"/>
+      <c r="O120" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="P120" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q120" s="8" t="inlineStr">
+        <is>
+          <t>166.80</t>
+        </is>
+      </c>
+      <c r="R120" s="13" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="S120" s="8" t="inlineStr"/>
+      <c r="T120" s="8" t="inlineStr"/>
+      <c r="U120" s="8" t="inlineStr"/>
+      <c r="V120" s="8" t="inlineStr"/>
+      <c r="W120" s="8" t="inlineStr"/>
+      <c r="X120" s="8" t="inlineStr"/>
+      <c r="Y120" s="8" t="inlineStr"/>
+      <c r="Z120" s="8" t="inlineStr">
         <is>
           <t>153.20</t>
         </is>
       </c>
-      <c r="Y119" s="8" t="inlineStr"/>
-      <c r="Z119" s="10" t="n">
+      <c r="AA120" s="8" t="inlineStr"/>
+      <c r="AB120" s="10" t="n">
         <v>152.9875</v>
       </c>
-      <c r="AA119" s="10" t="n">
+      <c r="AC120" s="10" t="n">
         <v>849.6624999999999</v>
       </c>
-      <c r="AB119" s="12" t="n">
+      <c r="AD120" s="12" t="n">
         <v>-0.01221720319096315</v>
       </c>
     </row>
-    <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121" ht="24" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Qbert
 Random: 163.9
 Human: 13455.0</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 4522</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr"/>
-      <c r="D120" s="4" t="inlineStr"/>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="4" t="inlineStr"/>
-      <c r="H120" s="4" t="inlineStr"/>
-      <c r="I120" s="4" t="inlineStr"/>
-      <c r="J120" s="4" t="inlineStr"/>
-      <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="4" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr"/>
-      <c r="O120" s="4" t="inlineStr"/>
-      <c r="P120" s="4" t="inlineStr"/>
-      <c r="Q120" s="4" t="inlineStr"/>
-      <c r="R120" s="4" t="inlineStr"/>
-      <c r="S120" s="4" t="inlineStr"/>
-      <c r="T120" s="4" t="inlineStr"/>
-      <c r="U120" s="4" t="inlineStr"/>
-      <c r="V120" s="4" t="inlineStr"/>
-      <c r="W120" s="4" t="inlineStr"/>
-      <c r="X120" s="4" t="inlineStr"/>
-      <c r="Y120" s="4" t="inlineStr"/>
-      <c r="Z120" s="5" t="inlineStr"/>
-      <c r="AA120" s="6" t="n">
+      <c r="C121" s="4" t="inlineStr"/>
+      <c r="D121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
+      <c r="G121" s="4" t="inlineStr"/>
+      <c r="H121" s="4" t="inlineStr"/>
+      <c r="I121" s="4" t="inlineStr"/>
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr"/>
+      <c r="L121" s="4" t="inlineStr"/>
+      <c r="M121" s="4" t="inlineStr"/>
+      <c r="N121" s="4" t="inlineStr"/>
+      <c r="O121" s="4" t="inlineStr"/>
+      <c r="P121" s="4" t="inlineStr"/>
+      <c r="Q121" s="4" t="inlineStr"/>
+      <c r="R121" s="4" t="inlineStr"/>
+      <c r="S121" s="4" t="inlineStr"/>
+      <c r="T121" s="4" t="inlineStr"/>
+      <c r="U121" s="4" t="inlineStr"/>
+      <c r="V121" s="4" t="inlineStr"/>
+      <c r="W121" s="4" t="inlineStr"/>
+      <c r="X121" s="4" t="inlineStr"/>
+      <c r="Y121" s="4" t="inlineStr"/>
+      <c r="Z121" s="4" t="inlineStr"/>
+      <c r="AA121" s="4" t="inlineStr"/>
+      <c r="AB121" s="5" t="inlineStr"/>
+      <c r="AC121" s="6" t="n">
         <v>-1662.9375</v>
       </c>
-      <c r="AB120" s="7" t="n">
+      <c r="AD121" s="7" t="n">
         <v>-0.1251166193919239</v>
       </c>
-    </row>
-    <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="1" t="n"/>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="inlineStr"/>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
-      <c r="F121" s="8" t="inlineStr"/>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="8" t="inlineStr"/>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
-      <c r="J121" s="8" t="inlineStr"/>
-      <c r="K121" s="8" t="inlineStr">
-        <is>
-          <t>3193.75</t>
-        </is>
-      </c>
-      <c r="L121" s="8" t="inlineStr"/>
-      <c r="M121" s="8" t="inlineStr"/>
-      <c r="N121" s="8" t="inlineStr"/>
-      <c r="O121" s="8" t="inlineStr">
-        <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="P121" s="8" t="inlineStr"/>
-      <c r="Q121" s="8" t="inlineStr"/>
-      <c r="R121" s="9" t="inlineStr"/>
-      <c r="S121" s="8" t="inlineStr"/>
-      <c r="T121" s="8" t="inlineStr"/>
-      <c r="U121" s="8" t="inlineStr"/>
-      <c r="V121" s="8" t="inlineStr"/>
-      <c r="W121" s="8" t="inlineStr"/>
-      <c r="X121" s="8" t="inlineStr"/>
-      <c r="Y121" s="8" t="inlineStr"/>
-      <c r="Z121" s="10" t="n">
-        <v>2859.0625</v>
-      </c>
-      <c r="AA121" s="11" t="inlineStr"/>
-      <c r="AB121" s="12" t="inlineStr"/>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>2818.75</t>
+          <t>1771.25</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr"/>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>1918.75</t>
+          <t>3786.25</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr"/>
@@ -7275,17 +7834,21 @@
       <c r="H122" s="8" t="inlineStr"/>
       <c r="I122" s="9" t="inlineStr">
         <is>
-          <t>2553.75</t>
+          <t>2940.00</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr"/>
-      <c r="K122" s="8" t="inlineStr"/>
+      <c r="K122" s="8" t="inlineStr">
+        <is>
+          <t>3193.75</t>
+        </is>
+      </c>
       <c r="L122" s="8" t="inlineStr"/>
       <c r="M122" s="8" t="inlineStr"/>
       <c r="N122" s="8" t="inlineStr"/>
       <c r="O122" s="8" t="inlineStr">
         <is>
-          <t>3782.50</t>
+          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
         </is>
       </c>
       <c r="P122" s="8" t="inlineStr"/>
@@ -7298,26 +7861,30 @@
       <c r="W122" s="8" t="inlineStr"/>
       <c r="X122" s="8" t="inlineStr"/>
       <c r="Y122" s="8" t="inlineStr"/>
-      <c r="Z122" s="10" t="inlineStr"/>
-      <c r="AA122" s="11" t="inlineStr"/>
-      <c r="AB122" s="12" t="inlineStr"/>
+      <c r="Z122" s="8" t="inlineStr"/>
+      <c r="AA122" s="8" t="inlineStr"/>
+      <c r="AB122" s="10" t="n">
+        <v>2859.0625</v>
+      </c>
+      <c r="AC122" s="11" t="inlineStr"/>
+      <c r="AD122" s="12" t="inlineStr"/>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>2702.50</t>
+          <t>2818.75</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>4056.25</t>
+          <t>1918.75</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr"/>
@@ -7325,30 +7892,22 @@
       <c r="H123" s="8" t="inlineStr"/>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>2338.75</t>
+          <t>2553.75</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr"/>
-      <c r="K123" s="8" t="inlineStr">
-        <is>
-          <t>2608.75</t>
-        </is>
-      </c>
+      <c r="K123" s="8" t="inlineStr"/>
       <c r="L123" s="8" t="inlineStr"/>
       <c r="M123" s="8" t="inlineStr"/>
       <c r="N123" s="8" t="inlineStr"/>
       <c r="O123" s="8" t="inlineStr">
         <is>
-          <t>2895.00</t>
+          <t>3782.50</t>
         </is>
       </c>
       <c r="P123" s="8" t="inlineStr"/>
       <c r="Q123" s="8" t="inlineStr"/>
-      <c r="R123" s="13" t="inlineStr">
-        <is>
-          <t>833.75, 683.75</t>
-        </is>
-      </c>
+      <c r="R123" s="9" t="inlineStr"/>
       <c r="S123" s="8" t="inlineStr"/>
       <c r="T123" s="8" t="inlineStr"/>
       <c r="U123" s="8" t="inlineStr"/>
@@ -7356,117 +7915,129 @@
       <c r="W123" s="8" t="inlineStr"/>
       <c r="X123" s="8" t="inlineStr"/>
       <c r="Y123" s="8" t="inlineStr"/>
-      <c r="Z123" s="10" t="n">
+      <c r="Z123" s="8" t="inlineStr"/>
+      <c r="AA123" s="8" t="inlineStr"/>
+      <c r="AB123" s="10" t="inlineStr"/>
+      <c r="AC123" s="11" t="inlineStr"/>
+      <c r="AD123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124" ht="24" customHeight="1">
+      <c r="A124" s="1" t="n"/>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>2702.50</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr"/>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>4056.25</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="inlineStr"/>
+      <c r="G124" s="8" t="inlineStr"/>
+      <c r="H124" s="8" t="inlineStr"/>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>2338.75</t>
+        </is>
+      </c>
+      <c r="J124" s="8" t="inlineStr"/>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>2608.75</t>
+        </is>
+      </c>
+      <c r="L124" s="8" t="inlineStr"/>
+      <c r="M124" s="8" t="inlineStr"/>
+      <c r="N124" s="8" t="inlineStr"/>
+      <c r="O124" s="8" t="inlineStr">
+        <is>
+          <t>2895.00</t>
+        </is>
+      </c>
+      <c r="P124" s="8" t="inlineStr"/>
+      <c r="Q124" s="8" t="inlineStr"/>
+      <c r="R124" s="13" t="inlineStr">
+        <is>
+          <t>833.75, 683.75</t>
+        </is>
+      </c>
+      <c r="S124" s="8" t="inlineStr"/>
+      <c r="T124" s="8" t="inlineStr"/>
+      <c r="U124" s="8" t="inlineStr"/>
+      <c r="V124" s="8" t="inlineStr"/>
+      <c r="W124" s="8" t="inlineStr"/>
+      <c r="X124" s="8" t="inlineStr"/>
+      <c r="Y124" s="8" t="inlineStr"/>
+      <c r="Z124" s="8" t="inlineStr"/>
+      <c r="AA124" s="8" t="inlineStr"/>
+      <c r="AB124" s="10" t="n">
         <v>3065.625</v>
       </c>
-      <c r="AA123" s="10" t="n">
+      <c r="AC124" s="10" t="n">
         <v>206.5625</v>
       </c>
-      <c r="AB123" s="12" t="n">
+      <c r="AD124" s="12" t="n">
         <v>0.01554141493179646</v>
       </c>
     </row>
-    <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125" ht="24" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>RoadRunner
 Random: 11.5
 Human: 7845.0</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 17564</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr"/>
-      <c r="D124" s="4" t="inlineStr"/>
-      <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr"/>
-      <c r="G124" s="4" t="inlineStr"/>
-      <c r="H124" s="4" t="inlineStr"/>
-      <c r="I124" s="4" t="inlineStr"/>
-      <c r="J124" s="4" t="inlineStr"/>
-      <c r="K124" s="4" t="inlineStr"/>
-      <c r="L124" s="4" t="inlineStr"/>
-      <c r="M124" s="4" t="inlineStr"/>
-      <c r="N124" s="4" t="inlineStr"/>
-      <c r="O124" s="4" t="inlineStr"/>
-      <c r="P124" s="4" t="inlineStr"/>
-      <c r="Q124" s="4" t="inlineStr"/>
-      <c r="R124" s="4" t="inlineStr"/>
-      <c r="S124" s="4" t="inlineStr"/>
-      <c r="T124" s="4" t="inlineStr"/>
-      <c r="U124" s="4" t="inlineStr"/>
-      <c r="V124" s="4" t="inlineStr"/>
-      <c r="W124" s="4" t="inlineStr"/>
-      <c r="X124" s="4" t="inlineStr"/>
-      <c r="Y124" s="4" t="inlineStr"/>
-      <c r="Z124" s="5" t="inlineStr"/>
-      <c r="AA124" s="6" t="n">
-        <v>-8519</v>
-      </c>
-      <c r="AB124" s="7" t="n">
-        <v>-1.087508776409013</v>
-      </c>
-    </row>
-    <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="1" t="n"/>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr"/>
-      <c r="D125" s="8" t="inlineStr"/>
-      <c r="E125" s="8" t="inlineStr"/>
-      <c r="F125" s="8" t="inlineStr"/>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="8" t="inlineStr"/>
-      <c r="I125" s="8" t="inlineStr"/>
-      <c r="J125" s="8" t="inlineStr"/>
-      <c r="K125" s="9" t="inlineStr">
-        <is>
-          <t>8610.00</t>
-        </is>
-      </c>
-      <c r="L125" s="8" t="inlineStr"/>
-      <c r="M125" s="8" t="inlineStr"/>
-      <c r="N125" s="8" t="inlineStr"/>
-      <c r="O125" s="8" t="inlineStr">
-        <is>
-          <t>7290.00</t>
-        </is>
-      </c>
-      <c r="P125" s="8" t="inlineStr">
-        <is>
-          <t>9690.00</t>
-        </is>
-      </c>
-      <c r="Q125" s="8" t="inlineStr">
-        <is>
-          <t>10155.00</t>
-        </is>
-      </c>
-      <c r="R125" s="8" t="inlineStr"/>
-      <c r="S125" s="8" t="inlineStr"/>
-      <c r="T125" s="8" t="inlineStr"/>
-      <c r="U125" s="8" t="inlineStr"/>
-      <c r="V125" s="8" t="inlineStr"/>
-      <c r="W125" s="8" t="inlineStr"/>
-      <c r="X125" s="8" t="inlineStr"/>
-      <c r="Y125" s="8" t="inlineStr"/>
-      <c r="Z125" s="10" t="n">
-        <v>9045</v>
-      </c>
-      <c r="AA125" s="11" t="inlineStr"/>
-      <c r="AB125" s="12" t="inlineStr"/>
+      <c r="C125" s="4" t="inlineStr"/>
+      <c r="D125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
+      <c r="G125" s="4" t="inlineStr"/>
+      <c r="H125" s="4" t="inlineStr"/>
+      <c r="I125" s="4" t="inlineStr"/>
+      <c r="J125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr"/>
+      <c r="L125" s="4" t="inlineStr"/>
+      <c r="M125" s="4" t="inlineStr"/>
+      <c r="N125" s="4" t="inlineStr"/>
+      <c r="O125" s="4" t="inlineStr"/>
+      <c r="P125" s="4" t="inlineStr"/>
+      <c r="Q125" s="4" t="inlineStr"/>
+      <c r="R125" s="4" t="inlineStr"/>
+      <c r="S125" s="4" t="inlineStr"/>
+      <c r="T125" s="4" t="inlineStr"/>
+      <c r="U125" s="4" t="inlineStr"/>
+      <c r="V125" s="4" t="inlineStr"/>
+      <c r="W125" s="4" t="inlineStr"/>
+      <c r="X125" s="4" t="inlineStr"/>
+      <c r="Y125" s="4" t="inlineStr"/>
+      <c r="Z125" s="4" t="inlineStr"/>
+      <c r="AA125" s="4" t="inlineStr"/>
+      <c r="AB125" s="5" t="inlineStr"/>
+      <c r="AC125" s="6" t="n">
+        <v>-5012.333333333334</v>
+      </c>
+      <c r="AD125" s="7" t="n">
+        <v>-0.6398587264100765</v>
+      </c>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="1" t="n"/>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr"/>
@@ -7477,26 +8048,34 @@
       <c r="H126" s="8" t="inlineStr"/>
       <c r="I126" s="8" t="inlineStr"/>
       <c r="J126" s="8" t="inlineStr"/>
-      <c r="K126" s="9" t="inlineStr"/>
+      <c r="K126" s="9" t="inlineStr">
+        <is>
+          <t>8610.00</t>
+        </is>
+      </c>
       <c r="L126" s="8" t="inlineStr"/>
       <c r="M126" s="8" t="inlineStr"/>
       <c r="N126" s="8" t="inlineStr"/>
-      <c r="O126" s="8" t="inlineStr">
-        <is>
-          <t>8520.00</t>
+      <c r="O126" s="9" t="inlineStr">
+        <is>
+          <t>7290.00</t>
         </is>
       </c>
       <c r="P126" s="8" t="inlineStr">
         <is>
-          <t>11830.00</t>
+          <t>9690.00</t>
         </is>
       </c>
       <c r="Q126" s="8" t="inlineStr">
         <is>
-          <t>16805.00</t>
-        </is>
-      </c>
-      <c r="R126" s="8" t="inlineStr"/>
+          <t>10155.00</t>
+        </is>
+      </c>
+      <c r="R126" s="8" t="inlineStr">
+        <is>
+          <t>17810.00</t>
+        </is>
+      </c>
       <c r="S126" s="8" t="inlineStr"/>
       <c r="T126" s="8" t="inlineStr"/>
       <c r="U126" s="8" t="inlineStr"/>
@@ -7504,15 +8083,19 @@
       <c r="W126" s="8" t="inlineStr"/>
       <c r="X126" s="8" t="inlineStr"/>
       <c r="Y126" s="8" t="inlineStr"/>
-      <c r="Z126" s="10" t="inlineStr"/>
-      <c r="AA126" s="11" t="inlineStr"/>
-      <c r="AB126" s="12" t="inlineStr"/>
+      <c r="Z126" s="8" t="inlineStr"/>
+      <c r="AA126" s="8" t="inlineStr"/>
+      <c r="AB126" s="10" t="n">
+        <v>12551.66666666667</v>
+      </c>
+      <c r="AC126" s="11" t="inlineStr"/>
+      <c r="AD126" s="12" t="inlineStr"/>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="1" t="n"/>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr"/>
@@ -7523,34 +8106,26 @@
       <c r="H127" s="8" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr"/>
       <c r="J127" s="8" t="inlineStr"/>
-      <c r="K127" s="9" t="inlineStr">
-        <is>
-          <t>8195.00</t>
-        </is>
-      </c>
+      <c r="K127" s="9" t="inlineStr"/>
       <c r="L127" s="8" t="inlineStr"/>
       <c r="M127" s="8" t="inlineStr"/>
       <c r="N127" s="8" t="inlineStr"/>
-      <c r="O127" s="8" t="inlineStr">
-        <is>
-          <t>8325.00</t>
+      <c r="O127" s="9" t="inlineStr">
+        <is>
+          <t>8520.00</t>
         </is>
       </c>
       <c r="P127" s="8" t="inlineStr">
         <is>
-          <t>12890.00</t>
+          <t>11830.00</t>
         </is>
       </c>
       <c r="Q127" s="8" t="inlineStr">
         <is>
-          <t>16980.00</t>
-        </is>
-      </c>
-      <c r="R127" s="15" t="inlineStr">
-        <is>
-          <t>16410.00</t>
-        </is>
-      </c>
+          <t>16805.00</t>
+        </is>
+      </c>
+      <c r="R127" s="8" t="inlineStr"/>
       <c r="S127" s="8" t="inlineStr"/>
       <c r="T127" s="8" t="inlineStr"/>
       <c r="U127" s="8" t="inlineStr"/>
@@ -7558,120 +8133,140 @@
       <c r="W127" s="8" t="inlineStr"/>
       <c r="X127" s="8" t="inlineStr"/>
       <c r="Y127" s="8" t="inlineStr"/>
-      <c r="Z127" s="10" t="n">
-        <v>12731.66666666667</v>
-      </c>
-      <c r="AA127" s="10" t="n">
-        <v>3686.666666666666</v>
-      </c>
-      <c r="AB127" s="12" t="n">
-        <v>0.4706282845045849</v>
-      </c>
+      <c r="Z127" s="8" t="inlineStr"/>
+      <c r="AA127" s="8" t="inlineStr"/>
+      <c r="AB127" s="10" t="inlineStr"/>
+      <c r="AC127" s="11" t="inlineStr"/>
+      <c r="AD127" s="12" t="inlineStr"/>
     </row>
     <row r="128" ht="24" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" s="1" t="n"/>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr"/>
+      <c r="D128" s="8" t="inlineStr"/>
+      <c r="E128" s="8" t="inlineStr"/>
+      <c r="F128" s="8" t="inlineStr"/>
+      <c r="G128" s="8" t="inlineStr"/>
+      <c r="H128" s="8" t="inlineStr"/>
+      <c r="I128" s="8" t="inlineStr"/>
+      <c r="J128" s="8" t="inlineStr"/>
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>8195.00</t>
+        </is>
+      </c>
+      <c r="L128" s="8" t="inlineStr"/>
+      <c r="M128" s="8" t="inlineStr"/>
+      <c r="N128" s="8" t="inlineStr"/>
+      <c r="O128" s="9" t="inlineStr">
+        <is>
+          <t>8325.00</t>
+        </is>
+      </c>
+      <c r="P128" s="8" t="inlineStr">
+        <is>
+          <t>12890.00</t>
+        </is>
+      </c>
+      <c r="Q128" s="8" t="inlineStr">
+        <is>
+          <t>16980.00</t>
+        </is>
+      </c>
+      <c r="R128" s="15" t="inlineStr">
+        <is>
+          <t>16410.00</t>
+        </is>
+      </c>
+      <c r="S128" s="15" t="inlineStr">
+        <is>
+          <t>18865.00</t>
+        </is>
+      </c>
+      <c r="T128" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="U128" s="8" t="inlineStr"/>
+      <c r="V128" s="8" t="inlineStr"/>
+      <c r="W128" s="8" t="inlineStr"/>
+      <c r="X128" s="8" t="inlineStr"/>
+      <c r="Y128" s="8" t="inlineStr"/>
+      <c r="Z128" s="8" t="inlineStr"/>
+      <c r="AA128" s="8" t="inlineStr"/>
+      <c r="AB128" s="10" t="n">
+        <v>15426.66666666667</v>
+      </c>
+      <c r="AC128" s="10" t="n">
+        <v>2875</v>
+      </c>
+      <c r="AD128" s="12" t="n">
+        <v>0.3670134677985575</v>
+      </c>
+    </row>
+    <row r="129" ht="24" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Seaquest
 Random: 68.4
 Human: 42054.7</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 525</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr"/>
-      <c r="D128" s="4" t="inlineStr"/>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
-      <c r="G128" s="4" t="inlineStr"/>
-      <c r="H128" s="4" t="inlineStr"/>
-      <c r="I128" s="4" t="inlineStr"/>
-      <c r="J128" s="4" t="inlineStr"/>
-      <c r="K128" s="4" t="inlineStr"/>
-      <c r="L128" s="4" t="inlineStr"/>
-      <c r="M128" s="4" t="inlineStr"/>
-      <c r="N128" s="4" t="inlineStr"/>
-      <c r="O128" s="4" t="inlineStr"/>
-      <c r="P128" s="4" t="inlineStr"/>
-      <c r="Q128" s="4" t="inlineStr"/>
-      <c r="R128" s="4" t="inlineStr"/>
-      <c r="S128" s="4" t="inlineStr"/>
-      <c r="T128" s="4" t="inlineStr"/>
-      <c r="U128" s="4" t="inlineStr"/>
-      <c r="V128" s="4" t="inlineStr"/>
-      <c r="W128" s="4" t="inlineStr"/>
-      <c r="X128" s="4" t="inlineStr"/>
-      <c r="Y128" s="4" t="inlineStr"/>
-      <c r="Z128" s="5" t="inlineStr"/>
-      <c r="AA128" s="6" t="n">
+      <c r="C129" s="4" t="inlineStr"/>
+      <c r="D129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
+      <c r="G129" s="4" t="inlineStr"/>
+      <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="inlineStr"/>
+      <c r="J129" s="4" t="inlineStr"/>
+      <c r="K129" s="4" t="inlineStr"/>
+      <c r="L129" s="4" t="inlineStr"/>
+      <c r="M129" s="4" t="inlineStr"/>
+      <c r="N129" s="4" t="inlineStr"/>
+      <c r="O129" s="4" t="inlineStr"/>
+      <c r="P129" s="4" t="inlineStr"/>
+      <c r="Q129" s="4" t="inlineStr"/>
+      <c r="R129" s="4" t="inlineStr"/>
+      <c r="S129" s="4" t="inlineStr"/>
+      <c r="T129" s="4" t="inlineStr"/>
+      <c r="U129" s="4" t="inlineStr"/>
+      <c r="V129" s="4" t="inlineStr"/>
+      <c r="W129" s="4" t="inlineStr"/>
+      <c r="X129" s="4" t="inlineStr"/>
+      <c r="Y129" s="4" t="inlineStr"/>
+      <c r="Z129" s="4" t="inlineStr"/>
+      <c r="AA129" s="4" t="inlineStr"/>
+      <c r="AB129" s="5" t="inlineStr"/>
+      <c r="AC129" s="6" t="n">
         <v>-64.33333333333331</v>
       </c>
-      <c r="AB128" s="7" t="n">
+      <c r="AD129" s="7" t="n">
         <v>-0.001532245835744834</v>
       </c>
-    </row>
-    <row r="129" ht="24" customHeight="1">
-      <c r="A129" s="1" t="n"/>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="inlineStr">
-        <is>
-          <t>454.00</t>
-        </is>
-      </c>
-      <c r="D129" s="8" t="inlineStr"/>
-      <c r="E129" s="8" t="inlineStr"/>
-      <c r="F129" s="8" t="inlineStr"/>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="8" t="inlineStr"/>
-      <c r="I129" s="8" t="inlineStr"/>
-      <c r="J129" s="8" t="inlineStr"/>
-      <c r="K129" s="8" t="inlineStr">
-        <is>
-          <t>494.00</t>
-        </is>
-      </c>
-      <c r="L129" s="8" t="inlineStr"/>
-      <c r="M129" s="8" t="inlineStr"/>
-      <c r="N129" s="8" t="inlineStr"/>
-      <c r="O129" s="8" t="inlineStr">
-        <is>
-          <t>418.00</t>
-        </is>
-      </c>
-      <c r="P129" s="8" t="inlineStr"/>
-      <c r="Q129" s="8" t="inlineStr"/>
-      <c r="R129" s="8" t="inlineStr"/>
-      <c r="S129" s="8" t="inlineStr"/>
-      <c r="T129" s="8" t="inlineStr"/>
-      <c r="U129" s="8" t="inlineStr"/>
-      <c r="V129" s="8" t="inlineStr"/>
-      <c r="W129" s="8" t="inlineStr"/>
-      <c r="X129" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
-      <c r="Y129" s="8" t="inlineStr"/>
-      <c r="Z129" s="10" t="n">
-        <v>460.6666666666667</v>
-      </c>
-      <c r="AA129" s="11" t="inlineStr"/>
-      <c r="AB129" s="12" t="inlineStr"/>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="1" t="n"/>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>454.00</t>
+        </is>
+      </c>
       <c r="D130" s="8" t="inlineStr"/>
       <c r="E130" s="8" t="inlineStr"/>
       <c r="F130" s="8" t="inlineStr"/>
@@ -7679,13 +8274,17 @@
       <c r="H130" s="8" t="inlineStr"/>
       <c r="I130" s="8" t="inlineStr"/>
       <c r="J130" s="8" t="inlineStr"/>
-      <c r="K130" s="8" t="inlineStr"/>
+      <c r="K130" s="8" t="inlineStr">
+        <is>
+          <t>494.00</t>
+        </is>
+      </c>
       <c r="L130" s="8" t="inlineStr"/>
       <c r="M130" s="8" t="inlineStr"/>
       <c r="N130" s="8" t="inlineStr"/>
       <c r="O130" s="8" t="inlineStr">
         <is>
-          <t>476.00</t>
+          <t>418.00</t>
         </is>
       </c>
       <c r="P130" s="8" t="inlineStr"/>
@@ -7696,21 +8295,25 @@
       <c r="U130" s="8" t="inlineStr"/>
       <c r="V130" s="8" t="inlineStr"/>
       <c r="W130" s="8" t="inlineStr"/>
-      <c r="X130" s="8" t="inlineStr">
-        <is>
-          <t>557.00</t>
-        </is>
-      </c>
+      <c r="X130" s="8" t="inlineStr"/>
       <c r="Y130" s="8" t="inlineStr"/>
-      <c r="Z130" s="10" t="inlineStr"/>
-      <c r="AA130" s="11" t="inlineStr"/>
-      <c r="AB130" s="12" t="inlineStr"/>
+      <c r="Z130" s="8" t="inlineStr">
+        <is>
+          <t>470.00</t>
+        </is>
+      </c>
+      <c r="AA130" s="8" t="inlineStr"/>
+      <c r="AB130" s="10" t="n">
+        <v>460.6666666666667</v>
+      </c>
+      <c r="AC130" s="11" t="inlineStr"/>
+      <c r="AD130" s="12" t="inlineStr"/>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="1" t="n"/>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr"/>
@@ -7721,17 +8324,13 @@
       <c r="H131" s="8" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr"/>
       <c r="J131" s="8" t="inlineStr"/>
-      <c r="K131" s="8" t="inlineStr">
-        <is>
-          <t>521.00</t>
-        </is>
-      </c>
+      <c r="K131" s="8" t="inlineStr"/>
       <c r="L131" s="8" t="inlineStr"/>
       <c r="M131" s="8" t="inlineStr"/>
       <c r="N131" s="8" t="inlineStr"/>
       <c r="O131" s="8" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>476.00</t>
         </is>
       </c>
       <c r="P131" s="8" t="inlineStr"/>
@@ -7742,27 +8341,23 @@
       <c r="U131" s="8" t="inlineStr"/>
       <c r="V131" s="8" t="inlineStr"/>
       <c r="W131" s="8" t="inlineStr"/>
-      <c r="X131" s="8" t="inlineStr">
-        <is>
-          <t>545.00</t>
-        </is>
-      </c>
+      <c r="X131" s="8" t="inlineStr"/>
       <c r="Y131" s="8" t="inlineStr"/>
-      <c r="Z131" s="10" t="n">
-        <v>505.3333333333333</v>
-      </c>
-      <c r="AA131" s="10" t="n">
-        <v>44.66666666666663</v>
-      </c>
-      <c r="AB131" s="12" t="n">
-        <v>0.001063839077667397</v>
-      </c>
+      <c r="Z131" s="8" t="inlineStr">
+        <is>
+          <t>557.00</t>
+        </is>
+      </c>
+      <c r="AA131" s="8" t="inlineStr"/>
+      <c r="AB131" s="10" t="inlineStr"/>
+      <c r="AC131" s="11" t="inlineStr"/>
+      <c r="AD131" s="12" t="inlineStr"/>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="1" t="n"/>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr"/>
@@ -7773,11 +8368,19 @@
       <c r="H132" s="8" t="inlineStr"/>
       <c r="I132" s="8" t="inlineStr"/>
       <c r="J132" s="8" t="inlineStr"/>
-      <c r="K132" s="8" t="inlineStr"/>
+      <c r="K132" s="8" t="inlineStr">
+        <is>
+          <t>521.00</t>
+        </is>
+      </c>
       <c r="L132" s="8" t="inlineStr"/>
       <c r="M132" s="8" t="inlineStr"/>
       <c r="N132" s="8" t="inlineStr"/>
-      <c r="O132" s="8" t="inlineStr"/>
+      <c r="O132" s="8" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
       <c r="P132" s="8" t="inlineStr"/>
       <c r="Q132" s="8" t="inlineStr"/>
       <c r="R132" s="8" t="inlineStr"/>
@@ -7786,21 +8389,29 @@
       <c r="U132" s="8" t="inlineStr"/>
       <c r="V132" s="8" t="inlineStr"/>
       <c r="W132" s="8" t="inlineStr"/>
-      <c r="X132" s="8" t="inlineStr">
-        <is>
-          <t>411.00</t>
-        </is>
-      </c>
+      <c r="X132" s="8" t="inlineStr"/>
       <c r="Y132" s="8" t="inlineStr"/>
-      <c r="Z132" s="10" t="inlineStr"/>
-      <c r="AA132" s="11" t="inlineStr"/>
-      <c r="AB132" s="12" t="inlineStr"/>
+      <c r="Z132" s="8" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
+      <c r="AA132" s="8" t="inlineStr"/>
+      <c r="AB132" s="10" t="n">
+        <v>505.3333333333333</v>
+      </c>
+      <c r="AC132" s="10" t="n">
+        <v>44.66666666666663</v>
+      </c>
+      <c r="AD132" s="12" t="n">
+        <v>0.001063839077667397</v>
+      </c>
     </row>
     <row r="133" ht="24" customHeight="1">
       <c r="A133" s="1" t="n"/>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [add]</t>
+          <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr"/>
@@ -7824,130 +8435,126 @@
       <c r="U133" s="8" t="inlineStr"/>
       <c r="V133" s="8" t="inlineStr"/>
       <c r="W133" s="8" t="inlineStr"/>
-      <c r="X133" s="8" t="inlineStr">
+      <c r="X133" s="8" t="inlineStr"/>
+      <c r="Y133" s="8" t="inlineStr"/>
+      <c r="Z133" s="8" t="inlineStr">
+        <is>
+          <t>411.00</t>
+        </is>
+      </c>
+      <c r="AA133" s="8" t="inlineStr"/>
+      <c r="AB133" s="10" t="inlineStr"/>
+      <c r="AC133" s="11" t="inlineStr"/>
+      <c r="AD133" s="12" t="inlineStr"/>
+    </row>
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="1" t="n"/>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr"/>
+      <c r="D134" s="8" t="inlineStr"/>
+      <c r="E134" s="8" t="inlineStr"/>
+      <c r="F134" s="8" t="inlineStr"/>
+      <c r="G134" s="8" t="inlineStr"/>
+      <c r="H134" s="8" t="inlineStr"/>
+      <c r="I134" s="8" t="inlineStr"/>
+      <c r="J134" s="8" t="inlineStr"/>
+      <c r="K134" s="8" t="inlineStr"/>
+      <c r="L134" s="8" t="inlineStr"/>
+      <c r="M134" s="8" t="inlineStr"/>
+      <c r="N134" s="8" t="inlineStr"/>
+      <c r="O134" s="8" t="inlineStr"/>
+      <c r="P134" s="8" t="inlineStr"/>
+      <c r="Q134" s="8" t="inlineStr"/>
+      <c r="R134" s="8" t="inlineStr"/>
+      <c r="S134" s="8" t="inlineStr"/>
+      <c r="T134" s="8" t="inlineStr"/>
+      <c r="U134" s="8" t="inlineStr"/>
+      <c r="V134" s="8" t="inlineStr"/>
+      <c r="W134" s="8" t="inlineStr"/>
+      <c r="X134" s="8" t="inlineStr"/>
+      <c r="Y134" s="8" t="inlineStr"/>
+      <c r="Z134" s="8" t="inlineStr">
         <is>
           <t>415.00</t>
         </is>
       </c>
-      <c r="Y133" s="8" t="inlineStr"/>
-      <c r="Z133" s="10" t="inlineStr"/>
-      <c r="AA133" s="11" t="inlineStr"/>
-      <c r="AB133" s="12" t="inlineStr"/>
-    </row>
-    <row r="134" ht="24" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="AA134" s="8" t="inlineStr"/>
+      <c r="AB134" s="10" t="inlineStr"/>
+      <c r="AC134" s="11" t="inlineStr"/>
+      <c r="AD134" s="12" t="inlineStr"/>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>UpNDown
 Random: 533.4
 Human: 11693.2</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>STORM (논문): 7985</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr"/>
-      <c r="D134" s="4" t="inlineStr"/>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="4" t="inlineStr"/>
-      <c r="H134" s="4" t="inlineStr"/>
-      <c r="I134" s="4" t="inlineStr"/>
-      <c r="J134" s="4" t="inlineStr"/>
-      <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="4" t="inlineStr"/>
-      <c r="M134" s="4" t="inlineStr"/>
-      <c r="N134" s="4" t="inlineStr"/>
-      <c r="O134" s="4" t="inlineStr"/>
-      <c r="P134" s="4" t="inlineStr"/>
-      <c r="Q134" s="4" t="inlineStr"/>
-      <c r="R134" s="4" t="inlineStr"/>
-      <c r="S134" s="4" t="inlineStr"/>
-      <c r="T134" s="4" t="inlineStr"/>
-      <c r="U134" s="4" t="inlineStr"/>
-      <c r="V134" s="4" t="inlineStr"/>
-      <c r="W134" s="4" t="inlineStr"/>
-      <c r="X134" s="4" t="inlineStr"/>
-      <c r="Y134" s="4" t="inlineStr"/>
-      <c r="Z134" s="5" t="inlineStr"/>
-      <c r="AA134" s="6" t="n">
+      <c r="C135" s="4" t="inlineStr"/>
+      <c r="D135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
+      <c r="G135" s="4" t="inlineStr"/>
+      <c r="H135" s="4" t="inlineStr"/>
+      <c r="I135" s="4" t="inlineStr"/>
+      <c r="J135" s="4" t="inlineStr"/>
+      <c r="K135" s="4" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr"/>
+      <c r="M135" s="4" t="inlineStr"/>
+      <c r="N135" s="4" t="inlineStr"/>
+      <c r="O135" s="4" t="inlineStr"/>
+      <c r="P135" s="4" t="inlineStr"/>
+      <c r="Q135" s="4" t="inlineStr"/>
+      <c r="R135" s="4" t="inlineStr"/>
+      <c r="S135" s="4" t="inlineStr"/>
+      <c r="T135" s="4" t="inlineStr"/>
+      <c r="U135" s="4" t="inlineStr"/>
+      <c r="V135" s="4" t="inlineStr"/>
+      <c r="W135" s="4" t="inlineStr"/>
+      <c r="X135" s="4" t="inlineStr"/>
+      <c r="Y135" s="4" t="inlineStr"/>
+      <c r="Z135" s="4" t="inlineStr"/>
+      <c r="AA135" s="4" t="inlineStr"/>
+      <c r="AB135" s="5" t="inlineStr"/>
+      <c r="AC135" s="6" t="n">
         <v>-2053.75</v>
       </c>
-      <c r="AB134" s="7" t="n">
+      <c r="AD135" s="7" t="n">
         <v>-0.1840310758257316</v>
       </c>
-    </row>
-    <row r="135" ht="24" customHeight="1">
-      <c r="A135" s="1" t="n"/>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C135" s="8" t="inlineStr">
-        <is>
-          <t>9044.00</t>
-        </is>
-      </c>
-      <c r="D135" s="8" t="inlineStr"/>
-      <c r="E135" s="8" t="inlineStr"/>
-      <c r="F135" s="8" t="inlineStr"/>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="8" t="inlineStr"/>
-      <c r="I135" s="8" t="inlineStr">
-        <is>
-          <t>5849.00</t>
-        </is>
-      </c>
-      <c r="J135" s="8" t="inlineStr"/>
-      <c r="K135" s="8" t="inlineStr"/>
-      <c r="L135" s="8" t="inlineStr"/>
-      <c r="M135" s="8" t="inlineStr"/>
-      <c r="N135" s="8" t="inlineStr"/>
-      <c r="O135" s="8" t="inlineStr">
-        <is>
-          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
-        </is>
-      </c>
-      <c r="P135" s="8" t="inlineStr">
-        <is>
-          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
-        </is>
-      </c>
-      <c r="Q135" s="9" t="inlineStr">
-        <is>
-          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="R135" s="8" t="inlineStr"/>
-      <c r="S135" s="8" t="inlineStr"/>
-      <c r="T135" s="8" t="inlineStr"/>
-      <c r="U135" s="8" t="inlineStr"/>
-      <c r="V135" s="8" t="inlineStr"/>
-      <c r="W135" s="8" t="inlineStr"/>
-      <c r="X135" s="8" t="inlineStr"/>
-      <c r="Y135" s="8" t="inlineStr"/>
-      <c r="Z135" s="10" t="n">
-        <v>5931.25</v>
-      </c>
-      <c r="AA135" s="11" t="inlineStr"/>
-      <c r="AB135" s="12" t="inlineStr"/>
     </row>
     <row r="136" ht="24" customHeight="1">
       <c r="A136" s="1" t="n"/>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C136" s="8" t="inlineStr"/>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>9044.00</t>
+        </is>
+      </c>
       <c r="D136" s="8" t="inlineStr"/>
       <c r="E136" s="8" t="inlineStr"/>
       <c r="F136" s="8" t="inlineStr"/>
       <c r="G136" s="8" t="inlineStr"/>
       <c r="H136" s="8" t="inlineStr"/>
-      <c r="I136" s="8" t="inlineStr"/>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>5849.00</t>
+        </is>
+      </c>
       <c r="J136" s="8" t="inlineStr"/>
       <c r="K136" s="8" t="inlineStr"/>
       <c r="L136" s="8" t="inlineStr"/>
@@ -7955,17 +8562,17 @@
       <c r="N136" s="8" t="inlineStr"/>
       <c r="O136" s="8" t="inlineStr">
         <is>
-          <t>5670.00</t>
+          <t>5321.50, 5529.50, 6154.50, 6104.50</t>
         </is>
       </c>
       <c r="P136" s="8" t="inlineStr">
         <is>
-          <t>7178.00</t>
+          <t>6541.00, 6151.00, 6281.50, 5752.50</t>
         </is>
       </c>
       <c r="Q136" s="9" t="inlineStr">
         <is>
-          <t>3066.00</t>
+          <t>3203.50, 3308.00, 3088.00, 3095.00</t>
         </is>
       </c>
       <c r="R136" s="8" t="inlineStr"/>
@@ -7976,15 +8583,19 @@
       <c r="W136" s="8" t="inlineStr"/>
       <c r="X136" s="8" t="inlineStr"/>
       <c r="Y136" s="8" t="inlineStr"/>
-      <c r="Z136" s="10" t="inlineStr"/>
-      <c r="AA136" s="11" t="inlineStr"/>
-      <c r="AB136" s="12" t="inlineStr"/>
+      <c r="Z136" s="8" t="inlineStr"/>
+      <c r="AA136" s="8" t="inlineStr"/>
+      <c r="AB136" s="10" t="n">
+        <v>5931.25</v>
+      </c>
+      <c r="AC136" s="11" t="inlineStr"/>
+      <c r="AD136" s="12" t="inlineStr"/>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="1" t="n"/>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr"/>
@@ -8001,24 +8612,20 @@
       <c r="N137" s="8" t="inlineStr"/>
       <c r="O137" s="8" t="inlineStr">
         <is>
-          <t>6043.00</t>
+          <t>5670.00</t>
         </is>
       </c>
       <c r="P137" s="8" t="inlineStr">
         <is>
-          <t>6658.00</t>
+          <t>7178.00</t>
         </is>
       </c>
       <c r="Q137" s="9" t="inlineStr">
         <is>
-          <t>2974.50</t>
-        </is>
-      </c>
-      <c r="R137" s="15" t="inlineStr">
-        <is>
-          <t>7972.50</t>
-        </is>
-      </c>
+          <t>3066.00</t>
+        </is>
+      </c>
+      <c r="R137" s="8" t="inlineStr"/>
       <c r="S137" s="8" t="inlineStr"/>
       <c r="T137" s="8" t="inlineStr"/>
       <c r="U137" s="8" t="inlineStr"/>
@@ -8026,44 +8633,102 @@
       <c r="W137" s="8" t="inlineStr"/>
       <c r="X137" s="8" t="inlineStr"/>
       <c r="Y137" s="8" t="inlineStr"/>
-      <c r="Z137" s="10" t="n">
+      <c r="Z137" s="8" t="inlineStr"/>
+      <c r="AA137" s="8" t="inlineStr"/>
+      <c r="AB137" s="10" t="inlineStr"/>
+      <c r="AC137" s="11" t="inlineStr"/>
+      <c r="AD137" s="12" t="inlineStr"/>
+    </row>
+    <row r="138" ht="24" customHeight="1">
+      <c r="A138" s="1" t="n"/>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr"/>
+      <c r="D138" s="8" t="inlineStr"/>
+      <c r="E138" s="8" t="inlineStr"/>
+      <c r="F138" s="8" t="inlineStr"/>
+      <c r="G138" s="8" t="inlineStr"/>
+      <c r="H138" s="8" t="inlineStr"/>
+      <c r="I138" s="8" t="inlineStr"/>
+      <c r="J138" s="8" t="inlineStr"/>
+      <c r="K138" s="8" t="inlineStr"/>
+      <c r="L138" s="8" t="inlineStr"/>
+      <c r="M138" s="8" t="inlineStr"/>
+      <c r="N138" s="8" t="inlineStr"/>
+      <c r="O138" s="8" t="inlineStr">
+        <is>
+          <t>6043.00</t>
+        </is>
+      </c>
+      <c r="P138" s="8" t="inlineStr">
+        <is>
+          <t>6658.00</t>
+        </is>
+      </c>
+      <c r="Q138" s="9" t="inlineStr">
+        <is>
+          <t>2974.50</t>
+        </is>
+      </c>
+      <c r="R138" s="15" t="inlineStr">
+        <is>
+          <t>7972.50</t>
+        </is>
+      </c>
+      <c r="S138" s="8" t="inlineStr"/>
+      <c r="T138" s="8" t="inlineStr"/>
+      <c r="U138" s="8" t="inlineStr"/>
+      <c r="V138" s="8" t="inlineStr"/>
+      <c r="W138" s="8" t="inlineStr"/>
+      <c r="X138" s="8" t="inlineStr"/>
+      <c r="Y138" s="8" t="inlineStr"/>
+      <c r="Z138" s="14" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="AA138" s="8" t="inlineStr"/>
+      <c r="AB138" s="10" t="n">
         <v>6350.5</v>
       </c>
-      <c r="AA137" s="10" t="n">
+      <c r="AC138" s="10" t="n">
         <v>419.25</v>
       </c>
-      <c r="AB137" s="12" t="n">
+      <c r="AD138" s="12" t="n">
         <v>0.03756787756052975</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A94:A97"/>
     <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A82:A87"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A128:A133"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="A117:A119"/>
-    <mergeCell ref="A124:A127"/>
-    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A84:A89"/>
+    <mergeCell ref="A78:A83"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A108:A113"/>
+    <mergeCell ref="A66:A71"/>
     <mergeCell ref="A26:A31"/>
+    <mergeCell ref="A135:A138"/>
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A100:A105"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A129:A134"/>
     <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A125:A128"/>
     <mergeCell ref="A32:A37"/>
     <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A118:A120"/>
     <mergeCell ref="A44:A47"/>
-    <mergeCell ref="A106:A111"/>
-    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="A121:A124"/>
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="A38:A43"/>
-    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="A102:A107"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="+0.00;-0.00;0.00"/>
     <numFmt numFmtId="165" formatCode="+0.0000;-0.0000;0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,7 +55,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="001F4E78"/>
       <sz val="16"/>
     </font>
     <font>
@@ -65,8 +65,14 @@
       <color rgb="00808080"/>
       <sz val="16"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +87,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -180,8 +191,10 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -264,18 +277,18 @@
     <author>STORM</author>
   </authors>
   <commentList>
-    <comment ref="AB1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>Retrieval 미사용과 target: 16 양쪽에 유효한 점수가 있는 공통 시드만 사용합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드는 제외합니다. 각 시드에 여러 결과가 있으면 첫 번째 점수를 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AF1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: Retrieval 미사용의 공통 시드 평균 − STORM 논문 점수.
 target: 16 행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: (Retrieval 미사용 평균 − STORM 논문 점수) / (Human − Random).
 target: 16 행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
@@ -452,6 +465,30 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
+    <comment ref="T29" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:3
+python -u train.py -n "BankHeist-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/BankHeist-v5" -trajectory_path "D_TRAJ/BankHeist.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="U29" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:7
+python -u train.py -n "BankHeist-6060" -seed 6060 -config_path "config_files/STORM.yaml" -env_name "ALE/BankHeist-v5" -trajectory_path "D_TRAJ/BankHeist.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="V29" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:12
+python -u train.py -n "BankHeist-6070" -seed 6070 -config_path "config_files/STORM.yaml" -env_name "ALE/BankHeist-v5" -trajectory_path "D_TRAJ/BankHeist.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="Q30" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BankHeist, seed 6020
@@ -588,6 +625,22 @@
     <comment ref="R41" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="S41" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:8
+python -u train.py -n "Boxing-6040" -seed 6040 -config_path "config_files/STORM.yaml" -env_name "ALE/Boxing-v5" -trajectory_path "D_TRAJ/Boxing.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="T41" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:13
+python -u train.py -n "Boxing-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/Boxing-v5" -trajectory_path "D_TRAJ/Boxing.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
@@ -626,11 +679,27 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
+    <comment ref="L57" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_3090.txt:1
+python -u train.py -n "CrazyClimber-2010" -seed 2010 -config_path "config_files/STORM.yaml" -env_name "ALE/CrazyClimber-v5" -trajectory_path "D_TRAJ/CrazyClimber.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="O57" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
+    <comment ref="P57" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:11
+python -u train.py -n "CrazyClimber-6010" -seed 6010 -config_path "config_files/STORM.yaml" -env_name "ALE/CrazyClimber-v5" -trajectory_path "D_TRAJ/CrazyClimber.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="R67" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Freeway, seed 6030
@@ -643,6 +712,22 @@
         <t>EXCLUDED_SEEDS: Freeway, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="C69" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:1
+python -u train.py -n "Freeway-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="D69" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:4
+python -u train.py -n "Freeway-2" -seed 2 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
     <comment ref="R69" authorId="0" shapeId="0">
@@ -653,6 +738,14 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
+    <comment ref="AC69" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_titan.txt:2
+python -u train.py -n "Freeway-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="R70" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Freeway, seed 6030
@@ -737,21 +830,21 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="V79" authorId="0" shapeId="0">
+    <comment ref="Y79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="W79" authorId="0" shapeId="0">
+    <comment ref="Z79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z79" authorId="0" shapeId="0">
+    <comment ref="AC79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -793,21 +886,21 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="V80" authorId="0" shapeId="0">
+    <comment ref="Y80" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="W80" authorId="0" shapeId="0">
+    <comment ref="Z80" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z80" authorId="0" shapeId="0">
+    <comment ref="AC80" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -852,7 +945,31 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="V81" authorId="0" shapeId="0">
+    <comment ref="T81" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:5
+python -u train.py -n "Gopher-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/Gopher-v5" -trajectory_path "D_TRAJ/Gopher.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="U81" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:9
+python -u train.py -n "Gopher-6060" -seed 6060 -config_path "config_files/STORM.yaml" -env_name "ALE/Gopher-v5" -trajectory_path "D_TRAJ/Gopher.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="X81" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_titan.txt:1
+python -u train.py -n "Gopher-9994" -seed 9994 -config_path "config_files/STORM.yaml" -env_name "ALE/Gopher-v5" -trajectory_path "D_TRAJ/Gopher.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="Y81" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -860,7 +977,7 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="W81" authorId="0" shapeId="0">
+    <comment ref="Z81" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -868,12 +985,12 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="X81" authorId="0" shapeId="0">
+    <comment ref="AA81" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="Z81" authorId="0" shapeId="0">
+    <comment ref="AC81" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -915,21 +1032,21 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="V82" authorId="0" shapeId="0">
+    <comment ref="Y82" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="W82" authorId="0" shapeId="0">
+    <comment ref="Z82" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z82" authorId="0" shapeId="0">
+    <comment ref="AC82" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -971,21 +1088,21 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="V83" authorId="0" shapeId="0">
+    <comment ref="Y83" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="W83" authorId="0" shapeId="0">
+    <comment ref="Z83" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z83" authorId="0" shapeId="0">
+    <comment ref="AC83" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -1004,7 +1121,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z95" authorId="0" shapeId="0">
+    <comment ref="AC95" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -1018,13 +1135,21 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z96" authorId="0" shapeId="0">
+    <comment ref="AC96" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="C97" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:2
+python -u train.py -n "Kangaroo-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Kangaroo-v5" -trajectory_path "D_TRAJ/Kangaroo.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="P97" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
@@ -1042,7 +1167,15 @@
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="Z97" authorId="0" shapeId="0">
+    <comment ref="S97" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:10
+python -u train.py -n "Kangaroo-6040" -seed 6040 -config_path "config_files/STORM.yaml" -env_name "ALE/Kangaroo-v5" -trajectory_path "D_TRAJ/Kangaroo.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="AC97" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -1106,6 +1239,14 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="C101" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:3
+python -u train.py -n "Krull-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Krull-v5" -trajectory_path "D_TRAJ/Krull.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="K101" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Krull, seed 2000
@@ -1141,6 +1282,30 @@
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
+    <comment ref="T101" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:1
+STORM_AMP_DTYPE=fp16 python -u train.py -n "Krull-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/Krull-v5" -trajectory_path "D_TRAJ/Krull.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="U101" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:4
+python -u train.py -n "Krull-6060" -seed 6060 -config_path "config_files/STORM.yaml" -env_name "ALE/Krull-v5" -trajectory_path "D_TRAJ/Krull.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="AB101" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_titan.txt:4
+python -u train.py -n "Krull-9998" -seed 9998 -config_path "config_files/STORM.yaml" -env_name "ALE/Krull-v5" -trajectory_path "D_TRAJ/Krull.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="L105" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
@@ -1160,7 +1325,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z116" authorId="0" shapeId="0">
+    <comment ref="AC116" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1258,6 +1423,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="S126" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:2
+python -u train.py --resume_warmup ckpt/RoadRunner-6040_Shared/shared_warmup_50507 -n RoadRunner-6040 -seed 6040 JointTrainAgent.Retrieval.enable "['baseline']"</t>
+      </text>
+    </comment>
     <comment ref="K127" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
@@ -1301,6 +1473,22 @@
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
+    <comment ref="U128" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:6
+python -u train.py -n "RoadRunner-6060" -seed 6060 -config_path "config_files/STORM.yaml" -env_name "ALE/RoadRunner-v5" -trajectory_path "D_TRAJ/RoadRunner.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="AC128" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_titan.txt:3
+python -u train.py -n "RoadRunner-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/RoadRunner-v5" -trajectory_path "D_TRAJ/RoadRunner.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="Q136" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
@@ -1327,7 +1515,7 @@
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="Z138" authorId="0" shapeId="0">
+    <comment ref="AC138" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1625,18 +1813,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD138"/>
+  <dimension ref="A1:AG138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
     <col width="54.7" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="21" max="21"/>
-    <col width="3" customWidth="1" min="27" max="27"/>
-    <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="46" customWidth="1" min="29" max="29"/>
-    <col width="32" customWidth="1" min="30" max="30"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="30" max="30"/>
+    <col width="30" customWidth="1" min="31" max="31"/>
+    <col width="46" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1708,42 +1896,51 @@
       <c r="T1" s="1" t="n">
         <v>6050</v>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="n">
+        <v>6060</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>6070</v>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>    </t>
         </is>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="X1" s="1" t="n">
+        <v>9994</v>
+      </c>
+      <c r="Y1" s="1" t="n">
         <v>9995</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="Z1" s="1" t="n">
         <v>9996</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="AA1" s="1" t="n">
         <v>9997</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="AB1" s="1" t="n">
         <v>9998</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="AC1" s="1" t="n">
         <v>9999</v>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>   </t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -1787,11 +1984,14 @@
       <c r="Y2" s="4" t="inlineStr"/>
       <c r="Z2" s="4" t="inlineStr"/>
       <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="5" t="inlineStr"/>
-      <c r="AC2" s="6" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="inlineStr"/>
+      <c r="AE2" s="5" t="inlineStr"/>
+      <c r="AF2" s="6" t="n">
         <v>107.625</v>
       </c>
-      <c r="AD2" s="7" t="n">
+      <c r="AG2" s="7" t="n">
         <v>0.01559805214568327</v>
       </c>
     </row>
@@ -1851,11 +2051,14 @@
       <c r="Y3" s="8" t="inlineStr"/>
       <c r="Z3" s="8" t="inlineStr"/>
       <c r="AA3" s="8" t="inlineStr"/>
-      <c r="AB3" s="10" t="n">
+      <c r="AB3" s="8" t="inlineStr"/>
+      <c r="AC3" s="8" t="inlineStr"/>
+      <c r="AD3" s="8" t="inlineStr"/>
+      <c r="AE3" s="10" t="n">
         <v>1091.625</v>
       </c>
-      <c r="AC3" s="11" t="inlineStr"/>
-      <c r="AD3" s="12" t="inlineStr"/>
+      <c r="AF3" s="11" t="inlineStr"/>
+      <c r="AG3" s="12" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -1905,9 +2108,12 @@
       <c r="Y4" s="8" t="inlineStr"/>
       <c r="Z4" s="8" t="inlineStr"/>
       <c r="AA4" s="8" t="inlineStr"/>
-      <c r="AB4" s="10" t="inlineStr"/>
-      <c r="AC4" s="11" t="inlineStr"/>
-      <c r="AD4" s="12" t="inlineStr"/>
+      <c r="AB4" s="8" t="inlineStr"/>
+      <c r="AC4" s="8" t="inlineStr"/>
+      <c r="AD4" s="8" t="inlineStr"/>
+      <c r="AE4" s="10" t="inlineStr"/>
+      <c r="AF4" s="11" t="inlineStr"/>
+      <c r="AG4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -1961,13 +2167,16 @@
       <c r="Y5" s="8" t="inlineStr"/>
       <c r="Z5" s="8" t="inlineStr"/>
       <c r="AA5" s="8" t="inlineStr"/>
-      <c r="AB5" s="10" t="n">
+      <c r="AB5" s="8" t="inlineStr"/>
+      <c r="AC5" s="8" t="inlineStr"/>
+      <c r="AD5" s="8" t="inlineStr"/>
+      <c r="AE5" s="10" t="n">
         <v>1147.875</v>
       </c>
-      <c r="AC5" s="10" t="n">
+      <c r="AF5" s="10" t="n">
         <v>56.25</v>
       </c>
-      <c r="AD5" s="12" t="n">
+      <c r="AG5" s="12" t="n">
         <v>0.0081522920622038</v>
       </c>
     </row>
@@ -2007,9 +2216,12 @@
       <c r="Y6" s="8" t="inlineStr"/>
       <c r="Z6" s="8" t="inlineStr"/>
       <c r="AA6" s="8" t="inlineStr"/>
-      <c r="AB6" s="10" t="inlineStr"/>
-      <c r="AC6" s="11" t="inlineStr"/>
-      <c r="AD6" s="12" t="inlineStr"/>
+      <c r="AB6" s="8" t="inlineStr"/>
+      <c r="AC6" s="8" t="inlineStr"/>
+      <c r="AD6" s="8" t="inlineStr"/>
+      <c r="AE6" s="10" t="inlineStr"/>
+      <c r="AF6" s="11" t="inlineStr"/>
+      <c r="AG6" s="12" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="1" t="n"/>
@@ -2047,9 +2259,12 @@
       <c r="Y7" s="8" t="inlineStr"/>
       <c r="Z7" s="8" t="inlineStr"/>
       <c r="AA7" s="8" t="inlineStr"/>
-      <c r="AB7" s="10" t="inlineStr"/>
-      <c r="AC7" s="11" t="inlineStr"/>
-      <c r="AD7" s="12" t="inlineStr"/>
+      <c r="AB7" s="8" t="inlineStr"/>
+      <c r="AC7" s="8" t="inlineStr"/>
+      <c r="AD7" s="8" t="inlineStr"/>
+      <c r="AE7" s="10" t="inlineStr"/>
+      <c r="AF7" s="11" t="inlineStr"/>
+      <c r="AG7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -2089,11 +2304,14 @@
       <c r="Y8" s="4" t="inlineStr"/>
       <c r="Z8" s="4" t="inlineStr"/>
       <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="5" t="inlineStr"/>
-      <c r="AC8" s="6" t="n">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="inlineStr"/>
+      <c r="AE8" s="5" t="inlineStr"/>
+      <c r="AF8" s="6" t="n">
         <v>3.599999999999994</v>
       </c>
-      <c r="AD8" s="7" t="n">
+      <c r="AG8" s="7" t="n">
         <v>0.002100717745229617</v>
       </c>
     </row>
@@ -2153,11 +2371,14 @@
       <c r="Y9" s="8" t="inlineStr"/>
       <c r="Z9" s="8" t="inlineStr"/>
       <c r="AA9" s="8" t="inlineStr"/>
-      <c r="AB9" s="10" t="n">
+      <c r="AB9" s="8" t="inlineStr"/>
+      <c r="AC9" s="8" t="inlineStr"/>
+      <c r="AD9" s="8" t="inlineStr"/>
+      <c r="AE9" s="10" t="n">
         <v>208.6</v>
       </c>
-      <c r="AC9" s="11" t="inlineStr"/>
-      <c r="AD9" s="12" t="inlineStr"/>
+      <c r="AF9" s="11" t="inlineStr"/>
+      <c r="AG9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -2207,9 +2428,12 @@
       <c r="Y10" s="8" t="inlineStr"/>
       <c r="Z10" s="8" t="inlineStr"/>
       <c r="AA10" s="8" t="inlineStr"/>
-      <c r="AB10" s="10" t="inlineStr"/>
-      <c r="AC10" s="11" t="inlineStr"/>
-      <c r="AD10" s="12" t="inlineStr"/>
+      <c r="AB10" s="8" t="inlineStr"/>
+      <c r="AC10" s="8" t="inlineStr"/>
+      <c r="AD10" s="8" t="inlineStr"/>
+      <c r="AE10" s="10" t="inlineStr"/>
+      <c r="AF10" s="11" t="inlineStr"/>
+      <c r="AG10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="1" t="n"/>
@@ -2263,13 +2487,16 @@
       <c r="Y11" s="8" t="inlineStr"/>
       <c r="Z11" s="8" t="inlineStr"/>
       <c r="AA11" s="8" t="inlineStr"/>
-      <c r="AB11" s="10" t="n">
+      <c r="AB11" s="8" t="inlineStr"/>
+      <c r="AC11" s="8" t="inlineStr"/>
+      <c r="AD11" s="8" t="inlineStr"/>
+      <c r="AE11" s="10" t="n">
         <v>169.15</v>
       </c>
-      <c r="AC11" s="10" t="n">
+      <c r="AF11" s="10" t="n">
         <v>39.44999999999999</v>
       </c>
-      <c r="AD11" s="12" t="n">
+      <c r="AG11" s="12" t="n">
         <v>-0.02302036529147458</v>
       </c>
     </row>
@@ -2309,9 +2536,12 @@
       <c r="Y12" s="8" t="inlineStr"/>
       <c r="Z12" s="8" t="inlineStr"/>
       <c r="AA12" s="8" t="inlineStr"/>
-      <c r="AB12" s="10" t="inlineStr"/>
-      <c r="AC12" s="11" t="inlineStr"/>
-      <c r="AD12" s="12" t="inlineStr"/>
+      <c r="AB12" s="8" t="inlineStr"/>
+      <c r="AC12" s="8" t="inlineStr"/>
+      <c r="AD12" s="8" t="inlineStr"/>
+      <c r="AE12" s="10" t="inlineStr"/>
+      <c r="AF12" s="11" t="inlineStr"/>
+      <c r="AG12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -2349,9 +2579,12 @@
       <c r="Y13" s="8" t="inlineStr"/>
       <c r="Z13" s="8" t="inlineStr"/>
       <c r="AA13" s="8" t="inlineStr"/>
-      <c r="AB13" s="10" t="inlineStr"/>
-      <c r="AC13" s="11" t="inlineStr"/>
-      <c r="AD13" s="12" t="inlineStr"/>
+      <c r="AB13" s="8" t="inlineStr"/>
+      <c r="AC13" s="8" t="inlineStr"/>
+      <c r="AD13" s="8" t="inlineStr"/>
+      <c r="AE13" s="10" t="inlineStr"/>
+      <c r="AF13" s="11" t="inlineStr"/>
+      <c r="AG13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2391,11 +2624,14 @@
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="5" t="inlineStr"/>
-      <c r="AC14" s="6" t="n">
+      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="inlineStr"/>
+      <c r="AE14" s="5" t="inlineStr"/>
+      <c r="AF14" s="6" t="n">
         <v>20.11249999999995</v>
       </c>
-      <c r="AD14" s="7" t="n">
+      <c r="AG14" s="7" t="n">
         <v>0.03870765973826011</v>
       </c>
     </row>
@@ -2455,11 +2691,14 @@
       <c r="Y15" s="8" t="inlineStr"/>
       <c r="Z15" s="8" t="inlineStr"/>
       <c r="AA15" s="8" t="inlineStr"/>
-      <c r="AB15" s="10" t="n">
+      <c r="AB15" s="8" t="inlineStr"/>
+      <c r="AC15" s="8" t="inlineStr"/>
+      <c r="AD15" s="8" t="inlineStr"/>
+      <c r="AE15" s="10" t="n">
         <v>821.1125</v>
       </c>
-      <c r="AC15" s="11" t="inlineStr"/>
-      <c r="AD15" s="12" t="inlineStr"/>
+      <c r="AF15" s="11" t="inlineStr"/>
+      <c r="AG15" s="12" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -2509,9 +2748,12 @@
       <c r="Y16" s="8" t="inlineStr"/>
       <c r="Z16" s="8" t="inlineStr"/>
       <c r="AA16" s="8" t="inlineStr"/>
-      <c r="AB16" s="10" t="inlineStr"/>
-      <c r="AC16" s="11" t="inlineStr"/>
-      <c r="AD16" s="12" t="inlineStr"/>
+      <c r="AB16" s="8" t="inlineStr"/>
+      <c r="AC16" s="8" t="inlineStr"/>
+      <c r="AD16" s="8" t="inlineStr"/>
+      <c r="AE16" s="10" t="inlineStr"/>
+      <c r="AF16" s="11" t="inlineStr"/>
+      <c r="AG16" s="12" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -2577,13 +2819,16 @@
       <c r="Y17" s="8" t="inlineStr"/>
       <c r="Z17" s="8" t="inlineStr"/>
       <c r="AA17" s="8" t="inlineStr"/>
-      <c r="AB17" s="10" t="n">
+      <c r="AB17" s="8" t="inlineStr"/>
+      <c r="AC17" s="8" t="inlineStr"/>
+      <c r="AD17" s="8" t="inlineStr"/>
+      <c r="AE17" s="10" t="n">
         <v>723.6625</v>
       </c>
-      <c r="AC17" s="10" t="n">
+      <c r="AF17" s="10" t="n">
         <v>97.44999999999993</v>
       </c>
-      <c r="AD17" s="12" t="n">
+      <c r="AG17" s="12" t="n">
         <v>-0.1875481139337951</v>
       </c>
     </row>
@@ -2623,9 +2868,12 @@
       <c r="Y18" s="8" t="inlineStr"/>
       <c r="Z18" s="8" t="inlineStr"/>
       <c r="AA18" s="8" t="inlineStr"/>
-      <c r="AB18" s="10" t="inlineStr"/>
-      <c r="AC18" s="11" t="inlineStr"/>
-      <c r="AD18" s="12" t="inlineStr"/>
+      <c r="AB18" s="8" t="inlineStr"/>
+      <c r="AC18" s="8" t="inlineStr"/>
+      <c r="AD18" s="8" t="inlineStr"/>
+      <c r="AE18" s="10" t="inlineStr"/>
+      <c r="AF18" s="11" t="inlineStr"/>
+      <c r="AG18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
@@ -2663,9 +2911,12 @@
       <c r="Y19" s="8" t="inlineStr"/>
       <c r="Z19" s="8" t="inlineStr"/>
       <c r="AA19" s="8" t="inlineStr"/>
-      <c r="AB19" s="10" t="inlineStr"/>
-      <c r="AC19" s="11" t="inlineStr"/>
-      <c r="AD19" s="12" t="inlineStr"/>
+      <c r="AB19" s="8" t="inlineStr"/>
+      <c r="AC19" s="8" t="inlineStr"/>
+      <c r="AD19" s="8" t="inlineStr"/>
+      <c r="AE19" s="10" t="inlineStr"/>
+      <c r="AF19" s="11" t="inlineStr"/>
+      <c r="AG19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2705,11 +2956,14 @@
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="5" t="inlineStr"/>
-      <c r="AC20" s="6" t="n">
+      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="inlineStr"/>
+      <c r="AE20" s="5" t="inlineStr"/>
+      <c r="AF20" s="6" t="n">
         <v>-350.5</v>
       </c>
-      <c r="AD20" s="7" t="n">
+      <c r="AG20" s="7" t="n">
         <v>-0.04226303160382478</v>
       </c>
     </row>
@@ -2765,11 +3019,14 @@
       <c r="Y21" s="8" t="inlineStr"/>
       <c r="Z21" s="8" t="inlineStr"/>
       <c r="AA21" s="8" t="inlineStr"/>
-      <c r="AB21" s="10" t="n">
+      <c r="AB21" s="8" t="inlineStr"/>
+      <c r="AC21" s="8" t="inlineStr"/>
+      <c r="AD21" s="8" t="inlineStr"/>
+      <c r="AE21" s="10" t="n">
         <v>677.5</v>
       </c>
-      <c r="AC21" s="11" t="inlineStr"/>
-      <c r="AD21" s="12" t="inlineStr"/>
+      <c r="AF21" s="11" t="inlineStr"/>
+      <c r="AG21" s="12" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="1" t="n"/>
@@ -2815,9 +3072,12 @@
       <c r="Y22" s="8" t="inlineStr"/>
       <c r="Z22" s="8" t="inlineStr"/>
       <c r="AA22" s="8" t="inlineStr"/>
-      <c r="AB22" s="10" t="inlineStr"/>
-      <c r="AC22" s="11" t="inlineStr"/>
-      <c r="AD22" s="12" t="inlineStr"/>
+      <c r="AB22" s="8" t="inlineStr"/>
+      <c r="AC22" s="8" t="inlineStr"/>
+      <c r="AD22" s="8" t="inlineStr"/>
+      <c r="AE22" s="10" t="inlineStr"/>
+      <c r="AF22" s="11" t="inlineStr"/>
+      <c r="AG22" s="12" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="1" t="n"/>
@@ -2867,13 +3127,16 @@
       <c r="Y23" s="8" t="inlineStr"/>
       <c r="Z23" s="8" t="inlineStr"/>
       <c r="AA23" s="8" t="inlineStr"/>
-      <c r="AB23" s="10" t="n">
+      <c r="AB23" s="8" t="inlineStr"/>
+      <c r="AC23" s="8" t="inlineStr"/>
+      <c r="AD23" s="8" t="inlineStr"/>
+      <c r="AE23" s="10" t="n">
         <v>759.375</v>
       </c>
-      <c r="AC23" s="10" t="n">
+      <c r="AF23" s="10" t="n">
         <v>81.875</v>
       </c>
-      <c r="AD23" s="12" t="n">
+      <c r="AG23" s="12" t="n">
         <v>0.009872427139980468</v>
       </c>
     </row>
@@ -2913,9 +3176,12 @@
       <c r="Y24" s="8" t="inlineStr"/>
       <c r="Z24" s="8" t="inlineStr"/>
       <c r="AA24" s="8" t="inlineStr"/>
-      <c r="AB24" s="10" t="inlineStr"/>
-      <c r="AC24" s="11" t="inlineStr"/>
-      <c r="AD24" s="12" t="inlineStr"/>
+      <c r="AB24" s="8" t="inlineStr"/>
+      <c r="AC24" s="8" t="inlineStr"/>
+      <c r="AD24" s="8" t="inlineStr"/>
+      <c r="AE24" s="10" t="inlineStr"/>
+      <c r="AF24" s="11" t="inlineStr"/>
+      <c r="AG24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -2953,9 +3219,12 @@
       <c r="Y25" s="8" t="inlineStr"/>
       <c r="Z25" s="8" t="inlineStr"/>
       <c r="AA25" s="8" t="inlineStr"/>
-      <c r="AB25" s="10" t="inlineStr"/>
-      <c r="AC25" s="11" t="inlineStr"/>
-      <c r="AD25" s="12" t="inlineStr"/>
+      <c r="AB25" s="8" t="inlineStr"/>
+      <c r="AC25" s="8" t="inlineStr"/>
+      <c r="AD25" s="8" t="inlineStr"/>
+      <c r="AE25" s="10" t="inlineStr"/>
+      <c r="AF25" s="11" t="inlineStr"/>
+      <c r="AG25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2995,11 +3264,14 @@
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="5" t="inlineStr"/>
-      <c r="AC26" s="6" t="n">
+      <c r="AB26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AE26" s="5" t="inlineStr"/>
+      <c r="AF26" s="6" t="n">
         <v>-84.75</v>
       </c>
-      <c r="AD26" s="7" t="n">
+      <c r="AG26" s="7" t="n">
         <v>-0.1146975233455136</v>
       </c>
     </row>
@@ -3056,22 +3328,25 @@
       <c r="V27" s="8" t="inlineStr"/>
       <c r="W27" s="8" t="inlineStr"/>
       <c r="X27" s="8" t="inlineStr"/>
-      <c r="Y27" s="8" t="inlineStr">
+      <c r="Y27" s="8" t="inlineStr"/>
+      <c r="Z27" s="8" t="inlineStr"/>
+      <c r="AA27" s="8" t="inlineStr"/>
+      <c r="AB27" s="8" t="inlineStr">
         <is>
           <t>694.50</t>
         </is>
       </c>
-      <c r="Z27" s="8" t="inlineStr">
+      <c r="AC27" s="8" t="inlineStr">
         <is>
           <t>668.50</t>
         </is>
       </c>
-      <c r="AA27" s="8" t="inlineStr"/>
-      <c r="AB27" s="10" t="n">
+      <c r="AD27" s="8" t="inlineStr"/>
+      <c r="AE27" s="10" t="n">
         <v>556.25</v>
       </c>
-      <c r="AC27" s="11" t="inlineStr"/>
-      <c r="AD27" s="12" t="inlineStr"/>
+      <c r="AF27" s="11" t="inlineStr"/>
+      <c r="AG27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -3103,15 +3378,18 @@
       <c r="W28" s="8" t="inlineStr"/>
       <c r="X28" s="8" t="inlineStr"/>
       <c r="Y28" s="8" t="inlineStr"/>
-      <c r="Z28" s="8" t="inlineStr">
+      <c r="Z28" s="8" t="inlineStr"/>
+      <c r="AA28" s="8" t="inlineStr"/>
+      <c r="AB28" s="8" t="inlineStr"/>
+      <c r="AC28" s="8" t="inlineStr">
         <is>
           <t>507.50</t>
         </is>
       </c>
-      <c r="AA28" s="8" t="inlineStr"/>
-      <c r="AB28" s="10" t="inlineStr"/>
-      <c r="AC28" s="11" t="inlineStr"/>
-      <c r="AD28" s="12" t="inlineStr"/>
+      <c r="AD28" s="8" t="inlineStr"/>
+      <c r="AE28" s="10" t="inlineStr"/>
+      <c r="AF28" s="11" t="inlineStr"/>
+      <c r="AG28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -3157,29 +3435,44 @@
           <t>179.00</t>
         </is>
       </c>
-      <c r="T29" s="8" t="inlineStr"/>
-      <c r="U29" s="8" t="inlineStr"/>
-      <c r="V29" s="8" t="inlineStr"/>
+      <c r="T29" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="U29" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="V29" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="W29" s="8" t="inlineStr"/>
       <c r="X29" s="8" t="inlineStr"/>
-      <c r="Y29" s="8" t="inlineStr">
+      <c r="Y29" s="8" t="inlineStr"/>
+      <c r="Z29" s="8" t="inlineStr"/>
+      <c r="AA29" s="8" t="inlineStr"/>
+      <c r="AB29" s="8" t="inlineStr">
         <is>
           <t>566.00</t>
         </is>
       </c>
-      <c r="Z29" s="8" t="inlineStr">
+      <c r="AC29" s="8" t="inlineStr">
         <is>
           <t>565.00</t>
         </is>
       </c>
-      <c r="AA29" s="8" t="inlineStr"/>
-      <c r="AB29" s="10" t="n">
+      <c r="AD29" s="8" t="inlineStr"/>
+      <c r="AE29" s="10" t="n">
         <v>483.5</v>
       </c>
-      <c r="AC29" s="10" t="n">
+      <c r="AF29" s="10" t="n">
         <v>72.75</v>
       </c>
-      <c r="AD29" s="12" t="n">
+      <c r="AG29" s="12" t="n">
         <v>-0.09845716605765327</v>
       </c>
     </row>
@@ -3213,15 +3506,18 @@
       <c r="W30" s="8" t="inlineStr"/>
       <c r="X30" s="8" t="inlineStr"/>
       <c r="Y30" s="8" t="inlineStr"/>
-      <c r="Z30" s="8" t="inlineStr">
+      <c r="Z30" s="8" t="inlineStr"/>
+      <c r="AA30" s="8" t="inlineStr"/>
+      <c r="AB30" s="8" t="inlineStr"/>
+      <c r="AC30" s="8" t="inlineStr">
         <is>
           <t>652.50</t>
         </is>
       </c>
-      <c r="AA30" s="8" t="inlineStr"/>
-      <c r="AB30" s="10" t="inlineStr"/>
-      <c r="AC30" s="11" t="inlineStr"/>
-      <c r="AD30" s="12" t="inlineStr"/>
+      <c r="AD30" s="8" t="inlineStr"/>
+      <c r="AE30" s="10" t="inlineStr"/>
+      <c r="AF30" s="11" t="inlineStr"/>
+      <c r="AG30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="1" t="n"/>
@@ -3253,15 +3549,18 @@
       <c r="W31" s="8" t="inlineStr"/>
       <c r="X31" s="8" t="inlineStr"/>
       <c r="Y31" s="8" t="inlineStr"/>
-      <c r="Z31" s="8" t="inlineStr">
+      <c r="Z31" s="8" t="inlineStr"/>
+      <c r="AA31" s="8" t="inlineStr"/>
+      <c r="AB31" s="8" t="inlineStr"/>
+      <c r="AC31" s="8" t="inlineStr">
         <is>
           <t>381.50</t>
         </is>
       </c>
-      <c r="AA31" s="8" t="inlineStr"/>
-      <c r="AB31" s="10" t="inlineStr"/>
-      <c r="AC31" s="11" t="inlineStr"/>
-      <c r="AD31" s="12" t="inlineStr"/>
+      <c r="AD31" s="8" t="inlineStr"/>
+      <c r="AE31" s="10" t="inlineStr"/>
+      <c r="AF31" s="11" t="inlineStr"/>
+      <c r="AG31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3301,11 +3600,14 @@
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="5" t="inlineStr"/>
-      <c r="AC32" s="6" t="n">
+      <c r="AB32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AD32" s="4" t="inlineStr"/>
+      <c r="AE32" s="5" t="inlineStr"/>
+      <c r="AF32" s="6" t="n">
         <v>-1327.5</v>
       </c>
-      <c r="AD32" s="7" t="n">
+      <c r="AG32" s="7" t="n">
         <v>-0.03811643098126481</v>
       </c>
     </row>
@@ -3365,11 +3667,14 @@
       <c r="Y33" s="8" t="inlineStr"/>
       <c r="Z33" s="8" t="inlineStr"/>
       <c r="AA33" s="8" t="inlineStr"/>
-      <c r="AB33" s="10" t="n">
+      <c r="AB33" s="8" t="inlineStr"/>
+      <c r="AC33" s="8" t="inlineStr"/>
+      <c r="AD33" s="8" t="inlineStr"/>
+      <c r="AE33" s="10" t="n">
         <v>12212.5</v>
       </c>
-      <c r="AC33" s="11" t="inlineStr"/>
-      <c r="AD33" s="12" t="inlineStr"/>
+      <c r="AF33" s="11" t="inlineStr"/>
+      <c r="AG33" s="12" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="1" t="n"/>
@@ -3423,9 +3728,12 @@
       <c r="Y34" s="8" t="inlineStr"/>
       <c r="Z34" s="8" t="inlineStr"/>
       <c r="AA34" s="8" t="inlineStr"/>
-      <c r="AB34" s="10" t="inlineStr"/>
-      <c r="AC34" s="11" t="inlineStr"/>
-      <c r="AD34" s="12" t="inlineStr"/>
+      <c r="AB34" s="8" t="inlineStr"/>
+      <c r="AC34" s="8" t="inlineStr"/>
+      <c r="AD34" s="8" t="inlineStr"/>
+      <c r="AE34" s="10" t="inlineStr"/>
+      <c r="AF34" s="11" t="inlineStr"/>
+      <c r="AG34" s="12" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="1" t="n"/>
@@ -3483,13 +3791,16 @@
       <c r="Y35" s="8" t="inlineStr"/>
       <c r="Z35" s="8" t="inlineStr"/>
       <c r="AA35" s="8" t="inlineStr"/>
-      <c r="AB35" s="10" t="n">
+      <c r="AB35" s="8" t="inlineStr"/>
+      <c r="AC35" s="8" t="inlineStr"/>
+      <c r="AD35" s="8" t="inlineStr"/>
+      <c r="AE35" s="10" t="n">
         <v>13125</v>
       </c>
-      <c r="AC35" s="10" t="n">
+      <c r="AF35" s="10" t="n">
         <v>912.5</v>
       </c>
-      <c r="AD35" s="12" t="n">
+      <c r="AG35" s="12" t="n">
         <v>0.026200559902376</v>
       </c>
     </row>
@@ -3533,9 +3844,12 @@
       <c r="Y36" s="8" t="inlineStr"/>
       <c r="Z36" s="8" t="inlineStr"/>
       <c r="AA36" s="8" t="inlineStr"/>
-      <c r="AB36" s="10" t="inlineStr"/>
-      <c r="AC36" s="11" t="inlineStr"/>
-      <c r="AD36" s="12" t="inlineStr"/>
+      <c r="AB36" s="8" t="inlineStr"/>
+      <c r="AC36" s="8" t="inlineStr"/>
+      <c r="AD36" s="8" t="inlineStr"/>
+      <c r="AE36" s="10" t="inlineStr"/>
+      <c r="AF36" s="11" t="inlineStr"/>
+      <c r="AG36" s="12" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="1" t="n"/>
@@ -3577,9 +3891,12 @@
       <c r="Y37" s="8" t="inlineStr"/>
       <c r="Z37" s="8" t="inlineStr"/>
       <c r="AA37" s="8" t="inlineStr"/>
-      <c r="AB37" s="10" t="inlineStr"/>
-      <c r="AC37" s="11" t="inlineStr"/>
-      <c r="AD37" s="12" t="inlineStr"/>
+      <c r="AB37" s="8" t="inlineStr"/>
+      <c r="AC37" s="8" t="inlineStr"/>
+      <c r="AD37" s="8" t="inlineStr"/>
+      <c r="AE37" s="10" t="inlineStr"/>
+      <c r="AF37" s="11" t="inlineStr"/>
+      <c r="AG37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3619,11 +3936,14 @@
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="inlineStr"/>
       <c r="AA38" s="4" t="inlineStr"/>
-      <c r="AB38" s="5" t="inlineStr"/>
-      <c r="AC38" s="6" t="n">
+      <c r="AB38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AD38" s="4" t="inlineStr"/>
+      <c r="AE38" s="5" t="inlineStr"/>
+      <c r="AF38" s="6" t="n">
         <v>-1.350000000000009</v>
       </c>
-      <c r="AD38" s="7" t="n">
+      <c r="AG38" s="7" t="n">
         <v>-0.1125000000000007</v>
       </c>
     </row>
@@ -3687,11 +4007,14 @@
       <c r="Y39" s="8" t="inlineStr"/>
       <c r="Z39" s="8" t="inlineStr"/>
       <c r="AA39" s="8" t="inlineStr"/>
-      <c r="AB39" s="10" t="n">
+      <c r="AB39" s="8" t="inlineStr"/>
+      <c r="AC39" s="8" t="inlineStr"/>
+      <c r="AD39" s="8" t="inlineStr"/>
+      <c r="AE39" s="10" t="n">
         <v>78.64999999999999</v>
       </c>
-      <c r="AC39" s="11" t="inlineStr"/>
-      <c r="AD39" s="12" t="inlineStr"/>
+      <c r="AF39" s="11" t="inlineStr"/>
+      <c r="AG39" s="12" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="1" t="n"/>
@@ -3733,9 +4056,12 @@
       <c r="Y40" s="8" t="inlineStr"/>
       <c r="Z40" s="8" t="inlineStr"/>
       <c r="AA40" s="8" t="inlineStr"/>
-      <c r="AB40" s="10" t="inlineStr"/>
-      <c r="AC40" s="11" t="inlineStr"/>
-      <c r="AD40" s="12" t="inlineStr"/>
+      <c r="AB40" s="8" t="inlineStr"/>
+      <c r="AC40" s="8" t="inlineStr"/>
+      <c r="AD40" s="8" t="inlineStr"/>
+      <c r="AE40" s="10" t="inlineStr"/>
+      <c r="AF40" s="11" t="inlineStr"/>
+      <c r="AG40" s="12" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="1" t="n"/>
@@ -3779,13 +4105,21 @@
           <t>87.90</t>
         </is>
       </c>
-      <c r="R41" s="14" t="inlineStr">
+      <c r="R41" s="15" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="S41" s="8" t="inlineStr"/>
-      <c r="T41" s="8" t="inlineStr"/>
+      <c r="S41" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="T41" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
       <c r="W41" s="8" t="inlineStr"/>
@@ -3793,13 +4127,16 @@
       <c r="Y41" s="8" t="inlineStr"/>
       <c r="Z41" s="8" t="inlineStr"/>
       <c r="AA41" s="8" t="inlineStr"/>
-      <c r="AB41" s="10" t="n">
+      <c r="AB41" s="8" t="inlineStr"/>
+      <c r="AC41" s="8" t="inlineStr"/>
+      <c r="AD41" s="8" t="inlineStr"/>
+      <c r="AE41" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="AC41" s="10" t="n">
+      <c r="AF41" s="10" t="n">
         <v>3.250000000000014</v>
       </c>
-      <c r="AD41" s="12" t="n">
+      <c r="AG41" s="12" t="n">
         <v>0.2708333333333345</v>
       </c>
     </row>
@@ -3839,9 +4176,12 @@
       <c r="Y42" s="8" t="inlineStr"/>
       <c r="Z42" s="8" t="inlineStr"/>
       <c r="AA42" s="8" t="inlineStr"/>
-      <c r="AB42" s="10" t="inlineStr"/>
-      <c r="AC42" s="11" t="inlineStr"/>
-      <c r="AD42" s="12" t="inlineStr"/>
+      <c r="AB42" s="8" t="inlineStr"/>
+      <c r="AC42" s="8" t="inlineStr"/>
+      <c r="AD42" s="8" t="inlineStr"/>
+      <c r="AE42" s="10" t="inlineStr"/>
+      <c r="AF42" s="11" t="inlineStr"/>
+      <c r="AG42" s="12" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
@@ -3879,9 +4219,12 @@
       <c r="Y43" s="8" t="inlineStr"/>
       <c r="Z43" s="8" t="inlineStr"/>
       <c r="AA43" s="8" t="inlineStr"/>
-      <c r="AB43" s="10" t="inlineStr"/>
-      <c r="AC43" s="11" t="inlineStr"/>
-      <c r="AD43" s="12" t="inlineStr"/>
+      <c r="AB43" s="8" t="inlineStr"/>
+      <c r="AC43" s="8" t="inlineStr"/>
+      <c r="AD43" s="8" t="inlineStr"/>
+      <c r="AE43" s="10" t="inlineStr"/>
+      <c r="AF43" s="11" t="inlineStr"/>
+      <c r="AG43" s="12" t="inlineStr"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3921,11 +4264,14 @@
       <c r="Y44" s="4" t="inlineStr"/>
       <c r="Z44" s="4" t="inlineStr"/>
       <c r="AA44" s="4" t="inlineStr"/>
-      <c r="AB44" s="5" t="inlineStr"/>
-      <c r="AC44" s="6" t="n">
+      <c r="AB44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AD44" s="4" t="inlineStr"/>
+      <c r="AE44" s="5" t="inlineStr"/>
+      <c r="AF44" s="6" t="n">
         <v>-4.266666666666666</v>
       </c>
-      <c r="AD44" s="7" t="n">
+      <c r="AG44" s="7" t="n">
         <v>-0.1481481481481481</v>
       </c>
     </row>
@@ -3981,11 +4327,14 @@
       <c r="Y45" s="8" t="inlineStr"/>
       <c r="Z45" s="8" t="inlineStr"/>
       <c r="AA45" s="8" t="inlineStr"/>
-      <c r="AB45" s="10" t="n">
+      <c r="AB45" s="8" t="inlineStr"/>
+      <c r="AC45" s="8" t="inlineStr"/>
+      <c r="AD45" s="8" t="inlineStr"/>
+      <c r="AE45" s="10" t="n">
         <v>11.73333333333333</v>
       </c>
-      <c r="AC45" s="11" t="inlineStr"/>
-      <c r="AD45" s="12" t="inlineStr"/>
+      <c r="AF45" s="11" t="inlineStr"/>
+      <c r="AG45" s="12" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="1" t="n"/>
@@ -4031,9 +4380,12 @@
       <c r="Y46" s="8" t="inlineStr"/>
       <c r="Z46" s="8" t="inlineStr"/>
       <c r="AA46" s="8" t="inlineStr"/>
-      <c r="AB46" s="10" t="inlineStr"/>
-      <c r="AC46" s="11" t="inlineStr"/>
-      <c r="AD46" s="12" t="inlineStr"/>
+      <c r="AB46" s="8" t="inlineStr"/>
+      <c r="AC46" s="8" t="inlineStr"/>
+      <c r="AD46" s="8" t="inlineStr"/>
+      <c r="AE46" s="10" t="inlineStr"/>
+      <c r="AF46" s="11" t="inlineStr"/>
+      <c r="AG46" s="12" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="1" t="n"/>
@@ -4083,13 +4435,16 @@
       <c r="Y47" s="8" t="inlineStr"/>
       <c r="Z47" s="8" t="inlineStr"/>
       <c r="AA47" s="8" t="inlineStr"/>
-      <c r="AB47" s="10" t="n">
+      <c r="AB47" s="8" t="inlineStr"/>
+      <c r="AC47" s="8" t="inlineStr"/>
+      <c r="AD47" s="8" t="inlineStr"/>
+      <c r="AE47" s="10" t="n">
         <v>12.36666666666667</v>
       </c>
-      <c r="AC47" s="10" t="n">
+      <c r="AF47" s="10" t="n">
         <v>0.6333333333333311</v>
       </c>
-      <c r="AD47" s="12" t="n">
+      <c r="AG47" s="12" t="n">
         <v>0.02199074074074066</v>
       </c>
     </row>
@@ -4131,11 +4486,14 @@
       <c r="Y48" s="4" t="inlineStr"/>
       <c r="Z48" s="4" t="inlineStr"/>
       <c r="AA48" s="4" t="inlineStr"/>
-      <c r="AB48" s="5" t="inlineStr"/>
-      <c r="AC48" s="6" t="n">
+      <c r="AB48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AD48" s="4" t="inlineStr"/>
+      <c r="AE48" s="5" t="inlineStr"/>
+      <c r="AF48" s="6" t="n">
         <v>-199.25</v>
       </c>
-      <c r="AD48" s="7" t="n">
+      <c r="AG48" s="7" t="n">
         <v>-0.03029588857803187</v>
       </c>
     </row>
@@ -4191,11 +4549,14 @@
       <c r="Y49" s="8" t="inlineStr"/>
       <c r="Z49" s="8" t="inlineStr"/>
       <c r="AA49" s="8" t="inlineStr"/>
-      <c r="AB49" s="10" t="n">
+      <c r="AB49" s="8" t="inlineStr"/>
+      <c r="AC49" s="8" t="inlineStr"/>
+      <c r="AD49" s="8" t="inlineStr"/>
+      <c r="AE49" s="10" t="n">
         <v>1688.75</v>
       </c>
-      <c r="AC49" s="11" t="inlineStr"/>
-      <c r="AD49" s="12" t="inlineStr"/>
+      <c r="AF49" s="11" t="inlineStr"/>
+      <c r="AG49" s="12" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="1" t="n"/>
@@ -4237,9 +4598,12 @@
       <c r="Y50" s="8" t="inlineStr"/>
       <c r="Z50" s="8" t="inlineStr"/>
       <c r="AA50" s="8" t="inlineStr"/>
-      <c r="AB50" s="10" t="inlineStr"/>
-      <c r="AC50" s="11" t="inlineStr"/>
-      <c r="AD50" s="12" t="inlineStr"/>
+      <c r="AB50" s="8" t="inlineStr"/>
+      <c r="AC50" s="8" t="inlineStr"/>
+      <c r="AD50" s="8" t="inlineStr"/>
+      <c r="AE50" s="10" t="inlineStr"/>
+      <c r="AF50" s="11" t="inlineStr"/>
+      <c r="AG50" s="12" t="inlineStr"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="1" t="n"/>
@@ -4289,13 +4653,16 @@
       <c r="Y51" s="8" t="inlineStr"/>
       <c r="Z51" s="8" t="inlineStr"/>
       <c r="AA51" s="8" t="inlineStr"/>
-      <c r="AB51" s="10" t="n">
+      <c r="AB51" s="8" t="inlineStr"/>
+      <c r="AC51" s="8" t="inlineStr"/>
+      <c r="AD51" s="8" t="inlineStr"/>
+      <c r="AE51" s="10" t="n">
         <v>1425</v>
       </c>
-      <c r="AC51" s="10" t="n">
+      <c r="AF51" s="10" t="n">
         <v>263.75</v>
       </c>
-      <c r="AD51" s="12" t="n">
+      <c r="AG51" s="12" t="n">
         <v>-0.04010308964846126</v>
       </c>
     </row>
@@ -4339,9 +4706,12 @@
       <c r="Y52" s="8" t="inlineStr"/>
       <c r="Z52" s="8" t="inlineStr"/>
       <c r="AA52" s="8" t="inlineStr"/>
-      <c r="AB52" s="10" t="inlineStr"/>
-      <c r="AC52" s="11" t="inlineStr"/>
-      <c r="AD52" s="12" t="inlineStr"/>
+      <c r="AB52" s="8" t="inlineStr"/>
+      <c r="AC52" s="8" t="inlineStr"/>
+      <c r="AD52" s="8" t="inlineStr"/>
+      <c r="AE52" s="10" t="inlineStr"/>
+      <c r="AF52" s="11" t="inlineStr"/>
+      <c r="AG52" s="12" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="1" t="n"/>
@@ -4383,9 +4753,12 @@
       <c r="Y53" s="8" t="inlineStr"/>
       <c r="Z53" s="8" t="inlineStr"/>
       <c r="AA53" s="8" t="inlineStr"/>
-      <c r="AB53" s="10" t="inlineStr"/>
-      <c r="AC53" s="11" t="inlineStr"/>
-      <c r="AD53" s="12" t="inlineStr"/>
+      <c r="AB53" s="8" t="inlineStr"/>
+      <c r="AC53" s="8" t="inlineStr"/>
+      <c r="AD53" s="8" t="inlineStr"/>
+      <c r="AE53" s="10" t="inlineStr"/>
+      <c r="AF53" s="11" t="inlineStr"/>
+      <c r="AG53" s="12" t="inlineStr"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -4425,11 +4798,14 @@
       <c r="Y54" s="4" t="inlineStr"/>
       <c r="Z54" s="4" t="inlineStr"/>
       <c r="AA54" s="4" t="inlineStr"/>
-      <c r="AB54" s="5" t="inlineStr"/>
-      <c r="AC54" s="6" t="n">
+      <c r="AB54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AD54" s="4" t="inlineStr"/>
+      <c r="AE54" s="5" t="inlineStr"/>
+      <c r="AF54" s="6" t="n">
         <v>-9204.333333333336</v>
       </c>
-      <c r="AD54" s="7" t="n">
+      <c r="AG54" s="7" t="n">
         <v>-0.3674545921510859</v>
       </c>
     </row>
@@ -4485,11 +4861,14 @@
       <c r="Y55" s="8" t="inlineStr"/>
       <c r="Z55" s="8" t="inlineStr"/>
       <c r="AA55" s="8" t="inlineStr"/>
-      <c r="AB55" s="10" t="n">
+      <c r="AB55" s="8" t="inlineStr"/>
+      <c r="AC55" s="8" t="inlineStr"/>
+      <c r="AD55" s="8" t="inlineStr"/>
+      <c r="AE55" s="10" t="n">
         <v>57571.66666666666</v>
       </c>
-      <c r="AC55" s="11" t="inlineStr"/>
-      <c r="AD55" s="12" t="inlineStr"/>
+      <c r="AF55" s="11" t="inlineStr"/>
+      <c r="AG55" s="12" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="1" t="n"/>
@@ -4527,9 +4906,12 @@
       <c r="Y56" s="8" t="inlineStr"/>
       <c r="Z56" s="8" t="inlineStr"/>
       <c r="AA56" s="8" t="inlineStr"/>
-      <c r="AB56" s="10" t="inlineStr"/>
-      <c r="AC56" s="11" t="inlineStr"/>
-      <c r="AD56" s="12" t="inlineStr"/>
+      <c r="AB56" s="8" t="inlineStr"/>
+      <c r="AC56" s="8" t="inlineStr"/>
+      <c r="AD56" s="8" t="inlineStr"/>
+      <c r="AE56" s="10" t="inlineStr"/>
+      <c r="AF56" s="11" t="inlineStr"/>
+      <c r="AG56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="1" t="n"/>
@@ -4559,15 +4941,23 @@
           <t>63275.00</t>
         </is>
       </c>
-      <c r="L57" s="8" t="inlineStr"/>
+      <c r="L57" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
-      <c r="O57" s="14" t="inlineStr">
+      <c r="O57" s="15" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="P57" s="8" t="inlineStr"/>
+      <c r="P57" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr"/>
@@ -4579,13 +4969,16 @@
       <c r="Y57" s="8" t="inlineStr"/>
       <c r="Z57" s="8" t="inlineStr"/>
       <c r="AA57" s="8" t="inlineStr"/>
-      <c r="AB57" s="10" t="n">
+      <c r="AB57" s="8" t="inlineStr"/>
+      <c r="AC57" s="8" t="inlineStr"/>
+      <c r="AD57" s="8" t="inlineStr"/>
+      <c r="AE57" s="10" t="n">
         <v>57908.33333333334</v>
       </c>
-      <c r="AC57" s="10" t="n">
+      <c r="AF57" s="10" t="n">
         <v>336.6666666666715</v>
       </c>
-      <c r="AD57" s="12" t="n">
+      <c r="AG57" s="12" t="n">
         <v>0.01344037728869018</v>
       </c>
     </row>
@@ -4625,9 +5018,12 @@
       <c r="Y58" s="8" t="inlineStr"/>
       <c r="Z58" s="8" t="inlineStr"/>
       <c r="AA58" s="8" t="inlineStr"/>
-      <c r="AB58" s="10" t="inlineStr"/>
-      <c r="AC58" s="11" t="inlineStr"/>
-      <c r="AD58" s="12" t="inlineStr"/>
+      <c r="AB58" s="8" t="inlineStr"/>
+      <c r="AC58" s="8" t="inlineStr"/>
+      <c r="AD58" s="8" t="inlineStr"/>
+      <c r="AE58" s="10" t="inlineStr"/>
+      <c r="AF58" s="11" t="inlineStr"/>
+      <c r="AG58" s="12" t="inlineStr"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="1" t="n"/>
@@ -4665,9 +5061,12 @@
       <c r="Y59" s="8" t="inlineStr"/>
       <c r="Z59" s="8" t="inlineStr"/>
       <c r="AA59" s="8" t="inlineStr"/>
-      <c r="AB59" s="10" t="inlineStr"/>
-      <c r="AC59" s="11" t="inlineStr"/>
-      <c r="AD59" s="12" t="inlineStr"/>
+      <c r="AB59" s="8" t="inlineStr"/>
+      <c r="AC59" s="8" t="inlineStr"/>
+      <c r="AD59" s="8" t="inlineStr"/>
+      <c r="AE59" s="10" t="inlineStr"/>
+      <c r="AF59" s="11" t="inlineStr"/>
+      <c r="AG59" s="12" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -4707,11 +5106,14 @@
       <c r="Y60" s="4" t="inlineStr"/>
       <c r="Z60" s="4" t="inlineStr"/>
       <c r="AA60" s="4" t="inlineStr"/>
-      <c r="AB60" s="5" t="inlineStr"/>
-      <c r="AC60" s="6" t="n">
+      <c r="AB60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AD60" s="4" t="inlineStr"/>
+      <c r="AE60" s="5" t="inlineStr"/>
+      <c r="AF60" s="6" t="n">
         <v>16.625</v>
       </c>
-      <c r="AD60" s="7" t="n">
+      <c r="AG60" s="7" t="n">
         <v>0.009140139644840287</v>
       </c>
     </row>
@@ -4767,11 +5169,14 @@
       <c r="Y61" s="8" t="inlineStr"/>
       <c r="Z61" s="8" t="inlineStr"/>
       <c r="AA61" s="8" t="inlineStr"/>
-      <c r="AB61" s="10" t="n">
+      <c r="AB61" s="8" t="inlineStr"/>
+      <c r="AC61" s="8" t="inlineStr"/>
+      <c r="AD61" s="8" t="inlineStr"/>
+      <c r="AE61" s="10" t="n">
         <v>181.625</v>
       </c>
-      <c r="AC61" s="11" t="inlineStr"/>
-      <c r="AD61" s="12" t="inlineStr"/>
+      <c r="AF61" s="11" t="inlineStr"/>
+      <c r="AG61" s="12" t="inlineStr"/>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="1" t="n"/>
@@ -4813,9 +5218,12 @@
       <c r="Y62" s="8" t="inlineStr"/>
       <c r="Z62" s="8" t="inlineStr"/>
       <c r="AA62" s="8" t="inlineStr"/>
-      <c r="AB62" s="10" t="inlineStr"/>
-      <c r="AC62" s="11" t="inlineStr"/>
-      <c r="AD62" s="12" t="inlineStr"/>
+      <c r="AB62" s="8" t="inlineStr"/>
+      <c r="AC62" s="8" t="inlineStr"/>
+      <c r="AD62" s="8" t="inlineStr"/>
+      <c r="AE62" s="10" t="inlineStr"/>
+      <c r="AF62" s="11" t="inlineStr"/>
+      <c r="AG62" s="12" t="inlineStr"/>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="1" t="n"/>
@@ -4865,13 +5273,16 @@
       <c r="Y63" s="8" t="inlineStr"/>
       <c r="Z63" s="8" t="inlineStr"/>
       <c r="AA63" s="8" t="inlineStr"/>
-      <c r="AB63" s="10" t="n">
+      <c r="AB63" s="8" t="inlineStr"/>
+      <c r="AC63" s="8" t="inlineStr"/>
+      <c r="AD63" s="8" t="inlineStr"/>
+      <c r="AE63" s="10" t="n">
         <v>155.125</v>
       </c>
-      <c r="AC63" s="10" t="n">
+      <c r="AF63" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="AD63" s="12" t="n">
+      <c r="AG63" s="12" t="n">
         <v>-0.01456924514816647</v>
       </c>
     </row>
@@ -4915,9 +5326,12 @@
       <c r="Y64" s="8" t="inlineStr"/>
       <c r="Z64" s="8" t="inlineStr"/>
       <c r="AA64" s="8" t="inlineStr"/>
-      <c r="AB64" s="10" t="inlineStr"/>
-      <c r="AC64" s="11" t="inlineStr"/>
-      <c r="AD64" s="12" t="inlineStr"/>
+      <c r="AB64" s="8" t="inlineStr"/>
+      <c r="AC64" s="8" t="inlineStr"/>
+      <c r="AD64" s="8" t="inlineStr"/>
+      <c r="AE64" s="10" t="inlineStr"/>
+      <c r="AF64" s="11" t="inlineStr"/>
+      <c r="AG64" s="12" t="inlineStr"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="1" t="n"/>
@@ -4959,9 +5373,12 @@
       <c r="Y65" s="8" t="inlineStr"/>
       <c r="Z65" s="8" t="inlineStr"/>
       <c r="AA65" s="8" t="inlineStr"/>
-      <c r="AB65" s="10" t="inlineStr"/>
-      <c r="AC65" s="11" t="inlineStr"/>
-      <c r="AD65" s="12" t="inlineStr"/>
+      <c r="AB65" s="8" t="inlineStr"/>
+      <c r="AC65" s="8" t="inlineStr"/>
+      <c r="AD65" s="8" t="inlineStr"/>
+      <c r="AE65" s="10" t="inlineStr"/>
+      <c r="AF65" s="11" t="inlineStr"/>
+      <c r="AG65" s="12" t="inlineStr"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -5001,11 +5418,14 @@
       <c r="Y66" s="4" t="inlineStr"/>
       <c r="Z66" s="4" t="inlineStr"/>
       <c r="AA66" s="4" t="inlineStr"/>
-      <c r="AB66" s="5" t="inlineStr"/>
-      <c r="AC66" s="6" t="n">
+      <c r="AB66" s="4" t="inlineStr"/>
+      <c r="AC66" s="4" t="inlineStr"/>
+      <c r="AD66" s="4" t="inlineStr"/>
+      <c r="AE66" s="5" t="inlineStr"/>
+      <c r="AF66" s="6" t="n">
         <v>-0.5500000000000043</v>
       </c>
-      <c r="AD66" s="7" t="n">
+      <c r="AG66" s="7" t="n">
         <v>-0.01858108108108122</v>
       </c>
     </row>
@@ -5057,11 +5477,14 @@
       <c r="Y67" s="8" t="inlineStr"/>
       <c r="Z67" s="8" t="inlineStr"/>
       <c r="AA67" s="8" t="inlineStr"/>
-      <c r="AB67" s="10" t="n">
+      <c r="AB67" s="8" t="inlineStr"/>
+      <c r="AC67" s="8" t="inlineStr"/>
+      <c r="AD67" s="8" t="inlineStr"/>
+      <c r="AE67" s="10" t="n">
         <v>33.45</v>
       </c>
-      <c r="AC67" s="11" t="inlineStr"/>
-      <c r="AD67" s="12" t="inlineStr"/>
+      <c r="AF67" s="11" t="inlineStr"/>
+      <c r="AG67" s="12" t="inlineStr"/>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="1" t="n"/>
@@ -5099,9 +5522,12 @@
       <c r="Y68" s="8" t="inlineStr"/>
       <c r="Z68" s="8" t="inlineStr"/>
       <c r="AA68" s="8" t="inlineStr"/>
-      <c r="AB68" s="10" t="inlineStr"/>
-      <c r="AC68" s="11" t="inlineStr"/>
-      <c r="AD68" s="12" t="inlineStr"/>
+      <c r="AB68" s="8" t="inlineStr"/>
+      <c r="AC68" s="8" t="inlineStr"/>
+      <c r="AD68" s="8" t="inlineStr"/>
+      <c r="AE68" s="10" t="inlineStr"/>
+      <c r="AF68" s="11" t="inlineStr"/>
+      <c r="AG68" s="12" t="inlineStr"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
@@ -5110,8 +5536,16 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr"/>
-      <c r="D69" s="8" t="inlineStr"/>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr"/>
@@ -5151,13 +5585,20 @@
       <c r="Y69" s="8" t="inlineStr"/>
       <c r="Z69" s="8" t="inlineStr"/>
       <c r="AA69" s="8" t="inlineStr"/>
-      <c r="AB69" s="10" t="n">
+      <c r="AB69" s="8" t="inlineStr"/>
+      <c r="AC69" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="AD69" s="8" t="inlineStr"/>
+      <c r="AE69" s="10" t="n">
         <v>33.35</v>
       </c>
-      <c r="AC69" s="10" t="n">
+      <c r="AF69" s="10" t="n">
         <v>0.09999999999999432</v>
       </c>
-      <c r="AD69" s="12" t="n">
+      <c r="AG69" s="12" t="n">
         <v>-0.003378378378378186</v>
       </c>
     </row>
@@ -5197,9 +5638,12 @@
       <c r="Y70" s="8" t="inlineStr"/>
       <c r="Z70" s="8" t="inlineStr"/>
       <c r="AA70" s="8" t="inlineStr"/>
-      <c r="AB70" s="10" t="inlineStr"/>
-      <c r="AC70" s="11" t="inlineStr"/>
-      <c r="AD70" s="12" t="inlineStr"/>
+      <c r="AB70" s="8" t="inlineStr"/>
+      <c r="AC70" s="8" t="inlineStr"/>
+      <c r="AD70" s="8" t="inlineStr"/>
+      <c r="AE70" s="10" t="inlineStr"/>
+      <c r="AF70" s="11" t="inlineStr"/>
+      <c r="AG70" s="12" t="inlineStr"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="1" t="n"/>
@@ -5237,9 +5681,12 @@
       <c r="Y71" s="8" t="inlineStr"/>
       <c r="Z71" s="8" t="inlineStr"/>
       <c r="AA71" s="8" t="inlineStr"/>
-      <c r="AB71" s="10" t="inlineStr"/>
-      <c r="AC71" s="11" t="inlineStr"/>
-      <c r="AD71" s="12" t="inlineStr"/>
+      <c r="AB71" s="8" t="inlineStr"/>
+      <c r="AC71" s="8" t="inlineStr"/>
+      <c r="AD71" s="8" t="inlineStr"/>
+      <c r="AE71" s="10" t="inlineStr"/>
+      <c r="AF71" s="11" t="inlineStr"/>
+      <c r="AG71" s="12" t="inlineStr"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -5279,11 +5726,14 @@
       <c r="Y72" s="4" t="inlineStr"/>
       <c r="Z72" s="4" t="inlineStr"/>
       <c r="AA72" s="4" t="inlineStr"/>
-      <c r="AB72" s="5" t="inlineStr"/>
-      <c r="AC72" s="6" t="n">
+      <c r="AB72" s="4" t="inlineStr"/>
+      <c r="AC72" s="4" t="inlineStr"/>
+      <c r="AD72" s="4" t="inlineStr"/>
+      <c r="AE72" s="5" t="inlineStr"/>
+      <c r="AF72" s="6" t="n">
         <v>426.375</v>
       </c>
-      <c r="AD72" s="7" t="n">
+      <c r="AG72" s="7" t="n">
         <v>0.09986532380840848</v>
       </c>
     </row>
@@ -5339,11 +5789,14 @@
       <c r="Y73" s="8" t="inlineStr"/>
       <c r="Z73" s="8" t="inlineStr"/>
       <c r="AA73" s="8" t="inlineStr"/>
-      <c r="AB73" s="10" t="n">
+      <c r="AB73" s="8" t="inlineStr"/>
+      <c r="AC73" s="8" t="inlineStr"/>
+      <c r="AD73" s="8" t="inlineStr"/>
+      <c r="AE73" s="10" t="n">
         <v>1742.375</v>
       </c>
-      <c r="AC73" s="11" t="inlineStr"/>
-      <c r="AD73" s="12" t="inlineStr"/>
+      <c r="AF73" s="11" t="inlineStr"/>
+      <c r="AG73" s="12" t="inlineStr"/>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="1" t="n"/>
@@ -5397,9 +5850,12 @@
       <c r="Y74" s="8" t="inlineStr"/>
       <c r="Z74" s="8" t="inlineStr"/>
       <c r="AA74" s="8" t="inlineStr"/>
-      <c r="AB74" s="10" t="inlineStr"/>
-      <c r="AC74" s="11" t="inlineStr"/>
-      <c r="AD74" s="12" t="inlineStr"/>
+      <c r="AB74" s="8" t="inlineStr"/>
+      <c r="AC74" s="8" t="inlineStr"/>
+      <c r="AD74" s="8" t="inlineStr"/>
+      <c r="AE74" s="10" t="inlineStr"/>
+      <c r="AF74" s="11" t="inlineStr"/>
+      <c r="AG74" s="12" t="inlineStr"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="1" t="n"/>
@@ -5461,13 +5917,16 @@
       <c r="Y75" s="8" t="inlineStr"/>
       <c r="Z75" s="8" t="inlineStr"/>
       <c r="AA75" s="8" t="inlineStr"/>
-      <c r="AB75" s="10" t="n">
+      <c r="AB75" s="8" t="inlineStr"/>
+      <c r="AC75" s="8" t="inlineStr"/>
+      <c r="AD75" s="8" t="inlineStr"/>
+      <c r="AE75" s="10" t="n">
         <v>1986.75</v>
       </c>
-      <c r="AC75" s="10" t="n">
+      <c r="AF75" s="10" t="n">
         <v>244.375</v>
       </c>
-      <c r="AD75" s="12" t="n">
+      <c r="AG75" s="12" t="n">
         <v>0.05723738142639653</v>
       </c>
     </row>
@@ -5511,9 +5970,12 @@
       <c r="Y76" s="8" t="inlineStr"/>
       <c r="Z76" s="8" t="inlineStr"/>
       <c r="AA76" s="8" t="inlineStr"/>
-      <c r="AB76" s="10" t="inlineStr"/>
-      <c r="AC76" s="11" t="inlineStr"/>
-      <c r="AD76" s="12" t="inlineStr"/>
+      <c r="AB76" s="8" t="inlineStr"/>
+      <c r="AC76" s="8" t="inlineStr"/>
+      <c r="AD76" s="8" t="inlineStr"/>
+      <c r="AE76" s="10" t="inlineStr"/>
+      <c r="AF76" s="11" t="inlineStr"/>
+      <c r="AG76" s="12" t="inlineStr"/>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="1" t="n"/>
@@ -5551,9 +6013,12 @@
       <c r="Y77" s="8" t="inlineStr"/>
       <c r="Z77" s="8" t="inlineStr"/>
       <c r="AA77" s="8" t="inlineStr"/>
-      <c r="AB77" s="10" t="inlineStr"/>
-      <c r="AC77" s="11" t="inlineStr"/>
-      <c r="AD77" s="12" t="inlineStr"/>
+      <c r="AB77" s="8" t="inlineStr"/>
+      <c r="AC77" s="8" t="inlineStr"/>
+      <c r="AD77" s="8" t="inlineStr"/>
+      <c r="AE77" s="10" t="inlineStr"/>
+      <c r="AF77" s="11" t="inlineStr"/>
+      <c r="AG77" s="12" t="inlineStr"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -5593,11 +6058,14 @@
       <c r="Y78" s="4" t="inlineStr"/>
       <c r="Z78" s="4" t="inlineStr"/>
       <c r="AA78" s="4" t="inlineStr"/>
-      <c r="AB78" s="5" t="inlineStr"/>
-      <c r="AC78" s="6" t="n">
+      <c r="AB78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AD78" s="4" t="inlineStr"/>
+      <c r="AE78" s="5" t="inlineStr"/>
+      <c r="AF78" s="6" t="n">
         <v>-3430.5</v>
       </c>
-      <c r="AD78" s="7" t="n">
+      <c r="AG78" s="7" t="n">
         <v>-1.591953222887373</v>
       </c>
     </row>
@@ -5655,29 +6123,32 @@
       <c r="S79" s="9" t="inlineStr"/>
       <c r="T79" s="8" t="inlineStr"/>
       <c r="U79" s="8" t="inlineStr"/>
-      <c r="V79" s="9" t="inlineStr"/>
-      <c r="W79" s="9" t="inlineStr"/>
-      <c r="X79" s="8" t="inlineStr">
+      <c r="V79" s="8" t="inlineStr"/>
+      <c r="W79" s="8" t="inlineStr"/>
+      <c r="X79" s="8" t="inlineStr"/>
+      <c r="Y79" s="9" t="inlineStr"/>
+      <c r="Z79" s="9" t="inlineStr"/>
+      <c r="AA79" s="8" t="inlineStr">
         <is>
           <t>8159.00</t>
         </is>
       </c>
-      <c r="Y79" s="8" t="inlineStr">
+      <c r="AB79" s="8" t="inlineStr">
         <is>
           <t>3585.00</t>
         </is>
       </c>
-      <c r="Z79" s="9" t="inlineStr">
+      <c r="AC79" s="9" t="inlineStr">
         <is>
           <t>2594.00</t>
         </is>
       </c>
-      <c r="AA79" s="8" t="inlineStr"/>
-      <c r="AB79" s="10" t="n">
+      <c r="AD79" s="8" t="inlineStr"/>
+      <c r="AE79" s="10" t="n">
         <v>4809.5</v>
       </c>
-      <c r="AC79" s="11" t="inlineStr"/>
-      <c r="AD79" s="12" t="inlineStr"/>
+      <c r="AF79" s="11" t="inlineStr"/>
+      <c r="AG79" s="12" t="inlineStr"/>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="1" t="n"/>
@@ -5709,19 +6180,22 @@
       <c r="S80" s="9" t="inlineStr"/>
       <c r="T80" s="8" t="inlineStr"/>
       <c r="U80" s="8" t="inlineStr"/>
-      <c r="V80" s="9" t="inlineStr"/>
-      <c r="W80" s="9" t="inlineStr"/>
+      <c r="V80" s="8" t="inlineStr"/>
+      <c r="W80" s="8" t="inlineStr"/>
       <c r="X80" s="8" t="inlineStr"/>
-      <c r="Y80" s="8" t="inlineStr">
-        <is>
-          <t>4472.00</t>
-        </is>
-      </c>
+      <c r="Y80" s="9" t="inlineStr"/>
       <c r="Z80" s="9" t="inlineStr"/>
       <c r="AA80" s="8" t="inlineStr"/>
-      <c r="AB80" s="10" t="inlineStr"/>
-      <c r="AC80" s="11" t="inlineStr"/>
-      <c r="AD80" s="12" t="inlineStr"/>
+      <c r="AB80" s="8" t="inlineStr">
+        <is>
+          <t>4472.00</t>
+        </is>
+      </c>
+      <c r="AC80" s="9" t="inlineStr"/>
+      <c r="AD80" s="8" t="inlineStr"/>
+      <c r="AE80" s="10" t="inlineStr"/>
+      <c r="AF80" s="11" t="inlineStr"/>
+      <c r="AG80" s="12" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
@@ -5775,41 +6249,56 @@
           <t>2775.00</t>
         </is>
       </c>
-      <c r="T81" s="8" t="inlineStr"/>
-      <c r="U81" s="8" t="inlineStr"/>
-      <c r="V81" s="13" t="inlineStr">
+      <c r="T81" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="U81" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="V81" s="8" t="inlineStr"/>
+      <c r="W81" s="8" t="inlineStr"/>
+      <c r="X81" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="Y81" s="13" t="inlineStr">
         <is>
           <t>1437.00</t>
         </is>
       </c>
-      <c r="W81" s="13" t="inlineStr">
+      <c r="Z81" s="13" t="inlineStr">
         <is>
           <t>3061.00</t>
         </is>
       </c>
-      <c r="X81" s="15" t="inlineStr">
+      <c r="AA81" s="16" t="inlineStr">
         <is>
           <t>8373.00</t>
         </is>
       </c>
-      <c r="Y81" s="8" t="inlineStr">
+      <c r="AB81" s="8" t="inlineStr">
         <is>
           <t>7531.00</t>
         </is>
       </c>
-      <c r="Z81" s="9" t="inlineStr">
+      <c r="AC81" s="9" t="inlineStr">
         <is>
           <t>1005.00</t>
         </is>
       </c>
-      <c r="AA81" s="8" t="inlineStr"/>
-      <c r="AB81" s="10" t="n">
+      <c r="AD81" s="8" t="inlineStr"/>
+      <c r="AE81" s="10" t="n">
         <v>5765</v>
       </c>
-      <c r="AC81" s="10" t="n">
+      <c r="AF81" s="10" t="n">
         <v>955.5</v>
       </c>
-      <c r="AD81" s="12" t="n">
+      <c r="AG81" s="12" t="n">
         <v>0.4434080467771126</v>
       </c>
     </row>
@@ -5839,19 +6328,22 @@
       <c r="S82" s="9" t="inlineStr"/>
       <c r="T82" s="8" t="inlineStr"/>
       <c r="U82" s="8" t="inlineStr"/>
-      <c r="V82" s="9" t="inlineStr"/>
-      <c r="W82" s="9" t="inlineStr"/>
+      <c r="V82" s="8" t="inlineStr"/>
+      <c r="W82" s="8" t="inlineStr"/>
       <c r="X82" s="8" t="inlineStr"/>
-      <c r="Y82" s="8" t="inlineStr">
-        <is>
-          <t>5320.00</t>
-        </is>
-      </c>
+      <c r="Y82" s="9" t="inlineStr"/>
       <c r="Z82" s="9" t="inlineStr"/>
       <c r="AA82" s="8" t="inlineStr"/>
-      <c r="AB82" s="10" t="inlineStr"/>
-      <c r="AC82" s="11" t="inlineStr"/>
-      <c r="AD82" s="12" t="inlineStr"/>
+      <c r="AB82" s="8" t="inlineStr">
+        <is>
+          <t>5320.00</t>
+        </is>
+      </c>
+      <c r="AC82" s="9" t="inlineStr"/>
+      <c r="AD82" s="8" t="inlineStr"/>
+      <c r="AE82" s="10" t="inlineStr"/>
+      <c r="AF82" s="11" t="inlineStr"/>
+      <c r="AG82" s="12" t="inlineStr"/>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="1" t="n"/>
@@ -5879,19 +6371,22 @@
       <c r="S83" s="9" t="inlineStr"/>
       <c r="T83" s="8" t="inlineStr"/>
       <c r="U83" s="8" t="inlineStr"/>
-      <c r="V83" s="9" t="inlineStr"/>
-      <c r="W83" s="9" t="inlineStr"/>
+      <c r="V83" s="8" t="inlineStr"/>
+      <c r="W83" s="8" t="inlineStr"/>
       <c r="X83" s="8" t="inlineStr"/>
-      <c r="Y83" s="8" t="inlineStr">
-        <is>
-          <t>2516.00</t>
-        </is>
-      </c>
+      <c r="Y83" s="9" t="inlineStr"/>
       <c r="Z83" s="9" t="inlineStr"/>
       <c r="AA83" s="8" t="inlineStr"/>
-      <c r="AB83" s="10" t="inlineStr"/>
-      <c r="AC83" s="11" t="inlineStr"/>
-      <c r="AD83" s="12" t="inlineStr"/>
+      <c r="AB83" s="8" t="inlineStr">
+        <is>
+          <t>2516.00</t>
+        </is>
+      </c>
+      <c r="AC83" s="9" t="inlineStr"/>
+      <c r="AD83" s="8" t="inlineStr"/>
+      <c r="AE83" s="10" t="inlineStr"/>
+      <c r="AF83" s="11" t="inlineStr"/>
+      <c r="AG83" s="12" t="inlineStr"/>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -5931,11 +6426,14 @@
       <c r="Y84" s="4" t="inlineStr"/>
       <c r="Z84" s="4" t="inlineStr"/>
       <c r="AA84" s="4" t="inlineStr"/>
-      <c r="AB84" s="5" t="inlineStr"/>
-      <c r="AC84" s="6" t="n">
+      <c r="AB84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AD84" s="4" t="inlineStr"/>
+      <c r="AE84" s="5" t="inlineStr"/>
+      <c r="AF84" s="6" t="n">
         <v>741.625</v>
       </c>
-      <c r="AD84" s="7" t="n">
+      <c r="AG84" s="7" t="n">
         <v>0.02488724605193393</v>
       </c>
     </row>
@@ -5987,11 +6485,14 @@
       <c r="Y85" s="8" t="inlineStr"/>
       <c r="Z85" s="8" t="inlineStr"/>
       <c r="AA85" s="8" t="inlineStr"/>
-      <c r="AB85" s="10" t="n">
+      <c r="AB85" s="8" t="inlineStr"/>
+      <c r="AC85" s="8" t="inlineStr"/>
+      <c r="AD85" s="8" t="inlineStr"/>
+      <c r="AE85" s="10" t="n">
         <v>11785.625</v>
       </c>
-      <c r="AC85" s="11" t="inlineStr"/>
-      <c r="AD85" s="12" t="inlineStr"/>
+      <c r="AF85" s="11" t="inlineStr"/>
+      <c r="AG85" s="12" t="inlineStr"/>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="1" t="n"/>
@@ -6029,9 +6530,12 @@
       <c r="Y86" s="8" t="inlineStr"/>
       <c r="Z86" s="8" t="inlineStr"/>
       <c r="AA86" s="8" t="inlineStr"/>
-      <c r="AB86" s="10" t="inlineStr"/>
-      <c r="AC86" s="11" t="inlineStr"/>
-      <c r="AD86" s="12" t="inlineStr"/>
+      <c r="AB86" s="8" t="inlineStr"/>
+      <c r="AC86" s="8" t="inlineStr"/>
+      <c r="AD86" s="8" t="inlineStr"/>
+      <c r="AE86" s="10" t="inlineStr"/>
+      <c r="AF86" s="11" t="inlineStr"/>
+      <c r="AG86" s="12" t="inlineStr"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="1" t="n"/>
@@ -6081,13 +6585,16 @@
       <c r="Y87" s="8" t="inlineStr"/>
       <c r="Z87" s="8" t="inlineStr"/>
       <c r="AA87" s="8" t="inlineStr"/>
-      <c r="AB87" s="10" t="n">
+      <c r="AB87" s="8" t="inlineStr"/>
+      <c r="AC87" s="8" t="inlineStr"/>
+      <c r="AD87" s="8" t="inlineStr"/>
+      <c r="AE87" s="10" t="n">
         <v>13229.25</v>
       </c>
-      <c r="AC87" s="10" t="n">
+      <c r="AF87" s="10" t="n">
         <v>1443.625</v>
       </c>
-      <c r="AD87" s="12" t="n">
+      <c r="AG87" s="12" t="n">
         <v>0.04844476734430894</v>
       </c>
     </row>
@@ -6127,9 +6634,12 @@
       <c r="Y88" s="8" t="inlineStr"/>
       <c r="Z88" s="8" t="inlineStr"/>
       <c r="AA88" s="8" t="inlineStr"/>
-      <c r="AB88" s="10" t="inlineStr"/>
-      <c r="AC88" s="11" t="inlineStr"/>
-      <c r="AD88" s="12" t="inlineStr"/>
+      <c r="AB88" s="8" t="inlineStr"/>
+      <c r="AC88" s="8" t="inlineStr"/>
+      <c r="AD88" s="8" t="inlineStr"/>
+      <c r="AE88" s="10" t="inlineStr"/>
+      <c r="AF88" s="11" t="inlineStr"/>
+      <c r="AG88" s="12" t="inlineStr"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="1" t="n"/>
@@ -6167,9 +6677,12 @@
       <c r="Y89" s="8" t="inlineStr"/>
       <c r="Z89" s="8" t="inlineStr"/>
       <c r="AA89" s="8" t="inlineStr"/>
-      <c r="AB89" s="10" t="inlineStr"/>
-      <c r="AC89" s="11" t="inlineStr"/>
-      <c r="AD89" s="12" t="inlineStr"/>
+      <c r="AB89" s="8" t="inlineStr"/>
+      <c r="AC89" s="8" t="inlineStr"/>
+      <c r="AD89" s="8" t="inlineStr"/>
+      <c r="AE89" s="10" t="inlineStr"/>
+      <c r="AF89" s="11" t="inlineStr"/>
+      <c r="AG89" s="12" t="inlineStr"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -6209,11 +6722,14 @@
       <c r="Y90" s="4" t="inlineStr"/>
       <c r="Z90" s="4" t="inlineStr"/>
       <c r="AA90" s="4" t="inlineStr"/>
-      <c r="AB90" s="5" t="inlineStr"/>
-      <c r="AC90" s="6" t="n">
+      <c r="AB90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AD90" s="4" t="inlineStr"/>
+      <c r="AE90" s="5" t="inlineStr"/>
+      <c r="AF90" s="6" t="n">
         <v>-35.66666666666669</v>
       </c>
-      <c r="AD90" s="7" t="n">
+      <c r="AG90" s="7" t="n">
         <v>-0.1302654005356709</v>
       </c>
     </row>
@@ -6259,17 +6775,20 @@
       <c r="W91" s="8" t="inlineStr"/>
       <c r="X91" s="8" t="inlineStr"/>
       <c r="Y91" s="8" t="inlineStr"/>
-      <c r="Z91" s="8" t="inlineStr">
+      <c r="Z91" s="8" t="inlineStr"/>
+      <c r="AA91" s="8" t="inlineStr"/>
+      <c r="AB91" s="8" t="inlineStr"/>
+      <c r="AC91" s="8" t="inlineStr">
         <is>
           <t>365.00</t>
         </is>
       </c>
-      <c r="AA91" s="8" t="inlineStr"/>
-      <c r="AB91" s="10" t="n">
+      <c r="AD91" s="8" t="inlineStr"/>
+      <c r="AE91" s="10" t="n">
         <v>473.3333333333333</v>
       </c>
-      <c r="AC91" s="11" t="inlineStr"/>
-      <c r="AD91" s="12" t="inlineStr"/>
+      <c r="AF91" s="11" t="inlineStr"/>
+      <c r="AG91" s="12" t="inlineStr"/>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="1" t="n"/>
@@ -6307,9 +6826,12 @@
       <c r="Y92" s="8" t="inlineStr"/>
       <c r="Z92" s="8" t="inlineStr"/>
       <c r="AA92" s="8" t="inlineStr"/>
-      <c r="AB92" s="10" t="inlineStr"/>
-      <c r="AC92" s="11" t="inlineStr"/>
-      <c r="AD92" s="12" t="inlineStr"/>
+      <c r="AB92" s="8" t="inlineStr"/>
+      <c r="AC92" s="8" t="inlineStr"/>
+      <c r="AD92" s="8" t="inlineStr"/>
+      <c r="AE92" s="10" t="inlineStr"/>
+      <c r="AF92" s="11" t="inlineStr"/>
+      <c r="AG92" s="12" t="inlineStr"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
@@ -6318,7 +6840,7 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C93" s="14" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
@@ -6353,19 +6875,22 @@
       <c r="W93" s="8" t="inlineStr"/>
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="8" t="inlineStr"/>
-      <c r="Z93" s="8" t="inlineStr">
+      <c r="Z93" s="8" t="inlineStr"/>
+      <c r="AA93" s="8" t="inlineStr"/>
+      <c r="AB93" s="8" t="inlineStr"/>
+      <c r="AC93" s="8" t="inlineStr">
         <is>
           <t>375.00</t>
         </is>
       </c>
-      <c r="AA93" s="8" t="inlineStr"/>
-      <c r="AB93" s="10" t="n">
+      <c r="AD93" s="8" t="inlineStr"/>
+      <c r="AE93" s="10" t="n">
         <v>535.8333333333334</v>
       </c>
-      <c r="AC93" s="10" t="n">
+      <c r="AF93" s="10" t="n">
         <v>62.50000000000006</v>
       </c>
-      <c r="AD93" s="12" t="n">
+      <c r="AG93" s="12" t="n">
         <v>0.2282688093498906</v>
       </c>
     </row>
@@ -6407,11 +6932,14 @@
       <c r="Y94" s="4" t="inlineStr"/>
       <c r="Z94" s="4" t="inlineStr"/>
       <c r="AA94" s="4" t="inlineStr"/>
-      <c r="AB94" s="5" t="inlineStr"/>
-      <c r="AC94" s="6" t="n">
+      <c r="AB94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AD94" s="4" t="inlineStr"/>
+      <c r="AE94" s="5" t="inlineStr"/>
+      <c r="AF94" s="6" t="n">
         <v>-2611.333333333333</v>
       </c>
-      <c r="AD94" s="7" t="n">
+      <c r="AG94" s="7" t="n">
         <v>-0.8754050731925354</v>
       </c>
     </row>
@@ -6465,13 +6993,16 @@
       <c r="W95" s="8" t="inlineStr"/>
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="8" t="inlineStr"/>
-      <c r="Z95" s="9" t="inlineStr"/>
+      <c r="Z95" s="8" t="inlineStr"/>
       <c r="AA95" s="8" t="inlineStr"/>
-      <c r="AB95" s="10" t="n">
+      <c r="AB95" s="8" t="inlineStr"/>
+      <c r="AC95" s="9" t="inlineStr"/>
+      <c r="AD95" s="8" t="inlineStr"/>
+      <c r="AE95" s="10" t="n">
         <v>1596.666666666667</v>
       </c>
-      <c r="AC95" s="11" t="inlineStr"/>
-      <c r="AD95" s="12" t="inlineStr"/>
+      <c r="AF95" s="11" t="inlineStr"/>
+      <c r="AG95" s="12" t="inlineStr"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="1" t="n"/>
@@ -6515,11 +7046,14 @@
       <c r="W96" s="8" t="inlineStr"/>
       <c r="X96" s="8" t="inlineStr"/>
       <c r="Y96" s="8" t="inlineStr"/>
-      <c r="Z96" s="9" t="inlineStr"/>
+      <c r="Z96" s="8" t="inlineStr"/>
       <c r="AA96" s="8" t="inlineStr"/>
-      <c r="AB96" s="10" t="inlineStr"/>
-      <c r="AC96" s="11" t="inlineStr"/>
-      <c r="AD96" s="12" t="inlineStr"/>
+      <c r="AB96" s="8" t="inlineStr"/>
+      <c r="AC96" s="9" t="inlineStr"/>
+      <c r="AD96" s="8" t="inlineStr"/>
+      <c r="AE96" s="10" t="inlineStr"/>
+      <c r="AF96" s="11" t="inlineStr"/>
+      <c r="AG96" s="12" t="inlineStr"/>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="1" t="n"/>
@@ -6528,7 +7062,11 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C97" s="8" t="inlineStr"/>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="D97" s="8" t="inlineStr"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
@@ -6558,36 +7096,43 @@
           <t>760.00</t>
         </is>
       </c>
-      <c r="Q97" s="14" t="inlineStr">
+      <c r="Q97" s="15" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="R97" s="15" t="inlineStr">
+      <c r="R97" s="16" t="inlineStr">
         <is>
           <t>2900.00</t>
         </is>
       </c>
-      <c r="S97" s="8" t="inlineStr"/>
+      <c r="S97" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr"/>
       <c r="X97" s="8" t="inlineStr"/>
       <c r="Y97" s="8" t="inlineStr"/>
-      <c r="Z97" s="13" t="inlineStr">
+      <c r="Z97" s="8" t="inlineStr"/>
+      <c r="AA97" s="8" t="inlineStr"/>
+      <c r="AB97" s="8" t="inlineStr"/>
+      <c r="AC97" s="13" t="inlineStr">
         <is>
           <t>1760.00</t>
         </is>
       </c>
-      <c r="AA97" s="8" t="inlineStr"/>
-      <c r="AB97" s="10" t="n">
+      <c r="AD97" s="8" t="inlineStr"/>
+      <c r="AE97" s="10" t="n">
         <v>1673.333333333333</v>
       </c>
-      <c r="AC97" s="10" t="n">
+      <c r="AF97" s="10" t="n">
         <v>76.66666666666652</v>
       </c>
-      <c r="AD97" s="12" t="n">
+      <c r="AG97" s="12" t="n">
         <v>0.02570119566431998</v>
       </c>
     </row>
@@ -6629,11 +7174,14 @@
       <c r="Y98" s="4" t="inlineStr"/>
       <c r="Z98" s="4" t="inlineStr"/>
       <c r="AA98" s="4" t="inlineStr"/>
-      <c r="AB98" s="5" t="inlineStr"/>
-      <c r="AC98" s="6" t="n">
+      <c r="AB98" s="4" t="inlineStr"/>
+      <c r="AC98" s="4" t="inlineStr"/>
+      <c r="AD98" s="4" t="inlineStr"/>
+      <c r="AE98" s="5" t="inlineStr"/>
+      <c r="AF98" s="6" t="n">
         <v>-2583.375</v>
       </c>
-      <c r="AD98" s="7" t="n">
+      <c r="AG98" s="7" t="n">
         <v>-2.420023419203747</v>
       </c>
     </row>
@@ -6695,17 +7243,20 @@
       <c r="W99" s="8" t="inlineStr"/>
       <c r="X99" s="8" t="inlineStr"/>
       <c r="Y99" s="8" t="inlineStr"/>
-      <c r="Z99" s="8" t="inlineStr">
+      <c r="Z99" s="8" t="inlineStr"/>
+      <c r="AA99" s="8" t="inlineStr"/>
+      <c r="AB99" s="8" t="inlineStr"/>
+      <c r="AC99" s="8" t="inlineStr">
         <is>
           <t>6289.00</t>
         </is>
       </c>
-      <c r="AA99" s="8" t="inlineStr"/>
-      <c r="AB99" s="10" t="n">
+      <c r="AD99" s="8" t="inlineStr"/>
+      <c r="AE99" s="10" t="n">
         <v>5829.625</v>
       </c>
-      <c r="AC99" s="11" t="inlineStr"/>
-      <c r="AD99" s="12" t="inlineStr"/>
+      <c r="AF99" s="11" t="inlineStr"/>
+      <c r="AG99" s="12" t="inlineStr"/>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="1" t="n"/>
@@ -6745,15 +7296,18 @@
       <c r="W100" s="8" t="inlineStr"/>
       <c r="X100" s="8" t="inlineStr"/>
       <c r="Y100" s="8" t="inlineStr"/>
-      <c r="Z100" s="8" t="inlineStr">
+      <c r="Z100" s="8" t="inlineStr"/>
+      <c r="AA100" s="8" t="inlineStr"/>
+      <c r="AB100" s="8" t="inlineStr"/>
+      <c r="AC100" s="8" t="inlineStr">
         <is>
           <t>6587.00</t>
         </is>
       </c>
-      <c r="AA100" s="8" t="inlineStr"/>
-      <c r="AB100" s="10" t="inlineStr"/>
-      <c r="AC100" s="11" t="inlineStr"/>
-      <c r="AD100" s="12" t="inlineStr"/>
+      <c r="AD100" s="8" t="inlineStr"/>
+      <c r="AE100" s="10" t="inlineStr"/>
+      <c r="AF100" s="11" t="inlineStr"/>
+      <c r="AG100" s="12" t="inlineStr"/>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="1" t="n"/>
@@ -6762,7 +7316,11 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr"/>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="D101" s="8" t="inlineStr"/>
       <c r="E101" s="8" t="inlineStr">
         <is>
@@ -6806,30 +7364,45 @@
           <t>5596.50</t>
         </is>
       </c>
-      <c r="S101" s="15" t="inlineStr">
+      <c r="S101" s="16" t="inlineStr">
         <is>
           <t>6424.00</t>
         </is>
       </c>
-      <c r="T101" s="8" t="inlineStr"/>
-      <c r="U101" s="8" t="inlineStr"/>
+      <c r="T101" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="U101" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="V101" s="8" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr"/>
       <c r="X101" s="8" t="inlineStr"/>
       <c r="Y101" s="8" t="inlineStr"/>
-      <c r="Z101" s="8" t="inlineStr">
+      <c r="Z101" s="8" t="inlineStr"/>
+      <c r="AA101" s="8" t="inlineStr"/>
+      <c r="AB101" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="AC101" s="8" t="inlineStr">
         <is>
           <t>6796.50</t>
         </is>
       </c>
-      <c r="AA101" s="8" t="inlineStr"/>
-      <c r="AB101" s="10" t="n">
+      <c r="AD101" s="8" t="inlineStr"/>
+      <c r="AE101" s="10" t="n">
         <v>6662.25</v>
       </c>
-      <c r="AC101" s="10" t="n">
+      <c r="AF101" s="10" t="n">
         <v>832.625</v>
       </c>
-      <c r="AD101" s="12" t="n">
+      <c r="AG101" s="12" t="n">
         <v>0.779976580796253</v>
       </c>
     </row>
@@ -6871,11 +7444,14 @@
       <c r="Y102" s="4" t="inlineStr"/>
       <c r="Z102" s="4" t="inlineStr"/>
       <c r="AA102" s="4" t="inlineStr"/>
-      <c r="AB102" s="5" t="inlineStr"/>
-      <c r="AC102" s="6" t="n">
+      <c r="AB102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AD102" s="4" t="inlineStr"/>
+      <c r="AE102" s="5" t="inlineStr"/>
+      <c r="AF102" s="6" t="n">
         <v>-1044.5</v>
       </c>
-      <c r="AD102" s="7" t="n">
+      <c r="AG102" s="7" t="n">
         <v>-0.04646807071866464</v>
       </c>
     </row>
@@ -6923,11 +7499,14 @@
       <c r="Y103" s="8" t="inlineStr"/>
       <c r="Z103" s="8" t="inlineStr"/>
       <c r="AA103" s="8" t="inlineStr"/>
-      <c r="AB103" s="10" t="n">
+      <c r="AB103" s="8" t="inlineStr"/>
+      <c r="AC103" s="8" t="inlineStr"/>
+      <c r="AD103" s="8" t="inlineStr"/>
+      <c r="AE103" s="10" t="n">
         <v>25137.5</v>
       </c>
-      <c r="AC103" s="11" t="inlineStr"/>
-      <c r="AD103" s="12" t="inlineStr"/>
+      <c r="AF103" s="11" t="inlineStr"/>
+      <c r="AG103" s="12" t="inlineStr"/>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="1" t="n"/>
@@ -6965,9 +7544,12 @@
       <c r="Y104" s="8" t="inlineStr"/>
       <c r="Z104" s="8" t="inlineStr"/>
       <c r="AA104" s="8" t="inlineStr"/>
-      <c r="AB104" s="10" t="inlineStr"/>
-      <c r="AC104" s="11" t="inlineStr"/>
-      <c r="AD104" s="12" t="inlineStr"/>
+      <c r="AB104" s="8" t="inlineStr"/>
+      <c r="AC104" s="8" t="inlineStr"/>
+      <c r="AD104" s="8" t="inlineStr"/>
+      <c r="AE104" s="10" t="inlineStr"/>
+      <c r="AF104" s="11" t="inlineStr"/>
+      <c r="AG104" s="12" t="inlineStr"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
@@ -6993,7 +7575,7 @@
           <t>20245.00</t>
         </is>
       </c>
-      <c r="L105" s="14" t="inlineStr">
+      <c r="L105" s="15" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
@@ -7013,13 +7595,16 @@
       <c r="Y105" s="8" t="inlineStr"/>
       <c r="Z105" s="8" t="inlineStr"/>
       <c r="AA105" s="8" t="inlineStr"/>
-      <c r="AB105" s="10" t="n">
+      <c r="AB105" s="8" t="inlineStr"/>
+      <c r="AC105" s="8" t="inlineStr"/>
+      <c r="AD105" s="8" t="inlineStr"/>
+      <c r="AE105" s="10" t="n">
         <v>25177.5</v>
       </c>
-      <c r="AC105" s="10" t="n">
+      <c r="AF105" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="AD105" s="12" t="n">
+      <c r="AG105" s="12" t="n">
         <v>0.001779533584247569</v>
       </c>
     </row>
@@ -7059,9 +7644,12 @@
       <c r="Y106" s="8" t="inlineStr"/>
       <c r="Z106" s="8" t="inlineStr"/>
       <c r="AA106" s="8" t="inlineStr"/>
-      <c r="AB106" s="10" t="inlineStr"/>
-      <c r="AC106" s="11" t="inlineStr"/>
-      <c r="AD106" s="12" t="inlineStr"/>
+      <c r="AB106" s="8" t="inlineStr"/>
+      <c r="AC106" s="8" t="inlineStr"/>
+      <c r="AD106" s="8" t="inlineStr"/>
+      <c r="AE106" s="10" t="inlineStr"/>
+      <c r="AF106" s="11" t="inlineStr"/>
+      <c r="AG106" s="12" t="inlineStr"/>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="1" t="n"/>
@@ -7099,9 +7687,12 @@
       <c r="Y107" s="8" t="inlineStr"/>
       <c r="Z107" s="8" t="inlineStr"/>
       <c r="AA107" s="8" t="inlineStr"/>
-      <c r="AB107" s="10" t="inlineStr"/>
-      <c r="AC107" s="11" t="inlineStr"/>
-      <c r="AD107" s="12" t="inlineStr"/>
+      <c r="AB107" s="8" t="inlineStr"/>
+      <c r="AC107" s="8" t="inlineStr"/>
+      <c r="AD107" s="8" t="inlineStr"/>
+      <c r="AE107" s="10" t="inlineStr"/>
+      <c r="AF107" s="11" t="inlineStr"/>
+      <c r="AG107" s="12" t="inlineStr"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -7141,11 +7732,14 @@
       <c r="Y108" s="4" t="inlineStr"/>
       <c r="Z108" s="4" t="inlineStr"/>
       <c r="AA108" s="4" t="inlineStr"/>
-      <c r="AB108" s="5" t="inlineStr"/>
-      <c r="AC108" s="6" t="n">
+      <c r="AB108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AD108" s="4" t="inlineStr"/>
+      <c r="AE108" s="5" t="inlineStr"/>
+      <c r="AF108" s="6" t="n">
         <v>-699.3333333333333</v>
       </c>
-      <c r="AD108" s="7" t="n">
+      <c r="AG108" s="7" t="n">
         <v>-0.1052531242317977</v>
       </c>
     </row>
@@ -7201,11 +7795,14 @@
       <c r="Y109" s="8" t="inlineStr"/>
       <c r="Z109" s="8" t="inlineStr"/>
       <c r="AA109" s="8" t="inlineStr"/>
-      <c r="AB109" s="10" t="n">
+      <c r="AB109" s="8" t="inlineStr"/>
+      <c r="AC109" s="8" t="inlineStr"/>
+      <c r="AD109" s="8" t="inlineStr"/>
+      <c r="AE109" s="10" t="n">
         <v>1973.666666666667</v>
       </c>
-      <c r="AC109" s="11" t="inlineStr"/>
-      <c r="AD109" s="12" t="inlineStr"/>
+      <c r="AF109" s="11" t="inlineStr"/>
+      <c r="AG109" s="12" t="inlineStr"/>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="1" t="n"/>
@@ -7243,9 +7840,12 @@
       <c r="Y110" s="8" t="inlineStr"/>
       <c r="Z110" s="8" t="inlineStr"/>
       <c r="AA110" s="8" t="inlineStr"/>
-      <c r="AB110" s="10" t="inlineStr"/>
-      <c r="AC110" s="11" t="inlineStr"/>
-      <c r="AD110" s="12" t="inlineStr"/>
+      <c r="AB110" s="8" t="inlineStr"/>
+      <c r="AC110" s="8" t="inlineStr"/>
+      <c r="AD110" s="8" t="inlineStr"/>
+      <c r="AE110" s="10" t="inlineStr"/>
+      <c r="AF110" s="11" t="inlineStr"/>
+      <c r="AG110" s="12" t="inlineStr"/>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="1" t="n"/>
@@ -7291,13 +7891,16 @@
       <c r="Y111" s="8" t="inlineStr"/>
       <c r="Z111" s="8" t="inlineStr"/>
       <c r="AA111" s="8" t="inlineStr"/>
-      <c r="AB111" s="10" t="n">
+      <c r="AB111" s="8" t="inlineStr"/>
+      <c r="AC111" s="8" t="inlineStr"/>
+      <c r="AD111" s="8" t="inlineStr"/>
+      <c r="AE111" s="10" t="n">
         <v>2007.166666666667</v>
       </c>
-      <c r="AC111" s="10" t="n">
+      <c r="AF111" s="10" t="n">
         <v>33.5</v>
       </c>
-      <c r="AD111" s="12" t="n">
+      <c r="AG111" s="12" t="n">
         <v>0.005041915626928344</v>
       </c>
     </row>
@@ -7341,9 +7944,12 @@
       <c r="Y112" s="8" t="inlineStr"/>
       <c r="Z112" s="8" t="inlineStr"/>
       <c r="AA112" s="8" t="inlineStr"/>
-      <c r="AB112" s="10" t="inlineStr"/>
-      <c r="AC112" s="11" t="inlineStr"/>
-      <c r="AD112" s="12" t="inlineStr"/>
+      <c r="AB112" s="8" t="inlineStr"/>
+      <c r="AC112" s="8" t="inlineStr"/>
+      <c r="AD112" s="8" t="inlineStr"/>
+      <c r="AE112" s="10" t="inlineStr"/>
+      <c r="AF112" s="11" t="inlineStr"/>
+      <c r="AG112" s="12" t="inlineStr"/>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="1" t="n"/>
@@ -7385,9 +7991,12 @@
       <c r="Y113" s="8" t="inlineStr"/>
       <c r="Z113" s="8" t="inlineStr"/>
       <c r="AA113" s="8" t="inlineStr"/>
-      <c r="AB113" s="10" t="inlineStr"/>
-      <c r="AC113" s="11" t="inlineStr"/>
-      <c r="AD113" s="12" t="inlineStr"/>
+      <c r="AB113" s="8" t="inlineStr"/>
+      <c r="AC113" s="8" t="inlineStr"/>
+      <c r="AD113" s="8" t="inlineStr"/>
+      <c r="AE113" s="10" t="inlineStr"/>
+      <c r="AF113" s="11" t="inlineStr"/>
+      <c r="AG113" s="12" t="inlineStr"/>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -7427,11 +8036,14 @@
       <c r="Y114" s="4" t="inlineStr"/>
       <c r="Z114" s="4" t="inlineStr"/>
       <c r="AA114" s="4" t="inlineStr"/>
-      <c r="AB114" s="5" t="inlineStr"/>
-      <c r="AC114" s="6" t="n">
+      <c r="AB114" s="4" t="inlineStr"/>
+      <c r="AC114" s="4" t="inlineStr"/>
+      <c r="AD114" s="4" t="inlineStr"/>
+      <c r="AE114" s="5" t="inlineStr"/>
+      <c r="AF114" s="6" t="n">
         <v>-5.4</v>
       </c>
-      <c r="AD114" s="7" t="n">
+      <c r="AG114" s="7" t="n">
         <v>-0.1529745042492918</v>
       </c>
     </row>
@@ -7483,11 +8095,14 @@
       <c r="Y115" s="8" t="inlineStr"/>
       <c r="Z115" s="8" t="inlineStr"/>
       <c r="AA115" s="8" t="inlineStr"/>
-      <c r="AB115" s="10" t="n">
+      <c r="AB115" s="8" t="inlineStr"/>
+      <c r="AC115" s="8" t="inlineStr"/>
+      <c r="AD115" s="8" t="inlineStr"/>
+      <c r="AE115" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="AC115" s="11" t="inlineStr"/>
-      <c r="AD115" s="12" t="inlineStr"/>
+      <c r="AF115" s="11" t="inlineStr"/>
+      <c r="AG115" s="12" t="inlineStr"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="1" t="n"/>
@@ -7535,19 +8150,22 @@
       <c r="W116" s="8" t="inlineStr"/>
       <c r="X116" s="8" t="inlineStr"/>
       <c r="Y116" s="8" t="inlineStr"/>
-      <c r="Z116" s="15" t="inlineStr">
+      <c r="Z116" s="8" t="inlineStr"/>
+      <c r="AA116" s="8" t="inlineStr"/>
+      <c r="AB116" s="8" t="inlineStr"/>
+      <c r="AC116" s="16" t="inlineStr">
         <is>
           <t>16.30</t>
         </is>
       </c>
-      <c r="AA116" s="8" t="inlineStr"/>
-      <c r="AB116" s="10" t="n">
+      <c r="AD116" s="8" t="inlineStr"/>
+      <c r="AE116" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="AC116" s="10" t="n">
+      <c r="AF116" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="AD116" s="12" t="n">
+      <c r="AG116" s="12" t="n">
         <v>0.09631728045325781</v>
       </c>
     </row>
@@ -7587,9 +8205,12 @@
       <c r="Y117" s="8" t="inlineStr"/>
       <c r="Z117" s="8" t="inlineStr"/>
       <c r="AA117" s="8" t="inlineStr"/>
-      <c r="AB117" s="10" t="inlineStr"/>
-      <c r="AC117" s="11" t="inlineStr"/>
-      <c r="AD117" s="12" t="inlineStr"/>
+      <c r="AB117" s="8" t="inlineStr"/>
+      <c r="AC117" s="8" t="inlineStr"/>
+      <c r="AD117" s="8" t="inlineStr"/>
+      <c r="AE117" s="10" t="inlineStr"/>
+      <c r="AF117" s="11" t="inlineStr"/>
+      <c r="AG117" s="12" t="inlineStr"/>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -7629,11 +8250,14 @@
       <c r="Y118" s="4" t="inlineStr"/>
       <c r="Z118" s="4" t="inlineStr"/>
       <c r="AA118" s="4" t="inlineStr"/>
-      <c r="AB118" s="5" t="inlineStr"/>
-      <c r="AC118" s="6" t="n">
+      <c r="AB118" s="4" t="inlineStr"/>
+      <c r="AC118" s="4" t="inlineStr"/>
+      <c r="AD118" s="4" t="inlineStr"/>
+      <c r="AE118" s="5" t="inlineStr"/>
+      <c r="AF118" s="6" t="n">
         <v>-6778.35</v>
       </c>
-      <c r="AD118" s="7" t="n">
+      <c r="AG118" s="7" t="n">
         <v>-0.09746514557187719</v>
       </c>
     </row>
@@ -7687,17 +8311,20 @@
       <c r="W119" s="8" t="inlineStr"/>
       <c r="X119" s="8" t="inlineStr"/>
       <c r="Y119" s="8" t="inlineStr"/>
-      <c r="Z119" s="8" t="inlineStr">
+      <c r="Z119" s="8" t="inlineStr"/>
+      <c r="AA119" s="8" t="inlineStr"/>
+      <c r="AB119" s="8" t="inlineStr"/>
+      <c r="AC119" s="8" t="inlineStr">
         <is>
           <t>159.50</t>
         </is>
       </c>
-      <c r="AA119" s="8" t="inlineStr"/>
-      <c r="AB119" s="10" t="n">
+      <c r="AD119" s="8" t="inlineStr"/>
+      <c r="AE119" s="10" t="n">
         <v>1002.65</v>
       </c>
-      <c r="AC119" s="11" t="inlineStr"/>
-      <c r="AD119" s="12" t="inlineStr"/>
+      <c r="AF119" s="11" t="inlineStr"/>
+      <c r="AG119" s="12" t="inlineStr"/>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="1" t="n"/>
@@ -7749,19 +8376,22 @@
       <c r="W120" s="8" t="inlineStr"/>
       <c r="X120" s="8" t="inlineStr"/>
       <c r="Y120" s="8" t="inlineStr"/>
-      <c r="Z120" s="8" t="inlineStr">
+      <c r="Z120" s="8" t="inlineStr"/>
+      <c r="AA120" s="8" t="inlineStr"/>
+      <c r="AB120" s="8" t="inlineStr"/>
+      <c r="AC120" s="8" t="inlineStr">
         <is>
           <t>153.20</t>
         </is>
       </c>
-      <c r="AA120" s="8" t="inlineStr"/>
-      <c r="AB120" s="10" t="n">
+      <c r="AD120" s="8" t="inlineStr"/>
+      <c r="AE120" s="10" t="n">
         <v>152.9875</v>
       </c>
-      <c r="AC120" s="10" t="n">
+      <c r="AF120" s="10" t="n">
         <v>849.6624999999999</v>
       </c>
-      <c r="AD120" s="12" t="n">
+      <c r="AG120" s="12" t="n">
         <v>-0.01221720319096315</v>
       </c>
     </row>
@@ -7803,11 +8433,14 @@
       <c r="Y121" s="4" t="inlineStr"/>
       <c r="Z121" s="4" t="inlineStr"/>
       <c r="AA121" s="4" t="inlineStr"/>
-      <c r="AB121" s="5" t="inlineStr"/>
-      <c r="AC121" s="6" t="n">
+      <c r="AB121" s="4" t="inlineStr"/>
+      <c r="AC121" s="4" t="inlineStr"/>
+      <c r="AD121" s="4" t="inlineStr"/>
+      <c r="AE121" s="5" t="inlineStr"/>
+      <c r="AF121" s="6" t="n">
         <v>-1662.9375</v>
       </c>
-      <c r="AD121" s="7" t="n">
+      <c r="AG121" s="7" t="n">
         <v>-0.1251166193919239</v>
       </c>
     </row>
@@ -7863,11 +8496,14 @@
       <c r="Y122" s="8" t="inlineStr"/>
       <c r="Z122" s="8" t="inlineStr"/>
       <c r="AA122" s="8" t="inlineStr"/>
-      <c r="AB122" s="10" t="n">
+      <c r="AB122" s="8" t="inlineStr"/>
+      <c r="AC122" s="8" t="inlineStr"/>
+      <c r="AD122" s="8" t="inlineStr"/>
+      <c r="AE122" s="10" t="n">
         <v>2859.0625</v>
       </c>
-      <c r="AC122" s="11" t="inlineStr"/>
-      <c r="AD122" s="12" t="inlineStr"/>
+      <c r="AF122" s="11" t="inlineStr"/>
+      <c r="AG122" s="12" t="inlineStr"/>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="1" t="n"/>
@@ -7917,9 +8553,12 @@
       <c r="Y123" s="8" t="inlineStr"/>
       <c r="Z123" s="8" t="inlineStr"/>
       <c r="AA123" s="8" t="inlineStr"/>
-      <c r="AB123" s="10" t="inlineStr"/>
-      <c r="AC123" s="11" t="inlineStr"/>
-      <c r="AD123" s="12" t="inlineStr"/>
+      <c r="AB123" s="8" t="inlineStr"/>
+      <c r="AC123" s="8" t="inlineStr"/>
+      <c r="AD123" s="8" t="inlineStr"/>
+      <c r="AE123" s="10" t="inlineStr"/>
+      <c r="AF123" s="11" t="inlineStr"/>
+      <c r="AG123" s="12" t="inlineStr"/>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="1" t="n"/>
@@ -7977,13 +8616,16 @@
       <c r="Y124" s="8" t="inlineStr"/>
       <c r="Z124" s="8" t="inlineStr"/>
       <c r="AA124" s="8" t="inlineStr"/>
-      <c r="AB124" s="10" t="n">
+      <c r="AB124" s="8" t="inlineStr"/>
+      <c r="AC124" s="8" t="inlineStr"/>
+      <c r="AD124" s="8" t="inlineStr"/>
+      <c r="AE124" s="10" t="n">
         <v>3065.625</v>
       </c>
-      <c r="AC124" s="10" t="n">
+      <c r="AF124" s="10" t="n">
         <v>206.5625</v>
       </c>
-      <c r="AD124" s="12" t="n">
+      <c r="AG124" s="12" t="n">
         <v>0.01554141493179646</v>
       </c>
     </row>
@@ -8025,11 +8667,14 @@
       <c r="Y125" s="4" t="inlineStr"/>
       <c r="Z125" s="4" t="inlineStr"/>
       <c r="AA125" s="4" t="inlineStr"/>
-      <c r="AB125" s="5" t="inlineStr"/>
-      <c r="AC125" s="6" t="n">
+      <c r="AB125" s="4" t="inlineStr"/>
+      <c r="AC125" s="4" t="inlineStr"/>
+      <c r="AD125" s="4" t="inlineStr"/>
+      <c r="AE125" s="5" t="inlineStr"/>
+      <c r="AF125" s="6" t="n">
         <v>-5012.333333333334</v>
       </c>
-      <c r="AD125" s="7" t="n">
+      <c r="AG125" s="7" t="n">
         <v>-0.6398587264100765</v>
       </c>
     </row>
@@ -8076,7 +8721,11 @@
           <t>17810.00</t>
         </is>
       </c>
-      <c r="S126" s="8" t="inlineStr"/>
+      <c r="S126" s="17" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="T126" s="8" t="inlineStr"/>
       <c r="U126" s="8" t="inlineStr"/>
       <c r="V126" s="8" t="inlineStr"/>
@@ -8085,11 +8734,14 @@
       <c r="Y126" s="8" t="inlineStr"/>
       <c r="Z126" s="8" t="inlineStr"/>
       <c r="AA126" s="8" t="inlineStr"/>
-      <c r="AB126" s="10" t="n">
+      <c r="AB126" s="8" t="inlineStr"/>
+      <c r="AC126" s="8" t="inlineStr"/>
+      <c r="AD126" s="8" t="inlineStr"/>
+      <c r="AE126" s="10" t="n">
         <v>12551.66666666667</v>
       </c>
-      <c r="AC126" s="11" t="inlineStr"/>
-      <c r="AD126" s="12" t="inlineStr"/>
+      <c r="AF126" s="11" t="inlineStr"/>
+      <c r="AG126" s="12" t="inlineStr"/>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="1" t="n"/>
@@ -8135,9 +8787,12 @@
       <c r="Y127" s="8" t="inlineStr"/>
       <c r="Z127" s="8" t="inlineStr"/>
       <c r="AA127" s="8" t="inlineStr"/>
-      <c r="AB127" s="10" t="inlineStr"/>
-      <c r="AC127" s="11" t="inlineStr"/>
-      <c r="AD127" s="12" t="inlineStr"/>
+      <c r="AB127" s="8" t="inlineStr"/>
+      <c r="AC127" s="8" t="inlineStr"/>
+      <c r="AD127" s="8" t="inlineStr"/>
+      <c r="AE127" s="10" t="inlineStr"/>
+      <c r="AF127" s="11" t="inlineStr"/>
+      <c r="AG127" s="12" t="inlineStr"/>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="1" t="n"/>
@@ -8177,35 +8832,46 @@
           <t>16980.00</t>
         </is>
       </c>
-      <c r="R128" s="15" t="inlineStr">
+      <c r="R128" s="16" t="inlineStr">
         <is>
           <t>16410.00</t>
         </is>
       </c>
-      <c r="S128" s="15" t="inlineStr">
+      <c r="S128" s="16" t="inlineStr">
         <is>
           <t>18865.00</t>
         </is>
       </c>
-      <c r="T128" s="14" t="inlineStr">
+      <c r="T128" s="15" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="U128" s="8" t="inlineStr"/>
+      <c r="U128" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="V128" s="8" t="inlineStr"/>
       <c r="W128" s="8" t="inlineStr"/>
       <c r="X128" s="8" t="inlineStr"/>
       <c r="Y128" s="8" t="inlineStr"/>
       <c r="Z128" s="8" t="inlineStr"/>
       <c r="AA128" s="8" t="inlineStr"/>
-      <c r="AB128" s="10" t="n">
+      <c r="AB128" s="8" t="inlineStr"/>
+      <c r="AC128" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="AD128" s="8" t="inlineStr"/>
+      <c r="AE128" s="10" t="n">
         <v>15426.66666666667</v>
       </c>
-      <c r="AC128" s="10" t="n">
+      <c r="AF128" s="10" t="n">
         <v>2875</v>
       </c>
-      <c r="AD128" s="12" t="n">
+      <c r="AG128" s="12" t="n">
         <v>0.3670134677985575</v>
       </c>
     </row>
@@ -8247,11 +8913,14 @@
       <c r="Y129" s="4" t="inlineStr"/>
       <c r="Z129" s="4" t="inlineStr"/>
       <c r="AA129" s="4" t="inlineStr"/>
-      <c r="AB129" s="5" t="inlineStr"/>
-      <c r="AC129" s="6" t="n">
+      <c r="AB129" s="4" t="inlineStr"/>
+      <c r="AC129" s="4" t="inlineStr"/>
+      <c r="AD129" s="4" t="inlineStr"/>
+      <c r="AE129" s="5" t="inlineStr"/>
+      <c r="AF129" s="6" t="n">
         <v>-64.33333333333331</v>
       </c>
-      <c r="AD129" s="7" t="n">
+      <c r="AG129" s="7" t="n">
         <v>-0.001532245835744834</v>
       </c>
     </row>
@@ -8297,17 +8966,20 @@
       <c r="W130" s="8" t="inlineStr"/>
       <c r="X130" s="8" t="inlineStr"/>
       <c r="Y130" s="8" t="inlineStr"/>
-      <c r="Z130" s="8" t="inlineStr">
+      <c r="Z130" s="8" t="inlineStr"/>
+      <c r="AA130" s="8" t="inlineStr"/>
+      <c r="AB130" s="8" t="inlineStr"/>
+      <c r="AC130" s="8" t="inlineStr">
         <is>
           <t>470.00</t>
         </is>
       </c>
-      <c r="AA130" s="8" t="inlineStr"/>
-      <c r="AB130" s="10" t="n">
+      <c r="AD130" s="8" t="inlineStr"/>
+      <c r="AE130" s="10" t="n">
         <v>460.6666666666667</v>
       </c>
-      <c r="AC130" s="11" t="inlineStr"/>
-      <c r="AD130" s="12" t="inlineStr"/>
+      <c r="AF130" s="11" t="inlineStr"/>
+      <c r="AG130" s="12" t="inlineStr"/>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="1" t="n"/>
@@ -8343,15 +9015,18 @@
       <c r="W131" s="8" t="inlineStr"/>
       <c r="X131" s="8" t="inlineStr"/>
       <c r="Y131" s="8" t="inlineStr"/>
-      <c r="Z131" s="8" t="inlineStr">
+      <c r="Z131" s="8" t="inlineStr"/>
+      <c r="AA131" s="8" t="inlineStr"/>
+      <c r="AB131" s="8" t="inlineStr"/>
+      <c r="AC131" s="8" t="inlineStr">
         <is>
           <t>557.00</t>
         </is>
       </c>
-      <c r="AA131" s="8" t="inlineStr"/>
-      <c r="AB131" s="10" t="inlineStr"/>
-      <c r="AC131" s="11" t="inlineStr"/>
-      <c r="AD131" s="12" t="inlineStr"/>
+      <c r="AD131" s="8" t="inlineStr"/>
+      <c r="AE131" s="10" t="inlineStr"/>
+      <c r="AF131" s="11" t="inlineStr"/>
+      <c r="AG131" s="12" t="inlineStr"/>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="1" t="n"/>
@@ -8391,19 +9066,22 @@
       <c r="W132" s="8" t="inlineStr"/>
       <c r="X132" s="8" t="inlineStr"/>
       <c r="Y132" s="8" t="inlineStr"/>
-      <c r="Z132" s="8" t="inlineStr">
+      <c r="Z132" s="8" t="inlineStr"/>
+      <c r="AA132" s="8" t="inlineStr"/>
+      <c r="AB132" s="8" t="inlineStr"/>
+      <c r="AC132" s="8" t="inlineStr">
         <is>
           <t>545.00</t>
         </is>
       </c>
-      <c r="AA132" s="8" t="inlineStr"/>
-      <c r="AB132" s="10" t="n">
+      <c r="AD132" s="8" t="inlineStr"/>
+      <c r="AE132" s="10" t="n">
         <v>505.3333333333333</v>
       </c>
-      <c r="AC132" s="10" t="n">
+      <c r="AF132" s="10" t="n">
         <v>44.66666666666663</v>
       </c>
-      <c r="AD132" s="12" t="n">
+      <c r="AG132" s="12" t="n">
         <v>0.001063839077667397</v>
       </c>
     </row>
@@ -8437,15 +9115,18 @@
       <c r="W133" s="8" t="inlineStr"/>
       <c r="X133" s="8" t="inlineStr"/>
       <c r="Y133" s="8" t="inlineStr"/>
-      <c r="Z133" s="8" t="inlineStr">
+      <c r="Z133" s="8" t="inlineStr"/>
+      <c r="AA133" s="8" t="inlineStr"/>
+      <c r="AB133" s="8" t="inlineStr"/>
+      <c r="AC133" s="8" t="inlineStr">
         <is>
           <t>411.00</t>
         </is>
       </c>
-      <c r="AA133" s="8" t="inlineStr"/>
-      <c r="AB133" s="10" t="inlineStr"/>
-      <c r="AC133" s="11" t="inlineStr"/>
-      <c r="AD133" s="12" t="inlineStr"/>
+      <c r="AD133" s="8" t="inlineStr"/>
+      <c r="AE133" s="10" t="inlineStr"/>
+      <c r="AF133" s="11" t="inlineStr"/>
+      <c r="AG133" s="12" t="inlineStr"/>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="1" t="n"/>
@@ -8477,15 +9158,18 @@
       <c r="W134" s="8" t="inlineStr"/>
       <c r="X134" s="8" t="inlineStr"/>
       <c r="Y134" s="8" t="inlineStr"/>
-      <c r="Z134" s="8" t="inlineStr">
+      <c r="Z134" s="8" t="inlineStr"/>
+      <c r="AA134" s="8" t="inlineStr"/>
+      <c r="AB134" s="8" t="inlineStr"/>
+      <c r="AC134" s="8" t="inlineStr">
         <is>
           <t>415.00</t>
         </is>
       </c>
-      <c r="AA134" s="8" t="inlineStr"/>
-      <c r="AB134" s="10" t="inlineStr"/>
-      <c r="AC134" s="11" t="inlineStr"/>
-      <c r="AD134" s="12" t="inlineStr"/>
+      <c r="AD134" s="8" t="inlineStr"/>
+      <c r="AE134" s="10" t="inlineStr"/>
+      <c r="AF134" s="11" t="inlineStr"/>
+      <c r="AG134" s="12" t="inlineStr"/>
     </row>
     <row r="135" ht="24" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
@@ -8525,11 +9209,14 @@
       <c r="Y135" s="4" t="inlineStr"/>
       <c r="Z135" s="4" t="inlineStr"/>
       <c r="AA135" s="4" t="inlineStr"/>
-      <c r="AB135" s="5" t="inlineStr"/>
-      <c r="AC135" s="6" t="n">
+      <c r="AB135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AD135" s="4" t="inlineStr"/>
+      <c r="AE135" s="5" t="inlineStr"/>
+      <c r="AF135" s="6" t="n">
         <v>-2053.75</v>
       </c>
-      <c r="AD135" s="7" t="n">
+      <c r="AG135" s="7" t="n">
         <v>-0.1840310758257316</v>
       </c>
     </row>
@@ -8585,11 +9272,14 @@
       <c r="Y136" s="8" t="inlineStr"/>
       <c r="Z136" s="8" t="inlineStr"/>
       <c r="AA136" s="8" t="inlineStr"/>
-      <c r="AB136" s="10" t="n">
+      <c r="AB136" s="8" t="inlineStr"/>
+      <c r="AC136" s="8" t="inlineStr"/>
+      <c r="AD136" s="8" t="inlineStr"/>
+      <c r="AE136" s="10" t="n">
         <v>5931.25</v>
       </c>
-      <c r="AC136" s="11" t="inlineStr"/>
-      <c r="AD136" s="12" t="inlineStr"/>
+      <c r="AF136" s="11" t="inlineStr"/>
+      <c r="AG136" s="12" t="inlineStr"/>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="1" t="n"/>
@@ -8635,9 +9325,12 @@
       <c r="Y137" s="8" t="inlineStr"/>
       <c r="Z137" s="8" t="inlineStr"/>
       <c r="AA137" s="8" t="inlineStr"/>
-      <c r="AB137" s="10" t="inlineStr"/>
-      <c r="AC137" s="11" t="inlineStr"/>
-      <c r="AD137" s="12" t="inlineStr"/>
+      <c r="AB137" s="8" t="inlineStr"/>
+      <c r="AC137" s="8" t="inlineStr"/>
+      <c r="AD137" s="8" t="inlineStr"/>
+      <c r="AE137" s="10" t="inlineStr"/>
+      <c r="AF137" s="11" t="inlineStr"/>
+      <c r="AG137" s="12" t="inlineStr"/>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="1" t="n"/>
@@ -8673,7 +9366,7 @@
           <t>2974.50</t>
         </is>
       </c>
-      <c r="R138" s="15" t="inlineStr">
+      <c r="R138" s="16" t="inlineStr">
         <is>
           <t>7972.50</t>
         </is>
@@ -8685,19 +9378,22 @@
       <c r="W138" s="8" t="inlineStr"/>
       <c r="X138" s="8" t="inlineStr"/>
       <c r="Y138" s="8" t="inlineStr"/>
-      <c r="Z138" s="14" t="inlineStr">
+      <c r="Z138" s="8" t="inlineStr"/>
+      <c r="AA138" s="8" t="inlineStr"/>
+      <c r="AB138" s="8" t="inlineStr"/>
+      <c r="AC138" s="15" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="AA138" s="8" t="inlineStr"/>
-      <c r="AB138" s="10" t="n">
+      <c r="AD138" s="8" t="inlineStr"/>
+      <c r="AE138" s="10" t="n">
         <v>6350.5</v>
       </c>
-      <c r="AC138" s="10" t="n">
+      <c r="AF138" s="10" t="n">
         <v>419.25</v>
       </c>
-      <c r="AD138" s="12" t="n">
+      <c r="AG138" s="12" t="n">
         <v>0.03756787756052975</v>
       </c>
     </row>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -61,14 +61,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <strike val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="00006100"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <strike val="1"/>
+      <color rgb="00808080"/>
       <sz val="16"/>
     </font>
   </fonts>
@@ -190,11 +190,11 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -277,18 +277,18 @@
     <author>STORM</author>
   </authors>
   <commentList>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>Retrieval 미사용과 target: 16 양쪽에 유효한 점수가 있는 공통 시드만 사용합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드는 제외합니다. 각 시드에 여러 결과가 있으면 첫 번째 점수를 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: Retrieval 미사용의 공통 시드 평균 − STORM 논문 점수.
 target: 16 행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>STORM (논문) 행: (Retrieval 미사용 평균 − STORM 논문 점수) / (Human − Random).
 target: 16 행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
@@ -473,195 +473,170 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="U29" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K33" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P33" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K34" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P34" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P35" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K36" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P36" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K37" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P37" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O39" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O40" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O41" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R41" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="O42" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O43" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="D45" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Breakout, seed 2
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O45" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:7
-python -u train.py -n "BankHeist-6060" -seed 6060 -config_path "config_files/STORM.yaml" -env_name "ALE/BankHeist-v5" -trajectory_path "D_TRAJ/BankHeist.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="V29" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:12
-python -u train.py -n "BankHeist-6070" -seed 6070 -config_path "config_files/STORM.yaml" -env_name "ALE/BankHeist-v5" -trajectory_path "D_TRAJ/BankHeist.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R30" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="S30" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q31" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R31" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="S31" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BankHeist, seed 6040
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K33" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K34" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P34" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K35" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P35" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K36" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P36" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="K37" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 2000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P37" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: BattleZone, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O39" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O40" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O41" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R41" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="S41" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:8
-python -u train.py -n "Boxing-6040" -seed 6040 -config_path "config_files/STORM.yaml" -env_name "ALE/Boxing-v5" -trajectory_path "D_TRAJ/Boxing.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="T41" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:13
-python -u train.py -n "Boxing-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/Boxing-v5" -trajectory_path "D_TRAJ/Boxing.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="O42" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O43" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Boxing, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="D45" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Breakout, seed 2
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+job_queue_A6000.txt:5
+python -u train.py -n "Breakout-6000" -seed 6000 -config_path "config_files/STORM.yaml" -env_name "ALE/Breakout-v5" -trajectory_path "D_TRAJ/Breakout.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
       </text>
     </comment>
     <comment ref="D46" authorId="0" shapeId="0">
@@ -677,6 +652,13 @@
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="O47" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:5
+python -u train.py -n "Breakout-6000" -seed 6000 -config_path "config_files/STORM.yaml" -env_name "ALE/Breakout-v5" -trajectory_path "D_TRAJ/Breakout.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
       </text>
     </comment>
     <comment ref="L57" authorId="0" shapeId="0">
@@ -692,42 +674,39 @@
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="P57" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:11
-python -u train.py -n "CrazyClimber-6010" -seed 6010 -config_path "config_files/STORM.yaml" -env_name "ALE/CrazyClimber-v5" -trajectory_path "D_TRAJ/CrazyClimber.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="R67" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Freeway, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R68" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Freeway, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="C69" authorId="0" shapeId="0">
+    <comment ref="C67" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
 job_queue_pro6k.txt:1
-python -u train.py -n "Freeway-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="D69" authorId="0" shapeId="0">
+python -u train.py -n "Freeway-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline', 'target1', 'value', 'add']" JointTrainAgent.UseDemonstration True</t>
+      </text>
+    </comment>
+    <comment ref="R67" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Freeway, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="C68" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_pro6k.txt:4
-python -u train.py -n "Freeway-2" -seed 2 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+job_queue_pro6k.txt:1
+python -u train.py -n "Freeway-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline', 'target1', 'value', 'add']" JointTrainAgent.UseDemonstration True</t>
+      </text>
+    </comment>
+    <comment ref="R68" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Freeway, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="C69" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:1
+python -u train.py -n "Freeway-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline', 'target1', 'value', 'add']" JointTrainAgent.UseDemonstration True</t>
       </text>
     </comment>
     <comment ref="R69" authorId="0" shapeId="0">
@@ -738,12 +717,11 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="AC69" authorId="0" shapeId="0">
+    <comment ref="C70" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_titan.txt:2
-python -u train.py -n "Freeway-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+job_queue_pro6k.txt:1
+python -u train.py -n "Freeway-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline', 'target1', 'value', 'add']" JointTrainAgent.UseDemonstration True</t>
       </text>
     </comment>
     <comment ref="R70" authorId="0" shapeId="0">
@@ -753,6 +731,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="C71" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:1
+python -u train.py -n "Freeway-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Freeway-v5" -trajectory_path "D_TRAJ/Freeway.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline', 'target1', 'value', 'add']" JointTrainAgent.UseDemonstration True</t>
+      </text>
+    </comment>
     <comment ref="R71" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Freeway, seed 6030
@@ -830,21 +815,21 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Y79" authorId="0" shapeId="0">
+    <comment ref="W79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z79" authorId="0" shapeId="0">
+    <comment ref="X79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="AC79" authorId="0" shapeId="0">
+    <comment ref="AA79" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -886,21 +871,21 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Y80" authorId="0" shapeId="0">
+    <comment ref="W80" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Z80" authorId="0" shapeId="0">
+    <comment ref="X80" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="AC80" authorId="0" shapeId="0">
+    <comment ref="AA80" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -948,20 +933,12 @@
     <comment ref="T81" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:5
+job_queue_A6000.txt:8
 python -u train.py -n "Gopher-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/Gopher-v5" -trajectory_path "D_TRAJ/Gopher.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="U81" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:9
-python -u train.py -n "Gopher-6060" -seed 6060 -config_path "config_files/STORM.yaml" -env_name "ALE/Gopher-v5" -trajectory_path "D_TRAJ/Gopher.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="X81" authorId="0" shapeId="0">
+    <comment ref="V81" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
 job_queue_titan.txt:1
@@ -969,7 +946,7 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="Y81" authorId="0" shapeId="0">
+    <comment ref="W81" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9995
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -977,7 +954,7 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="Z81" authorId="0" shapeId="0">
+    <comment ref="X81" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 9996
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -985,197 +962,197 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
+    <comment ref="Y81" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
     <comment ref="AA81" authorId="0" shapeId="0">
       <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="W82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9995
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="X82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA82" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6000
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="S83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 6040
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="W83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9995
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="X83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9996
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA83" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="C93" authorId="0" shapeId="0">
+      <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="AC81" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O82" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P82" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q82" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R82" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="S82" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6040
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Y82" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9995
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Z82" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9996
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="AC82" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="O83" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6000
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P83" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q83" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="R83" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6030
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="S83" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 6040
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Y83" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9995
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Z83" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9996
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="AC83" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Gopher, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="C93" authorId="0" shapeId="0">
+    <comment ref="P95" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA95" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P96" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA96" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="P97" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q97" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="P95" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="AC95" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="P96" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="AC96" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="C97" authorId="0" shapeId="0">
+    <comment ref="R97" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="S97" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_pro6k.txt:2
-python -u train.py -n "Kangaroo-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Kangaroo-v5" -trajectory_path "D_TRAJ/Kangaroo.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="P97" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Kangaroo, seed 6010
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q97" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="R97" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="S97" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:10
+job_queue_A6000.txt:6
 python -u train.py -n "Kangaroo-6040" -seed 6040 -config_path "config_files/STORM.yaml" -env_name "ALE/Kangaroo-v5" -trajectory_path "D_TRAJ/Kangaroo.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="AC97" authorId="0" shapeId="0">
+    <comment ref="T97" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:9
+python -u train.py -n "Kangaroo-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/Kangaroo-v5" -trajectory_path "D_TRAJ/Kangaroo.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA97" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Kangaroo, seed 9999
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -1237,14 +1214,6 @@
         <t>EXCLUDED_SEEDS: Krull, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="C101" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_pro6k.txt:3
-python -u train.py -n "Krull-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Krull-v5" -trajectory_path "D_TRAJ/Krull.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
     <comment ref="K101" authorId="0" shapeId="0">
@@ -1290,25 +1259,44 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="U101" authorId="0" shapeId="0">
+    <comment ref="AA103" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:4
-python -u train.py -n "Krull-6060" -seed 6060 -config_path "config_files/STORM.yaml" -env_name "ALE/Krull-v5" -trajectory_path "D_TRAJ/Krull.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="AB101" authorId="0" shapeId="0">
+job_queue_titan.txt:3
+python -u train.py -n "KungFuMaster-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/KungFuMaster-v5" -trajectory_path "D_TRAJ/KungFuMaster.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
+      </text>
+    </comment>
+    <comment ref="L105" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA105" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_titan.txt:4
-python -u train.py -n "Krull-9998" -seed 9998 -config_path "config_files/STORM.yaml" -env_name "ALE/Krull-v5" -trajectory_path "D_TRAJ/Krull.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="L105" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+job_queue_titan.txt:3
+python -u train.py -n "KungFuMaster-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/KungFuMaster-v5" -trajectory_path "D_TRAJ/KungFuMaster.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
+      </text>
+    </comment>
+    <comment ref="Q109" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:7
+python -u train.py -n "MsPacman-6020" -seed 6020 -config_path "config_files/STORM.yaml" -env_name "ALE/MsPacman-v5" -trajectory_path "D_TRAJ/MsPacman.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
+      </text>
+    </comment>
+    <comment ref="Q111" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:7
+python -u train.py -n "MsPacman-6020" -seed 6020 -config_path "config_files/STORM.yaml" -env_name "ALE/MsPacman-v5" -trajectory_path "D_TRAJ/MsPacman.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
+      </text>
+    </comment>
+    <comment ref="I115" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:2
+python -u train.py -n "Pong-3710" -seed 3710 -config_path "config_files/STORM.yaml" -env_name "ALE/Pong-v5" -trajectory_path "D_TRAJ/Pong.pkl" JointTrainAgent.Retrieval.enable "['baseline']"</t>
       </text>
     </comment>
     <comment ref="L115" authorId="0" shapeId="0">
@@ -1325,7 +1313,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="AC116" authorId="0" shapeId="0">
+    <comment ref="AA116" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1473,49 +1461,47 @@
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="U128" authorId="0" shapeId="0">
+    <comment ref="C132" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:6
-python -u train.py -n "RoadRunner-6060" -seed 6060 -config_path "config_files/STORM.yaml" -env_name "ALE/RoadRunner-v5" -trajectory_path "D_TRAJ/RoadRunner.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="AC128" authorId="0" shapeId="0">
+job_queue_pro6k.txt:3
+python -u train.py -n "Seaquest-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Seaquest-v5" -trajectory_path "D_TRAJ/Seaquest.pkl" JointTrainAgent.Retrieval.enable "['retrieval']"</t>
+      </text>
+    </comment>
+    <comment ref="Q136" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: UpNDown, seed 6020
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R136" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_titan.txt:3
-python -u train.py -n "RoadRunner-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/RoadRunner-v5" -trajectory_path "D_TRAJ/RoadRunner.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
-초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="Q136" authorId="0" shapeId="0">
+job_queue_A6000.txt:4
+python -u train.py -n "UpNDown-6030" -seed 6030 -config_path "config_files/STORM.yaml" -env_name "ALE/UpNDown-v5" -trajectory_path "D_TRAJ/UpNDown.pkl" JointTrainAgent.Retrieval.enable "['baseline']"</t>
+      </text>
+    </comment>
+    <comment ref="Q137" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q137" authorId="0" shapeId="0">
+    <comment ref="Q138" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q138" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: UpNDown, seed 6020
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
     <comment ref="R138" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="AC138" authorId="0" shapeId="0">
+    <comment ref="AA138" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1813,18 +1799,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG138"/>
+  <dimension ref="A1:AE138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
     <col width="54.7" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="30" max="30"/>
-    <col width="30" customWidth="1" min="31" max="31"/>
-    <col width="46" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="3" customWidth="1" min="21" max="21"/>
+    <col width="3" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="29" max="29"/>
+    <col width="46" customWidth="1" min="30" max="30"/>
+    <col width="32" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1896,51 +1882,45 @@
       <c r="T1" s="1" t="n">
         <v>6050</v>
       </c>
-      <c r="U1" s="1" t="n">
-        <v>6060</v>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>    </t>
+        </is>
       </c>
       <c r="V1" s="1" t="n">
-        <v>6070</v>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>    </t>
-        </is>
+        <v>9994</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>9995</v>
       </c>
       <c r="X1" s="1" t="n">
-        <v>9994</v>
+        <v>9996</v>
       </c>
       <c r="Y1" s="1" t="n">
-        <v>9995</v>
+        <v>9997</v>
       </c>
       <c r="Z1" s="1" t="n">
-        <v>9996</v>
+        <v>9998</v>
       </c>
       <c r="AA1" s="1" t="n">
-        <v>9997</v>
-      </c>
-      <c r="AB1" s="1" t="n">
-        <v>9998</v>
-      </c>
-      <c r="AC1" s="1" t="n">
         <v>9999</v>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>   </t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Mean (공통 시드)</t>
+        </is>
+      </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>   </t>
+          <t>Δ Score (행별 비교)</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Mean (공통 시드)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Δ Score (행별 비교)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -1985,13 +1965,11 @@
       <c r="Z2" s="4" t="inlineStr"/>
       <c r="AA2" s="4" t="inlineStr"/>
       <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="inlineStr"/>
-      <c r="AD2" s="4" t="inlineStr"/>
-      <c r="AE2" s="5" t="inlineStr"/>
-      <c r="AF2" s="6" t="n">
+      <c r="AC2" s="5" t="inlineStr"/>
+      <c r="AD2" s="6" t="n">
         <v>107.625</v>
       </c>
-      <c r="AG2" s="7" t="n">
+      <c r="AE2" s="7" t="n">
         <v>0.01559805214568327</v>
       </c>
     </row>
@@ -2052,13 +2030,11 @@
       <c r="Z3" s="8" t="inlineStr"/>
       <c r="AA3" s="8" t="inlineStr"/>
       <c r="AB3" s="8" t="inlineStr"/>
-      <c r="AC3" s="8" t="inlineStr"/>
-      <c r="AD3" s="8" t="inlineStr"/>
-      <c r="AE3" s="10" t="n">
+      <c r="AC3" s="10" t="n">
         <v>1091.625</v>
       </c>
-      <c r="AF3" s="11" t="inlineStr"/>
-      <c r="AG3" s="12" t="inlineStr"/>
+      <c r="AD3" s="11" t="inlineStr"/>
+      <c r="AE3" s="12" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -2109,11 +2085,9 @@
       <c r="Z4" s="8" t="inlineStr"/>
       <c r="AA4" s="8" t="inlineStr"/>
       <c r="AB4" s="8" t="inlineStr"/>
-      <c r="AC4" s="8" t="inlineStr"/>
-      <c r="AD4" s="8" t="inlineStr"/>
-      <c r="AE4" s="10" t="inlineStr"/>
-      <c r="AF4" s="11" t="inlineStr"/>
-      <c r="AG4" s="12" t="inlineStr"/>
+      <c r="AC4" s="10" t="inlineStr"/>
+      <c r="AD4" s="11" t="inlineStr"/>
+      <c r="AE4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -2168,15 +2142,13 @@
       <c r="Z5" s="8" t="inlineStr"/>
       <c r="AA5" s="8" t="inlineStr"/>
       <c r="AB5" s="8" t="inlineStr"/>
-      <c r="AC5" s="8" t="inlineStr"/>
-      <c r="AD5" s="8" t="inlineStr"/>
-      <c r="AE5" s="10" t="n">
+      <c r="AC5" s="10" t="n">
         <v>1147.875</v>
       </c>
-      <c r="AF5" s="10" t="n">
+      <c r="AD5" s="10" t="n">
         <v>56.25</v>
       </c>
-      <c r="AG5" s="12" t="n">
+      <c r="AE5" s="12" t="n">
         <v>0.0081522920622038</v>
       </c>
     </row>
@@ -2217,11 +2189,9 @@
       <c r="Z6" s="8" t="inlineStr"/>
       <c r="AA6" s="8" t="inlineStr"/>
       <c r="AB6" s="8" t="inlineStr"/>
-      <c r="AC6" s="8" t="inlineStr"/>
-      <c r="AD6" s="8" t="inlineStr"/>
-      <c r="AE6" s="10" t="inlineStr"/>
-      <c r="AF6" s="11" t="inlineStr"/>
-      <c r="AG6" s="12" t="inlineStr"/>
+      <c r="AC6" s="10" t="inlineStr"/>
+      <c r="AD6" s="11" t="inlineStr"/>
+      <c r="AE6" s="12" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="1" t="n"/>
@@ -2260,11 +2230,9 @@
       <c r="Z7" s="8" t="inlineStr"/>
       <c r="AA7" s="8" t="inlineStr"/>
       <c r="AB7" s="8" t="inlineStr"/>
-      <c r="AC7" s="8" t="inlineStr"/>
-      <c r="AD7" s="8" t="inlineStr"/>
-      <c r="AE7" s="10" t="inlineStr"/>
-      <c r="AF7" s="11" t="inlineStr"/>
-      <c r="AG7" s="12" t="inlineStr"/>
+      <c r="AC7" s="10" t="inlineStr"/>
+      <c r="AD7" s="11" t="inlineStr"/>
+      <c r="AE7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -2305,13 +2273,11 @@
       <c r="Z8" s="4" t="inlineStr"/>
       <c r="AA8" s="4" t="inlineStr"/>
       <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr"/>
-      <c r="AD8" s="4" t="inlineStr"/>
-      <c r="AE8" s="5" t="inlineStr"/>
-      <c r="AF8" s="6" t="n">
+      <c r="AC8" s="5" t="inlineStr"/>
+      <c r="AD8" s="6" t="n">
         <v>3.599999999999994</v>
       </c>
-      <c r="AG8" s="7" t="n">
+      <c r="AE8" s="7" t="n">
         <v>0.002100717745229617</v>
       </c>
     </row>
@@ -2372,13 +2338,11 @@
       <c r="Z9" s="8" t="inlineStr"/>
       <c r="AA9" s="8" t="inlineStr"/>
       <c r="AB9" s="8" t="inlineStr"/>
-      <c r="AC9" s="8" t="inlineStr"/>
-      <c r="AD9" s="8" t="inlineStr"/>
-      <c r="AE9" s="10" t="n">
+      <c r="AC9" s="10" t="n">
         <v>208.6</v>
       </c>
-      <c r="AF9" s="11" t="inlineStr"/>
-      <c r="AG9" s="12" t="inlineStr"/>
+      <c r="AD9" s="11" t="inlineStr"/>
+      <c r="AE9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -2429,11 +2393,9 @@
       <c r="Z10" s="8" t="inlineStr"/>
       <c r="AA10" s="8" t="inlineStr"/>
       <c r="AB10" s="8" t="inlineStr"/>
-      <c r="AC10" s="8" t="inlineStr"/>
-      <c r="AD10" s="8" t="inlineStr"/>
-      <c r="AE10" s="10" t="inlineStr"/>
-      <c r="AF10" s="11" t="inlineStr"/>
-      <c r="AG10" s="12" t="inlineStr"/>
+      <c r="AC10" s="10" t="inlineStr"/>
+      <c r="AD10" s="11" t="inlineStr"/>
+      <c r="AE10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="1" t="n"/>
@@ -2488,15 +2450,13 @@
       <c r="Z11" s="8" t="inlineStr"/>
       <c r="AA11" s="8" t="inlineStr"/>
       <c r="AB11" s="8" t="inlineStr"/>
-      <c r="AC11" s="8" t="inlineStr"/>
-      <c r="AD11" s="8" t="inlineStr"/>
-      <c r="AE11" s="10" t="n">
+      <c r="AC11" s="10" t="n">
         <v>169.15</v>
       </c>
-      <c r="AF11" s="10" t="n">
+      <c r="AD11" s="10" t="n">
         <v>39.44999999999999</v>
       </c>
-      <c r="AG11" s="12" t="n">
+      <c r="AE11" s="12" t="n">
         <v>-0.02302036529147458</v>
       </c>
     </row>
@@ -2537,11 +2497,9 @@
       <c r="Z12" s="8" t="inlineStr"/>
       <c r="AA12" s="8" t="inlineStr"/>
       <c r="AB12" s="8" t="inlineStr"/>
-      <c r="AC12" s="8" t="inlineStr"/>
-      <c r="AD12" s="8" t="inlineStr"/>
-      <c r="AE12" s="10" t="inlineStr"/>
-      <c r="AF12" s="11" t="inlineStr"/>
-      <c r="AG12" s="12" t="inlineStr"/>
+      <c r="AC12" s="10" t="inlineStr"/>
+      <c r="AD12" s="11" t="inlineStr"/>
+      <c r="AE12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -2580,11 +2538,9 @@
       <c r="Z13" s="8" t="inlineStr"/>
       <c r="AA13" s="8" t="inlineStr"/>
       <c r="AB13" s="8" t="inlineStr"/>
-      <c r="AC13" s="8" t="inlineStr"/>
-      <c r="AD13" s="8" t="inlineStr"/>
-      <c r="AE13" s="10" t="inlineStr"/>
-      <c r="AF13" s="11" t="inlineStr"/>
-      <c r="AG13" s="12" t="inlineStr"/>
+      <c r="AC13" s="10" t="inlineStr"/>
+      <c r="AD13" s="11" t="inlineStr"/>
+      <c r="AE13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2625,13 +2581,11 @@
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr"/>
-      <c r="AD14" s="4" t="inlineStr"/>
-      <c r="AE14" s="5" t="inlineStr"/>
-      <c r="AF14" s="6" t="n">
+      <c r="AC14" s="5" t="inlineStr"/>
+      <c r="AD14" s="6" t="n">
         <v>20.11249999999995</v>
       </c>
-      <c r="AG14" s="7" t="n">
+      <c r="AE14" s="7" t="n">
         <v>0.03870765973826011</v>
       </c>
     </row>
@@ -2692,13 +2646,11 @@
       <c r="Z15" s="8" t="inlineStr"/>
       <c r="AA15" s="8" t="inlineStr"/>
       <c r="AB15" s="8" t="inlineStr"/>
-      <c r="AC15" s="8" t="inlineStr"/>
-      <c r="AD15" s="8" t="inlineStr"/>
-      <c r="AE15" s="10" t="n">
+      <c r="AC15" s="10" t="n">
         <v>821.1125</v>
       </c>
-      <c r="AF15" s="11" t="inlineStr"/>
-      <c r="AG15" s="12" t="inlineStr"/>
+      <c r="AD15" s="11" t="inlineStr"/>
+      <c r="AE15" s="12" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -2749,11 +2701,9 @@
       <c r="Z16" s="8" t="inlineStr"/>
       <c r="AA16" s="8" t="inlineStr"/>
       <c r="AB16" s="8" t="inlineStr"/>
-      <c r="AC16" s="8" t="inlineStr"/>
-      <c r="AD16" s="8" t="inlineStr"/>
-      <c r="AE16" s="10" t="inlineStr"/>
-      <c r="AF16" s="11" t="inlineStr"/>
-      <c r="AG16" s="12" t="inlineStr"/>
+      <c r="AC16" s="10" t="inlineStr"/>
+      <c r="AD16" s="11" t="inlineStr"/>
+      <c r="AE16" s="12" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -2820,15 +2770,13 @@
       <c r="Z17" s="8" t="inlineStr"/>
       <c r="AA17" s="8" t="inlineStr"/>
       <c r="AB17" s="8" t="inlineStr"/>
-      <c r="AC17" s="8" t="inlineStr"/>
-      <c r="AD17" s="8" t="inlineStr"/>
-      <c r="AE17" s="10" t="n">
+      <c r="AC17" s="10" t="n">
         <v>723.6625</v>
       </c>
-      <c r="AF17" s="10" t="n">
+      <c r="AD17" s="10" t="n">
         <v>97.44999999999993</v>
       </c>
-      <c r="AG17" s="12" t="n">
+      <c r="AE17" s="12" t="n">
         <v>-0.1875481139337951</v>
       </c>
     </row>
@@ -2869,11 +2817,9 @@
       <c r="Z18" s="8" t="inlineStr"/>
       <c r="AA18" s="8" t="inlineStr"/>
       <c r="AB18" s="8" t="inlineStr"/>
-      <c r="AC18" s="8" t="inlineStr"/>
-      <c r="AD18" s="8" t="inlineStr"/>
-      <c r="AE18" s="10" t="inlineStr"/>
-      <c r="AF18" s="11" t="inlineStr"/>
-      <c r="AG18" s="12" t="inlineStr"/>
+      <c r="AC18" s="10" t="inlineStr"/>
+      <c r="AD18" s="11" t="inlineStr"/>
+      <c r="AE18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
@@ -2912,11 +2858,9 @@
       <c r="Z19" s="8" t="inlineStr"/>
       <c r="AA19" s="8" t="inlineStr"/>
       <c r="AB19" s="8" t="inlineStr"/>
-      <c r="AC19" s="8" t="inlineStr"/>
-      <c r="AD19" s="8" t="inlineStr"/>
-      <c r="AE19" s="10" t="inlineStr"/>
-      <c r="AF19" s="11" t="inlineStr"/>
-      <c r="AG19" s="12" t="inlineStr"/>
+      <c r="AC19" s="10" t="inlineStr"/>
+      <c r="AD19" s="11" t="inlineStr"/>
+      <c r="AE19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2957,13 +2901,11 @@
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
       <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="inlineStr"/>
-      <c r="AD20" s="4" t="inlineStr"/>
-      <c r="AE20" s="5" t="inlineStr"/>
-      <c r="AF20" s="6" t="n">
+      <c r="AC20" s="5" t="inlineStr"/>
+      <c r="AD20" s="6" t="n">
         <v>-350.5</v>
       </c>
-      <c r="AG20" s="7" t="n">
+      <c r="AE20" s="7" t="n">
         <v>-0.04226303160382478</v>
       </c>
     </row>
@@ -3020,13 +2962,11 @@
       <c r="Z21" s="8" t="inlineStr"/>
       <c r="AA21" s="8" t="inlineStr"/>
       <c r="AB21" s="8" t="inlineStr"/>
-      <c r="AC21" s="8" t="inlineStr"/>
-      <c r="AD21" s="8" t="inlineStr"/>
-      <c r="AE21" s="10" t="n">
+      <c r="AC21" s="10" t="n">
         <v>677.5</v>
       </c>
-      <c r="AF21" s="11" t="inlineStr"/>
-      <c r="AG21" s="12" t="inlineStr"/>
+      <c r="AD21" s="11" t="inlineStr"/>
+      <c r="AE21" s="12" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="1" t="n"/>
@@ -3073,11 +3013,9 @@
       <c r="Z22" s="8" t="inlineStr"/>
       <c r="AA22" s="8" t="inlineStr"/>
       <c r="AB22" s="8" t="inlineStr"/>
-      <c r="AC22" s="8" t="inlineStr"/>
-      <c r="AD22" s="8" t="inlineStr"/>
-      <c r="AE22" s="10" t="inlineStr"/>
-      <c r="AF22" s="11" t="inlineStr"/>
-      <c r="AG22" s="12" t="inlineStr"/>
+      <c r="AC22" s="10" t="inlineStr"/>
+      <c r="AD22" s="11" t="inlineStr"/>
+      <c r="AE22" s="12" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="1" t="n"/>
@@ -3128,15 +3066,13 @@
       <c r="Z23" s="8" t="inlineStr"/>
       <c r="AA23" s="8" t="inlineStr"/>
       <c r="AB23" s="8" t="inlineStr"/>
-      <c r="AC23" s="8" t="inlineStr"/>
-      <c r="AD23" s="8" t="inlineStr"/>
-      <c r="AE23" s="10" t="n">
+      <c r="AC23" s="10" t="n">
         <v>759.375</v>
       </c>
-      <c r="AF23" s="10" t="n">
+      <c r="AD23" s="10" t="n">
         <v>81.875</v>
       </c>
-      <c r="AG23" s="12" t="n">
+      <c r="AE23" s="12" t="n">
         <v>0.009872427139980468</v>
       </c>
     </row>
@@ -3177,11 +3113,9 @@
       <c r="Z24" s="8" t="inlineStr"/>
       <c r="AA24" s="8" t="inlineStr"/>
       <c r="AB24" s="8" t="inlineStr"/>
-      <c r="AC24" s="8" t="inlineStr"/>
-      <c r="AD24" s="8" t="inlineStr"/>
-      <c r="AE24" s="10" t="inlineStr"/>
-      <c r="AF24" s="11" t="inlineStr"/>
-      <c r="AG24" s="12" t="inlineStr"/>
+      <c r="AC24" s="10" t="inlineStr"/>
+      <c r="AD24" s="11" t="inlineStr"/>
+      <c r="AE24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -3220,11 +3154,9 @@
       <c r="Z25" s="8" t="inlineStr"/>
       <c r="AA25" s="8" t="inlineStr"/>
       <c r="AB25" s="8" t="inlineStr"/>
-      <c r="AC25" s="8" t="inlineStr"/>
-      <c r="AD25" s="8" t="inlineStr"/>
-      <c r="AE25" s="10" t="inlineStr"/>
-      <c r="AF25" s="11" t="inlineStr"/>
-      <c r="AG25" s="12" t="inlineStr"/>
+      <c r="AC25" s="10" t="inlineStr"/>
+      <c r="AD25" s="11" t="inlineStr"/>
+      <c r="AE25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -3265,13 +3197,11 @@
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
       <c r="AB26" s="4" t="inlineStr"/>
-      <c r="AC26" s="4" t="inlineStr"/>
-      <c r="AD26" s="4" t="inlineStr"/>
-      <c r="AE26" s="5" t="inlineStr"/>
-      <c r="AF26" s="6" t="n">
+      <c r="AC26" s="5" t="inlineStr"/>
+      <c r="AD26" s="6" t="n">
         <v>-84.75</v>
       </c>
-      <c r="AG26" s="7" t="n">
+      <c r="AE26" s="7" t="n">
         <v>-0.1146975233455136</v>
       </c>
     </row>
@@ -3329,24 +3259,22 @@
       <c r="W27" s="8" t="inlineStr"/>
       <c r="X27" s="8" t="inlineStr"/>
       <c r="Y27" s="8" t="inlineStr"/>
-      <c r="Z27" s="8" t="inlineStr"/>
-      <c r="AA27" s="8" t="inlineStr"/>
-      <c r="AB27" s="8" t="inlineStr">
+      <c r="Z27" s="8" t="inlineStr">
         <is>
           <t>694.50</t>
         </is>
       </c>
-      <c r="AC27" s="8" t="inlineStr">
+      <c r="AA27" s="8" t="inlineStr">
         <is>
           <t>668.50</t>
         </is>
       </c>
-      <c r="AD27" s="8" t="inlineStr"/>
-      <c r="AE27" s="10" t="n">
+      <c r="AB27" s="8" t="inlineStr"/>
+      <c r="AC27" s="10" t="n">
         <v>556.25</v>
       </c>
-      <c r="AF27" s="11" t="inlineStr"/>
-      <c r="AG27" s="12" t="inlineStr"/>
+      <c r="AD27" s="11" t="inlineStr"/>
+      <c r="AE27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -3379,17 +3307,15 @@
       <c r="X28" s="8" t="inlineStr"/>
       <c r="Y28" s="8" t="inlineStr"/>
       <c r="Z28" s="8" t="inlineStr"/>
-      <c r="AA28" s="8" t="inlineStr"/>
+      <c r="AA28" s="8" t="inlineStr">
+        <is>
+          <t>507.50</t>
+        </is>
+      </c>
       <c r="AB28" s="8" t="inlineStr"/>
-      <c r="AC28" s="8" t="inlineStr">
-        <is>
-          <t>507.50</t>
-        </is>
-      </c>
-      <c r="AD28" s="8" t="inlineStr"/>
-      <c r="AE28" s="10" t="inlineStr"/>
-      <c r="AF28" s="11" t="inlineStr"/>
-      <c r="AG28" s="12" t="inlineStr"/>
+      <c r="AC28" s="10" t="inlineStr"/>
+      <c r="AD28" s="11" t="inlineStr"/>
+      <c r="AE28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -3440,39 +3366,29 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="U29" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
-      <c r="V29" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="U29" s="8" t="inlineStr"/>
+      <c r="V29" s="8" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr"/>
       <c r="X29" s="8" t="inlineStr"/>
       <c r="Y29" s="8" t="inlineStr"/>
-      <c r="Z29" s="8" t="inlineStr"/>
-      <c r="AA29" s="8" t="inlineStr"/>
-      <c r="AB29" s="8" t="inlineStr">
+      <c r="Z29" s="8" t="inlineStr">
         <is>
           <t>566.00</t>
         </is>
       </c>
-      <c r="AC29" s="8" t="inlineStr">
+      <c r="AA29" s="8" t="inlineStr">
         <is>
           <t>565.00</t>
         </is>
       </c>
-      <c r="AD29" s="8" t="inlineStr"/>
-      <c r="AE29" s="10" t="n">
+      <c r="AB29" s="8" t="inlineStr"/>
+      <c r="AC29" s="10" t="n">
         <v>483.5</v>
       </c>
-      <c r="AF29" s="10" t="n">
+      <c r="AD29" s="10" t="n">
         <v>72.75</v>
       </c>
-      <c r="AG29" s="12" t="n">
+      <c r="AE29" s="12" t="n">
         <v>-0.09845716605765327</v>
       </c>
     </row>
@@ -3507,17 +3423,15 @@
       <c r="X30" s="8" t="inlineStr"/>
       <c r="Y30" s="8" t="inlineStr"/>
       <c r="Z30" s="8" t="inlineStr"/>
-      <c r="AA30" s="8" t="inlineStr"/>
+      <c r="AA30" s="8" t="inlineStr">
+        <is>
+          <t>652.50</t>
+        </is>
+      </c>
       <c r="AB30" s="8" t="inlineStr"/>
-      <c r="AC30" s="8" t="inlineStr">
-        <is>
-          <t>652.50</t>
-        </is>
-      </c>
-      <c r="AD30" s="8" t="inlineStr"/>
-      <c r="AE30" s="10" t="inlineStr"/>
-      <c r="AF30" s="11" t="inlineStr"/>
-      <c r="AG30" s="12" t="inlineStr"/>
+      <c r="AC30" s="10" t="inlineStr"/>
+      <c r="AD30" s="11" t="inlineStr"/>
+      <c r="AE30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="1" t="n"/>
@@ -3550,17 +3464,15 @@
       <c r="X31" s="8" t="inlineStr"/>
       <c r="Y31" s="8" t="inlineStr"/>
       <c r="Z31" s="8" t="inlineStr"/>
-      <c r="AA31" s="8" t="inlineStr"/>
+      <c r="AA31" s="8" t="inlineStr">
+        <is>
+          <t>381.50</t>
+        </is>
+      </c>
       <c r="AB31" s="8" t="inlineStr"/>
-      <c r="AC31" s="8" t="inlineStr">
-        <is>
-          <t>381.50</t>
-        </is>
-      </c>
-      <c r="AD31" s="8" t="inlineStr"/>
-      <c r="AE31" s="10" t="inlineStr"/>
-      <c r="AF31" s="11" t="inlineStr"/>
-      <c r="AG31" s="12" t="inlineStr"/>
+      <c r="AC31" s="10" t="inlineStr"/>
+      <c r="AD31" s="11" t="inlineStr"/>
+      <c r="AE31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3601,13 +3513,11 @@
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
       <c r="AB32" s="4" t="inlineStr"/>
-      <c r="AC32" s="4" t="inlineStr"/>
-      <c r="AD32" s="4" t="inlineStr"/>
-      <c r="AE32" s="5" t="inlineStr"/>
-      <c r="AF32" s="6" t="n">
+      <c r="AC32" s="5" t="inlineStr"/>
+      <c r="AD32" s="6" t="n">
         <v>-1327.5</v>
       </c>
-      <c r="AG32" s="7" t="n">
+      <c r="AE32" s="7" t="n">
         <v>-0.03811643098126481</v>
       </c>
     </row>
@@ -3668,13 +3578,11 @@
       <c r="Z33" s="8" t="inlineStr"/>
       <c r="AA33" s="8" t="inlineStr"/>
       <c r="AB33" s="8" t="inlineStr"/>
-      <c r="AC33" s="8" t="inlineStr"/>
-      <c r="AD33" s="8" t="inlineStr"/>
-      <c r="AE33" s="10" t="n">
+      <c r="AC33" s="10" t="n">
         <v>12212.5</v>
       </c>
-      <c r="AF33" s="11" t="inlineStr"/>
-      <c r="AG33" s="12" t="inlineStr"/>
+      <c r="AD33" s="11" t="inlineStr"/>
+      <c r="AE33" s="12" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="1" t="n"/>
@@ -3729,11 +3637,9 @@
       <c r="Z34" s="8" t="inlineStr"/>
       <c r="AA34" s="8" t="inlineStr"/>
       <c r="AB34" s="8" t="inlineStr"/>
-      <c r="AC34" s="8" t="inlineStr"/>
-      <c r="AD34" s="8" t="inlineStr"/>
-      <c r="AE34" s="10" t="inlineStr"/>
-      <c r="AF34" s="11" t="inlineStr"/>
-      <c r="AG34" s="12" t="inlineStr"/>
+      <c r="AC34" s="10" t="inlineStr"/>
+      <c r="AD34" s="11" t="inlineStr"/>
+      <c r="AE34" s="12" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="1" t="n"/>
@@ -3792,15 +3698,13 @@
       <c r="Z35" s="8" t="inlineStr"/>
       <c r="AA35" s="8" t="inlineStr"/>
       <c r="AB35" s="8" t="inlineStr"/>
-      <c r="AC35" s="8" t="inlineStr"/>
-      <c r="AD35" s="8" t="inlineStr"/>
-      <c r="AE35" s="10" t="n">
+      <c r="AC35" s="10" t="n">
         <v>13125</v>
       </c>
-      <c r="AF35" s="10" t="n">
+      <c r="AD35" s="10" t="n">
         <v>912.5</v>
       </c>
-      <c r="AG35" s="12" t="n">
+      <c r="AE35" s="12" t="n">
         <v>0.026200559902376</v>
       </c>
     </row>
@@ -3845,11 +3749,9 @@
       <c r="Z36" s="8" t="inlineStr"/>
       <c r="AA36" s="8" t="inlineStr"/>
       <c r="AB36" s="8" t="inlineStr"/>
-      <c r="AC36" s="8" t="inlineStr"/>
-      <c r="AD36" s="8" t="inlineStr"/>
-      <c r="AE36" s="10" t="inlineStr"/>
-      <c r="AF36" s="11" t="inlineStr"/>
-      <c r="AG36" s="12" t="inlineStr"/>
+      <c r="AC36" s="10" t="inlineStr"/>
+      <c r="AD36" s="11" t="inlineStr"/>
+      <c r="AE36" s="12" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="1" t="n"/>
@@ -3892,11 +3794,9 @@
       <c r="Z37" s="8" t="inlineStr"/>
       <c r="AA37" s="8" t="inlineStr"/>
       <c r="AB37" s="8" t="inlineStr"/>
-      <c r="AC37" s="8" t="inlineStr"/>
-      <c r="AD37" s="8" t="inlineStr"/>
-      <c r="AE37" s="10" t="inlineStr"/>
-      <c r="AF37" s="11" t="inlineStr"/>
-      <c r="AG37" s="12" t="inlineStr"/>
+      <c r="AC37" s="10" t="inlineStr"/>
+      <c r="AD37" s="11" t="inlineStr"/>
+      <c r="AE37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3937,13 +3837,11 @@
       <c r="Z38" s="4" t="inlineStr"/>
       <c r="AA38" s="4" t="inlineStr"/>
       <c r="AB38" s="4" t="inlineStr"/>
-      <c r="AC38" s="4" t="inlineStr"/>
-      <c r="AD38" s="4" t="inlineStr"/>
-      <c r="AE38" s="5" t="inlineStr"/>
-      <c r="AF38" s="6" t="n">
+      <c r="AC38" s="5" t="inlineStr"/>
+      <c r="AD38" s="6" t="n">
         <v>-1.350000000000009</v>
       </c>
-      <c r="AG38" s="7" t="n">
+      <c r="AE38" s="7" t="n">
         <v>-0.1125000000000007</v>
       </c>
     </row>
@@ -4008,13 +3906,11 @@
       <c r="Z39" s="8" t="inlineStr"/>
       <c r="AA39" s="8" t="inlineStr"/>
       <c r="AB39" s="8" t="inlineStr"/>
-      <c r="AC39" s="8" t="inlineStr"/>
-      <c r="AD39" s="8" t="inlineStr"/>
-      <c r="AE39" s="10" t="n">
+      <c r="AC39" s="10" t="n">
         <v>78.64999999999999</v>
       </c>
-      <c r="AF39" s="11" t="inlineStr"/>
-      <c r="AG39" s="12" t="inlineStr"/>
+      <c r="AD39" s="11" t="inlineStr"/>
+      <c r="AE39" s="12" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="1" t="n"/>
@@ -4057,11 +3953,9 @@
       <c r="Z40" s="8" t="inlineStr"/>
       <c r="AA40" s="8" t="inlineStr"/>
       <c r="AB40" s="8" t="inlineStr"/>
-      <c r="AC40" s="8" t="inlineStr"/>
-      <c r="AD40" s="8" t="inlineStr"/>
-      <c r="AE40" s="10" t="inlineStr"/>
-      <c r="AF40" s="11" t="inlineStr"/>
-      <c r="AG40" s="12" t="inlineStr"/>
+      <c r="AC40" s="10" t="inlineStr"/>
+      <c r="AD40" s="11" t="inlineStr"/>
+      <c r="AE40" s="12" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="1" t="n"/>
@@ -4110,16 +4004,8 @@
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="S41" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
-      <c r="T41" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="S41" s="8" t="inlineStr"/>
+      <c r="T41" s="8" t="inlineStr"/>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
       <c r="W41" s="8" t="inlineStr"/>
@@ -4128,15 +4014,13 @@
       <c r="Z41" s="8" t="inlineStr"/>
       <c r="AA41" s="8" t="inlineStr"/>
       <c r="AB41" s="8" t="inlineStr"/>
-      <c r="AC41" s="8" t="inlineStr"/>
-      <c r="AD41" s="8" t="inlineStr"/>
-      <c r="AE41" s="10" t="n">
+      <c r="AC41" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="AF41" s="10" t="n">
+      <c r="AD41" s="10" t="n">
         <v>3.250000000000014</v>
       </c>
-      <c r="AG41" s="12" t="n">
+      <c r="AE41" s="12" t="n">
         <v>0.2708333333333345</v>
       </c>
     </row>
@@ -4177,11 +4061,9 @@
       <c r="Z42" s="8" t="inlineStr"/>
       <c r="AA42" s="8" t="inlineStr"/>
       <c r="AB42" s="8" t="inlineStr"/>
-      <c r="AC42" s="8" t="inlineStr"/>
-      <c r="AD42" s="8" t="inlineStr"/>
-      <c r="AE42" s="10" t="inlineStr"/>
-      <c r="AF42" s="11" t="inlineStr"/>
-      <c r="AG42" s="12" t="inlineStr"/>
+      <c r="AC42" s="10" t="inlineStr"/>
+      <c r="AD42" s="11" t="inlineStr"/>
+      <c r="AE42" s="12" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="1" t="n"/>
@@ -4220,11 +4102,9 @@
       <c r="Z43" s="8" t="inlineStr"/>
       <c r="AA43" s="8" t="inlineStr"/>
       <c r="AB43" s="8" t="inlineStr"/>
-      <c r="AC43" s="8" t="inlineStr"/>
-      <c r="AD43" s="8" t="inlineStr"/>
-      <c r="AE43" s="10" t="inlineStr"/>
-      <c r="AF43" s="11" t="inlineStr"/>
-      <c r="AG43" s="12" t="inlineStr"/>
+      <c r="AC43" s="10" t="inlineStr"/>
+      <c r="AD43" s="11" t="inlineStr"/>
+      <c r="AE43" s="12" t="inlineStr"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -4265,13 +4145,11 @@
       <c r="Z44" s="4" t="inlineStr"/>
       <c r="AA44" s="4" t="inlineStr"/>
       <c r="AB44" s="4" t="inlineStr"/>
-      <c r="AC44" s="4" t="inlineStr"/>
-      <c r="AD44" s="4" t="inlineStr"/>
-      <c r="AE44" s="5" t="inlineStr"/>
-      <c r="AF44" s="6" t="n">
+      <c r="AC44" s="5" t="inlineStr"/>
+      <c r="AD44" s="6" t="n">
         <v>-4.266666666666666</v>
       </c>
-      <c r="AG44" s="7" t="n">
+      <c r="AE44" s="7" t="n">
         <v>-0.1481481481481481</v>
       </c>
     </row>
@@ -4314,7 +4192,11 @@
       <c r="L45" s="8" t="inlineStr"/>
       <c r="M45" s="8" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
-      <c r="O45" s="8" t="inlineStr"/>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="P45" s="8" t="inlineStr"/>
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
@@ -4328,13 +4210,11 @@
       <c r="Z45" s="8" t="inlineStr"/>
       <c r="AA45" s="8" t="inlineStr"/>
       <c r="AB45" s="8" t="inlineStr"/>
-      <c r="AC45" s="8" t="inlineStr"/>
-      <c r="AD45" s="8" t="inlineStr"/>
-      <c r="AE45" s="10" t="n">
+      <c r="AC45" s="10" t="n">
         <v>11.73333333333333</v>
       </c>
-      <c r="AF45" s="11" t="inlineStr"/>
-      <c r="AG45" s="12" t="inlineStr"/>
+      <c r="AD45" s="11" t="inlineStr"/>
+      <c r="AE45" s="12" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="1" t="n"/>
@@ -4381,11 +4261,9 @@
       <c r="Z46" s="8" t="inlineStr"/>
       <c r="AA46" s="8" t="inlineStr"/>
       <c r="AB46" s="8" t="inlineStr"/>
-      <c r="AC46" s="8" t="inlineStr"/>
-      <c r="AD46" s="8" t="inlineStr"/>
-      <c r="AE46" s="10" t="inlineStr"/>
-      <c r="AF46" s="11" t="inlineStr"/>
-      <c r="AG46" s="12" t="inlineStr"/>
+      <c r="AC46" s="10" t="inlineStr"/>
+      <c r="AD46" s="11" t="inlineStr"/>
+      <c r="AE46" s="12" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="1" t="n"/>
@@ -4422,7 +4300,11 @@
       <c r="L47" s="8" t="inlineStr"/>
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
-      <c r="O47" s="8" t="inlineStr"/>
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="P47" s="8" t="inlineStr"/>
       <c r="Q47" s="8" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
@@ -4436,15 +4318,13 @@
       <c r="Z47" s="8" t="inlineStr"/>
       <c r="AA47" s="8" t="inlineStr"/>
       <c r="AB47" s="8" t="inlineStr"/>
-      <c r="AC47" s="8" t="inlineStr"/>
-      <c r="AD47" s="8" t="inlineStr"/>
-      <c r="AE47" s="10" t="n">
+      <c r="AC47" s="10" t="n">
         <v>12.36666666666667</v>
       </c>
-      <c r="AF47" s="10" t="n">
+      <c r="AD47" s="10" t="n">
         <v>0.6333333333333311</v>
       </c>
-      <c r="AG47" s="12" t="n">
+      <c r="AE47" s="12" t="n">
         <v>0.02199074074074066</v>
       </c>
     </row>
@@ -4487,13 +4367,11 @@
       <c r="Z48" s="4" t="inlineStr"/>
       <c r="AA48" s="4" t="inlineStr"/>
       <c r="AB48" s="4" t="inlineStr"/>
-      <c r="AC48" s="4" t="inlineStr"/>
-      <c r="AD48" s="4" t="inlineStr"/>
-      <c r="AE48" s="5" t="inlineStr"/>
-      <c r="AF48" s="6" t="n">
+      <c r="AC48" s="5" t="inlineStr"/>
+      <c r="AD48" s="6" t="n">
         <v>-199.25</v>
       </c>
-      <c r="AG48" s="7" t="n">
+      <c r="AE48" s="7" t="n">
         <v>-0.03029588857803187</v>
       </c>
     </row>
@@ -4550,13 +4428,11 @@
       <c r="Z49" s="8" t="inlineStr"/>
       <c r="AA49" s="8" t="inlineStr"/>
       <c r="AB49" s="8" t="inlineStr"/>
-      <c r="AC49" s="8" t="inlineStr"/>
-      <c r="AD49" s="8" t="inlineStr"/>
-      <c r="AE49" s="10" t="n">
+      <c r="AC49" s="10" t="n">
         <v>1688.75</v>
       </c>
-      <c r="AF49" s="11" t="inlineStr"/>
-      <c r="AG49" s="12" t="inlineStr"/>
+      <c r="AD49" s="11" t="inlineStr"/>
+      <c r="AE49" s="12" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="1" t="n"/>
@@ -4599,11 +4475,9 @@
       <c r="Z50" s="8" t="inlineStr"/>
       <c r="AA50" s="8" t="inlineStr"/>
       <c r="AB50" s="8" t="inlineStr"/>
-      <c r="AC50" s="8" t="inlineStr"/>
-      <c r="AD50" s="8" t="inlineStr"/>
-      <c r="AE50" s="10" t="inlineStr"/>
-      <c r="AF50" s="11" t="inlineStr"/>
-      <c r="AG50" s="12" t="inlineStr"/>
+      <c r="AC50" s="10" t="inlineStr"/>
+      <c r="AD50" s="11" t="inlineStr"/>
+      <c r="AE50" s="12" t="inlineStr"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="1" t="n"/>
@@ -4654,15 +4528,13 @@
       <c r="Z51" s="8" t="inlineStr"/>
       <c r="AA51" s="8" t="inlineStr"/>
       <c r="AB51" s="8" t="inlineStr"/>
-      <c r="AC51" s="8" t="inlineStr"/>
-      <c r="AD51" s="8" t="inlineStr"/>
-      <c r="AE51" s="10" t="n">
+      <c r="AC51" s="10" t="n">
         <v>1425</v>
       </c>
-      <c r="AF51" s="10" t="n">
+      <c r="AD51" s="10" t="n">
         <v>263.75</v>
       </c>
-      <c r="AG51" s="12" t="n">
+      <c r="AE51" s="12" t="n">
         <v>-0.04010308964846126</v>
       </c>
     </row>
@@ -4707,11 +4579,9 @@
       <c r="Z52" s="8" t="inlineStr"/>
       <c r="AA52" s="8" t="inlineStr"/>
       <c r="AB52" s="8" t="inlineStr"/>
-      <c r="AC52" s="8" t="inlineStr"/>
-      <c r="AD52" s="8" t="inlineStr"/>
-      <c r="AE52" s="10" t="inlineStr"/>
-      <c r="AF52" s="11" t="inlineStr"/>
-      <c r="AG52" s="12" t="inlineStr"/>
+      <c r="AC52" s="10" t="inlineStr"/>
+      <c r="AD52" s="11" t="inlineStr"/>
+      <c r="AE52" s="12" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="1" t="n"/>
@@ -4754,11 +4624,9 @@
       <c r="Z53" s="8" t="inlineStr"/>
       <c r="AA53" s="8" t="inlineStr"/>
       <c r="AB53" s="8" t="inlineStr"/>
-      <c r="AC53" s="8" t="inlineStr"/>
-      <c r="AD53" s="8" t="inlineStr"/>
-      <c r="AE53" s="10" t="inlineStr"/>
-      <c r="AF53" s="11" t="inlineStr"/>
-      <c r="AG53" s="12" t="inlineStr"/>
+      <c r="AC53" s="10" t="inlineStr"/>
+      <c r="AD53" s="11" t="inlineStr"/>
+      <c r="AE53" s="12" t="inlineStr"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -4799,13 +4667,11 @@
       <c r="Z54" s="4" t="inlineStr"/>
       <c r="AA54" s="4" t="inlineStr"/>
       <c r="AB54" s="4" t="inlineStr"/>
-      <c r="AC54" s="4" t="inlineStr"/>
-      <c r="AD54" s="4" t="inlineStr"/>
-      <c r="AE54" s="5" t="inlineStr"/>
-      <c r="AF54" s="6" t="n">
+      <c r="AC54" s="5" t="inlineStr"/>
+      <c r="AD54" s="6" t="n">
         <v>-9204.333333333336</v>
       </c>
-      <c r="AG54" s="7" t="n">
+      <c r="AE54" s="7" t="n">
         <v>-0.3674545921510859</v>
       </c>
     </row>
@@ -4862,13 +4728,11 @@
       <c r="Z55" s="8" t="inlineStr"/>
       <c r="AA55" s="8" t="inlineStr"/>
       <c r="AB55" s="8" t="inlineStr"/>
-      <c r="AC55" s="8" t="inlineStr"/>
-      <c r="AD55" s="8" t="inlineStr"/>
-      <c r="AE55" s="10" t="n">
+      <c r="AC55" s="10" t="n">
         <v>57571.66666666666</v>
       </c>
-      <c r="AF55" s="11" t="inlineStr"/>
-      <c r="AG55" s="12" t="inlineStr"/>
+      <c r="AD55" s="11" t="inlineStr"/>
+      <c r="AE55" s="12" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="1" t="n"/>
@@ -4907,11 +4771,9 @@
       <c r="Z56" s="8" t="inlineStr"/>
       <c r="AA56" s="8" t="inlineStr"/>
       <c r="AB56" s="8" t="inlineStr"/>
-      <c r="AC56" s="8" t="inlineStr"/>
-      <c r="AD56" s="8" t="inlineStr"/>
-      <c r="AE56" s="10" t="inlineStr"/>
-      <c r="AF56" s="11" t="inlineStr"/>
-      <c r="AG56" s="12" t="inlineStr"/>
+      <c r="AC56" s="10" t="inlineStr"/>
+      <c r="AD56" s="11" t="inlineStr"/>
+      <c r="AE56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="1" t="n"/>
@@ -4953,11 +4815,7 @@
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="P57" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="P57" s="8" t="inlineStr"/>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr"/>
@@ -4970,15 +4828,13 @@
       <c r="Z57" s="8" t="inlineStr"/>
       <c r="AA57" s="8" t="inlineStr"/>
       <c r="AB57" s="8" t="inlineStr"/>
-      <c r="AC57" s="8" t="inlineStr"/>
-      <c r="AD57" s="8" t="inlineStr"/>
-      <c r="AE57" s="10" t="n">
+      <c r="AC57" s="10" t="n">
         <v>57908.33333333334</v>
       </c>
-      <c r="AF57" s="10" t="n">
+      <c r="AD57" s="10" t="n">
         <v>336.6666666666715</v>
       </c>
-      <c r="AG57" s="12" t="n">
+      <c r="AE57" s="12" t="n">
         <v>0.01344037728869018</v>
       </c>
     </row>
@@ -5019,11 +4875,9 @@
       <c r="Z58" s="8" t="inlineStr"/>
       <c r="AA58" s="8" t="inlineStr"/>
       <c r="AB58" s="8" t="inlineStr"/>
-      <c r="AC58" s="8" t="inlineStr"/>
-      <c r="AD58" s="8" t="inlineStr"/>
-      <c r="AE58" s="10" t="inlineStr"/>
-      <c r="AF58" s="11" t="inlineStr"/>
-      <c r="AG58" s="12" t="inlineStr"/>
+      <c r="AC58" s="10" t="inlineStr"/>
+      <c r="AD58" s="11" t="inlineStr"/>
+      <c r="AE58" s="12" t="inlineStr"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="1" t="n"/>
@@ -5062,11 +4916,9 @@
       <c r="Z59" s="8" t="inlineStr"/>
       <c r="AA59" s="8" t="inlineStr"/>
       <c r="AB59" s="8" t="inlineStr"/>
-      <c r="AC59" s="8" t="inlineStr"/>
-      <c r="AD59" s="8" t="inlineStr"/>
-      <c r="AE59" s="10" t="inlineStr"/>
-      <c r="AF59" s="11" t="inlineStr"/>
-      <c r="AG59" s="12" t="inlineStr"/>
+      <c r="AC59" s="10" t="inlineStr"/>
+      <c r="AD59" s="11" t="inlineStr"/>
+      <c r="AE59" s="12" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -5107,13 +4959,11 @@
       <c r="Z60" s="4" t="inlineStr"/>
       <c r="AA60" s="4" t="inlineStr"/>
       <c r="AB60" s="4" t="inlineStr"/>
-      <c r="AC60" s="4" t="inlineStr"/>
-      <c r="AD60" s="4" t="inlineStr"/>
-      <c r="AE60" s="5" t="inlineStr"/>
-      <c r="AF60" s="6" t="n">
+      <c r="AC60" s="5" t="inlineStr"/>
+      <c r="AD60" s="6" t="n">
         <v>16.625</v>
       </c>
-      <c r="AG60" s="7" t="n">
+      <c r="AE60" s="7" t="n">
         <v>0.009140139644840287</v>
       </c>
     </row>
@@ -5170,13 +5020,11 @@
       <c r="Z61" s="8" t="inlineStr"/>
       <c r="AA61" s="8" t="inlineStr"/>
       <c r="AB61" s="8" t="inlineStr"/>
-      <c r="AC61" s="8" t="inlineStr"/>
-      <c r="AD61" s="8" t="inlineStr"/>
-      <c r="AE61" s="10" t="n">
+      <c r="AC61" s="10" t="n">
         <v>181.625</v>
       </c>
-      <c r="AF61" s="11" t="inlineStr"/>
-      <c r="AG61" s="12" t="inlineStr"/>
+      <c r="AD61" s="11" t="inlineStr"/>
+      <c r="AE61" s="12" t="inlineStr"/>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="1" t="n"/>
@@ -5219,11 +5067,9 @@
       <c r="Z62" s="8" t="inlineStr"/>
       <c r="AA62" s="8" t="inlineStr"/>
       <c r="AB62" s="8" t="inlineStr"/>
-      <c r="AC62" s="8" t="inlineStr"/>
-      <c r="AD62" s="8" t="inlineStr"/>
-      <c r="AE62" s="10" t="inlineStr"/>
-      <c r="AF62" s="11" t="inlineStr"/>
-      <c r="AG62" s="12" t="inlineStr"/>
+      <c r="AC62" s="10" t="inlineStr"/>
+      <c r="AD62" s="11" t="inlineStr"/>
+      <c r="AE62" s="12" t="inlineStr"/>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="1" t="n"/>
@@ -5274,15 +5120,13 @@
       <c r="Z63" s="8" t="inlineStr"/>
       <c r="AA63" s="8" t="inlineStr"/>
       <c r="AB63" s="8" t="inlineStr"/>
-      <c r="AC63" s="8" t="inlineStr"/>
-      <c r="AD63" s="8" t="inlineStr"/>
-      <c r="AE63" s="10" t="n">
+      <c r="AC63" s="10" t="n">
         <v>155.125</v>
       </c>
-      <c r="AF63" s="10" t="n">
+      <c r="AD63" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="AG63" s="12" t="n">
+      <c r="AE63" s="12" t="n">
         <v>-0.01456924514816647</v>
       </c>
     </row>
@@ -5327,11 +5171,9 @@
       <c r="Z64" s="8" t="inlineStr"/>
       <c r="AA64" s="8" t="inlineStr"/>
       <c r="AB64" s="8" t="inlineStr"/>
-      <c r="AC64" s="8" t="inlineStr"/>
-      <c r="AD64" s="8" t="inlineStr"/>
-      <c r="AE64" s="10" t="inlineStr"/>
-      <c r="AF64" s="11" t="inlineStr"/>
-      <c r="AG64" s="12" t="inlineStr"/>
+      <c r="AC64" s="10" t="inlineStr"/>
+      <c r="AD64" s="11" t="inlineStr"/>
+      <c r="AE64" s="12" t="inlineStr"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="1" t="n"/>
@@ -5374,11 +5216,9 @@
       <c r="Z65" s="8" t="inlineStr"/>
       <c r="AA65" s="8" t="inlineStr"/>
       <c r="AB65" s="8" t="inlineStr"/>
-      <c r="AC65" s="8" t="inlineStr"/>
-      <c r="AD65" s="8" t="inlineStr"/>
-      <c r="AE65" s="10" t="inlineStr"/>
-      <c r="AF65" s="11" t="inlineStr"/>
-      <c r="AG65" s="12" t="inlineStr"/>
+      <c r="AC65" s="10" t="inlineStr"/>
+      <c r="AD65" s="11" t="inlineStr"/>
+      <c r="AE65" s="12" t="inlineStr"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -5419,13 +5259,11 @@
       <c r="Z66" s="4" t="inlineStr"/>
       <c r="AA66" s="4" t="inlineStr"/>
       <c r="AB66" s="4" t="inlineStr"/>
-      <c r="AC66" s="4" t="inlineStr"/>
-      <c r="AD66" s="4" t="inlineStr"/>
-      <c r="AE66" s="5" t="inlineStr"/>
-      <c r="AF66" s="6" t="n">
+      <c r="AC66" s="5" t="inlineStr"/>
+      <c r="AD66" s="6" t="n">
         <v>-0.5500000000000043</v>
       </c>
-      <c r="AG66" s="7" t="n">
+      <c r="AE66" s="7" t="n">
         <v>-0.01858108108108122</v>
       </c>
     </row>
@@ -5436,7 +5274,11 @@
           <t>Retrieval 미사용</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr"/>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="D67" s="8" t="inlineStr"/>
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr"/>
@@ -5478,13 +5320,11 @@
       <c r="Z67" s="8" t="inlineStr"/>
       <c r="AA67" s="8" t="inlineStr"/>
       <c r="AB67" s="8" t="inlineStr"/>
-      <c r="AC67" s="8" t="inlineStr"/>
-      <c r="AD67" s="8" t="inlineStr"/>
-      <c r="AE67" s="10" t="n">
+      <c r="AC67" s="10" t="n">
         <v>33.45</v>
       </c>
-      <c r="AF67" s="11" t="inlineStr"/>
-      <c r="AG67" s="12" t="inlineStr"/>
+      <c r="AD67" s="11" t="inlineStr"/>
+      <c r="AE67" s="12" t="inlineStr"/>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="1" t="n"/>
@@ -5493,7 +5333,11 @@
           <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr"/>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="D68" s="8" t="inlineStr"/>
       <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="8" t="inlineStr"/>
@@ -5523,11 +5367,9 @@
       <c r="Z68" s="8" t="inlineStr"/>
       <c r="AA68" s="8" t="inlineStr"/>
       <c r="AB68" s="8" t="inlineStr"/>
-      <c r="AC68" s="8" t="inlineStr"/>
-      <c r="AD68" s="8" t="inlineStr"/>
-      <c r="AE68" s="10" t="inlineStr"/>
-      <c r="AF68" s="11" t="inlineStr"/>
-      <c r="AG68" s="12" t="inlineStr"/>
+      <c r="AC68" s="10" t="inlineStr"/>
+      <c r="AD68" s="11" t="inlineStr"/>
+      <c r="AE68" s="12" t="inlineStr"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
@@ -5536,16 +5378,12 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C69" s="14" t="inlineStr">
+      <c r="C69" s="16" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="D69" s="8" t="inlineStr"/>
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr"/>
@@ -5586,19 +5424,13 @@
       <c r="Z69" s="8" t="inlineStr"/>
       <c r="AA69" s="8" t="inlineStr"/>
       <c r="AB69" s="8" t="inlineStr"/>
-      <c r="AC69" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
-      <c r="AD69" s="8" t="inlineStr"/>
-      <c r="AE69" s="10" t="n">
+      <c r="AC69" s="10" t="n">
         <v>33.35</v>
       </c>
-      <c r="AF69" s="10" t="n">
+      <c r="AD69" s="10" t="n">
         <v>0.09999999999999432</v>
       </c>
-      <c r="AG69" s="12" t="n">
+      <c r="AE69" s="12" t="n">
         <v>-0.003378378378378186</v>
       </c>
     </row>
@@ -5609,7 +5441,11 @@
           <t>target: 16 (anchor 미설정) [value]</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr"/>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="D70" s="8" t="inlineStr"/>
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr"/>
@@ -5639,11 +5475,9 @@
       <c r="Z70" s="8" t="inlineStr"/>
       <c r="AA70" s="8" t="inlineStr"/>
       <c r="AB70" s="8" t="inlineStr"/>
-      <c r="AC70" s="8" t="inlineStr"/>
-      <c r="AD70" s="8" t="inlineStr"/>
-      <c r="AE70" s="10" t="inlineStr"/>
-      <c r="AF70" s="11" t="inlineStr"/>
-      <c r="AG70" s="12" t="inlineStr"/>
+      <c r="AC70" s="10" t="inlineStr"/>
+      <c r="AD70" s="11" t="inlineStr"/>
+      <c r="AE70" s="12" t="inlineStr"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="1" t="n"/>
@@ -5652,7 +5486,11 @@
           <t>target: 16 (anchor 미설정) [add]</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr"/>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="D71" s="8" t="inlineStr"/>
       <c r="E71" s="8" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr"/>
@@ -5682,11 +5520,9 @@
       <c r="Z71" s="8" t="inlineStr"/>
       <c r="AA71" s="8" t="inlineStr"/>
       <c r="AB71" s="8" t="inlineStr"/>
-      <c r="AC71" s="8" t="inlineStr"/>
-      <c r="AD71" s="8" t="inlineStr"/>
-      <c r="AE71" s="10" t="inlineStr"/>
-      <c r="AF71" s="11" t="inlineStr"/>
-      <c r="AG71" s="12" t="inlineStr"/>
+      <c r="AC71" s="10" t="inlineStr"/>
+      <c r="AD71" s="11" t="inlineStr"/>
+      <c r="AE71" s="12" t="inlineStr"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -5727,13 +5563,11 @@
       <c r="Z72" s="4" t="inlineStr"/>
       <c r="AA72" s="4" t="inlineStr"/>
       <c r="AB72" s="4" t="inlineStr"/>
-      <c r="AC72" s="4" t="inlineStr"/>
-      <c r="AD72" s="4" t="inlineStr"/>
-      <c r="AE72" s="5" t="inlineStr"/>
-      <c r="AF72" s="6" t="n">
+      <c r="AC72" s="5" t="inlineStr"/>
+      <c r="AD72" s="6" t="n">
         <v>426.375</v>
       </c>
-      <c r="AG72" s="7" t="n">
+      <c r="AE72" s="7" t="n">
         <v>0.09986532380840848</v>
       </c>
     </row>
@@ -5790,13 +5624,11 @@
       <c r="Z73" s="8" t="inlineStr"/>
       <c r="AA73" s="8" t="inlineStr"/>
       <c r="AB73" s="8" t="inlineStr"/>
-      <c r="AC73" s="8" t="inlineStr"/>
-      <c r="AD73" s="8" t="inlineStr"/>
-      <c r="AE73" s="10" t="n">
+      <c r="AC73" s="10" t="n">
         <v>1742.375</v>
       </c>
-      <c r="AF73" s="11" t="inlineStr"/>
-      <c r="AG73" s="12" t="inlineStr"/>
+      <c r="AD73" s="11" t="inlineStr"/>
+      <c r="AE73" s="12" t="inlineStr"/>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="1" t="n"/>
@@ -5851,11 +5683,9 @@
       <c r="Z74" s="8" t="inlineStr"/>
       <c r="AA74" s="8" t="inlineStr"/>
       <c r="AB74" s="8" t="inlineStr"/>
-      <c r="AC74" s="8" t="inlineStr"/>
-      <c r="AD74" s="8" t="inlineStr"/>
-      <c r="AE74" s="10" t="inlineStr"/>
-      <c r="AF74" s="11" t="inlineStr"/>
-      <c r="AG74" s="12" t="inlineStr"/>
+      <c r="AC74" s="10" t="inlineStr"/>
+      <c r="AD74" s="11" t="inlineStr"/>
+      <c r="AE74" s="12" t="inlineStr"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="1" t="n"/>
@@ -5918,15 +5748,13 @@
       <c r="Z75" s="8" t="inlineStr"/>
       <c r="AA75" s="8" t="inlineStr"/>
       <c r="AB75" s="8" t="inlineStr"/>
-      <c r="AC75" s="8" t="inlineStr"/>
-      <c r="AD75" s="8" t="inlineStr"/>
-      <c r="AE75" s="10" t="n">
+      <c r="AC75" s="10" t="n">
         <v>1986.75</v>
       </c>
-      <c r="AF75" s="10" t="n">
+      <c r="AD75" s="10" t="n">
         <v>244.375</v>
       </c>
-      <c r="AG75" s="12" t="n">
+      <c r="AE75" s="12" t="n">
         <v>0.05723738142639653</v>
       </c>
     </row>
@@ -5971,11 +5799,9 @@
       <c r="Z76" s="8" t="inlineStr"/>
       <c r="AA76" s="8" t="inlineStr"/>
       <c r="AB76" s="8" t="inlineStr"/>
-      <c r="AC76" s="8" t="inlineStr"/>
-      <c r="AD76" s="8" t="inlineStr"/>
-      <c r="AE76" s="10" t="inlineStr"/>
-      <c r="AF76" s="11" t="inlineStr"/>
-      <c r="AG76" s="12" t="inlineStr"/>
+      <c r="AC76" s="10" t="inlineStr"/>
+      <c r="AD76" s="11" t="inlineStr"/>
+      <c r="AE76" s="12" t="inlineStr"/>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="1" t="n"/>
@@ -6014,11 +5840,9 @@
       <c r="Z77" s="8" t="inlineStr"/>
       <c r="AA77" s="8" t="inlineStr"/>
       <c r="AB77" s="8" t="inlineStr"/>
-      <c r="AC77" s="8" t="inlineStr"/>
-      <c r="AD77" s="8" t="inlineStr"/>
-      <c r="AE77" s="10" t="inlineStr"/>
-      <c r="AF77" s="11" t="inlineStr"/>
-      <c r="AG77" s="12" t="inlineStr"/>
+      <c r="AC77" s="10" t="inlineStr"/>
+      <c r="AD77" s="11" t="inlineStr"/>
+      <c r="AE77" s="12" t="inlineStr"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -6059,13 +5883,11 @@
       <c r="Z78" s="4" t="inlineStr"/>
       <c r="AA78" s="4" t="inlineStr"/>
       <c r="AB78" s="4" t="inlineStr"/>
-      <c r="AC78" s="4" t="inlineStr"/>
-      <c r="AD78" s="4" t="inlineStr"/>
-      <c r="AE78" s="5" t="inlineStr"/>
-      <c r="AF78" s="6" t="n">
+      <c r="AC78" s="5" t="inlineStr"/>
+      <c r="AD78" s="6" t="n">
         <v>-3430.5</v>
       </c>
-      <c r="AG78" s="7" t="n">
+      <c r="AE78" s="7" t="n">
         <v>-1.591953222887373</v>
       </c>
     </row>
@@ -6124,31 +5946,29 @@
       <c r="T79" s="8" t="inlineStr"/>
       <c r="U79" s="8" t="inlineStr"/>
       <c r="V79" s="8" t="inlineStr"/>
-      <c r="W79" s="8" t="inlineStr"/>
-      <c r="X79" s="8" t="inlineStr"/>
-      <c r="Y79" s="9" t="inlineStr"/>
-      <c r="Z79" s="9" t="inlineStr"/>
-      <c r="AA79" s="8" t="inlineStr">
+      <c r="W79" s="9" t="inlineStr"/>
+      <c r="X79" s="9" t="inlineStr"/>
+      <c r="Y79" s="8" t="inlineStr">
         <is>
           <t>8159.00</t>
         </is>
       </c>
-      <c r="AB79" s="8" t="inlineStr">
+      <c r="Z79" s="8" t="inlineStr">
         <is>
           <t>3585.00</t>
         </is>
       </c>
-      <c r="AC79" s="9" t="inlineStr">
+      <c r="AA79" s="9" t="inlineStr">
         <is>
           <t>2594.00</t>
         </is>
       </c>
-      <c r="AD79" s="8" t="inlineStr"/>
-      <c r="AE79" s="10" t="n">
+      <c r="AB79" s="8" t="inlineStr"/>
+      <c r="AC79" s="10" t="n">
         <v>4809.5</v>
       </c>
-      <c r="AF79" s="11" t="inlineStr"/>
-      <c r="AG79" s="12" t="inlineStr"/>
+      <c r="AD79" s="11" t="inlineStr"/>
+      <c r="AE79" s="12" t="inlineStr"/>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="1" t="n"/>
@@ -6181,21 +6001,19 @@
       <c r="T80" s="8" t="inlineStr"/>
       <c r="U80" s="8" t="inlineStr"/>
       <c r="V80" s="8" t="inlineStr"/>
-      <c r="W80" s="8" t="inlineStr"/>
-      <c r="X80" s="8" t="inlineStr"/>
-      <c r="Y80" s="9" t="inlineStr"/>
-      <c r="Z80" s="9" t="inlineStr"/>
-      <c r="AA80" s="8" t="inlineStr"/>
-      <c r="AB80" s="8" t="inlineStr">
+      <c r="W80" s="9" t="inlineStr"/>
+      <c r="X80" s="9" t="inlineStr"/>
+      <c r="Y80" s="8" t="inlineStr"/>
+      <c r="Z80" s="8" t="inlineStr">
         <is>
           <t>4472.00</t>
         </is>
       </c>
-      <c r="AC80" s="9" t="inlineStr"/>
-      <c r="AD80" s="8" t="inlineStr"/>
-      <c r="AE80" s="10" t="inlineStr"/>
-      <c r="AF80" s="11" t="inlineStr"/>
-      <c r="AG80" s="12" t="inlineStr"/>
+      <c r="AA80" s="9" t="inlineStr"/>
+      <c r="AB80" s="8" t="inlineStr"/>
+      <c r="AC80" s="10" t="inlineStr"/>
+      <c r="AD80" s="11" t="inlineStr"/>
+      <c r="AE80" s="12" t="inlineStr"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
@@ -6254,51 +6072,45 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="U81" s="14" t="inlineStr">
+      <c r="U81" s="8" t="inlineStr"/>
+      <c r="V81" s="14" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="V81" s="8" t="inlineStr"/>
-      <c r="W81" s="8" t="inlineStr"/>
-      <c r="X81" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
-      <c r="Y81" s="13" t="inlineStr">
+      <c r="W81" s="13" t="inlineStr">
         <is>
           <t>1437.00</t>
         </is>
       </c>
-      <c r="Z81" s="13" t="inlineStr">
+      <c r="X81" s="13" t="inlineStr">
         <is>
           <t>3061.00</t>
         </is>
       </c>
-      <c r="AA81" s="16" t="inlineStr">
+      <c r="Y81" s="17" t="inlineStr">
         <is>
           <t>8373.00</t>
         </is>
       </c>
-      <c r="AB81" s="8" t="inlineStr">
+      <c r="Z81" s="8" t="inlineStr">
         <is>
           <t>7531.00</t>
         </is>
       </c>
-      <c r="AC81" s="9" t="inlineStr">
+      <c r="AA81" s="9" t="inlineStr">
         <is>
           <t>1005.00</t>
         </is>
       </c>
-      <c r="AD81" s="8" t="inlineStr"/>
-      <c r="AE81" s="10" t="n">
+      <c r="AB81" s="8" t="inlineStr"/>
+      <c r="AC81" s="10" t="n">
         <v>5765</v>
       </c>
-      <c r="AF81" s="10" t="n">
+      <c r="AD81" s="10" t="n">
         <v>955.5</v>
       </c>
-      <c r="AG81" s="12" t="n">
+      <c r="AE81" s="12" t="n">
         <v>0.4434080467771126</v>
       </c>
     </row>
@@ -6329,21 +6141,19 @@
       <c r="T82" s="8" t="inlineStr"/>
       <c r="U82" s="8" t="inlineStr"/>
       <c r="V82" s="8" t="inlineStr"/>
-      <c r="W82" s="8" t="inlineStr"/>
-      <c r="X82" s="8" t="inlineStr"/>
-      <c r="Y82" s="9" t="inlineStr"/>
-      <c r="Z82" s="9" t="inlineStr"/>
-      <c r="AA82" s="8" t="inlineStr"/>
-      <c r="AB82" s="8" t="inlineStr">
+      <c r="W82" s="9" t="inlineStr"/>
+      <c r="X82" s="9" t="inlineStr"/>
+      <c r="Y82" s="8" t="inlineStr"/>
+      <c r="Z82" s="8" t="inlineStr">
         <is>
           <t>5320.00</t>
         </is>
       </c>
-      <c r="AC82" s="9" t="inlineStr"/>
-      <c r="AD82" s="8" t="inlineStr"/>
-      <c r="AE82" s="10" t="inlineStr"/>
-      <c r="AF82" s="11" t="inlineStr"/>
-      <c r="AG82" s="12" t="inlineStr"/>
+      <c r="AA82" s="9" t="inlineStr"/>
+      <c r="AB82" s="8" t="inlineStr"/>
+      <c r="AC82" s="10" t="inlineStr"/>
+      <c r="AD82" s="11" t="inlineStr"/>
+      <c r="AE82" s="12" t="inlineStr"/>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="1" t="n"/>
@@ -6372,21 +6182,19 @@
       <c r="T83" s="8" t="inlineStr"/>
       <c r="U83" s="8" t="inlineStr"/>
       <c r="V83" s="8" t="inlineStr"/>
-      <c r="W83" s="8" t="inlineStr"/>
-      <c r="X83" s="8" t="inlineStr"/>
-      <c r="Y83" s="9" t="inlineStr"/>
-      <c r="Z83" s="9" t="inlineStr"/>
-      <c r="AA83" s="8" t="inlineStr"/>
-      <c r="AB83" s="8" t="inlineStr">
+      <c r="W83" s="9" t="inlineStr"/>
+      <c r="X83" s="9" t="inlineStr"/>
+      <c r="Y83" s="8" t="inlineStr"/>
+      <c r="Z83" s="8" t="inlineStr">
         <is>
           <t>2516.00</t>
         </is>
       </c>
-      <c r="AC83" s="9" t="inlineStr"/>
-      <c r="AD83" s="8" t="inlineStr"/>
-      <c r="AE83" s="10" t="inlineStr"/>
-      <c r="AF83" s="11" t="inlineStr"/>
-      <c r="AG83" s="12" t="inlineStr"/>
+      <c r="AA83" s="9" t="inlineStr"/>
+      <c r="AB83" s="8" t="inlineStr"/>
+      <c r="AC83" s="10" t="inlineStr"/>
+      <c r="AD83" s="11" t="inlineStr"/>
+      <c r="AE83" s="12" t="inlineStr"/>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -6427,13 +6235,11 @@
       <c r="Z84" s="4" t="inlineStr"/>
       <c r="AA84" s="4" t="inlineStr"/>
       <c r="AB84" s="4" t="inlineStr"/>
-      <c r="AC84" s="4" t="inlineStr"/>
-      <c r="AD84" s="4" t="inlineStr"/>
-      <c r="AE84" s="5" t="inlineStr"/>
-      <c r="AF84" s="6" t="n">
+      <c r="AC84" s="5" t="inlineStr"/>
+      <c r="AD84" s="6" t="n">
         <v>741.625</v>
       </c>
-      <c r="AG84" s="7" t="n">
+      <c r="AE84" s="7" t="n">
         <v>0.02488724605193393</v>
       </c>
     </row>
@@ -6486,13 +6292,11 @@
       <c r="Z85" s="8" t="inlineStr"/>
       <c r="AA85" s="8" t="inlineStr"/>
       <c r="AB85" s="8" t="inlineStr"/>
-      <c r="AC85" s="8" t="inlineStr"/>
-      <c r="AD85" s="8" t="inlineStr"/>
-      <c r="AE85" s="10" t="n">
+      <c r="AC85" s="10" t="n">
         <v>11785.625</v>
       </c>
-      <c r="AF85" s="11" t="inlineStr"/>
-      <c r="AG85" s="12" t="inlineStr"/>
+      <c r="AD85" s="11" t="inlineStr"/>
+      <c r="AE85" s="12" t="inlineStr"/>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="1" t="n"/>
@@ -6531,11 +6335,9 @@
       <c r="Z86" s="8" t="inlineStr"/>
       <c r="AA86" s="8" t="inlineStr"/>
       <c r="AB86" s="8" t="inlineStr"/>
-      <c r="AC86" s="8" t="inlineStr"/>
-      <c r="AD86" s="8" t="inlineStr"/>
-      <c r="AE86" s="10" t="inlineStr"/>
-      <c r="AF86" s="11" t="inlineStr"/>
-      <c r="AG86" s="12" t="inlineStr"/>
+      <c r="AC86" s="10" t="inlineStr"/>
+      <c r="AD86" s="11" t="inlineStr"/>
+      <c r="AE86" s="12" t="inlineStr"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="1" t="n"/>
@@ -6586,15 +6388,13 @@
       <c r="Z87" s="8" t="inlineStr"/>
       <c r="AA87" s="8" t="inlineStr"/>
       <c r="AB87" s="8" t="inlineStr"/>
-      <c r="AC87" s="8" t="inlineStr"/>
-      <c r="AD87" s="8" t="inlineStr"/>
-      <c r="AE87" s="10" t="n">
+      <c r="AC87" s="10" t="n">
         <v>13229.25</v>
       </c>
-      <c r="AF87" s="10" t="n">
+      <c r="AD87" s="10" t="n">
         <v>1443.625</v>
       </c>
-      <c r="AG87" s="12" t="n">
+      <c r="AE87" s="12" t="n">
         <v>0.04844476734430894</v>
       </c>
     </row>
@@ -6635,11 +6435,9 @@
       <c r="Z88" s="8" t="inlineStr"/>
       <c r="AA88" s="8" t="inlineStr"/>
       <c r="AB88" s="8" t="inlineStr"/>
-      <c r="AC88" s="8" t="inlineStr"/>
-      <c r="AD88" s="8" t="inlineStr"/>
-      <c r="AE88" s="10" t="inlineStr"/>
-      <c r="AF88" s="11" t="inlineStr"/>
-      <c r="AG88" s="12" t="inlineStr"/>
+      <c r="AC88" s="10" t="inlineStr"/>
+      <c r="AD88" s="11" t="inlineStr"/>
+      <c r="AE88" s="12" t="inlineStr"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="1" t="n"/>
@@ -6678,11 +6476,9 @@
       <c r="Z89" s="8" t="inlineStr"/>
       <c r="AA89" s="8" t="inlineStr"/>
       <c r="AB89" s="8" t="inlineStr"/>
-      <c r="AC89" s="8" t="inlineStr"/>
-      <c r="AD89" s="8" t="inlineStr"/>
-      <c r="AE89" s="10" t="inlineStr"/>
-      <c r="AF89" s="11" t="inlineStr"/>
-      <c r="AG89" s="12" t="inlineStr"/>
+      <c r="AC89" s="10" t="inlineStr"/>
+      <c r="AD89" s="11" t="inlineStr"/>
+      <c r="AE89" s="12" t="inlineStr"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -6723,13 +6519,11 @@
       <c r="Z90" s="4" t="inlineStr"/>
       <c r="AA90" s="4" t="inlineStr"/>
       <c r="AB90" s="4" t="inlineStr"/>
-      <c r="AC90" s="4" t="inlineStr"/>
-      <c r="AD90" s="4" t="inlineStr"/>
-      <c r="AE90" s="5" t="inlineStr"/>
-      <c r="AF90" s="6" t="n">
+      <c r="AC90" s="5" t="inlineStr"/>
+      <c r="AD90" s="6" t="n">
         <v>-35.66666666666669</v>
       </c>
-      <c r="AG90" s="7" t="n">
+      <c r="AE90" s="7" t="n">
         <v>-0.1302654005356709</v>
       </c>
     </row>
@@ -6776,19 +6570,17 @@
       <c r="X91" s="8" t="inlineStr"/>
       <c r="Y91" s="8" t="inlineStr"/>
       <c r="Z91" s="8" t="inlineStr"/>
-      <c r="AA91" s="8" t="inlineStr"/>
+      <c r="AA91" s="8" t="inlineStr">
+        <is>
+          <t>365.00</t>
+        </is>
+      </c>
       <c r="AB91" s="8" t="inlineStr"/>
-      <c r="AC91" s="8" t="inlineStr">
-        <is>
-          <t>365.00</t>
-        </is>
-      </c>
-      <c r="AD91" s="8" t="inlineStr"/>
-      <c r="AE91" s="10" t="n">
+      <c r="AC91" s="10" t="n">
         <v>473.3333333333333</v>
       </c>
-      <c r="AF91" s="11" t="inlineStr"/>
-      <c r="AG91" s="12" t="inlineStr"/>
+      <c r="AD91" s="11" t="inlineStr"/>
+      <c r="AE91" s="12" t="inlineStr"/>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="1" t="n"/>
@@ -6827,11 +6619,9 @@
       <c r="Z92" s="8" t="inlineStr"/>
       <c r="AA92" s="8" t="inlineStr"/>
       <c r="AB92" s="8" t="inlineStr"/>
-      <c r="AC92" s="8" t="inlineStr"/>
-      <c r="AD92" s="8" t="inlineStr"/>
-      <c r="AE92" s="10" t="inlineStr"/>
-      <c r="AF92" s="11" t="inlineStr"/>
-      <c r="AG92" s="12" t="inlineStr"/>
+      <c r="AC92" s="10" t="inlineStr"/>
+      <c r="AD92" s="11" t="inlineStr"/>
+      <c r="AE92" s="12" t="inlineStr"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
@@ -6876,21 +6666,19 @@
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="8" t="inlineStr"/>
       <c r="Z93" s="8" t="inlineStr"/>
-      <c r="AA93" s="8" t="inlineStr"/>
+      <c r="AA93" s="8" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
       <c r="AB93" s="8" t="inlineStr"/>
-      <c r="AC93" s="8" t="inlineStr">
-        <is>
-          <t>375.00</t>
-        </is>
-      </c>
-      <c r="AD93" s="8" t="inlineStr"/>
-      <c r="AE93" s="10" t="n">
+      <c r="AC93" s="10" t="n">
         <v>535.8333333333334</v>
       </c>
-      <c r="AF93" s="10" t="n">
+      <c r="AD93" s="10" t="n">
         <v>62.50000000000006</v>
       </c>
-      <c r="AG93" s="12" t="n">
+      <c r="AE93" s="12" t="n">
         <v>0.2282688093498906</v>
       </c>
     </row>
@@ -6933,13 +6721,11 @@
       <c r="Z94" s="4" t="inlineStr"/>
       <c r="AA94" s="4" t="inlineStr"/>
       <c r="AB94" s="4" t="inlineStr"/>
-      <c r="AC94" s="4" t="inlineStr"/>
-      <c r="AD94" s="4" t="inlineStr"/>
-      <c r="AE94" s="5" t="inlineStr"/>
-      <c r="AF94" s="6" t="n">
+      <c r="AC94" s="5" t="inlineStr"/>
+      <c r="AD94" s="6" t="n">
         <v>-2611.333333333333</v>
       </c>
-      <c r="AG94" s="7" t="n">
+      <c r="AE94" s="7" t="n">
         <v>-0.8754050731925354</v>
       </c>
     </row>
@@ -6994,15 +6780,13 @@
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="8" t="inlineStr"/>
       <c r="Z95" s="8" t="inlineStr"/>
-      <c r="AA95" s="8" t="inlineStr"/>
+      <c r="AA95" s="9" t="inlineStr"/>
       <c r="AB95" s="8" t="inlineStr"/>
-      <c r="AC95" s="9" t="inlineStr"/>
-      <c r="AD95" s="8" t="inlineStr"/>
-      <c r="AE95" s="10" t="n">
+      <c r="AC95" s="10" t="n">
         <v>1596.666666666667</v>
       </c>
-      <c r="AF95" s="11" t="inlineStr"/>
-      <c r="AG95" s="12" t="inlineStr"/>
+      <c r="AD95" s="11" t="inlineStr"/>
+      <c r="AE95" s="12" t="inlineStr"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="1" t="n"/>
@@ -7047,13 +6831,11 @@
       <c r="X96" s="8" t="inlineStr"/>
       <c r="Y96" s="8" t="inlineStr"/>
       <c r="Z96" s="8" t="inlineStr"/>
-      <c r="AA96" s="8" t="inlineStr"/>
+      <c r="AA96" s="9" t="inlineStr"/>
       <c r="AB96" s="8" t="inlineStr"/>
-      <c r="AC96" s="9" t="inlineStr"/>
-      <c r="AD96" s="8" t="inlineStr"/>
-      <c r="AE96" s="10" t="inlineStr"/>
-      <c r="AF96" s="11" t="inlineStr"/>
-      <c r="AG96" s="12" t="inlineStr"/>
+      <c r="AC96" s="10" t="inlineStr"/>
+      <c r="AD96" s="11" t="inlineStr"/>
+      <c r="AE96" s="12" t="inlineStr"/>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="1" t="n"/>
@@ -7062,11 +6844,7 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C97" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="C97" s="8" t="inlineStr"/>
       <c r="D97" s="8" t="inlineStr"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
@@ -7101,7 +6879,7 @@
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="R97" s="16" t="inlineStr">
+      <c r="R97" s="17" t="inlineStr">
         <is>
           <t>2900.00</t>
         </is>
@@ -7111,28 +6889,30 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="T97" s="8" t="inlineStr"/>
+      <c r="T97" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr"/>
       <c r="X97" s="8" t="inlineStr"/>
       <c r="Y97" s="8" t="inlineStr"/>
       <c r="Z97" s="8" t="inlineStr"/>
-      <c r="AA97" s="8" t="inlineStr"/>
+      <c r="AA97" s="13" t="inlineStr">
+        <is>
+          <t>1760.00</t>
+        </is>
+      </c>
       <c r="AB97" s="8" t="inlineStr"/>
-      <c r="AC97" s="13" t="inlineStr">
-        <is>
-          <t>1760.00</t>
-        </is>
-      </c>
-      <c r="AD97" s="8" t="inlineStr"/>
-      <c r="AE97" s="10" t="n">
+      <c r="AC97" s="10" t="n">
         <v>1673.333333333333</v>
       </c>
-      <c r="AF97" s="10" t="n">
+      <c r="AD97" s="10" t="n">
         <v>76.66666666666652</v>
       </c>
-      <c r="AG97" s="12" t="n">
+      <c r="AE97" s="12" t="n">
         <v>0.02570119566431998</v>
       </c>
     </row>
@@ -7175,13 +6955,11 @@
       <c r="Z98" s="4" t="inlineStr"/>
       <c r="AA98" s="4" t="inlineStr"/>
       <c r="AB98" s="4" t="inlineStr"/>
-      <c r="AC98" s="4" t="inlineStr"/>
-      <c r="AD98" s="4" t="inlineStr"/>
-      <c r="AE98" s="5" t="inlineStr"/>
-      <c r="AF98" s="6" t="n">
+      <c r="AC98" s="5" t="inlineStr"/>
+      <c r="AD98" s="6" t="n">
         <v>-2583.375</v>
       </c>
-      <c r="AG98" s="7" t="n">
+      <c r="AE98" s="7" t="n">
         <v>-2.420023419203747</v>
       </c>
     </row>
@@ -7244,19 +7022,17 @@
       <c r="X99" s="8" t="inlineStr"/>
       <c r="Y99" s="8" t="inlineStr"/>
       <c r="Z99" s="8" t="inlineStr"/>
-      <c r="AA99" s="8" t="inlineStr"/>
+      <c r="AA99" s="8" t="inlineStr">
+        <is>
+          <t>6289.00</t>
+        </is>
+      </c>
       <c r="AB99" s="8" t="inlineStr"/>
-      <c r="AC99" s="8" t="inlineStr">
-        <is>
-          <t>6289.00</t>
-        </is>
-      </c>
-      <c r="AD99" s="8" t="inlineStr"/>
-      <c r="AE99" s="10" t="n">
+      <c r="AC99" s="10" t="n">
         <v>5829.625</v>
       </c>
-      <c r="AF99" s="11" t="inlineStr"/>
-      <c r="AG99" s="12" t="inlineStr"/>
+      <c r="AD99" s="11" t="inlineStr"/>
+      <c r="AE99" s="12" t="inlineStr"/>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="1" t="n"/>
@@ -7297,17 +7073,15 @@
       <c r="X100" s="8" t="inlineStr"/>
       <c r="Y100" s="8" t="inlineStr"/>
       <c r="Z100" s="8" t="inlineStr"/>
-      <c r="AA100" s="8" t="inlineStr"/>
+      <c r="AA100" s="8" t="inlineStr">
+        <is>
+          <t>6587.00</t>
+        </is>
+      </c>
       <c r="AB100" s="8" t="inlineStr"/>
-      <c r="AC100" s="8" t="inlineStr">
-        <is>
-          <t>6587.00</t>
-        </is>
-      </c>
-      <c r="AD100" s="8" t="inlineStr"/>
-      <c r="AE100" s="10" t="inlineStr"/>
-      <c r="AF100" s="11" t="inlineStr"/>
-      <c r="AG100" s="12" t="inlineStr"/>
+      <c r="AC100" s="10" t="inlineStr"/>
+      <c r="AD100" s="11" t="inlineStr"/>
+      <c r="AE100" s="12" t="inlineStr"/>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="1" t="n"/>
@@ -7316,11 +7090,7 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="C101" s="8" t="inlineStr"/>
       <c r="D101" s="8" t="inlineStr"/>
       <c r="E101" s="8" t="inlineStr">
         <is>
@@ -7364,7 +7134,7 @@
           <t>5596.50</t>
         </is>
       </c>
-      <c r="S101" s="16" t="inlineStr">
+      <c r="S101" s="17" t="inlineStr">
         <is>
           <t>6424.00</t>
         </is>
@@ -7374,35 +7144,25 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="U101" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="U101" s="8" t="inlineStr"/>
       <c r="V101" s="8" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr"/>
       <c r="X101" s="8" t="inlineStr"/>
       <c r="Y101" s="8" t="inlineStr"/>
       <c r="Z101" s="8" t="inlineStr"/>
-      <c r="AA101" s="8" t="inlineStr"/>
-      <c r="AB101" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
-      <c r="AC101" s="8" t="inlineStr">
+      <c r="AA101" s="8" t="inlineStr">
         <is>
           <t>6796.50</t>
         </is>
       </c>
-      <c r="AD101" s="8" t="inlineStr"/>
-      <c r="AE101" s="10" t="n">
+      <c r="AB101" s="8" t="inlineStr"/>
+      <c r="AC101" s="10" t="n">
         <v>6662.25</v>
       </c>
-      <c r="AF101" s="10" t="n">
+      <c r="AD101" s="10" t="n">
         <v>832.625</v>
       </c>
-      <c r="AG101" s="12" t="n">
+      <c r="AE101" s="12" t="n">
         <v>0.779976580796253</v>
       </c>
     </row>
@@ -7445,13 +7205,11 @@
       <c r="Z102" s="4" t="inlineStr"/>
       <c r="AA102" s="4" t="inlineStr"/>
       <c r="AB102" s="4" t="inlineStr"/>
-      <c r="AC102" s="4" t="inlineStr"/>
-      <c r="AD102" s="4" t="inlineStr"/>
-      <c r="AE102" s="5" t="inlineStr"/>
-      <c r="AF102" s="6" t="n">
+      <c r="AC102" s="5" t="inlineStr"/>
+      <c r="AD102" s="6" t="n">
         <v>-1044.5</v>
       </c>
-      <c r="AG102" s="7" t="n">
+      <c r="AE102" s="7" t="n">
         <v>-0.04646807071866464</v>
       </c>
     </row>
@@ -7498,15 +7256,17 @@
       <c r="X103" s="8" t="inlineStr"/>
       <c r="Y103" s="8" t="inlineStr"/>
       <c r="Z103" s="8" t="inlineStr"/>
-      <c r="AA103" s="8" t="inlineStr"/>
+      <c r="AA103" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="AB103" s="8" t="inlineStr"/>
-      <c r="AC103" s="8" t="inlineStr"/>
-      <c r="AD103" s="8" t="inlineStr"/>
-      <c r="AE103" s="10" t="n">
+      <c r="AC103" s="10" t="n">
         <v>25137.5</v>
       </c>
-      <c r="AF103" s="11" t="inlineStr"/>
-      <c r="AG103" s="12" t="inlineStr"/>
+      <c r="AD103" s="11" t="inlineStr"/>
+      <c r="AE103" s="12" t="inlineStr"/>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="1" t="n"/>
@@ -7545,11 +7305,9 @@
       <c r="Z104" s="8" t="inlineStr"/>
       <c r="AA104" s="8" t="inlineStr"/>
       <c r="AB104" s="8" t="inlineStr"/>
-      <c r="AC104" s="8" t="inlineStr"/>
-      <c r="AD104" s="8" t="inlineStr"/>
-      <c r="AE104" s="10" t="inlineStr"/>
-      <c r="AF104" s="11" t="inlineStr"/>
-      <c r="AG104" s="12" t="inlineStr"/>
+      <c r="AC104" s="10" t="inlineStr"/>
+      <c r="AD104" s="11" t="inlineStr"/>
+      <c r="AE104" s="12" t="inlineStr"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
@@ -7594,17 +7352,19 @@
       <c r="X105" s="8" t="inlineStr"/>
       <c r="Y105" s="8" t="inlineStr"/>
       <c r="Z105" s="8" t="inlineStr"/>
-      <c r="AA105" s="8" t="inlineStr"/>
+      <c r="AA105" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="AB105" s="8" t="inlineStr"/>
-      <c r="AC105" s="8" t="inlineStr"/>
-      <c r="AD105" s="8" t="inlineStr"/>
-      <c r="AE105" s="10" t="n">
+      <c r="AC105" s="10" t="n">
         <v>25177.5</v>
       </c>
-      <c r="AF105" s="10" t="n">
+      <c r="AD105" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="AG105" s="12" t="n">
+      <c r="AE105" s="12" t="n">
         <v>0.001779533584247569</v>
       </c>
     </row>
@@ -7645,11 +7405,9 @@
       <c r="Z106" s="8" t="inlineStr"/>
       <c r="AA106" s="8" t="inlineStr"/>
       <c r="AB106" s="8" t="inlineStr"/>
-      <c r="AC106" s="8" t="inlineStr"/>
-      <c r="AD106" s="8" t="inlineStr"/>
-      <c r="AE106" s="10" t="inlineStr"/>
-      <c r="AF106" s="11" t="inlineStr"/>
-      <c r="AG106" s="12" t="inlineStr"/>
+      <c r="AC106" s="10" t="inlineStr"/>
+      <c r="AD106" s="11" t="inlineStr"/>
+      <c r="AE106" s="12" t="inlineStr"/>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="1" t="n"/>
@@ -7688,11 +7446,9 @@
       <c r="Z107" s="8" t="inlineStr"/>
       <c r="AA107" s="8" t="inlineStr"/>
       <c r="AB107" s="8" t="inlineStr"/>
-      <c r="AC107" s="8" t="inlineStr"/>
-      <c r="AD107" s="8" t="inlineStr"/>
-      <c r="AE107" s="10" t="inlineStr"/>
-      <c r="AF107" s="11" t="inlineStr"/>
-      <c r="AG107" s="12" t="inlineStr"/>
+      <c r="AC107" s="10" t="inlineStr"/>
+      <c r="AD107" s="11" t="inlineStr"/>
+      <c r="AE107" s="12" t="inlineStr"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -7733,13 +7489,11 @@
       <c r="Z108" s="4" t="inlineStr"/>
       <c r="AA108" s="4" t="inlineStr"/>
       <c r="AB108" s="4" t="inlineStr"/>
-      <c r="AC108" s="4" t="inlineStr"/>
-      <c r="AD108" s="4" t="inlineStr"/>
-      <c r="AE108" s="5" t="inlineStr"/>
-      <c r="AF108" s="6" t="n">
+      <c r="AC108" s="5" t="inlineStr"/>
+      <c r="AD108" s="6" t="n">
         <v>-699.3333333333333</v>
       </c>
-      <c r="AG108" s="7" t="n">
+      <c r="AE108" s="7" t="n">
         <v>-0.1052531242317977</v>
       </c>
     </row>
@@ -7784,7 +7538,11 @@
           <t>1779.00</t>
         </is>
       </c>
-      <c r="Q109" s="8" t="inlineStr"/>
+      <c r="Q109" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="R109" s="8" t="inlineStr"/>
       <c r="S109" s="8" t="inlineStr"/>
       <c r="T109" s="8" t="inlineStr"/>
@@ -7796,13 +7554,11 @@
       <c r="Z109" s="8" t="inlineStr"/>
       <c r="AA109" s="8" t="inlineStr"/>
       <c r="AB109" s="8" t="inlineStr"/>
-      <c r="AC109" s="8" t="inlineStr"/>
-      <c r="AD109" s="8" t="inlineStr"/>
-      <c r="AE109" s="10" t="n">
+      <c r="AC109" s="10" t="n">
         <v>1973.666666666667</v>
       </c>
-      <c r="AF109" s="11" t="inlineStr"/>
-      <c r="AG109" s="12" t="inlineStr"/>
+      <c r="AD109" s="11" t="inlineStr"/>
+      <c r="AE109" s="12" t="inlineStr"/>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="1" t="n"/>
@@ -7841,11 +7597,9 @@
       <c r="Z110" s="8" t="inlineStr"/>
       <c r="AA110" s="8" t="inlineStr"/>
       <c r="AB110" s="8" t="inlineStr"/>
-      <c r="AC110" s="8" t="inlineStr"/>
-      <c r="AD110" s="8" t="inlineStr"/>
-      <c r="AE110" s="10" t="inlineStr"/>
-      <c r="AF110" s="11" t="inlineStr"/>
-      <c r="AG110" s="12" t="inlineStr"/>
+      <c r="AC110" s="10" t="inlineStr"/>
+      <c r="AD110" s="11" t="inlineStr"/>
+      <c r="AE110" s="12" t="inlineStr"/>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="1" t="n"/>
@@ -7880,7 +7634,11 @@
           <t>1885.00</t>
         </is>
       </c>
-      <c r="Q111" s="8" t="inlineStr"/>
+      <c r="Q111" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="R111" s="8" t="inlineStr"/>
       <c r="S111" s="8" t="inlineStr"/>
       <c r="T111" s="8" t="inlineStr"/>
@@ -7892,15 +7650,13 @@
       <c r="Z111" s="8" t="inlineStr"/>
       <c r="AA111" s="8" t="inlineStr"/>
       <c r="AB111" s="8" t="inlineStr"/>
-      <c r="AC111" s="8" t="inlineStr"/>
-      <c r="AD111" s="8" t="inlineStr"/>
-      <c r="AE111" s="10" t="n">
+      <c r="AC111" s="10" t="n">
         <v>2007.166666666667</v>
       </c>
-      <c r="AF111" s="10" t="n">
+      <c r="AD111" s="10" t="n">
         <v>33.5</v>
       </c>
-      <c r="AG111" s="12" t="n">
+      <c r="AE111" s="12" t="n">
         <v>0.005041915626928344</v>
       </c>
     </row>
@@ -7945,11 +7701,9 @@
       <c r="Z112" s="8" t="inlineStr"/>
       <c r="AA112" s="8" t="inlineStr"/>
       <c r="AB112" s="8" t="inlineStr"/>
-      <c r="AC112" s="8" t="inlineStr"/>
-      <c r="AD112" s="8" t="inlineStr"/>
-      <c r="AE112" s="10" t="inlineStr"/>
-      <c r="AF112" s="11" t="inlineStr"/>
-      <c r="AG112" s="12" t="inlineStr"/>
+      <c r="AC112" s="10" t="inlineStr"/>
+      <c r="AD112" s="11" t="inlineStr"/>
+      <c r="AE112" s="12" t="inlineStr"/>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="1" t="n"/>
@@ -7992,11 +7746,9 @@
       <c r="Z113" s="8" t="inlineStr"/>
       <c r="AA113" s="8" t="inlineStr"/>
       <c r="AB113" s="8" t="inlineStr"/>
-      <c r="AC113" s="8" t="inlineStr"/>
-      <c r="AD113" s="8" t="inlineStr"/>
-      <c r="AE113" s="10" t="inlineStr"/>
-      <c r="AF113" s="11" t="inlineStr"/>
-      <c r="AG113" s="12" t="inlineStr"/>
+      <c r="AC113" s="10" t="inlineStr"/>
+      <c r="AD113" s="11" t="inlineStr"/>
+      <c r="AE113" s="12" t="inlineStr"/>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -8037,13 +7789,11 @@
       <c r="Z114" s="4" t="inlineStr"/>
       <c r="AA114" s="4" t="inlineStr"/>
       <c r="AB114" s="4" t="inlineStr"/>
-      <c r="AC114" s="4" t="inlineStr"/>
-      <c r="AD114" s="4" t="inlineStr"/>
-      <c r="AE114" s="5" t="inlineStr"/>
-      <c r="AF114" s="6" t="n">
+      <c r="AC114" s="5" t="inlineStr"/>
+      <c r="AD114" s="6" t="n">
         <v>-5.4</v>
       </c>
-      <c r="AG114" s="7" t="n">
+      <c r="AE114" s="7" t="n">
         <v>-0.1529745042492918</v>
       </c>
     </row>
@@ -8068,7 +7818,11 @@
       </c>
       <c r="G115" s="8" t="inlineStr"/>
       <c r="H115" s="8" t="inlineStr"/>
-      <c r="I115" s="8" t="inlineStr"/>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="J115" s="8" t="inlineStr"/>
       <c r="K115" s="8" t="inlineStr">
         <is>
@@ -8096,13 +7850,11 @@
       <c r="Z115" s="8" t="inlineStr"/>
       <c r="AA115" s="8" t="inlineStr"/>
       <c r="AB115" s="8" t="inlineStr"/>
-      <c r="AC115" s="8" t="inlineStr"/>
-      <c r="AD115" s="8" t="inlineStr"/>
-      <c r="AE115" s="10" t="n">
+      <c r="AC115" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="AF115" s="11" t="inlineStr"/>
-      <c r="AG115" s="12" t="inlineStr"/>
+      <c r="AD115" s="11" t="inlineStr"/>
+      <c r="AE115" s="12" t="inlineStr"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="1" t="n"/>
@@ -8151,21 +7903,19 @@
       <c r="X116" s="8" t="inlineStr"/>
       <c r="Y116" s="8" t="inlineStr"/>
       <c r="Z116" s="8" t="inlineStr"/>
-      <c r="AA116" s="8" t="inlineStr"/>
+      <c r="AA116" s="17" t="inlineStr">
+        <is>
+          <t>16.30</t>
+        </is>
+      </c>
       <c r="AB116" s="8" t="inlineStr"/>
-      <c r="AC116" s="16" t="inlineStr">
-        <is>
-          <t>16.30</t>
-        </is>
-      </c>
-      <c r="AD116" s="8" t="inlineStr"/>
-      <c r="AE116" s="10" t="n">
+      <c r="AC116" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="AF116" s="10" t="n">
+      <c r="AD116" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="AG116" s="12" t="n">
+      <c r="AE116" s="12" t="n">
         <v>0.09631728045325781</v>
       </c>
     </row>
@@ -8206,11 +7956,9 @@
       <c r="Z117" s="8" t="inlineStr"/>
       <c r="AA117" s="8" t="inlineStr"/>
       <c r="AB117" s="8" t="inlineStr"/>
-      <c r="AC117" s="8" t="inlineStr"/>
-      <c r="AD117" s="8" t="inlineStr"/>
-      <c r="AE117" s="10" t="inlineStr"/>
-      <c r="AF117" s="11" t="inlineStr"/>
-      <c r="AG117" s="12" t="inlineStr"/>
+      <c r="AC117" s="10" t="inlineStr"/>
+      <c r="AD117" s="11" t="inlineStr"/>
+      <c r="AE117" s="12" t="inlineStr"/>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -8251,13 +7999,11 @@
       <c r="Z118" s="4" t="inlineStr"/>
       <c r="AA118" s="4" t="inlineStr"/>
       <c r="AB118" s="4" t="inlineStr"/>
-      <c r="AC118" s="4" t="inlineStr"/>
-      <c r="AD118" s="4" t="inlineStr"/>
-      <c r="AE118" s="5" t="inlineStr"/>
-      <c r="AF118" s="6" t="n">
+      <c r="AC118" s="5" t="inlineStr"/>
+      <c r="AD118" s="6" t="n">
         <v>-6778.35</v>
       </c>
-      <c r="AG118" s="7" t="n">
+      <c r="AE118" s="7" t="n">
         <v>-0.09746514557187719</v>
       </c>
     </row>
@@ -8312,19 +8058,17 @@
       <c r="X119" s="8" t="inlineStr"/>
       <c r="Y119" s="8" t="inlineStr"/>
       <c r="Z119" s="8" t="inlineStr"/>
-      <c r="AA119" s="8" t="inlineStr"/>
+      <c r="AA119" s="8" t="inlineStr">
+        <is>
+          <t>159.50</t>
+        </is>
+      </c>
       <c r="AB119" s="8" t="inlineStr"/>
-      <c r="AC119" s="8" t="inlineStr">
-        <is>
-          <t>159.50</t>
-        </is>
-      </c>
-      <c r="AD119" s="8" t="inlineStr"/>
-      <c r="AE119" s="10" t="n">
+      <c r="AC119" s="10" t="n">
         <v>1002.65</v>
       </c>
-      <c r="AF119" s="11" t="inlineStr"/>
-      <c r="AG119" s="12" t="inlineStr"/>
+      <c r="AD119" s="11" t="inlineStr"/>
+      <c r="AE119" s="12" t="inlineStr"/>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="1" t="n"/>
@@ -8377,21 +8121,19 @@
       <c r="X120" s="8" t="inlineStr"/>
       <c r="Y120" s="8" t="inlineStr"/>
       <c r="Z120" s="8" t="inlineStr"/>
-      <c r="AA120" s="8" t="inlineStr"/>
+      <c r="AA120" s="8" t="inlineStr">
+        <is>
+          <t>153.20</t>
+        </is>
+      </c>
       <c r="AB120" s="8" t="inlineStr"/>
-      <c r="AC120" s="8" t="inlineStr">
-        <is>
-          <t>153.20</t>
-        </is>
-      </c>
-      <c r="AD120" s="8" t="inlineStr"/>
-      <c r="AE120" s="10" t="n">
+      <c r="AC120" s="10" t="n">
         <v>152.9875</v>
       </c>
-      <c r="AF120" s="10" t="n">
+      <c r="AD120" s="10" t="n">
         <v>849.6624999999999</v>
       </c>
-      <c r="AG120" s="12" t="n">
+      <c r="AE120" s="12" t="n">
         <v>-0.01221720319096315</v>
       </c>
     </row>
@@ -8434,13 +8176,11 @@
       <c r="Z121" s="4" t="inlineStr"/>
       <c r="AA121" s="4" t="inlineStr"/>
       <c r="AB121" s="4" t="inlineStr"/>
-      <c r="AC121" s="4" t="inlineStr"/>
-      <c r="AD121" s="4" t="inlineStr"/>
-      <c r="AE121" s="5" t="inlineStr"/>
-      <c r="AF121" s="6" t="n">
+      <c r="AC121" s="5" t="inlineStr"/>
+      <c r="AD121" s="6" t="n">
         <v>-1662.9375</v>
       </c>
-      <c r="AG121" s="7" t="n">
+      <c r="AE121" s="7" t="n">
         <v>-0.1251166193919239</v>
       </c>
     </row>
@@ -8497,13 +8237,11 @@
       <c r="Z122" s="8" t="inlineStr"/>
       <c r="AA122" s="8" t="inlineStr"/>
       <c r="AB122" s="8" t="inlineStr"/>
-      <c r="AC122" s="8" t="inlineStr"/>
-      <c r="AD122" s="8" t="inlineStr"/>
-      <c r="AE122" s="10" t="n">
+      <c r="AC122" s="10" t="n">
         <v>2859.0625</v>
       </c>
-      <c r="AF122" s="11" t="inlineStr"/>
-      <c r="AG122" s="12" t="inlineStr"/>
+      <c r="AD122" s="11" t="inlineStr"/>
+      <c r="AE122" s="12" t="inlineStr"/>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="1" t="n"/>
@@ -8554,11 +8292,9 @@
       <c r="Z123" s="8" t="inlineStr"/>
       <c r="AA123" s="8" t="inlineStr"/>
       <c r="AB123" s="8" t="inlineStr"/>
-      <c r="AC123" s="8" t="inlineStr"/>
-      <c r="AD123" s="8" t="inlineStr"/>
-      <c r="AE123" s="10" t="inlineStr"/>
-      <c r="AF123" s="11" t="inlineStr"/>
-      <c r="AG123" s="12" t="inlineStr"/>
+      <c r="AC123" s="10" t="inlineStr"/>
+      <c r="AD123" s="11" t="inlineStr"/>
+      <c r="AE123" s="12" t="inlineStr"/>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="1" t="n"/>
@@ -8617,15 +8353,13 @@
       <c r="Z124" s="8" t="inlineStr"/>
       <c r="AA124" s="8" t="inlineStr"/>
       <c r="AB124" s="8" t="inlineStr"/>
-      <c r="AC124" s="8" t="inlineStr"/>
-      <c r="AD124" s="8" t="inlineStr"/>
-      <c r="AE124" s="10" t="n">
+      <c r="AC124" s="10" t="n">
         <v>3065.625</v>
       </c>
-      <c r="AF124" s="10" t="n">
+      <c r="AD124" s="10" t="n">
         <v>206.5625</v>
       </c>
-      <c r="AG124" s="12" t="n">
+      <c r="AE124" s="12" t="n">
         <v>0.01554141493179646</v>
       </c>
     </row>
@@ -8668,13 +8402,11 @@
       <c r="Z125" s="4" t="inlineStr"/>
       <c r="AA125" s="4" t="inlineStr"/>
       <c r="AB125" s="4" t="inlineStr"/>
-      <c r="AC125" s="4" t="inlineStr"/>
-      <c r="AD125" s="4" t="inlineStr"/>
-      <c r="AE125" s="5" t="inlineStr"/>
-      <c r="AF125" s="6" t="n">
+      <c r="AC125" s="5" t="inlineStr"/>
+      <c r="AD125" s="6" t="n">
         <v>-5012.333333333334</v>
       </c>
-      <c r="AG125" s="7" t="n">
+      <c r="AE125" s="7" t="n">
         <v>-0.6398587264100765</v>
       </c>
     </row>
@@ -8721,7 +8453,7 @@
           <t>17810.00</t>
         </is>
       </c>
-      <c r="S126" s="17" t="inlineStr">
+      <c r="S126" s="16" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
@@ -8735,13 +8467,11 @@
       <c r="Z126" s="8" t="inlineStr"/>
       <c r="AA126" s="8" t="inlineStr"/>
       <c r="AB126" s="8" t="inlineStr"/>
-      <c r="AC126" s="8" t="inlineStr"/>
-      <c r="AD126" s="8" t="inlineStr"/>
-      <c r="AE126" s="10" t="n">
+      <c r="AC126" s="10" t="n">
         <v>12551.66666666667</v>
       </c>
-      <c r="AF126" s="11" t="inlineStr"/>
-      <c r="AG126" s="12" t="inlineStr"/>
+      <c r="AD126" s="11" t="inlineStr"/>
+      <c r="AE126" s="12" t="inlineStr"/>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="1" t="n"/>
@@ -8788,11 +8518,9 @@
       <c r="Z127" s="8" t="inlineStr"/>
       <c r="AA127" s="8" t="inlineStr"/>
       <c r="AB127" s="8" t="inlineStr"/>
-      <c r="AC127" s="8" t="inlineStr"/>
-      <c r="AD127" s="8" t="inlineStr"/>
-      <c r="AE127" s="10" t="inlineStr"/>
-      <c r="AF127" s="11" t="inlineStr"/>
-      <c r="AG127" s="12" t="inlineStr"/>
+      <c r="AC127" s="10" t="inlineStr"/>
+      <c r="AD127" s="11" t="inlineStr"/>
+      <c r="AE127" s="12" t="inlineStr"/>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="1" t="n"/>
@@ -8832,12 +8560,12 @@
           <t>16980.00</t>
         </is>
       </c>
-      <c r="R128" s="16" t="inlineStr">
+      <c r="R128" s="17" t="inlineStr">
         <is>
           <t>16410.00</t>
         </is>
       </c>
-      <c r="S128" s="16" t="inlineStr">
+      <c r="S128" s="17" t="inlineStr">
         <is>
           <t>18865.00</t>
         </is>
@@ -8847,11 +8575,7 @@
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="U128" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="U128" s="8" t="inlineStr"/>
       <c r="V128" s="8" t="inlineStr"/>
       <c r="W128" s="8" t="inlineStr"/>
       <c r="X128" s="8" t="inlineStr"/>
@@ -8859,19 +8583,13 @@
       <c r="Z128" s="8" t="inlineStr"/>
       <c r="AA128" s="8" t="inlineStr"/>
       <c r="AB128" s="8" t="inlineStr"/>
-      <c r="AC128" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
-      <c r="AD128" s="8" t="inlineStr"/>
-      <c r="AE128" s="10" t="n">
+      <c r="AC128" s="10" t="n">
         <v>15426.66666666667</v>
       </c>
-      <c r="AF128" s="10" t="n">
+      <c r="AD128" s="10" t="n">
         <v>2875</v>
       </c>
-      <c r="AG128" s="12" t="n">
+      <c r="AE128" s="12" t="n">
         <v>0.3670134677985575</v>
       </c>
     </row>
@@ -8914,13 +8632,11 @@
       <c r="Z129" s="4" t="inlineStr"/>
       <c r="AA129" s="4" t="inlineStr"/>
       <c r="AB129" s="4" t="inlineStr"/>
-      <c r="AC129" s="4" t="inlineStr"/>
-      <c r="AD129" s="4" t="inlineStr"/>
-      <c r="AE129" s="5" t="inlineStr"/>
-      <c r="AF129" s="6" t="n">
+      <c r="AC129" s="5" t="inlineStr"/>
+      <c r="AD129" s="6" t="n">
         <v>-64.33333333333331</v>
       </c>
-      <c r="AG129" s="7" t="n">
+      <c r="AE129" s="7" t="n">
         <v>-0.001532245835744834</v>
       </c>
     </row>
@@ -8967,19 +8683,17 @@
       <c r="X130" s="8" t="inlineStr"/>
       <c r="Y130" s="8" t="inlineStr"/>
       <c r="Z130" s="8" t="inlineStr"/>
-      <c r="AA130" s="8" t="inlineStr"/>
+      <c r="AA130" s="8" t="inlineStr">
+        <is>
+          <t>470.00</t>
+        </is>
+      </c>
       <c r="AB130" s="8" t="inlineStr"/>
-      <c r="AC130" s="8" t="inlineStr">
-        <is>
-          <t>470.00</t>
-        </is>
-      </c>
-      <c r="AD130" s="8" t="inlineStr"/>
-      <c r="AE130" s="10" t="n">
+      <c r="AC130" s="10" t="n">
         <v>460.6666666666667</v>
       </c>
-      <c r="AF130" s="11" t="inlineStr"/>
-      <c r="AG130" s="12" t="inlineStr"/>
+      <c r="AD130" s="11" t="inlineStr"/>
+      <c r="AE130" s="12" t="inlineStr"/>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="1" t="n"/>
@@ -9016,17 +8730,15 @@
       <c r="X131" s="8" t="inlineStr"/>
       <c r="Y131" s="8" t="inlineStr"/>
       <c r="Z131" s="8" t="inlineStr"/>
-      <c r="AA131" s="8" t="inlineStr"/>
+      <c r="AA131" s="8" t="inlineStr">
+        <is>
+          <t>557.00</t>
+        </is>
+      </c>
       <c r="AB131" s="8" t="inlineStr"/>
-      <c r="AC131" s="8" t="inlineStr">
-        <is>
-          <t>557.00</t>
-        </is>
-      </c>
-      <c r="AD131" s="8" t="inlineStr"/>
-      <c r="AE131" s="10" t="inlineStr"/>
-      <c r="AF131" s="11" t="inlineStr"/>
-      <c r="AG131" s="12" t="inlineStr"/>
+      <c r="AC131" s="10" t="inlineStr"/>
+      <c r="AD131" s="11" t="inlineStr"/>
+      <c r="AE131" s="12" t="inlineStr"/>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="1" t="n"/>
@@ -9035,7 +8747,11 @@
           <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
-      <c r="C132" s="8" t="inlineStr"/>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="D132" s="8" t="inlineStr"/>
       <c r="E132" s="8" t="inlineStr"/>
       <c r="F132" s="8" t="inlineStr"/>
@@ -9067,21 +8783,19 @@
       <c r="X132" s="8" t="inlineStr"/>
       <c r="Y132" s="8" t="inlineStr"/>
       <c r="Z132" s="8" t="inlineStr"/>
-      <c r="AA132" s="8" t="inlineStr"/>
+      <c r="AA132" s="8" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
       <c r="AB132" s="8" t="inlineStr"/>
-      <c r="AC132" s="8" t="inlineStr">
-        <is>
-          <t>545.00</t>
-        </is>
-      </c>
-      <c r="AD132" s="8" t="inlineStr"/>
-      <c r="AE132" s="10" t="n">
+      <c r="AC132" s="10" t="n">
         <v>505.3333333333333</v>
       </c>
-      <c r="AF132" s="10" t="n">
+      <c r="AD132" s="10" t="n">
         <v>44.66666666666663</v>
       </c>
-      <c r="AG132" s="12" t="n">
+      <c r="AE132" s="12" t="n">
         <v>0.001063839077667397</v>
       </c>
     </row>
@@ -9116,17 +8830,15 @@
       <c r="X133" s="8" t="inlineStr"/>
       <c r="Y133" s="8" t="inlineStr"/>
       <c r="Z133" s="8" t="inlineStr"/>
-      <c r="AA133" s="8" t="inlineStr"/>
+      <c r="AA133" s="8" t="inlineStr">
+        <is>
+          <t>411.00</t>
+        </is>
+      </c>
       <c r="AB133" s="8" t="inlineStr"/>
-      <c r="AC133" s="8" t="inlineStr">
-        <is>
-          <t>411.00</t>
-        </is>
-      </c>
-      <c r="AD133" s="8" t="inlineStr"/>
-      <c r="AE133" s="10" t="inlineStr"/>
-      <c r="AF133" s="11" t="inlineStr"/>
-      <c r="AG133" s="12" t="inlineStr"/>
+      <c r="AC133" s="10" t="inlineStr"/>
+      <c r="AD133" s="11" t="inlineStr"/>
+      <c r="AE133" s="12" t="inlineStr"/>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="1" t="n"/>
@@ -9159,17 +8871,15 @@
       <c r="X134" s="8" t="inlineStr"/>
       <c r="Y134" s="8" t="inlineStr"/>
       <c r="Z134" s="8" t="inlineStr"/>
-      <c r="AA134" s="8" t="inlineStr"/>
+      <c r="AA134" s="8" t="inlineStr">
+        <is>
+          <t>415.00</t>
+        </is>
+      </c>
       <c r="AB134" s="8" t="inlineStr"/>
-      <c r="AC134" s="8" t="inlineStr">
-        <is>
-          <t>415.00</t>
-        </is>
-      </c>
-      <c r="AD134" s="8" t="inlineStr"/>
-      <c r="AE134" s="10" t="inlineStr"/>
-      <c r="AF134" s="11" t="inlineStr"/>
-      <c r="AG134" s="12" t="inlineStr"/>
+      <c r="AC134" s="10" t="inlineStr"/>
+      <c r="AD134" s="11" t="inlineStr"/>
+      <c r="AE134" s="12" t="inlineStr"/>
     </row>
     <row r="135" ht="24" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
@@ -9210,13 +8920,11 @@
       <c r="Z135" s="4" t="inlineStr"/>
       <c r="AA135" s="4" t="inlineStr"/>
       <c r="AB135" s="4" t="inlineStr"/>
-      <c r="AC135" s="4" t="inlineStr"/>
-      <c r="AD135" s="4" t="inlineStr"/>
-      <c r="AE135" s="5" t="inlineStr"/>
-      <c r="AF135" s="6" t="n">
+      <c r="AC135" s="5" t="inlineStr"/>
+      <c r="AD135" s="6" t="n">
         <v>-2053.75</v>
       </c>
-      <c r="AG135" s="7" t="n">
+      <c r="AE135" s="7" t="n">
         <v>-0.1840310758257316</v>
       </c>
     </row>
@@ -9262,7 +8970,11 @@
           <t>3203.50, 3308.00, 3088.00, 3095.00</t>
         </is>
       </c>
-      <c r="R136" s="8" t="inlineStr"/>
+      <c r="R136" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="S136" s="8" t="inlineStr"/>
       <c r="T136" s="8" t="inlineStr"/>
       <c r="U136" s="8" t="inlineStr"/>
@@ -9273,13 +8985,11 @@
       <c r="Z136" s="8" t="inlineStr"/>
       <c r="AA136" s="8" t="inlineStr"/>
       <c r="AB136" s="8" t="inlineStr"/>
-      <c r="AC136" s="8" t="inlineStr"/>
-      <c r="AD136" s="8" t="inlineStr"/>
-      <c r="AE136" s="10" t="n">
+      <c r="AC136" s="10" t="n">
         <v>5931.25</v>
       </c>
-      <c r="AF136" s="11" t="inlineStr"/>
-      <c r="AG136" s="12" t="inlineStr"/>
+      <c r="AD136" s="11" t="inlineStr"/>
+      <c r="AE136" s="12" t="inlineStr"/>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="1" t="n"/>
@@ -9326,11 +9036,9 @@
       <c r="Z137" s="8" t="inlineStr"/>
       <c r="AA137" s="8" t="inlineStr"/>
       <c r="AB137" s="8" t="inlineStr"/>
-      <c r="AC137" s="8" t="inlineStr"/>
-      <c r="AD137" s="8" t="inlineStr"/>
-      <c r="AE137" s="10" t="inlineStr"/>
-      <c r="AF137" s="11" t="inlineStr"/>
-      <c r="AG137" s="12" t="inlineStr"/>
+      <c r="AC137" s="10" t="inlineStr"/>
+      <c r="AD137" s="11" t="inlineStr"/>
+      <c r="AE137" s="12" t="inlineStr"/>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="1" t="n"/>
@@ -9366,7 +9074,7 @@
           <t>2974.50</t>
         </is>
       </c>
-      <c r="R138" s="16" t="inlineStr">
+      <c r="R138" s="17" t="inlineStr">
         <is>
           <t>7972.50</t>
         </is>
@@ -9379,21 +9087,19 @@
       <c r="X138" s="8" t="inlineStr"/>
       <c r="Y138" s="8" t="inlineStr"/>
       <c r="Z138" s="8" t="inlineStr"/>
-      <c r="AA138" s="8" t="inlineStr"/>
+      <c r="AA138" s="15" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="AB138" s="8" t="inlineStr"/>
-      <c r="AC138" s="15" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="AD138" s="8" t="inlineStr"/>
-      <c r="AE138" s="10" t="n">
+      <c r="AC138" s="10" t="n">
         <v>6350.5</v>
       </c>
-      <c r="AF138" s="10" t="n">
+      <c r="AD138" s="10" t="n">
         <v>419.25</v>
       </c>
-      <c r="AG138" s="12" t="n">
+      <c r="AE138" s="12" t="n">
         <v>0.03756787756052975</v>
       </c>
     </row>

--- a/results/converted_results.xlsx
+++ b/results/converted_results.xlsx
@@ -632,46 +632,40 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O45" authorId="0" shapeId="0">
+    <comment ref="D46" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Breakout, seed 2
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="D47" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Breakout, seed 2
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="O47" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
 job_queue_A6000.txt:5
-python -u train.py -n "Breakout-6000" -seed 6000 -config_path "config_files/STORM.yaml" -env_name "ALE/Breakout-v5" -trajectory_path "D_TRAJ/Breakout.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
-      </text>
-    </comment>
-    <comment ref="D46" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Breakout, seed 2
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="D47" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Breakout, seed 2
-STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.
+python -u train.py -n "Breakout-6000" -seed 6000 -config_path "config_files/STORM.yaml" -env_name "ALE/Breakout-v5" -trajectory_path "D_TRAJ/Breakout.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="O47" authorId="0" shapeId="0">
+    <comment ref="O57" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="S57" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:5
-python -u train.py -n "Breakout-6000" -seed 6000 -config_path "config_files/STORM.yaml" -env_name "ALE/Breakout-v5" -trajectory_path "D_TRAJ/Breakout.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
-      </text>
-    </comment>
-    <comment ref="L57" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_3090.txt:1
-python -u train.py -n "CrazyClimber-2010" -seed 2010 -config_path "config_files/STORM.yaml" -env_name "ALE/CrazyClimber-v5" -trajectory_path "D_TRAJ/CrazyClimber.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+job_queue_A6000.txt:6
+python -u train.py -n "CrazyClimber-6040" -seed 6040 -config_path "config_files/STORM.yaml" -env_name "ALE/CrazyClimber-v5" -trajectory_path "D_TRAJ/CrazyClimber.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="O57" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
     <comment ref="C67" authorId="0" shapeId="0">
@@ -933,7 +927,7 @@
     <comment ref="T81" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:8
+job_queue_A6000.txt:9
 python -u train.py -n "Gopher-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/Gopher-v5" -trajectory_path "D_TRAJ/Gopher.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1139,7 +1133,7 @@
     <comment ref="S97" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:6
+job_queue_A6000.txt:7
 python -u train.py -n "Kangaroo-6040" -seed 6040 -config_path "config_files/STORM.yaml" -env_name "ALE/Kangaroo-v5" -trajectory_path "D_TRAJ/Kangaroo.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1147,7 +1141,7 @@
     <comment ref="T97" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:9
+job_queue_A6000.txt:10
 python -u train.py -n "Kangaroo-6050" -seed 6050 -config_path "config_files/STORM.yaml" -env_name "ALE/Kangaroo-v5" -trajectory_path "D_TRAJ/Kangaroo.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1259,44 +1253,52 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="AA103" authorId="0" shapeId="0">
+    <comment ref="L105" authorId="0" shapeId="0">
+      <text>
+        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA105" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
 job_queue_titan.txt:3
-python -u train.py -n "KungFuMaster-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/KungFuMaster-v5" -trajectory_path "D_TRAJ/KungFuMaster.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
-      </text>
-    </comment>
-    <comment ref="L105" authorId="0" shapeId="0">
-      <text>
-        <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="AA105" authorId="0" shapeId="0">
+python -u train.py -n "KungFuMaster-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/KungFuMaster-v5" -trajectory_path "D_TRAJ/KungFuMaster.pkl" JointTrainAgent.Retrieval.enable "['retrieval']" JointTrainAgent.Retrieval.save_warmup True
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="Q109" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_titan.txt:3
-python -u train.py -n "KungFuMaster-9999" -seed 9999 -config_path "config_files/STORM.yaml" -env_name "ALE/KungFuMaster-v5" -trajectory_path "D_TRAJ/KungFuMaster.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
-      </text>
-    </comment>
-    <comment ref="Q109" authorId="0" shapeId="0">
+job_queue_A6000.txt:8
+python -u train.py -n "MsPacman-6020" -seed 6020 -config_path "config_files/STORM.yaml" -env_name "ALE/MsPacman-v5" -trajectory_path "D_TRAJ/MsPacman.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline', 'target1']"</t>
+      </text>
+    </comment>
+    <comment ref="L110" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:7
-python -u train.py -n "MsPacman-6020" -seed 6020 -config_path "config_files/STORM.yaml" -env_name "ALE/MsPacman-v5" -trajectory_path "D_TRAJ/MsPacman.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
+job_queue_3090.txt:1
+python -u train.py -n "MsPacman-2010" -seed 2010 -config_path "config_files/STORM.yaml" -env_name "ALE/MsPacman-v5" -trajectory_path "D_TRAJ/MsPacman.pkl" JointTrainAgent.Retrieval.enable "['target1']"</t>
+      </text>
+    </comment>
+    <comment ref="Q110" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_A6000.txt:8
+python -u train.py -n "MsPacman-6020" -seed 6020 -config_path "config_files/STORM.yaml" -env_name "ALE/MsPacman-v5" -trajectory_path "D_TRAJ/MsPacman.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline', 'target1']"</t>
       </text>
     </comment>
     <comment ref="Q111" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:7
-python -u train.py -n "MsPacman-6020" -seed 6020 -config_path "config_files/STORM.yaml" -env_name "ALE/MsPacman-v5" -trajectory_path "D_TRAJ/MsPacman.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline']"</t>
+job_queue_A6000.txt:8
+python -u train.py -n "MsPacman-6020" -seed 6020 -config_path "config_files/STORM.yaml" -env_name "ALE/MsPacman-v5" -trajectory_path "D_TRAJ/MsPacman.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'baseline', 'target1']"</t>
       </text>
     </comment>
     <comment ref="I115" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
 job_queue_pro6k.txt:2
-python -u train.py -n "Pong-3710" -seed 3710 -config_path "config_files/STORM.yaml" -env_name "ALE/Pong-v5" -trajectory_path "D_TRAJ/Pong.pkl" JointTrainAgent.Retrieval.enable "['baseline']"</t>
+python -u train.py -n "Pong-3710" -seed 3710 -config_path "config_files/STORM.yaml" -env_name "ALE/Pong-v5" -trajectory_path "D_TRAJ/Pong.pkl" JointTrainAgent.Retrieval.enable "['baseline', 'target1', 'value', 'add']"</t>
       </text>
     </comment>
     <comment ref="L115" authorId="0" shapeId="0">
@@ -1306,6 +1308,21 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="AA115" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_titan.txt:2
+python -u train.py --resume_warmup ckpt/Pong-9999_Shared JointTrainAgent.Retrieval.enable "['baseline', 'target1', 'add', 'value']"
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="I116" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:2
+python -u train.py -n "Pong-3710" -seed 3710 -config_path "config_files/STORM.yaml" -env_name "ALE/Pong-v5" -trajectory_path "D_TRAJ/Pong.pkl" JointTrainAgent.Retrieval.enable "['baseline', 'target1', 'value', 'add']"</t>
+      </text>
+    </comment>
     <comment ref="L116" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Pong, seed 2010
@@ -1315,38 +1332,90 @@
     </comment>
     <comment ref="AA116" authorId="0" shapeId="0">
       <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_titan.txt:2
+python -u train.py --resume_warmup ckpt/Pong-9999_Shared JointTrainAgent.Retrieval.enable "['baseline', 'target1', 'add', 'value']"
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="L117" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Pong, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA117" authorId="0" shapeId="0">
+      <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="L117" authorId="0" shapeId="0">
+    <comment ref="I118" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:2
+python -u train.py -n "Pong-3710" -seed 3710 -config_path "config_files/STORM.yaml" -env_name "ALE/Pong-v5" -trajectory_path "D_TRAJ/Pong.pkl" JointTrainAgent.Retrieval.enable "['baseline', 'target1', 'value', 'add']"</t>
+      </text>
+    </comment>
+    <comment ref="L118" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Pong, seed 2010
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O119" authorId="0" shapeId="0">
+    <comment ref="AA118" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_titan.txt:2
+python -u train.py --resume_warmup ckpt/Pong-9999_Shared JointTrainAgent.Retrieval.enable "['baseline', 'target1', 'add', 'value']"
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="I119" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:2
+python -u train.py -n "Pong-3710" -seed 3710 -config_path "config_files/STORM.yaml" -env_name "ALE/Pong-v5" -trajectory_path "D_TRAJ/Pong.pkl" JointTrainAgent.Retrieval.enable "['baseline', 'target1', 'value', 'add']"</t>
+      </text>
+    </comment>
+    <comment ref="L119" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Pong, seed 2010
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="AA119" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_titan.txt:2
+python -u train.py --resume_warmup ckpt/Pong-9999_Shared JointTrainAgent.Retrieval.enable "['baseline', 'target1', 'add', 'value']"
+초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="O121" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R119" authorId="0" shapeId="0">
+    <comment ref="R121" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O120" authorId="0" shapeId="0">
+    <comment ref="O122" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R120" authorId="0" shapeId="0">
+    <comment ref="R122" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: PrivateEye, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -1354,42 +1423,42 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="I122" authorId="0" shapeId="0">
+    <comment ref="I124" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R122" authorId="0" shapeId="0">
+    <comment ref="R124" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I123" authorId="0" shapeId="0">
+    <comment ref="I125" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R123" authorId="0" shapeId="0">
+    <comment ref="R125" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="I124" authorId="0" shapeId="0">
+    <comment ref="I126" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 3710
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R124" authorId="0" shapeId="0">
+    <comment ref="R126" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Qbert, seed 6030
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -1397,111 +1466,167 @@
 초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="K126" authorId="0" shapeId="0">
+    <comment ref="E127" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:4
+python -u train.py -n "Qbert-10" -seed 10 -config_path "config_files/STORM.yaml" -env_name "ALE/Qbert-v5" -trajectory_path "D_TRAJ/Qbert.pkl" JointTrainAgent.Retrieval.enable "['value', 'add']"</t>
+      </text>
+    </comment>
+    <comment ref="I127" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R127" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="E128" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:4
+python -u train.py -n "Qbert-10" -seed 10 -config_path "config_files/STORM.yaml" -env_name "ALE/Qbert-v5" -trajectory_path "D_TRAJ/Qbert.pkl" JointTrainAgent.Retrieval.enable "['value', 'add']"</t>
+      </text>
+    </comment>
+    <comment ref="I128" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 3710
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="R128" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Qbert, seed 6030
+STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K130" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O126" authorId="0" shapeId="0">
+    <comment ref="O130" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="S126" authorId="0" shapeId="0">
-      <text>
-        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
-job_queue_A6000.txt:2
-python -u train.py --resume_warmup ckpt/RoadRunner-6040_Shared/shared_warmup_50507 -n RoadRunner-6040 -seed 6040 JointTrainAgent.Retrieval.enable "['baseline']"</t>
-      </text>
-    </comment>
-    <comment ref="K127" authorId="0" shapeId="0">
+    <comment ref="K131" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O127" authorId="0" shapeId="0">
+    <comment ref="O131" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K128" authorId="0" shapeId="0">
+    <comment ref="K132" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 2000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O128" authorId="0" shapeId="0">
+    <comment ref="O132" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: RoadRunner, seed 6000
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R128" authorId="0" shapeId="0">
+    <comment ref="R132" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="S128" authorId="0" shapeId="0">
+    <comment ref="S132" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="T128" authorId="0" shapeId="0">
+    <comment ref="T132" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="C132" authorId="0" shapeId="0">
+    <comment ref="C135" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
 job_queue_pro6k.txt:3
-python -u train.py -n "Seaquest-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Seaquest-v5" -trajectory_path "D_TRAJ/Seaquest.pkl" JointTrainAgent.Retrieval.enable "['retrieval']"</t>
-      </text>
-    </comment>
-    <comment ref="Q136" authorId="0" shapeId="0">
+python -u train.py -n "Seaquest-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Seaquest-v5" -trajectory_path "D_TRAJ/Seaquest.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'target1', 'value', 'add']"</t>
+      </text>
+    </comment>
+    <comment ref="C136" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:3
+python -u train.py -n "Seaquest-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Seaquest-v5" -trajectory_path "D_TRAJ/Seaquest.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'target1', 'value', 'add']"</t>
+      </text>
+    </comment>
+    <comment ref="C137" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:3
+python -u train.py -n "Seaquest-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Seaquest-v5" -trajectory_path "D_TRAJ/Seaquest.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'target1', 'value', 'add']"</t>
+      </text>
+    </comment>
+    <comment ref="C138" authorId="0" shapeId="0">
+      <text>
+        <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
+job_queue_pro6k.txt:3
+python -u train.py -n "Seaquest-1" -seed 1 -config_path "config_files/STORM.yaml" -env_name "ALE/Seaquest-v5" -trajectory_path "D_TRAJ/Seaquest.pkl" JointTrainAgent.Retrieval.enable "['retrieval', 'target1', 'value', 'add']"</t>
+      </text>
+    </comment>
+    <comment ref="Q140" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R136" authorId="0" shapeId="0">
+    <comment ref="R140" authorId="0" shapeId="0">
       <text>
         <t>QUEUED (파란색): 엑셀 생성 시 현재 job queue에 남아 있는 예정 실험입니다. RUNNING과 함께 있으면 실행 중을 뜻하는 노란색을 우선합니다. 기존 점수는 유지하며 대기 표시는 점수 집계에 포함하지 않습니다.
 job_queue_A6000.txt:4
-python -u train.py -n "UpNDown-6030" -seed 6030 -config_path "config_files/STORM.yaml" -env_name "ALE/UpNDown-v5" -trajectory_path "D_TRAJ/UpNDown.pkl" JointTrainAgent.Retrieval.enable "['baseline']"</t>
-      </text>
-    </comment>
-    <comment ref="Q137" authorId="0" shapeId="0">
+python -u train.py --resume_warmup ckpt/UpNDown-6030_Shared JointTrainAgent.Retrieval.enable "['baseline']"</t>
+      </text>
+    </comment>
+    <comment ref="Q141" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="Q138" authorId="0" shapeId="0">
+    <comment ref="Q142" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: UpNDown, seed 6020
 STORM/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="R138" authorId="0" shapeId="0">
+    <comment ref="R142" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
     </comment>
-    <comment ref="AA138" authorId="0" shapeId="0">
+    <comment ref="AA142" authorId="0" shapeId="0">
       <text>
         <t>초록색 테두리: 이 셀에 표시된 run 중 config 또는 실행 인자에서 JointTrainAgent.Retrieval.save_warmup=True인 run이 있습니다. 자식 분기는 재저장을 방지하기 위해 최종 config가 False일 수 있습니다.</t>
       </text>
@@ -1799,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE138"/>
+  <dimension ref="A1:AE142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
@@ -4192,11 +4317,7 @@
       <c r="L45" s="8" t="inlineStr"/>
       <c r="M45" s="8" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
-      <c r="O45" s="16" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="O45" s="8" t="inlineStr"/>
       <c r="P45" s="8" t="inlineStr"/>
       <c r="Q45" s="8" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
@@ -4300,7 +4421,7 @@
       <c r="L47" s="8" t="inlineStr"/>
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
-      <c r="O47" s="16" t="inlineStr">
+      <c r="O47" s="14" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
@@ -4803,11 +4924,7 @@
           <t>63275.00</t>
         </is>
       </c>
-      <c r="L57" s="14" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="L57" s="8" t="inlineStr"/>
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
       <c r="O57" s="15" t="inlineStr">
@@ -4818,7 +4935,11 @@
       <c r="P57" s="8" t="inlineStr"/>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
-      <c r="S57" s="8" t="inlineStr"/>
+      <c r="S57" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="T57" s="8" t="inlineStr"/>
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr"/>
@@ -7256,11 +7377,7 @@
       <c r="X103" s="8" t="inlineStr"/>
       <c r="Y103" s="8" t="inlineStr"/>
       <c r="Z103" s="8" t="inlineStr"/>
-      <c r="AA103" s="16" t="inlineStr">
-        <is>
-          <t>QUEUED</t>
-        </is>
-      </c>
+      <c r="AA103" s="8" t="inlineStr"/>
       <c r="AB103" s="8" t="inlineStr"/>
       <c r="AC103" s="10" t="n">
         <v>25137.5</v>
@@ -7352,7 +7469,7 @@
       <c r="X105" s="8" t="inlineStr"/>
       <c r="Y105" s="8" t="inlineStr"/>
       <c r="Z105" s="8" t="inlineStr"/>
-      <c r="AA105" s="16" t="inlineStr">
+      <c r="AA105" s="14" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
@@ -7576,7 +7693,11 @@
       <c r="I110" s="8" t="inlineStr"/>
       <c r="J110" s="8" t="inlineStr"/>
       <c r="K110" s="8" t="inlineStr"/>
-      <c r="L110" s="8" t="inlineStr"/>
+      <c r="L110" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="M110" s="8" t="inlineStr"/>
       <c r="N110" s="8" t="inlineStr"/>
       <c r="O110" s="8" t="inlineStr">
@@ -7585,7 +7706,11 @@
         </is>
       </c>
       <c r="P110" s="8" t="inlineStr"/>
-      <c r="Q110" s="8" t="inlineStr"/>
+      <c r="Q110" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="R110" s="8" t="inlineStr"/>
       <c r="S110" s="8" t="inlineStr"/>
       <c r="T110" s="8" t="inlineStr"/>
@@ -7848,7 +7973,11 @@
       <c r="X115" s="8" t="inlineStr"/>
       <c r="Y115" s="8" t="inlineStr"/>
       <c r="Z115" s="8" t="inlineStr"/>
-      <c r="AA115" s="8" t="inlineStr"/>
+      <c r="AA115" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="AB115" s="8" t="inlineStr"/>
       <c r="AC115" s="10" t="n">
         <v>5.6</v>
@@ -7860,35 +7989,23 @@
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>target: 1 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr"/>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr"/>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t>8.20</t>
-        </is>
-      </c>
+      <c r="F116" s="8" t="inlineStr"/>
       <c r="G116" s="8" t="inlineStr"/>
       <c r="H116" s="8" t="inlineStr"/>
-      <c r="I116" s="8" t="inlineStr">
-        <is>
-          <t>14.45</t>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr"/>
-      <c r="K116" s="8" t="inlineStr">
-        <is>
-          <t>9.80</t>
-        </is>
-      </c>
-      <c r="L116" s="9" t="inlineStr">
-        <is>
-          <t>-19.90</t>
-        </is>
-      </c>
+      <c r="K116" s="8" t="inlineStr"/>
+      <c r="L116" s="9" t="inlineStr"/>
       <c r="M116" s="8" t="inlineStr"/>
       <c r="N116" s="8" t="inlineStr"/>
       <c r="O116" s="8" t="inlineStr"/>
@@ -7903,41 +8020,47 @@
       <c r="X116" s="8" t="inlineStr"/>
       <c r="Y116" s="8" t="inlineStr"/>
       <c r="Z116" s="8" t="inlineStr"/>
-      <c r="AA116" s="17" t="inlineStr">
-        <is>
-          <t>16.30</t>
+      <c r="AA116" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
         </is>
       </c>
       <c r="AB116" s="8" t="inlineStr"/>
-      <c r="AC116" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD116" s="10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE116" s="12" t="n">
-        <v>0.09631728045325781</v>
-      </c>
+      <c r="AC116" s="10" t="inlineStr"/>
+      <c r="AD116" s="11" t="inlineStr"/>
+      <c r="AE116" s="12" t="inlineStr"/>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정) [value]</t>
+          <t>target: 16 (anchor 미설정)</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr"/>
       <c r="D117" s="8" t="inlineStr"/>
       <c r="E117" s="8" t="inlineStr"/>
-      <c r="F117" s="8" t="inlineStr"/>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>8.20</t>
+        </is>
+      </c>
       <c r="G117" s="8" t="inlineStr"/>
       <c r="H117" s="8" t="inlineStr"/>
-      <c r="I117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
       <c r="J117" s="8" t="inlineStr"/>
-      <c r="K117" s="8" t="inlineStr"/>
+      <c r="K117" s="8" t="inlineStr">
+        <is>
+          <t>9.80</t>
+        </is>
+      </c>
       <c r="L117" s="9" t="inlineStr">
         <is>
-          <t>-20.40</t>
+          <t>-19.90</t>
         </is>
       </c>
       <c r="M117" s="8" t="inlineStr"/>
@@ -7954,102 +8077,98 @@
       <c r="X117" s="8" t="inlineStr"/>
       <c r="Y117" s="8" t="inlineStr"/>
       <c r="Z117" s="8" t="inlineStr"/>
-      <c r="AA117" s="8" t="inlineStr"/>
+      <c r="AA117" s="17" t="inlineStr">
+        <is>
+          <t>16.30</t>
+        </is>
+      </c>
       <c r="AB117" s="8" t="inlineStr"/>
-      <c r="AC117" s="10" t="inlineStr"/>
-      <c r="AD117" s="11" t="inlineStr"/>
-      <c r="AE117" s="12" t="inlineStr"/>
+      <c r="AC117" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD117" s="10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE117" s="12" t="n">
+        <v>0.09631728045325781</v>
+      </c>
     </row>
     <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>PrivateEye
-Random: 24.9
-Human: 69571.3</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 7781</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr"/>
-      <c r="D118" s="4" t="inlineStr"/>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
-      <c r="G118" s="4" t="inlineStr"/>
-      <c r="H118" s="4" t="inlineStr"/>
-      <c r="I118" s="4" t="inlineStr"/>
-      <c r="J118" s="4" t="inlineStr"/>
-      <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="4" t="inlineStr"/>
-      <c r="M118" s="4" t="inlineStr"/>
-      <c r="N118" s="4" t="inlineStr"/>
-      <c r="O118" s="4" t="inlineStr"/>
-      <c r="P118" s="4" t="inlineStr"/>
-      <c r="Q118" s="4" t="inlineStr"/>
-      <c r="R118" s="4" t="inlineStr"/>
-      <c r="S118" s="4" t="inlineStr"/>
-      <c r="T118" s="4" t="inlineStr"/>
-      <c r="U118" s="4" t="inlineStr"/>
-      <c r="V118" s="4" t="inlineStr"/>
-      <c r="W118" s="4" t="inlineStr"/>
-      <c r="X118" s="4" t="inlineStr"/>
-      <c r="Y118" s="4" t="inlineStr"/>
-      <c r="Z118" s="4" t="inlineStr"/>
-      <c r="AA118" s="4" t="inlineStr"/>
-      <c r="AB118" s="4" t="inlineStr"/>
-      <c r="AC118" s="5" t="inlineStr"/>
-      <c r="AD118" s="6" t="n">
-        <v>-6778.35</v>
-      </c>
-      <c r="AE118" s="7" t="n">
-        <v>-0.09746514557187719</v>
-      </c>
+      <c r="A118" s="1" t="n"/>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>target: 16 (anchor 미설정) [value]</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr"/>
+      <c r="D118" s="8" t="inlineStr"/>
+      <c r="E118" s="8" t="inlineStr"/>
+      <c r="F118" s="8" t="inlineStr"/>
+      <c r="G118" s="8" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr"/>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="J118" s="8" t="inlineStr"/>
+      <c r="K118" s="8" t="inlineStr"/>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>-20.40</t>
+        </is>
+      </c>
+      <c r="M118" s="8" t="inlineStr"/>
+      <c r="N118" s="8" t="inlineStr"/>
+      <c r="O118" s="8" t="inlineStr"/>
+      <c r="P118" s="8" t="inlineStr"/>
+      <c r="Q118" s="8" t="inlineStr"/>
+      <c r="R118" s="8" t="inlineStr"/>
+      <c r="S118" s="8" t="inlineStr"/>
+      <c r="T118" s="8" t="inlineStr"/>
+      <c r="U118" s="8" t="inlineStr"/>
+      <c r="V118" s="8" t="inlineStr"/>
+      <c r="W118" s="8" t="inlineStr"/>
+      <c r="X118" s="8" t="inlineStr"/>
+      <c r="Y118" s="8" t="inlineStr"/>
+      <c r="Z118" s="8" t="inlineStr"/>
+      <c r="AA118" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="AB118" s="8" t="inlineStr"/>
+      <c r="AC118" s="10" t="inlineStr"/>
+      <c r="AD118" s="11" t="inlineStr"/>
+      <c r="AE118" s="12" t="inlineStr"/>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>75.30</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정) [add]</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr"/>
       <c r="D119" s="8" t="inlineStr"/>
       <c r="E119" s="8" t="inlineStr"/>
       <c r="F119" s="8" t="inlineStr"/>
       <c r="G119" s="8" t="inlineStr"/>
       <c r="H119" s="8" t="inlineStr"/>
-      <c r="I119" s="8" t="inlineStr"/>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
       <c r="J119" s="8" t="inlineStr"/>
-      <c r="K119" s="8" t="inlineStr">
-        <is>
-          <t>199.35</t>
-        </is>
-      </c>
-      <c r="L119" s="8" t="inlineStr"/>
+      <c r="K119" s="8" t="inlineStr"/>
+      <c r="L119" s="9" t="inlineStr"/>
       <c r="M119" s="8" t="inlineStr"/>
       <c r="N119" s="8" t="inlineStr"/>
-      <c r="O119" s="9" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="P119" s="8" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="Q119" s="8" t="inlineStr">
-        <is>
-          <t>3551.75</t>
-        </is>
-      </c>
-      <c r="R119" s="9" t="inlineStr"/>
+      <c r="O119" s="8" t="inlineStr"/>
+      <c r="P119" s="8" t="inlineStr"/>
+      <c r="Q119" s="8" t="inlineStr"/>
+      <c r="R119" s="8" t="inlineStr"/>
       <c r="S119" s="8" t="inlineStr"/>
       <c r="T119" s="8" t="inlineStr"/>
       <c r="U119" s="8" t="inlineStr"/>
@@ -8058,175 +8177,169 @@
       <c r="X119" s="8" t="inlineStr"/>
       <c r="Y119" s="8" t="inlineStr"/>
       <c r="Z119" s="8" t="inlineStr"/>
-      <c r="AA119" s="8" t="inlineStr">
-        <is>
-          <t>159.50</t>
+      <c r="AA119" s="14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
         </is>
       </c>
       <c r="AB119" s="8" t="inlineStr"/>
-      <c r="AC119" s="10" t="n">
-        <v>1002.65</v>
-      </c>
+      <c r="AC119" s="10" t="inlineStr"/>
       <c r="AD119" s="11" t="inlineStr"/>
       <c r="AE119" s="12" t="inlineStr"/>
     </row>
     <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="1" t="n"/>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>target: 16 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr"/>
-      <c r="D120" s="8" t="inlineStr"/>
-      <c r="E120" s="8" t="inlineStr"/>
-      <c r="F120" s="8" t="inlineStr"/>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="8" t="inlineStr"/>
-      <c r="I120" s="8" t="inlineStr"/>
-      <c r="J120" s="8" t="inlineStr"/>
-      <c r="K120" s="8" t="inlineStr">
-        <is>
-          <t>191.95</t>
-        </is>
-      </c>
-      <c r="L120" s="8" t="inlineStr"/>
-      <c r="M120" s="8" t="inlineStr"/>
-      <c r="N120" s="8" t="inlineStr"/>
-      <c r="O120" s="9" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="P120" s="8" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>PrivateEye
+Random: 24.9
+Human: 69571.3</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 7781</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr"/>
+      <c r="D120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
+      <c r="G120" s="4" t="inlineStr"/>
+      <c r="H120" s="4" t="inlineStr"/>
+      <c r="I120" s="4" t="inlineStr"/>
+      <c r="J120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr"/>
+      <c r="L120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr"/>
+      <c r="N120" s="4" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr"/>
+      <c r="P120" s="4" t="inlineStr"/>
+      <c r="Q120" s="4" t="inlineStr"/>
+      <c r="R120" s="4" t="inlineStr"/>
+      <c r="S120" s="4" t="inlineStr"/>
+      <c r="T120" s="4" t="inlineStr"/>
+      <c r="U120" s="4" t="inlineStr"/>
+      <c r="V120" s="4" t="inlineStr"/>
+      <c r="W120" s="4" t="inlineStr"/>
+      <c r="X120" s="4" t="inlineStr"/>
+      <c r="Y120" s="4" t="inlineStr"/>
+      <c r="Z120" s="4" t="inlineStr"/>
+      <c r="AA120" s="4" t="inlineStr"/>
+      <c r="AB120" s="4" t="inlineStr"/>
+      <c r="AC120" s="5" t="inlineStr"/>
+      <c r="AD120" s="6" t="n">
+        <v>-6778.35</v>
+      </c>
+      <c r="AE120" s="7" t="n">
+        <v>-0.09746514557187719</v>
+      </c>
+    </row>
+    <row r="121" ht="24" customHeight="1">
+      <c r="A121" s="1" t="n"/>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval 미사용</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>75.30</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr"/>
+      <c r="E121" s="8" t="inlineStr"/>
+      <c r="F121" s="8" t="inlineStr"/>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr"/>
+      <c r="I121" s="8" t="inlineStr"/>
+      <c r="J121" s="8" t="inlineStr"/>
+      <c r="K121" s="8" t="inlineStr">
+        <is>
+          <t>199.35</t>
+        </is>
+      </c>
+      <c r="L121" s="8" t="inlineStr"/>
+      <c r="M121" s="8" t="inlineStr"/>
+      <c r="N121" s="8" t="inlineStr"/>
+      <c r="O121" s="9" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="Q120" s="8" t="inlineStr">
-        <is>
-          <t>166.80</t>
-        </is>
-      </c>
-      <c r="R120" s="13" t="inlineStr">
+      <c r="P121" s="8" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="S120" s="8" t="inlineStr"/>
-      <c r="T120" s="8" t="inlineStr"/>
-      <c r="U120" s="8" t="inlineStr"/>
-      <c r="V120" s="8" t="inlineStr"/>
-      <c r="W120" s="8" t="inlineStr"/>
-      <c r="X120" s="8" t="inlineStr"/>
-      <c r="Y120" s="8" t="inlineStr"/>
-      <c r="Z120" s="8" t="inlineStr"/>
-      <c r="AA120" s="8" t="inlineStr">
-        <is>
-          <t>153.20</t>
-        </is>
-      </c>
-      <c r="AB120" s="8" t="inlineStr"/>
-      <c r="AC120" s="10" t="n">
-        <v>152.9875</v>
-      </c>
-      <c r="AD120" s="10" t="n">
-        <v>849.6624999999999</v>
-      </c>
-      <c r="AE120" s="12" t="n">
-        <v>-0.01221720319096315</v>
-      </c>
-    </row>
-    <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Qbert
-Random: 163.9
-Human: 13455.0</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>STORM (논문): 4522</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr"/>
-      <c r="D121" s="4" t="inlineStr"/>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="4" t="inlineStr"/>
-      <c r="H121" s="4" t="inlineStr"/>
-      <c r="I121" s="4" t="inlineStr"/>
-      <c r="J121" s="4" t="inlineStr"/>
-      <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="4" t="inlineStr"/>
-      <c r="M121" s="4" t="inlineStr"/>
-      <c r="N121" s="4" t="inlineStr"/>
-      <c r="O121" s="4" t="inlineStr"/>
-      <c r="P121" s="4" t="inlineStr"/>
-      <c r="Q121" s="4" t="inlineStr"/>
-      <c r="R121" s="4" t="inlineStr"/>
-      <c r="S121" s="4" t="inlineStr"/>
-      <c r="T121" s="4" t="inlineStr"/>
-      <c r="U121" s="4" t="inlineStr"/>
-      <c r="V121" s="4" t="inlineStr"/>
-      <c r="W121" s="4" t="inlineStr"/>
-      <c r="X121" s="4" t="inlineStr"/>
-      <c r="Y121" s="4" t="inlineStr"/>
-      <c r="Z121" s="4" t="inlineStr"/>
-      <c r="AA121" s="4" t="inlineStr"/>
-      <c r="AB121" s="4" t="inlineStr"/>
-      <c r="AC121" s="5" t="inlineStr"/>
-      <c r="AD121" s="6" t="n">
-        <v>-1662.9375</v>
-      </c>
-      <c r="AE121" s="7" t="n">
-        <v>-0.1251166193919239</v>
-      </c>
+      <c r="Q121" s="8" t="inlineStr">
+        <is>
+          <t>3551.75</t>
+        </is>
+      </c>
+      <c r="R121" s="9" t="inlineStr"/>
+      <c r="S121" s="8" t="inlineStr"/>
+      <c r="T121" s="8" t="inlineStr"/>
+      <c r="U121" s="8" t="inlineStr"/>
+      <c r="V121" s="8" t="inlineStr"/>
+      <c r="W121" s="8" t="inlineStr"/>
+      <c r="X121" s="8" t="inlineStr"/>
+      <c r="Y121" s="8" t="inlineStr"/>
+      <c r="Z121" s="8" t="inlineStr"/>
+      <c r="AA121" s="8" t="inlineStr">
+        <is>
+          <t>159.50</t>
+        </is>
+      </c>
+      <c r="AB121" s="8" t="inlineStr"/>
+      <c r="AC121" s="10" t="n">
+        <v>1002.65</v>
+      </c>
+      <c r="AD121" s="11" t="inlineStr"/>
+      <c r="AE121" s="12" t="inlineStr"/>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Retrieval 미사용</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t>1771.25</t>
-        </is>
-      </c>
+          <t>target: 16 (anchor 미설정)</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr"/>
       <c r="D122" s="8" t="inlineStr"/>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>3786.25</t>
-        </is>
-      </c>
+      <c r="E122" s="8" t="inlineStr"/>
       <c r="F122" s="8" t="inlineStr"/>
       <c r="G122" s="8" t="inlineStr"/>
       <c r="H122" s="8" t="inlineStr"/>
-      <c r="I122" s="9" t="inlineStr">
-        <is>
-          <t>2940.00</t>
-        </is>
-      </c>
+      <c r="I122" s="8" t="inlineStr"/>
       <c r="J122" s="8" t="inlineStr"/>
       <c r="K122" s="8" t="inlineStr">
         <is>
-          <t>3193.75</t>
+          <t>191.95</t>
         </is>
       </c>
       <c r="L122" s="8" t="inlineStr"/>
       <c r="M122" s="8" t="inlineStr"/>
       <c r="N122" s="8" t="inlineStr"/>
-      <c r="O122" s="8" t="inlineStr">
-        <is>
-          <t>2685.00, 3401.25, 3125.00, 3095.00</t>
-        </is>
-      </c>
-      <c r="P122" s="8" t="inlineStr"/>
-      <c r="Q122" s="8" t="inlineStr"/>
-      <c r="R122" s="9" t="inlineStr"/>
+      <c r="O122" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="P122" s="8" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="Q122" s="8" t="inlineStr">
+        <is>
+          <t>166.80</t>
+        </is>
+      </c>
+      <c r="R122" s="13" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
       <c r="S122" s="8" t="inlineStr"/>
       <c r="T122" s="8" t="inlineStr"/>
       <c r="U122" s="8" t="inlineStr"/>
@@ -8235,83 +8348,85 @@
       <c r="X122" s="8" t="inlineStr"/>
       <c r="Y122" s="8" t="inlineStr"/>
       <c r="Z122" s="8" t="inlineStr"/>
-      <c r="AA122" s="8" t="inlineStr"/>
+      <c r="AA122" s="8" t="inlineStr">
+        <is>
+          <t>153.20</t>
+        </is>
+      </c>
       <c r="AB122" s="8" t="inlineStr"/>
       <c r="AC122" s="10" t="n">
-        <v>2859.0625</v>
-      </c>
-      <c r="AD122" s="11" t="inlineStr"/>
-      <c r="AE122" s="12" t="inlineStr"/>
+        <v>152.9875</v>
+      </c>
+      <c r="AD122" s="10" t="n">
+        <v>849.6624999999999</v>
+      </c>
+      <c r="AE122" s="12" t="n">
+        <v>-0.01221720319096315</v>
+      </c>
     </row>
     <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="1" t="n"/>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>target: 1 (anchor 미설정)</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>2818.75</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr"/>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t>1918.75</t>
-        </is>
-      </c>
-      <c r="F123" s="8" t="inlineStr"/>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="8" t="inlineStr"/>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>2553.75</t>
-        </is>
-      </c>
-      <c r="J123" s="8" t="inlineStr"/>
-      <c r="K123" s="8" t="inlineStr"/>
-      <c r="L123" s="8" t="inlineStr"/>
-      <c r="M123" s="8" t="inlineStr"/>
-      <c r="N123" s="8" t="inlineStr"/>
-      <c r="O123" s="8" t="inlineStr">
-        <is>
-          <t>3782.50</t>
-        </is>
-      </c>
-      <c r="P123" s="8" t="inlineStr"/>
-      <c r="Q123" s="8" t="inlineStr"/>
-      <c r="R123" s="9" t="inlineStr"/>
-      <c r="S123" s="8" t="inlineStr"/>
-      <c r="T123" s="8" t="inlineStr"/>
-      <c r="U123" s="8" t="inlineStr"/>
-      <c r="V123" s="8" t="inlineStr"/>
-      <c r="W123" s="8" t="inlineStr"/>
-      <c r="X123" s="8" t="inlineStr"/>
-      <c r="Y123" s="8" t="inlineStr"/>
-      <c r="Z123" s="8" t="inlineStr"/>
-      <c r="AA123" s="8" t="inlineStr"/>
-      <c r="AB123" s="8" t="inlineStr"/>
-      <c r="AC123" s="10" t="inlineStr"/>
-      <c r="AD123" s="11" t="inlineStr"/>
-      <c r="AE123" s="12" t="inlineStr"/>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Qbert
+Random: 163.9
+Human: 13455.0</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>STORM (논문): 4522</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr"/>
+      <c r="D123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
+      <c r="G123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" s="4" t="inlineStr"/>
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr"/>
+      <c r="L123" s="4" t="inlineStr"/>
+      <c r="M123" s="4" t="inlineStr"/>
+      <c r="N123" s="4" t="inlineStr"/>
+      <c r="O123" s="4" t="inlineStr"/>
+      <c r="P123" s="4" t="inlineStr"/>
+      <c r="Q123" s="4" t="inlineStr"/>
+      <c r="R123" s="4" t="inlineStr"/>
+      <c r="S123" s="4" t="inlineStr"/>
+      <c r="T123" s="4" t="inlineStr"/>
+      <c r="U123" s="4" t="inlineStr"/>
+      <c r="V123" s="4" t="inlineStr"/>
+      <c r="W123" s="4" t="inlineStr"/>
+      <c r="X123" s="4" t="inlineStr"/>
+      <c r="Y123" s="4" t="inlineStr"/>
+      <c r="Z123" s="4" t="inlineStr"/>
+      <c r="AA123" s="4" t="inlineStr"/>
+      <c r="AB123" s="4" t="inlineStr"/>
+      <c r="AC123" s="5" t="inlineStr"/>
+      <c r="AD123" s="6" t="n">
+        <v>-1662.9375</v>
+      </c>
+      <c r="AE123" s="7" t="n">
+        <v>-0.1251166193919239</v>
+      </c>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="1" t="n"/>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>target: 16 (anchor 미설정)</t>
+          <t>Retrieval 미사용</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>2702.50</t>
+          <t>1771.25</t>
         </is>
       </